--- a/data/PST.MI.xlsx
+++ b/data/PST.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2060" uniqueCount="2060">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2061" uniqueCount="2061">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,97 +38,97 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">3.90457582473755</t>
+    <t xml:space="preserve">3.90457558631897</t>
   </si>
   <si>
     <t xml:space="preserve">PST.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">4.03631544113159</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.97464966773987</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95222640037537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9157874584198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87934827804565</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.97184777259827</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.01949834823608</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99707412719727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94662070274353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.82889437675476</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.75601673126221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.54859399795532</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.68594169616699</t>
+    <t xml:space="preserve">4.03631639480591</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97465038299561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95222663879395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.91578793525696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87934899330139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97184729576111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.01949787139893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99707508087158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94661951065063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.82889461517334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.75601601600647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.54859471321106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.68594121932983</t>
   </si>
   <si>
     <t xml:space="preserve">3.73359251022339</t>
   </si>
   <si>
-    <t xml:space="preserve">3.65510821342468</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.76162362098694</t>
+    <t xml:space="preserve">3.65510869026184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.76162266731262</t>
   </si>
   <si>
     <t xml:space="preserve">3.80927348136902</t>
   </si>
   <si>
-    <t xml:space="preserve">3.73078989982605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.82609224319458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.72238087654114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64389681816101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.53177714347839</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.35518860816956</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.00481247901917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.89829897880554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.17019057273865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.03284311294556</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.04405474662781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.13655376434326</t>
+    <t xml:space="preserve">3.73078942298889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.82609105110168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.72238111495972</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64389634132385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.53177690505981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.35518836975098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.00481367111206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.89829921722412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.17018961906433</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.03284406661987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.04405522346497</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13655424118042</t>
   </si>
   <si>
     <t xml:space="preserve">3.12253904342651</t>
@@ -137,16 +137,16 @@
     <t xml:space="preserve">3.24867463111877</t>
   </si>
   <si>
-    <t xml:space="preserve">3.23465919494629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.30473351478577</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.42245936393738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.34677863121033</t>
+    <t xml:space="preserve">3.23465895652771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.3047342300415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.42246007919312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.34677886962891</t>
   </si>
   <si>
     <t xml:space="preserve">3.31314325332642</t>
@@ -155,106 +155,106 @@
     <t xml:space="preserve">3.40844440460205</t>
   </si>
   <si>
-    <t xml:space="preserve">3.45609617233276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.51495838165283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.48412537574768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.45329213142395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.47571682929993</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.43647527694702</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.45889925956726</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.43367099761963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61306381225586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.63829064369202</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.63548755645752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.60745739936829</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.58783674240112</t>
+    <t xml:space="preserve">3.45609569549561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.51495909690857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.48412609100342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.45329260826111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.47571706771851</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.43647480010986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.4588987827301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.43367171287537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61306405067444</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.6382908821106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.6354877948761</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.60745787620544</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.58783745765686</t>
   </si>
   <si>
     <t xml:space="preserve">3.60185194015503</t>
   </si>
   <si>
-    <t xml:space="preserve">3.67192649841309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.79525828361511</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77844071388245</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71397137641907</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.78404664993286</t>
+    <t xml:space="preserve">3.67192697525024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.79525876045227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.7784411907196</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71397185325623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.78404688835144</t>
   </si>
   <si>
     <t xml:space="preserve">3.72798681259155</t>
   </si>
   <si>
-    <t xml:space="preserve">3.67753291130066</t>
+    <t xml:space="preserve">3.67753267288208</t>
   </si>
   <si>
     <t xml:space="preserve">3.61586666107178</t>
   </si>
   <si>
-    <t xml:space="preserve">3.51215600967407</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.56821537017822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.58503341674805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.60465598106384</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.62147259712219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.6999568939209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.63268494606018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.62988090515137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.65791130065918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.62707853317261</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.67472982406616</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.68033576011658</t>
+    <t xml:space="preserve">3.51215553283691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.5682156085968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.58503317832947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.60465502738953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.62147283554077</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.69995713233948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.63268542289734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.62988185882568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.65791153907776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.62707901000977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.67472958564758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.68033528327942</t>
   </si>
   <si>
     <t xml:space="preserve">3.74480485916138</t>
@@ -263,121 +263,121 @@
     <t xml:space="preserve">3.79245567321777</t>
   </si>
   <si>
-    <t xml:space="preserve">3.80086541175842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73919892311096</t>
+    <t xml:space="preserve">3.80086493492126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73919916152954</t>
   </si>
   <si>
     <t xml:space="preserve">3.68313837051392</t>
   </si>
   <si>
-    <t xml:space="preserve">3.76722836494446</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.79806089401245</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77563738822937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.75881958007812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.78684949874878</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.68874502182007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.78965306282043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.74760794639587</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83169794082642</t>
+    <t xml:space="preserve">3.76722812652588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.79806137084961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77563762664795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.75881934165955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.78684997558594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.68874478340149</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.78965353965759</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.74760723114014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.83169674873352</t>
   </si>
   <si>
     <t xml:space="preserve">3.83730316162109</t>
   </si>
   <si>
-    <t xml:space="preserve">3.80647087097168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85972809791565</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85692453384399</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.86813616752625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84571266174316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85412192344666</t>
+    <t xml:space="preserve">3.8064706325531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85972785949707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85692477226257</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.86813640594482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84571313858032</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85412120819092</t>
   </si>
   <si>
     <t xml:space="preserve">3.92419624328613</t>
   </si>
   <si>
-    <t xml:space="preserve">3.93260478973389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84010648727417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.78124308586121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.76442551612854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87654519081116</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96498394012451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.91486811637878</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90602493286133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95024394989014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.63776183128357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.42256188392639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.51394891738892</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.50805282592773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.60533380508423</t>
+    <t xml:space="preserve">3.93260550498962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84010624885559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.78124332427979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.76442623138428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87654542922974</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96498322486877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.91486883163452</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90602469444275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95024371147156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.63776206970215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.42256140708923</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.51394844055176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.50805234909058</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.60533499717712</t>
   </si>
   <si>
     <t xml:space="preserve">3.52574038505554</t>
   </si>
   <si>
-    <t xml:space="preserve">3.43730211257935</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.3989782333374</t>
+    <t xml:space="preserve">3.43730187416077</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.39897847175598</t>
   </si>
   <si>
     <t xml:space="preserve">3.37244701385498</t>
   </si>
   <si>
-    <t xml:space="preserve">3.49920916557312</t>
+    <t xml:space="preserve">3.49920868873596</t>
   </si>
   <si>
     <t xml:space="preserve">3.65839695930481</t>
@@ -386,25 +386,25 @@
     <t xml:space="preserve">3.64955353736877</t>
   </si>
   <si>
-    <t xml:space="preserve">3.7350447177887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.67018890380859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.67313718795776</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.65250182151794</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.70851254463196</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.69672131538391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.6554491519928</t>
+    <t xml:space="preserve">3.73504400253296</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.67019009590149</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.67313694953918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.65250158309937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.7085132598877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.69672107696533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.65545010566711</t>
   </si>
   <si>
     <t xml:space="preserve">3.64660573005676</t>
@@ -413,13 +413,13 @@
     <t xml:space="preserve">3.60238695144653</t>
   </si>
   <si>
-    <t xml:space="preserve">3.58469843864441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.52868819236755</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80284667015076</t>
+    <t xml:space="preserve">3.58469891548157</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.52868890762329</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.80284643173218</t>
   </si>
   <si>
     <t xml:space="preserve">3.78221106529236</t>
@@ -428,103 +428,103 @@
     <t xml:space="preserve">3.80874276161194</t>
   </si>
   <si>
-    <t xml:space="preserve">3.81463813781738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.86770129203796</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87949275970459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.7998993396759</t>
+    <t xml:space="preserve">3.81463885307312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.86770176887512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87949419021606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.79989886283875</t>
   </si>
   <si>
     <t xml:space="preserve">3.72325253486633</t>
   </si>
   <si>
-    <t xml:space="preserve">3.76157641410828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66724109649658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.6819806098938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.74388813972473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.70261693000793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66134524345398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.67903232574463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.62597060203552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.69377255439758</t>
+    <t xml:space="preserve">3.76157569885254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66724181175232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.68198132514954</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.74388766288757</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.70261716842651</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66134548187256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.67903256416321</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.62597012519836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.69377326965332</t>
   </si>
   <si>
     <t xml:space="preserve">3.68492937088013</t>
   </si>
   <si>
-    <t xml:space="preserve">3.70556426048279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71735644340515</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77631521224976</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.76452422142029</t>
+    <t xml:space="preserve">3.70556402206421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71735596656799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77631545066833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.76452350616455</t>
   </si>
   <si>
     <t xml:space="preserve">3.56406354904175</t>
   </si>
   <si>
-    <t xml:space="preserve">3.61712598800659</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61417865753174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.58175110816956</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.59943866729736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.60828280448914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.58764743804932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.57880306243896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.57290768623352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.55816769599915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.56111526489258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.50215625762939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.54637598991394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.56701135635376</t>
+    <t xml:space="preserve">3.61712694168091</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61417841911316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.58175086975098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.59943890571594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.60828256607056</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.58764719963074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.57880258560181</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.57290697097778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.55816745758057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.56111574172974</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.50215649604797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.54637551307678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.56701111793518</t>
   </si>
   <si>
     <t xml:space="preserve">3.51689624786377</t>
@@ -533,34 +533,34 @@
     <t xml:space="preserve">3.57585597038269</t>
   </si>
   <si>
-    <t xml:space="preserve">3.64365768432617</t>
+    <t xml:space="preserve">3.64365816116333</t>
   </si>
   <si>
     <t xml:space="preserve">3.62302231788635</t>
   </si>
   <si>
-    <t xml:space="preserve">3.51100015640259</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.49036502838135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.51984453201294</t>
+    <t xml:space="preserve">3.51100039482117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.49036455154419</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.51984405517578</t>
   </si>
   <si>
     <t xml:space="preserve">3.55227208137512</t>
   </si>
   <si>
-    <t xml:space="preserve">3.54342842102051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.53163623809814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.52279186248779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.47857260704041</t>
+    <t xml:space="preserve">3.54342818260193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.53163695335388</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.52279210090637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.47857284545898</t>
   </si>
   <si>
     <t xml:space="preserve">3.44025015830994</t>
@@ -569,193 +569,193 @@
     <t xml:space="preserve">3.36655139923096</t>
   </si>
   <si>
-    <t xml:space="preserve">3.33117628097534</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.32527995109558</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.31938481330872</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.31054019927979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.2663209438324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.39603066444397</t>
+    <t xml:space="preserve">3.3311767578125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.32528042793274</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.31938433647156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.31053996086121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.26632165908813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.39603114128113</t>
   </si>
   <si>
     <t xml:space="preserve">3.45793747901917</t>
   </si>
   <si>
-    <t xml:space="preserve">3.46088528633118</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.45204210281372</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73209619522095</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.74683618545532</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73799204826355</t>
+    <t xml:space="preserve">3.46088552474976</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.45204186439514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73209643363953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.74683547019958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73799252510071</t>
   </si>
   <si>
     <t xml:space="preserve">3.72914838790894</t>
   </si>
   <si>
-    <t xml:space="preserve">3.77926278114319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.74093961715698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77336764335632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.79105520248413</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.76747155189514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.7144091129303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.63481402397156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.59649109840393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.56995844841003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.59354257583618</t>
+    <t xml:space="preserve">3.7792637348175</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.74093985557556</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.7733678817749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.79105496406555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.76747226715088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71440839767456</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.63481378555298</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.59649133682251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.56995916366577</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.59354305267334</t>
   </si>
   <si>
     <t xml:space="preserve">3.44909358024597</t>
   </si>
   <si>
-    <t xml:space="preserve">3.42845773696899</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.44614577293396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.53753232955933</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.53458380699158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.59059524536133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.69966840744019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.81758689880371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80579543113708</t>
+    <t xml:space="preserve">3.42845797538757</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.44614553451538</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.53753328323364</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.53458428382874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.59059572219849</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.6996693611145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.81758713722229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.80579471588135</t>
   </si>
   <si>
     <t xml:space="preserve">3.79695129394531</t>
   </si>
   <si>
-    <t xml:space="preserve">3.75862765312195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.82937836647034</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.79400300979614</t>
+    <t xml:space="preserve">3.75862741470337</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.82937812805176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.79400324821472</t>
   </si>
   <si>
     <t xml:space="preserve">3.67608571052551</t>
   </si>
   <si>
-    <t xml:space="preserve">3.71146106719971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.74978446960449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77041912078857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.68787693977356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.75273275375366</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83232593536377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84411787986755</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.72030448913574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.69082498550415</t>
+    <t xml:space="preserve">3.71146082878113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.74978399276733</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77041935920715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.6878764629364</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.75273156166077</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.83232617378235</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84411811828613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.72030472755432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.69082450866699</t>
   </si>
   <si>
     <t xml:space="preserve">3.81169080734253</t>
   </si>
   <si>
-    <t xml:space="preserve">3.82053446769714</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.78916716575623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8017144203186</t>
+    <t xml:space="preserve">3.82053470611572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.78916764259338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.80171418190002</t>
   </si>
   <si>
     <t xml:space="preserve">3.81426048278809</t>
   </si>
   <si>
-    <t xml:space="preserve">3.75780010223389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.76407361030579</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77662038803101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73898005485535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.78603076934814</t>
+    <t xml:space="preserve">3.75780081748962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.76407408714294</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77662014961243</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73897981643677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.78603005409241</t>
   </si>
   <si>
     <t xml:space="preserve">3.76093673706055</t>
   </si>
   <si>
-    <t xml:space="preserve">3.76721096038818</t>
+    <t xml:space="preserve">3.76721024513245</t>
   </si>
   <si>
     <t xml:space="preserve">3.74525308609009</t>
   </si>
   <si>
-    <t xml:space="preserve">3.72956919670105</t>
+    <t xml:space="preserve">3.72956967353821</t>
   </si>
   <si>
     <t xml:space="preserve">3.79544115066528</t>
   </si>
   <si>
-    <t xml:space="preserve">3.80485129356384</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84249138832092</t>
+    <t xml:space="preserve">3.80485081672668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8424916267395</t>
   </si>
   <si>
     <t xml:space="preserve">3.82367062568665</t>
@@ -770,46 +770,46 @@
     <t xml:space="preserve">3.75152683258057</t>
   </si>
   <si>
-    <t xml:space="preserve">3.74211597442627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77975726127625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.91463565826416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92718315124512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94600343704224</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.89267897605896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9020893573761</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90522599220276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94286632537842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83308172225952</t>
+    <t xml:space="preserve">3.74211573600769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77975749969482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.91463613510132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92718291282654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94600415229797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89267873764038</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90208911895752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90522694587708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94286680221558</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.83308243751526</t>
   </si>
   <si>
     <t xml:space="preserve">3.84562826156616</t>
   </si>
   <si>
-    <t xml:space="preserve">3.89895343780518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90836262702942</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85817551612854</t>
+    <t xml:space="preserve">3.89895296096802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.908362865448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85817527770996</t>
   </si>
   <si>
     <t xml:space="preserve">3.83935475349426</t>
@@ -818,148 +818,148 @@
     <t xml:space="preserve">3.8299446105957</t>
   </si>
   <si>
-    <t xml:space="preserve">3.85503888130188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.81739854812622</t>
+    <t xml:space="preserve">3.85503911972046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.81739830970764</t>
   </si>
   <si>
     <t xml:space="preserve">3.86131191253662</t>
   </si>
   <si>
-    <t xml:space="preserve">3.92090964317322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8958158493042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88640570640564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8895423412323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.86444807052612</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88013219833374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85190200805664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.873859167099</t>
+    <t xml:space="preserve">3.9209098815918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89581608772278</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88640546798706</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88954186439514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8644483089447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88013195991516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85190176963806</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87385964393616</t>
   </si>
   <si>
     <t xml:space="preserve">3.93031978607178</t>
   </si>
   <si>
-    <t xml:space="preserve">3.8675856590271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93659281730652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94914078712463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93345713615417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9397304058075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92404627799988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84876489639282</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83621740341187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.82680821418762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99305534362793</t>
+    <t xml:space="preserve">3.86758542060852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93659353256226</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94914031028748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93345665931702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93973088264465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92404651641846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84876537322998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8362181186676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8268084526062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99305486679077</t>
   </si>
   <si>
     <t xml:space="preserve">4.02128458023071</t>
   </si>
   <si>
-    <t xml:space="preserve">3.99619174003601</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98364472389221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.97109818458557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98678183555603</t>
+    <t xml:space="preserve">3.99619126319885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.98364520072937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97109699249268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.98678016662598</t>
   </si>
   <si>
     <t xml:space="preserve">3.99932837486267</t>
   </si>
   <si>
-    <t xml:space="preserve">4.01814794540405</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.03383159637451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.04637956619263</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.05892562866211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.04010581970215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.07147216796875</t>
+    <t xml:space="preserve">4.01814889907837</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.03383255004883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.04637861251831</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.05892610549927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.04010629653931</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.07147312164307</t>
   </si>
   <si>
     <t xml:space="preserve">4.10283994674683</t>
   </si>
   <si>
-    <t xml:space="preserve">4.09970378875732</t>
+    <t xml:space="preserve">4.09970331192017</t>
   </si>
   <si>
     <t xml:space="preserve">4.12793350219727</t>
   </si>
   <si>
-    <t xml:space="preserve">4.21889925003052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.21576166152954</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.2000789642334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.1718487739563</t>
+    <t xml:space="preserve">4.21889877319336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.2157621383667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.20007801055908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.17184829711914</t>
   </si>
   <si>
     <t xml:space="preserve">4.18753147125244</t>
   </si>
   <si>
-    <t xml:space="preserve">4.19694185256958</t>
+    <t xml:space="preserve">4.19694137573242</t>
   </si>
   <si>
     <t xml:space="preserve">4.17310285568237</t>
   </si>
   <si>
-    <t xml:space="preserve">4.15553665161133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.18063116073608</t>
+    <t xml:space="preserve">4.15553760528564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.18063068389893</t>
   </si>
   <si>
     <t xml:space="preserve">4.13044309616089</t>
   </si>
   <si>
-    <t xml:space="preserve">4.13922643661499</t>
+    <t xml:space="preserve">4.13922595977783</t>
   </si>
   <si>
     <t xml:space="preserve">4.01501178741455</t>
@@ -983,43 +983,43 @@
     <t xml:space="preserve">4.1291880607605</t>
   </si>
   <si>
-    <t xml:space="preserve">4.17561197280884</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.18188571929932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.2534031867981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.2408561706543</t>
+    <t xml:space="preserve">4.175612449646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.18188524246216</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.25340366363525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.24085664749146</t>
   </si>
   <si>
     <t xml:space="preserve">4.2069787979126</t>
   </si>
   <si>
-    <t xml:space="preserve">4.21074390411377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.17435741424561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.41651344299316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.43031406402588</t>
+    <t xml:space="preserve">4.21074295043945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.17435693740845</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.41651248931885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.43031454086304</t>
   </si>
   <si>
     <t xml:space="preserve">4.40271091461182</t>
   </si>
   <si>
-    <t xml:space="preserve">4.30735540390015</t>
+    <t xml:space="preserve">4.30735492706299</t>
   </si>
   <si>
     <t xml:space="preserve">4.33495807647705</t>
   </si>
   <si>
-    <t xml:space="preserve">4.37134456634521</t>
+    <t xml:space="preserve">4.3713436126709</t>
   </si>
   <si>
     <t xml:space="preserve">4.48677587509155</t>
@@ -1028,61 +1028,61 @@
     <t xml:space="preserve">4.60095262527466</t>
   </si>
   <si>
-    <t xml:space="preserve">4.57711315155029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.65490484237671</t>
+    <t xml:space="preserve">4.57711410522461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.65490436553955</t>
   </si>
   <si>
     <t xml:space="preserve">4.55452871322632</t>
   </si>
   <si>
-    <t xml:space="preserve">4.4955587387085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.56707572937012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.6385931968689</t>
+    <t xml:space="preserve">4.49555778503418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.56707525253296</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.63859272003174</t>
   </si>
   <si>
     <t xml:space="preserve">4.60346126556396</t>
   </si>
   <si>
-    <t xml:space="preserve">4.63482904434204</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.62604713439941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.58338689804077</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.54574537277222</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.52943468093872</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.54449033737183</t>
+    <t xml:space="preserve">4.6348295211792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.62604665756226</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.58338594436646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.54574632644653</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.52943563461304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.54449129104614</t>
   </si>
   <si>
     <t xml:space="preserve">4.61475467681885</t>
   </si>
   <si>
-    <t xml:space="preserve">4.62353658676147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.65866851806641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.73645973205566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.73144006729126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.76782703399658</t>
+    <t xml:space="preserve">4.62353754043579</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.65866947174072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.73645925521851</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.73144054412842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.76782655715942</t>
   </si>
   <si>
     <t xml:space="preserve">4.82052326202393</t>
@@ -1091,19 +1091,19 @@
     <t xml:space="preserve">4.81299543380737</t>
   </si>
   <si>
-    <t xml:space="preserve">4.81675958633423</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.81424951553345</t>
+    <t xml:space="preserve">4.81675910949707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.81424903869629</t>
   </si>
   <si>
     <t xml:space="preserve">4.8431077003479</t>
   </si>
   <si>
-    <t xml:space="preserve">4.88702201843262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.85690975189209</t>
+    <t xml:space="preserve">4.88702249526978</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.85690927505493</t>
   </si>
   <si>
     <t xml:space="preserve">4.86694765090942</t>
@@ -1112,7 +1112,7 @@
     <t xml:space="preserve">4.93720960617065</t>
   </si>
   <si>
-    <t xml:space="preserve">4.9422287940979</t>
+    <t xml:space="preserve">4.94222831726074</t>
   </si>
   <si>
     <t xml:space="preserve">4.96355819702148</t>
@@ -1121,13 +1121,13 @@
     <t xml:space="preserve">4.97359561920166</t>
   </si>
   <si>
-    <t xml:space="preserve">5.00119876861572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.08526277542114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.07146120071411</t>
+    <t xml:space="preserve">5.00119924545288</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.0852632522583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.07146215438843</t>
   </si>
   <si>
     <t xml:space="preserve">5.06267881393433</t>
@@ -1136,7 +1136,7 @@
     <t xml:space="preserve">5.11537647247314</t>
   </si>
   <si>
-    <t xml:space="preserve">5.09153652191162</t>
+    <t xml:space="preserve">5.09153747558594</t>
   </si>
   <si>
     <t xml:space="preserve">5.06769800186157</t>
@@ -1145,37 +1145,37 @@
     <t xml:space="preserve">5.11286640167236</t>
   </si>
   <si>
-    <t xml:space="preserve">5.15552663803101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.96230411529541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.95101165771484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.78037357330322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.79041194915771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.82930612564087</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.8054666519165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.83432579040527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.76029872894287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.60722589492798</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.40020227432251</t>
+    <t xml:space="preserve">5.15552568435669</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.96230316162109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.951012134552</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.78037309646606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.79041147232056</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.82930564880371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.80546760559082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.83432531356812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.76029825210571</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.60722541809082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.40020179748535</t>
   </si>
   <si>
     <t xml:space="preserve">4.584641456604</t>
@@ -1184,196 +1184,196 @@
     <t xml:space="preserve">4.59467887878418</t>
   </si>
   <si>
-    <t xml:space="preserve">4.68627214431763</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.71261978149414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.5884051322937</t>
+    <t xml:space="preserve">4.68627166748047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.7126202583313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.58840560913086</t>
   </si>
   <si>
     <t xml:space="preserve">4.58589601516724</t>
   </si>
   <si>
-    <t xml:space="preserve">4.56833124160767</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.44411611557007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.61600828170776</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.7038369178772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.79292011260986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.90584182739258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.78664636611938</t>
+    <t xml:space="preserve">4.56832981109619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.44411563873291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.61600875854492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.70383739471436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.79292058944702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.90584230422974</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.78664684295654</t>
   </si>
   <si>
     <t xml:space="preserve">4.86100292205811</t>
   </si>
   <si>
-    <t xml:space="preserve">4.91012954711914</t>
+    <t xml:space="preserve">4.91013097763062</t>
   </si>
   <si>
     <t xml:space="preserve">4.93270254135132</t>
   </si>
   <si>
-    <t xml:space="preserve">4.87162399291992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.8769359588623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.81320142745972</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.83577442169189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.76672983169556</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.76009130477905</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.80789136886597</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.81984090805054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.93403005599976</t>
+    <t xml:space="preserve">4.87162446975708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.87693691253662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.81320190429688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.83577394485474</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.7667293548584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.76009082794189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.80789041519165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.81983995437622</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.93403053283691</t>
   </si>
   <si>
     <t xml:space="preserve">4.97253561019897</t>
   </si>
   <si>
-    <t xml:space="preserve">5.01900863647461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.96589660644531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.03892517089844</t>
+    <t xml:space="preserve">5.01900815963745</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.96589708328247</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.03892612457275</t>
   </si>
   <si>
     <t xml:space="preserve">5.02697467803955</t>
   </si>
   <si>
-    <t xml:space="preserve">5.10000324249268</t>
+    <t xml:space="preserve">5.1000018119812</t>
   </si>
   <si>
     <t xml:space="preserve">5.1531138420105</t>
   </si>
   <si>
-    <t xml:space="preserve">5.18099689483643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.12124681472778</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.13452482223511</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.11859178543091</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.12788581848145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.2115364074707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.23410797119141</t>
+    <t xml:space="preserve">5.18099737167358</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.1212477684021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.13452529907227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.11859226226807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.1278862953186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.21153688430786</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.23410892486572</t>
   </si>
   <si>
     <t xml:space="preserve">5.25668096542358</t>
   </si>
   <si>
-    <t xml:space="preserve">5.28854751586914</t>
+    <t xml:space="preserve">5.2885479927063</t>
   </si>
   <si>
     <t xml:space="preserve">5.28058099746704</t>
   </si>
   <si>
-    <t xml:space="preserve">4.99510812759399</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.94465255737305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.92871904373169</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.86896896362305</t>
+    <t xml:space="preserve">4.99510765075684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.94465208053589</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.92871856689453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.86896944046021</t>
   </si>
   <si>
     <t xml:space="preserve">4.71627473831177</t>
   </si>
   <si>
-    <t xml:space="preserve">4.69635772705078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.74548482894897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.60474109649658</t>
+    <t xml:space="preserve">4.69635677337646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.74548530578613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.60474061965942</t>
   </si>
   <si>
     <t xml:space="preserve">4.54764652252197</t>
   </si>
   <si>
-    <t xml:space="preserve">4.4759464263916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.61801862716675</t>
+    <t xml:space="preserve">4.47594594955444</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.61801767349243</t>
   </si>
   <si>
     <t xml:space="preserve">4.52772998809814</t>
   </si>
   <si>
-    <t xml:space="preserve">4.51046800613403</t>
+    <t xml:space="preserve">4.51046895980835</t>
   </si>
   <si>
     <t xml:space="preserve">4.50250148773193</t>
   </si>
   <si>
-    <t xml:space="preserve">4.4852409362793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.50515747070312</t>
+    <t xml:space="preserve">4.48524045944214</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.50515651702881</t>
   </si>
   <si>
     <t xml:space="preserve">4.44673490524292</t>
   </si>
   <si>
-    <t xml:space="preserve">4.40291833877563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.47727346420288</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.59544706344604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.68440818786621</t>
+    <t xml:space="preserve">4.40291881561279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.4772744178772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.59544563293457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.68440771102905</t>
   </si>
   <si>
     <t xml:space="preserve">4.65519666671753</t>
   </si>
   <si>
-    <t xml:space="preserve">4.67378568649292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.78133583068848</t>
+    <t xml:space="preserve">4.67378520965576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.78133535385132</t>
   </si>
   <si>
     <t xml:space="preserve">4.75610780715942</t>
@@ -1385,10 +1385,10 @@
     <t xml:space="preserve">4.56225156784058</t>
   </si>
   <si>
-    <t xml:space="preserve">4.58880758285522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.63262414932251</t>
+    <t xml:space="preserve">4.58880710601807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.63262462615967</t>
   </si>
   <si>
     <t xml:space="preserve">4.61005115509033</t>
@@ -1400,49 +1400,49 @@
     <t xml:space="preserve">4.66050720214844</t>
   </si>
   <si>
-    <t xml:space="preserve">4.69901275634766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.72158527374268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.77735233306885</t>
+    <t xml:space="preserve">4.69901323318481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.72158622741699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.77735185623169</t>
   </si>
   <si>
     <t xml:space="preserve">4.80523586273193</t>
   </si>
   <si>
-    <t xml:space="preserve">4.77336883544922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.56889057159424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.51976251602173</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.4387674331665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.44806241989136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.45204544067383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.38167333602905</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.21968412399292</t>
+    <t xml:space="preserve">4.77336835861206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.56889009475708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.51976299285889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.43876791000366</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.4480619430542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.45204591751099</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.38167381286621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.21968555450439</t>
   </si>
   <si>
     <t xml:space="preserve">4.24225664138794</t>
   </si>
   <si>
-    <t xml:space="preserve">4.28474569320679</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.16657304763794</t>
+    <t xml:space="preserve">4.28474521636963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.1665735244751</t>
   </si>
   <si>
     <t xml:space="preserve">4.14798450469971</t>
@@ -1460,55 +1460,55 @@
     <t xml:space="preserve">4.06300640106201</t>
   </si>
   <si>
-    <t xml:space="preserve">4.16259050369263</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.14001846313477</t>
+    <t xml:space="preserve">4.16259002685547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.14001798629761</t>
   </si>
   <si>
     <t xml:space="preserve">4.14931201934814</t>
   </si>
   <si>
-    <t xml:space="preserve">3.98201274871826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.06831789016724</t>
+    <t xml:space="preserve">3.9820122718811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.06831741333008</t>
   </si>
   <si>
     <t xml:space="preserve">4.07230138778687</t>
   </si>
   <si>
-    <t xml:space="preserve">4.20109605789185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.10815191268921</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.21570158004761</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.34980773925781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.38432931900024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.32325172424316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.29536771774292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.43744039535522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.53038501739502</t>
+    <t xml:space="preserve">4.201096534729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.10815143585205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.21570110321045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.34980630874634</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.38432884216309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.32325124740601</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.29536819458008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.43744087219238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.53038549423218</t>
   </si>
   <si>
     <t xml:space="preserve">4.56092405319214</t>
   </si>
   <si>
-    <t xml:space="preserve">4.57021856307983</t>
+    <t xml:space="preserve">4.57021903991699</t>
   </si>
   <si>
     <t xml:space="preserve">4.57287406921387</t>
@@ -1517,10 +1517,10 @@
     <t xml:space="preserve">4.42681789398193</t>
   </si>
   <si>
-    <t xml:space="preserve">4.31528472900391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.32590627670288</t>
+    <t xml:space="preserve">4.31528520584106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.3259072303772</t>
   </si>
   <si>
     <t xml:space="preserve">4.35113477706909</t>
@@ -1532,13 +1532,13 @@
     <t xml:space="preserve">4.37105131149292</t>
   </si>
   <si>
-    <t xml:space="preserve">4.34847927093506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.54100847244263</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.51710653305054</t>
+    <t xml:space="preserve">4.34847974777222</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.54100751876831</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.51710748672485</t>
   </si>
   <si>
     <t xml:space="preserve">4.44939041137695</t>
@@ -1550,10 +1550,10 @@
     <t xml:space="preserve">4.55826902389526</t>
   </si>
   <si>
-    <t xml:space="preserve">4.5224175453186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.58216857910156</t>
+    <t xml:space="preserve">4.52241706848145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.5821681022644</t>
   </si>
   <si>
     <t xml:space="preserve">4.34051275253296</t>
@@ -1562,13 +1562,13 @@
     <t xml:space="preserve">4.36175727844238</t>
   </si>
   <si>
-    <t xml:space="preserve">4.31130123138428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.35379076004028</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.52905797958374</t>
+    <t xml:space="preserve">4.31130075454712</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.35379028320312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.52905607223511</t>
   </si>
   <si>
     <t xml:space="preserve">4.60075712203979</t>
@@ -1583,13 +1583,13 @@
     <t xml:space="preserve">4.71892976760864</t>
   </si>
   <si>
-    <t xml:space="preserve">4.65386867523193</t>
+    <t xml:space="preserve">4.65386915206909</t>
   </si>
   <si>
     <t xml:space="preserve">4.58615207672119</t>
   </si>
   <si>
-    <t xml:space="preserve">4.5356969833374</t>
+    <t xml:space="preserve">4.53569602966309</t>
   </si>
   <si>
     <t xml:space="preserve">4.63660764694214</t>
@@ -1598,16 +1598,16 @@
     <t xml:space="preserve">4.6273136138916</t>
   </si>
   <si>
-    <t xml:space="preserve">4.64590167999268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.70299673080444</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.67112922668457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.71760225296021</t>
+    <t xml:space="preserve">4.64590215682983</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.70299530029297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.67112970352173</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.71760177612305</t>
   </si>
   <si>
     <t xml:space="preserve">4.78000736236572</t>
@@ -1619,7 +1619,7 @@
     <t xml:space="preserve">4.81452989578247</t>
   </si>
   <si>
-    <t xml:space="preserve">4.79328489303589</t>
+    <t xml:space="preserve">4.79328536987305</t>
   </si>
   <si>
     <t xml:space="preserve">4.88224649429321</t>
@@ -1628,34 +1628,34 @@
     <t xml:space="preserve">4.91278553009033</t>
   </si>
   <si>
-    <t xml:space="preserve">5.03626871109009</t>
+    <t xml:space="preserve">5.0362696647644</t>
   </si>
   <si>
     <t xml:space="preserve">5.0455641746521</t>
   </si>
   <si>
-    <t xml:space="preserve">4.99776268005371</t>
+    <t xml:space="preserve">4.99776315689087</t>
   </si>
   <si>
     <t xml:space="preserve">5.0442361831665</t>
   </si>
   <si>
-    <t xml:space="preserve">5.05618572235107</t>
+    <t xml:space="preserve">5.05618619918823</t>
   </si>
   <si>
     <t xml:space="preserve">5.10664176940918</t>
   </si>
   <si>
-    <t xml:space="preserve">5.08406972885132</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.09203577041626</t>
+    <t xml:space="preserve">5.08406925201416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.09203624725342</t>
   </si>
   <si>
     <t xml:space="preserve">4.98846912384033</t>
   </si>
   <si>
-    <t xml:space="preserve">4.87826347351074</t>
+    <t xml:space="preserve">4.87826299667358</t>
   </si>
   <si>
     <t xml:space="preserve">4.99245262145996</t>
@@ -1664,34 +1664,34 @@
     <t xml:space="preserve">5.07477521896362</t>
   </si>
   <si>
-    <t xml:space="preserve">5.10265779495239</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.94863653182983</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.96456813812256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.02431917190552</t>
+    <t xml:space="preserve">5.10265827178955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.94863510131836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.96456909179688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.02431869506836</t>
   </si>
   <si>
     <t xml:space="preserve">5.09867525100708</t>
   </si>
   <si>
-    <t xml:space="preserve">5.15045881271362</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.08938074111938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.14249086380005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.1610803604126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.1451473236084</t>
+    <t xml:space="preserve">5.15045785903931</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.08938026428223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.14249134063721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.16108083724976</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.14514780044556</t>
   </si>
   <si>
     <t xml:space="preserve">5.13054180145264</t>
@@ -1706,106 +1706,106 @@
     <t xml:space="preserve">5.2434024810791</t>
   </si>
   <si>
-    <t xml:space="preserve">5.24473094940186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.26464748382568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.26863145828247</t>
+    <t xml:space="preserve">5.2447304725647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.26464700698853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.26863098144531</t>
   </si>
   <si>
     <t xml:space="preserve">5.23941993713379</t>
   </si>
   <si>
-    <t xml:space="preserve">5.26331949234009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.27394199371338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.27659702301025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.18630838394165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.24605846405029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.2712869644165</t>
+    <t xml:space="preserve">5.26331901550293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.27394151687622</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.27659749984741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.18630790710449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.24605894088745</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.27128648757935</t>
   </si>
   <si>
     <t xml:space="preserve">5.28456401824951</t>
   </si>
   <si>
-    <t xml:space="preserve">5.30580854415894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.36423063278198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.41070318222046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.55012035369873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.60323143005371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.73468017578125</t>
+    <t xml:space="preserve">5.30580902099609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.36423110961914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.4107027053833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.55011987686157</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.60323095321655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.73468112945557</t>
   </si>
   <si>
     <t xml:space="preserve">5.68289852142334</t>
   </si>
   <si>
-    <t xml:space="preserve">5.70281505584717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.72538805007935</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.72671461105347</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.70679712295532</t>
+    <t xml:space="preserve">5.70281410217285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.72538661956787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.72671604156494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.70679807662964</t>
   </si>
   <si>
     <t xml:space="preserve">5.75725364685059</t>
   </si>
   <si>
-    <t xml:space="preserve">5.74264860153198</t>
+    <t xml:space="preserve">5.74264812469482</t>
   </si>
   <si>
     <t xml:space="preserve">5.75990867614746</t>
   </si>
   <si>
-    <t xml:space="preserve">5.8063817024231</t>
+    <t xml:space="preserve">5.80638217926025</t>
   </si>
   <si>
     <t xml:space="preserve">5.80239820480347</t>
   </si>
   <si>
-    <t xml:space="preserve">5.8249716758728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.92455434799194</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.94579935073853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.93650484085083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.96836996078491</t>
+    <t xml:space="preserve">5.82497072219849</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.92455339431763</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.94579887390137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.93650531768799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.96837091445923</t>
   </si>
   <si>
     <t xml:space="preserve">5.95774841308594</t>
   </si>
   <si>
-    <t xml:space="preserve">6.02148246765137</t>
+    <t xml:space="preserve">6.02148103713989</t>
   </si>
   <si>
     <t xml:space="preserve">5.97633743286133</t>
@@ -1817,25 +1817,25 @@
     <t xml:space="preserve">6.32023286819458</t>
   </si>
   <si>
-    <t xml:space="preserve">6.28172636032104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.14894819259644</t>
+    <t xml:space="preserve">6.28172588348389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.14894914627075</t>
   </si>
   <si>
     <t xml:space="preserve">6.12372064590454</t>
   </si>
   <si>
-    <t xml:space="preserve">6.14230966567993</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.22330522537231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.31359386444092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.26712131500244</t>
+    <t xml:space="preserve">6.14230871200562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.22330474853516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.31359434127808</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.26712083816528</t>
   </si>
   <si>
     <t xml:space="preserve">6.20604276657104</t>
@@ -1850,94 +1850,94 @@
     <t xml:space="preserve">5.98032188415527</t>
   </si>
   <si>
-    <t xml:space="preserve">5.97500944137573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.90596532821655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.08787107467651</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.04936552047729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.12770366668701</t>
+    <t xml:space="preserve">5.97500991821289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.90596437454224</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.08787059783936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.04936599731445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.12770414352417</t>
   </si>
   <si>
     <t xml:space="preserve">5.99094295501709</t>
   </si>
   <si>
-    <t xml:space="preserve">6.04405450820923</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.08255910873413</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.82098627090454</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.92189836502075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.90729284286499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.86082029342651</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.83028173446655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.77584218978882</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.78779220581055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.93517684936523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.89401483535767</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.92588186264038</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.04272556304932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.09982013702393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.12903308868408</t>
+    <t xml:space="preserve">6.04405403137207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.08255958557129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.82098770141602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.92189884185791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.90729236602783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.86082124710083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.83028125762939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.77584266662598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.78779268264771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.93517589569092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.89401531219482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.92588138580322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.04272747039795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.09982061386108</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.12903165817261</t>
   </si>
   <si>
     <t xml:space="preserve">6.15293216705322</t>
   </si>
   <si>
-    <t xml:space="preserve">6.12106513977051</t>
+    <t xml:space="preserve">6.12106609344482</t>
   </si>
   <si>
     <t xml:space="preserve">6.16753768920898</t>
   </si>
   <si>
-    <t xml:space="preserve">6.2219762802124</t>
+    <t xml:space="preserve">6.22197580337524</t>
   </si>
   <si>
     <t xml:space="preserve">6.31624984741211</t>
   </si>
   <si>
-    <t xml:space="preserve">6.42833042144775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.38377618789673</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.35732173919678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.36289215087891</t>
+    <t xml:space="preserve">6.42833089828491</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.38377571105957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.35732269287109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.36289119720459</t>
   </si>
   <si>
     <t xml:space="preserve">6.44643020629883</t>
@@ -1949,67 +1949,67 @@
     <t xml:space="preserve">6.58983898162842</t>
   </si>
   <si>
-    <t xml:space="preserve">6.74577951431274</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.78754901885986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.76248598098755</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.75273990631104</t>
+    <t xml:space="preserve">6.74577856063843</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.78754997253418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.76248645782471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.75274085998535</t>
   </si>
   <si>
     <t xml:space="preserve">6.72071743011475</t>
   </si>
   <si>
-    <t xml:space="preserve">6.78615713119507</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.71932601928711</t>
+    <t xml:space="preserve">6.78615570068359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.71932458877563</t>
   </si>
   <si>
     <t xml:space="preserve">6.72350263595581</t>
   </si>
   <si>
-    <t xml:space="preserve">6.69426393508911</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.67337942123413</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.65945529937744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.5438928604126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.57313203811646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.53136253356934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.59540891647339</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.5480694770813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.67477178573608</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.50073146820068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.72489452362061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.79172563552856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.71236419677734</t>
+    <t xml:space="preserve">6.69426298141479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.6733775138855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.65945625305176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.54389381408691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.57313251495361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.53136205673218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.59540939331055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.54806995391846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.67477083206177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.50073099136353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.72489356994629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.79172515869141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.71236228942871</t>
   </si>
   <si>
     <t xml:space="preserve">6.6051549911499</t>
@@ -2024,16 +2024,16 @@
     <t xml:space="preserve">6.26125240325928</t>
   </si>
   <si>
-    <t xml:space="preserve">6.33504629135132</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.4812388420105</t>
+    <t xml:space="preserve">6.335045337677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.48123931884766</t>
   </si>
   <si>
     <t xml:space="preserve">6.36567640304565</t>
   </si>
   <si>
-    <t xml:space="preserve">6.61351013183594</t>
+    <t xml:space="preserve">6.61350774765015</t>
   </si>
   <si>
     <t xml:space="preserve">6.56756258010864</t>
@@ -2042,397 +2042,397 @@
     <t xml:space="preserve">6.7513484954834</t>
   </si>
   <si>
-    <t xml:space="preserve">6.7276782989502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.55781555175781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.61211633682251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.54249954223633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.85020446777344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.80286359786987</t>
+    <t xml:space="preserve">6.72767877578735</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.55781507492065</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.61211681365967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.54250001907349</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.85020399093628</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.80286502838135</t>
   </si>
   <si>
     <t xml:space="preserve">6.8752646446228</t>
   </si>
   <si>
-    <t xml:space="preserve">6.89197206497192</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.02424240112305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.9963960647583</t>
+    <t xml:space="preserve">6.89197158813477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.02424287796021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.99639701843262</t>
   </si>
   <si>
     <t xml:space="preserve">7.0137996673584</t>
   </si>
   <si>
-    <t xml:space="preserve">7.01728105545044</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.89893436431885</t>
+    <t xml:space="preserve">7.01728010177612</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.89893341064453</t>
   </si>
   <si>
     <t xml:space="preserve">6.92678117752075</t>
   </si>
   <si>
-    <t xml:space="preserve">7.04860925674438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.09037780761719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.00335788726807</t>
+    <t xml:space="preserve">7.04860830307007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.0903787612915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.00335884094238</t>
   </si>
   <si>
     <t xml:space="preserve">6.94348812103271</t>
   </si>
   <si>
-    <t xml:space="preserve">7.07297420501709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.08689737319946</t>
+    <t xml:space="preserve">7.07297515869141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.08689594268799</t>
   </si>
   <si>
     <t xml:space="preserve">7.00683784484863</t>
   </si>
   <si>
-    <t xml:space="preserve">7.15303230285645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.11126232147217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.10778093338013</t>
+    <t xml:space="preserve">7.15303182601929</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.1112642288208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.10778188705444</t>
   </si>
   <si>
     <t xml:space="preserve">7.14259004592896</t>
   </si>
   <si>
-    <t xml:space="preserve">7.26093673706055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.15999412536621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.93652629852295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.95184183120728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.94766473770142</t>
+    <t xml:space="preserve">7.26093721389771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.15999317169189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.93652725219727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.95184230804443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.94766569137573</t>
   </si>
   <si>
     <t xml:space="preserve">7.14607048034668</t>
   </si>
   <si>
-    <t xml:space="preserve">7.05208921432495</t>
+    <t xml:space="preserve">7.05208873748779</t>
   </si>
   <si>
     <t xml:space="preserve">7.13562774658203</t>
   </si>
   <si>
-    <t xml:space="preserve">7.36535978317261</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.37580251693726</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.47674465179443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.36884117126465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.45238065719604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.49414920806885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.51851511001587</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.60553598403931</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.62294006347656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.65078544616699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.56028604507446</t>
+    <t xml:space="preserve">7.36536026000977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.37580394744873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.47674512863159</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.36884069442749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.4523811340332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.49414968490601</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.51851558685303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.60553693771362</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.6229395866394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.65078592300415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.56028413772583</t>
   </si>
   <si>
     <t xml:space="preserve">7.59509229660034</t>
   </si>
   <si>
-    <t xml:space="preserve">7.58117151260376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.57420778274536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.67863178253174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.72388410568237</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.77609252929688</t>
+    <t xml:space="preserve">7.58117008209229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.57420682907104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.6786322593689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.72388315200806</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.77609491348267</t>
   </si>
   <si>
     <t xml:space="preserve">7.65426635742188</t>
   </si>
   <si>
-    <t xml:space="preserve">7.54636192321777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.63686275482178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.80046033859253</t>
+    <t xml:space="preserve">7.54636240005493</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.63686370849609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.80045890808105</t>
   </si>
   <si>
     <t xml:space="preserve">7.73780488967896</t>
   </si>
   <si>
-    <t xml:space="preserve">7.75520896911621</t>
+    <t xml:space="preserve">7.75521039962769</t>
   </si>
   <si>
     <t xml:space="preserve">7.7691330909729</t>
   </si>
   <si>
-    <t xml:space="preserve">7.81078147888184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.67666006088257</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.7472505569458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.65195417404175</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.71548366546631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.73666143417358</t>
+    <t xml:space="preserve">7.81078100204468</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.67666053771973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.74725103378296</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.65195369720459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.71548509597778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.73666191101074</t>
   </si>
   <si>
     <t xml:space="preserve">7.66607141494751</t>
   </si>
   <si>
-    <t xml:space="preserve">7.61665916442871</t>
+    <t xml:space="preserve">7.61665821075439</t>
   </si>
   <si>
     <t xml:space="preserve">7.50724458694458</t>
   </si>
   <si>
-    <t xml:space="preserve">7.47547960281372</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.23194217681885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.30959224700928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.40488767623901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.27076768875122</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.28135633468628</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.18958950042725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.29194355010986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.21076536178589</t>
+    <t xml:space="preserve">7.47547769546509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.23194313049316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.30959177017212</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.40488719940186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.27076721191406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.28135585784912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.1895899772644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.29194498062134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.21076726913452</t>
   </si>
   <si>
     <t xml:space="preserve">7.33076858520508</t>
   </si>
   <si>
-    <t xml:space="preserve">7.17899990081787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.24253225326538</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.17547082901001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.26723766326904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.36253356933594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.14370584487915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.19664716720581</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.10488224029541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.04346704483032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.22488451004028</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.12605714797974</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.2390022277832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.20723628997803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.16488265991211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.10135173797607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.09076309204102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.260178565979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.3272385597229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.34841632843018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.25311946868896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.47194910049438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.82136917114258</t>
+    <t xml:space="preserve">7.17900133132935</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.24253273010254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.17547035217285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.26723909378052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.36253595352173</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.14370632171631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.19664764404297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.10488033294678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.04346752166748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.22488403320312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.12605810165405</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.23900127410889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.20723676681519</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.16488170623779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.10135269165039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.09076261520386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.26017808914185</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.32724094390869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.34841728210449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.25311994552612</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.47194766998291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.82136821746826</t>
   </si>
   <si>
     <t xml:space="preserve">7.76136779785156</t>
   </si>
   <si>
-    <t xml:space="preserve">7.30606317520142</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.41547775268555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.55665588378906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.5707745552063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.62018823623657</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.69783544540405</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.78960418701172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.7507791519165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.72960138320923</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.71901416778564</t>
+    <t xml:space="preserve">7.30606365203857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.41547727584839</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.55665731430054</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.57077503204346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.62018728256226</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.69783782958984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.78960371017456</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.75077962875366</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.72960233688354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.7190146446228</t>
   </si>
   <si>
     <t xml:space="preserve">8.00490379333496</t>
   </si>
   <si>
-    <t xml:space="preserve">8.12490463256836</t>
+    <t xml:space="preserve">8.12490749359131</t>
   </si>
   <si>
     <t xml:space="preserve">7.96607828140259</t>
   </si>
   <si>
-    <t xml:space="preserve">7.97313785552979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.40841770172119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.29547452926636</t>
+    <t xml:space="preserve">7.97313594818115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.40841722488403</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.2954740524292</t>
   </si>
   <si>
     <t xml:space="preserve">7.44018459320068</t>
   </si>
   <si>
-    <t xml:space="preserve">7.11900091171265</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.78652000427246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.53804397583008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.79075527191162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.83875751495361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.65804672241211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.86275815963745</t>
+    <t xml:space="preserve">7.11900043487549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.78652095794678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.53804302215576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.79075574874878</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.83875703811646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.65804624557495</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.86275768280029</t>
   </si>
   <si>
     <t xml:space="preserve">5.97049999237061</t>
   </si>
   <si>
-    <t xml:space="preserve">5.56107759475708</t>
+    <t xml:space="preserve">5.5610785484314</t>
   </si>
   <si>
     <t xml:space="preserve">5.56248998641968</t>
   </si>
   <si>
-    <t xml:space="preserve">4.33704805374146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.76058721542358</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.58976030349731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.58552503585815</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.49658107757568</t>
+    <t xml:space="preserve">4.33704853057861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.76058864593506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.58975982666016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.585524559021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.49658155441284</t>
   </si>
   <si>
     <t xml:space="preserve">4.88059139251709</t>
@@ -2441,58 +2441,58 @@
     <t xml:space="preserve">4.89612054824829</t>
   </si>
   <si>
-    <t xml:space="preserve">5.0655369758606</t>
+    <t xml:space="preserve">5.06553649902344</t>
   </si>
   <si>
     <t xml:space="preserve">5.41142749786377</t>
   </si>
   <si>
-    <t xml:space="preserve">5.46084117889404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.71637582778931</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.54272508621216</t>
+    <t xml:space="preserve">5.46084022521973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.71637630462646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.542724609375</t>
   </si>
   <si>
     <t xml:space="preserve">5.58790302276611</t>
   </si>
   <si>
-    <t xml:space="preserve">5.44954586029053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.21801137924194</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.48625230789185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.52719497680664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.67543458938599</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.7573184967041</t>
+    <t xml:space="preserve">5.44954633712769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.2180118560791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.486252784729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.52719449996948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.67543411254883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.75731801986694</t>
   </si>
   <si>
     <t xml:space="preserve">5.84343767166138</t>
   </si>
   <si>
-    <t xml:space="preserve">5.86320304870605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.88720417022705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.36907386779785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.41283941268921</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.43542766571045</t>
+    <t xml:space="preserve">5.86320352554321</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.88720512390137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.36907339096069</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.41283988952637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.43542814254761</t>
   </si>
   <si>
     <t xml:space="preserve">5.37330865859985</t>
@@ -2501,70 +2501,70 @@
     <t xml:space="preserve">5.25895261764526</t>
   </si>
   <si>
-    <t xml:space="preserve">5.34225034713745</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.3069543838501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.22224617004395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.56390237808228</t>
+    <t xml:space="preserve">5.34224891662598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.30695486068726</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.22224712371826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.56390142440796</t>
   </si>
   <si>
     <t xml:space="preserve">5.55401945114136</t>
   </si>
   <si>
-    <t xml:space="preserve">5.66837453842163</t>
+    <t xml:space="preserve">5.66837596893311</t>
   </si>
   <si>
     <t xml:space="preserve">5.47213506698608</t>
   </si>
   <si>
-    <t xml:space="preserve">5.33942556381226</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.18836307525635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.10224294662476</t>
+    <t xml:space="preserve">5.3394250869751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.18836259841919</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.10224390029907</t>
   </si>
   <si>
     <t xml:space="preserve">5.36060285568237</t>
   </si>
   <si>
-    <t xml:space="preserve">5.47495889663696</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.25613021850586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.16012763977051</t>
+    <t xml:space="preserve">5.4749584197998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.25612878799438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.16012716293335</t>
   </si>
   <si>
     <t xml:space="preserve">5.07259607315063</t>
   </si>
   <si>
-    <t xml:space="preserve">5.26742458343506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.22648143768311</t>
+    <t xml:space="preserve">5.2674241065979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.22648191452026</t>
   </si>
   <si>
     <t xml:space="preserve">5.23495244979858</t>
   </si>
   <si>
-    <t xml:space="preserve">5.20248174667358</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.25330591201782</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.46225261688232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.54413604736328</t>
+    <t xml:space="preserve">5.20248079299927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.2533073425293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.46225214004517</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.54413652420044</t>
   </si>
   <si>
     <t xml:space="preserve">5.57237339019775</t>
@@ -2573,25 +2573,25 @@
     <t xml:space="preserve">5.62319755554199</t>
   </si>
   <si>
-    <t xml:space="preserve">5.68813943862915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.86038017272949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.04814958572388</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.19074201583862</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.31921434402466</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.12438631057739</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.05379676818848</t>
+    <t xml:space="preserve">5.68814039230347</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.86038064956665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.04814863204956</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.19074106216431</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.31921482086182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.12438583374023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.05379581451416</t>
   </si>
   <si>
     <t xml:space="preserve">5.73472929000854</t>
@@ -2600,55 +2600,55 @@
     <t xml:space="preserve">5.82226133346558</t>
   </si>
   <si>
-    <t xml:space="preserve">5.87167406082153</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.99026584625244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.96344041824341</t>
+    <t xml:space="preserve">5.87167453765869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.99026536941528</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.96344089508057</t>
   </si>
   <si>
     <t xml:space="preserve">5.92108678817749</t>
   </si>
   <si>
-    <t xml:space="preserve">5.80249691009521</t>
+    <t xml:space="preserve">5.80249738693237</t>
   </si>
   <si>
     <t xml:space="preserve">5.92205190658569</t>
   </si>
   <si>
-    <t xml:space="preserve">6.02327156066895</t>
+    <t xml:space="preserve">6.02327013015747</t>
   </si>
   <si>
     <t xml:space="preserve">5.75628709793091</t>
   </si>
   <si>
-    <t xml:space="preserve">5.79736185073853</t>
+    <t xml:space="preserve">5.79736089706421</t>
   </si>
   <si>
     <t xml:space="preserve">5.68147277832031</t>
   </si>
   <si>
-    <t xml:space="preserve">5.85457229614258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.67707252502441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.68734073638916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.71227931976318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.80469655990601</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.7724232673645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.72694826126099</t>
+    <t xml:space="preserve">5.85457277297974</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.67707204818726</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.68734121322632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.71227884292603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.80469608306885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.77242374420166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.72694778442383</t>
   </si>
   <si>
     <t xml:space="preserve">5.59198951721191</t>
@@ -2657,40 +2657,40 @@
     <t xml:space="preserve">5.64039850234985</t>
   </si>
   <si>
-    <t xml:space="preserve">5.74748516082764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.72548055648804</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.75041913986206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.76655673980713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.00420093536377</t>
+    <t xml:space="preserve">5.74748563766479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.72548246383667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.75041961669922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.76655530929565</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.00420141220093</t>
   </si>
   <si>
     <t xml:space="preserve">6.04820966720581</t>
   </si>
   <si>
-    <t xml:space="preserve">6.10248613357544</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.00566720962524</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.97632837295532</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.82670068740845</t>
+    <t xml:space="preserve">6.10248565673828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.00566673278809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.97632884979248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.82670021057129</t>
   </si>
   <si>
     <t xml:space="preserve">5.7944278717041</t>
   </si>
   <si>
-    <t xml:space="preserve">5.77975797653198</t>
+    <t xml:space="preserve">5.77975845336914</t>
   </si>
   <si>
     <t xml:space="preserve">5.58172082901001</t>
@@ -2699,7 +2699,7 @@
     <t xml:space="preserve">5.68587398529053</t>
   </si>
   <si>
-    <t xml:space="preserve">5.79149389266968</t>
+    <t xml:space="preserve">5.79149341583252</t>
   </si>
   <si>
     <t xml:space="preserve">5.8311014175415</t>
@@ -2708,25 +2708,25 @@
     <t xml:space="preserve">5.82963371276855</t>
   </si>
   <si>
-    <t xml:space="preserve">5.73868322372437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.78415966033936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.88537836074829</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.9792628288269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.97192859649658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.90004777908325</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.87510967254639</t>
+    <t xml:space="preserve">5.73868370056152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.7841591835022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.88537883758545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.97926330566406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.97192811965942</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.90004682540894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.87511014938354</t>
   </si>
   <si>
     <t xml:space="preserve">5.78269195556641</t>
@@ -2735,85 +2735,85 @@
     <t xml:space="preserve">5.76362228393555</t>
   </si>
   <si>
-    <t xml:space="preserve">5.82376623153687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.72401428222656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.80176210403442</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.8208327293396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.7533540725708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.7577543258667</t>
+    <t xml:space="preserve">5.82376718521118</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.7240138053894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.80176258087158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.82083177566528</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.75335359573364</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.75775384902954</t>
   </si>
   <si>
     <t xml:space="preserve">5.6726713180542</t>
   </si>
   <si>
-    <t xml:space="preserve">5.63012981414795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.64186525344849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.83696985244751</t>
+    <t xml:space="preserve">5.63012933731079</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.64186477661133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.83696937561035</t>
   </si>
   <si>
     <t xml:space="preserve">5.7166805267334</t>
   </si>
   <si>
-    <t xml:space="preserve">5.85310506820679</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.8428373336792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.84577083587646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.81203079223633</t>
+    <t xml:space="preserve">5.85310554504395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.84283685684204</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.84577035903931</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.81203126907349</t>
   </si>
   <si>
     <t xml:space="preserve">5.69320917129517</t>
   </si>
   <si>
-    <t xml:space="preserve">5.49517107009888</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.57291889190674</t>
+    <t xml:space="preserve">5.49517202377319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.57291984558105</t>
   </si>
   <si>
     <t xml:space="preserve">5.61839389801025</t>
   </si>
   <si>
-    <t xml:space="preserve">5.60665893554688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.56411743164062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.66973733901978</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.55678272247314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.55091619491577</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.50984048843384</t>
+    <t xml:space="preserve">5.60665941238403</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.56411790847778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.66973781585693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.5567831993103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.55091428756714</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.509840965271</t>
   </si>
   <si>
     <t xml:space="preserve">5.54211330413818</t>
   </si>
   <si>
-    <t xml:space="preserve">5.9323205947876</t>
+    <t xml:space="preserve">5.93232107162476</t>
   </si>
   <si>
     <t xml:space="preserve">5.88097763061523</t>
@@ -2822,28 +2822,28 @@
     <t xml:space="preserve">5.87804317474365</t>
   </si>
   <si>
-    <t xml:space="preserve">5.87951040267944</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.89271306991577</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.89418029785156</t>
+    <t xml:space="preserve">5.87950992584229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.89271402359009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.8941798210144</t>
   </si>
   <si>
     <t xml:space="preserve">5.59932422637939</t>
   </si>
   <si>
-    <t xml:space="preserve">5.6682710647583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.67560577392578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.56998538970947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.57878684997559</t>
+    <t xml:space="preserve">5.66827058792114</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.67560529708862</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.56998491287231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.57878637313843</t>
   </si>
   <si>
     <t xml:space="preserve">5.568519115448</t>
@@ -2855,31 +2855,31 @@
     <t xml:space="preserve">5.43942737579346</t>
   </si>
   <si>
-    <t xml:space="preserve">5.21058416366577</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.14017105102539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.1343035697937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.25752639770508</t>
+    <t xml:space="preserve">5.21058368682861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.14017009735107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.13430309295654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.25752592086792</t>
   </si>
   <si>
     <t xml:space="preserve">5.30740261077881</t>
   </si>
   <si>
-    <t xml:space="preserve">5.47463417053223</t>
+    <t xml:space="preserve">5.47463464736938</t>
   </si>
   <si>
     <t xml:space="preserve">5.65506792068481</t>
   </si>
   <si>
-    <t xml:space="preserve">5.56265068054199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.75922155380249</t>
+    <t xml:space="preserve">5.56265115737915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.75922107696533</t>
   </si>
   <si>
     <t xml:space="preserve">5.90151405334473</t>
@@ -2897,79 +2897,79 @@
     <t xml:space="preserve">6.3181266784668</t>
   </si>
   <si>
-    <t xml:space="preserve">6.4252142906189</t>
+    <t xml:space="preserve">6.42521381378174</t>
   </si>
   <si>
     <t xml:space="preserve">6.49415969848633</t>
   </si>
   <si>
-    <t xml:space="preserve">6.39440822601318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.42820262908936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.57317781448364</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.51040506362915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.5761661529541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.38486003875732</t>
+    <t xml:space="preserve">6.39440870285034</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.4282021522522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.57317686080933</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.51040458679199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.57616710662842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.38485956192017</t>
   </si>
   <si>
     <t xml:space="preserve">6.43567657470703</t>
   </si>
   <si>
-    <t xml:space="preserve">6.33254909515381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.35496854782104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.28322887420654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.27276706695557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.28173398971558</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.29070234298706</t>
+    <t xml:space="preserve">6.33254957199097</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.35496807098389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.28322839736938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.27276611328125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.28173351287842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.29070138931274</t>
   </si>
   <si>
     <t xml:space="preserve">6.2398853302002</t>
   </si>
   <si>
-    <t xml:space="preserve">6.23540210723877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.33553791046143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.26977777481079</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.24586343765259</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.10238456726074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.22792911529541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.25333738327026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.21746683120728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.23390626907349</t>
+    <t xml:space="preserve">6.23540115356445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.33553886413574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.26977729797363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.24586391448975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.10238361358643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.22792863845825</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.25333690643311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.21746635437012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.2339072227478</t>
   </si>
   <si>
     <t xml:space="preserve">6.19355344772339</t>
@@ -2978,31 +2978,31 @@
     <t xml:space="preserve">6.38187074661255</t>
   </si>
   <si>
-    <t xml:space="preserve">6.51488924026489</t>
+    <t xml:space="preserve">6.51488971710205</t>
   </si>
   <si>
     <t xml:space="preserve">6.42222499847412</t>
   </si>
   <si>
-    <t xml:space="preserve">6.37738752365112</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.30265760421753</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.241379737854</t>
+    <t xml:space="preserve">6.37738800048828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.30265808105469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.24138021469116</t>
   </si>
   <si>
     <t xml:space="preserve">6.26230382919312</t>
   </si>
   <si>
-    <t xml:space="preserve">6.20999383926392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.27426052093506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.21597194671631</t>
+    <t xml:space="preserve">6.20999431610107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.2742600440979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.21597242355347</t>
   </si>
   <si>
     <t xml:space="preserve">6.17860746383667</t>
@@ -3014,79 +3014,79 @@
     <t xml:space="preserve">6.24885320663452</t>
   </si>
   <si>
-    <t xml:space="preserve">6.09789991378784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.15320014953613</t>
+    <t xml:space="preserve">6.09789943695068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.15319919586182</t>
   </si>
   <si>
     <t xml:space="preserve">6.03512763977051</t>
   </si>
   <si>
-    <t xml:space="preserve">6.19803667068481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.18757390975952</t>
+    <t xml:space="preserve">6.19803619384766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.187575340271</t>
   </si>
   <si>
     <t xml:space="preserve">6.62847709655762</t>
   </si>
   <si>
-    <t xml:space="preserve">6.73459196090698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.8900294303894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.06638956069946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.15158033370972</t>
+    <t xml:space="preserve">6.73459339141846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.89003038406372</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.06639051437378</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.15158176422119</t>
   </si>
   <si>
     <t xml:space="preserve">7.10973262786865</t>
   </si>
   <si>
-    <t xml:space="preserve">7.21136426925659</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.23228883743286</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.3010401725769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.21286106109619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.08582019805908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.9528021812439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.02304649353027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.20688009262085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.12019491195679</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.13663482666016</t>
+    <t xml:space="preserve">7.21136474609375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.2322883605957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.30103921890259</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.21285915374756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.08581972122192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.95280170440674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.02304697036743</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.20688104629517</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.12019443511963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.13663530349731</t>
   </si>
   <si>
     <t xml:space="preserve">7.17997789382935</t>
   </si>
   <si>
-    <t xml:space="preserve">7.02753114700317</t>
+    <t xml:space="preserve">7.02753162384033</t>
   </si>
   <si>
     <t xml:space="preserve">7.34438276290894</t>
   </si>
   <si>
-    <t xml:space="preserve">7.38025331497192</t>
+    <t xml:space="preserve">7.38025283813477</t>
   </si>
   <si>
     <t xml:space="preserve">7.43555212020874</t>
@@ -3095,46 +3095,46 @@
     <t xml:space="preserve">7.45348691940308</t>
   </si>
   <si>
-    <t xml:space="preserve">7.3608226776123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.50280809402466</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.57753801345825</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.64479351043701</t>
+    <t xml:space="preserve">7.36082315444946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.50280857086182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.57753753662109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.64479398727417</t>
   </si>
   <si>
     <t xml:space="preserve">7.61116600036621</t>
   </si>
   <si>
-    <t xml:space="preserve">7.67842149734497</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.63358354568481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.7979884147644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.75688648223877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.81293439865112</t>
+    <t xml:space="preserve">7.67842197418213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.63358497619629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.79798936843872</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.75688791275024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.81293392181396</t>
   </si>
   <si>
     <t xml:space="preserve">7.72699642181396</t>
   </si>
   <si>
-    <t xml:space="preserve">7.85029935836792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.78304290771484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.82414293289185</t>
+    <t xml:space="preserve">7.85029888153076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.783043384552</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.82414484024048</t>
   </si>
   <si>
     <t xml:space="preserve">7.8166708946228</t>
@@ -3149,52 +3149,52 @@
     <t xml:space="preserve">8.11185073852539</t>
   </si>
   <si>
-    <t xml:space="preserve">8.10064220428467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.15295314788818</t>
+    <t xml:space="preserve">8.10064125061035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.15295124053955</t>
   </si>
   <si>
     <t xml:space="preserve">8.17536926269531</t>
   </si>
   <si>
-    <t xml:space="preserve">8.16416263580322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.04833126068115</t>
+    <t xml:space="preserve">8.16416168212891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.04833030700684</t>
   </si>
   <si>
     <t xml:space="preserve">8.06701374053955</t>
   </si>
   <si>
-    <t xml:space="preserve">8.05953979492188</t>
+    <t xml:space="preserve">8.05954074859619</t>
   </si>
   <si>
     <t xml:space="preserve">7.96986436843872</t>
   </si>
   <si>
-    <t xml:space="preserve">7.96239233016968</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.0520658493042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.04085826873779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.93250131607056</t>
+    <t xml:space="preserve">7.96239280700684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.05206680297852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.04085731506348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.9325008392334</t>
   </si>
   <si>
     <t xml:space="preserve">7.92876482009888</t>
   </si>
   <si>
-    <t xml:space="preserve">8.10811424255371</t>
+    <t xml:space="preserve">8.10811614990234</t>
   </si>
   <si>
     <t xml:space="preserve">8.07822418212891</t>
   </si>
   <si>
-    <t xml:space="preserve">8.08943271636963</t>
+    <t xml:space="preserve">8.08943176269531</t>
   </si>
   <si>
     <t xml:space="preserve">8.16042613983154</t>
@@ -3203,31 +3203,31 @@
     <t xml:space="preserve">8.15668869018555</t>
   </si>
   <si>
-    <t xml:space="preserve">8.14548015594482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.25757312774658</t>
+    <t xml:space="preserve">8.14547920227051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.25757217407227</t>
   </si>
   <si>
     <t xml:space="preserve">8.19779014587402</t>
   </si>
   <si>
-    <t xml:space="preserve">8.16789722442627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.22020816802979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.38834762573242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.35098457336426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.24636363983154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.25010108947754</t>
+    <t xml:space="preserve">8.1678991317749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.2202091217041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.38834857940674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.35098552703857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.24636268615723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.25009918212891</t>
   </si>
   <si>
     <t xml:space="preserve">8.30988311767578</t>
@@ -3236,61 +3236,61 @@
     <t xml:space="preserve">8.43692302703857</t>
   </si>
   <si>
-    <t xml:space="preserve">8.42571258544922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.3920841217041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.46307849884033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.5938549041748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.74331283569336</t>
+    <t xml:space="preserve">8.42571353912354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.39208507537842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.46307754516602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.59385395050049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.74331188201904</t>
   </si>
   <si>
     <t xml:space="preserve">8.62748241424561</t>
   </si>
   <si>
-    <t xml:space="preserve">8.53407096862793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.58638191223145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.59759044647217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.64242649078369</t>
+    <t xml:space="preserve">8.53407001495361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.58638095855713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.59758949279785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.64242744445801</t>
   </si>
   <si>
     <t xml:space="preserve">8.81804180145264</t>
   </si>
   <si>
-    <t xml:space="preserve">8.90024375915527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.01233768463135</t>
+    <t xml:space="preserve">8.90024471282959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.01233673095703</t>
   </si>
   <si>
     <t xml:space="preserve">9.02728271484375</t>
   </si>
   <si>
-    <t xml:space="preserve">8.95629024505615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.97870922088623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.95255279541016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.01980972290039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.96376323699951</t>
+    <t xml:space="preserve">8.95628929138184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.97871017456055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.95255374908447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.01981067657471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.9637622833252</t>
   </si>
   <si>
     <t xml:space="preserve">8.73957538604736</t>
@@ -3302,7 +3302,7 @@
     <t xml:space="preserve">8.73112106323242</t>
   </si>
   <si>
-    <t xml:space="preserve">8.62736129760742</t>
+    <t xml:space="preserve">8.62736225128174</t>
   </si>
   <si>
     <t xml:space="preserve">8.78107833862305</t>
@@ -3311,19 +3311,19 @@
     <t xml:space="preserve">8.75417995452881</t>
   </si>
   <si>
-    <t xml:space="preserve">8.6119909286499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.573561668396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.5697193145752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.66963291168213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.59277725219727</t>
+    <t xml:space="preserve">8.61198997497559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.57356071472168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.56971836090088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.66963386535645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.59277629852295</t>
   </si>
   <si>
     <t xml:space="preserve">8.71574974060059</t>
@@ -3338,46 +3338,46 @@
     <t xml:space="preserve">8.31992816925049</t>
   </si>
   <si>
-    <t xml:space="preserve">8.45058727264404</t>
+    <t xml:space="preserve">8.45058822631836</t>
   </si>
   <si>
     <t xml:space="preserve">8.48133087158203</t>
   </si>
   <si>
-    <t xml:space="preserve">8.47748756408691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.44674396514893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.33145809173584</t>
+    <t xml:space="preserve">8.47748851776123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.44674587249756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.33145713806152</t>
   </si>
   <si>
     <t xml:space="preserve">8.35835838317871</t>
   </si>
   <si>
-    <t xml:space="preserve">8.07398223876953</t>
+    <t xml:space="preserve">8.07398128509521</t>
   </si>
   <si>
     <t xml:space="preserve">8.15468311309814</t>
   </si>
   <si>
-    <t xml:space="preserve">8.41215705871582</t>
+    <t xml:space="preserve">8.41215896606445</t>
   </si>
   <si>
     <t xml:space="preserve">8.53897571563721</t>
   </si>
   <si>
-    <t xml:space="preserve">8.61583423614502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.6850061416626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.60046195983887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.5812463760376</t>
+    <t xml:space="preserve">8.6158332824707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.68500709533691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.60046291351318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.58124732971191</t>
   </si>
   <si>
     <t xml:space="preserve">8.55050373077393</t>
@@ -3386,10 +3386,10 @@
     <t xml:space="preserve">8.7272777557373</t>
   </si>
   <si>
-    <t xml:space="preserve">8.85793590545654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.90020942687988</t>
+    <t xml:space="preserve">8.85793685913086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.9002103805542</t>
   </si>
   <si>
     <t xml:space="preserve">8.93479633331299</t>
@@ -3398,7 +3398,7 @@
     <t xml:space="preserve">9.0078125</t>
   </si>
   <si>
-    <t xml:space="preserve">9.02702522277832</t>
+    <t xml:space="preserve">9.02702617645264</t>
   </si>
   <si>
     <t xml:space="preserve">8.98091125488281</t>
@@ -3407,7 +3407,7 @@
     <t xml:space="preserve">8.92326736450195</t>
   </si>
   <si>
-    <t xml:space="preserve">8.87330913543701</t>
+    <t xml:space="preserve">8.87331008911133</t>
   </si>
   <si>
     <t xml:space="preserve">8.94632530212402</t>
@@ -3416,31 +3416,31 @@
     <t xml:space="preserve">8.83487987518311</t>
   </si>
   <si>
-    <t xml:space="preserve">8.76954936981201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.96169567108154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.93863964080811</t>
+    <t xml:space="preserve">8.76955127716064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.96169757843018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.93864154815674</t>
   </si>
   <si>
     <t xml:space="preserve">8.90789604187012</t>
   </si>
   <si>
-    <t xml:space="preserve">8.82719421386719</t>
+    <t xml:space="preserve">8.82719326019287</t>
   </si>
   <si>
     <t xml:space="preserve">8.86562347412109</t>
   </si>
   <si>
-    <t xml:space="preserve">8.91173934936523</t>
+    <t xml:space="preserve">8.9117374420166</t>
   </si>
   <si>
     <t xml:space="preserve">8.94248294830322</t>
   </si>
   <si>
-    <t xml:space="preserve">8.80798053741455</t>
+    <t xml:space="preserve">8.80797958374023</t>
   </si>
   <si>
     <t xml:space="preserve">8.86946582794189</t>
@@ -3449,13 +3449,13 @@
     <t xml:space="preserve">8.88483810424805</t>
   </si>
   <si>
-    <t xml:space="preserve">8.96553993225098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.10772800445557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.02318382263184</t>
+    <t xml:space="preserve">8.96553897857666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.10772895812988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.02318286895752</t>
   </si>
   <si>
     <t xml:space="preserve">9.05776882171631</t>
@@ -3464,10 +3464,10 @@
     <t xml:space="preserve">9.13847160339355</t>
   </si>
   <si>
-    <t xml:space="preserve">9.20380020141602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.16921520233154</t>
+    <t xml:space="preserve">9.20380115509033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.16921615600586</t>
   </si>
   <si>
     <t xml:space="preserve">9.25375843048096</t>
@@ -3476,13 +3476,13 @@
     <t xml:space="preserve">9.03086948394775</t>
   </si>
   <si>
-    <t xml:space="preserve">9.09235572814941</t>
+    <t xml:space="preserve">9.09235668182373</t>
   </si>
   <si>
     <t xml:space="preserve">9.14999961853027</t>
   </si>
   <si>
-    <t xml:space="preserve">9.11157035827637</t>
+    <t xml:space="preserve">9.11157131195068</t>
   </si>
   <si>
     <t xml:space="preserve">9.2960319519043</t>
@@ -3497,10 +3497,10 @@
     <t xml:space="preserve">9.36136054992676</t>
   </si>
   <si>
-    <t xml:space="preserve">9.34598922729492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.46896266937256</t>
+    <t xml:space="preserve">9.34598731994629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.46896171569824</t>
   </si>
   <si>
     <t xml:space="preserve">9.50354862213135</t>
@@ -3515,31 +3515,31 @@
     <t xml:space="preserve">9.51891994476318</t>
   </si>
   <si>
-    <t xml:space="preserve">9.4151611328125</t>
+    <t xml:space="preserve">9.41516208648682</t>
   </si>
   <si>
     <t xml:space="preserve">9.64958000183105</t>
   </si>
   <si>
-    <t xml:space="preserve">9.61499500274658</t>
+    <t xml:space="preserve">9.61499309539795</t>
   </si>
   <si>
     <t xml:space="preserve">9.595778465271</t>
   </si>
   <si>
-    <t xml:space="preserve">9.7418098449707</t>
+    <t xml:space="preserve">9.74181079864502</t>
   </si>
   <si>
     <t xml:space="preserve">9.65726566314697</t>
   </si>
   <si>
-    <t xml:space="preserve">9.64189434051514</t>
+    <t xml:space="preserve">9.6418924331665</t>
   </si>
   <si>
     <t xml:space="preserve">9.48433494567871</t>
   </si>
   <si>
-    <t xml:space="preserve">9.56503486633301</t>
+    <t xml:space="preserve">9.56503582000732</t>
   </si>
   <si>
     <t xml:space="preserve">9.53044891357422</t>
@@ -3551,55 +3551,55 @@
     <t xml:space="preserve">9.57656383514404</t>
   </si>
   <si>
-    <t xml:space="preserve">9.60346603393555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.56119155883789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.46511936187744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.4113187789917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.42284774780273</t>
+    <t xml:space="preserve">9.60346508026123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.56119251251221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.46512031555176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.41131782531738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.42284679412842</t>
   </si>
   <si>
     <t xml:space="preserve">9.33446025848389</t>
   </si>
   <si>
-    <t xml:space="preserve">9.27297115325928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.25345897674561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.17930698394775</t>
+    <t xml:space="preserve">9.27297210693359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.25345993041992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.17930793762207</t>
   </si>
   <si>
     <t xml:space="preserve">9.15198802947998</t>
   </si>
   <si>
-    <t xml:space="preserve">9.01538944244385</t>
+    <t xml:space="preserve">9.01539039611816</t>
   </si>
   <si>
     <t xml:space="preserve">8.64462757110596</t>
   </si>
   <si>
-    <t xml:space="preserve">8.73829460144043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.69536399841309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.85928058624268</t>
+    <t xml:space="preserve">8.73829555511475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.6953649520874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.85927963256836</t>
   </si>
   <si>
     <t xml:space="preserve">8.76561260223389</t>
   </si>
   <si>
-    <t xml:space="preserve">8.69926738739014</t>
+    <t xml:space="preserve">8.69926643371582</t>
   </si>
   <si>
     <t xml:space="preserve">8.73048877716064</t>
@@ -3608,7 +3608,7 @@
     <t xml:space="preserve">8.85147476196289</t>
   </si>
   <si>
-    <t xml:space="preserve">8.72658729553223</t>
+    <t xml:space="preserve">8.72658634185791</t>
   </si>
   <si>
     <t xml:space="preserve">8.66414165496826</t>
@@ -3626,31 +3626,31 @@
     <t xml:space="preserve">8.6875581741333</t>
   </si>
   <si>
-    <t xml:space="preserve">8.75000286102295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.76171016693115</t>
+    <t xml:space="preserve">8.75000190734863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.76171112060547</t>
   </si>
   <si>
     <t xml:space="preserve">8.56266975402832</t>
   </si>
   <si>
-    <t xml:space="preserve">8.70316982269287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.78903102874756</t>
+    <t xml:space="preserve">8.70316886901855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.78903007507324</t>
   </si>
   <si>
     <t xml:space="preserve">8.86708545684814</t>
   </si>
   <si>
-    <t xml:space="preserve">8.94514179229736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.0192928314209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.99977970123291</t>
+    <t xml:space="preserve">8.94514083862305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.01929378509521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.99977874755859</t>
   </si>
   <si>
     <t xml:space="preserve">9.00758457183838</t>
@@ -3665,13 +3665,13 @@
     <t xml:space="preserve">9.1832103729248</t>
   </si>
   <si>
-    <t xml:space="preserve">9.1051549911499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.13247394561768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.15979290008545</t>
+    <t xml:space="preserve">9.10515403747559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.13247299194336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.15979385375977</t>
   </si>
   <si>
     <t xml:space="preserve">9.09734916687012</t>
@@ -3683,7 +3683,7 @@
     <t xml:space="preserve">9.06222343444824</t>
   </si>
   <si>
-    <t xml:space="preserve">9.027099609375</t>
+    <t xml:space="preserve">9.02709865570068</t>
   </si>
   <si>
     <t xml:space="preserve">9.04661273956299</t>
@@ -3692,43 +3692,43 @@
     <t xml:space="preserve">9.12076568603516</t>
   </si>
   <si>
-    <t xml:space="preserve">8.96465492248535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.60560035705566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.81634902954102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.01148796081543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.90221118927002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.31200122833252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.31980514526367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.5002269744873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.55486297607422</t>
+    <t xml:space="preserve">8.96465396881104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.60559940338135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.8163480758667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.01148891448975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.9022102355957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.31200218200684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.31980609893799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.50022506713867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.55486392974854</t>
   </si>
   <si>
     <t xml:space="preserve">8.59389209747314</t>
   </si>
   <si>
-    <t xml:space="preserve">8.42607402801514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.58218288421631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.66023921966553</t>
+    <t xml:space="preserve">8.42607307434082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.58218383789062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.66024017333984</t>
   </si>
   <si>
     <t xml:space="preserve">8.69146060943604</t>
@@ -3740,7 +3740,7 @@
     <t xml:space="preserve">8.40265655517578</t>
   </si>
   <si>
-    <t xml:space="preserve">8.37143421173096</t>
+    <t xml:space="preserve">8.37143516540527</t>
   </si>
   <si>
     <t xml:space="preserve">8.30118465423584</t>
@@ -3749,13 +3749,13 @@
     <t xml:space="preserve">7.83675575256348</t>
   </si>
   <si>
-    <t xml:space="preserve">8.09433937072754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.02018451690674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.69625520706177</t>
+    <t xml:space="preserve">8.09433746337891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.02018547058105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.69625568389893</t>
   </si>
   <si>
     <t xml:space="preserve">7.68376588821411</t>
@@ -3764,31 +3764,31 @@
     <t xml:space="preserve">7.57605075836182</t>
   </si>
   <si>
-    <t xml:space="preserve">7.08742332458496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.93443632125854</t>
+    <t xml:space="preserve">7.08742380142212</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.93443584442139</t>
   </si>
   <si>
     <t xml:space="preserve">7.25602293014526</t>
   </si>
   <si>
-    <t xml:space="preserve">7.89919900894165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.49955654144287</t>
+    <t xml:space="preserve">7.89919996261597</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.49955558776855</t>
   </si>
   <si>
     <t xml:space="preserve">7.54482889175415</t>
   </si>
   <si>
-    <t xml:space="preserve">7.74933290481567</t>
+    <t xml:space="preserve">7.74933385848999</t>
   </si>
   <si>
     <t xml:space="preserve">7.70718288421631</t>
   </si>
   <si>
-    <t xml:space="preserve">8.0553092956543</t>
+    <t xml:space="preserve">8.05531024932861</t>
   </si>
   <si>
     <t xml:space="preserve">7.88749027252197</t>
@@ -3800,88 +3800,88 @@
     <t xml:space="preserve">7.89529609680176</t>
   </si>
   <si>
-    <t xml:space="preserve">8.10214328765869</t>
+    <t xml:space="preserve">8.10214424133301</t>
   </si>
   <si>
     <t xml:space="preserve">8.09043502807617</t>
   </si>
   <si>
-    <t xml:space="preserve">8.23483848571777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.12555885314941</t>
+    <t xml:space="preserve">8.23483753204346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.12556076049805</t>
   </si>
   <si>
     <t xml:space="preserve">8.2192268371582</t>
   </si>
   <si>
-    <t xml:space="preserve">8.28947734832764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.25435066223145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.11775493621826</t>
+    <t xml:space="preserve">8.28947639465332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.25435161590576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.11775398254395</t>
   </si>
   <si>
     <t xml:space="preserve">7.99676895141602</t>
   </si>
   <si>
-    <t xml:space="preserve">7.82504653930664</t>
+    <t xml:space="preserve">7.82504749298096</t>
   </si>
   <si>
     <t xml:space="preserve">7.70562219619751</t>
   </si>
   <si>
-    <t xml:space="preserve">7.85626935958862</t>
+    <t xml:space="preserve">7.85626840591431</t>
   </si>
   <si>
     <t xml:space="preserve">7.79304456710815</t>
   </si>
   <si>
-    <t xml:space="preserve">7.67596101760864</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.5979061126709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.65879011154175</t>
+    <t xml:space="preserve">7.67596006393433</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.59790563583374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.65878820419312</t>
   </si>
   <si>
     <t xml:space="preserve">7.53546190261841</t>
   </si>
   <si>
-    <t xml:space="preserve">7.73372077941895</t>
+    <t xml:space="preserve">7.73372173309326</t>
   </si>
   <si>
     <t xml:space="preserve">7.70874500274658</t>
   </si>
   <si>
-    <t xml:space="preserve">7.57292795181274</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.35905647277832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.26070690155029</t>
+    <t xml:space="preserve">7.57292747497559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.35905694961548</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.26070642471313</t>
   </si>
   <si>
     <t xml:space="preserve">7.23729085922241</t>
   </si>
   <si>
-    <t xml:space="preserve">7.28412294387817</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.32002925872803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.246657371521</t>
+    <t xml:space="preserve">7.28412342071533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.32002878189087</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.24665689468384</t>
   </si>
   <si>
     <t xml:space="preserve">7.18889570236206</t>
   </si>
   <si>
-    <t xml:space="preserve">7.1326961517334</t>
+    <t xml:space="preserve">7.13269567489624</t>
   </si>
   <si>
     <t xml:space="preserve">7.02654075622559</t>
@@ -3890,16 +3890,16 @@
     <t xml:space="preserve">6.84389066696167</t>
   </si>
   <si>
-    <t xml:space="preserve">7.0062460899353</t>
+    <t xml:space="preserve">7.00624656677246</t>
   </si>
   <si>
     <t xml:space="preserve">7.16860103607178</t>
   </si>
   <si>
-    <t xml:space="preserve">7.39340114593506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.54795122146606</t>
+    <t xml:space="preserve">7.3934006690979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.54795169830322</t>
   </si>
   <si>
     <t xml:space="preserve">7.44179582595825</t>
@@ -3908,25 +3908,25 @@
     <t xml:space="preserve">7.51204490661621</t>
   </si>
   <si>
-    <t xml:space="preserve">7.46677255630493</t>
+    <t xml:space="preserve">7.46677350997925</t>
   </si>
   <si>
     <t xml:space="preserve">7.44023370742798</t>
   </si>
   <si>
-    <t xml:space="preserve">7.41837787628174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.563560962677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.43554973602295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.55887889862061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.61195611953735</t>
+    <t xml:space="preserve">7.41837978363037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.56356048583984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.43555116653442</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.55887746810913</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.61195468902588</t>
   </si>
   <si>
     <t xml:space="preserve">7.75245571136475</t>
@@ -3935,10 +3935,10 @@
     <t xml:space="preserve">7.92261505126953</t>
   </si>
   <si>
-    <t xml:space="preserve">7.82114458084106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.8172402381897</t>
+    <t xml:space="preserve">7.82114362716675</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.81724119186401</t>
   </si>
   <si>
     <t xml:space="preserve">7.743088722229</t>
@@ -3947,13 +3947,13 @@
     <t xml:space="preserve">7.89139366149902</t>
   </si>
   <si>
-    <t xml:space="preserve">7.87578439712524</t>
+    <t xml:space="preserve">7.87578296661377</t>
   </si>
   <si>
     <t xml:space="preserve">7.7665057182312</t>
   </si>
   <si>
-    <t xml:space="preserve">7.14362335205078</t>
+    <t xml:space="preserve">7.14362382888794</t>
   </si>
   <si>
     <t xml:space="preserve">6.90477418899536</t>
@@ -3965,73 +3965,73 @@
     <t xml:space="preserve">7.35125112533569</t>
   </si>
   <si>
-    <t xml:space="preserve">6.98595142364502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.02185773849487</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.18777847290039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.12729644775391</t>
+    <t xml:space="preserve">6.98595094680786</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.02185821533203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.18777894973755</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.12729549407959</t>
   </si>
   <si>
     <t xml:space="preserve">7.15998983383179</t>
   </si>
   <si>
-    <t xml:space="preserve">7.10441064834595</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.31201648712158</t>
+    <t xml:space="preserve">7.10441017150879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.31201696395874</t>
   </si>
   <si>
     <t xml:space="preserve">7.27605390548706</t>
   </si>
   <si>
-    <t xml:space="preserve">7.42154121398926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.36596155166626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.2842264175415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.28749561309814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.28095722198486</t>
+    <t xml:space="preserve">7.42154169082642</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.36596298217773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.28422689437866</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.2874960899353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.28095769882202</t>
   </si>
   <si>
     <t xml:space="preserve">6.98834609985352</t>
   </si>
   <si>
-    <t xml:space="preserve">7.03248357772827</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.21393537521362</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.10114097595215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.96709489822388</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.99815559387207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.8510308265686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.5028395652771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.66794443130493</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.79381704330444</t>
+    <t xml:space="preserve">7.03248310089111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.21393442153931</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.10114049911499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.96709394454956</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.99815464019775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.85103130340576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.50284004211426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.66794490814209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.7938175201416</t>
   </si>
   <si>
     <t xml:space="preserve">7.01940536499023</t>
@@ -4049,58 +4049,58 @@
     <t xml:space="preserve">6.64342451095581</t>
   </si>
   <si>
-    <t xml:space="preserve">6.62871122360229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.64015483856201</t>
+    <t xml:space="preserve">6.62871170043945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.64015436172485</t>
   </si>
   <si>
     <t xml:space="preserve">6.58457469940186</t>
   </si>
   <si>
-    <t xml:space="preserve">6.67775297164917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.74314117431641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.66140556335449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.77420091629028</t>
+    <t xml:space="preserve">6.67775344848633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.74314069747925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.66140508651733</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.77420043945312</t>
   </si>
   <si>
     <t xml:space="preserve">6.85266542434692</t>
   </si>
   <si>
-    <t xml:space="preserve">6.92949628829956</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.8657431602478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.82814502716064</t>
+    <t xml:space="preserve">6.92949676513672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.86574363708496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.82814598083496</t>
   </si>
   <si>
     <t xml:space="preserve">6.8690128326416</t>
   </si>
   <si>
-    <t xml:space="preserve">6.97036361694336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.97690391540527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.91805410385132</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.82651090621948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.70227289199829</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.53226470947266</t>
+    <t xml:space="preserve">6.97036409378052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.97690296173096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.91805362701416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.82651042938232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.70227336883545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.5322642326355</t>
   </si>
   <si>
     <t xml:space="preserve">6.63198184967041</t>
@@ -4115,22 +4115,22 @@
     <t xml:space="preserve">6.42927885055542</t>
   </si>
   <si>
-    <t xml:space="preserve">6.34754323959351</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.49466609954834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.44562530517578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.62053823471069</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.44889450073242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.52245569229126</t>
+    <t xml:space="preserve">6.34754276275635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.4946665763855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.44562578201294</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.62053871154785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.44889497756958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.52245616912842</t>
   </si>
   <si>
     <t xml:space="preserve">6.54043817520142</t>
@@ -4139,106 +4139,106 @@
     <t xml:space="preserve">6.60909557342529</t>
   </si>
   <si>
-    <t xml:space="preserve">6.71044635772705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.80035543441772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.8134331703186</t>
+    <t xml:space="preserve">6.71044683456421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.80035495758057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.81343364715576</t>
   </si>
   <si>
     <t xml:space="preserve">6.86737823486328</t>
   </si>
   <si>
-    <t xml:space="preserve">6.7611231803894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.79054641723633</t>
+    <t xml:space="preserve">6.76112270355225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.79054689407349</t>
   </si>
   <si>
     <t xml:space="preserve">6.64832782745361</t>
   </si>
   <si>
-    <t xml:space="preserve">6.64505910873413</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.4537992477417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.51918649673462</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.38350677490234</t>
+    <t xml:space="preserve">6.64505863189697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.45379877090454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.51918697357178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.38350629806519</t>
   </si>
   <si>
     <t xml:space="preserve">6.3916802406311</t>
   </si>
   <si>
-    <t xml:space="preserve">6.25926971435547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.36715936660767</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.4979362487793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.68919610977173</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.59274816513062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.48158836364746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.39331483840942</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.40802669525146</t>
+    <t xml:space="preserve">6.25926923751831</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.36716032028198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.49793577194214</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.68919563293457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.59274864196777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.48158884048462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.39331531524658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.40802764892578</t>
   </si>
   <si>
     <t xml:space="preserve">6.26090383529663</t>
   </si>
   <si>
-    <t xml:space="preserve">6.36389017105103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.46033763885498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.62217283248901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.86247396469116</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.82487630844116</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.80199003219604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.73660182952881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.89189958572388</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.95565176010132</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.02104043960571</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.2270131111145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.17143249511719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.20903015136719</t>
+    <t xml:space="preserve">6.36388969421387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.46033716201782</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.62217330932617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.862473487854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.824875831604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.80198907852173</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.73660230636597</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.8918981552124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.95565223693848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.02103996276855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.22701263427734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.1714334487915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.20903062820435</t>
   </si>
   <si>
     <t xml:space="preserve">7.23028135299683</t>
@@ -4247,49 +4247,49 @@
     <t xml:space="preserve">7.19268369674683</t>
   </si>
   <si>
-    <t xml:space="preserve">7.14854717254639</t>
+    <t xml:space="preserve">7.14854669570923</t>
   </si>
   <si>
     <t xml:space="preserve">7.37740421295166</t>
   </si>
   <si>
-    <t xml:space="preserve">7.50327730178833</t>
+    <t xml:space="preserve">7.50327682495117</t>
   </si>
   <si>
     <t xml:space="preserve">7.54904890060425</t>
   </si>
   <si>
-    <t xml:space="preserve">7.64222526550293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.97243499755859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.87762260437012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.93157005310059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.96099281311035</t>
+    <t xml:space="preserve">7.64222574234009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.97243595123291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.87762308120728</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.93156814575195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.96099328994751</t>
   </si>
   <si>
     <t xml:space="preserve">7.86618041992188</t>
   </si>
   <si>
-    <t xml:space="preserve">7.8122353553772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.8498330116272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.81473731994629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.77797031402588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.85819005966187</t>
+    <t xml:space="preserve">7.81223487854004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.84983348846436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.81473779678345</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.77796983718872</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.85819053649902</t>
   </si>
   <si>
     <t xml:space="preserve">7.75624322891235</t>
@@ -4304,67 +4304,67 @@
     <t xml:space="preserve">7.87323093414307</t>
   </si>
   <si>
-    <t xml:space="preserve">7.84314775466919</t>
+    <t xml:space="preserve">7.84314870834351</t>
   </si>
   <si>
     <t xml:space="preserve">7.89662790298462</t>
   </si>
   <si>
-    <t xml:space="preserve">7.87657356262207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.80972337722778</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.90498399734497</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.7629280090332</t>
+    <t xml:space="preserve">7.87657260894775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.80972290039062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.9049859046936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.76292896270752</t>
   </si>
   <si>
     <t xml:space="preserve">7.83479261398315</t>
   </si>
   <si>
-    <t xml:space="preserve">7.83646297454834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.93172454833984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.93339586257935</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.51892757415771</t>
+    <t xml:space="preserve">7.8364634513855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.931725025177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.93339490890503</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.51892805099487</t>
   </si>
   <si>
     <t xml:space="preserve">7.56070804595947</t>
   </si>
   <si>
-    <t xml:space="preserve">7.56739282608032</t>
+    <t xml:space="preserve">7.56739377975464</t>
   </si>
   <si>
     <t xml:space="preserve">7.69775056838989</t>
   </si>
   <si>
-    <t xml:space="preserve">7.76125812530518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.69607925415039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.70443534851074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.7144627571106</t>
+    <t xml:space="preserve">7.76125764846802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.69607877731323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.70443630218506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.71446228027344</t>
   </si>
   <si>
     <t xml:space="preserve">7.6442699432373</t>
   </si>
   <si>
-    <t xml:space="preserve">7.72950458526611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.62588691711426</t>
+    <t xml:space="preserve">7.72950410842896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.6258864402771</t>
   </si>
   <si>
     <t xml:space="preserve">7.86487483978271</t>
@@ -4373,28 +4373,28 @@
     <t xml:space="preserve">8.06041049957275</t>
   </si>
   <si>
-    <t xml:space="preserve">7.94843673706055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.02698612213135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.01194477081299</t>
+    <t xml:space="preserve">7.94843626022339</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.02698516845703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.01194381713867</t>
   </si>
   <si>
     <t xml:space="preserve">8.10553359985352</t>
   </si>
   <si>
-    <t xml:space="preserve">8.0353422164917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.10887718200684</t>
+    <t xml:space="preserve">8.03534126281738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.10887622833252</t>
   </si>
   <si>
     <t xml:space="preserve">8.13060188293457</t>
   </si>
   <si>
-    <t xml:space="preserve">8.17572593688965</t>
+    <t xml:space="preserve">8.17572784423828</t>
   </si>
   <si>
     <t xml:space="preserve">8.12391757965088</t>
@@ -4403,10 +4403,10 @@
     <t xml:space="preserve">8.16068458557129</t>
   </si>
   <si>
-    <t xml:space="preserve">7.98186159133911</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.00692939758301</t>
+    <t xml:space="preserve">7.98186206817627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.00693035125732</t>
   </si>
   <si>
     <t xml:space="preserve">8.04536914825439</t>
@@ -4418,22 +4418,22 @@
     <t xml:space="preserve">8.16904067993164</t>
   </si>
   <si>
-    <t xml:space="preserve">8.14230060577393</t>
+    <t xml:space="preserve">8.14230155944824</t>
   </si>
   <si>
     <t xml:space="preserve">8.17739772796631</t>
   </si>
   <si>
-    <t xml:space="preserve">8.20246601104736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.51498794555664</t>
+    <t xml:space="preserve">8.20246696472168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.51498889923096</t>
   </si>
   <si>
     <t xml:space="preserve">8.42306995391846</t>
   </si>
   <si>
-    <t xml:space="preserve">8.43142700195312</t>
+    <t xml:space="preserve">8.43142604827881</t>
   </si>
   <si>
     <t xml:space="preserve">8.43978214263916</t>
@@ -4442,13 +4442,13 @@
     <t xml:space="preserve">8.57348251342773</t>
   </si>
   <si>
-    <t xml:space="preserve">8.3980016708374</t>
+    <t xml:space="preserve">8.39800262451172</t>
   </si>
   <si>
     <t xml:space="preserve">8.51916599273682</t>
   </si>
   <si>
-    <t xml:space="preserve">8.4732084274292</t>
+    <t xml:space="preserve">8.47320747375488</t>
   </si>
   <si>
     <t xml:space="preserve">8.54841423034668</t>
@@ -4457,22 +4457,22 @@
     <t xml:space="preserve">8.5442361831665</t>
   </si>
   <si>
-    <t xml:space="preserve">8.2793436050415</t>
+    <t xml:space="preserve">8.27934265136719</t>
   </si>
   <si>
     <t xml:space="preserve">8.33783626556396</t>
   </si>
   <si>
-    <t xml:space="preserve">8.23589134216309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.35287761688232</t>
+    <t xml:space="preserve">8.23589038848877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.35287857055664</t>
   </si>
   <si>
     <t xml:space="preserve">8.52334499359131</t>
   </si>
   <si>
-    <t xml:space="preserve">8.39382457733154</t>
+    <t xml:space="preserve">8.39382266998291</t>
   </si>
   <si>
     <t xml:space="preserve">8.38964557647705</t>
@@ -4481,22 +4481,22 @@
     <t xml:space="preserve">8.46485137939453</t>
   </si>
   <si>
-    <t xml:space="preserve">8.61944198608398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.56512641906738</t>
+    <t xml:space="preserve">8.61944103240967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.56512546539307</t>
   </si>
   <si>
     <t xml:space="preserve">8.54005813598633</t>
   </si>
   <si>
-    <t xml:space="preserve">8.48156356811523</t>
+    <t xml:space="preserve">8.48156261444092</t>
   </si>
   <si>
     <t xml:space="preserve">8.34619235992432</t>
   </si>
   <si>
-    <t xml:space="preserve">8.00860214233398</t>
+    <t xml:space="preserve">8.00860118865967</t>
   </si>
   <si>
     <t xml:space="preserve">8.13561630249023</t>
@@ -4505,7 +4505,7 @@
     <t xml:space="preserve">7.74287366867065</t>
   </si>
   <si>
-    <t xml:space="preserve">7.53062534332275</t>
+    <t xml:space="preserve">7.53062677383423</t>
   </si>
   <si>
     <t xml:space="preserve">7.6091742515564</t>
@@ -4514,94 +4514,94 @@
     <t xml:space="preserve">7.86821699142456</t>
   </si>
   <si>
-    <t xml:space="preserve">7.81640911102295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.83145046234131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.68437957763672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.8247652053833</t>
+    <t xml:space="preserve">7.81640863418579</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.83144855499268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.68438005447388</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.82476568222046</t>
   </si>
   <si>
     <t xml:space="preserve">7.95010805130005</t>
   </si>
   <si>
-    <t xml:space="preserve">7.86320352554321</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.7930121421814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.63257122039795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.72281789779663</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.81306600570679</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.84649229049683</t>
+    <t xml:space="preserve">7.8632025718689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.79301166534424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.63257217407227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.72281885147095</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.81306552886963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.84649181365967</t>
   </si>
   <si>
     <t xml:space="preserve">7.9751763343811</t>
   </si>
   <si>
-    <t xml:space="preserve">7.85484647750854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.90832567214966</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.99188947677612</t>
+    <t xml:space="preserve">7.85484790802002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.90832614898682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.99188899993896</t>
   </si>
   <si>
     <t xml:space="preserve">7.91334104537964</t>
   </si>
   <si>
-    <t xml:space="preserve">8.00525856018066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.928382396698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.86988830566406</t>
+    <t xml:space="preserve">8.00525951385498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.92838191986084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.86988878250122</t>
   </si>
   <si>
     <t xml:space="preserve">7.9584641456604</t>
   </si>
   <si>
-    <t xml:space="preserve">7.68939447402954</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.75791549682617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.67268228530884</t>
+    <t xml:space="preserve">7.68939399719238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.75791501998901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.67268180847168</t>
   </si>
   <si>
     <t xml:space="preserve">7.91835403442383</t>
   </si>
   <si>
-    <t xml:space="preserve">7.95679235458374</t>
+    <t xml:space="preserve">7.95679378509521</t>
   </si>
   <si>
     <t xml:space="preserve">8.04035568237305</t>
   </si>
   <si>
-    <t xml:space="preserve">7.94175100326538</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.02531337738037</t>
+    <t xml:space="preserve">7.94175291061401</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.02531433105469</t>
   </si>
   <si>
     <t xml:space="preserve">8.09717655181885</t>
   </si>
   <si>
-    <t xml:space="preserve">8.04703998565674</t>
+    <t xml:space="preserve">8.04703903198242</t>
   </si>
   <si>
     <t xml:space="preserve">8.09550666809082</t>
@@ -4616,70 +4616,70 @@
     <t xml:space="preserve">8.27433013916016</t>
   </si>
   <si>
-    <t xml:space="preserve">8.08715057373047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.18575382232666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.16402816772461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.10219097137451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.15567111968994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.35622119903564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.27767181396484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.30775356292725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.3361644744873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.27600193023682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.34786415100098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.37293338775635</t>
+    <t xml:space="preserve">8.08714962005615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.18575286865234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.16402721405029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.10219192504883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.15567207336426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.35622024536133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.27767276763916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.30775451660156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.33616542816162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.2760009765625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.34786319732666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.37293243408203</t>
   </si>
   <si>
     <t xml:space="preserve">8.43560409545898</t>
   </si>
   <si>
-    <t xml:space="preserve">8.41053581237793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.4300594329834</t>
+    <t xml:space="preserve">8.41053485870361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.43006134033203</t>
   </si>
   <si>
     <t xml:space="preserve">8.34443187713623</t>
   </si>
   <si>
-    <t xml:space="preserve">8.31647109985352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.28326892852783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.31996631622314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.29200553894043</t>
+    <t xml:space="preserve">8.3164701461792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.28326797485352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.31996726989746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.29200649261475</t>
   </si>
   <si>
     <t xml:space="preserve">8.49471855163574</t>
   </si>
   <si>
-    <t xml:space="preserve">8.59782409667969</t>
+    <t xml:space="preserve">8.59782314300537</t>
   </si>
   <si>
     <t xml:space="preserve">8.61180305480957</t>
@@ -4688,16 +4688,16 @@
     <t xml:space="preserve">8.66422843933105</t>
   </si>
   <si>
-    <t xml:space="preserve">8.63976287841797</t>
+    <t xml:space="preserve">8.63976383209229</t>
   </si>
   <si>
     <t xml:space="preserve">8.63277244567871</t>
   </si>
   <si>
-    <t xml:space="preserve">8.59957027435303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.47374725341797</t>
+    <t xml:space="preserve">8.59957122802734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.47374820709229</t>
   </si>
   <si>
     <t xml:space="preserve">8.53840732574463</t>
@@ -4715,28 +4715,28 @@
     <t xml:space="preserve">8.6956844329834</t>
   </si>
   <si>
-    <t xml:space="preserve">8.6817045211792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.68519878387451</t>
+    <t xml:space="preserve">8.68170356750488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.6851978302002</t>
   </si>
   <si>
     <t xml:space="preserve">8.70966529846191</t>
   </si>
   <si>
-    <t xml:space="preserve">8.82500076293945</t>
+    <t xml:space="preserve">8.82500171661377</t>
   </si>
   <si>
     <t xml:space="preserve">8.83373832702637</t>
   </si>
   <si>
-    <t xml:space="preserve">8.93859100341797</t>
+    <t xml:space="preserve">8.93859004974365</t>
   </si>
   <si>
     <t xml:space="preserve">9.03033447265625</t>
   </si>
   <si>
-    <t xml:space="preserve">9.00412273406982</t>
+    <t xml:space="preserve">9.00412178039551</t>
   </si>
   <si>
     <t xml:space="preserve">9.09586715698242</t>
@@ -4745,49 +4745,49 @@
     <t xml:space="preserve">9.08276176452637</t>
   </si>
   <si>
-    <t xml:space="preserve">8.98664665222168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.79005146026611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.78568267822266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.80315589904785</t>
+    <t xml:space="preserve">8.98664569854736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.7900505065918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.78568172454834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.80315685272217</t>
   </si>
   <si>
     <t xml:space="preserve">8.67995643615723</t>
   </si>
   <si>
-    <t xml:space="preserve">8.81626415252686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.88616466522217</t>
+    <t xml:space="preserve">8.81626319885254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.88616371154785</t>
   </si>
   <si>
     <t xml:space="preserve">8.85558319091797</t>
   </si>
   <si>
-    <t xml:space="preserve">8.87742614746094</t>
+    <t xml:space="preserve">8.87742710113525</t>
   </si>
   <si>
     <t xml:space="preserve">8.77257537841797</t>
   </si>
   <si>
-    <t xml:space="preserve">8.73762512207031</t>
+    <t xml:space="preserve">8.737624168396</t>
   </si>
   <si>
     <t xml:space="preserve">8.75510025024414</t>
   </si>
   <si>
-    <t xml:space="preserve">8.78131198883057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.79441928863525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.82063102722168</t>
+    <t xml:space="preserve">8.78131294250488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.79441833496094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.82063293457031</t>
   </si>
   <si>
     <t xml:space="preserve">8.94732666015625</t>
@@ -4796,16 +4796,16 @@
     <t xml:space="preserve">9.02159786224365</t>
   </si>
   <si>
-    <t xml:space="preserve">8.96043491363525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.93422222137451</t>
+    <t xml:space="preserve">8.96043395996094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.9342212677002</t>
   </si>
   <si>
     <t xml:space="preserve">8.87305736541748</t>
   </si>
   <si>
-    <t xml:space="preserve">8.79878711700439</t>
+    <t xml:space="preserve">8.79878807067871</t>
   </si>
   <si>
     <t xml:space="preserve">8.99538516998291</t>
@@ -4814,7 +4814,7 @@
     <t xml:space="preserve">8.89490222930908</t>
   </si>
   <si>
-    <t xml:space="preserve">8.8424768447876</t>
+    <t xml:space="preserve">8.84247493743896</t>
   </si>
   <si>
     <t xml:space="preserve">8.83810710906982</t>
@@ -4835,7 +4835,7 @@
     <t xml:space="preserve">8.62054061889648</t>
   </si>
   <si>
-    <t xml:space="preserve">8.45452499389648</t>
+    <t xml:space="preserve">8.4545259475708</t>
   </si>
   <si>
     <t xml:space="preserve">8.36015892028809</t>
@@ -4853,10 +4853,10 @@
     <t xml:space="preserve">8.52966976165771</t>
   </si>
   <si>
-    <t xml:space="preserve">8.59257888793945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.51743602752686</t>
+    <t xml:space="preserve">8.59258079528809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.51743698120117</t>
   </si>
   <si>
     <t xml:space="preserve">8.62578296661377</t>
@@ -4865,10 +4865,10 @@
     <t xml:space="preserve">8.64850044250488</t>
   </si>
   <si>
-    <t xml:space="preserve">8.46326351165771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.02812957763672</t>
+    <t xml:space="preserve">8.4632625579834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.0281286239624</t>
   </si>
   <si>
     <t xml:space="preserve">8.00890731811523</t>
@@ -4877,37 +4877,37 @@
     <t xml:space="preserve">8.01240253448486</t>
   </si>
   <si>
-    <t xml:space="preserve">7.95123910903931</t>
+    <t xml:space="preserve">7.95123958587646</t>
   </si>
   <si>
     <t xml:space="preserve">8.06482696533203</t>
   </si>
   <si>
-    <t xml:space="preserve">7.98793649673462</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.03686714172363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.16094303131104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.14521408081055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.24307632446289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.3269567489624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.37239170074463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.634521484375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.73587799072266</t>
+    <t xml:space="preserve">7.98793697357178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.03686809539795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.16094207763672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.14521312713623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.24307537078857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.32695579528809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.37239265441895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.63452053070068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.73587703704834</t>
   </si>
   <si>
     <t xml:space="preserve">8.76383781433105</t>
@@ -4916,25 +4916,25 @@
     <t xml:space="preserve">8.919264793396</t>
   </si>
   <si>
-    <t xml:space="preserve">8.83874988555908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.79401874542236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.79938697814941</t>
+    <t xml:space="preserve">8.83874893188477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.79401969909668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.79938793182373</t>
   </si>
   <si>
     <t xml:space="preserve">8.83338165283203</t>
   </si>
   <si>
-    <t xml:space="preserve">8.73318672180176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.79222965240479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.77970600128174</t>
+    <t xml:space="preserve">8.73318576812744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.7922306060791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.77970504760742</t>
   </si>
   <si>
     <t xml:space="preserve">8.83517169952393</t>
@@ -4952,7 +4952,7 @@
     <t xml:space="preserve">8.95952224731445</t>
   </si>
   <si>
-    <t xml:space="preserve">8.92284297943115</t>
+    <t xml:space="preserve">8.92284393310547</t>
   </si>
   <si>
     <t xml:space="preserve">8.97741413116455</t>
@@ -4961,19 +4961,19 @@
     <t xml:space="preserve">9.02214527130127</t>
   </si>
   <si>
-    <t xml:space="preserve">8.98636150360107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.05345630645752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.1473913192749</t>
+    <t xml:space="preserve">8.98636054992676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.0534553527832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.14739036560059</t>
   </si>
   <si>
     <t xml:space="preserve">9.12502479553223</t>
   </si>
   <si>
-    <t xml:space="preserve">9.10713386535645</t>
+    <t xml:space="preserve">9.10713291168213</t>
   </si>
   <si>
     <t xml:space="preserve">9.19212055206299</t>
@@ -5009,7 +5009,7 @@
     <t xml:space="preserve">9.03109169006348</t>
   </si>
   <si>
-    <t xml:space="preserve">9.07582187652588</t>
+    <t xml:space="preserve">9.0758228302002</t>
   </si>
   <si>
     <t xml:space="preserve">9.08029365539551</t>
@@ -5030,13 +5030,13 @@
     <t xml:space="preserve">9.13844394683838</t>
   </si>
   <si>
-    <t xml:space="preserve">9.22343349456787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.2279052734375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.99530601501465</t>
+    <t xml:space="preserve">9.22343254089355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.22790622711182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.99530696868896</t>
   </si>
   <si>
     <t xml:space="preserve">8.94252490997314</t>
@@ -5045,10 +5045,10 @@
     <t xml:space="preserve">9.00425148010254</t>
   </si>
   <si>
-    <t xml:space="preserve">9.0087251663208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.02661895751953</t>
+    <t xml:space="preserve">9.00872611999512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.02661800384521</t>
   </si>
   <si>
     <t xml:space="preserve">8.88705825805664</t>
@@ -5063,10 +5063,10 @@
     <t xml:space="preserve">8.81906795501709</t>
   </si>
   <si>
-    <t xml:space="preserve">8.90137195587158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.03556346893311</t>
+    <t xml:space="preserve">8.9013729095459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.03556442260742</t>
   </si>
   <si>
     <t xml:space="preserve">9.04450988769531</t>
@@ -5090,10 +5090,10 @@
     <t xml:space="preserve">10.0956773757935</t>
   </si>
   <si>
-    <t xml:space="preserve">10.033055305481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1896123886108</t>
+    <t xml:space="preserve">10.0330543518066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1896114349365</t>
   </si>
   <si>
     <t xml:space="preserve">10.252233505249</t>
@@ -5102,7 +5102,7 @@
     <t xml:space="preserve">10.2924919128418</t>
   </si>
   <si>
-    <t xml:space="preserve">10.350640296936</t>
+    <t xml:space="preserve">10.3506412506104</t>
   </si>
   <si>
     <t xml:space="preserve">10.399845123291</t>
@@ -5111,10 +5111,10 @@
     <t xml:space="preserve">10.4177370071411</t>
   </si>
   <si>
-    <t xml:space="preserve">10.475887298584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4848327636719</t>
+    <t xml:space="preserve">10.4758863449097</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4848337173462</t>
   </si>
   <si>
     <t xml:space="preserve">10.5385093688965</t>
@@ -5126,7 +5126,7 @@
     <t xml:space="preserve">10.2611808776855</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2835445404053</t>
+    <t xml:space="preserve">10.2835454940796</t>
   </si>
   <si>
     <t xml:space="preserve">10.2343416213989</t>
@@ -5144,13 +5144,13 @@
     <t xml:space="preserve">10.3819522857666</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3148555755615</t>
+    <t xml:space="preserve">10.3148565292358</t>
   </si>
   <si>
     <t xml:space="preserve">10.4356288909912</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3059120178223</t>
+    <t xml:space="preserve">10.3059110641479</t>
   </si>
   <si>
     <t xml:space="preserve">10.4535217285156</t>
@@ -5165,7 +5165,7 @@
     <t xml:space="preserve">10.3551139831543</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4311561584473</t>
+    <t xml:space="preserve">10.4311571121216</t>
   </si>
   <si>
     <t xml:space="preserve">10.2880182266235</t>
@@ -5174,7 +5174,7 @@
     <t xml:space="preserve">10.2745990753174</t>
   </si>
   <si>
-    <t xml:space="preserve">10.426682472229</t>
+    <t xml:space="preserve">10.4266834259033</t>
   </si>
   <si>
     <t xml:space="preserve">10.4222097396851</t>
@@ -5186,7 +5186,7 @@
     <t xml:space="preserve">10.6682281494141</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5519285202026</t>
+    <t xml:space="preserve">10.551929473877</t>
   </si>
   <si>
     <t xml:space="preserve">10.5564012527466</t>
@@ -5207,10 +5207,10 @@
     <t xml:space="preserve">11.0573825836182</t>
   </si>
   <si>
-    <t xml:space="preserve">11.017126083374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9723958969116</t>
+    <t xml:space="preserve">11.0171251296997</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9723968505859</t>
   </si>
   <si>
     <t xml:space="preserve">11.0081796646118</t>
@@ -5225,22 +5225,22 @@
     <t xml:space="preserve">11.0797491073608</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0931673049927</t>
+    <t xml:space="preserve">11.093168258667</t>
   </si>
   <si>
     <t xml:space="preserve">11.0618562698364</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1200075149536</t>
+    <t xml:space="preserve">11.1200065612793</t>
   </si>
   <si>
     <t xml:space="preserve">11.0350179672241</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1110601425171</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2989282608032</t>
+    <t xml:space="preserve">11.1110591888428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2989292144775</t>
   </si>
   <si>
     <t xml:space="preserve">11.2810354232788</t>
@@ -5255,7 +5255,7 @@
     <t xml:space="preserve">11.2720909118652</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5091619491577</t>
+    <t xml:space="preserve">11.5091609954834</t>
   </si>
   <si>
     <t xml:space="preserve">11.4420652389526</t>
@@ -5276,16 +5276,16 @@
     <t xml:space="preserve">11.0842218399048</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8918800354004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1155338287354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.289981842041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2407779693604</t>
+    <t xml:space="preserve">10.8918809890747</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.115532875061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2899808883667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2407789230347</t>
   </si>
   <si>
     <t xml:space="preserve">11.2716856002808</t>
@@ -6192,6 +6192,9 @@
   </si>
   <si>
     <t xml:space="preserve">20.4400005340576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4699993133545</t>
   </si>
 </sst>
 </file>
@@ -71166,7 +71169,7 @@
     </row>
     <row r="2487">
       <c r="A2487" s="1" t="n">
-        <v>45940.6500810185</v>
+        <v>45940.2916666667</v>
       </c>
       <c r="B2487" t="n">
         <v>1477655</v>
@@ -71187,6 +71190,32 @@
         <v>2059</v>
       </c>
       <c r="H2487" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2488">
+      <c r="A2488" s="1" t="n">
+        <v>45943.652025463</v>
+      </c>
+      <c r="B2488" t="n">
+        <v>1350205</v>
+      </c>
+      <c r="C2488" t="n">
+        <v>20.6800003051758</v>
+      </c>
+      <c r="D2488" t="n">
+        <v>20.4099998474121</v>
+      </c>
+      <c r="E2488" t="n">
+        <v>20.6000003814697</v>
+      </c>
+      <c r="F2488" t="n">
+        <v>20.4699993133545</v>
+      </c>
+      <c r="G2488" t="s">
+        <v>2060</v>
+      </c>
+      <c r="H2488" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/PST.MI.xlsx
+++ b/data/PST.MI.xlsx
@@ -38,31 +38,31 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">3.90457510948181</t>
+    <t xml:space="preserve">3.90457582473755</t>
   </si>
   <si>
     <t xml:space="preserve">PST.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">4.03631591796875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.97464990615845</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95222663879395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.91578722000122</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8793478012085</t>
+    <t xml:space="preserve">4.03631639480591</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97465014457703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95222687721252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9157874584198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87934875488281</t>
   </si>
   <si>
     <t xml:space="preserve">3.97184777259827</t>
   </si>
   <si>
-    <t xml:space="preserve">4.01949834823608</t>
+    <t xml:space="preserve">4.01949787139893</t>
   </si>
   <si>
     <t xml:space="preserve">3.99707460403442</t>
@@ -71,64 +71,64 @@
     <t xml:space="preserve">3.94661974906921</t>
   </si>
   <si>
-    <t xml:space="preserve">3.82889413833618</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.75601625442505</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.5485942363739</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.68594121932983</t>
+    <t xml:space="preserve">3.82889437675476</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.75601577758789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.54859471321106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.68594169616699</t>
   </si>
   <si>
     <t xml:space="preserve">3.73359251022339</t>
   </si>
   <si>
-    <t xml:space="preserve">3.655109167099</t>
+    <t xml:space="preserve">3.65510869026184</t>
   </si>
   <si>
     <t xml:space="preserve">3.76162266731262</t>
   </si>
   <si>
-    <t xml:space="preserve">3.8092737197876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73078989982605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.82609152793884</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.72238063812256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64389681816101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.53177690505981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.35518789291382</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.00481271743774</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.8982994556427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.17019009590149</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.03284335136414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.04405522346497</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.13655424118042</t>
+    <t xml:space="preserve">3.80927348136902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73078942298889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.82609128952026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.72238039970398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64389705657959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.53177666664124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.3551881313324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.0048131942749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.89829969406128</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.17018961906433</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.03284287452698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.04405474662781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13655376434326</t>
   </si>
   <si>
     <t xml:space="preserve">3.12253952026367</t>
@@ -137,79 +137,79 @@
     <t xml:space="preserve">3.24867391586304</t>
   </si>
   <si>
-    <t xml:space="preserve">3.23465847969055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.30473470687866</t>
+    <t xml:space="preserve">3.23465943336487</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.30473375320435</t>
   </si>
   <si>
     <t xml:space="preserve">3.42245984077454</t>
   </si>
   <si>
-    <t xml:space="preserve">3.34677910804749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.31314253807068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.40844511985779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.45609569549561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.51495933532715</t>
+    <t xml:space="preserve">3.34677934646606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.31314325332642</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.40844535827637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.45609617233276</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.51495862007141</t>
   </si>
   <si>
     <t xml:space="preserve">3.48412609100342</t>
   </si>
   <si>
-    <t xml:space="preserve">3.45329284667969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.47571635246277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.43647527694702</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.45889902114868</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.43367123603821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61306428909302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.6382908821106</t>
+    <t xml:space="preserve">3.45329236984253</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.47571682929993</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.43647480010986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.45889925956726</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.43367171287537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61306357383728</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.63829040527344</t>
   </si>
   <si>
     <t xml:space="preserve">3.63548827171326</t>
   </si>
   <si>
-    <t xml:space="preserve">3.60745739936829</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.5878369808197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.60185146331787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.67192673683167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.79525899887085</t>
+    <t xml:space="preserve">3.60745787620544</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.58783721923828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.60185194015503</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.67192649841309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.79525828361511</t>
   </si>
   <si>
     <t xml:space="preserve">3.77844047546387</t>
   </si>
   <si>
-    <t xml:space="preserve">3.71397137641907</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.78404664993286</t>
+    <t xml:space="preserve">3.7139720916748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.78404712677002</t>
   </si>
   <si>
     <t xml:space="preserve">3.72798657417297</t>
@@ -218,91 +218,91 @@
     <t xml:space="preserve">3.67753291130066</t>
   </si>
   <si>
-    <t xml:space="preserve">3.61586713790894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.51215529441833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.56821608543396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.58503365516663</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.60465478897095</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.62147212028503</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.6999568939209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.63268446922302</t>
+    <t xml:space="preserve">3.61586666107178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.51215577125549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.56821537017822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.58503413200378</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.60465431213379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.62147307395935</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.69995665550232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.6326847076416</t>
   </si>
   <si>
     <t xml:space="preserve">3.6298816204071</t>
   </si>
   <si>
-    <t xml:space="preserve">3.6579122543335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.6270797252655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.674729347229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.68033576011658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.74480485916138</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.79245567321777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80086445808411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73919892311096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.68313789367676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.76722860336304</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.79806137084961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77563738822937</t>
+    <t xml:space="preserve">3.65791153907776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.62707853317261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.67472958564758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.68033599853516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.74480438232422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.79245519638062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.80086421966553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73919796943665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.68313837051392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.76722812652588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.79806184768677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77563762664795</t>
   </si>
   <si>
     <t xml:space="preserve">3.75881958007812</t>
   </si>
   <si>
-    <t xml:space="preserve">3.78684949874878</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.68874549865723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.78965282440186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.74760770797729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83169746398926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83730340003967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80647039413452</t>
+    <t xml:space="preserve">3.78684997558594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.68874478340149</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.78965258598328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.74760699272156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.83169794082642</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.83730363845825</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.80647087097168</t>
   </si>
   <si>
     <t xml:space="preserve">3.85972762107849</t>
@@ -320,130 +320,130 @@
     <t xml:space="preserve">3.8541214466095</t>
   </si>
   <si>
-    <t xml:space="preserve">3.92419576644897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93260526657104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84010601043701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.78124380111694</t>
+    <t xml:space="preserve">3.92419672012329</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93260598182678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84010648727417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.78124356269836</t>
   </si>
   <si>
     <t xml:space="preserve">3.76442551612854</t>
   </si>
   <si>
-    <t xml:space="preserve">3.87654590606689</t>
+    <t xml:space="preserve">3.87654519081116</t>
   </si>
   <si>
     <t xml:space="preserve">3.96498346328735</t>
   </si>
   <si>
-    <t xml:space="preserve">3.91486883163452</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90602469444275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95024371147156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.63776206970215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.42256140708923</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.51394820213318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.50805258750916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.60533380508423</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.52574038505554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.43730163574219</t>
+    <t xml:space="preserve">3.91486811637878</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90602540969849</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95024347305298</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.63776230812073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.42256212234497</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.5139479637146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.50805234909058</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.60533452033997</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.52574062347412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.43730187416077</t>
   </si>
   <si>
     <t xml:space="preserve">3.39897871017456</t>
   </si>
   <si>
-    <t xml:space="preserve">3.37244749069214</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.49920845031738</t>
+    <t xml:space="preserve">3.37244701385498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.49920868873596</t>
   </si>
   <si>
     <t xml:space="preserve">3.65839767456055</t>
   </si>
   <si>
-    <t xml:space="preserve">3.64955401420593</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73504424095154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.67018985748291</t>
+    <t xml:space="preserve">3.64955449104309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73504447937012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.67018914222717</t>
   </si>
   <si>
     <t xml:space="preserve">3.67313742637634</t>
   </si>
   <si>
-    <t xml:space="preserve">3.65250158309937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.70851302146912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.69672107696533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.6554491519928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64660620689392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.60238695144653</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.58469915390015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.5286877155304</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80284738540649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.78221082687378</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80874228477478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8146390914917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.86770153045654</t>
+    <t xml:space="preserve">3.65250182151794</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.70851230621338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.69672083854675</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.65544939041138</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64660549163818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.60238671302795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.58469891548157</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.52868819236755</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.80284762382507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.78221154212952</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.80874300003052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.81463861465454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.86770224571228</t>
   </si>
   <si>
     <t xml:space="preserve">3.87949419021606</t>
   </si>
   <si>
-    <t xml:space="preserve">3.79989910125732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.72325325012207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.7615749835968</t>
+    <t xml:space="preserve">3.79989838600159</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.72325134277344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.76157522201538</t>
   </si>
   <si>
     <t xml:space="preserve">3.66724133491516</t>
@@ -452,28 +452,28 @@
     <t xml:space="preserve">3.68198156356812</t>
   </si>
   <si>
-    <t xml:space="preserve">3.74388766288757</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.70261645317078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66134572029114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.67903304100037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.62597060203552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.69377255439758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.68492937088013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.70556473731995</t>
+    <t xml:space="preserve">3.74388742446899</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.70261669158936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.6613450050354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.67903280258179</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.62597036361694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.69377303123474</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.68492889404297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.70556497573853</t>
   </si>
   <si>
     <t xml:space="preserve">3.71735644340515</t>
@@ -482,52 +482,52 @@
     <t xml:space="preserve">3.77631521224976</t>
   </si>
   <si>
-    <t xml:space="preserve">3.76452398300171</t>
+    <t xml:space="preserve">3.76452350616455</t>
   </si>
   <si>
     <t xml:space="preserve">3.56406354904175</t>
   </si>
   <si>
-    <t xml:space="preserve">3.61712670326233</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.6141791343689</t>
+    <t xml:space="preserve">3.61712741851807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61417865753174</t>
   </si>
   <si>
     <t xml:space="preserve">3.58175110816956</t>
   </si>
   <si>
-    <t xml:space="preserve">3.59943890571594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.6082820892334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.58764696121216</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.57880353927612</t>
+    <t xml:space="preserve">3.59943842887878</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.60828256607056</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.58764672279358</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.57880306243896</t>
   </si>
   <si>
     <t xml:space="preserve">3.57290720939636</t>
   </si>
   <si>
-    <t xml:space="preserve">3.55816745758057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.56111526489258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.50215673446655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.54637598991394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.5670120716095</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.51689624786377</t>
+    <t xml:space="preserve">3.5581681728363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.56111550331116</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.50215697288513</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.54637551307678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.56701183319092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.51689720153809</t>
   </si>
   <si>
     <t xml:space="preserve">3.57585525512695</t>
@@ -536,112 +536,112 @@
     <t xml:space="preserve">3.64365792274475</t>
   </si>
   <si>
-    <t xml:space="preserve">3.62302279472351</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.51099991798401</t>
+    <t xml:space="preserve">3.62302184104919</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.51100039482117</t>
   </si>
   <si>
     <t xml:space="preserve">3.49036502838135</t>
   </si>
   <si>
-    <t xml:space="preserve">3.51984429359436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.55227160453796</t>
+    <t xml:space="preserve">3.51984453201294</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.55227208137512</t>
   </si>
   <si>
     <t xml:space="preserve">3.54342842102051</t>
   </si>
   <si>
-    <t xml:space="preserve">3.53163623809814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.52279233932495</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.47857308387756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.44024991989136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.36655139923096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.33117628097534</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.32527995109558</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.31938409805298</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.31054019927979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.2663209438324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.39603090286255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.45793747901917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.46088528633118</t>
+    <t xml:space="preserve">3.53163552284241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.52279138565063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.47857284545898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.44025039672852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.3665509223938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.33117604255676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.32527947425842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.31938433647156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.31053996086121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.26632118225098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.39603066444397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.45793771743774</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.46088552474976</t>
   </si>
   <si>
     <t xml:space="preserve">3.45204162597656</t>
   </si>
   <si>
-    <t xml:space="preserve">3.73209595680237</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.74683570861816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73799204826355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.72914886474609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77926349639893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.74094009399414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77336716651917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.79105496406555</t>
+    <t xml:space="preserve">3.73209619522095</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.74683594703674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73799180984497</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.7291476726532</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77926301956177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.74093914031982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77336764335632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.79105520248413</t>
   </si>
   <si>
     <t xml:space="preserve">3.76747155189514</t>
   </si>
   <si>
-    <t xml:space="preserve">3.71440863609314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.63481426239014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.59649062156677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.56995964050293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.5935423374176</t>
+    <t xml:space="preserve">3.71440887451172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.63481450080872</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.59649109840393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.56995892524719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.59354281425476</t>
   </si>
   <si>
     <t xml:space="preserve">3.44909405708313</t>
   </si>
   <si>
-    <t xml:space="preserve">3.42845773696899</t>
+    <t xml:space="preserve">3.42845845222473</t>
   </si>
   <si>
     <t xml:space="preserve">3.44614505767822</t>
@@ -653,28 +653,28 @@
     <t xml:space="preserve">3.53458404541016</t>
   </si>
   <si>
-    <t xml:space="preserve">3.59059524536133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.69966864585876</t>
+    <t xml:space="preserve">3.59059453010559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.69966888427734</t>
   </si>
   <si>
     <t xml:space="preserve">3.81758642196655</t>
   </si>
   <si>
-    <t xml:space="preserve">3.80579543113708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.79695081710815</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.75862836837769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.82937812805176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.79400229454041</t>
+    <t xml:space="preserve">3.80579495429993</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.79695153236389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.75862741470337</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8293788433075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.79400300979614</t>
   </si>
   <si>
     <t xml:space="preserve">3.67608547210693</t>
@@ -683,10 +683,10 @@
     <t xml:space="preserve">3.71146082878113</t>
   </si>
   <si>
-    <t xml:space="preserve">3.74978303909302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77041912078857</t>
+    <t xml:space="preserve">3.74978375434875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77041983604431</t>
   </si>
   <si>
     <t xml:space="preserve">3.68787670135498</t>
@@ -695,304 +695,301 @@
     <t xml:space="preserve">3.7527322769165</t>
   </si>
   <si>
-    <t xml:space="preserve">3.83232688903809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84411859512329</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.72030448913574</t>
+    <t xml:space="preserve">3.83232593536377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84411835670471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.72030472755432</t>
   </si>
   <si>
     <t xml:space="preserve">3.69082570075989</t>
   </si>
   <si>
-    <t xml:space="preserve">3.81169152259827</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.82053422927856</t>
+    <t xml:space="preserve">3.81169080734253</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.82053446769714</t>
   </si>
   <si>
     <t xml:space="preserve">3.78916716575623</t>
   </si>
   <si>
-    <t xml:space="preserve">3.80171394348145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.81426119804382</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.75780010223389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.76407408714294</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77662014961243</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73897933959961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.82053470611572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.78603029251099</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.76093673706055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.76721048355103</t>
+    <t xml:space="preserve">3.8017144203186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.81426095962524</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.75779914855957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.76407384872437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77662038803101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73897981643677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.7860312461853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.76093697547913</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.76721119880676</t>
   </si>
   <si>
     <t xml:space="preserve">3.74525332450867</t>
   </si>
   <si>
-    <t xml:space="preserve">3.72956919670105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.79544067382812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80485057830811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84249114990234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.82367062568665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80798816680908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.79857754707336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.75152635574341</t>
+    <t xml:space="preserve">3.72956967353821</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.79544115066528</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.80485129356384</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84249138832092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8236711025238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8079879283905</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.79857683181763</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.75152707099915</t>
   </si>
   <si>
     <t xml:space="preserve">3.74211692810059</t>
   </si>
   <si>
-    <t xml:space="preserve">3.77975606918335</t>
+    <t xml:space="preserve">3.77975749969482</t>
   </si>
   <si>
     <t xml:space="preserve">3.91463613510132</t>
   </si>
   <si>
-    <t xml:space="preserve">3.92718386650085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94600391387939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.89267945289612</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90208983421326</t>
+    <t xml:space="preserve">3.92718410491943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94600343704224</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89267921447754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9020893573761</t>
   </si>
   <si>
     <t xml:space="preserve">3.90522599220276</t>
   </si>
   <si>
-    <t xml:space="preserve">3.94286775588989</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83308148384094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84562849998474</t>
+    <t xml:space="preserve">3.94286727905273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.83308172225952</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84562873840332</t>
   </si>
   <si>
     <t xml:space="preserve">3.89895296096802</t>
   </si>
   <si>
-    <t xml:space="preserve">3.90836334228516</t>
+    <t xml:space="preserve">3.908362865448</t>
   </si>
   <si>
     <t xml:space="preserve">3.85817551612854</t>
   </si>
   <si>
-    <t xml:space="preserve">3.83935499191284</t>
+    <t xml:space="preserve">3.83935475349426</t>
   </si>
   <si>
     <t xml:space="preserve">3.8299446105957</t>
   </si>
   <si>
-    <t xml:space="preserve">3.8550386428833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.81739807128906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.86131191253662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9209098815918</t>
+    <t xml:space="preserve">3.85503840446472</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.81739711761475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.86131238937378</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92090964317322</t>
   </si>
   <si>
     <t xml:space="preserve">3.8958158493042</t>
   </si>
   <si>
-    <t xml:space="preserve">3.88640546798706</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88954257965088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.86444902420044</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8801326751709</t>
+    <t xml:space="preserve">3.88640570640564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88954281806946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.86444759368896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88013219833374</t>
   </si>
   <si>
     <t xml:space="preserve">3.85190153121948</t>
   </si>
   <si>
-    <t xml:space="preserve">3.87385940551758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9303195476532</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.86758494377136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93659424781799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94913983345032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9334568977356</t>
+    <t xml:space="preserve">3.873859167099</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93031978607178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8675856590271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93659377098083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94914078712463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93345665931702</t>
   </si>
   <si>
     <t xml:space="preserve">3.93972992897034</t>
   </si>
   <si>
-    <t xml:space="preserve">3.92404699325562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8487651348114</t>
+    <t xml:space="preserve">3.92404627799988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8487663269043</t>
   </si>
   <si>
     <t xml:space="preserve">3.83621788024902</t>
   </si>
   <si>
-    <t xml:space="preserve">3.82680797576904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99305438995361</t>
+    <t xml:space="preserve">3.82680821418762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99305486679077</t>
   </si>
   <si>
     <t xml:space="preserve">4.02128458023071</t>
   </si>
   <si>
-    <t xml:space="preserve">3.99619150161743</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98364448547363</t>
+    <t xml:space="preserve">3.99619102478027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.98364424705505</t>
   </si>
   <si>
     <t xml:space="preserve">3.97109723091125</t>
   </si>
   <si>
-    <t xml:space="preserve">3.98678112030029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99932813644409</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.01814842224121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.03383255004883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.04637908935547</t>
+    <t xml:space="preserve">3.98678135871887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99932789802551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.01814794540405</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.03383207321167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.04637956619263</t>
   </si>
   <si>
     <t xml:space="preserve">4.05892562866211</t>
   </si>
   <si>
-    <t xml:space="preserve">4.04010486602783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.07147359848022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.10284042358398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.09970378875732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.12793350219727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.2188982963562</t>
+    <t xml:space="preserve">4.04010629653931</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.07147264480591</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.10283994674683</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.09970331192017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.12793445587158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.21889877319336</t>
   </si>
   <si>
     <t xml:space="preserve">4.21576261520386</t>
   </si>
   <si>
-    <t xml:space="preserve">4.20007801055908</t>
+    <t xml:space="preserve">4.2000789642334</t>
   </si>
   <si>
     <t xml:space="preserve">4.17184829711914</t>
   </si>
   <si>
-    <t xml:space="preserve">4.18753147125244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.19694185256958</t>
+    <t xml:space="preserve">4.18753242492676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.19694232940674</t>
   </si>
   <si>
     <t xml:space="preserve">4.17310237884521</t>
   </si>
   <si>
-    <t xml:space="preserve">4.15553712844849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.18063116073608</t>
+    <t xml:space="preserve">4.15553665161133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.18063068389893</t>
   </si>
   <si>
     <t xml:space="preserve">4.13044309616089</t>
   </si>
   <si>
-    <t xml:space="preserve">4.13922643661499</t>
+    <t xml:space="preserve">4.13922595977783</t>
   </si>
   <si>
     <t xml:space="preserve">4.01501226425171</t>
   </si>
   <si>
-    <t xml:space="preserve">4.12166023254395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.04387044906616</t>
+    <t xml:space="preserve">4.1216607093811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.043869972229</t>
   </si>
   <si>
     <t xml:space="preserve">4.03759574890137</t>
   </si>
   <si>
-    <t xml:space="preserve">4.05516290664673</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.09531116485596</t>
+    <t xml:space="preserve">4.05516195297241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.09531164169312</t>
   </si>
   <si>
     <t xml:space="preserve">4.1291880607605</t>
   </si>
   <si>
-    <t xml:space="preserve">4.175612449646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.18188667297363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.25340270996094</t>
+    <t xml:space="preserve">4.17561197280884</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.18188571929932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.2534031867981</t>
   </si>
   <si>
     <t xml:space="preserve">4.2408561706543</t>
@@ -1001,22 +998,22 @@
     <t xml:space="preserve">4.20697927474976</t>
   </si>
   <si>
-    <t xml:space="preserve">4.21074342727661</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.17435741424561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.41651248931885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.43031406402588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.40271139144897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.30735445022583</t>
+    <t xml:space="preserve">4.21074390411377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.17435693740845</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.41651296615601</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.43031454086304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.40271186828613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.30735492706299</t>
   </si>
   <si>
     <t xml:space="preserve">4.33495807647705</t>
@@ -1025,52 +1022,52 @@
     <t xml:space="preserve">4.37134408950806</t>
   </si>
   <si>
-    <t xml:space="preserve">4.48677492141724</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.60095167160034</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.57711315155029</t>
+    <t xml:space="preserve">4.48677539825439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.60095262527466</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.57711410522461</t>
   </si>
   <si>
     <t xml:space="preserve">4.65490484237671</t>
   </si>
   <si>
-    <t xml:space="preserve">4.55452919006348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.49555921554565</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.56707668304443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.63859272003174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.60346221923828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.63482904434204</t>
+    <t xml:space="preserve">4.55452871322632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.49555826187134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.56707620620728</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.63859367370605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.60346078872681</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.63482856750488</t>
   </si>
   <si>
     <t xml:space="preserve">4.6260461807251</t>
   </si>
   <si>
-    <t xml:space="preserve">4.58338594436646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.54574680328369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.52943420410156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.5444917678833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.61475372314453</t>
+    <t xml:space="preserve">4.58338737487793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.54574584960938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.52943515777588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.54449081420898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.61475419998169</t>
   </si>
   <si>
     <t xml:space="preserve">4.62353706359863</t>
@@ -1079,70 +1076,70 @@
     <t xml:space="preserve">4.65866899490356</t>
   </si>
   <si>
-    <t xml:space="preserve">4.73645830154419</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.73144054412842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.76782703399658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.82052421569824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.81299591064453</t>
+    <t xml:space="preserve">4.73645973205566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.73144006729126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.76782655715942</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.82052326202393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.81299543380737</t>
   </si>
   <si>
     <t xml:space="preserve">4.81675958633423</t>
   </si>
   <si>
-    <t xml:space="preserve">4.81425094604492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.84310722351074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.88702154159546</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.85691022872925</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.86694765090942</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.93721008300781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.94222784042358</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.96355819702148</t>
+    <t xml:space="preserve">4.81424999237061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.8431077003479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.88702201843262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.85690975189209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.86694717407227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.93720960617065</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.94222831726074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.96355772018433</t>
   </si>
   <si>
     <t xml:space="preserve">4.97359561920166</t>
   </si>
   <si>
-    <t xml:space="preserve">5.00119876861572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.08526229858398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.07146167755127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.06267833709717</t>
+    <t xml:space="preserve">5.00119924545288</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.08526372909546</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.07146120071411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.06267881393433</t>
   </si>
   <si>
     <t xml:space="preserve">5.11537551879883</t>
   </si>
   <si>
-    <t xml:space="preserve">5.09153652191162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.06769800186157</t>
+    <t xml:space="preserve">5.09153699874878</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.06769752502441</t>
   </si>
   <si>
     <t xml:space="preserve">5.11286592483521</t>
@@ -1157,217 +1154,220 @@
     <t xml:space="preserve">4.95101022720337</t>
   </si>
   <si>
-    <t xml:space="preserve">4.78037309646606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.7904109954834</t>
+    <t xml:space="preserve">4.78037261962891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.79041147232056</t>
   </si>
   <si>
     <t xml:space="preserve">4.82930612564087</t>
   </si>
   <si>
-    <t xml:space="preserve">4.80546712875366</t>
+    <t xml:space="preserve">4.80546617507935</t>
   </si>
   <si>
     <t xml:space="preserve">4.83432483673096</t>
   </si>
   <si>
-    <t xml:space="preserve">4.76029777526855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.60722589492798</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.40020132064819</t>
+    <t xml:space="preserve">4.76029825210571</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.60722541809082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.40020179748535</t>
   </si>
   <si>
     <t xml:space="preserve">4.584641456604</t>
   </si>
   <si>
-    <t xml:space="preserve">4.59467935562134</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.68627119064331</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.71261978149414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.58840608596802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.58589553833008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.56833076477051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.44411659240723</t>
+    <t xml:space="preserve">4.59467887878418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.68627166748047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.7126202583313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.58840560913086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.58589649200439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.56832981109619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.44411611557007</t>
   </si>
   <si>
     <t xml:space="preserve">4.61600828170776</t>
   </si>
   <si>
-    <t xml:space="preserve">4.70383787155151</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.79292058944702</t>
+    <t xml:space="preserve">4.70383739471436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.79292011260986</t>
   </si>
   <si>
     <t xml:space="preserve">4.90584230422974</t>
   </si>
   <si>
+    <t xml:space="preserve">4.78664636611938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.86100244522095</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.9101300239563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.93270206451416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.87162351608276</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.8769359588623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.81320238113403</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.83577489852905</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.76673078536987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.76009130477905</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.80789089202881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.81984090805054</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.93403053283691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.97253513336182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.01900815963745</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.96589708328247</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.03892517089844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.02697467803955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.10000276565552</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.15311288833618</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.18099737167358</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.12124729156494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.13452529907227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.11859083175659</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.1278862953186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.21153688430786</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.23410892486572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.25668001174927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.2885479927063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.28058004379272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.99510812759399</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.94465208053589</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.92871904373169</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.86896896362305</t>
+  </si>
+  <si>
     <t xml:space="preserve">4.78664684295654</t>
   </si>
   <si>
-    <t xml:space="preserve">4.86100244522095</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.9101300239563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.93270206451416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.87162446975708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.8769359588623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.81320238113403</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.83577489852905</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.76673030853271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.76009130477905</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.80789184570312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.81984186172485</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.93403005599976</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.97253561019897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.01900768280029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.96589660644531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.03892517089844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.02697467803955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.10000324249268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.15311336517334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.18099737167358</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.12124681472778</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.13452482223511</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.11859083175659</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.12788534164429</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.21153736114502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.23410844802856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.25668096542358</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.28854751586914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.28058052062988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.99510860443115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.94465208053589</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.92871952056885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.86896848678589</t>
-  </si>
-  <si>
     <t xml:space="preserve">4.71627426147461</t>
   </si>
   <si>
     <t xml:space="preserve">4.69635772705078</t>
   </si>
   <si>
-    <t xml:space="preserve">4.74548482894897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.60474061965942</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.54764652252197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.4759464263916</t>
+    <t xml:space="preserve">4.74548625946045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.60474109649658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.54764604568481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.47594547271729</t>
   </si>
   <si>
     <t xml:space="preserve">4.61801815032959</t>
   </si>
   <si>
-    <t xml:space="preserve">4.52772951126099</t>
+    <t xml:space="preserve">4.52772998809814</t>
   </si>
   <si>
     <t xml:space="preserve">4.51046848297119</t>
   </si>
   <si>
-    <t xml:space="preserve">4.50250244140625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.48523998260498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.50515747070312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.4467339515686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.40291786193848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.47727394104004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.59544610977173</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.68440771102905</t>
+    <t xml:space="preserve">4.50250196456909</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.48524045944214</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.50515651702881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.44673442840576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.40291833877563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.47727346420288</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.59544658660889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.68440818786621</t>
   </si>
   <si>
     <t xml:space="preserve">4.65519666671753</t>
@@ -1376,7 +1376,7 @@
     <t xml:space="preserve">4.67378520965576</t>
   </si>
   <si>
-    <t xml:space="preserve">4.78133583068848</t>
+    <t xml:space="preserve">4.78133535385132</t>
   </si>
   <si>
     <t xml:space="preserve">4.75610828399658</t>
@@ -1388,52 +1388,52 @@
     <t xml:space="preserve">4.56225156784058</t>
   </si>
   <si>
-    <t xml:space="preserve">4.58880710601807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.63262414932251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.61005163192749</t>
+    <t xml:space="preserve">4.58880662918091</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.63262462615967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.61005115509033</t>
   </si>
   <si>
     <t xml:space="preserve">4.59810209274292</t>
   </si>
   <si>
-    <t xml:space="preserve">4.6605076789856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.69901371002197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.72158527374268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.77735233306885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.80523538589478</t>
+    <t xml:space="preserve">4.66050672531128</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.69901275634766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.72158479690552</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.77735185623169</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.80523586273193</t>
   </si>
   <si>
     <t xml:space="preserve">4.77336883544922</t>
   </si>
   <si>
-    <t xml:space="preserve">4.56889057159424</t>
+    <t xml:space="preserve">4.56889009475708</t>
   </si>
   <si>
     <t xml:space="preserve">4.51976251602173</t>
   </si>
   <si>
-    <t xml:space="preserve">4.43876838684082</t>
+    <t xml:space="preserve">4.43876886367798</t>
   </si>
   <si>
     <t xml:space="preserve">4.4480619430542</t>
   </si>
   <si>
-    <t xml:space="preserve">4.45204544067383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.38167333602905</t>
+    <t xml:space="preserve">4.45204591751099</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.38167381286621</t>
   </si>
   <si>
     <t xml:space="preserve">4.21968460083008</t>
@@ -1442,16 +1442,16 @@
     <t xml:space="preserve">4.24225664138794</t>
   </si>
   <si>
-    <t xml:space="preserve">4.28474617004395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.16657400131226</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.14798498153687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.16391801834106</t>
+    <t xml:space="preserve">4.28474521636963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.16657304763794</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.14798450469971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.16391754150391</t>
   </si>
   <si>
     <t xml:space="preserve">4.23296213150024</t>
@@ -1466,100 +1466,100 @@
     <t xml:space="preserve">4.16259002685547</t>
   </si>
   <si>
-    <t xml:space="preserve">4.14001846313477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.1493124961853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98201322555542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.06831741333008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.07230043411255</t>
+    <t xml:space="preserve">4.14001750946045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.14931201934814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.98201179504395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.06831789016724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.07229995727539</t>
   </si>
   <si>
     <t xml:space="preserve">4.20109558105469</t>
   </si>
   <si>
-    <t xml:space="preserve">4.10815095901489</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.21570158004761</t>
+    <t xml:space="preserve">4.10815143585205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.21570110321045</t>
   </si>
   <si>
     <t xml:space="preserve">4.3498067855835</t>
   </si>
   <si>
-    <t xml:space="preserve">4.3843297958374</t>
+    <t xml:space="preserve">4.38432931900024</t>
   </si>
   <si>
     <t xml:space="preserve">4.32325124740601</t>
   </si>
   <si>
-    <t xml:space="preserve">4.29536819458008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.43744039535522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.53038549423218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.56092405319214</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.57021856307983</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.57287406921387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.42681884765625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.31528520584106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.3259072303772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.35113477706909</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.23163461685181</t>
+    <t xml:space="preserve">4.29536771774292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.43744087219238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.53038501739502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.56092309951782</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.57021903991699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.57287454605103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.42681837081909</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.31528472900391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.32590675354004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.35113525390625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.23163414001465</t>
   </si>
   <si>
     <t xml:space="preserve">4.37105131149292</t>
   </si>
   <si>
-    <t xml:space="preserve">4.34847927093506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.54100751876831</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.51710748672485</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.44938993453979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.45071840286255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.55826807022095</t>
+    <t xml:space="preserve">4.3484787940979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.54100799560547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.5171070098877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.44939041137695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.45071792602539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.55826854705811</t>
   </si>
   <si>
     <t xml:space="preserve">4.52241849899292</t>
   </si>
   <si>
-    <t xml:space="preserve">4.5821681022644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.34051275253296</t>
+    <t xml:space="preserve">4.58216905593872</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.3405122756958</t>
   </si>
   <si>
     <t xml:space="preserve">4.36175727844238</t>
@@ -1571,13 +1571,13 @@
     <t xml:space="preserve">4.35379028320312</t>
   </si>
   <si>
-    <t xml:space="preserve">4.52905750274658</t>
+    <t xml:space="preserve">4.52905702590942</t>
   </si>
   <si>
     <t xml:space="preserve">4.60075759887695</t>
   </si>
   <si>
-    <t xml:space="preserve">4.57818508148193</t>
+    <t xml:space="preserve">4.57818460464478</t>
   </si>
   <si>
     <t xml:space="preserve">4.57154655456543</t>
@@ -1589,76 +1589,76 @@
     <t xml:space="preserve">4.65386867523193</t>
   </si>
   <si>
-    <t xml:space="preserve">4.58615207672119</t>
+    <t xml:space="preserve">4.58615159988403</t>
   </si>
   <si>
     <t xml:space="preserve">4.53569650650024</t>
   </si>
   <si>
-    <t xml:space="preserve">4.63660717010498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.62731170654297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.64590215682983</t>
+    <t xml:space="preserve">4.63660764694214</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.62731266021729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.64590263366699</t>
   </si>
   <si>
     <t xml:space="preserve">4.70299673080444</t>
   </si>
   <si>
-    <t xml:space="preserve">4.67112970352173</t>
+    <t xml:space="preserve">4.67112874984741</t>
   </si>
   <si>
     <t xml:space="preserve">4.71760177612305</t>
   </si>
   <si>
-    <t xml:space="preserve">4.78000736236572</t>
+    <t xml:space="preserve">4.78000783920288</t>
   </si>
   <si>
     <t xml:space="preserve">4.79195737838745</t>
   </si>
   <si>
-    <t xml:space="preserve">4.81453037261963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.79328489303589</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.88224744796753</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.91278553009033</t>
+    <t xml:space="preserve">4.81452989578247</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.79328584671021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.88224697113037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.91278600692749</t>
   </si>
   <si>
     <t xml:space="preserve">5.03626918792725</t>
   </si>
   <si>
-    <t xml:space="preserve">5.0455641746521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.99776411056519</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.0442361831665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.05618572235107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.10664176940918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.08406972885132</t>
+    <t xml:space="preserve">5.04556369781494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.99776363372803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.04423666000366</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.05618619918823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.10664129257202</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.084068775177</t>
   </si>
   <si>
     <t xml:space="preserve">5.09203624725342</t>
   </si>
   <si>
-    <t xml:space="preserve">4.98846912384033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.87826299667358</t>
+    <t xml:space="preserve">4.98846960067749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.8782639503479</t>
   </si>
   <si>
     <t xml:space="preserve">4.99245262145996</t>
@@ -1667,7 +1667,7 @@
     <t xml:space="preserve">5.07477474212646</t>
   </si>
   <si>
-    <t xml:space="preserve">5.10265874862671</t>
+    <t xml:space="preserve">5.10265827178955</t>
   </si>
   <si>
     <t xml:space="preserve">4.94863605499268</t>
@@ -1676,46 +1676,46 @@
     <t xml:space="preserve">4.96456909179688</t>
   </si>
   <si>
-    <t xml:space="preserve">5.02432012557983</t>
+    <t xml:space="preserve">5.02431964874268</t>
   </si>
   <si>
     <t xml:space="preserve">5.09867477416992</t>
   </si>
   <si>
-    <t xml:space="preserve">5.15045881271362</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.08938026428223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.14249134063721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.16108083724976</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.14514780044556</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.13054084777832</t>
+    <t xml:space="preserve">5.15045833587646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.08937978744507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.14249086380005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.1610803604126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.14514636993408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.13054180145264</t>
   </si>
   <si>
     <t xml:space="preserve">5.16639184951782</t>
   </si>
   <si>
-    <t xml:space="preserve">5.18763637542725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.24340295791626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.24473094940186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.26464748382568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.26863050460815</t>
+    <t xml:space="preserve">5.18763589859009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.2434024810791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.24473142623901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.2646484375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.26863145828247</t>
   </si>
   <si>
     <t xml:space="preserve">5.23941850662231</t>
@@ -1724,10 +1724,10 @@
     <t xml:space="preserve">5.26331949234009</t>
   </si>
   <si>
-    <t xml:space="preserve">5.27394199371338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.2765965461731</t>
+    <t xml:space="preserve">5.27394151687622</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.27659749984741</t>
   </si>
   <si>
     <t xml:space="preserve">5.18630838394165</t>
@@ -1736,115 +1736,115 @@
     <t xml:space="preserve">5.24605798721313</t>
   </si>
   <si>
-    <t xml:space="preserve">5.27128553390503</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.28456449508667</t>
+    <t xml:space="preserve">5.27128648757935</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.28456401824951</t>
   </si>
   <si>
     <t xml:space="preserve">5.30580854415894</t>
   </si>
   <si>
-    <t xml:space="preserve">5.36423110961914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.41070222854614</t>
+    <t xml:space="preserve">5.36423063278198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.4107027053833</t>
   </si>
   <si>
     <t xml:space="preserve">5.55011987686157</t>
   </si>
   <si>
-    <t xml:space="preserve">5.60323190689087</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.73468065261841</t>
+    <t xml:space="preserve">5.60323095321655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.73468017578125</t>
   </si>
   <si>
     <t xml:space="preserve">5.68289804458618</t>
   </si>
   <si>
-    <t xml:space="preserve">5.70281553268433</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.72538614273071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.72671508789062</t>
+    <t xml:space="preserve">5.70281457901001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.72538661956787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.72671604156494</t>
   </si>
   <si>
     <t xml:space="preserve">5.7067985534668</t>
   </si>
   <si>
-    <t xml:space="preserve">5.75725269317627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.74264812469482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.75990915298462</t>
+    <t xml:space="preserve">5.75725412368774</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.74264860153198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.75991010665894</t>
   </si>
   <si>
     <t xml:space="preserve">5.8063817024231</t>
   </si>
   <si>
-    <t xml:space="preserve">5.80239772796631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.82497072219849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.9245548248291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.94579935073853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.93650484085083</t>
+    <t xml:space="preserve">5.80239915847778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.82497119903564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.92455387115479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.94579887390137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.93650436401367</t>
   </si>
   <si>
     <t xml:space="preserve">5.96837043762207</t>
   </si>
   <si>
-    <t xml:space="preserve">5.95774841308594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.02148151397705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.97633647918701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.31757640838623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.32023239135742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.28172636032104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.14894962310791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.12372064590454</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.14231061935425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.22330570220947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.3135929107666</t>
+    <t xml:space="preserve">5.9577488899231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.02148103713989</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.97633695602417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.31757783889771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.32023286819458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.28172540664673</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.14894914627075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.12372159957886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.14230918884277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.223304271698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.31359386444092</t>
   </si>
   <si>
     <t xml:space="preserve">6.26712131500244</t>
   </si>
   <si>
-    <t xml:space="preserve">6.2060432434082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.25251579284668</t>
+    <t xml:space="preserve">6.20604276657104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.252516746521</t>
   </si>
   <si>
     <t xml:space="preserve">6.0546760559082</t>
@@ -1853,43 +1853,43 @@
     <t xml:space="preserve">5.98032093048096</t>
   </si>
   <si>
-    <t xml:space="preserve">5.97500944137573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.90596437454224</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.08787155151367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.04936504364014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.12770366668701</t>
+    <t xml:space="preserve">5.97500991821289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.90596532821655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.08787202835083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.04936599731445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.12770462036133</t>
   </si>
   <si>
     <t xml:space="preserve">5.99094343185425</t>
   </si>
   <si>
-    <t xml:space="preserve">6.04405355453491</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.08256006240845</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.82098817825317</t>
+    <t xml:space="preserve">6.04405450820923</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.08255910873413</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.82098722457886</t>
   </si>
   <si>
     <t xml:space="preserve">5.92189931869507</t>
   </si>
   <si>
-    <t xml:space="preserve">5.90729141235352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.86082077026367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.83028173446655</t>
+    <t xml:space="preserve">5.90729331970215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.86082124710083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.83028125762939</t>
   </si>
   <si>
     <t xml:space="preserve">5.77584171295166</t>
@@ -1898,295 +1898,295 @@
     <t xml:space="preserve">5.78779315948486</t>
   </si>
   <si>
-    <t xml:space="preserve">5.93517637252808</t>
+    <t xml:space="preserve">5.93517541885376</t>
   </si>
   <si>
     <t xml:space="preserve">5.89401531219482</t>
   </si>
   <si>
-    <t xml:space="preserve">5.92588138580322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.04272651672363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.09982109069824</t>
+    <t xml:space="preserve">5.92588233947754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.04272747039795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.09982061386108</t>
   </si>
   <si>
     <t xml:space="preserve">6.12903261184692</t>
   </si>
   <si>
-    <t xml:space="preserve">6.1529335975647</t>
+    <t xml:space="preserve">6.15293264389038</t>
   </si>
   <si>
     <t xml:space="preserve">6.12106561660767</t>
   </si>
   <si>
-    <t xml:space="preserve">6.16753673553467</t>
+    <t xml:space="preserve">6.16753721237183</t>
   </si>
   <si>
     <t xml:space="preserve">6.22197675704956</t>
   </si>
   <si>
-    <t xml:space="preserve">6.31624937057495</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.42833089828491</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.38377714157104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.35732221603394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.36289167404175</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.44643068313599</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.43529319763184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.58984088897705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.74577951431274</t>
+    <t xml:space="preserve">6.31624889373779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.42833137512207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.38377809524536</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.35732173919678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.36289310455322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.4464316368103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.43529224395752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.58983898162842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.74577903747559</t>
   </si>
   <si>
     <t xml:space="preserve">6.78754854202271</t>
   </si>
   <si>
-    <t xml:space="preserve">6.76248598098755</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.75274133682251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.72071743011475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.78615665435791</t>
+    <t xml:space="preserve">6.76248788833618</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.75273942947388</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.72071695327759</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.78615760803223</t>
   </si>
   <si>
     <t xml:space="preserve">6.71932554244995</t>
   </si>
   <si>
-    <t xml:space="preserve">6.72350168228149</t>
+    <t xml:space="preserve">6.72350263595581</t>
   </si>
   <si>
     <t xml:space="preserve">6.69426298141479</t>
   </si>
   <si>
-    <t xml:space="preserve">6.67337989807129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.65945625305176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.54389238357544</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.57313203811646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.53136205673218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.59540939331055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.54807090759277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.67477035522461</t>
+    <t xml:space="preserve">6.67337894439697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.65945482254028</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.54389190673828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.57313299179077</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.53136157989502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.59540843963623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.5480694770813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.67477130889893</t>
   </si>
   <si>
     <t xml:space="preserve">6.50073051452637</t>
   </si>
   <si>
-    <t xml:space="preserve">6.72489404678345</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.79172563552856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.71236276626587</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.60515403747559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.60097789764404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.7095799446106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.26125335693359</t>
+    <t xml:space="preserve">6.72489452362061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.79172468185425</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.71236371994019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.60515546798706</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.6009783744812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.70957899093628</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.26125288009644</t>
   </si>
   <si>
     <t xml:space="preserve">6.33504486083984</t>
   </si>
   <si>
-    <t xml:space="preserve">6.48123931884766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.3656759262085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.61350917816162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.56756353378296</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.75134754180908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.7276782989502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.55781650543213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.61211729049683</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.54250049591064</t>
+    <t xml:space="preserve">6.4812388420105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.36567640304565</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.61350870132446</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.56756210327148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.75134801864624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.72767782211304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.55781698226929</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.61211585998535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.54250001907349</t>
   </si>
   <si>
     <t xml:space="preserve">6.85020351409912</t>
   </si>
   <si>
-    <t xml:space="preserve">6.80286455154419</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.8752646446228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.89197206497192</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.02424240112305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.99639654159546</t>
+    <t xml:space="preserve">6.80286407470703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.87526512145996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.89197254180908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.02424335479736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.9963960647583</t>
   </si>
   <si>
     <t xml:space="preserve">7.01380014419556</t>
   </si>
   <si>
-    <t xml:space="preserve">7.0172815322876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.89893484115601</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.92678117752075</t>
+    <t xml:space="preserve">7.01727962493896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.89893436431885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.92678022384644</t>
   </si>
   <si>
     <t xml:space="preserve">7.04860830307007</t>
   </si>
   <si>
-    <t xml:space="preserve">7.0903787612915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.00335884094238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.94348859786987</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.07297325134277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.08689641952515</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.00683975219727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.15303182601929</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.11126375198364</t>
+    <t xml:space="preserve">7.09037828445435</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.0033597946167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.94348907470703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.07297420501709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.08689832687378</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.00683832168579</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.15303230285645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.11126327514648</t>
   </si>
   <si>
     <t xml:space="preserve">7.10778141021729</t>
   </si>
   <si>
-    <t xml:space="preserve">7.1425895690918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.26093578338623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.15999460220337</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.93652725219727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.95184326171875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.94766521453857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.14606952667236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.05208921432495</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.13562822341919</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.36536121368408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.37580347061157</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.47674512863159</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.36884117126465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.45238018035889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.49414968490601</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.51851415634155</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.60553598403931</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.62293863296509</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.65078592300415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.56028509140015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.59509134292603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.58116912841797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.57420778274536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.6786322593689</t>
+    <t xml:space="preserve">7.14258909225464</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.26093626022339</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.15999317169189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.93652629852295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.95184278488159</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.94766473770142</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.14607048034668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.05209016799927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.13562917709351</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.36536169052124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.37580251693726</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.47674608230591</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.36884212493896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.45237970352173</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.49414873123169</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.51851511001587</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.60553503036499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.6229395866394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.65078496932983</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.56028318405151</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.59509181976318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.58117151260376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.57420825958252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.67863130569458</t>
   </si>
   <si>
     <t xml:space="preserve">7.72388219833374</t>
@@ -2195,118 +2195,118 @@
     <t xml:space="preserve">7.77609395980835</t>
   </si>
   <si>
-    <t xml:space="preserve">7.65426635742188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.54636192321777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.63686275482178</t>
+    <t xml:space="preserve">7.65426540374756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.54636144638062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.63686084747314</t>
   </si>
   <si>
     <t xml:space="preserve">7.80045986175537</t>
   </si>
   <si>
-    <t xml:space="preserve">7.73780393600464</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.75521087646484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.76913166046143</t>
+    <t xml:space="preserve">7.73780488967896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.75521039962769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.76913213729858</t>
   </si>
   <si>
     <t xml:space="preserve">7.81078100204468</t>
   </si>
   <si>
-    <t xml:space="preserve">7.67666101455688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.7472505569458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.65195369720459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.71548557281494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.73666095733643</t>
+    <t xml:space="preserve">7.67666006088257</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.74724960327148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.65195322036743</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.71548366546631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.73666000366211</t>
   </si>
   <si>
     <t xml:space="preserve">7.66607141494751</t>
   </si>
   <si>
-    <t xml:space="preserve">7.61665868759155</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.50724411010742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.4754786491394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.23194360733032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.30959367752075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.40488767623901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.27076768875122</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.28135538101196</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.1895899772644</t>
+    <t xml:space="preserve">7.61665916442871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.50724315643311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.47547912597656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.23194313049316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.30959129333496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.40488862991333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.27076721191406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.28135681152344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.18958902359009</t>
   </si>
   <si>
     <t xml:space="preserve">7.2919454574585</t>
   </si>
   <si>
-    <t xml:space="preserve">7.21076726913452</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.33076858520508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.1790018081665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.24253129959106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.17547130584717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.26723766326904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.36253356933594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.14370584487915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.19664764404297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.10488224029541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.04346752166748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.22488307952881</t>
+    <t xml:space="preserve">7.21076679229736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.33076763153076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.17900037765503</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.24253273010254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.17547178268433</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.26723718643188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.36253452301025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.14370679855347</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.19664669036865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.10488128662109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.04346704483032</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.22488355636597</t>
   </si>
   <si>
     <t xml:space="preserve">7.12605714797974</t>
   </si>
   <si>
-    <t xml:space="preserve">7.2390022277832</t>
+    <t xml:space="preserve">7.23900127410889</t>
   </si>
   <si>
     <t xml:space="preserve">7.20723628997803</t>
@@ -2315,103 +2315,103 @@
     <t xml:space="preserve">7.16488170623779</t>
   </si>
   <si>
-    <t xml:space="preserve">7.10135269165039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.09076356887817</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.26017999649048</t>
+    <t xml:space="preserve">7.10135126113892</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.09076309204102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.26017904281616</t>
   </si>
   <si>
     <t xml:space="preserve">7.32723951339722</t>
   </si>
   <si>
-    <t xml:space="preserve">7.34841680526733</t>
+    <t xml:space="preserve">7.34841775894165</t>
   </si>
   <si>
     <t xml:space="preserve">7.25311994552612</t>
   </si>
   <si>
-    <t xml:space="preserve">7.47194910049438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.82136869430542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.76136779785156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.30606317520142</t>
+    <t xml:space="preserve">7.47194766998291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.82136964797974</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.76136684417725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.3060622215271</t>
   </si>
   <si>
     <t xml:space="preserve">7.41547822952271</t>
   </si>
   <si>
-    <t xml:space="preserve">7.55665683746338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.5707745552063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.62018775939941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.69783639907837</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.78960371017456</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.75078010559082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.72960186004639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.71901321411133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.00490379333496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.12490653991699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.96607971191406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.97313737869263</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.40841722488403</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.29547500610352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.44018363952637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.11899948120117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.78652000427246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.53804445266724</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.79075622558594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.8387565612793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.65804624557495</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.86275768280029</t>
+    <t xml:space="preserve">7.5566577911377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.57077503204346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.62018871307373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.69783735275269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.78960466384888</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.7507791519165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.72960376739502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.71901369094849</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.00490283966064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.12490558624268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.96607875823975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.97313642501831</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.40841770172119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.29547214508057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.44018507003784</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.11899900436401</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.78652048110962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.53804397583008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.79075527191162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.83875703811646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.65804672241211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.86275815963745</t>
   </si>
   <si>
     <t xml:space="preserve">5.97050046920776</t>
@@ -2420,28 +2420,28 @@
     <t xml:space="preserve">5.56107807159424</t>
   </si>
   <si>
-    <t xml:space="preserve">5.56249094009399</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.33704853057861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.76058769226074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.58976078033447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.58552408218384</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.49658155441284</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.88059043884277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.89612054824829</t>
+    <t xml:space="preserve">5.56248998641968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.33704805374146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.7605881690979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.58976030349731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.585524559021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.49658107757568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.88059091567993</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.89612007141113</t>
   </si>
   <si>
     <t xml:space="preserve">5.06553649902344</t>
@@ -2453,28 +2453,28 @@
     <t xml:space="preserve">5.46084022521973</t>
   </si>
   <si>
-    <t xml:space="preserve">5.71637630462646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.54272556304932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.58790254592896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.44954586029053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.21801090240479</t>
+    <t xml:space="preserve">5.71637535095215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.54272508621216</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.5879020690918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.44954538345337</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.21801137924194</t>
   </si>
   <si>
     <t xml:space="preserve">5.48625373840332</t>
   </si>
   <si>
-    <t xml:space="preserve">5.52719497680664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.67543363571167</t>
+    <t xml:space="preserve">5.52719402313232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.67543411254883</t>
   </si>
   <si>
     <t xml:space="preserve">5.7573184967041</t>
@@ -2483,37 +2483,37 @@
     <t xml:space="preserve">5.84343767166138</t>
   </si>
   <si>
-    <t xml:space="preserve">5.8632025718689</t>
+    <t xml:space="preserve">5.86320304870605</t>
   </si>
   <si>
     <t xml:space="preserve">5.88720369338989</t>
   </si>
   <si>
-    <t xml:space="preserve">5.36907339096069</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.41283988952637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.43542718887329</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.37330961227417</t>
+    <t xml:space="preserve">5.36907386779785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.41283941268921</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.43542814254761</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.37330913543701</t>
   </si>
   <si>
     <t xml:space="preserve">5.25895309448242</t>
   </si>
   <si>
-    <t xml:space="preserve">5.34224987030029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.30695486068726</t>
+    <t xml:space="preserve">5.34224891662598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.30695390701294</t>
   </si>
   <si>
     <t xml:space="preserve">5.22224617004395</t>
   </si>
   <si>
-    <t xml:space="preserve">5.56390237808228</t>
+    <t xml:space="preserve">5.56390190124512</t>
   </si>
   <si>
     <t xml:space="preserve">5.55401945114136</t>
@@ -2525,22 +2525,22 @@
     <t xml:space="preserve">5.47213459014893</t>
   </si>
   <si>
-    <t xml:space="preserve">5.33942461013794</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.18836307525635</t>
+    <t xml:space="preserve">5.33942556381226</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.18836355209351</t>
   </si>
   <si>
     <t xml:space="preserve">5.10224342346191</t>
   </si>
   <si>
-    <t xml:space="preserve">5.36060237884521</t>
+    <t xml:space="preserve">5.36060285568237</t>
   </si>
   <si>
     <t xml:space="preserve">5.4749584197998</t>
   </si>
   <si>
-    <t xml:space="preserve">5.2561297416687</t>
+    <t xml:space="preserve">5.25613021850586</t>
   </si>
   <si>
     <t xml:space="preserve">5.16012668609619</t>
@@ -2549,37 +2549,37 @@
     <t xml:space="preserve">5.07259559631348</t>
   </si>
   <si>
-    <t xml:space="preserve">5.2674241065979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.22648096084595</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.23495292663574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.20248126983643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.25330638885498</t>
+    <t xml:space="preserve">5.26742362976074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.22648143768311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.23495244979858</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.20248079299927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.25330591201782</t>
   </si>
   <si>
     <t xml:space="preserve">5.46225166320801</t>
   </si>
   <si>
-    <t xml:space="preserve">5.5441370010376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.5723729133606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.62319803237915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.68813991546631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.86038064956665</t>
+    <t xml:space="preserve">5.54413652420044</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.57237243652344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.62319850921631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.68813943862915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.86038017272949</t>
   </si>
   <si>
     <t xml:space="preserve">6.04814863204956</t>
@@ -2591,28 +2591,28 @@
     <t xml:space="preserve">6.31921482086182</t>
   </si>
   <si>
-    <t xml:space="preserve">6.12438678741455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.05379676818848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.73472881317139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.82226133346558</t>
+    <t xml:space="preserve">6.12438631057739</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.05379629135132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.7347297668457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.82226085662842</t>
   </si>
   <si>
     <t xml:space="preserve">5.87167406082153</t>
   </si>
   <si>
-    <t xml:space="preserve">5.99026536941528</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.96344137191772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.92108631134033</t>
+    <t xml:space="preserve">5.99026584625244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.96344041824341</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.92108678817749</t>
   </si>
   <si>
     <t xml:space="preserve">5.80249691009521</t>
@@ -2621,40 +2621,40 @@
     <t xml:space="preserve">5.92205238342285</t>
   </si>
   <si>
-    <t xml:space="preserve">6.02327060699463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.75628709793091</t>
+    <t xml:space="preserve">6.02327108383179</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.75628757476807</t>
   </si>
   <si>
     <t xml:space="preserve">5.79736137390137</t>
   </si>
   <si>
-    <t xml:space="preserve">5.68147230148315</t>
+    <t xml:space="preserve">5.68147325515747</t>
   </si>
   <si>
     <t xml:space="preserve">5.85457277297974</t>
   </si>
   <si>
-    <t xml:space="preserve">5.67707204818726</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.68734073638916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.71227931976318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.80469608306885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.7724232673645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.72694778442383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.59198999404907</t>
+    <t xml:space="preserve">5.67707252502441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.687340259552</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.71227884292603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.80469655990601</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.77242279052734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.72694826126099</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.59198951721191</t>
   </si>
   <si>
     <t xml:space="preserve">5.64039850234985</t>
@@ -2663,13 +2663,13 @@
     <t xml:space="preserve">5.74748516082764</t>
   </si>
   <si>
-    <t xml:space="preserve">5.72548151016235</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.75041961669922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.76655626296997</t>
+    <t xml:space="preserve">5.72548198699951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.75041913986206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.76655578613281</t>
   </si>
   <si>
     <t xml:space="preserve">6.00420045852661</t>
@@ -2678,49 +2678,49 @@
     <t xml:space="preserve">6.04820919036865</t>
   </si>
   <si>
-    <t xml:space="preserve">6.10248613357544</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.00566720962524</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.97632884979248</t>
+    <t xml:space="preserve">6.10248565673828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.0056676864624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.97632932662964</t>
   </si>
   <si>
     <t xml:space="preserve">5.82670021057129</t>
   </si>
   <si>
-    <t xml:space="preserve">5.79442739486694</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.7797589302063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.58172082901001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.68587350845337</t>
+    <t xml:space="preserve">5.7944278717041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.77975797653198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.58172130584717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.68587446212769</t>
   </si>
   <si>
     <t xml:space="preserve">5.79149389266968</t>
   </si>
   <si>
-    <t xml:space="preserve">5.83110094070435</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.82963418960571</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.73868417739868</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.78415966033936</t>
+    <t xml:space="preserve">5.8311014175415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.82963514328003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.73868370056152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.78415822982788</t>
   </si>
   <si>
     <t xml:space="preserve">5.88537836074829</t>
   </si>
   <si>
-    <t xml:space="preserve">5.97926330566406</t>
+    <t xml:space="preserve">5.9792628288269</t>
   </si>
   <si>
     <t xml:space="preserve">5.97192811965942</t>
@@ -2732,7 +2732,7 @@
     <t xml:space="preserve">5.87511014938354</t>
   </si>
   <si>
-    <t xml:space="preserve">5.78269195556641</t>
+    <t xml:space="preserve">5.78269243240356</t>
   </si>
   <si>
     <t xml:space="preserve">5.76362133026123</t>
@@ -2741,40 +2741,40 @@
     <t xml:space="preserve">5.82376623153687</t>
   </si>
   <si>
-    <t xml:space="preserve">5.72401428222656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.80176258087158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.8208327293396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.75335359573364</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.75775384902954</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.67267179489136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.63012981414795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.64186573028564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.83696985244751</t>
+    <t xml:space="preserve">5.7240138053894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.80176210403442</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.82083177566528</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.75335311889648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.7577543258667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.6726713180542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.63013029098511</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.64186525344849</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.83696937561035</t>
   </si>
   <si>
     <t xml:space="preserve">5.71668004989624</t>
   </si>
   <si>
-    <t xml:space="preserve">5.8531060218811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.8428373336792</t>
+    <t xml:space="preserve">5.85310554504395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.84283685684204</t>
   </si>
   <si>
     <t xml:space="preserve">5.84577083587646</t>
@@ -2786,22 +2786,22 @@
     <t xml:space="preserve">5.69320869445801</t>
   </si>
   <si>
-    <t xml:space="preserve">5.49517107009888</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.57291984558105</t>
+    <t xml:space="preserve">5.49517202377319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.5729193687439</t>
   </si>
   <si>
     <t xml:space="preserve">5.61839437484741</t>
   </si>
   <si>
-    <t xml:space="preserve">5.60665941238403</t>
+    <t xml:space="preserve">5.60665845870972</t>
   </si>
   <si>
     <t xml:space="preserve">5.56411743164062</t>
   </si>
   <si>
-    <t xml:space="preserve">5.66973781585693</t>
+    <t xml:space="preserve">5.66973733901978</t>
   </si>
   <si>
     <t xml:space="preserve">5.5567831993103</t>
@@ -2813,10 +2813,10 @@
     <t xml:space="preserve">5.50984048843384</t>
   </si>
   <si>
-    <t xml:space="preserve">5.54211330413818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.93232011795044</t>
+    <t xml:space="preserve">5.5421142578125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.9323205947876</t>
   </si>
   <si>
     <t xml:space="preserve">5.88097667694092</t>
@@ -2825,16 +2825,16 @@
     <t xml:space="preserve">5.87804365158081</t>
   </si>
   <si>
-    <t xml:space="preserve">5.87951040267944</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.89271306991577</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.89418029785156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.59932422637939</t>
+    <t xml:space="preserve">5.8795108795166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.89271354675293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.8941798210144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.59932374954224</t>
   </si>
   <si>
     <t xml:space="preserve">5.66827058792114</t>
@@ -2846,40 +2846,40 @@
     <t xml:space="preserve">5.56998538970947</t>
   </si>
   <si>
-    <t xml:space="preserve">5.57878637313843</t>
+    <t xml:space="preserve">5.57878684997559</t>
   </si>
   <si>
     <t xml:space="preserve">5.56851863861084</t>
   </si>
   <si>
-    <t xml:space="preserve">5.47903490066528</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.43942737579346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.21058368682861</t>
+    <t xml:space="preserve">5.47903442382812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.4394268989563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.21058416366577</t>
   </si>
   <si>
     <t xml:space="preserve">5.14017105102539</t>
   </si>
   <si>
-    <t xml:space="preserve">5.13430261611938</t>
+    <t xml:space="preserve">5.1343035697937</t>
   </si>
   <si>
     <t xml:space="preserve">5.25752639770508</t>
   </si>
   <si>
-    <t xml:space="preserve">5.30740261077881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.47463369369507</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.65506792068481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.56265115737915</t>
+    <t xml:space="preserve">5.30740213394165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.47463417053223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.65506839752197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.56265068054199</t>
   </si>
   <si>
     <t xml:space="preserve">5.75922107696533</t>
@@ -2888,28 +2888,28 @@
     <t xml:space="preserve">5.90151453018188</t>
   </si>
   <si>
-    <t xml:space="preserve">5.85897254943848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.03647232055664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.23744487762451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.31812620162964</t>
+    <t xml:space="preserve">5.85897302627563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.03647375106812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.23744440078735</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.31812715530396</t>
   </si>
   <si>
     <t xml:space="preserve">6.42521381378174</t>
   </si>
   <si>
-    <t xml:space="preserve">6.49415969848633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.39440870285034</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.42820262908936</t>
+    <t xml:space="preserve">6.49416017532349</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.39440822601318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.42820310592651</t>
   </si>
   <si>
     <t xml:space="preserve">6.5731782913208</t>
@@ -2918,13 +2918,13 @@
     <t xml:space="preserve">6.51040506362915</t>
   </si>
   <si>
-    <t xml:space="preserve">6.57616758346558</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.38485956192017</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.43567609786987</t>
+    <t xml:space="preserve">6.57616662979126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.38485908508301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.43567657470703</t>
   </si>
   <si>
     <t xml:space="preserve">6.33254957199097</t>
@@ -2933,13 +2933,13 @@
     <t xml:space="preserve">6.35496807098389</t>
   </si>
   <si>
-    <t xml:space="preserve">6.28322792053223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.27276659011841</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.28173398971558</t>
+    <t xml:space="preserve">6.28322839736938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.27276611328125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.28173446655273</t>
   </si>
   <si>
     <t xml:space="preserve">6.29070091247559</t>
@@ -2951,163 +2951,163 @@
     <t xml:space="preserve">6.23540210723877</t>
   </si>
   <si>
-    <t xml:space="preserve">6.33553838729858</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.26977729797363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.24586343765259</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.10238361358643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.22792816162109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.25333642959595</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.21746635437012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.23390674591064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.19355297088623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.38187026977539</t>
+    <t xml:space="preserve">6.33553791046143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.26977777481079</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.24586296081543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.10238409042358</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.22792911529541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.25333690643311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.21746587753296</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.23390626907349</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.19355344772339</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.38187074661255</t>
   </si>
   <si>
     <t xml:space="preserve">6.51488924026489</t>
   </si>
   <si>
-    <t xml:space="preserve">6.42222499847412</t>
+    <t xml:space="preserve">6.42222452163696</t>
   </si>
   <si>
     <t xml:space="preserve">6.37738752365112</t>
   </si>
   <si>
-    <t xml:space="preserve">6.30265760421753</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.24138021469116</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.26230430603027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.20999336242676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.27426099777222</t>
+    <t xml:space="preserve">6.30265808105469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.241379737854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.26230478286743</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.2099928855896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.27426052093506</t>
   </si>
   <si>
     <t xml:space="preserve">6.21597194671631</t>
   </si>
   <si>
-    <t xml:space="preserve">6.17860794067383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.13377046585083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.24885368347168</t>
+    <t xml:space="preserve">6.17860746383667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.13376998901367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.24885272979736</t>
   </si>
   <si>
     <t xml:space="preserve">6.09789991378784</t>
   </si>
   <si>
-    <t xml:space="preserve">6.15320062637329</t>
+    <t xml:space="preserve">6.15319967269897</t>
   </si>
   <si>
     <t xml:space="preserve">6.03512811660767</t>
   </si>
   <si>
-    <t xml:space="preserve">6.19803619384766</t>
+    <t xml:space="preserve">6.19803667068481</t>
   </si>
   <si>
     <t xml:space="preserve">6.18757486343384</t>
   </si>
   <si>
-    <t xml:space="preserve">6.6284761428833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.73459243774414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.89002895355225</t>
+    <t xml:space="preserve">6.62847709655762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.7345929145813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.89002847671509</t>
   </si>
   <si>
     <t xml:space="preserve">7.06639003753662</t>
   </si>
   <si>
-    <t xml:space="preserve">7.15158081054688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.10973358154297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.21136331558228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.23228931427002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.30103969573975</t>
+    <t xml:space="preserve">7.15158176422119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.10973262786865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.21136379241943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.23228883743286</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.3010401725769</t>
   </si>
   <si>
     <t xml:space="preserve">7.21286010742188</t>
   </si>
   <si>
-    <t xml:space="preserve">7.08581972122192</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.9528021812439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.02304649353027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.20688152313232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.12019491195679</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.13663530349731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.1799783706665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.02753114700317</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.34438180923462</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.38025188446045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.43555307388306</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.45348691940308</t>
+    <t xml:space="preserve">7.08581924438477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.95280075073242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.02304744720459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.20688199996948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.12019538879395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.13663578033447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.17997884750366</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.02753162384033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.34438276290894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.38025236129761</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.4355525970459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.45348596572876</t>
   </si>
   <si>
     <t xml:space="preserve">7.36082363128662</t>
   </si>
   <si>
-    <t xml:space="preserve">7.50280809402466</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.57753753662109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.64479398727417</t>
+    <t xml:space="preserve">7.5028076171875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.57753849029541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.64479446411133</t>
   </si>
   <si>
     <t xml:space="preserve">7.61116647720337</t>
@@ -3116,49 +3116,49 @@
     <t xml:space="preserve">7.67842149734497</t>
   </si>
   <si>
-    <t xml:space="preserve">7.63358449935913</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.79798936843872</t>
+    <t xml:space="preserve">7.63358402252197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.7979884147644</t>
   </si>
   <si>
     <t xml:space="preserve">7.75688695907593</t>
   </si>
   <si>
-    <t xml:space="preserve">7.8129358291626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.72699546813965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.85029983520508</t>
+    <t xml:space="preserve">7.81293487548828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.72699642181396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.85029888153076</t>
   </si>
   <si>
     <t xml:space="preserve">7.783043384552</t>
   </si>
   <si>
-    <t xml:space="preserve">7.824143409729</t>
+    <t xml:space="preserve">7.82414436340332</t>
   </si>
   <si>
     <t xml:space="preserve">7.81667041778564</t>
   </si>
   <si>
-    <t xml:space="preserve">7.88392686843872</t>
+    <t xml:space="preserve">7.88392782211304</t>
   </si>
   <si>
     <t xml:space="preserve">8.05580425262451</t>
   </si>
   <si>
-    <t xml:space="preserve">8.11185073852539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.10064315795898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.15295124053955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.17537117004395</t>
+    <t xml:space="preserve">8.11184978485107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.10064220428467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.15295219421387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.17537021636963</t>
   </si>
   <si>
     <t xml:space="preserve">8.16416263580322</t>
@@ -3170,13 +3170,13 @@
     <t xml:space="preserve">8.06701374053955</t>
   </si>
   <si>
-    <t xml:space="preserve">8.05953979492188</t>
+    <t xml:space="preserve">8.05954074859619</t>
   </si>
   <si>
     <t xml:space="preserve">7.96986627578735</t>
   </si>
   <si>
-    <t xml:space="preserve">7.96239185333252</t>
+    <t xml:space="preserve">7.96239280700684</t>
   </si>
   <si>
     <t xml:space="preserve">8.05206775665283</t>
@@ -3185,13 +3185,13 @@
     <t xml:space="preserve">8.04085922241211</t>
   </si>
   <si>
-    <t xml:space="preserve">7.93250036239624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.9287633895874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.10811328887939</t>
+    <t xml:space="preserve">7.93250131607056</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.92876386642456</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.10811519622803</t>
   </si>
   <si>
     <t xml:space="preserve">8.07822322845459</t>
@@ -3203,49 +3203,49 @@
     <t xml:space="preserve">8.16042518615723</t>
   </si>
   <si>
-    <t xml:space="preserve">8.15668678283691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.14547920227051</t>
+    <t xml:space="preserve">8.15668869018555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.14547824859619</t>
   </si>
   <si>
     <t xml:space="preserve">8.25757217407227</t>
   </si>
   <si>
-    <t xml:space="preserve">8.19779014587402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.16789817810059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.22020816802979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.38835048675537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.35098552703857</t>
+    <t xml:space="preserve">8.19778919219971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.16789722442627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.22020721435547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.38834953308105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.35098457336426</t>
   </si>
   <si>
     <t xml:space="preserve">8.24636363983154</t>
   </si>
   <si>
-    <t xml:space="preserve">8.25009918212891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.30988311767578</t>
+    <t xml:space="preserve">8.25010013580322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.3098840713501</t>
   </si>
   <si>
     <t xml:space="preserve">8.43692398071289</t>
   </si>
   <si>
-    <t xml:space="preserve">8.42571258544922</t>
+    <t xml:space="preserve">8.42571449279785</t>
   </si>
   <si>
     <t xml:space="preserve">8.39208602905273</t>
   </si>
   <si>
-    <t xml:space="preserve">8.46307849884033</t>
+    <t xml:space="preserve">8.46307754516602</t>
   </si>
   <si>
     <t xml:space="preserve">8.59385395050049</t>
@@ -3254,7 +3254,7 @@
     <t xml:space="preserve">8.74331283569336</t>
   </si>
   <si>
-    <t xml:space="preserve">8.62748146057129</t>
+    <t xml:space="preserve">8.62748241424561</t>
   </si>
   <si>
     <t xml:space="preserve">8.53407096862793</t>
@@ -3266,13 +3266,13 @@
     <t xml:space="preserve">8.59759044647217</t>
   </si>
   <si>
-    <t xml:space="preserve">8.64242744445801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.81804180145264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.90024280548096</t>
+    <t xml:space="preserve">8.64242839813232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.81804084777832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.90024375915527</t>
   </si>
   <si>
     <t xml:space="preserve">9.01233768463135</t>
@@ -3281,52 +3281,52 @@
     <t xml:space="preserve">9.02728271484375</t>
   </si>
   <si>
-    <t xml:space="preserve">8.95628929138184</t>
+    <t xml:space="preserve">8.95629119873047</t>
   </si>
   <si>
     <t xml:space="preserve">8.97871017456055</t>
   </si>
   <si>
-    <t xml:space="preserve">8.95255470275879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.01980972290039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.96376323699951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.73957633972168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.85025215148926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.73112106323242</t>
+    <t xml:space="preserve">8.95255279541016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.01981067657471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.9637622833252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.73957538604736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.85025310516357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.73112010955811</t>
   </si>
   <si>
     <t xml:space="preserve">8.62736225128174</t>
   </si>
   <si>
-    <t xml:space="preserve">8.78107833862305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.75417900085449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.61198997497559</t>
+    <t xml:space="preserve">8.78108024597168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.75417804718018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.6119909286499</t>
   </si>
   <si>
     <t xml:space="preserve">8.573561668396</t>
   </si>
   <si>
-    <t xml:space="preserve">8.56971836090088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.66963291168213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.59277725219727</t>
+    <t xml:space="preserve">8.56971740722656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.66963386535645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.59277534484863</t>
   </si>
   <si>
     <t xml:space="preserve">8.71574974060059</t>
@@ -3335,79 +3335,79 @@
     <t xml:space="preserve">8.58509063720703</t>
   </si>
   <si>
-    <t xml:space="preserve">8.61967658996582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.3199291229248</t>
+    <t xml:space="preserve">8.61967754364014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.31992816925049</t>
   </si>
   <si>
     <t xml:space="preserve">8.45058822631836</t>
   </si>
   <si>
-    <t xml:space="preserve">8.48133087158203</t>
+    <t xml:space="preserve">8.48133182525635</t>
   </si>
   <si>
     <t xml:space="preserve">8.47748851776123</t>
   </si>
   <si>
-    <t xml:space="preserve">8.44674491882324</t>
+    <t xml:space="preserve">8.44674301147461</t>
   </si>
   <si>
     <t xml:space="preserve">8.33145809173584</t>
   </si>
   <si>
-    <t xml:space="preserve">8.35835838317871</t>
+    <t xml:space="preserve">8.35835742950439</t>
   </si>
   <si>
     <t xml:space="preserve">8.07398223876953</t>
   </si>
   <si>
-    <t xml:space="preserve">8.15468311309814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.41215705871582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.53897476196289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.61583423614502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.68500709533691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.60046195983887</t>
+    <t xml:space="preserve">8.15468215942383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.41215801239014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.53897571563721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.6158332824707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.68500518798828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.60046100616455</t>
   </si>
   <si>
     <t xml:space="preserve">8.58124732971191</t>
   </si>
   <si>
-    <t xml:space="preserve">8.55050563812256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.7272777557373</t>
+    <t xml:space="preserve">8.55050468444824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.72727680206299</t>
   </si>
   <si>
     <t xml:space="preserve">8.85793781280518</t>
   </si>
   <si>
-    <t xml:space="preserve">8.9002103805542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.9347972869873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.00781154632568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.027024269104</t>
+    <t xml:space="preserve">8.90020942687988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.93479633331299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.0078125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.02702522277832</t>
   </si>
   <si>
     <t xml:space="preserve">8.98091125488281</t>
   </si>
   <si>
-    <t xml:space="preserve">8.92326736450195</t>
+    <t xml:space="preserve">8.92326641082764</t>
   </si>
   <si>
     <t xml:space="preserve">8.87330913543701</t>
@@ -3416,22 +3416,22 @@
     <t xml:space="preserve">8.94632625579834</t>
   </si>
   <si>
-    <t xml:space="preserve">8.83488082885742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.76954936981201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.96169567108154</t>
+    <t xml:space="preserve">8.83487987518311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.76955032348633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.96169662475586</t>
   </si>
   <si>
     <t xml:space="preserve">8.93863868713379</t>
   </si>
   <si>
-    <t xml:space="preserve">8.90789604187012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.82719326019287</t>
+    <t xml:space="preserve">8.9078950881958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.82719421386719</t>
   </si>
   <si>
     <t xml:space="preserve">8.86562347412109</t>
@@ -3446,19 +3446,19 @@
     <t xml:space="preserve">8.80798053741455</t>
   </si>
   <si>
-    <t xml:space="preserve">8.86946582794189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.88483810424805</t>
+    <t xml:space="preserve">8.86946773529053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.88483715057373</t>
   </si>
   <si>
     <t xml:space="preserve">8.96553993225098</t>
   </si>
   <si>
-    <t xml:space="preserve">9.10772800445557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.02318286895752</t>
+    <t xml:space="preserve">9.10772895812988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.02318382263184</t>
   </si>
   <si>
     <t xml:space="preserve">9.05777072906494</t>
@@ -3470,28 +3470,28 @@
     <t xml:space="preserve">9.20380115509033</t>
   </si>
   <si>
-    <t xml:space="preserve">9.16921615600586</t>
+    <t xml:space="preserve">9.16921520233154</t>
   </si>
   <si>
     <t xml:space="preserve">9.25375938415527</t>
   </si>
   <si>
-    <t xml:space="preserve">9.03086853027344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.0923547744751</t>
+    <t xml:space="preserve">9.03086948394775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.09235572814941</t>
   </si>
   <si>
     <t xml:space="preserve">9.15000057220459</t>
   </si>
   <si>
-    <t xml:space="preserve">9.11156940460205</t>
+    <t xml:space="preserve">9.11157035827637</t>
   </si>
   <si>
     <t xml:space="preserve">9.29603099822998</t>
   </si>
   <si>
-    <t xml:space="preserve">9.24222850799561</t>
+    <t xml:space="preserve">9.24222946166992</t>
   </si>
   <si>
     <t xml:space="preserve">9.35751819610596</t>
@@ -3509,10 +3509,10 @@
     <t xml:space="preserve">9.50354862213135</t>
   </si>
   <si>
-    <t xml:space="preserve">9.60730648040771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.54966449737549</t>
+    <t xml:space="preserve">9.60730743408203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.54966354370117</t>
   </si>
   <si>
     <t xml:space="preserve">9.5189208984375</t>
@@ -3524,37 +3524,37 @@
     <t xml:space="preserve">9.64958000183105</t>
   </si>
   <si>
-    <t xml:space="preserve">9.61499309539795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.595778465271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.7418098449707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.65726566314697</t>
+    <t xml:space="preserve">9.61499404907227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.59577941894531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.74181079864502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.65726470947266</t>
   </si>
   <si>
     <t xml:space="preserve">9.64189434051514</t>
   </si>
   <si>
-    <t xml:space="preserve">9.48433303833008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.56503582000732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.5304479598999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.64573669433594</t>
+    <t xml:space="preserve">9.48433589935303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.56503486633301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.53044986724854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.64573764801025</t>
   </si>
   <si>
     <t xml:space="preserve">9.57656478881836</t>
   </si>
   <si>
-    <t xml:space="preserve">9.60346603393555</t>
+    <t xml:space="preserve">9.60346508026123</t>
   </si>
   <si>
     <t xml:space="preserve">9.56119251251221</t>
@@ -3566,16 +3566,16 @@
     <t xml:space="preserve">9.4113187789917</t>
   </si>
   <si>
-    <t xml:space="preserve">9.42284870147705</t>
+    <t xml:space="preserve">9.42284774780273</t>
   </si>
   <si>
     <t xml:space="preserve">9.33446025848389</t>
   </si>
   <si>
-    <t xml:space="preserve">9.27297306060791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.25345993041992</t>
+    <t xml:space="preserve">9.27297401428223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.25345802307129</t>
   </si>
   <si>
     <t xml:space="preserve">9.17930698394775</t>
@@ -3590,10 +3590,10 @@
     <t xml:space="preserve">8.64462757110596</t>
   </si>
   <si>
-    <t xml:space="preserve">8.73829364776611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.6953649520874</t>
+    <t xml:space="preserve">8.73829460144043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.69536304473877</t>
   </si>
   <si>
     <t xml:space="preserve">8.85928153991699</t>
@@ -3614,16 +3614,16 @@
     <t xml:space="preserve">8.72658634185791</t>
   </si>
   <si>
-    <t xml:space="preserve">8.66414165496826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.62511348724365</t>
+    <t xml:space="preserve">8.66414260864258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.62511444091797</t>
   </si>
   <si>
     <t xml:space="preserve">8.6290168762207</t>
   </si>
   <si>
-    <t xml:space="preserve">8.64852905273438</t>
+    <t xml:space="preserve">8.64853096008301</t>
   </si>
   <si>
     <t xml:space="preserve">8.6875581741333</t>
@@ -3632,16 +3632,16 @@
     <t xml:space="preserve">8.75000286102295</t>
   </si>
   <si>
-    <t xml:space="preserve">8.76171016693115</t>
+    <t xml:space="preserve">8.76171207427979</t>
   </si>
   <si>
     <t xml:space="preserve">8.56267070770264</t>
   </si>
   <si>
-    <t xml:space="preserve">8.70316982269287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.78903102874756</t>
+    <t xml:space="preserve">8.70316886901855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.78903007507324</t>
   </si>
   <si>
     <t xml:space="preserve">8.86708545684814</t>
@@ -3650,25 +3650,25 @@
     <t xml:space="preserve">8.94514179229736</t>
   </si>
   <si>
-    <t xml:space="preserve">9.01929378509521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.99977874755859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.00758457183838</t>
+    <t xml:space="preserve">9.0192928314209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.99977970123291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.00758647918701</t>
   </si>
   <si>
     <t xml:space="preserve">9.13637638092041</t>
   </si>
   <si>
-    <t xml:space="preserve">9.14808464050293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.18321132659912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.1051549911499</t>
+    <t xml:space="preserve">9.14808559417725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.1832103729248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.10515403747559</t>
   </si>
   <si>
     <t xml:space="preserve">9.13247394561768</t>
@@ -3677,40 +3677,40 @@
     <t xml:space="preserve">9.15979290008545</t>
   </si>
   <si>
-    <t xml:space="preserve">9.09734916687012</t>
+    <t xml:space="preserve">9.09735012054443</t>
   </si>
   <si>
     <t xml:space="preserve">9.05441856384277</t>
   </si>
   <si>
-    <t xml:space="preserve">9.06222343444824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.027099609375</t>
+    <t xml:space="preserve">9.06222248077393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.02709865570068</t>
   </si>
   <si>
     <t xml:space="preserve">9.04661273956299</t>
   </si>
   <si>
-    <t xml:space="preserve">9.12076568603516</t>
+    <t xml:space="preserve">9.12076473236084</t>
   </si>
   <si>
     <t xml:space="preserve">8.96465396881104</t>
   </si>
   <si>
-    <t xml:space="preserve">8.60560035705566</t>
+    <t xml:space="preserve">8.60559940338135</t>
   </si>
   <si>
     <t xml:space="preserve">8.81634902954102</t>
   </si>
   <si>
-    <t xml:space="preserve">9.01148891448975</t>
+    <t xml:space="preserve">9.01148700714111</t>
   </si>
   <si>
     <t xml:space="preserve">8.90221118927002</t>
   </si>
   <si>
-    <t xml:space="preserve">9.31200313568115</t>
+    <t xml:space="preserve">9.31200218200684</t>
   </si>
   <si>
     <t xml:space="preserve">9.3198070526123</t>
@@ -3722,10 +3722,10 @@
     <t xml:space="preserve">8.55486392974854</t>
   </si>
   <si>
-    <t xml:space="preserve">8.59389114379883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.42607402801514</t>
+    <t xml:space="preserve">8.59389209747314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.4260721206665</t>
   </si>
   <si>
     <t xml:space="preserve">8.58218383789062</t>
@@ -3734,58 +3734,58 @@
     <t xml:space="preserve">8.66023921966553</t>
   </si>
   <si>
-    <t xml:space="preserve">8.69146156311035</t>
+    <t xml:space="preserve">8.69146060943604</t>
   </si>
   <si>
     <t xml:space="preserve">8.61340618133545</t>
   </si>
   <si>
-    <t xml:space="preserve">8.40265464782715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.37143421173096</t>
+    <t xml:space="preserve">8.40265655517578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.37143516540527</t>
   </si>
   <si>
     <t xml:space="preserve">8.30118465423584</t>
   </si>
   <si>
-    <t xml:space="preserve">7.83675527572632</t>
+    <t xml:space="preserve">7.836754322052</t>
   </si>
   <si>
     <t xml:space="preserve">8.09433841705322</t>
   </si>
   <si>
-    <t xml:space="preserve">8.02018547058105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.69625616073608</t>
+    <t xml:space="preserve">8.02018451690674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.69625520706177</t>
   </si>
   <si>
     <t xml:space="preserve">7.68376636505127</t>
   </si>
   <si>
-    <t xml:space="preserve">7.57604932785034</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.08742523193359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.93443489074707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.25602340698242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.89919853210449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.49955749511719</t>
+    <t xml:space="preserve">7.57605075836182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.08742427825928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.93443536758423</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.25602436065674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.89920043945312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.49955654144287</t>
   </si>
   <si>
     <t xml:space="preserve">7.54482841491699</t>
   </si>
   <si>
-    <t xml:space="preserve">7.74933290481567</t>
+    <t xml:space="preserve">7.74933385848999</t>
   </si>
   <si>
     <t xml:space="preserve">7.70718336105347</t>
@@ -3794,43 +3794,43 @@
     <t xml:space="preserve">8.0553092956543</t>
   </si>
   <si>
-    <t xml:space="preserve">7.88749074935913</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.86407518386841</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.89529657363892</t>
+    <t xml:space="preserve">7.88749170303345</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.86407423019409</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.89529848098755</t>
   </si>
   <si>
     <t xml:space="preserve">8.10214328765869</t>
   </si>
   <si>
-    <t xml:space="preserve">8.09043598175049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.23483753204346</t>
+    <t xml:space="preserve">8.09043502807617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.23483848571777</t>
   </si>
   <si>
     <t xml:space="preserve">8.12555980682373</t>
   </si>
   <si>
-    <t xml:space="preserve">8.21922779083252</t>
+    <t xml:space="preserve">8.21922588348389</t>
   </si>
   <si>
     <t xml:space="preserve">8.289475440979</t>
   </si>
   <si>
-    <t xml:space="preserve">8.25434970855713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.11775398254395</t>
+    <t xml:space="preserve">8.25435066223145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.11775493621826</t>
   </si>
   <si>
     <t xml:space="preserve">7.99676895141602</t>
   </si>
   <si>
-    <t xml:space="preserve">7.82504749298096</t>
+    <t xml:space="preserve">7.82504653930664</t>
   </si>
   <si>
     <t xml:space="preserve">7.70562314987183</t>
@@ -3839,10 +3839,10 @@
     <t xml:space="preserve">7.85626888275146</t>
   </si>
   <si>
-    <t xml:space="preserve">7.793044090271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.67596006393433</t>
+    <t xml:space="preserve">7.79304504394531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.6759614944458</t>
   </si>
   <si>
     <t xml:space="preserve">7.5979061126709</t>
@@ -3851,46 +3851,46 @@
     <t xml:space="preserve">7.65878915786743</t>
   </si>
   <si>
-    <t xml:space="preserve">7.53546237945557</t>
+    <t xml:space="preserve">7.53546190261841</t>
   </si>
   <si>
     <t xml:space="preserve">7.73372268676758</t>
   </si>
   <si>
-    <t xml:space="preserve">7.7087459564209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.5729284286499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.35905647277832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.26070737838745</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.23729085922241</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.28412342071533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.32002830505371</t>
+    <t xml:space="preserve">7.70874500274658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.57292890548706</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.35905790328979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.26070642471313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.23729038238525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.28412389755249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.32002878189087</t>
   </si>
   <si>
     <t xml:space="preserve">7.246657371521</t>
   </si>
   <si>
-    <t xml:space="preserve">7.18889665603638</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.13269662857056</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.02654027938843</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.84389162063599</t>
+    <t xml:space="preserve">7.18889570236206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.1326961517334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.02654123306274</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.84389114379883</t>
   </si>
   <si>
     <t xml:space="preserve">7.00624656677246</t>
@@ -3899,25 +3899,25 @@
     <t xml:space="preserve">7.16860055923462</t>
   </si>
   <si>
-    <t xml:space="preserve">7.3934006690979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.54795026779175</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.44179630279541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.51204586029053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.46677303314209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.44023370742798</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.41837882995605</t>
+    <t xml:space="preserve">7.39340114593506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.54795122146606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.44179582595825</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.51204442977905</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.46677255630493</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.44023275375366</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.41837787628174</t>
   </si>
   <si>
     <t xml:space="preserve">7.563560962677</t>
@@ -3926,7 +3926,7 @@
     <t xml:space="preserve">7.43555068969727</t>
   </si>
   <si>
-    <t xml:space="preserve">7.55887794494629</t>
+    <t xml:space="preserve">7.55887889862061</t>
   </si>
   <si>
     <t xml:space="preserve">7.6119556427002</t>
@@ -3944,7 +3944,7 @@
     <t xml:space="preserve">7.81724071502686</t>
   </si>
   <si>
-    <t xml:space="preserve">7.74308967590332</t>
+    <t xml:space="preserve">7.743088722229</t>
   </si>
   <si>
     <t xml:space="preserve">7.89139366149902</t>
@@ -3956,28 +3956,28 @@
     <t xml:space="preserve">7.76650524139404</t>
   </si>
   <si>
-    <t xml:space="preserve">7.14362382888794</t>
+    <t xml:space="preserve">7.1436243057251</t>
   </si>
   <si>
     <t xml:space="preserve">6.90477466583252</t>
   </si>
   <si>
-    <t xml:space="preserve">7.11708498001099</t>
+    <t xml:space="preserve">7.11708545684814</t>
   </si>
   <si>
     <t xml:space="preserve">7.35125207901001</t>
   </si>
   <si>
-    <t xml:space="preserve">6.98595142364502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.02185821533203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.18777799606323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.12729549407959</t>
+    <t xml:space="preserve">6.98595190048218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.02185773849487</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.18777894973755</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.12729597091675</t>
   </si>
   <si>
     <t xml:space="preserve">7.15998983383179</t>
@@ -3986,7 +3986,7 @@
     <t xml:space="preserve">7.10441017150879</t>
   </si>
   <si>
-    <t xml:space="preserve">7.31201696395874</t>
+    <t xml:space="preserve">7.31201601028442</t>
   </si>
   <si>
     <t xml:space="preserve">7.2760534286499</t>
@@ -3998,7 +3998,7 @@
     <t xml:space="preserve">7.36596202850342</t>
   </si>
   <si>
-    <t xml:space="preserve">7.28422689437866</t>
+    <t xml:space="preserve">7.28422594070435</t>
   </si>
   <si>
     <t xml:space="preserve">7.2874960899353</t>
@@ -4022,10 +4022,10 @@
     <t xml:space="preserve">6.96709489822388</t>
   </si>
   <si>
-    <t xml:space="preserve">6.99815511703491</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.85103178024292</t>
+    <t xml:space="preserve">6.99815464019775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.85103130340576</t>
   </si>
   <si>
     <t xml:space="preserve">6.5028395652771</t>
@@ -4037,7 +4037,7 @@
     <t xml:space="preserve">6.7938175201416</t>
   </si>
   <si>
-    <t xml:space="preserve">7.01940488815308</t>
+    <t xml:space="preserve">7.01940536499023</t>
   </si>
   <si>
     <t xml:space="preserve">6.86410856246948</t>
@@ -4052,16 +4052,16 @@
     <t xml:space="preserve">6.64342403411865</t>
   </si>
   <si>
-    <t xml:space="preserve">6.62871074676514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.64015436172485</t>
+    <t xml:space="preserve">6.62871122360229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.64015483856201</t>
   </si>
   <si>
     <t xml:space="preserve">6.5845742225647</t>
   </si>
   <si>
-    <t xml:space="preserve">6.67775297164917</t>
+    <t xml:space="preserve">6.67775344848633</t>
   </si>
   <si>
     <t xml:space="preserve">6.74314117431641</t>
@@ -4070,19 +4070,19 @@
     <t xml:space="preserve">6.66140508651733</t>
   </si>
   <si>
-    <t xml:space="preserve">6.77420043945312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.85266590118408</t>
+    <t xml:space="preserve">6.77419996261597</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.85266542434692</t>
   </si>
   <si>
     <t xml:space="preserve">6.92949676513672</t>
   </si>
   <si>
-    <t xml:space="preserve">6.8657431602478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.8281455039978</t>
+    <t xml:space="preserve">6.86574268341064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.82814502716064</t>
   </si>
   <si>
     <t xml:space="preserve">6.8690128326416</t>
@@ -4094,34 +4094,34 @@
     <t xml:space="preserve">6.97690343856812</t>
   </si>
   <si>
-    <t xml:space="preserve">6.91805362701416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.82651090621948</t>
+    <t xml:space="preserve">6.91805410385132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.82651042938232</t>
   </si>
   <si>
     <t xml:space="preserve">6.70227336883545</t>
   </si>
   <si>
-    <t xml:space="preserve">6.53226470947266</t>
+    <t xml:space="preserve">6.53226518630981</t>
   </si>
   <si>
     <t xml:space="preserve">6.63198184967041</t>
   </si>
   <si>
-    <t xml:space="preserve">6.59928750991821</t>
+    <t xml:space="preserve">6.59928703308105</t>
   </si>
   <si>
     <t xml:space="preserve">6.57803630828857</t>
   </si>
   <si>
-    <t xml:space="preserve">6.42927837371826</t>
+    <t xml:space="preserve">6.42927885055542</t>
   </si>
   <si>
     <t xml:space="preserve">6.34754323959351</t>
   </si>
   <si>
-    <t xml:space="preserve">6.4946665763855</t>
+    <t xml:space="preserve">6.49466609954834</t>
   </si>
   <si>
     <t xml:space="preserve">6.44562530517578</t>
@@ -4136,13 +4136,13 @@
     <t xml:space="preserve">6.52245616912842</t>
   </si>
   <si>
-    <t xml:space="preserve">6.54043769836426</t>
+    <t xml:space="preserve">6.5404372215271</t>
   </si>
   <si>
     <t xml:space="preserve">6.60909557342529</t>
   </si>
   <si>
-    <t xml:space="preserve">6.71044683456421</t>
+    <t xml:space="preserve">6.71044635772705</t>
   </si>
   <si>
     <t xml:space="preserve">6.80035543441772</t>
@@ -4151,7 +4151,7 @@
     <t xml:space="preserve">6.8134331703186</t>
   </si>
   <si>
-    <t xml:space="preserve">6.86737871170044</t>
+    <t xml:space="preserve">6.86737823486328</t>
   </si>
   <si>
     <t xml:space="preserve">6.7611231803894</t>
@@ -4172,7 +4172,7 @@
     <t xml:space="preserve">6.51918697357178</t>
   </si>
   <si>
-    <t xml:space="preserve">6.3835072517395</t>
+    <t xml:space="preserve">6.38350677490234</t>
   </si>
   <si>
     <t xml:space="preserve">6.3916802406311</t>
@@ -4184,7 +4184,7 @@
     <t xml:space="preserve">6.36715936660767</t>
   </si>
   <si>
-    <t xml:space="preserve">6.49793577194214</t>
+    <t xml:space="preserve">6.4979362487793</t>
   </si>
   <si>
     <t xml:space="preserve">6.68919610977173</t>
@@ -4205,7 +4205,7 @@
     <t xml:space="preserve">6.26090383529663</t>
   </si>
   <si>
-    <t xml:space="preserve">6.36389017105103</t>
+    <t xml:space="preserve">6.36388969421387</t>
   </si>
   <si>
     <t xml:space="preserve">6.46033763885498</t>
@@ -4214,13 +4214,13 @@
     <t xml:space="preserve">6.62217330932617</t>
   </si>
   <si>
-    <t xml:space="preserve">6.86247444152832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.824875831604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.80198955535889</t>
+    <t xml:space="preserve">6.86247396469116</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.82487630844116</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.80199003219604</t>
   </si>
   <si>
     <t xml:space="preserve">6.73660182952881</t>
@@ -4259,13 +4259,13 @@
     <t xml:space="preserve">7.50327634811401</t>
   </si>
   <si>
-    <t xml:space="preserve">7.54904842376709</t>
+    <t xml:space="preserve">7.54904937744141</t>
   </si>
   <si>
     <t xml:space="preserve">7.64222574234009</t>
   </si>
   <si>
-    <t xml:space="preserve">7.97243499755859</t>
+    <t xml:space="preserve">7.97243595123291</t>
   </si>
   <si>
     <t xml:space="preserve">7.87762260437012</t>
@@ -4277,7 +4277,7 @@
     <t xml:space="preserve">7.96099376678467</t>
   </si>
   <si>
-    <t xml:space="preserve">7.86618041992188</t>
+    <t xml:space="preserve">7.86617946624756</t>
   </si>
   <si>
     <t xml:space="preserve">7.8122353553772</t>
@@ -16472,7 +16472,7 @@
         <v>6.09000015258789</v>
       </c>
       <c r="G382" t="s">
-        <v>240</v>
+        <v>232</v>
       </c>
       <c r="H382" t="s">
         <v>9</v>
@@ -16498,7 +16498,7 @@
         <v>6.03499984741211</v>
       </c>
       <c r="G383" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="H383" t="s">
         <v>9</v>
@@ -16524,7 +16524,7 @@
         <v>5.99499988555908</v>
       </c>
       <c r="G384" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="H384" t="s">
         <v>9</v>
@@ -16550,7 +16550,7 @@
         <v>6.00500011444092</v>
       </c>
       <c r="G385" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="H385" t="s">
         <v>9</v>
@@ -16576,7 +16576,7 @@
         <v>5.96999979019165</v>
       </c>
       <c r="G386" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="H386" t="s">
         <v>9</v>
@@ -16602,7 +16602,7 @@
         <v>5.94500017166138</v>
       </c>
       <c r="G387" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="H387" t="s">
         <v>9</v>
@@ -16628,7 +16628,7 @@
         <v>6.05000019073486</v>
       </c>
       <c r="G388" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="H388" t="s">
         <v>9</v>
@@ -16654,7 +16654,7 @@
         <v>6.06500005722046</v>
       </c>
       <c r="G389" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="H389" t="s">
         <v>9</v>
@@ -16706,7 +16706,7 @@
         <v>6.06500005722046</v>
       </c>
       <c r="G391" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="H391" t="s">
         <v>9</v>
@@ -16732,7 +16732,7 @@
         <v>6.125</v>
       </c>
       <c r="G392" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H392" t="s">
         <v>9</v>
@@ -16758,7 +16758,7 @@
         <v>6.09499979019165</v>
       </c>
       <c r="G393" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="H393" t="s">
         <v>9</v>
@@ -16810,7 +16810,7 @@
         <v>6.07000017166138</v>
       </c>
       <c r="G395" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="H395" t="s">
         <v>9</v>
@@ -16836,7 +16836,7 @@
         <v>6.05499982833862</v>
       </c>
       <c r="G396" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="H396" t="s">
         <v>9</v>
@@ -16862,7 +16862,7 @@
         <v>5.98000001907349</v>
       </c>
       <c r="G397" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="H397" t="s">
         <v>9</v>
@@ -16888,7 +16888,7 @@
         <v>5.96500015258789</v>
       </c>
       <c r="G398" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="H398" t="s">
         <v>9</v>
@@ -16914,7 +16914,7 @@
         <v>6.02500009536743</v>
       </c>
       <c r="G399" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="H399" t="s">
         <v>9</v>
@@ -16940,7 +16940,7 @@
         <v>6.03499984741211</v>
       </c>
       <c r="G400" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="H400" t="s">
         <v>9</v>
@@ -16966,7 +16966,7 @@
         <v>6.23999977111816</v>
       </c>
       <c r="G401" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="H401" t="s">
         <v>9</v>
@@ -16992,7 +16992,7 @@
         <v>6.26000022888184</v>
       </c>
       <c r="G402" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="H402" t="s">
         <v>9</v>
@@ -17018,7 +17018,7 @@
         <v>6.28999996185303</v>
       </c>
       <c r="G403" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="H403" t="s">
         <v>9</v>
@@ -17044,7 +17044,7 @@
         <v>6.20499992370605</v>
       </c>
       <c r="G404" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="H404" t="s">
         <v>9</v>
@@ -17070,7 +17070,7 @@
         <v>6.21999979019165</v>
       </c>
       <c r="G405" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="H405" t="s">
         <v>9</v>
@@ -17096,7 +17096,7 @@
         <v>6.22499990463257</v>
       </c>
       <c r="G406" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="H406" t="s">
         <v>9</v>
@@ -17122,7 +17122,7 @@
         <v>6.28499984741211</v>
       </c>
       <c r="G407" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="H407" t="s">
         <v>9</v>
@@ -17148,7 +17148,7 @@
         <v>6.1100001335144</v>
       </c>
       <c r="G408" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="H408" t="s">
         <v>9</v>
@@ -17174,7 +17174,7 @@
         <v>6.13000011444092</v>
       </c>
       <c r="G409" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="H409" t="s">
         <v>9</v>
@@ -17200,7 +17200,7 @@
         <v>6.21500015258789</v>
       </c>
       <c r="G410" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="H410" t="s">
         <v>9</v>
@@ -17226,7 +17226,7 @@
         <v>6.23000001907349</v>
       </c>
       <c r="G411" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="H411" t="s">
         <v>9</v>
@@ -17252,7 +17252,7 @@
         <v>6.21500015258789</v>
       </c>
       <c r="G412" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="H412" t="s">
         <v>9</v>
@@ -17278,7 +17278,7 @@
         <v>6.15000009536743</v>
       </c>
       <c r="G413" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="H413" t="s">
         <v>9</v>
@@ -17304,7 +17304,7 @@
         <v>6.1100001335144</v>
       </c>
       <c r="G414" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="H414" t="s">
         <v>9</v>
@@ -17330,7 +17330,7 @@
         <v>6.1100001335144</v>
       </c>
       <c r="G415" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="H415" t="s">
         <v>9</v>
@@ -17356,7 +17356,7 @@
         <v>6.15000009536743</v>
       </c>
       <c r="G416" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="H416" t="s">
         <v>9</v>
@@ -17382,7 +17382,7 @@
         <v>6.11999988555908</v>
       </c>
       <c r="G417" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="H417" t="s">
         <v>9</v>
@@ -17408,7 +17408,7 @@
         <v>6.10500001907349</v>
       </c>
       <c r="G418" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="H418" t="s">
         <v>9</v>
@@ -17434,7 +17434,7 @@
         <v>6.1100001335144</v>
       </c>
       <c r="G419" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="H419" t="s">
         <v>9</v>
@@ -17460,7 +17460,7 @@
         <v>6.06500005722046</v>
       </c>
       <c r="G420" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="H420" t="s">
         <v>9</v>
@@ -17486,7 +17486,7 @@
         <v>6.06500005722046</v>
       </c>
       <c r="G421" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="H421" t="s">
         <v>9</v>
@@ -17512,7 +17512,7 @@
         <v>6.11999988555908</v>
       </c>
       <c r="G422" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="H422" t="s">
         <v>9</v>
@@ -17538,7 +17538,7 @@
         <v>6.1100001335144</v>
       </c>
       <c r="G423" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="H423" t="s">
         <v>9</v>
@@ -17564,7 +17564,7 @@
         <v>6.125</v>
       </c>
       <c r="G424" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H424" t="s">
         <v>9</v>
@@ -17590,7 +17590,7 @@
         <v>6.09000015258789</v>
       </c>
       <c r="G425" t="s">
-        <v>240</v>
+        <v>232</v>
       </c>
       <c r="H425" t="s">
         <v>9</v>
@@ -17616,7 +17616,7 @@
         <v>6.14499998092651</v>
       </c>
       <c r="G426" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="H426" t="s">
         <v>9</v>
@@ -17642,7 +17642,7 @@
         <v>6.10500001907349</v>
       </c>
       <c r="G427" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="H427" t="s">
         <v>9</v>
@@ -17668,7 +17668,7 @@
         <v>6.11999988555908</v>
       </c>
       <c r="G428" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="H428" t="s">
         <v>9</v>
@@ -17694,7 +17694,7 @@
         <v>6.07000017166138</v>
       </c>
       <c r="G429" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="H429" t="s">
         <v>9</v>
@@ -17720,7 +17720,7 @@
         <v>6.03499984741211</v>
       </c>
       <c r="G430" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="H430" t="s">
         <v>9</v>
@@ -17746,7 +17746,7 @@
         <v>6.06500005722046</v>
       </c>
       <c r="G431" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="H431" t="s">
         <v>9</v>
@@ -17772,7 +17772,7 @@
         <v>6.06500005722046</v>
       </c>
       <c r="G432" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="H432" t="s">
         <v>9</v>
@@ -17798,7 +17798,7 @@
         <v>6.08500003814697</v>
       </c>
       <c r="G433" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="H433" t="s">
         <v>9</v>
@@ -17824,7 +17824,7 @@
         <v>6.15500020980835</v>
       </c>
       <c r="G434" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="H434" t="s">
         <v>9</v>
@@ -17850,7 +17850,7 @@
         <v>6.25</v>
       </c>
       <c r="G435" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="H435" t="s">
         <v>9</v>
@@ -17876,7 +17876,7 @@
         <v>6.21000003814697</v>
       </c>
       <c r="G436" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="H436" t="s">
         <v>9</v>
@@ -17902,7 +17902,7 @@
         <v>6.19500017166138</v>
       </c>
       <c r="G437" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="H437" t="s">
         <v>9</v>
@@ -17928,7 +17928,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G438" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="H438" t="s">
         <v>9</v>
@@ -17954,7 +17954,7 @@
         <v>6.20499992370605</v>
       </c>
       <c r="G439" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="H439" t="s">
         <v>9</v>
@@ -17980,7 +17980,7 @@
         <v>6.15000009536743</v>
       </c>
       <c r="G440" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="H440" t="s">
         <v>9</v>
@@ -18006,7 +18006,7 @@
         <v>6.15999984741211</v>
       </c>
       <c r="G441" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="H441" t="s">
         <v>9</v>
@@ -18032,7 +18032,7 @@
         <v>6.14499998092651</v>
       </c>
       <c r="G442" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="H442" t="s">
         <v>9</v>
@@ -18058,7 +18058,7 @@
         <v>6.18499994277954</v>
       </c>
       <c r="G443" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="H443" t="s">
         <v>9</v>
@@ -18084,7 +18084,7 @@
         <v>6.15000009536743</v>
       </c>
       <c r="G444" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="H444" t="s">
         <v>9</v>
@@ -18110,7 +18110,7 @@
         <v>6.1399998664856</v>
       </c>
       <c r="G445" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="H445" t="s">
         <v>9</v>
@@ -18136,7 +18136,7 @@
         <v>6.17500019073486</v>
       </c>
       <c r="G446" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="H446" t="s">
         <v>9</v>
@@ -18162,7 +18162,7 @@
         <v>6.21500015258789</v>
       </c>
       <c r="G447" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="H447" t="s">
         <v>9</v>
@@ -18188,7 +18188,7 @@
         <v>6.23000001907349</v>
       </c>
       <c r="G448" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="H448" t="s">
         <v>9</v>
@@ -18214,7 +18214,7 @@
         <v>6.2649998664856</v>
       </c>
       <c r="G449" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="H449" t="s">
         <v>9</v>
@@ -18240,7 +18240,7 @@
         <v>6.25</v>
       </c>
       <c r="G450" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="H450" t="s">
         <v>9</v>
@@ -18266,7 +18266,7 @@
         <v>6.19500017166138</v>
       </c>
       <c r="G451" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="H451" t="s">
         <v>9</v>
@@ -18292,7 +18292,7 @@
         <v>6.15999984741211</v>
       </c>
       <c r="G452" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="H452" t="s">
         <v>9</v>
@@ -18318,7 +18318,7 @@
         <v>6.14499998092651</v>
       </c>
       <c r="G453" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="H453" t="s">
         <v>9</v>
@@ -18344,7 +18344,7 @@
         <v>6.17500019073486</v>
       </c>
       <c r="G454" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="H454" t="s">
         <v>9</v>
@@ -18370,7 +18370,7 @@
         <v>6.14499998092651</v>
       </c>
       <c r="G455" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="H455" t="s">
         <v>9</v>
@@ -18396,7 +18396,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G456" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="H456" t="s">
         <v>9</v>
@@ -18422,7 +18422,7 @@
         <v>6.18499994277954</v>
       </c>
       <c r="G457" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="H457" t="s">
         <v>9</v>
@@ -18448,7 +18448,7 @@
         <v>6.16499996185303</v>
       </c>
       <c r="G458" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="H458" t="s">
         <v>9</v>
@@ -18474,7 +18474,7 @@
         <v>6.21000003814697</v>
       </c>
       <c r="G459" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="H459" t="s">
         <v>9</v>
@@ -18500,7 +18500,7 @@
         <v>6.19500017166138</v>
       </c>
       <c r="G460" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="H460" t="s">
         <v>9</v>
@@ -18526,7 +18526,7 @@
         <v>6.25</v>
       </c>
       <c r="G461" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="H461" t="s">
         <v>9</v>
@@ -18552,7 +18552,7 @@
         <v>6.23999977111816</v>
       </c>
       <c r="G462" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="H462" t="s">
         <v>9</v>
@@ -18578,7 +18578,7 @@
         <v>6.21000003814697</v>
       </c>
       <c r="G463" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="H463" t="s">
         <v>9</v>
@@ -18604,7 +18604,7 @@
         <v>6.18499994277954</v>
       </c>
       <c r="G464" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="H464" t="s">
         <v>9</v>
@@ -18630,7 +18630,7 @@
         <v>6.22499990463257</v>
       </c>
       <c r="G465" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="H465" t="s">
         <v>9</v>
@@ -18656,7 +18656,7 @@
         <v>6.20499992370605</v>
       </c>
       <c r="G466" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="H466" t="s">
         <v>9</v>
@@ -18682,7 +18682,7 @@
         <v>6.27500009536743</v>
       </c>
       <c r="G467" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="H467" t="s">
         <v>9</v>
@@ -18708,7 +18708,7 @@
         <v>6.23000001907349</v>
       </c>
       <c r="G468" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="H468" t="s">
         <v>9</v>
@@ -18734,7 +18734,7 @@
         <v>6.26000022888184</v>
       </c>
       <c r="G469" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="H469" t="s">
         <v>9</v>
@@ -18760,7 +18760,7 @@
         <v>6.27500009536743</v>
       </c>
       <c r="G470" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="H470" t="s">
         <v>9</v>
@@ -18786,7 +18786,7 @@
         <v>6.29500007629395</v>
       </c>
       <c r="G471" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="H471" t="s">
         <v>9</v>
@@ -18812,7 +18812,7 @@
         <v>6.26999998092651</v>
       </c>
       <c r="G472" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="H472" t="s">
         <v>9</v>
@@ -18838,7 +18838,7 @@
         <v>6.23999977111816</v>
       </c>
       <c r="G473" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="H473" t="s">
         <v>9</v>
@@ -18864,7 +18864,7 @@
         <v>6.28000020980835</v>
       </c>
       <c r="G474" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="H474" t="s">
         <v>9</v>
@@ -18890,7 +18890,7 @@
         <v>6.25500011444092</v>
       </c>
       <c r="G475" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="H475" t="s">
         <v>9</v>
@@ -18916,7 +18916,7 @@
         <v>6.22499990463257</v>
       </c>
       <c r="G476" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="H476" t="s">
         <v>9</v>
@@ -18942,7 +18942,7 @@
         <v>6.17500019073486</v>
       </c>
       <c r="G477" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="H477" t="s">
         <v>9</v>
@@ -18968,7 +18968,7 @@
         <v>6.13500022888184</v>
       </c>
       <c r="G478" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="H478" t="s">
         <v>9</v>
@@ -18994,7 +18994,7 @@
         <v>6.08500003814697</v>
       </c>
       <c r="G479" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="H479" t="s">
         <v>9</v>
@@ -19020,7 +19020,7 @@
         <v>6.11999988555908</v>
       </c>
       <c r="G480" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="H480" t="s">
         <v>9</v>
@@ -19046,7 +19046,7 @@
         <v>6.15999984741211</v>
       </c>
       <c r="G481" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="H481" t="s">
         <v>9</v>
@@ -19072,7 +19072,7 @@
         <v>6.13000011444092</v>
       </c>
       <c r="G482" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="H482" t="s">
         <v>9</v>
@@ -19098,7 +19098,7 @@
         <v>6.11499977111816</v>
       </c>
       <c r="G483" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="H483" t="s">
         <v>9</v>
@@ -19124,7 +19124,7 @@
         <v>6.10500001907349</v>
       </c>
       <c r="G484" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="H484" t="s">
         <v>9</v>
@@ -19150,7 +19150,7 @@
         <v>6.13500022888184</v>
       </c>
       <c r="G485" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="H485" t="s">
         <v>9</v>
@@ -19176,7 +19176,7 @@
         <v>6.11999988555908</v>
       </c>
       <c r="G486" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="H486" t="s">
         <v>9</v>
@@ -19202,7 +19202,7 @@
         <v>6.15000009536743</v>
       </c>
       <c r="G487" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="H487" t="s">
         <v>9</v>
@@ -19228,7 +19228,7 @@
         <v>6.125</v>
       </c>
       <c r="G488" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H488" t="s">
         <v>9</v>
@@ -19254,7 +19254,7 @@
         <v>6.09999990463257</v>
       </c>
       <c r="G489" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="H489" t="s">
         <v>9</v>
@@ -19280,7 +19280,7 @@
         <v>6.1399998664856</v>
       </c>
       <c r="G490" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="H490" t="s">
         <v>9</v>
@@ -19306,7 +19306,7 @@
         <v>6.14499998092651</v>
       </c>
       <c r="G491" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="H491" t="s">
         <v>9</v>
@@ -19332,7 +19332,7 @@
         <v>6.13500022888184</v>
       </c>
       <c r="G492" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="H492" t="s">
         <v>9</v>
@@ -19358,7 +19358,7 @@
         <v>6.09000015258789</v>
       </c>
       <c r="G493" t="s">
-        <v>240</v>
+        <v>232</v>
       </c>
       <c r="H493" t="s">
         <v>9</v>
@@ -19384,7 +19384,7 @@
         <v>6.1399998664856</v>
       </c>
       <c r="G494" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="H494" t="s">
         <v>9</v>
@@ -19410,7 +19410,7 @@
         <v>6.14499998092651</v>
       </c>
       <c r="G495" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="H495" t="s">
         <v>9</v>
@@ -19436,7 +19436,7 @@
         <v>6.09000015258789</v>
       </c>
       <c r="G496" t="s">
-        <v>240</v>
+        <v>232</v>
       </c>
       <c r="H496" t="s">
         <v>9</v>
@@ -19462,7 +19462,7 @@
         <v>6.09999990463257</v>
       </c>
       <c r="G497" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="H497" t="s">
         <v>9</v>
@@ -19488,7 +19488,7 @@
         <v>6.125</v>
       </c>
       <c r="G498" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H498" t="s">
         <v>9</v>
@@ -19514,7 +19514,7 @@
         <v>6.11999988555908</v>
       </c>
       <c r="G499" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="H499" t="s">
         <v>9</v>
@@ -19540,7 +19540,7 @@
         <v>6.1399998664856</v>
       </c>
       <c r="G500" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="H500" t="s">
         <v>9</v>
@@ -19566,7 +19566,7 @@
         <v>6.13000011444092</v>
       </c>
       <c r="G501" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="H501" t="s">
         <v>9</v>
@@ -19592,7 +19592,7 @@
         <v>6.11499977111816</v>
       </c>
       <c r="G502" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="H502" t="s">
         <v>9</v>
@@ -19618,7 +19618,7 @@
         <v>6.36499977111816</v>
       </c>
       <c r="G503" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="H503" t="s">
         <v>9</v>
@@ -19644,7 +19644,7 @@
         <v>6.40999984741211</v>
       </c>
       <c r="G504" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="H504" t="s">
         <v>9</v>
@@ -19670,7 +19670,7 @@
         <v>6.36999988555908</v>
       </c>
       <c r="G505" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="H505" t="s">
         <v>9</v>
@@ -19696,7 +19696,7 @@
         <v>6.34999990463257</v>
       </c>
       <c r="G506" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="H506" t="s">
         <v>9</v>
@@ -19722,7 +19722,7 @@
         <v>6.36999988555908</v>
       </c>
       <c r="G507" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="H507" t="s">
         <v>9</v>
@@ -19748,7 +19748,7 @@
         <v>6.32999992370605</v>
       </c>
       <c r="G508" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="H508" t="s">
         <v>9</v>
@@ -19774,7 +19774,7 @@
         <v>6.32999992370605</v>
       </c>
       <c r="G509" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="H509" t="s">
         <v>9</v>
@@ -19800,7 +19800,7 @@
         <v>6.32999992370605</v>
       </c>
       <c r="G510" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="H510" t="s">
         <v>9</v>
@@ -19826,7 +19826,7 @@
         <v>6.27500009536743</v>
       </c>
       <c r="G511" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="H511" t="s">
         <v>9</v>
@@ -19852,7 +19852,7 @@
         <v>6.29500007629395</v>
       </c>
       <c r="G512" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="H512" t="s">
         <v>9</v>
@@ -19878,7 +19878,7 @@
         <v>6.35500001907349</v>
       </c>
       <c r="G513" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="H513" t="s">
         <v>9</v>
@@ -19904,7 +19904,7 @@
         <v>6.375</v>
       </c>
       <c r="G514" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="H514" t="s">
         <v>9</v>
@@ -19930,7 +19930,7 @@
         <v>6.40500020980835</v>
       </c>
       <c r="G515" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="H515" t="s">
         <v>9</v>
@@ -19956,7 +19956,7 @@
         <v>6.42999982833862</v>
       </c>
       <c r="G516" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="H516" t="s">
         <v>9</v>
@@ -19982,7 +19982,7 @@
         <v>6.44999980926514</v>
       </c>
       <c r="G517" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="H517" t="s">
         <v>9</v>
@@ -20008,7 +20008,7 @@
         <v>6.46999979019165</v>
       </c>
       <c r="G518" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="H518" t="s">
         <v>9</v>
@@ -20034,7 +20034,7 @@
         <v>6.44000005722046</v>
       </c>
       <c r="G519" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="H519" t="s">
         <v>9</v>
@@ -20060,7 +20060,7 @@
         <v>6.48999977111816</v>
       </c>
       <c r="G520" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="H520" t="s">
         <v>9</v>
@@ -20086,7 +20086,7 @@
         <v>6.53999996185303</v>
       </c>
       <c r="G521" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="H521" t="s">
         <v>9</v>
@@ -20112,7 +20112,7 @@
         <v>6.53999996185303</v>
       </c>
       <c r="G522" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="H522" t="s">
         <v>9</v>
@@ -20138,7 +20138,7 @@
         <v>6.53499984741211</v>
       </c>
       <c r="G523" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="H523" t="s">
         <v>9</v>
@@ -20164,7 +20164,7 @@
         <v>6.57999992370605</v>
       </c>
       <c r="G524" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="H524" t="s">
         <v>9</v>
@@ -20190,7 +20190,7 @@
         <v>6.72499990463257</v>
       </c>
       <c r="G525" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="H525" t="s">
         <v>9</v>
@@ -20216,7 +20216,7 @@
         <v>6.71999979019165</v>
       </c>
       <c r="G526" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="H526" t="s">
         <v>9</v>
@@ -20242,7 +20242,7 @@
         <v>6.69500017166138</v>
       </c>
       <c r="G527" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="H527" t="s">
         <v>9</v>
@@ -20268,7 +20268,7 @@
         <v>6.65000009536743</v>
       </c>
       <c r="G528" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="H528" t="s">
         <v>9</v>
@@ -20294,7 +20294,7 @@
         <v>6.67500019073486</v>
       </c>
       <c r="G529" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="H529" t="s">
         <v>9</v>
@@ -20320,7 +20320,7 @@
         <v>6.69000005722046</v>
       </c>
       <c r="G530" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="H530" t="s">
         <v>9</v>
@@ -20346,7 +20346,7 @@
         <v>6.65199995040894</v>
       </c>
       <c r="G531" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="H531" t="s">
         <v>9</v>
@@ -20372,7 +20372,7 @@
         <v>6.62400007247925</v>
       </c>
       <c r="G532" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="H532" t="s">
         <v>9</v>
@@ -20398,7 +20398,7 @@
         <v>6.66400003433228</v>
       </c>
       <c r="G533" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="H533" t="s">
         <v>9</v>
@@ -20424,7 +20424,7 @@
         <v>6.65199995040894</v>
       </c>
       <c r="G534" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="H534" t="s">
         <v>9</v>
@@ -20450,7 +20450,7 @@
         <v>6.58400011062622</v>
       </c>
       <c r="G535" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="H535" t="s">
         <v>9</v>
@@ -20476,7 +20476,7 @@
         <v>6.59800004959106</v>
       </c>
       <c r="G536" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="H536" t="s">
         <v>9</v>
@@ -20502,7 +20502,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G537" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="H537" t="s">
         <v>9</v>
@@ -20528,7 +20528,7 @@
         <v>6.57000017166138</v>
       </c>
       <c r="G538" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="H538" t="s">
         <v>9</v>
@@ -20554,7 +20554,7 @@
         <v>6.44600009918213</v>
       </c>
       <c r="G539" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="H539" t="s">
         <v>9</v>
@@ -20580,7 +20580,7 @@
         <v>6.43599987030029</v>
       </c>
       <c r="G540" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="H540" t="s">
         <v>9</v>
@@ -20606,7 +20606,7 @@
         <v>6.53999996185303</v>
       </c>
       <c r="G541" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="H541" t="s">
         <v>9</v>
@@ -20632,7 +20632,7 @@
         <v>6.46400022506714</v>
       </c>
       <c r="G542" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="H542" t="s">
         <v>9</v>
@@ -20658,7 +20658,7 @@
         <v>6.52799987792969</v>
       </c>
       <c r="G543" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="H543" t="s">
         <v>9</v>
@@ -20684,7 +20684,7 @@
         <v>6.58199977874756</v>
       </c>
       <c r="G544" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="H544" t="s">
         <v>9</v>
@@ -20710,7 +20710,7 @@
         <v>6.6560001373291</v>
       </c>
       <c r="G545" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="H545" t="s">
         <v>9</v>
@@ -20736,7 +20736,7 @@
         <v>6.66599988937378</v>
       </c>
       <c r="G546" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="H546" t="s">
         <v>9</v>
@@ -20762,7 +20762,7 @@
         <v>6.78000020980835</v>
       </c>
       <c r="G547" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="H547" t="s">
         <v>9</v>
@@ -20788,7 +20788,7 @@
         <v>6.76000022888184</v>
       </c>
       <c r="G548" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="H548" t="s">
         <v>9</v>
@@ -20814,7 +20814,7 @@
         <v>6.70599985122681</v>
       </c>
       <c r="G549" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="H549" t="s">
         <v>9</v>
@@ -20840,7 +20840,7 @@
         <v>6.71199989318848</v>
       </c>
       <c r="G550" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="H550" t="s">
         <v>9</v>
@@ -20866,7 +20866,7 @@
         <v>6.65399980545044</v>
       </c>
       <c r="G551" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="H551" t="s">
         <v>9</v>
@@ -20892,7 +20892,7 @@
         <v>7.03999996185303</v>
       </c>
       <c r="G552" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="H552" t="s">
         <v>9</v>
@@ -20918,7 +20918,7 @@
         <v>7.06199979782104</v>
       </c>
       <c r="G553" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="H553" t="s">
         <v>9</v>
@@ -20944,7 +20944,7 @@
         <v>7.01800012588501</v>
       </c>
       <c r="G554" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="H554" t="s">
         <v>9</v>
@@ -20970,7 +20970,7 @@
         <v>6.86600017547607</v>
       </c>
       <c r="G555" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="H555" t="s">
         <v>9</v>
@@ -20996,7 +20996,7 @@
         <v>6.90999984741211</v>
       </c>
       <c r="G556" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="H556" t="s">
         <v>9</v>
@@ -21022,7 +21022,7 @@
         <v>6.96799993515015</v>
       </c>
       <c r="G557" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="H557" t="s">
         <v>9</v>
@@ -21048,7 +21048,7 @@
         <v>7.15199995040894</v>
       </c>
       <c r="G558" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="H558" t="s">
         <v>9</v>
@@ -21074,7 +21074,7 @@
         <v>7.33400011062622</v>
       </c>
       <c r="G559" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="H559" t="s">
         <v>9</v>
@@ -21100,7 +21100,7 @@
         <v>7.2960000038147</v>
       </c>
       <c r="G560" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="H560" t="s">
         <v>9</v>
@@ -21126,7 +21126,7 @@
         <v>7.42000007629395</v>
       </c>
       <c r="G561" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="H561" t="s">
         <v>9</v>
@@ -21152,7 +21152,7 @@
         <v>7.26000022888184</v>
       </c>
       <c r="G562" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="H562" t="s">
         <v>9</v>
@@ -21178,7 +21178,7 @@
         <v>7.16599988937378</v>
       </c>
       <c r="G563" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="H563" t="s">
         <v>9</v>
@@ -21204,7 +21204,7 @@
         <v>7.28000020980835</v>
       </c>
       <c r="G564" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="H564" t="s">
         <v>9</v>
@@ -21230,7 +21230,7 @@
         <v>7.39400005340576</v>
       </c>
       <c r="G565" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="H565" t="s">
         <v>9</v>
@@ -21256,7 +21256,7 @@
         <v>7.33799982070923</v>
       </c>
       <c r="G566" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="H566" t="s">
         <v>9</v>
@@ -21282,7 +21282,7 @@
         <v>7.38800001144409</v>
       </c>
       <c r="G567" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="H567" t="s">
         <v>9</v>
@@ -21308,7 +21308,7 @@
         <v>7.37400007247925</v>
       </c>
       <c r="G568" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="H568" t="s">
         <v>9</v>
@@ -21334,7 +21334,7 @@
         <v>7.30600023269653</v>
       </c>
       <c r="G569" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="H569" t="s">
         <v>9</v>
@@ -21360,7 +21360,7 @@
         <v>7.24599981307983</v>
       </c>
       <c r="G570" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="H570" t="s">
         <v>9</v>
@@ -21386,7 +21386,7 @@
         <v>7.21999979019165</v>
       </c>
       <c r="G571" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="H571" t="s">
         <v>9</v>
@@ -21412,7 +21412,7 @@
         <v>7.24399995803833</v>
       </c>
       <c r="G572" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="H572" t="s">
         <v>9</v>
@@ -21438,7 +21438,7 @@
         <v>7.35599994659424</v>
       </c>
       <c r="G573" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="H573" t="s">
         <v>9</v>
@@ -21464,7 +21464,7 @@
         <v>7.42000007629395</v>
       </c>
       <c r="G574" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="H574" t="s">
         <v>9</v>
@@ -21490,7 +21490,7 @@
         <v>7.36999988555908</v>
       </c>
       <c r="G575" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="H575" t="s">
         <v>9</v>
@@ -21516,7 +21516,7 @@
         <v>7.42600011825562</v>
       </c>
       <c r="G576" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="H576" t="s">
         <v>9</v>
@@ -21542,7 +21542,7 @@
         <v>7.55000019073486</v>
       </c>
       <c r="G577" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="H577" t="s">
         <v>9</v>
@@ -21568,7 +21568,7 @@
         <v>7.54199981689453</v>
       </c>
       <c r="G578" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="H578" t="s">
         <v>9</v>
@@ -21594,7 +21594,7 @@
         <v>7.59999990463257</v>
       </c>
       <c r="G579" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="H579" t="s">
         <v>9</v>
@@ -21620,7 +21620,7 @@
         <v>7.68400001525879</v>
       </c>
       <c r="G580" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="H580" t="s">
         <v>9</v>
@@ -21646,7 +21646,7 @@
         <v>7.67199993133545</v>
       </c>
       <c r="G581" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="H581" t="s">
         <v>9</v>
@@ -21672,7 +21672,7 @@
         <v>7.67799997329712</v>
       </c>
       <c r="G582" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="H582" t="s">
         <v>9</v>
@@ -21698,7 +21698,7 @@
         <v>7.67399978637695</v>
       </c>
       <c r="G583" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="H583" t="s">
         <v>9</v>
@@ -21724,7 +21724,7 @@
         <v>7.71999979019165</v>
       </c>
       <c r="G584" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="H584" t="s">
         <v>9</v>
@@ -21750,7 +21750,7 @@
         <v>7.78999996185303</v>
       </c>
       <c r="G585" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="H585" t="s">
         <v>9</v>
@@ -21776,7 +21776,7 @@
         <v>7.74200010299683</v>
       </c>
       <c r="G586" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="H586" t="s">
         <v>9</v>
@@ -21802,7 +21802,7 @@
         <v>7.75799989700317</v>
       </c>
       <c r="G587" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="H587" t="s">
         <v>9</v>
@@ -21828,7 +21828,7 @@
         <v>7.78999996185303</v>
       </c>
       <c r="G588" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="H588" t="s">
         <v>9</v>
@@ -21854,7 +21854,7 @@
         <v>7.86999988555908</v>
       </c>
       <c r="G589" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="H589" t="s">
         <v>9</v>
@@ -21880,7 +21880,7 @@
         <v>7.87799978256226</v>
       </c>
       <c r="G590" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="H590" t="s">
         <v>9</v>
@@ -21906,7 +21906,7 @@
         <v>7.91200017929077</v>
       </c>
       <c r="G591" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="H591" t="s">
         <v>9</v>
@@ -21932,7 +21932,7 @@
         <v>7.92799997329712</v>
       </c>
       <c r="G592" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="H592" t="s">
         <v>9</v>
@@ -21958,7 +21958,7 @@
         <v>7.97200012207031</v>
       </c>
       <c r="G593" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="H593" t="s">
         <v>9</v>
@@ -21984,7 +21984,7 @@
         <v>8.10599994659424</v>
       </c>
       <c r="G594" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="H594" t="s">
         <v>9</v>
@@ -22010,7 +22010,7 @@
         <v>8.08399963378906</v>
       </c>
       <c r="G595" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="H595" t="s">
         <v>9</v>
@@ -22036,7 +22036,7 @@
         <v>8.06999969482422</v>
       </c>
       <c r="G596" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="H596" t="s">
         <v>9</v>
@@ -22062,7 +22062,7 @@
         <v>8.1540002822876</v>
       </c>
       <c r="G597" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="H597" t="s">
         <v>9</v>
@@ -22088,7 +22088,7 @@
         <v>8.11600017547607</v>
       </c>
       <c r="G598" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="H598" t="s">
         <v>9</v>
@@ -22114,7 +22114,7 @@
         <v>8.07800006866455</v>
       </c>
       <c r="G599" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="H599" t="s">
         <v>9</v>
@@ -22140,7 +22140,7 @@
         <v>8.10599994659424</v>
       </c>
       <c r="G600" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="H600" t="s">
         <v>9</v>
@@ -22166,7 +22166,7 @@
         <v>8.11600017547607</v>
       </c>
       <c r="G601" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="H601" t="s">
         <v>9</v>
@@ -22192,7 +22192,7 @@
         <v>8.14999961853027</v>
       </c>
       <c r="G602" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="H602" t="s">
         <v>9</v>
@@ -22218,7 +22218,7 @@
         <v>8.1540002822876</v>
       </c>
       <c r="G603" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="H603" t="s">
         <v>9</v>
@@ -22244,7 +22244,7 @@
         <v>8.2180004119873</v>
       </c>
       <c r="G604" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="H604" t="s">
         <v>9</v>
@@ -22270,7 +22270,7 @@
         <v>7.90999984741211</v>
       </c>
       <c r="G605" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="H605" t="s">
         <v>9</v>
@@ -22296,7 +22296,7 @@
         <v>7.89200019836426</v>
       </c>
       <c r="G606" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="H606" t="s">
         <v>9</v>
@@ -22322,7 +22322,7 @@
         <v>7.61999988555908</v>
       </c>
       <c r="G607" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="H607" t="s">
         <v>9</v>
@@ -22348,7 +22348,7 @@
         <v>7.63600015640259</v>
       </c>
       <c r="G608" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="H608" t="s">
         <v>9</v>
@@ -22374,7 +22374,7 @@
         <v>7.69799995422363</v>
       </c>
       <c r="G609" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="H609" t="s">
         <v>9</v>
@@ -22400,7 +22400,7 @@
         <v>7.65999984741211</v>
       </c>
       <c r="G610" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="H610" t="s">
         <v>9</v>
@@ -22426,7 +22426,7 @@
         <v>7.70599985122681</v>
       </c>
       <c r="G611" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="H611" t="s">
         <v>9</v>
@@ -22452,7 +22452,7 @@
         <v>7.58799982070923</v>
       </c>
       <c r="G612" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="H612" t="s">
         <v>9</v>
@@ -22478,7 +22478,7 @@
         <v>7.3439998626709</v>
       </c>
       <c r="G613" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="H613" t="s">
         <v>9</v>
@@ -22504,7 +22504,7 @@
         <v>7.01399993896484</v>
       </c>
       <c r="G614" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="H614" t="s">
         <v>9</v>
@@ -22530,7 +22530,7 @@
         <v>7.30800008773804</v>
       </c>
       <c r="G615" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="H615" t="s">
         <v>9</v>
@@ -22556,7 +22556,7 @@
         <v>7.32399988174438</v>
       </c>
       <c r="G616" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="H616" t="s">
         <v>9</v>
@@ -22582,7 +22582,7 @@
         <v>7.46999979019165</v>
       </c>
       <c r="G617" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="H617" t="s">
         <v>9</v>
@@ -22608,7 +22608,7 @@
         <v>7.51200008392334</v>
       </c>
       <c r="G618" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="H618" t="s">
         <v>9</v>
@@ -22634,7 +22634,7 @@
         <v>7.31400012969971</v>
       </c>
       <c r="G619" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="H619" t="s">
         <v>9</v>
@@ -22660,7 +22660,7 @@
         <v>7.30999994277954</v>
       </c>
       <c r="G620" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="H620" t="s">
         <v>9</v>
@@ -22686,7 +22686,7 @@
         <v>7.28200006484985</v>
       </c>
       <c r="G621" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="H621" t="s">
         <v>9</v>
@@ -22712,7 +22712,7 @@
         <v>7.08400011062622</v>
       </c>
       <c r="G622" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="H622" t="s">
         <v>9</v>
@@ -22738,7 +22738,7 @@
         <v>7.35799980163574</v>
       </c>
       <c r="G623" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="H623" t="s">
         <v>9</v>
@@ -22764,7 +22764,7 @@
         <v>7.4980001449585</v>
       </c>
       <c r="G624" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="H624" t="s">
         <v>9</v>
@@ -22790,7 +22790,7 @@
         <v>7.6399998664856</v>
       </c>
       <c r="G625" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="H625" t="s">
         <v>9</v>
@@ -22816,7 +22816,7 @@
         <v>7.82000017166138</v>
       </c>
       <c r="G626" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="H626" t="s">
         <v>9</v>
@@ -22842,7 +22842,7 @@
         <v>7.63000011444092</v>
       </c>
       <c r="G627" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="H627" t="s">
         <v>9</v>
@@ -22868,7 +22868,7 @@
         <v>7.32200002670288</v>
       </c>
       <c r="G628" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="H628" t="s">
         <v>9</v>
@@ -22894,7 +22894,7 @@
         <v>7.39599990844727</v>
       </c>
       <c r="G629" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="H629" t="s">
         <v>9</v>
@@ -22920,7 +22920,7 @@
         <v>7.42999982833862</v>
       </c>
       <c r="G630" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="H630" t="s">
         <v>9</v>
@@ -22946,7 +22946,7 @@
         <v>7.33799982070923</v>
       </c>
       <c r="G631" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="H631" t="s">
         <v>9</v>
@@ -22972,7 +22972,7 @@
         <v>7.34600019454956</v>
       </c>
       <c r="G632" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="H632" t="s">
         <v>9</v>
@@ -22998,7 +22998,7 @@
         <v>7.25</v>
       </c>
       <c r="G633" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="H633" t="s">
         <v>9</v>
@@ -23024,7 +23024,7 @@
         <v>7.28399991989136</v>
       </c>
       <c r="G634" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H634" t="s">
         <v>9</v>
@@ -23050,7 +23050,7 @@
         <v>7.25</v>
       </c>
       <c r="G635" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="H635" t="s">
         <v>9</v>
@@ -23076,7 +23076,7 @@
         <v>7.17999982833862</v>
       </c>
       <c r="G636" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="H636" t="s">
         <v>9</v>
@@ -23102,7 +23102,7 @@
         <v>7.17000007629395</v>
       </c>
       <c r="G637" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="H637" t="s">
         <v>9</v>
@@ -23128,7 +23128,7 @@
         <v>7.17999982833862</v>
       </c>
       <c r="G638" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="H638" t="s">
         <v>9</v>
@@ -23154,7 +23154,7 @@
         <v>7.24200010299683</v>
       </c>
       <c r="G639" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="H639" t="s">
         <v>9</v>
@@ -23180,7 +23180,7 @@
         <v>7.26000022888184</v>
       </c>
       <c r="G640" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="H640" t="s">
         <v>9</v>
@@ -23206,7 +23206,7 @@
         <v>7.39599990844727</v>
       </c>
       <c r="G641" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="H641" t="s">
         <v>9</v>
@@ -23232,7 +23232,7 @@
         <v>7.43200016021729</v>
       </c>
       <c r="G642" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="H642" t="s">
         <v>9</v>
@@ -23258,7 +23258,7 @@
         <v>7.48999977111816</v>
       </c>
       <c r="G643" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="H643" t="s">
         <v>9</v>
@@ -23284,7 +23284,7 @@
         <v>7.55999994277954</v>
       </c>
       <c r="G644" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="H644" t="s">
         <v>9</v>
@@ -23310,7 +23310,7 @@
         <v>7.48000001907349</v>
       </c>
       <c r="G645" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="H645" t="s">
         <v>9</v>
@@ -23336,7 +23336,7 @@
         <v>7.59000015258789</v>
       </c>
       <c r="G646" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="H646" t="s">
         <v>9</v>
@@ -23362,7 +23362,7 @@
         <v>7.57200002670288</v>
       </c>
       <c r="G647" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="H647" t="s">
         <v>9</v>
@@ -23388,7 +23388,7 @@
         <v>7.68200016021729</v>
       </c>
       <c r="G648" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="H648" t="s">
         <v>9</v>
@@ -23414,7 +23414,7 @@
         <v>7.76200008392334</v>
       </c>
       <c r="G649" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="H649" t="s">
         <v>9</v>
@@ -23440,7 +23440,7 @@
         <v>7.76200008392334</v>
       </c>
       <c r="G650" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="H650" t="s">
         <v>9</v>
@@ -23466,7 +23466,7 @@
         <v>7.80399990081787</v>
       </c>
       <c r="G651" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="H651" t="s">
         <v>9</v>
@@ -23492,7 +23492,7 @@
         <v>7.71400022506714</v>
       </c>
       <c r="G652" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="H652" t="s">
         <v>9</v>
@@ -23518,7 +23518,7 @@
         <v>7.73400020599365</v>
       </c>
       <c r="G653" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="H653" t="s">
         <v>9</v>
@@ -23544,7 +23544,7 @@
         <v>7.71000003814697</v>
       </c>
       <c r="G654" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="H654" t="s">
         <v>9</v>
@@ -23570,7 +23570,7 @@
         <v>7.72399997711182</v>
       </c>
       <c r="G655" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="H655" t="s">
         <v>9</v>
@@ -23596,7 +23596,7 @@
         <v>7.84999990463257</v>
       </c>
       <c r="G656" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="H656" t="s">
         <v>9</v>
@@ -23622,7 +23622,7 @@
         <v>7.88399982452393</v>
       </c>
       <c r="G657" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="H657" t="s">
         <v>9</v>
@@ -23648,7 +23648,7 @@
         <v>7.91800022125244</v>
       </c>
       <c r="G658" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="H658" t="s">
         <v>9</v>
@@ -23674,7 +23674,7 @@
         <v>7.96600008010864</v>
       </c>
       <c r="G659" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="H659" t="s">
         <v>9</v>
@@ -23700,7 +23700,7 @@
         <v>7.9539999961853</v>
       </c>
       <c r="G660" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="H660" t="s">
         <v>9</v>
@@ -23726,7 +23726,7 @@
         <v>7.52400016784668</v>
       </c>
       <c r="G661" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="H661" t="s">
         <v>9</v>
@@ -23752,7 +23752,7 @@
         <v>7.44799995422363</v>
       </c>
       <c r="G662" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="H662" t="s">
         <v>9</v>
@@ -23778,7 +23778,7 @@
         <v>7.39599990844727</v>
       </c>
       <c r="G663" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="H663" t="s">
         <v>9</v>
@@ -23804,7 +23804,7 @@
         <v>7.42399978637695</v>
       </c>
       <c r="G664" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="H664" t="s">
         <v>9</v>
@@ -23830,7 +23830,7 @@
         <v>7.33400011062622</v>
       </c>
       <c r="G665" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="H665" t="s">
         <v>9</v>
@@ -23856,7 +23856,7 @@
         <v>7.21000003814697</v>
       </c>
       <c r="G666" t="s">
-        <v>401</v>
+        <v>434</v>
       </c>
       <c r="H666" t="s">
         <v>9</v>
@@ -26872,7 +26872,7 @@
         <v>7.68200016021729</v>
       </c>
       <c r="G782" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="H782" t="s">
         <v>9</v>
@@ -71314,7 +71314,7 @@
     </row>
     <row r="2492">
       <c r="A2492" s="1" t="n">
-        <v>45947.6494560185</v>
+        <v>45947.2916666667</v>
       </c>
       <c r="B2492" t="n">
         <v>3301130</v>
@@ -71335,6 +71335,32 @@
         <v>2065</v>
       </c>
       <c r="H2492" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2493">
+      <c r="A2493" s="1" t="n">
+        <v>45950.6494097222</v>
+      </c>
+      <c r="B2493" t="n">
+        <v>1077240</v>
+      </c>
+      <c r="C2493" t="n">
+        <v>20.3099994659424</v>
+      </c>
+      <c r="D2493" t="n">
+        <v>20.0400009155273</v>
+      </c>
+      <c r="E2493" t="n">
+        <v>20.1200008392334</v>
+      </c>
+      <c r="F2493" t="n">
+        <v>20.1900005340576</v>
+      </c>
+      <c r="G2493" t="s">
+        <v>2025</v>
+      </c>
+      <c r="H2493" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/PST.MI.xlsx
+++ b/data/PST.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2066" uniqueCount="2066">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2067" uniqueCount="2067">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,52 +38,52 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">3.90457582473755</t>
+    <t xml:space="preserve">3.90457558631897</t>
   </si>
   <si>
     <t xml:space="preserve">PST.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">4.03631639480591</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.97465014457703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95222687721252</t>
+    <t xml:space="preserve">4.03631687164307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97465109825134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95222640037537</t>
   </si>
   <si>
     <t xml:space="preserve">3.9157874584198</t>
   </si>
   <si>
-    <t xml:space="preserve">3.87934875488281</t>
+    <t xml:space="preserve">3.87934827804565</t>
   </si>
   <si>
     <t xml:space="preserve">3.97184777259827</t>
   </si>
   <si>
-    <t xml:space="preserve">4.01949787139893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99707460403442</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94661974906921</t>
+    <t xml:space="preserve">4.01949739456177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99707412719727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94661998748779</t>
   </si>
   <si>
     <t xml:space="preserve">3.82889437675476</t>
   </si>
   <si>
-    <t xml:space="preserve">3.75601577758789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.54859471321106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.68594169616699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73359251022339</t>
+    <t xml:space="preserve">3.75601720809937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.54859495162964</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.68594193458557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73359203338623</t>
   </si>
   <si>
     <t xml:space="preserve">3.65510869026184</t>
@@ -92,34 +92,34 @@
     <t xml:space="preserve">3.76162266731262</t>
   </si>
   <si>
-    <t xml:space="preserve">3.80927348136902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73078942298889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.82609128952026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.72238039970398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64389705657959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.53177666664124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.3551881313324</t>
+    <t xml:space="preserve">3.8092737197876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73078966140747</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.82609176635742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.7223801612854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64389729499817</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.53177714347839</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.35518789291382</t>
   </si>
   <si>
     <t xml:space="preserve">3.0048131942749</t>
   </si>
   <si>
-    <t xml:space="preserve">2.89829969406128</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.17018961906433</t>
+    <t xml:space="preserve">2.89829921722412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.17019009590149</t>
   </si>
   <si>
     <t xml:space="preserve">3.03284287452698</t>
@@ -128,97 +128,97 @@
     <t xml:space="preserve">3.04405474662781</t>
   </si>
   <si>
-    <t xml:space="preserve">3.13655376434326</t>
+    <t xml:space="preserve">3.13655424118042</t>
   </si>
   <si>
     <t xml:space="preserve">3.12253952026367</t>
   </si>
   <si>
-    <t xml:space="preserve">3.24867391586304</t>
+    <t xml:space="preserve">3.24867367744446</t>
   </si>
   <si>
     <t xml:space="preserve">3.23465943336487</t>
   </si>
   <si>
-    <t xml:space="preserve">3.30473375320435</t>
+    <t xml:space="preserve">3.30473399162292</t>
   </si>
   <si>
     <t xml:space="preserve">3.42245984077454</t>
   </si>
   <si>
-    <t xml:space="preserve">3.34677934646606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.31314325332642</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.40844535827637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.45609617233276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.51495862007141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.48412609100342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.45329236984253</t>
+    <t xml:space="preserve">3.34677863121033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.3131422996521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.40844511985779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.45609521865845</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.51495933532715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.48412561416626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.45329284667969</t>
   </si>
   <si>
     <t xml:space="preserve">3.47571682929993</t>
   </si>
   <si>
-    <t xml:space="preserve">3.43647480010986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.45889925956726</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.43367171287537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61306357383728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.63829040527344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.63548827171326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.60745787620544</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.58783721923828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.60185194015503</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.67192649841309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.79525828361511</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77844047546387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.7139720916748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.78404712677002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.72798657417297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.67753291130066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61586666107178</t>
+    <t xml:space="preserve">3.43647527694702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.45889830589294</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.43367266654968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61306381225586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.63829112052917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.6354877948761</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.60745811462402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.58783674240112</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.60185170173645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.67192697525024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.79525899887085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77844095230103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71397113800049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.7840461730957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.72798752784729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.67753314971924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61586594581604</t>
   </si>
   <si>
     <t xml:space="preserve">3.51215577125549</t>
@@ -227,58 +227,58 @@
     <t xml:space="preserve">3.56821537017822</t>
   </si>
   <si>
-    <t xml:space="preserve">3.58503413200378</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.60465431213379</t>
+    <t xml:space="preserve">3.58503365516663</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.60465478897095</t>
   </si>
   <si>
     <t xml:space="preserve">3.62147307395935</t>
   </si>
   <si>
-    <t xml:space="preserve">3.69995665550232</t>
+    <t xml:space="preserve">3.69995641708374</t>
   </si>
   <si>
     <t xml:space="preserve">3.6326847076416</t>
   </si>
   <si>
-    <t xml:space="preserve">3.6298816204071</t>
+    <t xml:space="preserve">3.62988185882568</t>
   </si>
   <si>
     <t xml:space="preserve">3.65791153907776</t>
   </si>
   <si>
-    <t xml:space="preserve">3.62707853317261</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.67472958564758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.68033599853516</t>
+    <t xml:space="preserve">3.62707805633545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.67473006248474</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.68033576011658</t>
   </si>
   <si>
     <t xml:space="preserve">3.74480438232422</t>
   </si>
   <si>
-    <t xml:space="preserve">3.79245519638062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80086421966553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73919796943665</t>
+    <t xml:space="preserve">3.79245543479919</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.80086493492126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73919820785522</t>
   </si>
   <si>
     <t xml:space="preserve">3.68313837051392</t>
   </si>
   <si>
-    <t xml:space="preserve">3.76722812652588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.79806184768677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77563762664795</t>
+    <t xml:space="preserve">3.7672290802002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.79806137084961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77563834190369</t>
   </si>
   <si>
     <t xml:space="preserve">3.75881958007812</t>
@@ -287,34 +287,34 @@
     <t xml:space="preserve">3.78684997558594</t>
   </si>
   <si>
-    <t xml:space="preserve">3.68874478340149</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.78965258598328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.74760699272156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83169794082642</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83730363845825</t>
+    <t xml:space="preserve">3.68874454498291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.78965306282043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.74760675430298</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.831698179245</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.83730316162109</t>
   </si>
   <si>
     <t xml:space="preserve">3.80647087097168</t>
   </si>
   <si>
-    <t xml:space="preserve">3.85972762107849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85692453384399</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8681366443634</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84571313858032</t>
+    <t xml:space="preserve">3.85972785949707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85692501068115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.86813688278198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84571170806885</t>
   </si>
   <si>
     <t xml:space="preserve">3.8541214466095</t>
@@ -323,49 +323,49 @@
     <t xml:space="preserve">3.92419672012329</t>
   </si>
   <si>
-    <t xml:space="preserve">3.93260598182678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84010648727417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.78124356269836</t>
+    <t xml:space="preserve">3.9326057434082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84010624885559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.78124332427979</t>
   </si>
   <si>
     <t xml:space="preserve">3.76442551612854</t>
   </si>
   <si>
-    <t xml:space="preserve">3.87654519081116</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96498346328735</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.91486811637878</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90602540969849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95024347305298</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.63776230812073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.42256212234497</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.5139479637146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.50805234909058</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.60533452033997</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.52574062347412</t>
+    <t xml:space="preserve">3.87654495239258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96498322486877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.91486835479736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90602445602417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95024418830872</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.63776111602783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.42256236076355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.51394891738892</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.50805258750916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.60533428192139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.52573990821838</t>
   </si>
   <si>
     <t xml:space="preserve">3.43730187416077</t>
@@ -377,94 +377,94 @@
     <t xml:space="preserve">3.37244701385498</t>
   </si>
   <si>
-    <t xml:space="preserve">3.49920868873596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.65839767456055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64955449104309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73504447937012</t>
+    <t xml:space="preserve">3.49920773506165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.65839791297913</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64955377578735</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.7350447177887</t>
   </si>
   <si>
     <t xml:space="preserve">3.67018914222717</t>
   </si>
   <si>
-    <t xml:space="preserve">3.67313742637634</t>
+    <t xml:space="preserve">3.67313694953918</t>
   </si>
   <si>
     <t xml:space="preserve">3.65250182151794</t>
   </si>
   <si>
-    <t xml:space="preserve">3.70851230621338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.69672083854675</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.65544939041138</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64660549163818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.60238671302795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.58469891548157</t>
+    <t xml:space="preserve">3.70851254463196</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.69672131538391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.65544962882996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64660596847534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.60238647460938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.58469915390015</t>
   </si>
   <si>
     <t xml:space="preserve">3.52868819236755</t>
   </si>
   <si>
-    <t xml:space="preserve">3.80284762382507</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.78221154212952</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80874300003052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.81463861465454</t>
+    <t xml:space="preserve">3.8028461933136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.78221225738525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8087432384491</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.81463813781738</t>
   </si>
   <si>
     <t xml:space="preserve">3.86770224571228</t>
   </si>
   <si>
-    <t xml:space="preserve">3.87949419021606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.79989838600159</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.72325134277344</t>
+    <t xml:space="preserve">3.87949371337891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.79989886283875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.72325253486633</t>
   </si>
   <si>
     <t xml:space="preserve">3.76157522201538</t>
   </si>
   <si>
-    <t xml:space="preserve">3.66724133491516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.68198156356812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.74388742446899</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.70261669158936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.6613450050354</t>
+    <t xml:space="preserve">3.66724061965942</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.68198108673096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.74388837814331</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.70261740684509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.6613461971283</t>
   </si>
   <si>
     <t xml:space="preserve">3.67903280258179</t>
   </si>
   <si>
-    <t xml:space="preserve">3.62597036361694</t>
+    <t xml:space="preserve">3.62597012519836</t>
   </si>
   <si>
     <t xml:space="preserve">3.69377303123474</t>
@@ -473,373 +473,373 @@
     <t xml:space="preserve">3.68492889404297</t>
   </si>
   <si>
-    <t xml:space="preserve">3.70556497573853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71735644340515</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77631521224976</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.76452350616455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.56406354904175</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61712741851807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61417865753174</t>
+    <t xml:space="preserve">3.70556473731995</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71735620498657</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.7763147354126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.76452398300171</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.56406402587891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61712646484375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61417889595032</t>
   </si>
   <si>
     <t xml:space="preserve">3.58175110816956</t>
   </si>
   <si>
-    <t xml:space="preserve">3.59943842887878</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.60828256607056</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.58764672279358</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.57880306243896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.57290720939636</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.5581681728363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.56111550331116</t>
+    <t xml:space="preserve">3.59943866729736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.60828280448914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.58764719963074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.57880282402039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.57290768623352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.55816721916199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.56111598014832</t>
   </si>
   <si>
     <t xml:space="preserve">3.50215697288513</t>
   </si>
   <si>
-    <t xml:space="preserve">3.54637551307678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.56701183319092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.51689720153809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.57585525512695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64365792274475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.62302184104919</t>
+    <t xml:space="preserve">3.54637598991394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.56701135635376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.51689648628235</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.57585549354553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64365816116333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.62302231788635</t>
   </si>
   <si>
     <t xml:space="preserve">3.51100039482117</t>
   </si>
   <si>
-    <t xml:space="preserve">3.49036502838135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.51984453201294</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.55227208137512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.54342842102051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.53163552284241</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.52279138565063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.47857284545898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.44025039672852</t>
+    <t xml:space="preserve">3.49036478996277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.51984405517578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.55227136611938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.54342794418335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.53163599967957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.52279233932495</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.47857356071472</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.4402494430542</t>
   </si>
   <si>
     <t xml:space="preserve">3.3665509223938</t>
   </si>
   <si>
-    <t xml:space="preserve">3.33117604255676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.32527947425842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.31938433647156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.31053996086121</t>
+    <t xml:space="preserve">3.3311755657196</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.32528042793274</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.31938409805298</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.31053972244263</t>
   </si>
   <si>
     <t xml:space="preserve">3.26632118225098</t>
   </si>
   <si>
-    <t xml:space="preserve">3.39603066444397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.45793771743774</t>
+    <t xml:space="preserve">3.39603042602539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.45793700218201</t>
   </si>
   <si>
     <t xml:space="preserve">3.46088552474976</t>
   </si>
   <si>
-    <t xml:space="preserve">3.45204162597656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73209619522095</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.74683594703674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73799180984497</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.7291476726532</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77926301956177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.74093914031982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77336764335632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.79105520248413</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.76747155189514</t>
+    <t xml:space="preserve">3.45204138755798</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73209643363953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.74683666229248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73799252510071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.72914886474609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77926254272461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.74094033241272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77336740493774</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.79105544090271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.76747131347656</t>
   </si>
   <si>
     <t xml:space="preserve">3.71440887451172</t>
   </si>
   <si>
-    <t xml:space="preserve">3.63481450080872</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.59649109840393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.56995892524719</t>
+    <t xml:space="preserve">3.63481330871582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.59649062156677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.56995868682861</t>
   </si>
   <si>
     <t xml:space="preserve">3.59354281425476</t>
   </si>
   <si>
-    <t xml:space="preserve">3.44909405708313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.42845845222473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.44614505767822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.53753209114075</t>
+    <t xml:space="preserve">3.44909358024597</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.42845869064331</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.44614577293396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.53753185272217</t>
   </si>
   <si>
     <t xml:space="preserve">3.53458404541016</t>
   </si>
   <si>
-    <t xml:space="preserve">3.59059453010559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.69966888427734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.81758642196655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80579495429993</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.79695153236389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.75862741470337</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8293788433075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.79400300979614</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.67608547210693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71146082878113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.74978375434875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77041983604431</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.68787670135498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.7527322769165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83232593536377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84411835670471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.72030472755432</t>
+    <t xml:space="preserve">3.59059500694275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.69966912269592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.81758689880371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.80579447746277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.79695057868958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.75862693786621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.82937860488892</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.79400324821472</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.67608523368835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71146059036255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.74978446960449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77041959762573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.68787693977356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.75273156166077</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.83232688903809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84411811828613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.72030401229858</t>
   </si>
   <si>
     <t xml:space="preserve">3.69082570075989</t>
   </si>
   <si>
-    <t xml:space="preserve">3.81169080734253</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.82053446769714</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.78916716575623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8017144203186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.81426095962524</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.75779914855957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.76407384872437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77662038803101</t>
+    <t xml:space="preserve">3.81169104576111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.82053470611572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.7891674041748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.80171465873718</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.81426072120667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.75779986381531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.76407313346863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77662110328674</t>
   </si>
   <si>
     <t xml:space="preserve">3.73897981643677</t>
   </si>
   <si>
-    <t xml:space="preserve">3.7860312461853</t>
+    <t xml:space="preserve">3.78603029251099</t>
   </si>
   <si>
     <t xml:space="preserve">3.76093697547913</t>
   </si>
   <si>
-    <t xml:space="preserve">3.76721119880676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.74525332450867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.72956967353821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.79544115066528</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80485129356384</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84249138832092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8236711025238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8079879283905</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.79857683181763</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.75152707099915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.74211692810059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77975749969482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.91463613510132</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92718410491943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94600343704224</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.89267921447754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9020893573761</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90522599220276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94286727905273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83308172225952</t>
+    <t xml:space="preserve">3.76720929145813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.74525284767151</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.72956895828247</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.79544043540955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.80485081672668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8424916267395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.82367157936096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.80798864364624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.79857730865479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.75152587890625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.74211621284485</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77975702285767</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.91463589668274</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9271833896637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94600391387939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89267945289612</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90208864212036</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90522646903992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94286751747131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.83308100700378</t>
   </si>
   <si>
     <t xml:space="preserve">3.84562873840332</t>
   </si>
   <si>
-    <t xml:space="preserve">3.89895296096802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.908362865448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85817551612854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83935475349426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8299446105957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85503840446472</t>
+    <t xml:space="preserve">3.89895272254944</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90836310386658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85817575454712</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.83935523033142</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.82994508743286</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85503888130188</t>
   </si>
   <si>
     <t xml:space="preserve">3.81739711761475</t>
   </si>
   <si>
-    <t xml:space="preserve">3.86131238937378</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92090964317322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8958158493042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88640570640564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88954281806946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.86444759368896</t>
+    <t xml:space="preserve">3.8613121509552</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92091012001038</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89581727981567</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8864061832428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88954210281372</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.86444854736328</t>
   </si>
   <si>
     <t xml:space="preserve">3.88013219833374</t>
@@ -848,79 +848,79 @@
     <t xml:space="preserve">3.85190153121948</t>
   </si>
   <si>
-    <t xml:space="preserve">3.873859167099</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93031978607178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8675856590271</t>
+    <t xml:space="preserve">3.87385940551758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93032050132751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.86758518218994</t>
   </si>
   <si>
     <t xml:space="preserve">3.93659377098083</t>
   </si>
   <si>
-    <t xml:space="preserve">3.94914078712463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93345665931702</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93972992897034</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92404627799988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8487663269043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83621788024902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.82680821418762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99305486679077</t>
+    <t xml:space="preserve">3.94914031028748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93345737457275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93973064422607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92404651641846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8487651348114</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.83621740341187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.82680773735046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99305391311646</t>
   </si>
   <si>
     <t xml:space="preserve">4.02128458023071</t>
   </si>
   <si>
-    <t xml:space="preserve">3.99619102478027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98364424705505</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.97109723091125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98678135871887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99932789802551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.01814794540405</t>
+    <t xml:space="preserve">3.99619078636169</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.98364400863647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97109746932983</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.98678183555603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99932861328125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.01814842224121</t>
   </si>
   <si>
     <t xml:space="preserve">4.03383207321167</t>
   </si>
   <si>
-    <t xml:space="preserve">4.04637956619263</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.05892562866211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.04010629653931</t>
+    <t xml:space="preserve">4.04637813568115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.05892515182495</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.04010534286499</t>
   </si>
   <si>
     <t xml:space="preserve">4.07147264480591</t>
   </si>
   <si>
-    <t xml:space="preserve">4.10283994674683</t>
+    <t xml:space="preserve">4.10284042358398</t>
   </si>
   <si>
     <t xml:space="preserve">4.09970331192017</t>
@@ -929,34 +929,34 @@
     <t xml:space="preserve">4.12793445587158</t>
   </si>
   <si>
-    <t xml:space="preserve">4.21889877319336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.21576261520386</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.2000789642334</t>
+    <t xml:space="preserve">4.21889972686768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.21576166152954</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.20007848739624</t>
   </si>
   <si>
     <t xml:space="preserve">4.17184829711914</t>
   </si>
   <si>
-    <t xml:space="preserve">4.18753242492676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.19694232940674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.17310237884521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.15553665161133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.18063068389893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.13044309616089</t>
+    <t xml:space="preserve">4.1875319480896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.19694185256958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.17310285568237</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.15553712844849</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.18063116073608</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.13044357299805</t>
   </si>
   <si>
     <t xml:space="preserve">4.13922595977783</t>
@@ -965,7 +965,7 @@
     <t xml:space="preserve">4.01501226425171</t>
   </si>
   <si>
-    <t xml:space="preserve">4.1216607093811</t>
+    <t xml:space="preserve">4.12166023254395</t>
   </si>
   <si>
     <t xml:space="preserve">4.043869972229</t>
@@ -974,148 +974,148 @@
     <t xml:space="preserve">4.03759574890137</t>
   </si>
   <si>
-    <t xml:space="preserve">4.05516195297241</t>
+    <t xml:space="preserve">4.0551609992981</t>
   </si>
   <si>
     <t xml:space="preserve">4.09531164169312</t>
   </si>
   <si>
-    <t xml:space="preserve">4.1291880607605</t>
+    <t xml:space="preserve">4.12918901443481</t>
   </si>
   <si>
     <t xml:space="preserve">4.17561197280884</t>
   </si>
   <si>
-    <t xml:space="preserve">4.18188571929932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.2534031867981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.2408561706543</t>
+    <t xml:space="preserve">4.18188667297363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.25340270996094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.24085664749146</t>
   </si>
   <si>
     <t xml:space="preserve">4.20697927474976</t>
   </si>
   <si>
-    <t xml:space="preserve">4.21074390411377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.17435693740845</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.41651296615601</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.43031454086304</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.40271186828613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.30735492706299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.33495807647705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.37134408950806</t>
+    <t xml:space="preserve">4.21074342727661</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.17435741424561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.41651344299316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.43031406402588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.40271043777466</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.30735445022583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.33495759963989</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.3713436126709</t>
   </si>
   <si>
     <t xml:space="preserve">4.48677539825439</t>
   </si>
   <si>
-    <t xml:space="preserve">4.60095262527466</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.57711410522461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.65490484237671</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.55452871322632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.49555826187134</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.56707620620728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.63859367370605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.60346078872681</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.63482856750488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.6260461807251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.58338737487793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.54574584960938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.52943515777588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.54449081420898</t>
+    <t xml:space="preserve">4.6009521484375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.57711362838745</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.65490388870239</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.55452966690063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.49555778503418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.56707572937012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.63859272003174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.60346174240112</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.63482904434204</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.62604665756226</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.58338642120361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.54574537277222</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.52943563461304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.5444917678833</t>
   </si>
   <si>
     <t xml:space="preserve">4.61475419998169</t>
   </si>
   <si>
-    <t xml:space="preserve">4.62353706359863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.65866899490356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.73645973205566</t>
+    <t xml:space="preserve">4.62353658676147</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.65866851806641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.73645925521851</t>
   </si>
   <si>
     <t xml:space="preserve">4.73144006729126</t>
   </si>
   <si>
-    <t xml:space="preserve">4.76782655715942</t>
+    <t xml:space="preserve">4.76782608032227</t>
   </si>
   <si>
     <t xml:space="preserve">4.82052326202393</t>
   </si>
   <si>
-    <t xml:space="preserve">4.81299543380737</t>
+    <t xml:space="preserve">4.81299495697021</t>
   </si>
   <si>
     <t xml:space="preserve">4.81675958633423</t>
   </si>
   <si>
-    <t xml:space="preserve">4.81424999237061</t>
+    <t xml:space="preserve">4.81425046920776</t>
   </si>
   <si>
     <t xml:space="preserve">4.8431077003479</t>
   </si>
   <si>
-    <t xml:space="preserve">4.88702201843262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.85690975189209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.86694717407227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.93720960617065</t>
+    <t xml:space="preserve">4.88702154159546</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.85690927505493</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.86694765090942</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.93721008300781</t>
   </si>
   <si>
     <t xml:space="preserve">4.94222831726074</t>
   </si>
   <si>
-    <t xml:space="preserve">4.96355772018433</t>
+    <t xml:space="preserve">4.96355819702148</t>
   </si>
   <si>
     <t xml:space="preserve">4.97359561920166</t>
@@ -1124,7 +1124,7 @@
     <t xml:space="preserve">5.00119924545288</t>
   </si>
   <si>
-    <t xml:space="preserve">5.08526372909546</t>
+    <t xml:space="preserve">5.08526277542114</t>
   </si>
   <si>
     <t xml:space="preserve">5.07146120071411</t>
@@ -1133,7 +1133,7 @@
     <t xml:space="preserve">5.06267881393433</t>
   </si>
   <si>
-    <t xml:space="preserve">5.11537551879883</t>
+    <t xml:space="preserve">5.11537599563599</t>
   </si>
   <si>
     <t xml:space="preserve">5.09153699874878</t>
@@ -1142,37 +1142,37 @@
     <t xml:space="preserve">5.06769752502441</t>
   </si>
   <si>
-    <t xml:space="preserve">5.11286592483521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.15552616119385</t>
+    <t xml:space="preserve">5.11286640167236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.15552663803101</t>
   </si>
   <si>
     <t xml:space="preserve">4.96230316162109</t>
   </si>
   <si>
-    <t xml:space="preserve">4.95101022720337</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.78037261962891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.79041147232056</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.82930612564087</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.80546617507935</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.83432483673096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.76029825210571</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.60722541809082</t>
+    <t xml:space="preserve">4.95101165771484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.78037309646606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.7904109954834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.82930707931519</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.80546712875366</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.8343243598938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.76029872894287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.60722589492798</t>
   </si>
   <si>
     <t xml:space="preserve">4.40020179748535</t>
@@ -1181,127 +1181,127 @@
     <t xml:space="preserve">4.584641456604</t>
   </si>
   <si>
-    <t xml:space="preserve">4.59467887878418</t>
+    <t xml:space="preserve">4.5946798324585</t>
   </si>
   <si>
     <t xml:space="preserve">4.68627166748047</t>
   </si>
   <si>
-    <t xml:space="preserve">4.7126202583313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.58840560913086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.58589649200439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.56832981109619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.44411611557007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.61600828170776</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.70383739471436</t>
+    <t xml:space="preserve">4.71262073516846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.58840608596802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.58589506149292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.56833028793335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.44411659240723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.61600875854492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.7038369178772</t>
   </si>
   <si>
     <t xml:space="preserve">4.79292011260986</t>
   </si>
   <si>
-    <t xml:space="preserve">4.90584230422974</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.78664636611938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.86100244522095</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.9101300239563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.93270206451416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.87162351608276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.8769359588623</t>
+    <t xml:space="preserve">4.90584325790405</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.7866473197937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.86100339889526</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.91012954711914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.93270301818848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.87162494659424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.87693500518799</t>
   </si>
   <si>
     <t xml:space="preserve">4.81320238113403</t>
   </si>
   <si>
-    <t xml:space="preserve">4.83577489852905</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.76673078536987</t>
+    <t xml:space="preserve">4.83577394485474</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.7667293548584</t>
   </si>
   <si>
     <t xml:space="preserve">4.76009130477905</t>
   </si>
   <si>
-    <t xml:space="preserve">4.80789089202881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.81984090805054</t>
+    <t xml:space="preserve">4.80789136886597</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.8198413848877</t>
   </si>
   <si>
     <t xml:space="preserve">4.93403053283691</t>
   </si>
   <si>
-    <t xml:space="preserve">4.97253513336182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.01900815963745</t>
+    <t xml:space="preserve">4.97253608703613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.01900768280029</t>
   </si>
   <si>
     <t xml:space="preserve">4.96589708328247</t>
   </si>
   <si>
-    <t xml:space="preserve">5.03892517089844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.02697467803955</t>
+    <t xml:space="preserve">5.03892612457275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.02697420120239</t>
   </si>
   <si>
     <t xml:space="preserve">5.10000276565552</t>
   </si>
   <si>
-    <t xml:space="preserve">5.15311288833618</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.18099737167358</t>
+    <t xml:space="preserve">5.15311431884766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.18099784851074</t>
   </si>
   <si>
     <t xml:space="preserve">5.12124729156494</t>
   </si>
   <si>
-    <t xml:space="preserve">5.13452529907227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.11859083175659</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.1278862953186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.21153688430786</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.23410892486572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.25668001174927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.2885479927063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.28058004379272</t>
+    <t xml:space="preserve">5.13452577590942</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.11859178543091</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.12788581848145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.21153593063354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.23410844802856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.25668096542358</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.28854751586914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.28058099746704</t>
   </si>
   <si>
     <t xml:space="preserve">4.99510812759399</t>
@@ -1310,7 +1310,7 @@
     <t xml:space="preserve">4.94465208053589</t>
   </si>
   <si>
-    <t xml:space="preserve">4.92871904373169</t>
+    <t xml:space="preserve">4.92871809005737</t>
   </si>
   <si>
     <t xml:space="preserve">4.86896896362305</t>
@@ -1319,25 +1319,25 @@
     <t xml:space="preserve">4.78664684295654</t>
   </si>
   <si>
-    <t xml:space="preserve">4.71627426147461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.69635772705078</t>
+    <t xml:space="preserve">4.71627521514893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.69635725021362</t>
   </si>
   <si>
     <t xml:space="preserve">4.74548625946045</t>
   </si>
   <si>
-    <t xml:space="preserve">4.60474109649658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.54764604568481</t>
+    <t xml:space="preserve">4.60474061965942</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.54764556884766</t>
   </si>
   <si>
     <t xml:space="preserve">4.47594547271729</t>
   </si>
   <si>
-    <t xml:space="preserve">4.61801815032959</t>
+    <t xml:space="preserve">4.61801862716675</t>
   </si>
   <si>
     <t xml:space="preserve">4.52772998809814</t>
@@ -1349,100 +1349,100 @@
     <t xml:space="preserve">4.50250196456909</t>
   </si>
   <si>
-    <t xml:space="preserve">4.48524045944214</t>
+    <t xml:space="preserve">4.4852409362793</t>
   </si>
   <si>
     <t xml:space="preserve">4.50515651702881</t>
   </si>
   <si>
-    <t xml:space="preserve">4.44673442840576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.40291833877563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.47727346420288</t>
+    <t xml:space="preserve">4.44673490524292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.40291738510132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.47727298736572</t>
   </si>
   <si>
     <t xml:space="preserve">4.59544658660889</t>
   </si>
   <si>
-    <t xml:space="preserve">4.68440818786621</t>
+    <t xml:space="preserve">4.68440771102905</t>
   </si>
   <si>
     <t xml:space="preserve">4.65519666671753</t>
   </si>
   <si>
-    <t xml:space="preserve">4.67378520965576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.78133535385132</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.75610828399658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.68175172805786</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.56225156784058</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.58880662918091</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.63262462615967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.61005115509033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.59810209274292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.66050672531128</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.69901275634766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.72158479690552</t>
+    <t xml:space="preserve">4.67378568649292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.78133487701416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.75610780715942</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.68175220489502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.56225204467773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.58880710601807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.63262414932251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.61005163192749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.59810256958008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.66050720214844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.69901323318481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.72158575057983</t>
   </si>
   <si>
     <t xml:space="preserve">4.77735185623169</t>
   </si>
   <si>
-    <t xml:space="preserve">4.80523586273193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.77336883544922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.56889009475708</t>
+    <t xml:space="preserve">4.80523538589478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.77336978912354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.56889057159424</t>
   </si>
   <si>
     <t xml:space="preserve">4.51976251602173</t>
   </si>
   <si>
-    <t xml:space="preserve">4.43876886367798</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.4480619430542</t>
+    <t xml:space="preserve">4.43876791000366</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.44806289672852</t>
   </si>
   <si>
     <t xml:space="preserve">4.45204591751099</t>
   </si>
   <si>
-    <t xml:space="preserve">4.38167381286621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.21968460083008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.24225664138794</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.28474521636963</t>
+    <t xml:space="preserve">4.38167333602905</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.21968412399292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.2422571182251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.28474617004395</t>
   </si>
   <si>
     <t xml:space="preserve">4.16657304763794</t>
@@ -1451,37 +1451,37 @@
     <t xml:space="preserve">4.14798450469971</t>
   </si>
   <si>
-    <t xml:space="preserve">4.16391754150391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.23296213150024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.17985057830811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.06300640106201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.16259002685547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.14001750946045</t>
+    <t xml:space="preserve">4.16391801834106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.2329626083374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.17985105514526</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.06300687789917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.16259050369263</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.14001846313477</t>
   </si>
   <si>
     <t xml:space="preserve">4.14931201934814</t>
   </si>
   <si>
-    <t xml:space="preserve">3.98201179504395</t>
+    <t xml:space="preserve">3.98201251029968</t>
   </si>
   <si>
     <t xml:space="preserve">4.06831789016724</t>
   </si>
   <si>
-    <t xml:space="preserve">4.07229995727539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.20109558105469</t>
+    <t xml:space="preserve">4.07230043411255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.20109605789185</t>
   </si>
   <si>
     <t xml:space="preserve">4.10815143585205</t>
@@ -1490,34 +1490,34 @@
     <t xml:space="preserve">4.21570110321045</t>
   </si>
   <si>
-    <t xml:space="preserve">4.3498067855835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.38432931900024</t>
+    <t xml:space="preserve">4.34980726242065</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.3843297958374</t>
   </si>
   <si>
     <t xml:space="preserve">4.32325124740601</t>
   </si>
   <si>
-    <t xml:space="preserve">4.29536771774292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.43744087219238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.53038501739502</t>
+    <t xml:space="preserve">4.29536724090576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.43744039535522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.53038454055786</t>
   </si>
   <si>
     <t xml:space="preserve">4.56092309951782</t>
   </si>
   <si>
-    <t xml:space="preserve">4.57021903991699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.57287454605103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.42681837081909</t>
+    <t xml:space="preserve">4.57021856307983</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.57287359237671</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.42681884765625</t>
   </si>
   <si>
     <t xml:space="preserve">4.31528472900391</t>
@@ -1526,97 +1526,97 @@
     <t xml:space="preserve">4.32590675354004</t>
   </si>
   <si>
-    <t xml:space="preserve">4.35113525390625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.23163414001465</t>
+    <t xml:space="preserve">4.35113430023193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.23163509368896</t>
   </si>
   <si>
     <t xml:space="preserve">4.37105131149292</t>
   </si>
   <si>
-    <t xml:space="preserve">4.3484787940979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.54100799560547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.5171070098877</t>
+    <t xml:space="preserve">4.34847927093506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.54100751876831</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.51710748672485</t>
   </si>
   <si>
     <t xml:space="preserve">4.44939041137695</t>
   </si>
   <si>
-    <t xml:space="preserve">4.45071792602539</t>
+    <t xml:space="preserve">4.45071840286255</t>
   </si>
   <si>
     <t xml:space="preserve">4.55826854705811</t>
   </si>
   <si>
-    <t xml:space="preserve">4.52241849899292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.58216905593872</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.3405122756958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.36175727844238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.31130123138428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.35379028320312</t>
+    <t xml:space="preserve">4.52241897583008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.58216857910156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.34051322937012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.36175680160522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.31130170822144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.35379123687744</t>
   </si>
   <si>
     <t xml:space="preserve">4.52905702590942</t>
   </si>
   <si>
-    <t xml:space="preserve">4.60075759887695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.57818460464478</t>
+    <t xml:space="preserve">4.60075664520264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.57818555831909</t>
   </si>
   <si>
     <t xml:space="preserve">4.57154655456543</t>
   </si>
   <si>
-    <t xml:space="preserve">4.71892976760864</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.65386867523193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.58615159988403</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.53569650650024</t>
+    <t xml:space="preserve">4.71892929077148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.65386915206909</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.58615112304688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.5356969833374</t>
   </si>
   <si>
     <t xml:space="preserve">4.63660764694214</t>
   </si>
   <si>
-    <t xml:space="preserve">4.62731266021729</t>
+    <t xml:space="preserve">4.62731313705444</t>
   </si>
   <si>
     <t xml:space="preserve">4.64590263366699</t>
   </si>
   <si>
-    <t xml:space="preserve">4.70299673080444</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.67112874984741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.71760177612305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.78000783920288</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.79195737838745</t>
+    <t xml:space="preserve">4.7029972076416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.67112970352173</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.71760320663452</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.78000736236572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.79195880889893</t>
   </si>
   <si>
     <t xml:space="preserve">4.81452989578247</t>
@@ -1625,7 +1625,7 @@
     <t xml:space="preserve">4.79328584671021</t>
   </si>
   <si>
-    <t xml:space="preserve">4.88224697113037</t>
+    <t xml:space="preserve">4.88224649429321</t>
   </si>
   <si>
     <t xml:space="preserve">4.91278600692749</t>
@@ -1640,7 +1640,7 @@
     <t xml:space="preserve">4.99776363372803</t>
   </si>
   <si>
-    <t xml:space="preserve">5.04423666000366</t>
+    <t xml:space="preserve">5.04423570632935</t>
   </si>
   <si>
     <t xml:space="preserve">5.05618619918823</t>
@@ -1649,49 +1649,49 @@
     <t xml:space="preserve">5.10664129257202</t>
   </si>
   <si>
-    <t xml:space="preserve">5.084068775177</t>
+    <t xml:space="preserve">5.08406972885132</t>
   </si>
   <si>
     <t xml:space="preserve">5.09203624725342</t>
   </si>
   <si>
-    <t xml:space="preserve">4.98846960067749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.8782639503479</t>
+    <t xml:space="preserve">4.98846864700317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.87826299667358</t>
   </si>
   <si>
     <t xml:space="preserve">4.99245262145996</t>
   </si>
   <si>
-    <t xml:space="preserve">5.07477474212646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.10265827178955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.94863605499268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.96456909179688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.02431964874268</t>
+    <t xml:space="preserve">5.07477426528931</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.10265779495239</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.9486346244812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.96456861495972</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.02431917190552</t>
   </si>
   <si>
     <t xml:space="preserve">5.09867477416992</t>
   </si>
   <si>
-    <t xml:space="preserve">5.15045833587646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.08937978744507</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.14249086380005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.1610803604126</t>
+    <t xml:space="preserve">5.15045928955078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.08938026428223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.14249038696289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.16108131408691</t>
   </si>
   <si>
     <t xml:space="preserve">5.14514636993408</t>
@@ -1700,43 +1700,43 @@
     <t xml:space="preserve">5.13054180145264</t>
   </si>
   <si>
-    <t xml:space="preserve">5.16639184951782</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.18763589859009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.2434024810791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.24473142623901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.2646484375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.26863145828247</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.23941850662231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.26331949234009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.27394151687622</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.27659749984741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.18630838394165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.24605798721313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.27128648757935</t>
+    <t xml:space="preserve">5.16639137268066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.18763637542725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.24340295791626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.24473094940186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.26464748382568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.268630027771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.23941993713379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.26331996917725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.27394104003906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.27659797668457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.18630886077881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.24605894088745</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.27128601074219</t>
   </si>
   <si>
     <t xml:space="preserve">5.28456401824951</t>
@@ -1754,112 +1754,112 @@
     <t xml:space="preserve">5.55011987686157</t>
   </si>
   <si>
-    <t xml:space="preserve">5.60323095321655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.73468017578125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.68289804458618</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.70281457901001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.72538661956787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.72671604156494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.7067985534668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.75725412368774</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.74264860153198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.75991010665894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.8063817024231</t>
+    <t xml:space="preserve">5.60323047637939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.73468208312988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.6828989982605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.70281505584717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.72538614273071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.72671413421631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.70679807662964</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.75725317001343</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.74264764785767</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.75990962982178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.80638217926025</t>
   </si>
   <si>
     <t xml:space="preserve">5.80239915847778</t>
   </si>
   <si>
-    <t xml:space="preserve">5.82497119903564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.92455387115479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.94579887390137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.93650436401367</t>
+    <t xml:space="preserve">5.82497024536133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.92455339431763</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.94579839706421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.93650341033936</t>
   </si>
   <si>
     <t xml:space="preserve">5.96837043762207</t>
   </si>
   <si>
-    <t xml:space="preserve">5.9577488899231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.02148103713989</t>
+    <t xml:space="preserve">5.95774841308594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.02148199081421</t>
   </si>
   <si>
     <t xml:space="preserve">5.97633695602417</t>
   </si>
   <si>
-    <t xml:space="preserve">6.31757783889771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.32023286819458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.28172540664673</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.14894914627075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.12372159957886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.14230918884277</t>
+    <t xml:space="preserve">6.31757640838623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.3202338218689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.28172636032104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.14894866943359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.1237211227417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.14230871200562</t>
   </si>
   <si>
     <t xml:space="preserve">6.223304271698</t>
   </si>
   <si>
-    <t xml:space="preserve">6.31359386444092</t>
+    <t xml:space="preserve">6.31359481811523</t>
   </si>
   <si>
     <t xml:space="preserve">6.26712131500244</t>
   </si>
   <si>
-    <t xml:space="preserve">6.20604276657104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.252516746521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.0546760559082</t>
+    <t xml:space="preserve">6.2060432434082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.25251531600952</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.05467653274536</t>
   </si>
   <si>
     <t xml:space="preserve">5.98032093048096</t>
   </si>
   <si>
-    <t xml:space="preserve">5.97500991821289</t>
+    <t xml:space="preserve">5.97500896453857</t>
   </si>
   <si>
     <t xml:space="preserve">5.90596532821655</t>
   </si>
   <si>
-    <t xml:space="preserve">6.08787202835083</t>
+    <t xml:space="preserve">6.08787107467651</t>
   </si>
   <si>
     <t xml:space="preserve">6.04936599731445</t>
@@ -1868,196 +1868,196 @@
     <t xml:space="preserve">6.12770462036133</t>
   </si>
   <si>
-    <t xml:space="preserve">5.99094343185425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.04405450820923</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.08255910873413</t>
+    <t xml:space="preserve">5.99094247817993</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.04405498504639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.08256006240845</t>
   </si>
   <si>
     <t xml:space="preserve">5.82098722457886</t>
   </si>
   <si>
-    <t xml:space="preserve">5.92189931869507</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.90729331970215</t>
+    <t xml:space="preserve">5.92189836502075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.90729284286499</t>
   </si>
   <si>
     <t xml:space="preserve">5.86082124710083</t>
   </si>
   <si>
-    <t xml:space="preserve">5.83028125762939</t>
+    <t xml:space="preserve">5.83028221130371</t>
   </si>
   <si>
     <t xml:space="preserve">5.77584171295166</t>
   </si>
   <si>
-    <t xml:space="preserve">5.78779315948486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.93517541885376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.89401531219482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.92588233947754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.04272747039795</t>
+    <t xml:space="preserve">5.78779363632202</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.93517589569092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.89401483535767</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.92588090896606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.04272699356079</t>
   </si>
   <si>
     <t xml:space="preserve">6.09982061386108</t>
   </si>
   <si>
-    <t xml:space="preserve">6.12903261184692</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.15293264389038</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.12106561660767</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.16753721237183</t>
+    <t xml:space="preserve">6.12903308868408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.15293216705322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.12106609344482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.16753768920898</t>
   </si>
   <si>
     <t xml:space="preserve">6.22197675704956</t>
   </si>
   <si>
-    <t xml:space="preserve">6.31624889373779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.42833137512207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.38377809524536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.35732173919678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.36289310455322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.4464316368103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.43529224395752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.58983898162842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.74577903747559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.78754854202271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.76248788833618</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.75273942947388</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.72071695327759</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.78615760803223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.71932554244995</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.72350263595581</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.69426298141479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.67337894439697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.65945482254028</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.54389190673828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.57313299179077</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.53136157989502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.59540843963623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.5480694770813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.67477130889893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.50073051452637</t>
+    <t xml:space="preserve">6.31624937057495</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.42833089828491</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.38377714157104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.35732269287109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.36289119720459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.44643068313599</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.43529272079468</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.58983945846558</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.74577856063843</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.78754806518555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.76248598098755</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.75274038314819</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.7207179069519</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.78615665435791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.71932506561279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.72350072860718</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.69426441192627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.67337942123413</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.6594557762146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.54389238357544</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.57313203811646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.53136205673218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.59540939331055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.54806995391846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.67477035522461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.50073146820068</t>
   </si>
   <si>
     <t xml:space="preserve">6.72489452362061</t>
   </si>
   <si>
-    <t xml:space="preserve">6.79172468185425</t>
+    <t xml:space="preserve">6.79172515869141</t>
   </si>
   <si>
     <t xml:space="preserve">6.71236371994019</t>
   </si>
   <si>
-    <t xml:space="preserve">6.60515546798706</t>
+    <t xml:space="preserve">6.60515594482422</t>
   </si>
   <si>
     <t xml:space="preserve">6.6009783744812</t>
   </si>
   <si>
-    <t xml:space="preserve">6.70957899093628</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.26125288009644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.33504486083984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.4812388420105</t>
+    <t xml:space="preserve">6.70957803726196</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.26125192642212</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.335045337677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.48123931884766</t>
   </si>
   <si>
     <t xml:space="preserve">6.36567640304565</t>
   </si>
   <si>
-    <t xml:space="preserve">6.61350870132446</t>
+    <t xml:space="preserve">6.61350917816162</t>
   </si>
   <si>
     <t xml:space="preserve">6.56756210327148</t>
   </si>
   <si>
-    <t xml:space="preserve">6.75134801864624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.72767782211304</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.55781698226929</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.61211585998535</t>
+    <t xml:space="preserve">6.75134754180908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.72767877578735</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.55781507492065</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.61211729049683</t>
   </si>
   <si>
     <t xml:space="preserve">6.54250001907349</t>
   </si>
   <si>
-    <t xml:space="preserve">6.85020351409912</t>
+    <t xml:space="preserve">6.8502025604248</t>
   </si>
   <si>
     <t xml:space="preserve">6.80286407470703</t>
@@ -2066,70 +2066,70 @@
     <t xml:space="preserve">6.87526512145996</t>
   </si>
   <si>
-    <t xml:space="preserve">6.89197254180908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.02424335479736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.9963960647583</t>
+    <t xml:space="preserve">6.89197111129761</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.02424287796021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.99639654159546</t>
   </si>
   <si>
     <t xml:space="preserve">7.01380014419556</t>
   </si>
   <si>
-    <t xml:space="preserve">7.01727962493896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.89893436431885</t>
+    <t xml:space="preserve">7.01728105545044</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.89893388748169</t>
   </si>
   <si>
     <t xml:space="preserve">6.92678022384644</t>
   </si>
   <si>
-    <t xml:space="preserve">7.04860830307007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.09037828445435</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.0033597946167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.94348907470703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.07297420501709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.08689832687378</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.00683832168579</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.15303230285645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.11126327514648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.10778141021729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.14258909225464</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.26093626022339</t>
+    <t xml:space="preserve">7.04860782623291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.09037923812866</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.00335836410522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.94348669052124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.07297372817993</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.08689641952515</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.00683736801147</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.15303182601929</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.11126279830933</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.10778188705444</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.1425895690918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.26093578338623</t>
   </si>
   <si>
     <t xml:space="preserve">7.15999317169189</t>
   </si>
   <si>
-    <t xml:space="preserve">6.93652629852295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.95184278488159</t>
+    <t xml:space="preserve">6.93652582168579</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.95184230804443</t>
   </si>
   <si>
     <t xml:space="preserve">6.94766473770142</t>
@@ -2138,31 +2138,31 @@
     <t xml:space="preserve">7.14607048034668</t>
   </si>
   <si>
-    <t xml:space="preserve">7.05209016799927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.13562917709351</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.36536169052124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.37580251693726</t>
+    <t xml:space="preserve">7.05208873748779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.13562774658203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.36536026000977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.37580299377441</t>
   </si>
   <si>
     <t xml:space="preserve">7.47674608230591</t>
   </si>
   <si>
-    <t xml:space="preserve">7.36884212493896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.45237970352173</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.49414873123169</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.51851511001587</t>
+    <t xml:space="preserve">7.36884164810181</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.4523811340332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.49414920806885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.51851606369019</t>
   </si>
   <si>
     <t xml:space="preserve">7.60553503036499</t>
@@ -2171,55 +2171,55 @@
     <t xml:space="preserve">7.6229395866394</t>
   </si>
   <si>
-    <t xml:space="preserve">7.65078496932983</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.56028318405151</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.59509181976318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.58117151260376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.57420825958252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.67863130569458</t>
+    <t xml:space="preserve">7.65078639984131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.56028413772583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.59509134292603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.58116817474365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.57420778274536</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.67863178253174</t>
   </si>
   <si>
     <t xml:space="preserve">7.72388219833374</t>
   </si>
   <si>
-    <t xml:space="preserve">7.77609395980835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.65426540374756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.54636144638062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.63686084747314</t>
+    <t xml:space="preserve">7.77609300613403</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.65426588058472</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.54636240005493</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.63686323165894</t>
   </si>
   <si>
     <t xml:space="preserve">7.80045986175537</t>
   </si>
   <si>
-    <t xml:space="preserve">7.73780488967896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.75521039962769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.76913213729858</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.81078100204468</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.67666006088257</t>
+    <t xml:space="preserve">7.73780679702759</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.75520944595337</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.7691330909729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.81078052520752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.67665910720825</t>
   </si>
   <si>
     <t xml:space="preserve">7.74724960327148</t>
@@ -2228,169 +2228,169 @@
     <t xml:space="preserve">7.65195322036743</t>
   </si>
   <si>
-    <t xml:space="preserve">7.71548366546631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.73666000366211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.66607141494751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.61665916442871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.50724315643311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.47547912597656</t>
+    <t xml:space="preserve">7.7154860496521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.73666191101074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.66607189178467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.61665868759155</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.50724363327026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.47547817230225</t>
   </si>
   <si>
     <t xml:space="preserve">7.23194313049316</t>
   </si>
   <si>
-    <t xml:space="preserve">7.30959129333496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.40488862991333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.27076721191406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.28135681152344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.18958902359009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.2919454574585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.21076679229736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.33076763153076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.17900037765503</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.24253273010254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.17547178268433</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.26723718643188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.36253452301025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.14370679855347</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.19664669036865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.10488128662109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.04346704483032</t>
+    <t xml:space="preserve">7.30959272384644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.40488958358765</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.2707667350769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.28135585784912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.18959093093872</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.29194355010986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.21076583862305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.33076953887939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.17900133132935</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.24253177642822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.17546987533569</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.26723766326904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.36253499984741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.14370441436768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.19664859771729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.10488080978394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.04346752166748</t>
   </si>
   <si>
     <t xml:space="preserve">7.22488355636597</t>
   </si>
   <si>
-    <t xml:space="preserve">7.12605714797974</t>
+    <t xml:space="preserve">7.12605905532837</t>
   </si>
   <si>
     <t xml:space="preserve">7.23900127410889</t>
   </si>
   <si>
-    <t xml:space="preserve">7.20723628997803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.16488170623779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.10135126113892</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.09076309204102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.26017904281616</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.32723951339722</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.34841775894165</t>
+    <t xml:space="preserve">7.20723724365234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.16488218307495</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.10135173797607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.09076261520386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.26017808914185</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.32723903656006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.34841537475586</t>
   </si>
   <si>
     <t xml:space="preserve">7.25311994552612</t>
   </si>
   <si>
-    <t xml:space="preserve">7.47194766998291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.82136964797974</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.76136684417725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.3060622215271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.41547822952271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.5566577911377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.57077503204346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.62018871307373</t>
+    <t xml:space="preserve">7.47194862365723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.8213677406311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.76136636734009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.30606317520142</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.41547679901123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.55665874481201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.57077550888062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.62018775939941</t>
   </si>
   <si>
     <t xml:space="preserve">7.69783735275269</t>
   </si>
   <si>
-    <t xml:space="preserve">7.78960466384888</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.7507791519165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.72960376739502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.71901369094849</t>
+    <t xml:space="preserve">7.78960418701172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.75077962875366</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.72960186004639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.71901416778564</t>
   </si>
   <si>
     <t xml:space="preserve">8.00490283966064</t>
   </si>
   <si>
-    <t xml:space="preserve">8.12490558624268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.96607875823975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.97313642501831</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.40841770172119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.29547214508057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.44018507003784</t>
+    <t xml:space="preserve">8.12490653991699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.9660792350769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.97313785552979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.40841817855835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.2954740524292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.44018411636353</t>
   </si>
   <si>
     <t xml:space="preserve">7.11899900436401</t>
@@ -2405,82 +2405,82 @@
     <t xml:space="preserve">6.79075527191162</t>
   </si>
   <si>
-    <t xml:space="preserve">6.83875703811646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.65804672241211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.86275815963745</t>
+    <t xml:space="preserve">6.83875608444214</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.65804719924927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.86275720596313</t>
   </si>
   <si>
     <t xml:space="preserve">5.97050046920776</t>
   </si>
   <si>
-    <t xml:space="preserve">5.56107807159424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.56248998641968</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.33704805374146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.7605881690979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.58976030349731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.585524559021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.49658107757568</t>
+    <t xml:space="preserve">5.56107759475708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.56248950958252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.33704853057861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.76058721542358</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.589759349823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.58552408218384</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.49658155441284</t>
   </si>
   <si>
     <t xml:space="preserve">4.88059091567993</t>
   </si>
   <si>
-    <t xml:space="preserve">4.89612007141113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.06553649902344</t>
+    <t xml:space="preserve">4.89612054824829</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.0655369758606</t>
   </si>
   <si>
     <t xml:space="preserve">5.41142702102661</t>
   </si>
   <si>
-    <t xml:space="preserve">5.46084022521973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.71637535095215</t>
+    <t xml:space="preserve">5.46084117889404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.71637582778931</t>
   </si>
   <si>
     <t xml:space="preserve">5.54272508621216</t>
   </si>
   <si>
-    <t xml:space="preserve">5.5879020690918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.44954538345337</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.21801137924194</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.48625373840332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.52719402313232</t>
+    <t xml:space="preserve">5.58790302276611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.44954586029053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.2180118560791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.48625326156616</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.5271954536438</t>
   </si>
   <si>
     <t xml:space="preserve">5.67543411254883</t>
   </si>
   <si>
-    <t xml:space="preserve">5.7573184967041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.84343767166138</t>
+    <t xml:space="preserve">5.75731897354126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.84343814849854</t>
   </si>
   <si>
     <t xml:space="preserve">5.86320304870605</t>
@@ -2489,13 +2489,13 @@
     <t xml:space="preserve">5.88720369338989</t>
   </si>
   <si>
-    <t xml:space="preserve">5.36907386779785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.41283941268921</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.43542814254761</t>
+    <t xml:space="preserve">5.36907339096069</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.41283988952637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.43542766571045</t>
   </si>
   <si>
     <t xml:space="preserve">5.37330913543701</t>
@@ -2504,25 +2504,25 @@
     <t xml:space="preserve">5.25895309448242</t>
   </si>
   <si>
-    <t xml:space="preserve">5.34224891662598</t>
+    <t xml:space="preserve">5.34225034713745</t>
   </si>
   <si>
     <t xml:space="preserve">5.30695390701294</t>
   </si>
   <si>
-    <t xml:space="preserve">5.22224617004395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.56390190124512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.55401945114136</t>
+    <t xml:space="preserve">5.2222466468811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.56390237808228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.55401849746704</t>
   </si>
   <si>
     <t xml:space="preserve">5.66837501525879</t>
   </si>
   <si>
-    <t xml:space="preserve">5.47213459014893</t>
+    <t xml:space="preserve">5.47213554382324</t>
   </si>
   <si>
     <t xml:space="preserve">5.33942556381226</t>
@@ -2531,7 +2531,7 @@
     <t xml:space="preserve">5.18836355209351</t>
   </si>
   <si>
-    <t xml:space="preserve">5.10224342346191</t>
+    <t xml:space="preserve">5.10224294662476</t>
   </si>
   <si>
     <t xml:space="preserve">5.36060285568237</t>
@@ -2540,10 +2540,10 @@
     <t xml:space="preserve">5.4749584197998</t>
   </si>
   <si>
-    <t xml:space="preserve">5.25613021850586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.16012668609619</t>
+    <t xml:space="preserve">5.2561297416687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.16012763977051</t>
   </si>
   <si>
     <t xml:space="preserve">5.07259559631348</t>
@@ -2558,22 +2558,22 @@
     <t xml:space="preserve">5.23495244979858</t>
   </si>
   <si>
-    <t xml:space="preserve">5.20248079299927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.25330591201782</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.46225166320801</t>
+    <t xml:space="preserve">5.20248126983643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.25330543518066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.46225214004517</t>
   </si>
   <si>
     <t xml:space="preserve">5.54413652420044</t>
   </si>
   <si>
-    <t xml:space="preserve">5.57237243652344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.62319850921631</t>
+    <t xml:space="preserve">5.5723729133606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.62319755554199</t>
   </si>
   <si>
     <t xml:space="preserve">5.68813943862915</t>
@@ -2582,19 +2582,19 @@
     <t xml:space="preserve">5.86038017272949</t>
   </si>
   <si>
-    <t xml:space="preserve">6.04814863204956</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.19074201583862</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.31921482086182</t>
+    <t xml:space="preserve">6.04814910888672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.19074106216431</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.31921434402466</t>
   </si>
   <si>
     <t xml:space="preserve">6.12438631057739</t>
   </si>
   <si>
-    <t xml:space="preserve">6.05379629135132</t>
+    <t xml:space="preserve">6.05379676818848</t>
   </si>
   <si>
     <t xml:space="preserve">5.7347297668457</t>
@@ -2603,43 +2603,43 @@
     <t xml:space="preserve">5.82226085662842</t>
   </si>
   <si>
-    <t xml:space="preserve">5.87167406082153</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.99026584625244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.96344041824341</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.92108678817749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.80249691009521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.92205238342285</t>
+    <t xml:space="preserve">5.87167358398438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.99026536941528</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.96344089508057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.92108774185181</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.80249643325806</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.92205142974854</t>
   </si>
   <si>
     <t xml:space="preserve">6.02327108383179</t>
   </si>
   <si>
-    <t xml:space="preserve">5.75628757476807</t>
+    <t xml:space="preserve">5.75628709793091</t>
   </si>
   <si>
     <t xml:space="preserve">5.79736137390137</t>
   </si>
   <si>
-    <t xml:space="preserve">5.68147325515747</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.85457277297974</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.67707252502441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.687340259552</t>
+    <t xml:space="preserve">5.68147230148315</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.85457181930542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.67707204818726</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.68734121322632</t>
   </si>
   <si>
     <t xml:space="preserve">5.71227884292603</t>
@@ -2648,40 +2648,40 @@
     <t xml:space="preserve">5.80469655990601</t>
   </si>
   <si>
-    <t xml:space="preserve">5.77242279052734</t>
+    <t xml:space="preserve">5.77242374420166</t>
   </si>
   <si>
     <t xml:space="preserve">5.72694826126099</t>
   </si>
   <si>
-    <t xml:space="preserve">5.59198951721191</t>
+    <t xml:space="preserve">5.59199047088623</t>
   </si>
   <si>
     <t xml:space="preserve">5.64039850234985</t>
   </si>
   <si>
-    <t xml:space="preserve">5.74748516082764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.72548198699951</t>
+    <t xml:space="preserve">5.74748611450195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.72548151016235</t>
   </si>
   <si>
     <t xml:space="preserve">5.75041913986206</t>
   </si>
   <si>
-    <t xml:space="preserve">5.76655578613281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.00420045852661</t>
+    <t xml:space="preserve">5.76655626296997</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.00420093536377</t>
   </si>
   <si>
     <t xml:space="preserve">6.04820919036865</t>
   </si>
   <si>
-    <t xml:space="preserve">6.10248565673828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.0056676864624</t>
+    <t xml:space="preserve">6.10248613357544</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.00566720962524</t>
   </si>
   <si>
     <t xml:space="preserve">5.97632932662964</t>
@@ -2690,31 +2690,31 @@
     <t xml:space="preserve">5.82670021057129</t>
   </si>
   <si>
-    <t xml:space="preserve">5.7944278717041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.77975797653198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.58172130584717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.68587446212769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.79149389266968</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.8311014175415</t>
+    <t xml:space="preserve">5.79442691802979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.77975845336914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.58172035217285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.68587398529053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.79149341583252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.83110094070435</t>
   </si>
   <si>
     <t xml:space="preserve">5.82963514328003</t>
   </si>
   <si>
-    <t xml:space="preserve">5.73868370056152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.78415822982788</t>
+    <t xml:space="preserve">5.73868417739868</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.7841591835022</t>
   </si>
   <si>
     <t xml:space="preserve">5.88537836074829</t>
@@ -2726,46 +2726,46 @@
     <t xml:space="preserve">5.97192811965942</t>
   </si>
   <si>
-    <t xml:space="preserve">5.90004730224609</t>
+    <t xml:space="preserve">5.90004777908325</t>
   </si>
   <si>
     <t xml:space="preserve">5.87511014938354</t>
   </si>
   <si>
-    <t xml:space="preserve">5.78269243240356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.76362133026123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.82376623153687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.7240138053894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.80176210403442</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.82083177566528</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.75335311889648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.7577543258667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.6726713180542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.63013029098511</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.64186525344849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.83696937561035</t>
+    <t xml:space="preserve">5.78269290924072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.76362228393555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.82376718521118</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.72401475906372</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.80176258087158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.8208327293396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.75335264205933</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.75775384902954</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.67267179489136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.63013076782227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.64186477661133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.83696842193604</t>
   </si>
   <si>
     <t xml:space="preserve">5.71668004989624</t>
@@ -2780,22 +2780,22 @@
     <t xml:space="preserve">5.84577083587646</t>
   </si>
   <si>
-    <t xml:space="preserve">5.81203079223633</t>
+    <t xml:space="preserve">5.81203031539917</t>
   </si>
   <si>
     <t xml:space="preserve">5.69320869445801</t>
   </si>
   <si>
-    <t xml:space="preserve">5.49517202377319</t>
+    <t xml:space="preserve">5.49517107009888</t>
   </si>
   <si>
     <t xml:space="preserve">5.5729193687439</t>
   </si>
   <si>
-    <t xml:space="preserve">5.61839437484741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.60665845870972</t>
+    <t xml:space="preserve">5.61839389801025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.60665893554688</t>
   </si>
   <si>
     <t xml:space="preserve">5.56411743164062</t>
@@ -2804,28 +2804,28 @@
     <t xml:space="preserve">5.66973733901978</t>
   </si>
   <si>
-    <t xml:space="preserve">5.5567831993103</t>
+    <t xml:space="preserve">5.55678272247314</t>
   </si>
   <si>
     <t xml:space="preserve">5.55091524124146</t>
   </si>
   <si>
-    <t xml:space="preserve">5.50984048843384</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.5421142578125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.9323205947876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.88097667694092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.87804365158081</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.8795108795166</t>
+    <t xml:space="preserve">5.509840965271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.54211378097534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.93232107162476</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.88097715377808</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.87804269790649</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.87950992584229</t>
   </si>
   <si>
     <t xml:space="preserve">5.89271354675293</t>
@@ -2834,37 +2834,37 @@
     <t xml:space="preserve">5.8941798210144</t>
   </si>
   <si>
-    <t xml:space="preserve">5.59932374954224</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.66827058792114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.67560482025146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.56998538970947</t>
+    <t xml:space="preserve">5.59932327270508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.6682710647583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.67560529708862</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.56998586654663</t>
   </si>
   <si>
     <t xml:space="preserve">5.57878684997559</t>
   </si>
   <si>
-    <t xml:space="preserve">5.56851863861084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.47903442382812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.4394268989563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.21058416366577</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.14017105102539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.1343035697937</t>
+    <t xml:space="preserve">5.568519115448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.47903490066528</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.43942785263062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.21058464050293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.14017057418823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.13430309295654</t>
   </si>
   <si>
     <t xml:space="preserve">5.25752639770508</t>
@@ -2879,40 +2879,40 @@
     <t xml:space="preserve">5.65506839752197</t>
   </si>
   <si>
-    <t xml:space="preserve">5.56265068054199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.75922107696533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.90151453018188</t>
+    <t xml:space="preserve">5.56265020370483</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.75922155380249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.90151357650757</t>
   </si>
   <si>
     <t xml:space="preserve">5.85897302627563</t>
   </si>
   <si>
-    <t xml:space="preserve">6.03647375106812</t>
+    <t xml:space="preserve">6.0364727973938</t>
   </si>
   <si>
     <t xml:space="preserve">6.23744440078735</t>
   </si>
   <si>
-    <t xml:space="preserve">6.31812715530396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.42521381378174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.49416017532349</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.39440822601318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.42820310592651</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.5731782913208</t>
+    <t xml:space="preserve">6.3181266784668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.42521333694458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.49415969848633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.39440774917603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.42820262908936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.57317733764648</t>
   </si>
   <si>
     <t xml:space="preserve">6.51040506362915</t>
@@ -2921,13 +2921,13 @@
     <t xml:space="preserve">6.57616662979126</t>
   </si>
   <si>
-    <t xml:space="preserve">6.38485908508301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.43567657470703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.33254957199097</t>
+    <t xml:space="preserve">6.38485860824585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.43567562103271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.33254909515381</t>
   </si>
   <si>
     <t xml:space="preserve">6.35496807098389</t>
@@ -2942,37 +2942,37 @@
     <t xml:space="preserve">6.28173446655273</t>
   </si>
   <si>
-    <t xml:space="preserve">6.29070091247559</t>
+    <t xml:space="preserve">6.29070138931274</t>
   </si>
   <si>
     <t xml:space="preserve">6.23988580703735</t>
   </si>
   <si>
-    <t xml:space="preserve">6.23540210723877</t>
+    <t xml:space="preserve">6.23540115356445</t>
   </si>
   <si>
     <t xml:space="preserve">6.33553791046143</t>
   </si>
   <si>
-    <t xml:space="preserve">6.26977777481079</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.24586296081543</t>
+    <t xml:space="preserve">6.26977729797363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.24586391448975</t>
   </si>
   <si>
     <t xml:space="preserve">6.10238409042358</t>
   </si>
   <si>
-    <t xml:space="preserve">6.22792911529541</t>
+    <t xml:space="preserve">6.22792863845825</t>
   </si>
   <si>
     <t xml:space="preserve">6.25333690643311</t>
   </si>
   <si>
-    <t xml:space="preserve">6.21746587753296</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.23390626907349</t>
+    <t xml:space="preserve">6.21746683120728</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.23390674591064</t>
   </si>
   <si>
     <t xml:space="preserve">6.19355344772339</t>
@@ -2981,10 +2981,10 @@
     <t xml:space="preserve">6.38187074661255</t>
   </si>
   <si>
-    <t xml:space="preserve">6.51488924026489</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.42222452163696</t>
+    <t xml:space="preserve">6.51488876342773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.42222499847412</t>
   </si>
   <si>
     <t xml:space="preserve">6.37738752365112</t>
@@ -2993,157 +2993,157 @@
     <t xml:space="preserve">6.30265808105469</t>
   </si>
   <si>
-    <t xml:space="preserve">6.241379737854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.26230478286743</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.2099928855896</t>
+    <t xml:space="preserve">6.24138069152832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.26230430603027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.20999383926392</t>
   </si>
   <si>
     <t xml:space="preserve">6.27426052093506</t>
   </si>
   <si>
-    <t xml:space="preserve">6.21597194671631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.17860746383667</t>
+    <t xml:space="preserve">6.21597146987915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.17860698699951</t>
   </si>
   <si>
     <t xml:space="preserve">6.13376998901367</t>
   </si>
   <si>
-    <t xml:space="preserve">6.24885272979736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.09789991378784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.15319967269897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.03512811660767</t>
+    <t xml:space="preserve">6.24885368347168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.09789943695068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.15320014953613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.03512763977051</t>
   </si>
   <si>
     <t xml:space="preserve">6.19803667068481</t>
   </si>
   <si>
-    <t xml:space="preserve">6.18757486343384</t>
+    <t xml:space="preserve">6.18757438659668</t>
   </si>
   <si>
     <t xml:space="preserve">6.62847709655762</t>
   </si>
   <si>
-    <t xml:space="preserve">6.7345929145813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.89002847671509</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.06639003753662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.15158176422119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.10973262786865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.21136379241943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.23228883743286</t>
+    <t xml:space="preserve">6.73459243774414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.89002990722656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.06639099121094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.15158081054688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.10973215103149</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.21136522293091</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.23228931427002</t>
   </si>
   <si>
     <t xml:space="preserve">7.3010401725769</t>
   </si>
   <si>
-    <t xml:space="preserve">7.21286010742188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.08581924438477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.95280075073242</t>
+    <t xml:space="preserve">7.2128586769104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.08582019805908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.95280170440674</t>
   </si>
   <si>
     <t xml:space="preserve">7.02304744720459</t>
   </si>
   <si>
-    <t xml:space="preserve">7.20688199996948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.12019538879395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.13663578033447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.17997884750366</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.02753162384033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.34438276290894</t>
+    <t xml:space="preserve">7.20688056945801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.12019443511963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.13663530349731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.17997741699219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.02753019332886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.34438323974609</t>
   </si>
   <si>
     <t xml:space="preserve">7.38025236129761</t>
   </si>
   <si>
-    <t xml:space="preserve">7.4355525970459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.45348596572876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.36082363128662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.5028076171875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.57753849029541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.64479446411133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.61116647720337</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.67842149734497</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.63358402252197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.7979884147644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.75688695907593</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.81293487548828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.72699642181396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.85029888153076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.783043384552</t>
+    <t xml:space="preserve">7.43555212020874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.45348739624023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.36082172393799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.50280857086182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.57753753662109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.64479398727417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.61116552352905</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.67842054367065</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.63358449935913</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.79798936843872</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.75688648223877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.81293392181396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.72699594497681</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.85029935836792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.78304243087769</t>
   </si>
   <si>
     <t xml:space="preserve">7.82414436340332</t>
   </si>
   <si>
-    <t xml:space="preserve">7.81667041778564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.88392782211304</t>
+    <t xml:space="preserve">7.8166708946228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.88392686843872</t>
   </si>
   <si>
     <t xml:space="preserve">8.05580425262451</t>
@@ -3155,49 +3155,49 @@
     <t xml:space="preserve">8.10064220428467</t>
   </si>
   <si>
-    <t xml:space="preserve">8.15295219421387</t>
+    <t xml:space="preserve">8.15295124053955</t>
   </si>
   <si>
     <t xml:space="preserve">8.17537021636963</t>
   </si>
   <si>
-    <t xml:space="preserve">8.16416263580322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.04833126068115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.06701374053955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.05954074859619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.96986627578735</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.96239280700684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.05206775665283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.04085922241211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.93250131607056</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.92876386642456</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.10811519622803</t>
+    <t xml:space="preserve">8.16416072845459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.04833221435547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.06701278686523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.05953979492188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.9698657989502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.96239185333252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.05206680297852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.04085826873779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.93250179290771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.92876434326172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.10811424255371</t>
   </si>
   <si>
     <t xml:space="preserve">8.07822322845459</t>
   </si>
   <si>
-    <t xml:space="preserve">8.08943176269531</t>
+    <t xml:space="preserve">8.08943271636963</t>
   </si>
   <si>
     <t xml:space="preserve">8.16042518615723</t>
@@ -3209,13 +3209,13 @@
     <t xml:space="preserve">8.14547824859619</t>
   </si>
   <si>
-    <t xml:space="preserve">8.25757217407227</t>
+    <t xml:space="preserve">8.2575740814209</t>
   </si>
   <si>
     <t xml:space="preserve">8.19778919219971</t>
   </si>
   <si>
-    <t xml:space="preserve">8.16789722442627</t>
+    <t xml:space="preserve">8.16789817810059</t>
   </si>
   <si>
     <t xml:space="preserve">8.22020721435547</t>
@@ -3227,40 +3227,40 @@
     <t xml:space="preserve">8.35098457336426</t>
   </si>
   <si>
-    <t xml:space="preserve">8.24636363983154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.25010013580322</t>
+    <t xml:space="preserve">8.24636459350586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.25009918212891</t>
   </si>
   <si>
     <t xml:space="preserve">8.3098840713501</t>
   </si>
   <si>
-    <t xml:space="preserve">8.43692398071289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.42571449279785</t>
+    <t xml:space="preserve">8.43692302703857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.4257116317749</t>
   </si>
   <si>
     <t xml:space="preserve">8.39208602905273</t>
   </si>
   <si>
-    <t xml:space="preserve">8.46307754516602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.59385395050049</t>
+    <t xml:space="preserve">8.4630765914917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.59385299682617</t>
   </si>
   <si>
     <t xml:space="preserve">8.74331283569336</t>
   </si>
   <si>
-    <t xml:space="preserve">8.62748241424561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.53407096862793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.58638191223145</t>
+    <t xml:space="preserve">8.62748336791992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.53407001495361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.58638000488281</t>
   </si>
   <si>
     <t xml:space="preserve">8.59759044647217</t>
@@ -3275,25 +3275,25 @@
     <t xml:space="preserve">8.90024375915527</t>
   </si>
   <si>
-    <t xml:space="preserve">9.01233768463135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.02728271484375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.95629119873047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.97871017456055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.95255279541016</t>
+    <t xml:space="preserve">9.01233863830566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.02728176116943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.95629024505615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.97870922088623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.95255374908447</t>
   </si>
   <si>
     <t xml:space="preserve">9.01981067657471</t>
   </si>
   <si>
-    <t xml:space="preserve">8.9637622833252</t>
+    <t xml:space="preserve">8.96376419067383</t>
   </si>
   <si>
     <t xml:space="preserve">8.73957538604736</t>
@@ -3302,37 +3302,37 @@
     <t xml:space="preserve">8.85025310516357</t>
   </si>
   <si>
-    <t xml:space="preserve">8.73112010955811</t>
+    <t xml:space="preserve">8.73112201690674</t>
   </si>
   <si>
     <t xml:space="preserve">8.62736225128174</t>
   </si>
   <si>
-    <t xml:space="preserve">8.78108024597168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.75417804718018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.6119909286499</t>
+    <t xml:space="preserve">8.78107929229736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.75417900085449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.61198997497559</t>
   </si>
   <si>
     <t xml:space="preserve">8.573561668396</t>
   </si>
   <si>
-    <t xml:space="preserve">8.56971740722656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.66963386535645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.59277534484863</t>
+    <t xml:space="preserve">8.5697193145752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.66963291168213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.59277629852295</t>
   </si>
   <si>
     <t xml:space="preserve">8.71574974060059</t>
   </si>
   <si>
-    <t xml:space="preserve">8.58509063720703</t>
+    <t xml:space="preserve">8.58508968353271</t>
   </si>
   <si>
     <t xml:space="preserve">8.61967754364014</t>
@@ -3341,7 +3341,7 @@
     <t xml:space="preserve">8.31992816925049</t>
   </si>
   <si>
-    <t xml:space="preserve">8.45058822631836</t>
+    <t xml:space="preserve">8.45058727264404</t>
   </si>
   <si>
     <t xml:space="preserve">8.48133182525635</t>
@@ -3350,13 +3350,13 @@
     <t xml:space="preserve">8.47748851776123</t>
   </si>
   <si>
-    <t xml:space="preserve">8.44674301147461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.33145809173584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.35835742950439</t>
+    <t xml:space="preserve">8.44674396514893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.33145713806152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.35835647583008</t>
   </si>
   <si>
     <t xml:space="preserve">8.07398223876953</t>
@@ -3365,91 +3365,91 @@
     <t xml:space="preserve">8.15468215942383</t>
   </si>
   <si>
-    <t xml:space="preserve">8.41215801239014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.53897571563721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.6158332824707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.68500518798828</t>
+    <t xml:space="preserve">8.41215991973877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.53897476196289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.61583423614502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.6850061416626</t>
   </si>
   <si>
     <t xml:space="preserve">8.60046100616455</t>
   </si>
   <si>
-    <t xml:space="preserve">8.58124732971191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.55050468444824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.72727680206299</t>
+    <t xml:space="preserve">8.58124828338623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.55050563812256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.72727870941162</t>
   </si>
   <si>
     <t xml:space="preserve">8.85793781280518</t>
   </si>
   <si>
-    <t xml:space="preserve">8.90020942687988</t>
+    <t xml:space="preserve">8.9002103805542</t>
   </si>
   <si>
     <t xml:space="preserve">8.93479633331299</t>
   </si>
   <si>
-    <t xml:space="preserve">9.0078125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.02702522277832</t>
+    <t xml:space="preserve">9.00781154632568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.02702617645264</t>
   </si>
   <si>
     <t xml:space="preserve">8.98091125488281</t>
   </si>
   <si>
-    <t xml:space="preserve">8.92326641082764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.87330913543701</t>
+    <t xml:space="preserve">8.92326736450195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.87331008911133</t>
   </si>
   <si>
     <t xml:space="preserve">8.94632625579834</t>
   </si>
   <si>
-    <t xml:space="preserve">8.83487987518311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.76955032348633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.96169662475586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.93863868713379</t>
+    <t xml:space="preserve">8.83488082885742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.76955127716064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.96169757843018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.93863964080811</t>
   </si>
   <si>
     <t xml:space="preserve">8.9078950881958</t>
   </si>
   <si>
-    <t xml:space="preserve">8.82719421386719</t>
+    <t xml:space="preserve">8.82719230651855</t>
   </si>
   <si>
     <t xml:space="preserve">8.86562347412109</t>
   </si>
   <si>
-    <t xml:space="preserve">8.91173934936523</t>
+    <t xml:space="preserve">8.91173839569092</t>
   </si>
   <si>
     <t xml:space="preserve">8.94248294830322</t>
   </si>
   <si>
-    <t xml:space="preserve">8.80798053741455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.86946773529053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.88483715057373</t>
+    <t xml:space="preserve">8.80797958374023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.86946678161621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.88483905792236</t>
   </si>
   <si>
     <t xml:space="preserve">8.96553993225098</t>
@@ -3458,22 +3458,22 @@
     <t xml:space="preserve">9.10772895812988</t>
   </si>
   <si>
-    <t xml:space="preserve">9.02318382263184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.05777072906494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.13847064971924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.20380115509033</t>
+    <t xml:space="preserve">9.02318286895752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.05776977539062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.13847255706787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.20380210876465</t>
   </si>
   <si>
     <t xml:space="preserve">9.16921520233154</t>
   </si>
   <si>
-    <t xml:space="preserve">9.25375938415527</t>
+    <t xml:space="preserve">9.25375843048096</t>
   </si>
   <si>
     <t xml:space="preserve">9.03086948394775</t>
@@ -3482,22 +3482,22 @@
     <t xml:space="preserve">9.09235572814941</t>
   </si>
   <si>
-    <t xml:space="preserve">9.15000057220459</t>
+    <t xml:space="preserve">9.14999866485596</t>
   </si>
   <si>
     <t xml:space="preserve">9.11157035827637</t>
   </si>
   <si>
-    <t xml:space="preserve">9.29603099822998</t>
+    <t xml:space="preserve">9.2960319519043</t>
   </si>
   <si>
     <t xml:space="preserve">9.24222946166992</t>
   </si>
   <si>
-    <t xml:space="preserve">9.35751819610596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.36136150360107</t>
+    <t xml:space="preserve">9.35751914978027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.36136054992676</t>
   </si>
   <si>
     <t xml:space="preserve">9.34598922729492</t>
@@ -3506,7 +3506,7 @@
     <t xml:space="preserve">9.46896266937256</t>
   </si>
   <si>
-    <t xml:space="preserve">9.50354862213135</t>
+    <t xml:space="preserve">9.50354766845703</t>
   </si>
   <si>
     <t xml:space="preserve">9.60730743408203</t>
@@ -3518,13 +3518,13 @@
     <t xml:space="preserve">9.5189208984375</t>
   </si>
   <si>
-    <t xml:space="preserve">9.41516208648682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.64958000183105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.61499404907227</t>
+    <t xml:space="preserve">9.4151611328125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.64958095550537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.61499309539795</t>
   </si>
   <si>
     <t xml:space="preserve">9.59577941894531</t>
@@ -3533,13 +3533,13 @@
     <t xml:space="preserve">9.74181079864502</t>
   </si>
   <si>
-    <t xml:space="preserve">9.65726470947266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.64189434051514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.48433589935303</t>
+    <t xml:space="preserve">9.65726566314697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.64189338684082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.48433399200439</t>
   </si>
   <si>
     <t xml:space="preserve">9.56503486633301</t>
@@ -3548,7 +3548,7 @@
     <t xml:space="preserve">9.53044986724854</t>
   </si>
   <si>
-    <t xml:space="preserve">9.64573764801025</t>
+    <t xml:space="preserve">9.64573669433594</t>
   </si>
   <si>
     <t xml:space="preserve">9.57656478881836</t>
@@ -3557,49 +3557,49 @@
     <t xml:space="preserve">9.60346508026123</t>
   </si>
   <si>
-    <t xml:space="preserve">9.56119251251221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.46511936187744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.4113187789917</t>
+    <t xml:space="preserve">9.56119346618652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.46511840820312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.41131782531738</t>
   </si>
   <si>
     <t xml:space="preserve">9.42284774780273</t>
   </si>
   <si>
-    <t xml:space="preserve">9.33446025848389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.27297401428223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.25345802307129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.17930698394775</t>
+    <t xml:space="preserve">9.33445930480957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.27297306060791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.25345897674561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.17930793762207</t>
   </si>
   <si>
     <t xml:space="preserve">9.15198802947998</t>
   </si>
   <si>
-    <t xml:space="preserve">9.01539134979248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.64462757110596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.73829460144043</t>
+    <t xml:space="preserve">9.01539039611816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.64462661743164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.73829364776611</t>
   </si>
   <si>
     <t xml:space="preserve">8.69536304473877</t>
   </si>
   <si>
-    <t xml:space="preserve">8.85928153991699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.7656135559082</t>
+    <t xml:space="preserve">8.85928058624268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.76561260223389</t>
   </si>
   <si>
     <t xml:space="preserve">8.69926738739014</t>
@@ -3629,16 +3629,16 @@
     <t xml:space="preserve">8.6875581741333</t>
   </si>
   <si>
-    <t xml:space="preserve">8.75000286102295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.76171207427979</t>
+    <t xml:space="preserve">8.75000190734863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.76171112060547</t>
   </si>
   <si>
     <t xml:space="preserve">8.56267070770264</t>
   </si>
   <si>
-    <t xml:space="preserve">8.70316886901855</t>
+    <t xml:space="preserve">8.70316982269287</t>
   </si>
   <si>
     <t xml:space="preserve">8.78903007507324</t>
@@ -3647,7 +3647,7 @@
     <t xml:space="preserve">8.86708545684814</t>
   </si>
   <si>
-    <t xml:space="preserve">8.94514179229736</t>
+    <t xml:space="preserve">8.94514083862305</t>
   </si>
   <si>
     <t xml:space="preserve">9.0192928314209</t>
@@ -3656,16 +3656,16 @@
     <t xml:space="preserve">8.99977970123291</t>
   </si>
   <si>
-    <t xml:space="preserve">9.00758647918701</t>
+    <t xml:space="preserve">9.0075855255127</t>
   </si>
   <si>
     <t xml:space="preserve">9.13637638092041</t>
   </si>
   <si>
-    <t xml:space="preserve">9.14808559417725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.1832103729248</t>
+    <t xml:space="preserve">9.14808464050293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.18320846557617</t>
   </si>
   <si>
     <t xml:space="preserve">9.10515403747559</t>
@@ -3674,16 +3674,16 @@
     <t xml:space="preserve">9.13247394561768</t>
   </si>
   <si>
-    <t xml:space="preserve">9.15979290008545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.09735012054443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.05441856384277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.06222248077393</t>
+    <t xml:space="preserve">9.15979194641113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.09734916687012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.05441761016846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.06222343444824</t>
   </si>
   <si>
     <t xml:space="preserve">9.02709865570068</t>
@@ -3692,7 +3692,7 @@
     <t xml:space="preserve">9.04661273956299</t>
   </si>
   <si>
-    <t xml:space="preserve">9.12076473236084</t>
+    <t xml:space="preserve">9.12076568603516</t>
   </si>
   <si>
     <t xml:space="preserve">8.96465396881104</t>
@@ -3704,10 +3704,10 @@
     <t xml:space="preserve">8.81634902954102</t>
   </si>
   <si>
-    <t xml:space="preserve">9.01148700714111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.90221118927002</t>
+    <t xml:space="preserve">9.01148796081543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.9022102355957</t>
   </si>
   <si>
     <t xml:space="preserve">9.31200218200684</t>
@@ -3734,7 +3734,7 @@
     <t xml:space="preserve">8.66023921966553</t>
   </si>
   <si>
-    <t xml:space="preserve">8.69146060943604</t>
+    <t xml:space="preserve">8.69146251678467</t>
   </si>
   <si>
     <t xml:space="preserve">8.61340618133545</t>
@@ -3743,25 +3743,25 @@
     <t xml:space="preserve">8.40265655517578</t>
   </si>
   <si>
-    <t xml:space="preserve">8.37143516540527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.30118465423584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.836754322052</t>
+    <t xml:space="preserve">8.37143325805664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.30118370056152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.83675527572632</t>
   </si>
   <si>
     <t xml:space="preserve">8.09433841705322</t>
   </si>
   <si>
-    <t xml:space="preserve">8.02018451690674</t>
+    <t xml:space="preserve">8.02018547058105</t>
   </si>
   <si>
     <t xml:space="preserve">7.69625520706177</t>
   </si>
   <si>
-    <t xml:space="preserve">7.68376636505127</t>
+    <t xml:space="preserve">7.68376588821411</t>
   </si>
   <si>
     <t xml:space="preserve">7.57605075836182</t>
@@ -3770,37 +3770,37 @@
     <t xml:space="preserve">7.08742427825928</t>
   </si>
   <si>
-    <t xml:space="preserve">6.93443536758423</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.25602436065674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.89920043945312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.49955654144287</t>
+    <t xml:space="preserve">6.93443584442139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.25602293014526</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.89919948577881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.49955558776855</t>
   </si>
   <si>
     <t xml:space="preserve">7.54482841491699</t>
   </si>
   <si>
-    <t xml:space="preserve">7.74933385848999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.70718336105347</t>
+    <t xml:space="preserve">7.74933481216431</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.70718383789062</t>
   </si>
   <si>
     <t xml:space="preserve">8.0553092956543</t>
   </si>
   <si>
-    <t xml:space="preserve">7.88749170303345</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.86407423019409</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.89529848098755</t>
+    <t xml:space="preserve">7.88749027252197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.86407518386841</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.89529609680176</t>
   </si>
   <si>
     <t xml:space="preserve">8.10214328765869</t>
@@ -3809,79 +3809,79 @@
     <t xml:space="preserve">8.09043502807617</t>
   </si>
   <si>
-    <t xml:space="preserve">8.23483848571777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.12555980682373</t>
+    <t xml:space="preserve">8.23483753204346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.12555885314941</t>
   </si>
   <si>
     <t xml:space="preserve">8.21922588348389</t>
   </si>
   <si>
-    <t xml:space="preserve">8.289475440979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.25435066223145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.11775493621826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.99676895141602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.82504653930664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.70562314987183</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.85626888275146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.79304504394531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.6759614944458</t>
+    <t xml:space="preserve">8.28947639465332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.25435161590576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.11775398254395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.9967679977417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.8250470161438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.70562219619751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.85626935958862</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.79304456710815</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.67596101760864</t>
   </si>
   <si>
     <t xml:space="preserve">7.5979061126709</t>
   </si>
   <si>
-    <t xml:space="preserve">7.65878915786743</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.53546190261841</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.73372268676758</t>
+    <t xml:space="preserve">7.65878963470459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.53546237945557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.73372316360474</t>
   </si>
   <si>
     <t xml:space="preserve">7.70874500274658</t>
   </si>
   <si>
-    <t xml:space="preserve">7.57292890548706</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.35905790328979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.26070642471313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.23729038238525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.28412389755249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.32002878189087</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.246657371521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.18889570236206</t>
+    <t xml:space="preserve">7.57292795181274</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.35905742645264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.26070690155029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.2372899055481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.28412294387817</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.32002973556519</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.24665689468384</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.18889665603638</t>
   </si>
   <si>
     <t xml:space="preserve">7.1326961517334</t>
@@ -3890,16 +3890,16 @@
     <t xml:space="preserve">7.02654123306274</t>
   </si>
   <si>
-    <t xml:space="preserve">6.84389114379883</t>
+    <t xml:space="preserve">6.84389066696167</t>
   </si>
   <si>
     <t xml:space="preserve">7.00624656677246</t>
   </si>
   <si>
-    <t xml:space="preserve">7.16860055923462</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.39340114593506</t>
+    <t xml:space="preserve">7.16860151290894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.3934006690979</t>
   </si>
   <si>
     <t xml:space="preserve">7.54795122146606</t>
@@ -3911,16 +3911,16 @@
     <t xml:space="preserve">7.51204442977905</t>
   </si>
   <si>
-    <t xml:space="preserve">7.46677255630493</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.44023275375366</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.41837787628174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.563560962677</t>
+    <t xml:space="preserve">7.46677303314209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.44023370742798</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.4183783531189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.56356048583984</t>
   </si>
   <si>
     <t xml:space="preserve">7.43555068969727</t>
@@ -3935,19 +3935,19 @@
     <t xml:space="preserve">7.75245571136475</t>
   </si>
   <si>
-    <t xml:space="preserve">7.92261600494385</t>
+    <t xml:space="preserve">7.92261552810669</t>
   </si>
   <si>
     <t xml:space="preserve">7.82114458084106</t>
   </si>
   <si>
-    <t xml:space="preserve">7.81724071502686</t>
+    <t xml:space="preserve">7.81724119186401</t>
   </si>
   <si>
     <t xml:space="preserve">7.743088722229</t>
   </si>
   <si>
-    <t xml:space="preserve">7.89139366149902</t>
+    <t xml:space="preserve">7.89139461517334</t>
   </si>
   <si>
     <t xml:space="preserve">7.87578296661377</t>
@@ -3959,61 +3959,61 @@
     <t xml:space="preserve">7.1436243057251</t>
   </si>
   <si>
-    <t xml:space="preserve">6.90477466583252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.11708545684814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.35125207901001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.98595190048218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.02185773849487</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.18777894973755</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.12729597091675</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.15998983383179</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.10441017150879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.31201601028442</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.2760534286499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.42154169082642</t>
+    <t xml:space="preserve">6.90477418899536</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.11708498001099</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.35125160217285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.98595142364502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.02185869216919</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.18777847290039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.12729549407959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.15998888015747</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.10440969467163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.31201648712158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.27605390548706</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.42154121398926</t>
   </si>
   <si>
     <t xml:space="preserve">7.36596202850342</t>
   </si>
   <si>
-    <t xml:space="preserve">7.28422594070435</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.2874960899353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.28095769882202</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.98834657669067</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.03248310089111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.21393537521362</t>
+    <t xml:space="preserve">7.2842264175415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.28749656677246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.28095817565918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.98834609985352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.03248262405396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.21393442153931</t>
   </si>
   <si>
     <t xml:space="preserve">7.10114049911499</t>
@@ -4022,28 +4022,28 @@
     <t xml:space="preserve">6.96709489822388</t>
   </si>
   <si>
-    <t xml:space="preserve">6.99815464019775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.85103130340576</t>
+    <t xml:space="preserve">6.99815368652344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.85103178024292</t>
   </si>
   <si>
     <t xml:space="preserve">6.5028395652771</t>
   </si>
   <si>
-    <t xml:space="preserve">6.66794538497925</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.7938175201416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.01940536499023</t>
+    <t xml:space="preserve">6.66794490814209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.79381704330444</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.01940584182739</t>
   </si>
   <si>
     <t xml:space="preserve">6.86410856246948</t>
   </si>
   <si>
-    <t xml:space="preserve">6.5289945602417</t>
+    <t xml:space="preserve">6.52899503707886</t>
   </si>
   <si>
     <t xml:space="preserve">6.61563396453857</t>
@@ -4058,43 +4058,43 @@
     <t xml:space="preserve">6.64015483856201</t>
   </si>
   <si>
-    <t xml:space="preserve">6.5845742225647</t>
+    <t xml:space="preserve">6.58457469940186</t>
   </si>
   <si>
     <t xml:space="preserve">6.67775344848633</t>
   </si>
   <si>
-    <t xml:space="preserve">6.74314117431641</t>
+    <t xml:space="preserve">6.74314069747925</t>
   </si>
   <si>
     <t xml:space="preserve">6.66140508651733</t>
   </si>
   <si>
-    <t xml:space="preserve">6.77419996261597</t>
+    <t xml:space="preserve">6.77420043945312</t>
   </si>
   <si>
     <t xml:space="preserve">6.85266542434692</t>
   </si>
   <si>
-    <t xml:space="preserve">6.92949676513672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.86574268341064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.82814502716064</t>
+    <t xml:space="preserve">6.92949724197388</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.8657431602478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.8281455039978</t>
   </si>
   <si>
     <t xml:space="preserve">6.8690128326416</t>
   </si>
   <si>
-    <t xml:space="preserve">6.97036361694336</t>
+    <t xml:space="preserve">6.97036409378052</t>
   </si>
   <si>
     <t xml:space="preserve">6.97690343856812</t>
   </si>
   <si>
-    <t xml:space="preserve">6.91805410385132</t>
+    <t xml:space="preserve">6.918053150177</t>
   </si>
   <si>
     <t xml:space="preserve">6.82651042938232</t>
@@ -4103,25 +4103,25 @@
     <t xml:space="preserve">6.70227336883545</t>
   </si>
   <si>
-    <t xml:space="preserve">6.53226518630981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.63198184967041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.59928703308105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.57803630828857</t>
+    <t xml:space="preserve">6.53226470947266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.63198137283325</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.59928750991821</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.57803678512573</t>
   </si>
   <si>
     <t xml:space="preserve">6.42927885055542</t>
   </si>
   <si>
-    <t xml:space="preserve">6.34754323959351</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.49466609954834</t>
+    <t xml:space="preserve">6.34754276275635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.4946665763855</t>
   </si>
   <si>
     <t xml:space="preserve">6.44562530517578</t>
@@ -4130,49 +4130,49 @@
     <t xml:space="preserve">6.62053871154785</t>
   </si>
   <si>
-    <t xml:space="preserve">6.44889497756958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.52245616912842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.5404372215271</t>
+    <t xml:space="preserve">6.44889450073242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.52245664596558</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.54043769836426</t>
   </si>
   <si>
     <t xml:space="preserve">6.60909557342529</t>
   </si>
   <si>
-    <t xml:space="preserve">6.71044635772705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.80035543441772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.8134331703186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.86737823486328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.7611231803894</t>
+    <t xml:space="preserve">6.71044731140137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.80035591125488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.81343221664429</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.86737871170044</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.76112270355225</t>
   </si>
   <si>
     <t xml:space="preserve">6.79054689407349</t>
   </si>
   <si>
-    <t xml:space="preserve">6.64832782745361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.64505910873413</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.45379972457886</t>
+    <t xml:space="preserve">6.64832830429077</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.64505863189697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.45379829406738</t>
   </si>
   <si>
     <t xml:space="preserve">6.51918697357178</t>
   </si>
   <si>
-    <t xml:space="preserve">6.38350677490234</t>
+    <t xml:space="preserve">6.38350629806519</t>
   </si>
   <si>
     <t xml:space="preserve">6.3916802406311</t>
@@ -4181,22 +4181,22 @@
     <t xml:space="preserve">6.25926971435547</t>
   </si>
   <si>
-    <t xml:space="preserve">6.36715936660767</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.4979362487793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.68919610977173</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.59274768829346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.48158836364746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.39331483840942</t>
+    <t xml:space="preserve">6.36716032028198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.49793529510498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.68919563293457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.59274816513062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.48158884048462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.39331531524658</t>
   </si>
   <si>
     <t xml:space="preserve">6.40802717208862</t>
@@ -4208,7 +4208,7 @@
     <t xml:space="preserve">6.36388969421387</t>
   </si>
   <si>
-    <t xml:space="preserve">6.46033763885498</t>
+    <t xml:space="preserve">6.46033716201782</t>
   </si>
   <si>
     <t xml:space="preserve">6.62217330932617</t>
@@ -4217,10 +4217,10 @@
     <t xml:space="preserve">6.86247396469116</t>
   </si>
   <si>
-    <t xml:space="preserve">6.82487630844116</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.80199003219604</t>
+    <t xml:space="preserve">6.82487678527832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.80198955535889</t>
   </si>
   <si>
     <t xml:space="preserve">6.73660182952881</t>
@@ -4235,7 +4235,7 @@
     <t xml:space="preserve">7.02103996276855</t>
   </si>
   <si>
-    <t xml:space="preserve">7.2270131111145</t>
+    <t xml:space="preserve">7.22701263427734</t>
   </si>
   <si>
     <t xml:space="preserve">7.17143249511719</t>
@@ -4247,52 +4247,52 @@
     <t xml:space="preserve">7.23028182983398</t>
   </si>
   <si>
-    <t xml:space="preserve">7.19268417358398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.14854717254639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.37740468978882</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.50327634811401</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.54904937744141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.64222574234009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.97243595123291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.87762260437012</t>
+    <t xml:space="preserve">7.19268369674683</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.14854764938354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.37740421295166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.50327825546265</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.54904794692993</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.64222621917725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.97243499755859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.87762308120728</t>
   </si>
   <si>
     <t xml:space="preserve">7.93156909942627</t>
   </si>
   <si>
-    <t xml:space="preserve">7.96099376678467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.86617946624756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.8122353553772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.84983396530151</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.81473731994629</t>
+    <t xml:space="preserve">7.96099328994751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.8661789894104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.81223440170288</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.84983348846436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.81473684310913</t>
   </si>
   <si>
     <t xml:space="preserve">7.77796936035156</t>
   </si>
   <si>
-    <t xml:space="preserve">7.85819005966187</t>
+    <t xml:space="preserve">7.85818958282471</t>
   </si>
   <si>
     <t xml:space="preserve">7.75624322891235</t>
@@ -4304,64 +4304,64 @@
     <t xml:space="preserve">7.80303859710693</t>
   </si>
   <si>
-    <t xml:space="preserve">7.87323093414307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.84314775466919</t>
+    <t xml:space="preserve">7.87323141098022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.84314823150635</t>
   </si>
   <si>
     <t xml:space="preserve">7.89662790298462</t>
   </si>
   <si>
-    <t xml:space="preserve">7.87657260894775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.80972242355347</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.90498399734497</t>
+    <t xml:space="preserve">7.87657356262207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.80972290039062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.90498495101929</t>
   </si>
   <si>
     <t xml:space="preserve">7.76292896270752</t>
   </si>
   <si>
-    <t xml:space="preserve">7.83479261398315</t>
+    <t xml:space="preserve">7.834792137146</t>
   </si>
   <si>
     <t xml:space="preserve">7.83646392822266</t>
   </si>
   <si>
-    <t xml:space="preserve">7.93172359466553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.93339586257935</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.5189266204834</t>
+    <t xml:space="preserve">7.93172454833984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.9333963394165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.51892757415771</t>
   </si>
   <si>
     <t xml:space="preserve">7.56070804595947</t>
   </si>
   <si>
-    <t xml:space="preserve">7.56739282608032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.69775056838989</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.76125812530518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.69607925415039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.70443534851074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.71446371078491</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.64427089691162</t>
+    <t xml:space="preserve">7.56739377975464</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.69775009155273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.76125717163086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.69607830047607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.70443439483643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.71446323394775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.64427042007446</t>
   </si>
   <si>
     <t xml:space="preserve">7.7295036315918</t>
@@ -4370,7 +4370,7 @@
     <t xml:space="preserve">7.62588691711426</t>
   </si>
   <si>
-    <t xml:space="preserve">7.86487483978271</t>
+    <t xml:space="preserve">7.86487531661987</t>
   </si>
   <si>
     <t xml:space="preserve">8.06041049957275</t>
@@ -4379,43 +4379,43 @@
     <t xml:space="preserve">7.94843673706055</t>
   </si>
   <si>
-    <t xml:space="preserve">8.02698516845703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.01194477081299</t>
+    <t xml:space="preserve">8.02698612213135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.01194381713867</t>
   </si>
   <si>
     <t xml:space="preserve">8.10553359985352</t>
   </si>
   <si>
-    <t xml:space="preserve">8.03534126281738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.10887622833252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.13060188293457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.17572593688965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.12391757965088</t>
+    <t xml:space="preserve">8.0353422164917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.10887718200684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.13060283660889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.17572689056396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.1239185333252</t>
   </si>
   <si>
     <t xml:space="preserve">8.16068458557129</t>
   </si>
   <si>
-    <t xml:space="preserve">7.98186159133911</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.00692939758301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.04537010192871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.05372619628906</t>
+    <t xml:space="preserve">7.98186206817627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.00693035125732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.04536914825439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.05372524261475</t>
   </si>
   <si>
     <t xml:space="preserve">8.16904067993164</t>
@@ -4433,22 +4433,22 @@
     <t xml:space="preserve">8.51498889923096</t>
   </si>
   <si>
-    <t xml:space="preserve">8.42306900024414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.43142604827881</t>
+    <t xml:space="preserve">8.42307090759277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.43142700195312</t>
   </si>
   <si>
     <t xml:space="preserve">8.43978309631348</t>
   </si>
   <si>
-    <t xml:space="preserve">8.57348251342773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.39800071716309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.51916599273682</t>
+    <t xml:space="preserve">8.57348346710205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.39800262451172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.51916694641113</t>
   </si>
   <si>
     <t xml:space="preserve">8.4732084274292</t>
@@ -4460,31 +4460,31 @@
     <t xml:space="preserve">8.5442361831665</t>
   </si>
   <si>
-    <t xml:space="preserve">8.2793436050415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.33783626556396</t>
+    <t xml:space="preserve">8.27934265136719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.33783721923828</t>
   </si>
   <si>
     <t xml:space="preserve">8.23589134216309</t>
   </si>
   <si>
-    <t xml:space="preserve">8.35287857055664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.52334594726562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.39382362365723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.38964462280273</t>
+    <t xml:space="preserve">8.35287952423096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.52334499359131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.39382457733154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.38964557647705</t>
   </si>
   <si>
     <t xml:space="preserve">8.46485137939453</t>
   </si>
   <si>
-    <t xml:space="preserve">8.61944198608398</t>
+    <t xml:space="preserve">8.61944007873535</t>
   </si>
   <si>
     <t xml:space="preserve">8.56512641906738</t>
@@ -4493,55 +4493,55 @@
     <t xml:space="preserve">8.54005813598633</t>
   </si>
   <si>
-    <t xml:space="preserve">8.48156452178955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.34619331359863</t>
+    <t xml:space="preserve">8.48156356811523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.34619426727295</t>
   </si>
   <si>
     <t xml:space="preserve">8.00860214233398</t>
   </si>
   <si>
-    <t xml:space="preserve">8.13561725616455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.74287462234497</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.53062582015991</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.60917377471924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.86821699142456</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.81640815734863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.83144950866699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.68437957763672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.8247652053833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.95010805130005</t>
+    <t xml:space="preserve">8.13561630249023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.74287366867065</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.53062629699707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.60917472839355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.86821746826172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.81640863418579</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.83144998550415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.68438005447388</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.82476472854614</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.95010852813721</t>
   </si>
   <si>
     <t xml:space="preserve">7.86320352554321</t>
   </si>
   <si>
-    <t xml:space="preserve">7.79301118850708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.63257169723511</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.72281885147095</t>
+    <t xml:space="preserve">7.79301071166992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.63257265090942</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.72281837463379</t>
   </si>
   <si>
     <t xml:space="preserve">7.81306600570679</t>
@@ -4550,55 +4550,55 @@
     <t xml:space="preserve">7.84649133682251</t>
   </si>
   <si>
-    <t xml:space="preserve">7.97517728805542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.85484647750854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.90832662582397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.99188947677612</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.91334009170532</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.00525856018066</t>
+    <t xml:space="preserve">7.97517681121826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.85484743118286</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.90832710266113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.99188995361328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.91334104537964</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.00525951385498</t>
   </si>
   <si>
     <t xml:space="preserve">7.928382396698</t>
   </si>
   <si>
-    <t xml:space="preserve">7.86988925933838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.9584641456604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.68939447402954</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.75791549682617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.67268228530884</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.91835403442383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.95679235458374</t>
+    <t xml:space="preserve">7.86988830566406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.95846462249756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.68939399719238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.75791501998901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.67268180847168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.91835498809814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.95679378509521</t>
   </si>
   <si>
     <t xml:space="preserve">8.04035568237305</t>
   </si>
   <si>
-    <t xml:space="preserve">7.94175100326538</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.02531433105469</t>
+    <t xml:space="preserve">7.94175243377686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.025315284729</t>
   </si>
   <si>
     <t xml:space="preserve">8.09717750549316</t>
@@ -4607,7 +4607,7 @@
     <t xml:space="preserve">8.04703998565674</t>
   </si>
   <si>
-    <t xml:space="preserve">8.0955057144165</t>
+    <t xml:space="preserve">8.09550666809082</t>
   </si>
   <si>
     <t xml:space="preserve">8.06876659393311</t>
@@ -4616,10 +4616,10 @@
     <t xml:space="preserve">8.29772663116455</t>
   </si>
   <si>
-    <t xml:space="preserve">8.27433013916016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.08714962005615</t>
+    <t xml:space="preserve">8.27432918548584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.08715057373047</t>
   </si>
   <si>
     <t xml:space="preserve">8.18575382232666</t>
@@ -4631,37 +4631,37 @@
     <t xml:space="preserve">8.10219192504883</t>
   </si>
   <si>
-    <t xml:space="preserve">8.15567111968994</t>
+    <t xml:space="preserve">8.15567207336426</t>
   </si>
   <si>
     <t xml:space="preserve">8.35622024536133</t>
   </si>
   <si>
-    <t xml:space="preserve">8.27767181396484</t>
+    <t xml:space="preserve">8.27767276763916</t>
   </si>
   <si>
     <t xml:space="preserve">8.30775356292725</t>
   </si>
   <si>
-    <t xml:space="preserve">8.33616352081299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.2760009765625</t>
+    <t xml:space="preserve">8.33616638183594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.27600193023682</t>
   </si>
   <si>
     <t xml:space="preserve">8.34786415100098</t>
   </si>
   <si>
-    <t xml:space="preserve">8.37293243408203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.4356050491333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.41053676605225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.43006038665771</t>
+    <t xml:space="preserve">8.37293338775635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.43560600280762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.41053581237793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.4300594329834</t>
   </si>
   <si>
     <t xml:space="preserve">8.34443187713623</t>
@@ -4676,7 +4676,7 @@
     <t xml:space="preserve">8.31996631622314</t>
   </si>
   <si>
-    <t xml:space="preserve">8.29200553894043</t>
+    <t xml:space="preserve">8.29200649261475</t>
   </si>
   <si>
     <t xml:space="preserve">8.49471855163574</t>
@@ -4688,16 +4688,16 @@
     <t xml:space="preserve">8.61180305480957</t>
   </si>
   <si>
-    <t xml:space="preserve">8.66422843933105</t>
+    <t xml:space="preserve">8.66422939300537</t>
   </si>
   <si>
     <t xml:space="preserve">8.63976383209229</t>
   </si>
   <si>
-    <t xml:space="preserve">8.63277244567871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.59957122802734</t>
+    <t xml:space="preserve">8.63277339935303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.59957027435303</t>
   </si>
   <si>
     <t xml:space="preserve">8.47374820709229</t>
@@ -4706,13 +4706,13 @@
     <t xml:space="preserve">8.53840732574463</t>
   </si>
   <si>
-    <t xml:space="preserve">8.54714393615723</t>
+    <t xml:space="preserve">8.54714298248291</t>
   </si>
   <si>
     <t xml:space="preserve">8.58034706115723</t>
   </si>
   <si>
-    <t xml:space="preserve">8.71141242980957</t>
+    <t xml:space="preserve">8.71141147613525</t>
   </si>
   <si>
     <t xml:space="preserve">8.6956844329834</t>
@@ -4724,7 +4724,7 @@
     <t xml:space="preserve">8.68519878387451</t>
   </si>
   <si>
-    <t xml:space="preserve">8.70966529846191</t>
+    <t xml:space="preserve">8.7096643447876</t>
   </si>
   <si>
     <t xml:space="preserve">8.82500076293945</t>
@@ -4733,10 +4733,10 @@
     <t xml:space="preserve">8.83373832702637</t>
   </si>
   <si>
-    <t xml:space="preserve">8.93859004974365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.03033542633057</t>
+    <t xml:space="preserve">8.93858909606934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.03033447265625</t>
   </si>
   <si>
     <t xml:space="preserve">9.00412273406982</t>
@@ -4745,13 +4745,13 @@
     <t xml:space="preserve">9.09586715698242</t>
   </si>
   <si>
-    <t xml:space="preserve">9.08276081085205</t>
+    <t xml:space="preserve">9.08276176452637</t>
   </si>
   <si>
     <t xml:space="preserve">8.98664665222168</t>
   </si>
   <si>
-    <t xml:space="preserve">8.79005146026611</t>
+    <t xml:space="preserve">8.7900505065918</t>
   </si>
   <si>
     <t xml:space="preserve">8.78568172454834</t>
@@ -4760,40 +4760,40 @@
     <t xml:space="preserve">8.80315685272217</t>
   </si>
   <si>
-    <t xml:space="preserve">8.67995643615723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.81626319885254</t>
+    <t xml:space="preserve">8.67995738983154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.81626415252686</t>
   </si>
   <si>
     <t xml:space="preserve">8.88616466522217</t>
   </si>
   <si>
-    <t xml:space="preserve">8.85558223724365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.87742614746094</t>
+    <t xml:space="preserve">8.85558319091797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.87742710113525</t>
   </si>
   <si>
     <t xml:space="preserve">8.77257537841797</t>
   </si>
   <si>
-    <t xml:space="preserve">8.737624168396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.75510120391846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.78131294250488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.79442024230957</t>
+    <t xml:space="preserve">8.73762512207031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.75510025024414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.7813138961792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.79441833496094</t>
   </si>
   <si>
     <t xml:space="preserve">8.820631980896</t>
   </si>
   <si>
-    <t xml:space="preserve">8.94732761383057</t>
+    <t xml:space="preserve">8.94732666015625</t>
   </si>
   <si>
     <t xml:space="preserve">9.02159786224365</t>
@@ -4802,34 +4802,34 @@
     <t xml:space="preserve">8.96043491363525</t>
   </si>
   <si>
-    <t xml:space="preserve">8.9342212677002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.87305736541748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.79878711700439</t>
+    <t xml:space="preserve">8.93422222137451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.87305641174316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.79878807067871</t>
   </si>
   <si>
     <t xml:space="preserve">8.99538516998291</t>
   </si>
   <si>
-    <t xml:space="preserve">8.89490127563477</t>
+    <t xml:space="preserve">8.8949031829834</t>
   </si>
   <si>
     <t xml:space="preserve">8.8424768447876</t>
   </si>
   <si>
-    <t xml:space="preserve">8.83810710906982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.92985248565674</t>
+    <t xml:space="preserve">8.83810806274414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.92985343933105</t>
   </si>
   <si>
     <t xml:space="preserve">8.8118953704834</t>
   </si>
   <si>
-    <t xml:space="preserve">8.75073146820068</t>
+    <t xml:space="preserve">8.75073051452637</t>
   </si>
   <si>
     <t xml:space="preserve">8.67296600341797</t>
@@ -4847,31 +4847,31 @@
     <t xml:space="preserve">8.34268474578857</t>
   </si>
   <si>
-    <t xml:space="preserve">8.41957569122314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.33744049072266</t>
+    <t xml:space="preserve">8.41957473754883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.33744239807129</t>
   </si>
   <si>
     <t xml:space="preserve">8.52966976165771</t>
   </si>
   <si>
-    <t xml:space="preserve">8.59257984161377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.51743602752686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.62578296661377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.64850044250488</t>
+    <t xml:space="preserve">8.59257888793945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.51743698120117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.62578201293945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.6485013961792</t>
   </si>
   <si>
     <t xml:space="preserve">8.46326351165771</t>
   </si>
   <si>
-    <t xml:space="preserve">8.02813053131104</t>
+    <t xml:space="preserve">8.02812957763672</t>
   </si>
   <si>
     <t xml:space="preserve">8.00890731811523</t>
@@ -4886,31 +4886,31 @@
     <t xml:space="preserve">8.06482791900635</t>
   </si>
   <si>
-    <t xml:space="preserve">7.98793745040894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.03686714172363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.16094303131104</t>
+    <t xml:space="preserve">7.98793649673462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.03686809539795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.16094207763672</t>
   </si>
   <si>
     <t xml:space="preserve">8.14521312713623</t>
   </si>
   <si>
-    <t xml:space="preserve">8.24307537078857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.32695579528809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.37239265441895</t>
+    <t xml:space="preserve">8.24307632446289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.3269567489624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.37239170074463</t>
   </si>
   <si>
     <t xml:space="preserve">8.63452053070068</t>
   </si>
   <si>
-    <t xml:space="preserve">8.73587799072266</t>
+    <t xml:space="preserve">8.73587703704834</t>
   </si>
   <si>
     <t xml:space="preserve">8.76383781433105</t>
@@ -4919,7 +4919,7 @@
     <t xml:space="preserve">8.919264793396</t>
   </si>
   <si>
-    <t xml:space="preserve">8.83874893188477</t>
+    <t xml:space="preserve">8.8387508392334</t>
   </si>
   <si>
     <t xml:space="preserve">8.79401969909668</t>
@@ -4934,10 +4934,10 @@
     <t xml:space="preserve">8.73318576812744</t>
   </si>
   <si>
-    <t xml:space="preserve">8.7922306060791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.77970504760742</t>
+    <t xml:space="preserve">8.79222965240479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.77970600128174</t>
   </si>
   <si>
     <t xml:space="preserve">8.83517169952393</t>
@@ -4946,7 +4946,7 @@
     <t xml:space="preserve">8.87453460693359</t>
   </si>
   <si>
-    <t xml:space="preserve">8.89600467681885</t>
+    <t xml:space="preserve">8.89600563049316</t>
   </si>
   <si>
     <t xml:space="preserve">8.91568660736084</t>
@@ -4955,7 +4955,7 @@
     <t xml:space="preserve">8.95952224731445</t>
   </si>
   <si>
-    <t xml:space="preserve">8.92284393310547</t>
+    <t xml:space="preserve">8.92284297943115</t>
   </si>
   <si>
     <t xml:space="preserve">8.97741413116455</t>
@@ -4967,16 +4967,16 @@
     <t xml:space="preserve">8.98636054992676</t>
   </si>
   <si>
-    <t xml:space="preserve">9.0534553527832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.14739036560059</t>
+    <t xml:space="preserve">9.05345630645752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.1473913192749</t>
   </si>
   <si>
     <t xml:space="preserve">9.12502479553223</t>
   </si>
   <si>
-    <t xml:space="preserve">9.10713291168213</t>
+    <t xml:space="preserve">9.10713386535645</t>
   </si>
   <si>
     <t xml:space="preserve">9.19212055206299</t>
@@ -4997,7 +4997,7 @@
     <t xml:space="preserve">9.27710819244385</t>
   </si>
   <si>
-    <t xml:space="preserve">9.11160564422607</t>
+    <t xml:space="preserve">9.11160659790039</t>
   </si>
   <si>
     <t xml:space="preserve">9.20553970336914</t>
@@ -5012,7 +5012,7 @@
     <t xml:space="preserve">9.03109169006348</t>
   </si>
   <si>
-    <t xml:space="preserve">9.0758228302002</t>
+    <t xml:space="preserve">9.07582187652588</t>
   </si>
   <si>
     <t xml:space="preserve">9.08029365539551</t>
@@ -5030,16 +5030,16 @@
     <t xml:space="preserve">9.04003620147705</t>
   </si>
   <si>
-    <t xml:space="preserve">9.13844394683838</t>
+    <t xml:space="preserve">9.1384449005127</t>
   </si>
   <si>
     <t xml:space="preserve">9.22343254089355</t>
   </si>
   <si>
-    <t xml:space="preserve">9.22790622711182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.99530696868896</t>
+    <t xml:space="preserve">9.22790431976318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.99530601501465</t>
   </si>
   <si>
     <t xml:space="preserve">8.94252490997314</t>
@@ -5048,13 +5048,13 @@
     <t xml:space="preserve">9.00425148010254</t>
   </si>
   <si>
-    <t xml:space="preserve">9.00872611999512</t>
+    <t xml:space="preserve">9.0087251663208</t>
   </si>
   <si>
     <t xml:space="preserve">9.02661800384521</t>
   </si>
   <si>
-    <t xml:space="preserve">8.88705825805664</t>
+    <t xml:space="preserve">8.88705921173096</t>
   </si>
   <si>
     <t xml:space="preserve">8.82264709472656</t>
@@ -5063,7 +5063,7 @@
     <t xml:space="preserve">8.76002407073975</t>
   </si>
   <si>
-    <t xml:space="preserve">8.81906795501709</t>
+    <t xml:space="preserve">8.81906890869141</t>
   </si>
   <si>
     <t xml:space="preserve">8.9013729095459</t>
@@ -5078,7 +5078,7 @@
     <t xml:space="preserve">9.10266017913818</t>
   </si>
   <si>
-    <t xml:space="preserve">9.16975498199463</t>
+    <t xml:space="preserve">9.16975593566895</t>
   </si>
   <si>
     <t xml:space="preserve">9.35762405395508</t>
@@ -5093,13 +5093,13 @@
     <t xml:space="preserve">10.0956773757935</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0330543518066</t>
+    <t xml:space="preserve">10.033055305481</t>
   </si>
   <si>
     <t xml:space="preserve">10.1896114349365</t>
   </si>
   <si>
-    <t xml:space="preserve">10.252233505249</t>
+    <t xml:space="preserve">10.2522344589233</t>
   </si>
   <si>
     <t xml:space="preserve">10.2924919128418</t>
@@ -5117,7 +5117,7 @@
     <t xml:space="preserve">10.4758863449097</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4848337173462</t>
+    <t xml:space="preserve">10.4848327636719</t>
   </si>
   <si>
     <t xml:space="preserve">10.5385093688965</t>
@@ -5132,7 +5132,7 @@
     <t xml:space="preserve">10.2835454940796</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2343416213989</t>
+    <t xml:space="preserve">10.2343406677246</t>
   </si>
   <si>
     <t xml:space="preserve">10.2477607727051</t>
@@ -5141,10 +5141,10 @@
     <t xml:space="preserve">10.3372230529785</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3461675643921</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3819522857666</t>
+    <t xml:space="preserve">10.3461685180664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3819532394409</t>
   </si>
   <si>
     <t xml:space="preserve">10.3148565292358</t>
@@ -5153,13 +5153,13 @@
     <t xml:space="preserve">10.4356288909912</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3059110641479</t>
+    <t xml:space="preserve">10.3059120178223</t>
   </si>
   <si>
     <t xml:space="preserve">10.4535217285156</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3103837966919</t>
+    <t xml:space="preserve">10.3103828430176</t>
   </si>
   <si>
     <t xml:space="preserve">10.4132642745972</t>
@@ -5168,7 +5168,7 @@
     <t xml:space="preserve">10.3551139831543</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4311571121216</t>
+    <t xml:space="preserve">10.4311552047729</t>
   </si>
   <si>
     <t xml:space="preserve">10.2880182266235</t>
@@ -5177,7 +5177,7 @@
     <t xml:space="preserve">10.2745990753174</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4266834259033</t>
+    <t xml:space="preserve">10.426682472229</t>
   </si>
   <si>
     <t xml:space="preserve">10.4222097396851</t>
@@ -5186,13 +5186,13 @@
     <t xml:space="preserve">10.4937782287598</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6682281494141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.551929473877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5564012527466</t>
+    <t xml:space="preserve">10.6682271957397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5519285202026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5564022064209</t>
   </si>
   <si>
     <t xml:space="preserve">10.6861200332642</t>
@@ -5213,7 +5213,7 @@
     <t xml:space="preserve">11.0171251296997</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9723968505859</t>
+    <t xml:space="preserve">10.9723949432373</t>
   </si>
   <si>
     <t xml:space="preserve">11.0081796646118</t>
@@ -5228,22 +5228,22 @@
     <t xml:space="preserve">11.0797491073608</t>
   </si>
   <si>
-    <t xml:space="preserve">11.093168258667</t>
+    <t xml:space="preserve">11.0931673049927</t>
   </si>
   <si>
     <t xml:space="preserve">11.0618562698364</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1200065612793</t>
+    <t xml:space="preserve">11.1200075149536</t>
   </si>
   <si>
     <t xml:space="preserve">11.0350179672241</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1110591888428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2989292144775</t>
+    <t xml:space="preserve">11.1110601425171</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2989282608032</t>
   </si>
   <si>
     <t xml:space="preserve">11.2810354232788</t>
@@ -5252,19 +5252,19 @@
     <t xml:space="preserve">11.2631435394287</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2094669342041</t>
+    <t xml:space="preserve">11.2094659805298</t>
   </si>
   <si>
     <t xml:space="preserve">11.2720909118652</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5091609954834</t>
+    <t xml:space="preserve">11.5091619491577</t>
   </si>
   <si>
     <t xml:space="preserve">11.4420652389526</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5896768569946</t>
+    <t xml:space="preserve">11.5896759033203</t>
   </si>
   <si>
     <t xml:space="preserve">11.4465389251709</t>
@@ -5282,13 +5282,13 @@
     <t xml:space="preserve">10.8918809890747</t>
   </si>
   <si>
-    <t xml:space="preserve">11.115532875061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2899808883667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2407789230347</t>
+    <t xml:space="preserve">11.1155338287354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.289981842041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2407779693604</t>
   </si>
   <si>
     <t xml:space="preserve">11.2716856002808</t>
@@ -6210,6 +6210,9 @@
   </si>
   <si>
     <t xml:space="preserve">19.9349994659424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1700000762939</t>
   </si>
 </sst>
 </file>
@@ -71340,7 +71343,7 @@
     </row>
     <row r="2493">
       <c r="A2493" s="1" t="n">
-        <v>45950.6494097222</v>
+        <v>45950.2916666667</v>
       </c>
       <c r="B2493" t="n">
         <v>1077240</v>
@@ -71361,6 +71364,32 @@
         <v>2025</v>
       </c>
       <c r="H2493" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2494">
+      <c r="A2494" s="1" t="n">
+        <v>45951.6493402778</v>
+      </c>
+      <c r="B2494" t="n">
+        <v>999141</v>
+      </c>
+      <c r="C2494" t="n">
+        <v>20.3400001525879</v>
+      </c>
+      <c r="D2494" t="n">
+        <v>20.1700000762939</v>
+      </c>
+      <c r="E2494" t="n">
+        <v>20.2399997711182</v>
+      </c>
+      <c r="F2494" t="n">
+        <v>20.1700000762939</v>
+      </c>
+      <c r="G2494" t="s">
+        <v>2066</v>
+      </c>
+      <c r="H2494" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/PST.MI.xlsx
+++ b/data/PST.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2069" uniqueCount="2069">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2070" uniqueCount="2070">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,208 +38,208 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">3.90457463264465</t>
+    <t xml:space="preserve">3.90457534790039</t>
   </si>
   <si>
     <t xml:space="preserve">PST.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">4.03631591796875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.97465085983276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95222616195679</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.91578793525696</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87934803962708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.97184777259827</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.01949882507324</t>
+    <t xml:space="preserve">4.03631687164307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97465062141418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95222663879395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.91578722000122</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87934994697571</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97184705734253</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.01949787139893</t>
   </si>
   <si>
     <t xml:space="preserve">3.99707460403442</t>
   </si>
   <si>
-    <t xml:space="preserve">3.94662022590637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8288950920105</t>
+    <t xml:space="preserve">3.94662070274353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8288938999176</t>
   </si>
   <si>
     <t xml:space="preserve">3.75601673126221</t>
   </si>
   <si>
-    <t xml:space="preserve">3.54859495162964</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.68594145774841</t>
+    <t xml:space="preserve">3.54859447479248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.68594121932983</t>
   </si>
   <si>
     <t xml:space="preserve">3.73359251022339</t>
   </si>
   <si>
-    <t xml:space="preserve">3.65510845184326</t>
+    <t xml:space="preserve">3.65510869026184</t>
   </si>
   <si>
     <t xml:space="preserve">3.76162266731262</t>
   </si>
   <si>
-    <t xml:space="preserve">3.80927324295044</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73079013824463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.82609176635742</t>
+    <t xml:space="preserve">3.80927395820618</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73078894615173</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.82609105110168</t>
   </si>
   <si>
     <t xml:space="preserve">3.72238063812256</t>
   </si>
   <si>
-    <t xml:space="preserve">3.64389681816101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.53177738189697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.35518789291382</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.0048131942749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.8982994556427</t>
+    <t xml:space="preserve">3.64389634132385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.53177714347839</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.35518836975098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.00481295585632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.89829921722412</t>
   </si>
   <si>
     <t xml:space="preserve">3.17019009590149</t>
   </si>
   <si>
-    <t xml:space="preserve">3.03284311294556</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.04405474662781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.13655471801758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.12253928184509</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.24867486953735</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.23465967178345</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.30473470687866</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.42246007919312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.34677910804749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.313143491745</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.40844464302063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.45609593391418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.51495885848999</t>
+    <t xml:space="preserve">3.0328426361084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.04405498504639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13655400276184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.12253975868225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.24867343902588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.23465943336487</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.30473399162292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.42245984077454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.34677863121033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.31314301490784</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.40844535827637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.45609569549561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.51495838165283</t>
   </si>
   <si>
     <t xml:space="preserve">3.48412561416626</t>
   </si>
   <si>
-    <t xml:space="preserve">3.45329284667969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.47571659088135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.43647456169128</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.45889925956726</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.43367218971252</t>
+    <t xml:space="preserve">3.45329308509827</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.47571706771851</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.43647503852844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.4588987827301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.43367195129395</t>
   </si>
   <si>
     <t xml:space="preserve">3.61306381225586</t>
   </si>
   <si>
-    <t xml:space="preserve">3.63829064369202</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.6354877948761</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.60745811462402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.58783721923828</t>
+    <t xml:space="preserve">3.63829040527344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.63548827171326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.60745787620544</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.5878369808197</t>
   </si>
   <si>
     <t xml:space="preserve">3.60185217857361</t>
   </si>
   <si>
-    <t xml:space="preserve">3.67192673683167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.79525852203369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77844095230103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71397113800049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.78404569625854</t>
+    <t xml:space="preserve">3.67192649841309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.79525899887085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77843999862671</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.7139720916748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.7840461730957</t>
   </si>
   <si>
     <t xml:space="preserve">3.72798657417297</t>
   </si>
   <si>
-    <t xml:space="preserve">3.6775324344635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61586594581604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.51215577125549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.56821537017822</t>
+    <t xml:space="preserve">3.67753338813782</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.6158664226532</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.51215553283691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.5682156085968</t>
   </si>
   <si>
     <t xml:space="preserve">3.58503341674805</t>
   </si>
   <si>
-    <t xml:space="preserve">3.60465502738953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.62147307395935</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.69995641708374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.63268518447876</t>
+    <t xml:space="preserve">3.60465455055237</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.62147235870361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.69995594024658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.6326847076416</t>
   </si>
   <si>
     <t xml:space="preserve">3.62988138198853</t>
@@ -248,217 +248,217 @@
     <t xml:space="preserve">3.65791177749634</t>
   </si>
   <si>
-    <t xml:space="preserve">3.62707924842834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.67473030090332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.68033504486084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.7448046207428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.79245448112488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80086493492126</t>
+    <t xml:space="preserve">3.62707805633545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.67473006248474</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.68033528327942</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.74480438232422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.79245519638062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.80086517333984</t>
   </si>
   <si>
     <t xml:space="preserve">3.73919868469238</t>
   </si>
   <si>
-    <t xml:space="preserve">3.68313956260681</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.76722860336304</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.79806160926819</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77563786506653</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.7588198184967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.78684997558594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.68874430656433</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.78965282440186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.74760723114014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83169722557068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83730340003967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80647039413452</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85972785949707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8569233417511</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.86813592910767</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84571266174316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8541214466095</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92419719696045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93260550498962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84010624885559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.78124356269836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.7644259929657</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87654566764832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96498346328735</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9148690700531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90602397918701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95024371147156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.63776254653931</t>
+    <t xml:space="preserve">3.68313908576965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.76722884178162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.79806113243103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77563762664795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.75881934165955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.7868492603302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.68874478340149</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.78965258598328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.74760818481445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.831698179245</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.83730411529541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8064706325531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85972762107849</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85692405700684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8681366443634</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84571242332458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85412120819092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92419672012329</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93260502815247</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84010577201843</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.78124403953552</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.76442551612854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87654542922974</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96498370170593</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.91486883163452</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90602517127991</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95024418830872</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.63776206970215</t>
   </si>
   <si>
     <t xml:space="preserve">3.42256188392639</t>
   </si>
   <si>
-    <t xml:space="preserve">3.51394820213318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.50805234909058</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.60533499717712</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.52574014663696</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.43730211257935</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.39897847175598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.3724467754364</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.49920845031738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.65839815139771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64955425262451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73504400253296</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.67018890380859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.6731379032135</t>
+    <t xml:space="preserve">3.51394867897034</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.50805258750916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.60533428192139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.52574038505554</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.43730187416077</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.39897871017456</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.37244701385498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.49920916557312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.65839791297913</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64955353736877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73504424095154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.67018985748291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.67313814163208</t>
   </si>
   <si>
     <t xml:space="preserve">3.65250182151794</t>
   </si>
   <si>
-    <t xml:space="preserve">3.70851278305054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.69672131538391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.65544939041138</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64660668373108</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.60238647460938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.58469891548157</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.5286877155304</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80284595489502</t>
+    <t xml:space="preserve">3.70851254463196</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.69672060012817</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.65544962882996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64660596847534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.60238695144653</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.5846996307373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.52868866920471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.80284643173218</t>
   </si>
   <si>
     <t xml:space="preserve">3.78221154212952</t>
   </si>
   <si>
-    <t xml:space="preserve">3.8087432384491</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.81463885307312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.86770129203796</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87949275970459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.7998993396759</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.72325253486633</t>
+    <t xml:space="preserve">3.80874276161194</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8146378993988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8677020072937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87949347496033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.79989862442017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.72325205802917</t>
   </si>
   <si>
     <t xml:space="preserve">3.76157569885254</t>
   </si>
   <si>
-    <t xml:space="preserve">3.667240858078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.68198156356812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.74388766288757</t>
+    <t xml:space="preserve">3.66724133491516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.68198108673096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.74388790130615</t>
   </si>
   <si>
     <t xml:space="preserve">3.70261669158936</t>
   </si>
   <si>
-    <t xml:space="preserve">3.6613461971283</t>
+    <t xml:space="preserve">3.66134572029114</t>
   </si>
   <si>
     <t xml:space="preserve">3.67903304100037</t>
@@ -470,46 +470,46 @@
     <t xml:space="preserve">3.69377303123474</t>
   </si>
   <si>
-    <t xml:space="preserve">3.68492889404297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.70556449890137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71735572814941</t>
+    <t xml:space="preserve">3.68492984771729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.70556569099426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71735692024231</t>
   </si>
   <si>
     <t xml:space="preserve">3.77631592750549</t>
   </si>
   <si>
-    <t xml:space="preserve">3.76452350616455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.56406331062317</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61712646484375</t>
+    <t xml:space="preserve">3.76452374458313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.56406354904175</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61712694168091</t>
   </si>
   <si>
     <t xml:space="preserve">3.61417818069458</t>
   </si>
   <si>
-    <t xml:space="preserve">3.58175134658813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.59943890571594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.60828351974487</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.58764696121216</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.57880306243896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.57290744781494</t>
+    <t xml:space="preserve">3.58175110816956</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.59943819046021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.60828256607056</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.58764719963074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.57880282402039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.5729079246521</t>
   </si>
   <si>
     <t xml:space="preserve">3.55816745758057</t>
@@ -518,406 +518,406 @@
     <t xml:space="preserve">3.56111550331116</t>
   </si>
   <si>
-    <t xml:space="preserve">3.50215625762939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.54637575149536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.56701111793518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.51689648628235</t>
+    <t xml:space="preserve">3.50215673446655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.54637551307678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.56701135635376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.51689600944519</t>
   </si>
   <si>
     <t xml:space="preserve">3.57585525512695</t>
   </si>
   <si>
-    <t xml:space="preserve">3.64365768432617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.62302303314209</t>
+    <t xml:space="preserve">3.64365792274475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.62302231788635</t>
   </si>
   <si>
     <t xml:space="preserve">3.51100063323975</t>
   </si>
   <si>
-    <t xml:space="preserve">3.49036502838135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.51984429359436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.55227112770081</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.54342865943909</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.53163623809814</t>
+    <t xml:space="preserve">3.49036455154419</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.51984357833862</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.5522723197937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.54342818260193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.53163552284241</t>
   </si>
   <si>
     <t xml:space="preserve">3.52279186248779</t>
   </si>
   <si>
-    <t xml:space="preserve">3.47857284545898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.4402494430542</t>
+    <t xml:space="preserve">3.47857356071472</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.44025015830994</t>
   </si>
   <si>
     <t xml:space="preserve">3.3665509223938</t>
   </si>
   <si>
-    <t xml:space="preserve">3.33117508888245</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.32528066635132</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.31938433647156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.31054067611694</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.26632142066956</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.39603114128113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.45793724060059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.4608850479126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.45204091072083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73209595680237</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.74683618545532</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73799252510071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.7291476726532</t>
+    <t xml:space="preserve">3.33117580413818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.32528042793274</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.3193838596344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.31054019927979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.26632118225098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.39603090286255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.45793747901917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.46088528633118</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.4520411491394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73209571838379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.7468364238739</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73799228668213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.72914838790894</t>
   </si>
   <si>
     <t xml:space="preserve">3.77926278114319</t>
   </si>
   <si>
-    <t xml:space="preserve">3.74093961715698</t>
+    <t xml:space="preserve">3.74094009399414</t>
   </si>
   <si>
     <t xml:space="preserve">3.77336764335632</t>
   </si>
   <si>
-    <t xml:space="preserve">3.79105520248413</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.76747107505798</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71440839767456</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.63481450080872</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.59649085998535</t>
+    <t xml:space="preserve">3.79105424880981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.76747131347656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.7144091129303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.63481402397156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.59649109840393</t>
   </si>
   <si>
     <t xml:space="preserve">3.56995940208435</t>
   </si>
   <si>
-    <t xml:space="preserve">3.5935435295105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.44909334182739</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.42845821380615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.44614577293396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.53753256797791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.53458452224731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.59059476852417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.6996693611145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.81758594512939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80579423904419</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.79695129394531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.75862693786621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.82937788963318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.79400324821472</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.67608547210693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71146035194397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.74978423118591</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77041959762573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.68787741661072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.75273156166077</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83232593536377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84411811828613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.72030448913574</t>
+    <t xml:space="preserve">3.5935423374176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.44909381866455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.42845726013184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.44614553451538</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.53753185272217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.534583568573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.59059429168701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.69966840744019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.81758618354797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.80579543113708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.79695105552673</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.75862741470337</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.82937812805176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.79400253295898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.67608571052551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71146011352539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.74978399276733</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77041935920715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.68787717819214</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.75273203849792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.83232617378235</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84411787986755</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.72030425071716</t>
   </si>
   <si>
     <t xml:space="preserve">3.69082498550415</t>
   </si>
   <si>
-    <t xml:space="preserve">3.81169033050537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8205349445343</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.78916692733765</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80171418190002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.81426095962524</t>
+    <t xml:space="preserve">3.81169080734253</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.82053422927856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.78916716575623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8017144203186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8142614364624</t>
   </si>
   <si>
     <t xml:space="preserve">3.75779986381531</t>
   </si>
   <si>
-    <t xml:space="preserve">3.76407432556152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77661967277527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73898005485535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.78603005409241</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.76093697547913</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.76721024513245</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.74525213241577</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.72956991195679</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.79544067382812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80485129356384</t>
+    <t xml:space="preserve">3.76407361030579</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77662086486816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73897957801819</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.78603053092957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.76093649864197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.76721048355103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.74525260925293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.72956943511963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.79544115066528</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.80485105514526</t>
   </si>
   <si>
     <t xml:space="preserve">3.84249186515808</t>
   </si>
   <si>
-    <t xml:space="preserve">3.8236711025238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80798816680908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.79857778549194</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.75152587890625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.74211645126343</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77975726127625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.91463565826416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92718291282654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94600391387939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.89267921447754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90208864212036</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90522646903992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94286632537842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83308124542236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8456289768219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.89895296096802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90836310386658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85817575454712</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83935546875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.82994532585144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85503816604614</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.81739783287048</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8613121509552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92091012001038</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.89581727981567</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88640570640564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88954329490662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8644483089447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88013243675232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85190200805664</t>
+    <t xml:space="preserve">3.82367062568665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.80798840522766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.79857754707336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.75152611732483</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.74211597442627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77975797653198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.91463613510132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92718362808228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94600319862366</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89267992973328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9020893573761</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90522623062134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94286751747131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8330819606781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84562802314758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89895248413086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90836358070374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85817551612854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.83935451507568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8299446105957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8550386428833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8173975944519</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.86131238937378</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92091083526611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89581632614136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88640594482422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88954305648804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.86444902420044</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88013219833374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85190057754517</t>
   </si>
   <si>
     <t xml:space="preserve">3.873859167099</t>
   </si>
   <si>
-    <t xml:space="preserve">3.9303195476532</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.86758589744568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93659353256226</t>
+    <t xml:space="preserve">3.93031978607178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.86758494377136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93659329414368</t>
   </si>
   <si>
     <t xml:space="preserve">3.94914078712463</t>
   </si>
   <si>
-    <t xml:space="preserve">3.93345713615417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93973064422607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92404675483704</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84876537322998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83621835708618</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.82680773735046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99305486679077</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.02128553390503</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99619054794312</t>
+    <t xml:space="preserve">3.93345665931702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9397304058075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92404699325562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8487651348114</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.83621788024902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8268084526062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99305415153503</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.02128458023071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99619126319885</t>
   </si>
   <si>
     <t xml:space="preserve">3.98364400863647</t>
   </si>
   <si>
-    <t xml:space="preserve">3.97109818458557</t>
+    <t xml:space="preserve">3.97109746932983</t>
   </si>
   <si>
     <t xml:space="preserve">3.98678112030029</t>
   </si>
   <si>
-    <t xml:space="preserve">3.99932813644409</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.01814889907837</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.03383207321167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.04637908935547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.05892562866211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.04010486602783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.07147264480591</t>
+    <t xml:space="preserve">3.99932789802551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.01814842224121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.03383159637451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.04637861251831</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.05892658233643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.04010534286499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.07147216796875</t>
   </si>
   <si>
     <t xml:space="preserve">4.10283994674683</t>
@@ -926,82 +926,82 @@
     <t xml:space="preserve">4.09970331192017</t>
   </si>
   <si>
-    <t xml:space="preserve">4.12793302536011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.21889877319336</t>
+    <t xml:space="preserve">4.12793350219727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.21889925003052</t>
   </si>
   <si>
     <t xml:space="preserve">4.2157621383667</t>
   </si>
   <si>
-    <t xml:space="preserve">4.2000789642334</t>
+    <t xml:space="preserve">4.20007944107056</t>
   </si>
   <si>
     <t xml:space="preserve">4.17184829711914</t>
   </si>
   <si>
-    <t xml:space="preserve">4.18753147125244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.19694185256958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.17310237884521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.15553760528564</t>
+    <t xml:space="preserve">4.1875319480896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.19694232940674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.17310285568237</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.15553712844849</t>
   </si>
   <si>
     <t xml:space="preserve">4.18063116073608</t>
   </si>
   <si>
-    <t xml:space="preserve">4.13044404983521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.13922595977783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.01501226425171</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.12166023254395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.04387044906616</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.03759622573853</t>
+    <t xml:space="preserve">4.13044309616089</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.13922643661499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.01501131057739</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.1216607093811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.043869972229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.03759670257568</t>
   </si>
   <si>
     <t xml:space="preserve">4.05516242980957</t>
   </si>
   <si>
-    <t xml:space="preserve">4.09531164169312</t>
+    <t xml:space="preserve">4.09531211853027</t>
   </si>
   <si>
     <t xml:space="preserve">4.12918853759766</t>
   </si>
   <si>
-    <t xml:space="preserve">4.175612449646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.18188619613647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.25340366363525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.24085664749146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.2069787979126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.21074390411377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.17435741424561</t>
+    <t xml:space="preserve">4.17561292648315</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.181884765625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.25340270996094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.24085569381714</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.20698022842407</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.21074342727661</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.17435646057129</t>
   </si>
   <si>
     <t xml:space="preserve">4.41651296615601</t>
@@ -1010,178 +1010,178 @@
     <t xml:space="preserve">4.43031454086304</t>
   </si>
   <si>
-    <t xml:space="preserve">4.40271091461182</t>
+    <t xml:space="preserve">4.40271139144897</t>
   </si>
   <si>
     <t xml:space="preserve">4.30735492706299</t>
   </si>
   <si>
-    <t xml:space="preserve">4.33495759963989</t>
+    <t xml:space="preserve">4.33495807647705</t>
   </si>
   <si>
     <t xml:space="preserve">4.37134408950806</t>
   </si>
   <si>
-    <t xml:space="preserve">4.48677539825439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.60095262527466</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.57711362838745</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.65490484237671</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.55452919006348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.49555921554565</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.56707572937012</t>
+    <t xml:space="preserve">4.48677492141724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.60095310211182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.57711315155029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.65490388870239</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.55452871322632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.4955587387085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.56707668304443</t>
   </si>
   <si>
     <t xml:space="preserve">4.6385931968689</t>
   </si>
   <si>
-    <t xml:space="preserve">4.60346126556396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.6348295211792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.6260461807251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.58338689804077</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.54574632644653</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.52943468093872</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.5444917678833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.61475324630737</t>
+    <t xml:space="preserve">4.60346221923828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.63482904434204</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.62604570388794</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.58338785171509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.54574584960938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.52943563461304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.54449081420898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.61475467681885</t>
   </si>
   <si>
     <t xml:space="preserve">4.62353658676147</t>
   </si>
   <si>
-    <t xml:space="preserve">4.65866804122925</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.73645877838135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.73144102096558</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.76782608032227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.82052326202393</t>
+    <t xml:space="preserve">4.65866756439209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.73645973205566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.73144006729126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.76782703399658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.82052421569824</t>
   </si>
   <si>
     <t xml:space="preserve">4.81299543380737</t>
   </si>
   <si>
-    <t xml:space="preserve">4.81676054000854</t>
+    <t xml:space="preserve">4.81676006317139</t>
   </si>
   <si>
     <t xml:space="preserve">4.81424999237061</t>
   </si>
   <si>
-    <t xml:space="preserve">4.8431077003479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.88702249526978</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.85690927505493</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.86694717407227</t>
+    <t xml:space="preserve">4.84310722351074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.88702201843262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.85690975189209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.86694669723511</t>
   </si>
   <si>
     <t xml:space="preserve">4.93721008300781</t>
   </si>
   <si>
-    <t xml:space="preserve">4.94222784042358</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.96355772018433</t>
+    <t xml:space="preserve">4.9422287940979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.96355867385864</t>
   </si>
   <si>
     <t xml:space="preserve">4.97359609603882</t>
   </si>
   <si>
-    <t xml:space="preserve">5.0012001991272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.08526277542114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.07146215438843</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.06267833709717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.11537599563599</t>
+    <t xml:space="preserve">5.00119972229004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.0852632522583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.07146167755127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.06267786026001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.11537551879883</t>
   </si>
   <si>
     <t xml:space="preserve">5.09153652191162</t>
   </si>
   <si>
-    <t xml:space="preserve">5.06769752502441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.11286640167236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.15552568435669</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.96230363845825</t>
+    <t xml:space="preserve">5.06769800186157</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.11286687850952</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.15552663803101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.96230316162109</t>
   </si>
   <si>
     <t xml:space="preserve">4.95101165771484</t>
   </si>
   <si>
-    <t xml:space="preserve">4.78037309646606</t>
+    <t xml:space="preserve">4.78037214279175</t>
   </si>
   <si>
     <t xml:space="preserve">4.7904109954834</t>
   </si>
   <si>
-    <t xml:space="preserve">4.82930612564087</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.80546760559082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.83432483673096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.76029825210571</t>
+    <t xml:space="preserve">4.82930660247803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.8054666519165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.83432531356812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.76029777526855</t>
   </si>
   <si>
     <t xml:space="preserve">4.60722541809082</t>
   </si>
   <si>
-    <t xml:space="preserve">4.40020227432251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.58464193344116</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.59467887878418</t>
+    <t xml:space="preserve">4.40020132064819</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.584641456604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.59467840194702</t>
   </si>
   <si>
     <t xml:space="preserve">4.68627166748047</t>
@@ -1190,13 +1190,13 @@
     <t xml:space="preserve">4.7126202583313</t>
   </si>
   <si>
-    <t xml:space="preserve">4.58840608596802</t>
+    <t xml:space="preserve">4.58840560913086</t>
   </si>
   <si>
     <t xml:space="preserve">4.58589601516724</t>
   </si>
   <si>
-    <t xml:space="preserve">4.56833028793335</t>
+    <t xml:space="preserve">4.56833076477051</t>
   </si>
   <si>
     <t xml:space="preserve">4.44411611557007</t>
@@ -1205,25 +1205,25 @@
     <t xml:space="preserve">4.61600923538208</t>
   </si>
   <si>
-    <t xml:space="preserve">4.7038369178772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.79292011260986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.90584278106689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.7866473197937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.86100244522095</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.91012954711914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.93270254135132</t>
+    <t xml:space="preserve">4.70383739471436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.79291915893555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.90584325790405</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.78664684295654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.86100196838379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.91013050079346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.93270206451416</t>
   </si>
   <si>
     <t xml:space="preserve">4.87162399291992</t>
@@ -1232,28 +1232,28 @@
     <t xml:space="preserve">4.8769359588623</t>
   </si>
   <si>
-    <t xml:space="preserve">4.81320238113403</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.83577394485474</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.7667293548584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.76009130477905</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.80789136886597</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.8198413848877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.93403005599976</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.97253656387329</t>
+    <t xml:space="preserve">4.81320190429688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.83577489852905</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.76673030853271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.76009082794189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.80789089202881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.81984186172485</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.93403053283691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.97253561019897</t>
   </si>
   <si>
     <t xml:space="preserve">5.01900768280029</t>
@@ -1262,109 +1262,109 @@
     <t xml:space="preserve">4.96589708328247</t>
   </si>
   <si>
-    <t xml:space="preserve">5.03892517089844</t>
+    <t xml:space="preserve">5.0389256477356</t>
   </si>
   <si>
     <t xml:space="preserve">5.02697515487671</t>
   </si>
   <si>
-    <t xml:space="preserve">5.10000371932983</t>
+    <t xml:space="preserve">5.10000276565552</t>
   </si>
   <si>
     <t xml:space="preserve">5.15311431884766</t>
   </si>
   <si>
-    <t xml:space="preserve">5.18099784851074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.12124681472778</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.13452434539795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.11859226226807</t>
+    <t xml:space="preserve">5.18099737167358</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.1212477684021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.13452529907227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.11859130859375</t>
   </si>
   <si>
     <t xml:space="preserve">5.12788581848145</t>
   </si>
   <si>
-    <t xml:space="preserve">5.2115364074707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.23410844802856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.25668048858643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.28854703903198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.28058099746704</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.99510860443115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.94465208053589</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.92871856689453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.86896896362305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.78664684295654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.71627473831177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.69635725021362</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.74548530578613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.60474061965942</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.54764556884766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.4759464263916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.61801910400391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.52772903442383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.51046800613403</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.50250196456909</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.48524045944214</t>
+    <t xml:space="preserve">5.21153545379639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.23410797119141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.25668096542358</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.28854656219482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.28058004379272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.99510812759399</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.94465255737305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.92871952056885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.86896848678589</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.78664636611938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.71627378463745</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.69635677337646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.74548578262329</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.60474014282227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.54764604568481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.47594547271729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.61801862716675</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.52772998809814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.51046895980835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.50250148773193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.48523998260498</t>
   </si>
   <si>
     <t xml:space="preserve">4.50515699386597</t>
   </si>
   <si>
-    <t xml:space="preserve">4.44673490524292</t>
+    <t xml:space="preserve">4.44673538208008</t>
   </si>
   <si>
     <t xml:space="preserve">4.40291833877563</t>
   </si>
   <si>
-    <t xml:space="preserve">4.47727346420288</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.59544610977173</t>
+    <t xml:space="preserve">4.47727394104004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.59544706344604</t>
   </si>
   <si>
     <t xml:space="preserve">4.68440771102905</t>
@@ -1376,7 +1376,7 @@
     <t xml:space="preserve">4.67378520965576</t>
   </si>
   <si>
-    <t xml:space="preserve">4.78133583068848</t>
+    <t xml:space="preserve">4.78133535385132</t>
   </si>
   <si>
     <t xml:space="preserve">4.75610828399658</t>
@@ -1391,25 +1391,25 @@
     <t xml:space="preserve">4.58880710601807</t>
   </si>
   <si>
-    <t xml:space="preserve">4.63262414932251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.61005115509033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.59810161590576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.66050720214844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.69901275634766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.72158575057983</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.77735280990601</t>
+    <t xml:space="preserve">4.63262367248535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.61005210876465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.5981011390686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.6605076789856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.69901371002197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.72158432006836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.77735185623169</t>
   </si>
   <si>
     <t xml:space="preserve">4.80523538589478</t>
@@ -1418,109 +1418,109 @@
     <t xml:space="preserve">4.77336883544922</t>
   </si>
   <si>
-    <t xml:space="preserve">4.5688910484314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.51976251602173</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.43876838684082</t>
+    <t xml:space="preserve">4.56889152526855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.51976299285889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.43876695632935</t>
   </si>
   <si>
     <t xml:space="preserve">4.4480619430542</t>
   </si>
   <si>
-    <t xml:space="preserve">4.45204544067383</t>
+    <t xml:space="preserve">4.45204591751099</t>
   </si>
   <si>
     <t xml:space="preserve">4.38167333602905</t>
   </si>
   <si>
-    <t xml:space="preserve">4.21968460083008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.24225616455078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.28474617004395</t>
+    <t xml:space="preserve">4.21968364715576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.2422571182251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.28474569320679</t>
   </si>
   <si>
     <t xml:space="preserve">4.1665735244751</t>
   </si>
   <si>
-    <t xml:space="preserve">4.14798498153687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.16391801834106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.2329626083374</t>
+    <t xml:space="preserve">4.14798402786255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.16391706466675</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.23296213150024</t>
   </si>
   <si>
     <t xml:space="preserve">4.17985153198242</t>
   </si>
   <si>
-    <t xml:space="preserve">4.06300592422485</t>
+    <t xml:space="preserve">4.06300687789917</t>
   </si>
   <si>
     <t xml:space="preserve">4.16259002685547</t>
   </si>
   <si>
-    <t xml:space="preserve">4.14001798629761</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.14931201934814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98201131820679</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.06831836700439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.07230234146118</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.20109510421753</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.10815191268921</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.21570158004761</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.3498067855835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.38432931900024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.32325220108032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.29536867141724</t>
+    <t xml:space="preserve">4.14001750946045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.1493124961853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.98201203346252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.06831789016724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.07230138778687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.20109558105469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.10815095901489</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.21570110321045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.34980726242065</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.38432836532593</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.32325172424316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.29536771774292</t>
   </si>
   <si>
     <t xml:space="preserve">4.43744039535522</t>
   </si>
   <si>
-    <t xml:space="preserve">4.53038501739502</t>
+    <t xml:space="preserve">4.53038549423218</t>
   </si>
   <si>
     <t xml:space="preserve">4.56092405319214</t>
   </si>
   <si>
-    <t xml:space="preserve">4.57021903991699</t>
+    <t xml:space="preserve">4.57021856307983</t>
   </si>
   <si>
     <t xml:space="preserve">4.57287406921387</t>
   </si>
   <si>
-    <t xml:space="preserve">4.42681837081909</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.31528520584106</t>
+    <t xml:space="preserve">4.42681884765625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.31528472900391</t>
   </si>
   <si>
     <t xml:space="preserve">4.32590627670288</t>
@@ -1541,70 +1541,70 @@
     <t xml:space="preserve">4.54100751876831</t>
   </si>
   <si>
-    <t xml:space="preserve">4.51710653305054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.44938993453979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.45071792602539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.55826950073242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.52241849899292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.5821681022644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.34051275253296</t>
+    <t xml:space="preserve">4.5171070098877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.44939088821411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.45071840286255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.55826854705811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.52241802215576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.58216857910156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.34051179885864</t>
   </si>
   <si>
     <t xml:space="preserve">4.36175727844238</t>
   </si>
   <si>
-    <t xml:space="preserve">4.31130123138428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.35379123687744</t>
+    <t xml:space="preserve">4.31130170822144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.35379076004028</t>
   </si>
   <si>
     <t xml:space="preserve">4.52905750274658</t>
   </si>
   <si>
-    <t xml:space="preserve">4.60075712203979</t>
+    <t xml:space="preserve">4.60075759887695</t>
   </si>
   <si>
     <t xml:space="preserve">4.57818555831909</t>
   </si>
   <si>
-    <t xml:space="preserve">4.57154703140259</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.7189302444458</t>
+    <t xml:space="preserve">4.57154655456543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.71892976760864</t>
   </si>
   <si>
     <t xml:space="preserve">4.65386915206909</t>
   </si>
   <si>
-    <t xml:space="preserve">4.58615255355835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.53569555282593</t>
+    <t xml:space="preserve">4.58615207672119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.53569650650024</t>
   </si>
   <si>
     <t xml:space="preserve">4.63660764694214</t>
   </si>
   <si>
-    <t xml:space="preserve">4.62731313705444</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.64590215682983</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.70299625396729</t>
+    <t xml:space="preserve">4.62731266021729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.64590120315552</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.70299673080444</t>
   </si>
   <si>
     <t xml:space="preserve">4.67112970352173</t>
@@ -1613,37 +1613,37 @@
     <t xml:space="preserve">4.71760225296021</t>
   </si>
   <si>
-    <t xml:space="preserve">4.78000783920288</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.79195833206177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.81453037261963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.79328536987305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.88224649429321</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.91278553009033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.03626871109009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.04556274414062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.99776411056519</t>
+    <t xml:space="preserve">4.78000736236572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.79195737838745</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.81452989578247</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.79328632354736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.88224697113037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.91278600692749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.0362696647644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.04556369781494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.99776363372803</t>
   </si>
   <si>
     <t xml:space="preserve">5.04423570632935</t>
   </si>
   <si>
-    <t xml:space="preserve">5.05618667602539</t>
+    <t xml:space="preserve">5.05618572235107</t>
   </si>
   <si>
     <t xml:space="preserve">5.10664129257202</t>
@@ -1652,16 +1652,16 @@
     <t xml:space="preserve">5.08406925201416</t>
   </si>
   <si>
-    <t xml:space="preserve">5.09203624725342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.98846912384033</t>
+    <t xml:space="preserve">5.09203672409058</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.98846864700317</t>
   </si>
   <si>
     <t xml:space="preserve">4.87826299667358</t>
   </si>
   <si>
-    <t xml:space="preserve">4.99245262145996</t>
+    <t xml:space="preserve">4.99245357513428</t>
   </si>
   <si>
     <t xml:space="preserve">5.07477474212646</t>
@@ -1673,52 +1673,52 @@
     <t xml:space="preserve">4.94863557815552</t>
   </si>
   <si>
-    <t xml:space="preserve">4.96456956863403</t>
+    <t xml:space="preserve">4.96456909179688</t>
   </si>
   <si>
     <t xml:space="preserve">5.02431917190552</t>
   </si>
   <si>
-    <t xml:space="preserve">5.09867429733276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.15045833587646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.08937978744507</t>
+    <t xml:space="preserve">5.09867477416992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.15045881271362</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.08938026428223</t>
   </si>
   <si>
     <t xml:space="preserve">5.14249181747437</t>
   </si>
   <si>
-    <t xml:space="preserve">5.16107988357544</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.1451473236084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.13054227828979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.16639184951782</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.18763589859009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.24340343475342</t>
+    <t xml:space="preserve">5.1610803604126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.14514684677124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.13054180145264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.16639232635498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.18763637542725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.24340295791626</t>
   </si>
   <si>
     <t xml:space="preserve">5.24473142623901</t>
   </si>
   <si>
-    <t xml:space="preserve">5.26464796066284</t>
+    <t xml:space="preserve">5.26464748382568</t>
   </si>
   <si>
     <t xml:space="preserve">5.26863050460815</t>
   </si>
   <si>
-    <t xml:space="preserve">5.23942041397095</t>
+    <t xml:space="preserve">5.23941946029663</t>
   </si>
   <si>
     <t xml:space="preserve">5.26331949234009</t>
@@ -1727,49 +1727,49 @@
     <t xml:space="preserve">5.27394199371338</t>
   </si>
   <si>
-    <t xml:space="preserve">5.27659797668457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.18630886077881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.24605894088745</t>
+    <t xml:space="preserve">5.27659702301025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.18630838394165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.24605798721313</t>
   </si>
   <si>
     <t xml:space="preserve">5.27128648757935</t>
   </si>
   <si>
-    <t xml:space="preserve">5.28456449508667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.30580854415894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.36423110961914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.41070222854614</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.55011940002441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.60323095321655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.73468160629272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.68289756774902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.70281457901001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.72538709640503</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.72671461105347</t>
+    <t xml:space="preserve">5.28456401824951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.30580902099609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.36423063278198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.41070318222046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.55012035369873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.60323143005371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.73468065261841</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.68289852142334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.70281410217285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.72538757324219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.72671508789062</t>
   </si>
   <si>
     <t xml:space="preserve">5.70679807662964</t>
@@ -1778,7 +1778,7 @@
     <t xml:space="preserve">5.75725364685059</t>
   </si>
   <si>
-    <t xml:space="preserve">5.74264812469482</t>
+    <t xml:space="preserve">5.74264860153198</t>
   </si>
   <si>
     <t xml:space="preserve">5.75990867614746</t>
@@ -1793,34 +1793,34 @@
     <t xml:space="preserve">5.82497024536133</t>
   </si>
   <si>
-    <t xml:space="preserve">5.92455530166626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.94579887390137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.93650484085083</t>
+    <t xml:space="preserve">5.9245548248291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.94579839706421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.93650388717651</t>
   </si>
   <si>
     <t xml:space="preserve">5.96836996078491</t>
   </si>
   <si>
-    <t xml:space="preserve">5.95774936676025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.02148151397705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.97633790969849</t>
+    <t xml:space="preserve">5.9577488899231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.02148103713989</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.97633695602417</t>
   </si>
   <si>
     <t xml:space="preserve">6.31757640838623</t>
   </si>
   <si>
-    <t xml:space="preserve">6.32023239135742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.28172779083252</t>
+    <t xml:space="preserve">6.32023191452026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.2817268371582</t>
   </si>
   <si>
     <t xml:space="preserve">6.14894866943359</t>
@@ -1832,100 +1832,100 @@
     <t xml:space="preserve">6.14231014251709</t>
   </si>
   <si>
-    <t xml:space="preserve">6.223304271698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.31359434127808</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.26712036132812</t>
+    <t xml:space="preserve">6.22330522537231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.31359338760376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.26712131500244</t>
   </si>
   <si>
     <t xml:space="preserve">6.20604372024536</t>
   </si>
   <si>
-    <t xml:space="preserve">6.25251579284668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.05467653274536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.98032093048096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.97500944137573</t>
+    <t xml:space="preserve">6.25251722335815</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.05467557907104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.98032188415527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.97500991821289</t>
   </si>
   <si>
     <t xml:space="preserve">5.90596532821655</t>
   </si>
   <si>
-    <t xml:space="preserve">6.08787059783936</t>
+    <t xml:space="preserve">6.08787155151367</t>
   </si>
   <si>
     <t xml:space="preserve">6.04936552047729</t>
   </si>
   <si>
-    <t xml:space="preserve">6.12770509719849</t>
+    <t xml:space="preserve">6.12770414352417</t>
   </si>
   <si>
     <t xml:space="preserve">5.99094295501709</t>
   </si>
   <si>
-    <t xml:space="preserve">6.04405450820923</t>
+    <t xml:space="preserve">6.04405498504639</t>
   </si>
   <si>
     <t xml:space="preserve">6.08256053924561</t>
   </si>
   <si>
-    <t xml:space="preserve">5.82098722457886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.92189931869507</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.90729188919067</t>
+    <t xml:space="preserve">5.8209867477417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.92189836502075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.90729236602783</t>
   </si>
   <si>
     <t xml:space="preserve">5.86082077026367</t>
   </si>
   <si>
-    <t xml:space="preserve">5.83028173446655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.77584218978882</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.78779268264771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.93517589569092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.89401435852051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.92588138580322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.04272651672363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.09982061386108</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.12903308868408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.15293216705322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.12106466293335</t>
+    <t xml:space="preserve">5.83028125762939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.77584266662598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.78779220581055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.93517637252808</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.89401531219482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.92588186264038</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.04272747039795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.09982109069824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.12903165817261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.15293073654175</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.12106561660767</t>
   </si>
   <si>
     <t xml:space="preserve">6.16753721237183</t>
   </si>
   <si>
-    <t xml:space="preserve">6.2219762802124</t>
+    <t xml:space="preserve">6.22197580337524</t>
   </si>
   <si>
     <t xml:space="preserve">6.31624937057495</t>
@@ -1934,295 +1934,295 @@
     <t xml:space="preserve">6.42833137512207</t>
   </si>
   <si>
-    <t xml:space="preserve">6.38377618789673</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.35732269287109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.36289262771606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.44643068313599</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.43529319763184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.58983993530273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.74577760696411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.78754901885986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.76248550415039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.75273990631104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.72071695327759</t>
+    <t xml:space="preserve">6.3837776184082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.35732221603394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.36289167404175</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.44642925262451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.43529272079468</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.58983945846558</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.74577903747559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.78754806518555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.76248645782471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.75274038314819</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.7207179069519</t>
   </si>
   <si>
     <t xml:space="preserve">6.78615665435791</t>
   </si>
   <si>
-    <t xml:space="preserve">6.71932649612427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.72350215911865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.69426488876343</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.67337846755981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.65945529937744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.5438928604126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.57313299179077</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.53136301040649</t>
+    <t xml:space="preserve">6.71932458877563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.72350120544434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.69426393508911</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.67337942123413</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.65945625305176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.54389238357544</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.57313251495361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.53136157989502</t>
   </si>
   <si>
     <t xml:space="preserve">6.59540843963623</t>
   </si>
   <si>
-    <t xml:space="preserve">6.5480694770813</t>
+    <t xml:space="preserve">6.54806995391846</t>
   </si>
   <si>
     <t xml:space="preserve">6.67477035522461</t>
   </si>
   <si>
-    <t xml:space="preserve">6.50073146820068</t>
+    <t xml:space="preserve">6.50073194503784</t>
   </si>
   <si>
     <t xml:space="preserve">6.72489452362061</t>
   </si>
   <si>
-    <t xml:space="preserve">6.79172563552856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.71236181259155</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.60515403747559</t>
+    <t xml:space="preserve">6.79172468185425</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.71236419677734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.60515451431274</t>
   </si>
   <si>
     <t xml:space="preserve">6.60097885131836</t>
   </si>
   <si>
-    <t xml:space="preserve">6.70957851409912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.26125288009644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.33504581451416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.48123836517334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.36567640304565</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.6135082244873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.56756162643433</t>
+    <t xml:space="preserve">6.70957899093628</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.26125240325928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.33504486083984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.48123931884766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.36567735671997</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.61350965499878</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.56756258010864</t>
   </si>
   <si>
     <t xml:space="preserve">6.7513484954834</t>
   </si>
   <si>
-    <t xml:space="preserve">6.72767972946167</t>
+    <t xml:space="preserve">6.7276782989502</t>
   </si>
   <si>
     <t xml:space="preserve">6.55781650543213</t>
   </si>
   <si>
-    <t xml:space="preserve">6.61211633682251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.54250001907349</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.85020208358765</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.80286455154419</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.87526416778564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.89197206497192</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.02424240112305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.9963960647583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.01380109786987</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.01728200912476</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.89893388748169</t>
+    <t xml:space="preserve">6.61211729049683</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.54250049591064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.85020303726196</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.80286407470703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.87526559829712</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.89197254180908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.02424335479736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.99639558792114</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.01380014419556</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.01728105545044</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.89893341064453</t>
   </si>
   <si>
     <t xml:space="preserve">6.92678070068359</t>
   </si>
   <si>
-    <t xml:space="preserve">7.04860830307007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.09037733078003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.00335788726807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.94348812103271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.07297325134277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.08689785003662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.00683784484863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.15303182601929</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.11126327514648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.10778141021729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.14259004592896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.26093721389771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.15999364852905</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.93652629852295</t>
+    <t xml:space="preserve">7.04860877990723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.09037780761719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.00335836410522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.94348907470703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.07297229766846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.08689737319946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.00683879852295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.15303230285645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.11126232147217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.10778093338013</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.14259099960327</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.26093626022339</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.15999412536621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.93652582168579</t>
   </si>
   <si>
     <t xml:space="preserve">6.95184230804443</t>
   </si>
   <si>
-    <t xml:space="preserve">6.94766473770142</t>
+    <t xml:space="preserve">6.94766569137573</t>
   </si>
   <si>
     <t xml:space="preserve">7.14607000350952</t>
   </si>
   <si>
-    <t xml:space="preserve">7.05208826065063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.13562774658203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.36536026000977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.37580299377441</t>
+    <t xml:space="preserve">7.05208873748779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.13562917709351</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.36536073684692</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.37580394744873</t>
   </si>
   <si>
     <t xml:space="preserve">7.47674512863159</t>
   </si>
   <si>
-    <t xml:space="preserve">7.36884069442749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.45238161087036</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.49414920806885</t>
+    <t xml:space="preserve">7.36884164810181</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.45237922668457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.49414825439453</t>
   </si>
   <si>
     <t xml:space="preserve">7.51851558685303</t>
   </si>
   <si>
-    <t xml:space="preserve">7.60553550720215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.62294054031372</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.65078592300415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.5602855682373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.59509181976318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.58116817474365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.57420825958252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.67863178253174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.7238826751709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.77609443664551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.65426683425903</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.54636240005493</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.63686370849609</t>
+    <t xml:space="preserve">7.60553646087646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.6229395866394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.65078544616699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.56028461456299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.59509325027466</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.58116960525513</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.57420873641968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.67863273620605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.72388410568237</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.77609395980835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.65426588058472</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.54636096954346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.63686323165894</t>
   </si>
   <si>
     <t xml:space="preserve">7.80045890808105</t>
   </si>
   <si>
-    <t xml:space="preserve">7.7378044128418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.75520992279053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.76913261413574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.81078052520752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.67665958404541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.7472505569458</t>
+    <t xml:space="preserve">7.73780536651611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.75520849227905</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.7691330909729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.81078147888184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.67666053771973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.74724960327148</t>
   </si>
   <si>
     <t xml:space="preserve">7.65195417404175</t>
@@ -2231,208 +2231,208 @@
     <t xml:space="preserve">7.71548509597778</t>
   </si>
   <si>
-    <t xml:space="preserve">7.73666191101074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.66607189178467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.61665773391724</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.50724458694458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.47547817230225</t>
+    <t xml:space="preserve">7.73666095733643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.66607046127319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.61666011810303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.50724363327026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.47547912597656</t>
   </si>
   <si>
     <t xml:space="preserve">7.23194360733032</t>
   </si>
   <si>
-    <t xml:space="preserve">7.30959272384644</t>
+    <t xml:space="preserve">7.30959177017212</t>
   </si>
   <si>
     <t xml:space="preserve">7.40488815307617</t>
   </si>
   <si>
-    <t xml:space="preserve">7.27076768875122</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.28135681152344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.18958854675293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.29194402694702</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.21076679229736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.33076906204224</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.17900085449219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.24253177642822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.17547130584717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.26723861694336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.36253499984741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.14370489120483</t>
+    <t xml:space="preserve">7.2707667350769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.28135538101196</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.18958806991577</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.29194641113281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.21076583862305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.33076953887939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.17900037765503</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.2425332069397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.17547035217285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.2672381401062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.3625340461731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.14370536804199</t>
   </si>
   <si>
     <t xml:space="preserve">7.19664812088013</t>
   </si>
   <si>
-    <t xml:space="preserve">7.10488033294678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.04346752166748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.22488451004028</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.12605857849121</t>
+    <t xml:space="preserve">7.10488080978394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.04346799850464</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.22488403320312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.12605810165405</t>
   </si>
   <si>
     <t xml:space="preserve">7.2390022277832</t>
   </si>
   <si>
-    <t xml:space="preserve">7.20723628997803</t>
+    <t xml:space="preserve">7.20723676681519</t>
   </si>
   <si>
     <t xml:space="preserve">7.16488313674927</t>
   </si>
   <si>
-    <t xml:space="preserve">7.10135173797607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.0907621383667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.26017904281616</t>
+    <t xml:space="preserve">7.10135316848755</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.09076261520386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.26018047332764</t>
   </si>
   <si>
     <t xml:space="preserve">7.32723999023438</t>
   </si>
   <si>
-    <t xml:space="preserve">7.34841632843018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.25311994552612</t>
+    <t xml:space="preserve">7.34841537475586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.25311899185181</t>
   </si>
   <si>
     <t xml:space="preserve">7.47194862365723</t>
   </si>
   <si>
-    <t xml:space="preserve">7.82137060165405</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.76136827468872</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.30606412887573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.41547822952271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.55665826797485</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.57077646255493</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.62018728256226</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.697838306427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.7896032333374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.75077867507935</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.72960376739502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.71901416778564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.00490283966064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.12490653991699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.9660792350769</t>
+    <t xml:space="preserve">7.82136964797974</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.7613673210144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.30606317520142</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.41547536849976</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.55665588378906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.5707745552063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.62018775939941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.69783592224121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.78960418701172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.75078010559082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.72960186004639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.71901559829712</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.00490379333496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.12490558624268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.96607875823975</t>
   </si>
   <si>
     <t xml:space="preserve">7.97313785552979</t>
   </si>
   <si>
-    <t xml:space="preserve">7.40841674804688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.29547452926636</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.44018411636353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.11899852752686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.7865195274353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.53804349899292</t>
+    <t xml:space="preserve">7.40841722488403</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.29547500610352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.44018363952637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.11899995803833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.78652143478394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.53804397583008</t>
   </si>
   <si>
     <t xml:space="preserve">6.79075574874878</t>
   </si>
   <si>
-    <t xml:space="preserve">6.8387565612793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.65804719924927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.86275625228882</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.97049999237061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.56107759475708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.56249046325684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.33704853057861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.76058769226074</t>
+    <t xml:space="preserve">6.83875608444214</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.65804576873779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.86275768280029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.97050094604492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.56107807159424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.56249094009399</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.33704805374146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.7605881690979</t>
   </si>
   <si>
     <t xml:space="preserve">4.58976030349731</t>
   </si>
   <si>
-    <t xml:space="preserve">4.58552408218384</t>
+    <t xml:space="preserve">4.58552503585815</t>
   </si>
   <si>
     <t xml:space="preserve">4.49658155441284</t>
@@ -2444,64 +2444,64 @@
     <t xml:space="preserve">4.89612054824829</t>
   </si>
   <si>
-    <t xml:space="preserve">5.0655369758606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.41142702102661</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.46083974838257</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.71637535095215</t>
+    <t xml:space="preserve">5.06553649902344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.41142749786377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.46084070205688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.71637582778931</t>
   </si>
   <si>
     <t xml:space="preserve">5.542724609375</t>
   </si>
   <si>
-    <t xml:space="preserve">5.58790254592896</t>
+    <t xml:space="preserve">5.58790302276611</t>
   </si>
   <si>
     <t xml:space="preserve">5.44954586029053</t>
   </si>
   <si>
-    <t xml:space="preserve">5.21801137924194</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.486252784729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.52719497680664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.67543363571167</t>
+    <t xml:space="preserve">5.21801090240479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.48625373840332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.52719449996948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.67543411254883</t>
   </si>
   <si>
     <t xml:space="preserve">5.7573184967041</t>
   </si>
   <si>
-    <t xml:space="preserve">5.84343814849854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.86320352554321</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.88720369338989</t>
+    <t xml:space="preserve">5.84343767166138</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.86320304870605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.88720464706421</t>
   </si>
   <si>
     <t xml:space="preserve">5.36907339096069</t>
   </si>
   <si>
-    <t xml:space="preserve">5.41283988952637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.43542814254761</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.37330961227417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.25895261764526</t>
+    <t xml:space="preserve">5.41283893585205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.43542766571045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.37330865859985</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.25895309448242</t>
   </si>
   <si>
     <t xml:space="preserve">5.34224939346313</t>
@@ -2510,7 +2510,7 @@
     <t xml:space="preserve">5.3069543838501</t>
   </si>
   <si>
-    <t xml:space="preserve">5.22224569320679</t>
+    <t xml:space="preserve">5.22224617004395</t>
   </si>
   <si>
     <t xml:space="preserve">5.56390190124512</t>
@@ -2519,19 +2519,19 @@
     <t xml:space="preserve">5.5540189743042</t>
   </si>
   <si>
-    <t xml:space="preserve">5.66837501525879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.47213554382324</t>
+    <t xml:space="preserve">5.66837549209595</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.47213506698608</t>
   </si>
   <si>
     <t xml:space="preserve">5.33942556381226</t>
   </si>
   <si>
-    <t xml:space="preserve">5.18836355209351</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.10224342346191</t>
+    <t xml:space="preserve">5.18836307525635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.10224390029907</t>
   </si>
   <si>
     <t xml:space="preserve">5.36060285568237</t>
@@ -2540,10 +2540,10 @@
     <t xml:space="preserve">5.47495889663696</t>
   </si>
   <si>
-    <t xml:space="preserve">5.25612926483154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.16012716293335</t>
+    <t xml:space="preserve">5.25613021850586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.16012763977051</t>
   </si>
   <si>
     <t xml:space="preserve">5.07259607315063</t>
@@ -2552,40 +2552,40 @@
     <t xml:space="preserve">5.2674241065979</t>
   </si>
   <si>
-    <t xml:space="preserve">5.22648143768311</t>
+    <t xml:space="preserve">5.22648191452026</t>
   </si>
   <si>
     <t xml:space="preserve">5.23495244979858</t>
   </si>
   <si>
-    <t xml:space="preserve">5.20248174667358</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.25330543518066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.46225214004517</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.54413652420044</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.5723729133606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.62319755554199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.68814039230347</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.86038017272949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.04814958572388</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.19074153900146</t>
+    <t xml:space="preserve">5.20248079299927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.25330591201782</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.46225261688232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.5441370010376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.57237243652344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.62319803237915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.68813943862915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.86037969589233</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.0481481552124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.19074058532715</t>
   </si>
   <si>
     <t xml:space="preserve">6.31921482086182</t>
@@ -2603,22 +2603,22 @@
     <t xml:space="preserve">5.82226085662842</t>
   </si>
   <si>
-    <t xml:space="preserve">5.87167358398438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.99026536941528</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.96344041824341</t>
+    <t xml:space="preserve">5.87167406082153</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.99026584625244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.96344137191772</t>
   </si>
   <si>
     <t xml:space="preserve">5.92108678817749</t>
   </si>
   <si>
-    <t xml:space="preserve">5.80249643325806</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.92205190658569</t>
+    <t xml:space="preserve">5.80249691009521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.92205238342285</t>
   </si>
   <si>
     <t xml:space="preserve">6.02327108383179</t>
@@ -2627,175 +2627,175 @@
     <t xml:space="preserve">5.75628709793091</t>
   </si>
   <si>
-    <t xml:space="preserve">5.79736185073853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.68147325515747</t>
+    <t xml:space="preserve">5.79736089706421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.68147277832031</t>
   </si>
   <si>
     <t xml:space="preserve">5.85457181930542</t>
   </si>
   <si>
-    <t xml:space="preserve">5.6770715713501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.68734121322632</t>
+    <t xml:space="preserve">5.67707300186157</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.68734073638916</t>
   </si>
   <si>
     <t xml:space="preserve">5.71227884292603</t>
   </si>
   <si>
-    <t xml:space="preserve">5.80469703674316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.77242374420166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.72694778442383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.59198951721191</t>
+    <t xml:space="preserve">5.80469655990601</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.7724232673645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.72694873809814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.59198999404907</t>
   </si>
   <si>
     <t xml:space="preserve">5.64039754867554</t>
   </si>
   <si>
-    <t xml:space="preserve">5.74748563766479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.72548151016235</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.75041913986206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.76655530929565</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.00420141220093</t>
+    <t xml:space="preserve">5.74748516082764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.7254810333252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.75041961669922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.76655578613281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.00420045852661</t>
   </si>
   <si>
     <t xml:space="preserve">6.04820919036865</t>
   </si>
   <si>
-    <t xml:space="preserve">6.10248613357544</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.00566720962524</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.97632932662964</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.82670068740845</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.7944278717041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.77975845336914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.58172082901001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.68587398529053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.79149389266968</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.83110046386719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.82963418960571</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.73868417739868</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.78415870666504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.88537883758545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.9792628288269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.97192811965942</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.90004825592041</t>
+    <t xml:space="preserve">6.10248565673828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.0056676864624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.97632884979248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.82670021057129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.79442739486694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.7797589302063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.58172130584717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.68587350845337</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.79149436950684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.8311014175415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.82963466644287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.73868370056152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.7841591835022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.88537788391113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.97926330566406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.97192859649658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.90004730224609</t>
   </si>
   <si>
     <t xml:space="preserve">5.87511014938354</t>
   </si>
   <si>
-    <t xml:space="preserve">5.78269243240356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.76362180709839</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.82376766204834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.72401475906372</t>
+    <t xml:space="preserve">5.78269195556641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.76362085342407</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.82376670837402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.72401428222656</t>
   </si>
   <si>
     <t xml:space="preserve">5.80176210403442</t>
   </si>
   <si>
-    <t xml:space="preserve">5.8208327293396</t>
+    <t xml:space="preserve">5.82083177566528</t>
   </si>
   <si>
     <t xml:space="preserve">5.75335359573364</t>
   </si>
   <si>
-    <t xml:space="preserve">5.7577543258667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.6726713180542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.63012981414795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.64186477661133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.83696889877319</t>
+    <t xml:space="preserve">5.75775337219238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.67267179489136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.63013029098511</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.64186573028564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.83696937561035</t>
   </si>
   <si>
     <t xml:space="preserve">5.71668004989624</t>
   </si>
   <si>
-    <t xml:space="preserve">5.85310554504395</t>
+    <t xml:space="preserve">5.85310506820679</t>
   </si>
   <si>
     <t xml:space="preserve">5.8428373336792</t>
   </si>
   <si>
-    <t xml:space="preserve">5.84577035903931</t>
+    <t xml:space="preserve">5.84577083587646</t>
   </si>
   <si>
     <t xml:space="preserve">5.81203079223633</t>
   </si>
   <si>
-    <t xml:space="preserve">5.69320869445801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.49517107009888</t>
+    <t xml:space="preserve">5.69320821762085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.49517154693604</t>
   </si>
   <si>
     <t xml:space="preserve">5.5729193687439</t>
   </si>
   <si>
-    <t xml:space="preserve">5.61839437484741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.60665941238403</t>
+    <t xml:space="preserve">5.61839485168457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.60665845870972</t>
   </si>
   <si>
     <t xml:space="preserve">5.56411743164062</t>
@@ -2804,19 +2804,19 @@
     <t xml:space="preserve">5.66973733901978</t>
   </si>
   <si>
-    <t xml:space="preserve">5.55678224563599</t>
+    <t xml:space="preserve">5.55678272247314</t>
   </si>
   <si>
     <t xml:space="preserve">5.5509147644043</t>
   </si>
   <si>
-    <t xml:space="preserve">5.509840965271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.5421142578125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.93232107162476</t>
+    <t xml:space="preserve">5.50984048843384</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.54211378097534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.9323205947876</t>
   </si>
   <si>
     <t xml:space="preserve">5.88097763061523</t>
@@ -2825,70 +2825,70 @@
     <t xml:space="preserve">5.87804317474365</t>
   </si>
   <si>
-    <t xml:space="preserve">5.87950944900513</t>
+    <t xml:space="preserve">5.87951040267944</t>
   </si>
   <si>
     <t xml:space="preserve">5.89271306991577</t>
   </si>
   <si>
-    <t xml:space="preserve">5.8941798210144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.59932374954224</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.66827058792114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.67560434341431</t>
+    <t xml:space="preserve">5.89418029785156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.59932470321655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.6682710647583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.67560577392578</t>
   </si>
   <si>
     <t xml:space="preserve">5.56998538970947</t>
   </si>
   <si>
-    <t xml:space="preserve">5.5787878036499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.56851863861084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.47903442382812</t>
+    <t xml:space="preserve">5.57878684997559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.56851816177368</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.47903490066528</t>
   </si>
   <si>
     <t xml:space="preserve">5.43942737579346</t>
   </si>
   <si>
-    <t xml:space="preserve">5.21058416366577</t>
+    <t xml:space="preserve">5.21058368682861</t>
   </si>
   <si>
     <t xml:space="preserve">5.14017105102539</t>
   </si>
   <si>
-    <t xml:space="preserve">5.13430309295654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.25752687454224</t>
+    <t xml:space="preserve">5.1343035697937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.25752639770508</t>
   </si>
   <si>
     <t xml:space="preserve">5.30740213394165</t>
   </si>
   <si>
-    <t xml:space="preserve">5.47463464736938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.65506839752197</t>
+    <t xml:space="preserve">5.47463369369507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.65506792068481</t>
   </si>
   <si>
     <t xml:space="preserve">5.56265068054199</t>
   </si>
   <si>
-    <t xml:space="preserve">5.75922155380249</t>
+    <t xml:space="preserve">5.75922107696533</t>
   </si>
   <si>
     <t xml:space="preserve">5.90151453018188</t>
   </si>
   <si>
-    <t xml:space="preserve">5.85897350311279</t>
+    <t xml:space="preserve">5.85897302627563</t>
   </si>
   <si>
     <t xml:space="preserve">6.03647327423096</t>
@@ -2897,64 +2897,64 @@
     <t xml:space="preserve">6.23744440078735</t>
   </si>
   <si>
-    <t xml:space="preserve">6.31812715530396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.42521381378174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.49415922164917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.39440774917603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.4282021522522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.57317733764648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.51040554046631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.57616662979126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.38485908508301</t>
+    <t xml:space="preserve">6.3181266784668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.42521333694458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.49416065216064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.39440822601318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.42820262908936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.57317686080933</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.51040506362915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.57616710662842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.38485860824585</t>
   </si>
   <si>
     <t xml:space="preserve">6.43567562103271</t>
   </si>
   <si>
-    <t xml:space="preserve">6.33254957199097</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.35496854782104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.28322839736938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.27276611328125</t>
+    <t xml:space="preserve">6.33254909515381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.35496759414673</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.28322887420654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.27276659011841</t>
   </si>
   <si>
     <t xml:space="preserve">6.28173351287842</t>
   </si>
   <si>
-    <t xml:space="preserve">6.2907018661499</t>
+    <t xml:space="preserve">6.29070138931274</t>
   </si>
   <si>
     <t xml:space="preserve">6.23988580703735</t>
   </si>
   <si>
-    <t xml:space="preserve">6.23540163040161</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.33553791046143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.26977682113647</t>
+    <t xml:space="preserve">6.23540210723877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.33553838729858</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.26977777481079</t>
   </si>
   <si>
     <t xml:space="preserve">6.24586343765259</t>
@@ -2963,31 +2963,31 @@
     <t xml:space="preserve">6.10238361358643</t>
   </si>
   <si>
-    <t xml:space="preserve">6.22792911529541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.25333738327026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.21746730804443</t>
+    <t xml:space="preserve">6.22792863845825</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.25333595275879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.21746683120728</t>
   </si>
   <si>
     <t xml:space="preserve">6.23390674591064</t>
   </si>
   <si>
-    <t xml:space="preserve">6.19355249404907</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.38186979293823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.51488924026489</t>
+    <t xml:space="preserve">6.19355392456055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.38187074661255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.51488971710205</t>
   </si>
   <si>
     <t xml:space="preserve">6.42222499847412</t>
   </si>
   <si>
-    <t xml:space="preserve">6.37738752365112</t>
+    <t xml:space="preserve">6.37738800048828</t>
   </si>
   <si>
     <t xml:space="preserve">6.30265808105469</t>
@@ -2996,7 +2996,7 @@
     <t xml:space="preserve">6.241379737854</t>
   </si>
   <si>
-    <t xml:space="preserve">6.26230382919312</t>
+    <t xml:space="preserve">6.26230430603027</t>
   </si>
   <si>
     <t xml:space="preserve">6.20999383926392</t>
@@ -3005,10 +3005,10 @@
     <t xml:space="preserve">6.27426052093506</t>
   </si>
   <si>
-    <t xml:space="preserve">6.21597194671631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.17860746383667</t>
+    <t xml:space="preserve">6.21597242355347</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.17860794067383</t>
   </si>
   <si>
     <t xml:space="preserve">6.13376998901367</t>
@@ -3017,133 +3017,133 @@
     <t xml:space="preserve">6.24885272979736</t>
   </si>
   <si>
-    <t xml:space="preserve">6.09789991378784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.15319967269897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.03512763977051</t>
+    <t xml:space="preserve">6.097900390625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.15320062637329</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.03512811660767</t>
   </si>
   <si>
     <t xml:space="preserve">6.19803619384766</t>
   </si>
   <si>
-    <t xml:space="preserve">6.18757438659668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.62847709655762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.73459243774414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.8900294303894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.06639003753662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.15158081054688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.10973215103149</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.21136474609375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.23228788375854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.30104064941406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.21285963058472</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.08582019805908</t>
+    <t xml:space="preserve">6.18757486343384</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.62847757339478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.7345929145813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.89002895355225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.06638956069946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.15158128738403</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.10973405838013</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.21136426925659</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.2322883605957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.30103826522827</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.21285915374756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.08582067489624</t>
   </si>
   <si>
     <t xml:space="preserve">6.95280122756958</t>
   </si>
   <si>
-    <t xml:space="preserve">7.02304697036743</t>
+    <t xml:space="preserve">7.02304649353027</t>
   </si>
   <si>
     <t xml:space="preserve">7.20688056945801</t>
   </si>
   <si>
-    <t xml:space="preserve">7.12019538879395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.13663530349731</t>
+    <t xml:space="preserve">7.1201958656311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.13663625717163</t>
   </si>
   <si>
     <t xml:space="preserve">7.1799783706665</t>
   </si>
   <si>
-    <t xml:space="preserve">7.02753067016602</t>
+    <t xml:space="preserve">7.02753162384033</t>
   </si>
   <si>
     <t xml:space="preserve">7.34438276290894</t>
   </si>
   <si>
-    <t xml:space="preserve">7.38025283813477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.43555164337158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.45348691940308</t>
+    <t xml:space="preserve">7.38025379180908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.43555212020874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.45348787307739</t>
   </si>
   <si>
     <t xml:space="preserve">7.3608226776123</t>
   </si>
   <si>
-    <t xml:space="preserve">7.50280809402466</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.57753610610962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.64479303359985</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.61116647720337</t>
+    <t xml:space="preserve">7.50280714035034</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.57753801345825</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.64479398727417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.61116456985474</t>
   </si>
   <si>
     <t xml:space="preserve">7.67842054367065</t>
   </si>
   <si>
-    <t xml:space="preserve">7.63358449935913</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.79798936843872</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.75688648223877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.81293487548828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.72699594497681</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.85029935836792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.78304243087769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.824143409729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.81667184829712</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.88392686843872</t>
+    <t xml:space="preserve">7.63358402252197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.79798889160156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.7568883895874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.81293392181396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.72699689865112</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.85029792785645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.78304147720337</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.82414436340332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.8166708946228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.88392543792725</t>
   </si>
   <si>
     <t xml:space="preserve">8.05580425262451</t>
@@ -3155,67 +3155,67 @@
     <t xml:space="preserve">8.10064220428467</t>
   </si>
   <si>
-    <t xml:space="preserve">8.15295219421387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.17537117004395</t>
+    <t xml:space="preserve">8.15295124053955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.17537021636963</t>
   </si>
   <si>
     <t xml:space="preserve">8.16416168212891</t>
   </si>
   <si>
-    <t xml:space="preserve">8.04833221435547</t>
+    <t xml:space="preserve">8.04833126068115</t>
   </si>
   <si>
     <t xml:space="preserve">8.06701374053955</t>
   </si>
   <si>
-    <t xml:space="preserve">8.05954074859619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.9698657989502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.96239280700684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.05206775665283</t>
+    <t xml:space="preserve">8.05953884124756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.96986532211304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.96239328384399</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.05206680297852</t>
   </si>
   <si>
     <t xml:space="preserve">8.04085826873779</t>
   </si>
   <si>
-    <t xml:space="preserve">7.93249988555908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.9287633895874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.10811519622803</t>
+    <t xml:space="preserve">7.93250226974487</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.92876434326172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.10811424255371</t>
   </si>
   <si>
     <t xml:space="preserve">8.07822322845459</t>
   </si>
   <si>
-    <t xml:space="preserve">8.08943176269531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.16042423248291</t>
+    <t xml:space="preserve">8.08943271636963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.16042518615723</t>
   </si>
   <si>
     <t xml:space="preserve">8.15668773651123</t>
   </si>
   <si>
-    <t xml:space="preserve">8.14547824859619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.2575740814209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.19779014587402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.16789722442627</t>
+    <t xml:space="preserve">8.14547920227051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.25757217407227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.19778919219971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.16789817810059</t>
   </si>
   <si>
     <t xml:space="preserve">8.22020816802979</t>
@@ -3224,64 +3224,64 @@
     <t xml:space="preserve">8.38834953308105</t>
   </si>
   <si>
-    <t xml:space="preserve">8.35098457336426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.24636459350586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.25009918212891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.3098840713501</t>
+    <t xml:space="preserve">8.35098552703857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.24636363983154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.25010108947754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.30988121032715</t>
   </si>
   <si>
     <t xml:space="preserve">8.43692302703857</t>
   </si>
   <si>
-    <t xml:space="preserve">8.42571449279785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.3920841217041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.4630765914917</t>
+    <t xml:space="preserve">8.42571353912354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.39208507537842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.46307849884033</t>
   </si>
   <si>
     <t xml:space="preserve">8.59385395050049</t>
   </si>
   <si>
-    <t xml:space="preserve">8.74331188201904</t>
+    <t xml:space="preserve">8.74331092834473</t>
   </si>
   <si>
     <t xml:space="preserve">8.62748241424561</t>
   </si>
   <si>
-    <t xml:space="preserve">8.53407096862793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.58638095855713</t>
+    <t xml:space="preserve">8.53407001495361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.58638286590576</t>
   </si>
   <si>
     <t xml:space="preserve">8.59758949279785</t>
   </si>
   <si>
-    <t xml:space="preserve">8.64242839813232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.81804180145264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.90024375915527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.01233863830566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.02728366851807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.95629024505615</t>
+    <t xml:space="preserve">8.64242744445801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.81804275512695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.90024280548096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.01233768463135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.02728462219238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.95629119873047</t>
   </si>
   <si>
     <t xml:space="preserve">8.97871017456055</t>
@@ -3290,58 +3290,58 @@
     <t xml:space="preserve">8.95255374908447</t>
   </si>
   <si>
-    <t xml:space="preserve">9.01981067657471</t>
+    <t xml:space="preserve">9.01980972290039</t>
   </si>
   <si>
     <t xml:space="preserve">8.96376323699951</t>
   </si>
   <si>
-    <t xml:space="preserve">8.73957633972168</t>
+    <t xml:space="preserve">8.73957538604736</t>
   </si>
   <si>
     <t xml:space="preserve">8.85025215148926</t>
   </si>
   <si>
-    <t xml:space="preserve">8.73112201690674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.62736320495605</t>
+    <t xml:space="preserve">8.73112010955811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.62736225128174</t>
   </si>
   <si>
     <t xml:space="preserve">8.78107929229736</t>
   </si>
   <si>
-    <t xml:space="preserve">8.75418090820312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.6119909286499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.57356071472168</t>
+    <t xml:space="preserve">8.75417995452881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.61199188232422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.573561668396</t>
   </si>
   <si>
     <t xml:space="preserve">8.56971836090088</t>
   </si>
   <si>
-    <t xml:space="preserve">8.66963291168213</t>
+    <t xml:space="preserve">8.66963481903076</t>
   </si>
   <si>
     <t xml:space="preserve">8.59277629852295</t>
   </si>
   <si>
-    <t xml:space="preserve">8.71574878692627</t>
+    <t xml:space="preserve">8.71574974060059</t>
   </si>
   <si>
     <t xml:space="preserve">8.58508968353271</t>
   </si>
   <si>
-    <t xml:space="preserve">8.61967754364014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.31992816925049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.45058727264404</t>
+    <t xml:space="preserve">8.6196756362915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.3199291229248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.45058822631836</t>
   </si>
   <si>
     <t xml:space="preserve">8.48133087158203</t>
@@ -3359,46 +3359,46 @@
     <t xml:space="preserve">8.35835838317871</t>
   </si>
   <si>
-    <t xml:space="preserve">8.07398223876953</t>
+    <t xml:space="preserve">8.0739803314209</t>
   </si>
   <si>
     <t xml:space="preserve">8.15468215942383</t>
   </si>
   <si>
-    <t xml:space="preserve">8.41215801239014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.53897571563721</t>
+    <t xml:space="preserve">8.41215896606445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.53897476196289</t>
   </si>
   <si>
     <t xml:space="preserve">8.61583423614502</t>
   </si>
   <si>
-    <t xml:space="preserve">8.68500518798828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.60046195983887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.58124732971191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.55050373077393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.72727870941162</t>
+    <t xml:space="preserve">8.68500709533691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.60046100616455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.5812463760376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.55050468444824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.72727680206299</t>
   </si>
   <si>
     <t xml:space="preserve">8.85793781280518</t>
   </si>
   <si>
-    <t xml:space="preserve">8.90020942687988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.93479633331299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.00781059265137</t>
+    <t xml:space="preserve">8.9002103805542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.9347972869873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.00781154632568</t>
   </si>
   <si>
     <t xml:space="preserve">9.02702522277832</t>
@@ -3407,22 +3407,22 @@
     <t xml:space="preserve">8.98091220855713</t>
   </si>
   <si>
-    <t xml:space="preserve">8.92326736450195</t>
+    <t xml:space="preserve">8.92326641082764</t>
   </si>
   <si>
     <t xml:space="preserve">8.87330913543701</t>
   </si>
   <si>
-    <t xml:space="preserve">8.94632530212402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.83487987518311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.76955127716064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.96169662475586</t>
+    <t xml:space="preserve">8.94632434844971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.83487892150879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.76954936981201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.96169567108154</t>
   </si>
   <si>
     <t xml:space="preserve">8.93863964080811</t>
@@ -3431,46 +3431,46 @@
     <t xml:space="preserve">8.9078950881958</t>
   </si>
   <si>
-    <t xml:space="preserve">8.82719326019287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.86562442779541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.91174030303955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.94248199462891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.80797863006592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.86946678161621</t>
+    <t xml:space="preserve">8.82719421386719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.86562347412109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.91173934936523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.94248294830322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.80798053741455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.86946773529053</t>
   </si>
   <si>
     <t xml:space="preserve">8.88483905792236</t>
   </si>
   <si>
-    <t xml:space="preserve">8.96553993225098</t>
+    <t xml:space="preserve">8.96553897857666</t>
   </si>
   <si>
     <t xml:space="preserve">9.10772800445557</t>
   </si>
   <si>
-    <t xml:space="preserve">9.02318286895752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.05776977539062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.13847064971924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.20380210876465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.16921615600586</t>
+    <t xml:space="preserve">9.02318382263184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.05776882171631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.13847160339355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.20380115509033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.16921520233154</t>
   </si>
   <si>
     <t xml:space="preserve">9.25375843048096</t>
@@ -3479,7 +3479,7 @@
     <t xml:space="preserve">9.03086948394775</t>
   </si>
   <si>
-    <t xml:space="preserve">9.09235668182373</t>
+    <t xml:space="preserve">9.09235572814941</t>
   </si>
   <si>
     <t xml:space="preserve">9.14999961853027</t>
@@ -3488,25 +3488,25 @@
     <t xml:space="preserve">9.11157035827637</t>
   </si>
   <si>
-    <t xml:space="preserve">9.29603004455566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.24222946166992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.35751819610596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.36136054992676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.34598827362061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.46896266937256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.50354957580566</t>
+    <t xml:space="preserve">9.29603099822998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.24222850799561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.35751914978027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.36136150360107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.34598731994629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.46896362304688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.50354862213135</t>
   </si>
   <si>
     <t xml:space="preserve">9.60730743408203</t>
@@ -3515,13 +3515,13 @@
     <t xml:space="preserve">9.54966449737549</t>
   </si>
   <si>
-    <t xml:space="preserve">9.5189208984375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.41516208648682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.64958095550537</t>
+    <t xml:space="preserve">9.51891994476318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.4151611328125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.64958000183105</t>
   </si>
   <si>
     <t xml:space="preserve">9.61499404907227</t>
@@ -3530,10 +3530,10 @@
     <t xml:space="preserve">9.59577941894531</t>
   </si>
   <si>
-    <t xml:space="preserve">9.74181079864502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.65726566314697</t>
+    <t xml:space="preserve">9.74181175231934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.65726470947266</t>
   </si>
   <si>
     <t xml:space="preserve">9.64189434051514</t>
@@ -3545,25 +3545,25 @@
     <t xml:space="preserve">9.56503486633301</t>
   </si>
   <si>
-    <t xml:space="preserve">9.53044891357422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.64573669433594</t>
+    <t xml:space="preserve">9.53044986724854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.64573764801025</t>
   </si>
   <si>
     <t xml:space="preserve">9.57656478881836</t>
   </si>
   <si>
-    <t xml:space="preserve">9.60346508026123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.56119155883789</t>
+    <t xml:space="preserve">9.60346603393555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.56119251251221</t>
   </si>
   <si>
     <t xml:space="preserve">9.46511840820312</t>
   </si>
   <si>
-    <t xml:space="preserve">9.4113187789917</t>
+    <t xml:space="preserve">9.41131782531738</t>
   </si>
   <si>
     <t xml:space="preserve">9.42284870147705</t>
@@ -3572,13 +3572,13 @@
     <t xml:space="preserve">9.3344612121582</t>
   </si>
   <si>
-    <t xml:space="preserve">9.27297401428223</t>
+    <t xml:space="preserve">9.27297210693359</t>
   </si>
   <si>
     <t xml:space="preserve">9.25345897674561</t>
   </si>
   <si>
-    <t xml:space="preserve">9.17930603027344</t>
+    <t xml:space="preserve">9.17930698394775</t>
   </si>
   <si>
     <t xml:space="preserve">9.15198802947998</t>
@@ -3590,31 +3590,31 @@
     <t xml:space="preserve">8.64462757110596</t>
   </si>
   <si>
-    <t xml:space="preserve">8.73829460144043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.69536399841309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.85928058624268</t>
+    <t xml:space="preserve">8.73829364776611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.69536304473877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.85928153991699</t>
   </si>
   <si>
     <t xml:space="preserve">8.7656135559082</t>
   </si>
   <si>
-    <t xml:space="preserve">8.69926643371582</t>
+    <t xml:space="preserve">8.69926738739014</t>
   </si>
   <si>
     <t xml:space="preserve">8.73048877716064</t>
   </si>
   <si>
-    <t xml:space="preserve">8.85147380828857</t>
+    <t xml:space="preserve">8.85147571563721</t>
   </si>
   <si>
     <t xml:space="preserve">8.72658634185791</t>
   </si>
   <si>
-    <t xml:space="preserve">8.66414260864258</t>
+    <t xml:space="preserve">8.66414165496826</t>
   </si>
   <si>
     <t xml:space="preserve">8.62511348724365</t>
@@ -3626,25 +3626,25 @@
     <t xml:space="preserve">8.64853096008301</t>
   </si>
   <si>
-    <t xml:space="preserve">8.68755912780762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.75000190734863</t>
+    <t xml:space="preserve">8.68755722045898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.75000286102295</t>
   </si>
   <si>
     <t xml:space="preserve">8.76171112060547</t>
   </si>
   <si>
-    <t xml:space="preserve">8.56267070770264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.70316982269287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.78903102874756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.86708354949951</t>
+    <t xml:space="preserve">8.562668800354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.70316791534424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.78903198242188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.86708545684814</t>
   </si>
   <si>
     <t xml:space="preserve">8.94514083862305</t>
@@ -3653,28 +3653,28 @@
     <t xml:space="preserve">9.01929378509521</t>
   </si>
   <si>
-    <t xml:space="preserve">8.99977970123291</t>
+    <t xml:space="preserve">8.99978065490723</t>
   </si>
   <si>
     <t xml:space="preserve">9.0075855255127</t>
   </si>
   <si>
-    <t xml:space="preserve">9.13637638092041</t>
+    <t xml:space="preserve">9.13637733459473</t>
   </si>
   <si>
     <t xml:space="preserve">9.14808464050293</t>
   </si>
   <si>
-    <t xml:space="preserve">9.1832103729248</t>
+    <t xml:space="preserve">9.18321132659912</t>
   </si>
   <si>
     <t xml:space="preserve">9.1051549911499</t>
   </si>
   <si>
-    <t xml:space="preserve">9.13247394561768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.15979290008545</t>
+    <t xml:space="preserve">9.13247299194336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.15979385375977</t>
   </si>
   <si>
     <t xml:space="preserve">9.09734916687012</t>
@@ -3683,19 +3683,19 @@
     <t xml:space="preserve">9.05441951751709</t>
   </si>
   <si>
-    <t xml:space="preserve">9.06222343444824</t>
+    <t xml:space="preserve">9.06222438812256</t>
   </si>
   <si>
     <t xml:space="preserve">9.02709865570068</t>
   </si>
   <si>
-    <t xml:space="preserve">9.0466136932373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.12076473236084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.96465396881104</t>
+    <t xml:space="preserve">9.04661273956299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.12076663970947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.96465587615967</t>
   </si>
   <si>
     <t xml:space="preserve">8.60559940338135</t>
@@ -3707,25 +3707,25 @@
     <t xml:space="preserve">9.01148796081543</t>
   </si>
   <si>
-    <t xml:space="preserve">8.9022102355957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.31200122833252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.31980514526367</t>
+    <t xml:space="preserve">8.90221118927002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.31200218200684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.31980609893799</t>
   </si>
   <si>
     <t xml:space="preserve">8.50022602081299</t>
   </si>
   <si>
-    <t xml:space="preserve">8.55486488342285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.59389305114746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.4260721206665</t>
+    <t xml:space="preserve">8.55486392974854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.59389209747314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.42607307434082</t>
   </si>
   <si>
     <t xml:space="preserve">8.58218288421631</t>
@@ -3737,76 +3737,76 @@
     <t xml:space="preserve">8.69146060943604</t>
   </si>
   <si>
-    <t xml:space="preserve">8.61340522766113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.40265655517578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.37143516540527</t>
+    <t xml:space="preserve">8.61340618133545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.4026575088501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.37143421173096</t>
   </si>
   <si>
     <t xml:space="preserve">8.30118465423584</t>
   </si>
   <si>
-    <t xml:space="preserve">7.836754322052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.09433746337891</t>
+    <t xml:space="preserve">7.83675527572632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.09433841705322</t>
   </si>
   <si>
     <t xml:space="preserve">8.02018451690674</t>
   </si>
   <si>
-    <t xml:space="preserve">7.69625520706177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.68376684188843</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.57605028152466</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.08742427825928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.93443536758423</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.25602340698242</t>
+    <t xml:space="preserve">7.69625616073608</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.68376588821411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.57605075836182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.08742380142212</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.93443489074707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.25602293014526</t>
   </si>
   <si>
     <t xml:space="preserve">7.89919948577881</t>
   </si>
   <si>
-    <t xml:space="preserve">7.49955606460571</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.54482746124268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.74933290481567</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.70718288421631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.0553092956543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.88749122619629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.86407518386841</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.89529609680176</t>
+    <t xml:space="preserve">7.49955654144287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.54482841491699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.74933338165283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.70718336105347</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.05531024932861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.88748979568481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.86407423019409</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.89529657363892</t>
   </si>
   <si>
     <t xml:space="preserve">8.10214424133301</t>
   </si>
   <si>
-    <t xml:space="preserve">8.09043598175049</t>
+    <t xml:space="preserve">8.09043502807617</t>
   </si>
   <si>
     <t xml:space="preserve">8.23483657836914</t>
@@ -3818,34 +3818,34 @@
     <t xml:space="preserve">8.21922588348389</t>
   </si>
   <si>
-    <t xml:space="preserve">8.289475440979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.25434970855713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.11775493621826</t>
+    <t xml:space="preserve">8.28947734832764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.25435066223145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.11775398254395</t>
   </si>
   <si>
     <t xml:space="preserve">7.99676895141602</t>
   </si>
   <si>
-    <t xml:space="preserve">7.8250470161438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.70562314987183</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.85626840591431</t>
+    <t xml:space="preserve">7.82504653930664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.70562219619751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.85626983642578</t>
   </si>
   <si>
     <t xml:space="preserve">7.79304456710815</t>
   </si>
   <si>
-    <t xml:space="preserve">7.67596101760864</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.5979061126709</t>
+    <t xml:space="preserve">7.67596054077148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.59790754318237</t>
   </si>
   <si>
     <t xml:space="preserve">7.65878915786743</t>
@@ -3854,19 +3854,19 @@
     <t xml:space="preserve">7.53546190261841</t>
   </si>
   <si>
-    <t xml:space="preserve">7.73372220993042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.70874500274658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.57292747497559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.35905694961548</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.26070737838745</t>
+    <t xml:space="preserve">7.73372268676758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.7087459564209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.5729284286499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.35905647277832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.26070690155029</t>
   </si>
   <si>
     <t xml:space="preserve">7.2372899055481</t>
@@ -3875,133 +3875,133 @@
     <t xml:space="preserve">7.28412342071533</t>
   </si>
   <si>
-    <t xml:space="preserve">7.32002878189087</t>
+    <t xml:space="preserve">7.32002925872803</t>
   </si>
   <si>
     <t xml:space="preserve">7.24665689468384</t>
   </si>
   <si>
-    <t xml:space="preserve">7.18889713287354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.13269567489624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.02654123306274</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.84389019012451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.00624561309814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.16860151290894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.3934006690979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.54795026779175</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.44179487228394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.51204442977905</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.46677398681641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.44023370742798</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.4183783531189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.56356000900269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.43555068969727</t>
+    <t xml:space="preserve">7.1888952255249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.13269519805908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.02654075622559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.84389114379883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.0062460899353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.16860198974609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.39340114593506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.54795074462891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.44179534912109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.51204395294189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.46677303314209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.44023418426514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.41837787628174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.56356143951416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.43555116653442</t>
   </si>
   <si>
     <t xml:space="preserve">7.55887794494629</t>
   </si>
   <si>
-    <t xml:space="preserve">7.61195659637451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.75245475769043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.92261648178101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.82114458084106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.8172402381897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.74308919906616</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.89139366149902</t>
+    <t xml:space="preserve">7.6119556427002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.75245571136475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.92261600494385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.82114553451538</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.81724119186401</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.743088722229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.89139461517334</t>
   </si>
   <si>
     <t xml:space="preserve">7.87578296661377</t>
   </si>
   <si>
-    <t xml:space="preserve">7.76650524139404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.14362478256226</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.90477418899536</t>
+    <t xml:space="preserve">7.76650619506836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.14362382888794</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.90477466583252</t>
   </si>
   <si>
     <t xml:space="preserve">7.11708498001099</t>
   </si>
   <si>
-    <t xml:space="preserve">7.35125160217285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.98595190048218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.02185869216919</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.18777942657471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.12729549407959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.15998983383179</t>
+    <t xml:space="preserve">7.35125207901001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.98595142364502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.02185821533203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.18777894973755</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.12729597091675</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.15998935699463</t>
   </si>
   <si>
     <t xml:space="preserve">7.10441064834595</t>
   </si>
   <si>
-    <t xml:space="preserve">7.31201696395874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.27605390548706</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.42154169082642</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.36596250534058</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.28422594070435</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.2874960899353</t>
+    <t xml:space="preserve">7.3120174407959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.2760534286499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.42154121398926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.3659610748291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.2842264175415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.28749656677246</t>
   </si>
   <si>
     <t xml:space="preserve">7.28095817565918</t>
@@ -4010,31 +4010,31 @@
     <t xml:space="preserve">6.98834657669067</t>
   </si>
   <si>
-    <t xml:space="preserve">7.03248262405396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.21393537521362</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.10114002227783</t>
+    <t xml:space="preserve">7.03248310089111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.21393585205078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.10114049911499</t>
   </si>
   <si>
     <t xml:space="preserve">6.96709489822388</t>
   </si>
   <si>
-    <t xml:space="preserve">6.9981541633606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.85103130340576</t>
+    <t xml:space="preserve">6.99815464019775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.8510308265686</t>
   </si>
   <si>
     <t xml:space="preserve">6.5028395652771</t>
   </si>
   <si>
-    <t xml:space="preserve">6.66794443130493</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.79381704330444</t>
+    <t xml:space="preserve">6.66794490814209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.7938175201416</t>
   </si>
   <si>
     <t xml:space="preserve">7.01940536499023</t>
@@ -4046,67 +4046,67 @@
     <t xml:space="preserve">6.52899503707886</t>
   </si>
   <si>
-    <t xml:space="preserve">6.61563444137573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.64342451095581</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.62871170043945</t>
+    <t xml:space="preserve">6.61563396453857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.64342403411865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.62871122360229</t>
   </si>
   <si>
     <t xml:space="preserve">6.64015436172485</t>
   </si>
   <si>
-    <t xml:space="preserve">6.58457517623901</t>
+    <t xml:space="preserve">6.58457469940186</t>
   </si>
   <si>
     <t xml:space="preserve">6.67775297164917</t>
   </si>
   <si>
-    <t xml:space="preserve">6.74314022064209</t>
+    <t xml:space="preserve">6.74314117431641</t>
   </si>
   <si>
     <t xml:space="preserve">6.66140556335449</t>
   </si>
   <si>
-    <t xml:space="preserve">6.77419996261597</t>
+    <t xml:space="preserve">6.77420043945312</t>
   </si>
   <si>
     <t xml:space="preserve">6.85266590118408</t>
   </si>
   <si>
-    <t xml:space="preserve">6.92949676513672</t>
+    <t xml:space="preserve">6.92949628829956</t>
   </si>
   <si>
     <t xml:space="preserve">6.86574268341064</t>
   </si>
   <si>
-    <t xml:space="preserve">6.8281455039978</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.8690128326416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.97036361694336</t>
+    <t xml:space="preserve">6.82814502716064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.86901235580444</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.97036409378052</t>
   </si>
   <si>
     <t xml:space="preserve">6.97690343856812</t>
   </si>
   <si>
-    <t xml:space="preserve">6.918053150177</t>
+    <t xml:space="preserve">6.91805362701416</t>
   </si>
   <si>
     <t xml:space="preserve">6.82651090621948</t>
   </si>
   <si>
-    <t xml:space="preserve">6.70227336883545</t>
+    <t xml:space="preserve">6.70227241516113</t>
   </si>
   <si>
     <t xml:space="preserve">6.53226470947266</t>
   </si>
   <si>
-    <t xml:space="preserve">6.63198137283325</t>
+    <t xml:space="preserve">6.63198184967041</t>
   </si>
   <si>
     <t xml:space="preserve">6.59928750991821</t>
@@ -4115,10 +4115,10 @@
     <t xml:space="preserve">6.57803630828857</t>
   </si>
   <si>
-    <t xml:space="preserve">6.42927837371826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.34754323959351</t>
+    <t xml:space="preserve">6.42927885055542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.34754276275635</t>
   </si>
   <si>
     <t xml:space="preserve">6.4946665763855</t>
@@ -4127,10 +4127,10 @@
     <t xml:space="preserve">6.44562530517578</t>
   </si>
   <si>
-    <t xml:space="preserve">6.62053871154785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.44889450073242</t>
+    <t xml:space="preserve">6.62053918838501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.44889497756958</t>
   </si>
   <si>
     <t xml:space="preserve">6.52245616912842</t>
@@ -4139,16 +4139,16 @@
     <t xml:space="preserve">6.54043769836426</t>
   </si>
   <si>
-    <t xml:space="preserve">6.60909605026245</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.71044683456421</t>
+    <t xml:space="preserve">6.60909557342529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.71044731140137</t>
   </si>
   <si>
     <t xml:space="preserve">6.80035495758057</t>
   </si>
   <si>
-    <t xml:space="preserve">6.81343364715576</t>
+    <t xml:space="preserve">6.8134331703186</t>
   </si>
   <si>
     <t xml:space="preserve">6.86737871170044</t>
@@ -4160,13 +4160,13 @@
     <t xml:space="preserve">6.79054689407349</t>
   </si>
   <si>
-    <t xml:space="preserve">6.64832782745361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.64505910873413</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.45379829406738</t>
+    <t xml:space="preserve">6.64832830429077</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.64505863189697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.45379877090454</t>
   </si>
   <si>
     <t xml:space="preserve">6.51918697357178</t>
@@ -4184,13 +4184,13 @@
     <t xml:space="preserve">6.36715984344482</t>
   </si>
   <si>
-    <t xml:space="preserve">6.49793529510498</t>
+    <t xml:space="preserve">6.49793577194214</t>
   </si>
   <si>
     <t xml:space="preserve">6.68919563293457</t>
   </si>
   <si>
-    <t xml:space="preserve">6.59274816513062</t>
+    <t xml:space="preserve">6.59274864196777</t>
   </si>
   <si>
     <t xml:space="preserve">6.48158884048462</t>
@@ -4205,28 +4205,28 @@
     <t xml:space="preserve">6.26090383529663</t>
   </si>
   <si>
-    <t xml:space="preserve">6.36388969421387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.46033763885498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.62217330932617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.86247396469116</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.82487630844116</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.80198907852173</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.73660230636597</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.89189863204956</t>
+    <t xml:space="preserve">6.36389017105103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.46033716201782</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.62217283248901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.86247444152832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.824875831604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.80198955535889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.73660182952881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.89189910888672</t>
   </si>
   <si>
     <t xml:space="preserve">6.95565223693848</t>
@@ -4238,142 +4238,142 @@
     <t xml:space="preserve">7.22701263427734</t>
   </si>
   <si>
-    <t xml:space="preserve">7.17143201828003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.20903062820435</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.23028135299683</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.19268417358398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.14854764938354</t>
+    <t xml:space="preserve">7.17143249511719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.20903015136719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.23028182983398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.19268465042114</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.14854669570923</t>
   </si>
   <si>
     <t xml:space="preserve">7.37740516662598</t>
   </si>
   <si>
-    <t xml:space="preserve">7.50327730178833</t>
+    <t xml:space="preserve">7.50327634811401</t>
   </si>
   <si>
     <t xml:space="preserve">7.54904842376709</t>
   </si>
   <si>
-    <t xml:space="preserve">7.64222621917725</t>
+    <t xml:space="preserve">7.6422266960144</t>
   </si>
   <si>
     <t xml:space="preserve">7.97243595123291</t>
   </si>
   <si>
-    <t xml:space="preserve">7.87762403488159</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.93156909942627</t>
+    <t xml:space="preserve">7.87762212753296</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.93156814575195</t>
   </si>
   <si>
     <t xml:space="preserve">7.96099233627319</t>
   </si>
   <si>
-    <t xml:space="preserve">7.86618041992188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.81223440170288</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.84983348846436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.81473779678345</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.77796936035156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.85819053649902</t>
+    <t xml:space="preserve">7.86617946624756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.81223487854004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.84983253479004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.81473636627197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.77796840667725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.85819101333618</t>
   </si>
   <si>
     <t xml:space="preserve">7.75624322891235</t>
   </si>
   <si>
-    <t xml:space="preserve">7.89328575134277</t>
+    <t xml:space="preserve">7.89328622817993</t>
   </si>
   <si>
     <t xml:space="preserve">7.80303859710693</t>
   </si>
   <si>
-    <t xml:space="preserve">7.87323141098022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.84314823150635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.89662790298462</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.87657260894775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.80972290039062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.90498399734497</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.76292991638184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.83479309082031</t>
+    <t xml:space="preserve">7.87323045730591</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.84314775466919</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.89662837982178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.87657308578491</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.80972385406494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.90498447418213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.76292848587036</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.83479261398315</t>
   </si>
   <si>
     <t xml:space="preserve">7.83646392822266</t>
   </si>
   <si>
-    <t xml:space="preserve">7.93172407150269</t>
+    <t xml:space="preserve">7.93172454833984</t>
   </si>
   <si>
     <t xml:space="preserve">7.9333963394165</t>
   </si>
   <si>
-    <t xml:space="preserve">7.51892709732056</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.56070804595947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.56739377975464</t>
+    <t xml:space="preserve">7.51892757415771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.56070899963379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.56739234924316</t>
   </si>
   <si>
     <t xml:space="preserve">7.69775009155273</t>
   </si>
   <si>
-    <t xml:space="preserve">7.76125717163086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.69607925415039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.70443439483643</t>
+    <t xml:space="preserve">7.76125764846802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.69607830047607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.70443534851074</t>
   </si>
   <si>
     <t xml:space="preserve">7.71446323394775</t>
   </si>
   <si>
-    <t xml:space="preserve">7.64427137374878</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.72950267791748</t>
+    <t xml:space="preserve">7.64426946640015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.72950410842896</t>
   </si>
   <si>
     <t xml:space="preserve">7.62588691711426</t>
   </si>
   <si>
-    <t xml:space="preserve">7.86487531661987</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.06041049957275</t>
+    <t xml:space="preserve">7.86487436294556</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.06040954589844</t>
   </si>
   <si>
     <t xml:space="preserve">7.94843673706055</t>
@@ -4388,25 +4388,25 @@
     <t xml:space="preserve">8.10553359985352</t>
   </si>
   <si>
-    <t xml:space="preserve">8.0353422164917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.10887718200684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.13060283660889</t>
+    <t xml:space="preserve">8.03534126281738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.10887622833252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.13060188293457</t>
   </si>
   <si>
     <t xml:space="preserve">8.17572593688965</t>
   </si>
   <si>
-    <t xml:space="preserve">8.1239185333252</t>
+    <t xml:space="preserve">8.12391757965088</t>
   </si>
   <si>
     <t xml:space="preserve">8.16068458557129</t>
   </si>
   <si>
-    <t xml:space="preserve">7.98186111450195</t>
+    <t xml:space="preserve">7.98186159133911</t>
   </si>
   <si>
     <t xml:space="preserve">8.00693035125732</t>
@@ -4415,10 +4415,10 @@
     <t xml:space="preserve">8.04536914825439</t>
   </si>
   <si>
-    <t xml:space="preserve">8.05372524261475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.16904163360596</t>
+    <t xml:space="preserve">8.05372428894043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.16904067993164</t>
   </si>
   <si>
     <t xml:space="preserve">8.14230155944824</t>
@@ -4430,7 +4430,7 @@
     <t xml:space="preserve">8.20246601104736</t>
   </si>
   <si>
-    <t xml:space="preserve">8.51498794555664</t>
+    <t xml:space="preserve">8.51498889923096</t>
   </si>
   <si>
     <t xml:space="preserve">8.42306995391846</t>
@@ -4442,7 +4442,7 @@
     <t xml:space="preserve">8.43978214263916</t>
   </si>
   <si>
-    <t xml:space="preserve">8.57348346710205</t>
+    <t xml:space="preserve">8.57348251342773</t>
   </si>
   <si>
     <t xml:space="preserve">8.39800262451172</t>
@@ -4451,7 +4451,7 @@
     <t xml:space="preserve">8.51916599273682</t>
   </si>
   <si>
-    <t xml:space="preserve">8.4732084274292</t>
+    <t xml:space="preserve">8.47320747375488</t>
   </si>
   <si>
     <t xml:space="preserve">8.54841327667236</t>
@@ -4463,28 +4463,28 @@
     <t xml:space="preserve">8.2793436050415</t>
   </si>
   <si>
-    <t xml:space="preserve">8.33783721923828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.23589038848877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.35287952423096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.52334499359131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.39382362365723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.38964653015137</t>
+    <t xml:space="preserve">8.33783531188965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.23589134216309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.35287857055664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.52334594726562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.39382266998291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.38964557647705</t>
   </si>
   <si>
     <t xml:space="preserve">8.46485137939453</t>
   </si>
   <si>
-    <t xml:space="preserve">8.61944198608398</t>
+    <t xml:space="preserve">8.61944103240967</t>
   </si>
   <si>
     <t xml:space="preserve">8.56512546539307</t>
@@ -4496,37 +4496,37 @@
     <t xml:space="preserve">8.48156356811523</t>
   </si>
   <si>
-    <t xml:space="preserve">8.34619426727295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.00860118865967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.13561534881592</t>
+    <t xml:space="preserve">8.34619235992432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.00860214233398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.13561630249023</t>
   </si>
   <si>
     <t xml:space="preserve">7.74287462234497</t>
   </si>
   <si>
-    <t xml:space="preserve">7.53062629699707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.60917329788208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.8682165145874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.81640863418579</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.83144998550415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.68437910079956</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.82476472854614</t>
+    <t xml:space="preserve">7.5306248664856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.6091742515564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.86821699142456</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.81640720367432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.83144950866699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.68438053131104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.8247652053833</t>
   </si>
   <si>
     <t xml:space="preserve">7.95010757446289</t>
@@ -4535,22 +4535,22 @@
     <t xml:space="preserve">7.86320352554321</t>
   </si>
   <si>
-    <t xml:space="preserve">7.79301071166992</t>
+    <t xml:space="preserve">7.79301166534424</t>
   </si>
   <si>
     <t xml:space="preserve">7.63257122039795</t>
   </si>
   <si>
-    <t xml:space="preserve">7.72281837463379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.8130669593811</t>
+    <t xml:space="preserve">7.72281885147095</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.81306648254395</t>
   </si>
   <si>
     <t xml:space="preserve">7.84649133682251</t>
   </si>
   <si>
-    <t xml:space="preserve">7.97517681121826</t>
+    <t xml:space="preserve">7.97517728805542</t>
   </si>
   <si>
     <t xml:space="preserve">7.85484647750854</t>
@@ -4559,67 +4559,67 @@
     <t xml:space="preserve">7.90832710266113</t>
   </si>
   <si>
-    <t xml:space="preserve">7.99188995361328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.91334009170532</t>
+    <t xml:space="preserve">7.99188947677612</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.9133415222168</t>
   </si>
   <si>
     <t xml:space="preserve">8.00525951385498</t>
   </si>
   <si>
-    <t xml:space="preserve">7.92838144302368</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.86988925933838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.95846462249756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.68939399719238</t>
+    <t xml:space="preserve">7.92838096618652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.86988973617554</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.9584641456604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.68939304351807</t>
   </si>
   <si>
     <t xml:space="preserve">7.75791501998901</t>
   </si>
   <si>
-    <t xml:space="preserve">7.67268180847168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.91835498809814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.9567928314209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.04035377502441</t>
+    <t xml:space="preserve">7.67268085479736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.91835403442383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.95679330825806</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.04035568237305</t>
   </si>
   <si>
     <t xml:space="preserve">7.94175148010254</t>
   </si>
   <si>
-    <t xml:space="preserve">8.02531433105469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.09717655181885</t>
+    <t xml:space="preserve">8.02531337738037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.09717750549316</t>
   </si>
   <si>
     <t xml:space="preserve">8.04703998565674</t>
   </si>
   <si>
-    <t xml:space="preserve">8.0955057144165</t>
+    <t xml:space="preserve">8.09550666809082</t>
   </si>
   <si>
     <t xml:space="preserve">8.06876659393311</t>
   </si>
   <si>
-    <t xml:space="preserve">8.29772663116455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.27432918548584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.08715057373047</t>
+    <t xml:space="preserve">8.29772758483887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.27433013916016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.08714962005615</t>
   </si>
   <si>
     <t xml:space="preserve">8.18575286865234</t>
@@ -4628,40 +4628,40 @@
     <t xml:space="preserve">8.16402816772461</t>
   </si>
   <si>
-    <t xml:space="preserve">8.10219097137451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.15567207336426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.35621929168701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.27767181396484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.30775547027588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.33616542816162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.2760009765625</t>
+    <t xml:space="preserve">8.1021900177002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.15567111968994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.35622024536133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.27767276763916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.30775451660156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.3361644744873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.27600193023682</t>
   </si>
   <si>
     <t xml:space="preserve">8.34786319732666</t>
   </si>
   <si>
-    <t xml:space="preserve">8.37293338775635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.43560600280762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.41053581237793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.43006038665771</t>
+    <t xml:space="preserve">8.37293434143066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.4356050491333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.41053676605225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.4300594329834</t>
   </si>
   <si>
     <t xml:space="preserve">8.34443187713623</t>
@@ -4673,7 +4673,7 @@
     <t xml:space="preserve">8.28326797485352</t>
   </si>
   <si>
-    <t xml:space="preserve">8.31996726989746</t>
+    <t xml:space="preserve">8.31996631622314</t>
   </si>
   <si>
     <t xml:space="preserve">8.29200553894043</t>
@@ -4688,13 +4688,13 @@
     <t xml:space="preserve">8.61180305480957</t>
   </si>
   <si>
-    <t xml:space="preserve">8.66422939300537</t>
+    <t xml:space="preserve">8.66422843933105</t>
   </si>
   <si>
     <t xml:space="preserve">8.63976287841797</t>
   </si>
   <si>
-    <t xml:space="preserve">8.63277244567871</t>
+    <t xml:space="preserve">8.63277339935303</t>
   </si>
   <si>
     <t xml:space="preserve">8.59957027435303</t>
@@ -4709,16 +4709,16 @@
     <t xml:space="preserve">8.54714393615723</t>
   </si>
   <si>
-    <t xml:space="preserve">8.58034801483154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.71141147613525</t>
+    <t xml:space="preserve">8.58034610748291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.71141242980957</t>
   </si>
   <si>
     <t xml:space="preserve">8.6956844329834</t>
   </si>
   <si>
-    <t xml:space="preserve">8.68170356750488</t>
+    <t xml:space="preserve">8.6817045211792</t>
   </si>
   <si>
     <t xml:space="preserve">8.68519878387451</t>
@@ -4727,19 +4727,19 @@
     <t xml:space="preserve">8.70966529846191</t>
   </si>
   <si>
-    <t xml:space="preserve">8.82500171661377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.83373832702637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.93858909606934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.03033447265625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.00412368774414</t>
+    <t xml:space="preserve">8.82500076293945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.83373928070068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.93859004974365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.03033638000488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.00412273406982</t>
   </si>
   <si>
     <t xml:space="preserve">9.09586715698242</t>
@@ -4748,7 +4748,7 @@
     <t xml:space="preserve">9.08276176452637</t>
   </si>
   <si>
-    <t xml:space="preserve">8.986647605896</t>
+    <t xml:space="preserve">8.98664665222168</t>
   </si>
   <si>
     <t xml:space="preserve">8.7900505065918</t>
@@ -4757,10 +4757,10 @@
     <t xml:space="preserve">8.78568172454834</t>
   </si>
   <si>
-    <t xml:space="preserve">8.80315780639648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.67995738983154</t>
+    <t xml:space="preserve">8.80315685272217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.67995643615723</t>
   </si>
   <si>
     <t xml:space="preserve">8.81626319885254</t>
@@ -4769,34 +4769,34 @@
     <t xml:space="preserve">8.88616466522217</t>
   </si>
   <si>
-    <t xml:space="preserve">8.85558319091797</t>
+    <t xml:space="preserve">8.85558223724365</t>
   </si>
   <si>
     <t xml:space="preserve">8.87742614746094</t>
   </si>
   <si>
-    <t xml:space="preserve">8.77257633209229</t>
+    <t xml:space="preserve">8.77257537841797</t>
   </si>
   <si>
     <t xml:space="preserve">8.737624168396</t>
   </si>
   <si>
-    <t xml:space="preserve">8.75510025024414</t>
+    <t xml:space="preserve">8.75510120391846</t>
   </si>
   <si>
     <t xml:space="preserve">8.7813138961792</t>
   </si>
   <si>
-    <t xml:space="preserve">8.79441928863525</t>
+    <t xml:space="preserve">8.79442024230957</t>
   </si>
   <si>
     <t xml:space="preserve">8.82063293457031</t>
   </si>
   <si>
-    <t xml:space="preserve">8.94732761383057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.02159690856934</t>
+    <t xml:space="preserve">8.94732666015625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.02159786224365</t>
   </si>
   <si>
     <t xml:space="preserve">8.96043491363525</t>
@@ -4805,16 +4805,16 @@
     <t xml:space="preserve">8.9342212677002</t>
   </si>
   <si>
-    <t xml:space="preserve">8.87305736541748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.79878807067871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.99538516998291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.89490222930908</t>
+    <t xml:space="preserve">8.8730583190918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.79878711700439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.99538421630859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.89490127563477</t>
   </si>
   <si>
     <t xml:space="preserve">8.8424768447876</t>
@@ -4829,28 +4829,28 @@
     <t xml:space="preserve">8.8118953704834</t>
   </si>
   <si>
-    <t xml:space="preserve">8.75073146820068</t>
+    <t xml:space="preserve">8.75073051452637</t>
   </si>
   <si>
     <t xml:space="preserve">8.67296600341797</t>
   </si>
   <si>
-    <t xml:space="preserve">8.62054061889648</t>
+    <t xml:space="preserve">8.62053966522217</t>
   </si>
   <si>
     <t xml:space="preserve">8.45452499389648</t>
   </si>
   <si>
-    <t xml:space="preserve">8.3601598739624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.34268474578857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.41957473754883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.33744144439697</t>
+    <t xml:space="preserve">8.36015892028809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.34268379211426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.41957569122314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.33744049072266</t>
   </si>
   <si>
     <t xml:space="preserve">8.52966976165771</t>
@@ -4865,31 +4865,31 @@
     <t xml:space="preserve">8.62578296661377</t>
   </si>
   <si>
-    <t xml:space="preserve">8.6485013961792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.4632625579834</t>
+    <t xml:space="preserve">8.64850044250488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.46326351165771</t>
   </si>
   <si>
     <t xml:space="preserve">8.02812957763672</t>
   </si>
   <si>
-    <t xml:space="preserve">8.00890731811523</t>
+    <t xml:space="preserve">8.00890636444092</t>
   </si>
   <si>
     <t xml:space="preserve">8.01240253448486</t>
   </si>
   <si>
-    <t xml:space="preserve">7.95124006271362</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.06482601165771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.98793649673462</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.03686809539795</t>
+    <t xml:space="preserve">7.95123863220215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.06482791900635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.98793745040894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.03686714172363</t>
   </si>
   <si>
     <t xml:space="preserve">8.16094207763672</t>
@@ -4898,22 +4898,22 @@
     <t xml:space="preserve">8.14521312713623</t>
   </si>
   <si>
-    <t xml:space="preserve">8.24307632446289</t>
+    <t xml:space="preserve">8.24307537078857</t>
   </si>
   <si>
     <t xml:space="preserve">8.3269567489624</t>
   </si>
   <si>
-    <t xml:space="preserve">8.37239265441895</t>
+    <t xml:space="preserve">8.37239170074463</t>
   </si>
   <si>
     <t xml:space="preserve">8.63452053070068</t>
   </si>
   <si>
-    <t xml:space="preserve">8.73587703704834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.76383876800537</t>
+    <t xml:space="preserve">8.73587799072266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.76383781433105</t>
   </si>
   <si>
     <t xml:space="preserve">8.919264793396</t>
@@ -4925,7 +4925,7 @@
     <t xml:space="preserve">8.79401969909668</t>
   </si>
   <si>
-    <t xml:space="preserve">8.79938697814941</t>
+    <t xml:space="preserve">8.79938793182373</t>
   </si>
   <si>
     <t xml:space="preserve">8.83338165283203</t>
@@ -4934,10 +4934,10 @@
     <t xml:space="preserve">8.73318576812744</t>
   </si>
   <si>
-    <t xml:space="preserve">8.79222965240479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.77970600128174</t>
+    <t xml:space="preserve">8.7922306060791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.77970504760742</t>
   </si>
   <si>
     <t xml:space="preserve">8.83517169952393</t>
@@ -4946,16 +4946,16 @@
     <t xml:space="preserve">8.87453460693359</t>
   </si>
   <si>
-    <t xml:space="preserve">8.89600563049316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.91568660736084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.95952224731445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.92284297943115</t>
+    <t xml:space="preserve">8.89600467681885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.91568565368652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.95952320098877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.92284393310547</t>
   </si>
   <si>
     <t xml:space="preserve">8.97741413116455</t>
@@ -4970,10 +4970,10 @@
     <t xml:space="preserve">9.05345630645752</t>
   </si>
   <si>
-    <t xml:space="preserve">9.14739036560059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.12502479553223</t>
+    <t xml:space="preserve">9.1473913192749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.12502574920654</t>
   </si>
   <si>
     <t xml:space="preserve">9.10713291168213</t>
@@ -4982,7 +4982,7 @@
     <t xml:space="preserve">9.19212055206299</t>
   </si>
   <si>
-    <t xml:space="preserve">9.15186309814453</t>
+    <t xml:space="preserve">9.15186214447021</t>
   </si>
   <si>
     <t xml:space="preserve">9.1831750869751</t>
@@ -4997,16 +4997,16 @@
     <t xml:space="preserve">9.27710819244385</t>
   </si>
   <si>
-    <t xml:space="preserve">9.11160659790039</t>
+    <t xml:space="preserve">9.11160564422607</t>
   </si>
   <si>
     <t xml:space="preserve">9.20553970336914</t>
   </si>
   <si>
-    <t xml:space="preserve">9.18764781951904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.12949848175049</t>
+    <t xml:space="preserve">9.18764877319336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.12949752807617</t>
   </si>
   <si>
     <t xml:space="preserve">9.03109169006348</t>
@@ -5030,10 +5030,10 @@
     <t xml:space="preserve">9.04003715515137</t>
   </si>
   <si>
-    <t xml:space="preserve">9.13844394683838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.22343254089355</t>
+    <t xml:space="preserve">9.1384449005127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.22343158721924</t>
   </si>
   <si>
     <t xml:space="preserve">9.2279052734375</t>
@@ -5045,16 +5045,16 @@
     <t xml:space="preserve">8.94252490997314</t>
   </si>
   <si>
-    <t xml:space="preserve">9.00425243377686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.0087251663208</t>
+    <t xml:space="preserve">9.00425148010254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.00872611999512</t>
   </si>
   <si>
     <t xml:space="preserve">9.02661800384521</t>
   </si>
   <si>
-    <t xml:space="preserve">8.88705921173096</t>
+    <t xml:space="preserve">8.88705825805664</t>
   </si>
   <si>
     <t xml:space="preserve">8.82264709472656</t>
@@ -5063,16 +5063,16 @@
     <t xml:space="preserve">8.76002407073975</t>
   </si>
   <si>
-    <t xml:space="preserve">8.81906890869141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.90137195587158</t>
+    <t xml:space="preserve">8.81906795501709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.9013729095459</t>
   </si>
   <si>
     <t xml:space="preserve">9.03556442260742</t>
   </si>
   <si>
-    <t xml:space="preserve">9.04450988769531</t>
+    <t xml:space="preserve">9.044508934021</t>
   </si>
   <si>
     <t xml:space="preserve">9.10266017913818</t>
@@ -5084,13 +5084,13 @@
     <t xml:space="preserve">9.35762405395508</t>
   </si>
   <si>
-    <t xml:space="preserve">9.40682888031006</t>
+    <t xml:space="preserve">9.40682792663574</t>
   </si>
   <si>
     <t xml:space="preserve">9.69757556915283</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0956773757935</t>
+    <t xml:space="preserve">10.0956783294678</t>
   </si>
   <si>
     <t xml:space="preserve">10.0330543518066</t>
@@ -5117,7 +5117,7 @@
     <t xml:space="preserve">10.4758863449097</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4848327636719</t>
+    <t xml:space="preserve">10.4848337173462</t>
   </si>
   <si>
     <t xml:space="preserve">10.5385093688965</t>
@@ -5126,13 +5126,13 @@
     <t xml:space="preserve">10.672700881958</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2611799240112</t>
+    <t xml:space="preserve">10.2611808776855</t>
   </si>
   <si>
     <t xml:space="preserve">10.2835454940796</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2343406677246</t>
+    <t xml:space="preserve">10.2343416213989</t>
   </si>
   <si>
     <t xml:space="preserve">10.2477607727051</t>
@@ -5141,52 +5141,52 @@
     <t xml:space="preserve">10.3372230529785</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3461685180664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3819522857666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3148565292358</t>
+    <t xml:space="preserve">10.3461675643921</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3819532394409</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3148574829102</t>
   </si>
   <si>
     <t xml:space="preserve">10.4356288909912</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3059120178223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4535207748413</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3103837966919</t>
+    <t xml:space="preserve">10.3059110641479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4535217285156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3103828430176</t>
   </si>
   <si>
     <t xml:space="preserve">10.4132642745972</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3551149368286</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4311552047729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2880191802979</t>
+    <t xml:space="preserve">10.3551139831543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4311561584473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2880182266235</t>
   </si>
   <si>
     <t xml:space="preserve">10.2745990753174</t>
   </si>
   <si>
-    <t xml:space="preserve">10.426682472229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4222087860107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4937782287598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6682271957397</t>
+    <t xml:space="preserve">10.4266834259033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4222106933594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4937791824341</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6682281494141</t>
   </si>
   <si>
     <t xml:space="preserve">10.5519285202026</t>
@@ -5195,10 +5195,10 @@
     <t xml:space="preserve">10.5564022064209</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6861190795898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6637544631958</t>
+    <t xml:space="preserve">10.6861200332642</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6637554168701</t>
   </si>
   <si>
     <t xml:space="preserve">10.6548089981079</t>
@@ -5207,22 +5207,22 @@
     <t xml:space="preserve">10.8158388137817</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0573835372925</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.017126083374</t>
+    <t xml:space="preserve">11.0573825836182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0171251296997</t>
   </si>
   <si>
     <t xml:space="preserve">10.9723958969116</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0081806182861</t>
+    <t xml:space="preserve">11.0081796646118</t>
   </si>
   <si>
     <t xml:space="preserve">10.9992341995239</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2273597717285</t>
+    <t xml:space="preserve">11.2273588180542</t>
   </si>
   <si>
     <t xml:space="preserve">11.0797491073608</t>
@@ -5234,13 +5234,13 @@
     <t xml:space="preserve">11.0618562698364</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1200065612793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0350179672241</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1110601425171</t>
+    <t xml:space="preserve">11.120005607605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0350189208984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1110591888428</t>
   </si>
   <si>
     <t xml:space="preserve">11.2989282608032</t>
@@ -5249,7 +5249,7 @@
     <t xml:space="preserve">11.2810354232788</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2631435394287</t>
+    <t xml:space="preserve">11.263144493103</t>
   </si>
   <si>
     <t xml:space="preserve">11.2094669342041</t>
@@ -5264,31 +5264,31 @@
     <t xml:space="preserve">11.4420652389526</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5896759033203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4465389251709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4107542037964</t>
+    <t xml:space="preserve">11.5896768569946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4465379714966</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4107551574707</t>
   </si>
   <si>
     <t xml:space="preserve">11.2497243881226</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0842218399048</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8918809890747</t>
+    <t xml:space="preserve">11.0842227935791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8918800354004</t>
   </si>
   <si>
     <t xml:space="preserve">11.115532875061</t>
   </si>
   <si>
-    <t xml:space="preserve">11.289981842041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2407779693604</t>
+    <t xml:space="preserve">11.2899808883667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2407789230347</t>
   </si>
   <si>
     <t xml:space="preserve">11.2716856002808</t>
@@ -6219,6 +6219,9 @@
   </si>
   <si>
     <t xml:space="preserve">20.3500003814697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6800003051758</t>
   </si>
 </sst>
 </file>
@@ -71453,7 +71456,7 @@
     </row>
     <row r="2497">
       <c r="A2497" s="1" t="n">
-        <v>45954.651099537</v>
+        <v>45954.2916666667</v>
       </c>
       <c r="B2497" t="n">
         <v>854704</v>
@@ -71474,6 +71477,32 @@
         <v>2068</v>
       </c>
       <c r="H2497" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2498">
+      <c r="A2498" s="1" t="n">
+        <v>45957.6910300926</v>
+      </c>
+      <c r="B2498" t="n">
+        <v>2114152</v>
+      </c>
+      <c r="C2498" t="n">
+        <v>20.7399997711182</v>
+      </c>
+      <c r="D2498" t="n">
+        <v>20.2999992370605</v>
+      </c>
+      <c r="E2498" t="n">
+        <v>20.5</v>
+      </c>
+      <c r="F2498" t="n">
+        <v>20.6800003051758</v>
+      </c>
+      <c r="G2498" t="s">
+        <v>2069</v>
+      </c>
+      <c r="H2498" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/PST.MI.xlsx
+++ b/data/PST.MI.xlsx
@@ -38,145 +38,145 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">3.90457510948181</t>
+    <t xml:space="preserve">3.90457534790039</t>
   </si>
   <si>
     <t xml:space="preserve">PST.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">4.03631687164307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.97465062141418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95222663879395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9157874584198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87934827804565</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.97184681892395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.0194993019104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99707436561584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94662117958069</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.82889485359192</t>
+    <t xml:space="preserve">4.03631639480591</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97465014457703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95222616195679</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.91578769683838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87934851646423</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97184753417969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.01949787139893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99707508087158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94662022590637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.82889437675476</t>
   </si>
   <si>
     <t xml:space="preserve">3.75601696968079</t>
   </si>
   <si>
-    <t xml:space="preserve">3.54859519004822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.68594193458557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73359227180481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.65510869026184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.7616229057312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80927395820618</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73078989982605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.82609152793884</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.72238087654114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64389657974243</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.53177690505981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.35518836975098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.00481271743774</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.89829969406128</t>
+    <t xml:space="preserve">3.5485942363739</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.68594145774841</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73359298706055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.65510845184326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.76162219047546</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8092737197876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73078966140747</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.82609176635742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.72238063812256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64389634132385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.53177714347839</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.3551881313324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.00481343269348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.8982994556427</t>
   </si>
   <si>
     <t xml:space="preserve">3.17019033432007</t>
   </si>
   <si>
-    <t xml:space="preserve">3.03284287452698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.04405522346497</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.13655400276184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.12253999710083</t>
+    <t xml:space="preserve">3.03284311294556</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.04405474662781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13655424118042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.12253904342651</t>
   </si>
   <si>
     <t xml:space="preserve">3.2486743927002</t>
   </si>
   <si>
-    <t xml:space="preserve">3.23465871810913</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.3047342300415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.42246055603027</t>
+    <t xml:space="preserve">3.23465943336487</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.30473399162292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.42246031761169</t>
   </si>
   <si>
     <t xml:space="preserve">3.34677863121033</t>
   </si>
   <si>
-    <t xml:space="preserve">3.31314325332642</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.40844440460205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.45609545707703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.51495862007141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.48412609100342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.45329284667969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.47571635246277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.4364755153656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.45889925956726</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.43367099761963</t>
+    <t xml:space="preserve">3.31314301490784</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.40844464302063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.45609617233276</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.51495933532715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.48412656784058</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.45329308509827</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.47571659088135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.43647503852844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.45889902114868</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.43367195129395</t>
   </si>
   <si>
     <t xml:space="preserve">3.61306381225586</t>
@@ -185,73 +185,73 @@
     <t xml:space="preserve">3.63829040527344</t>
   </si>
   <si>
-    <t xml:space="preserve">3.63548827171326</t>
+    <t xml:space="preserve">3.6354877948761</t>
   </si>
   <si>
     <t xml:space="preserve">3.60745739936829</t>
   </si>
   <si>
-    <t xml:space="preserve">3.58783650398254</t>
+    <t xml:space="preserve">3.58783721923828</t>
   </si>
   <si>
     <t xml:space="preserve">3.60185170173645</t>
   </si>
   <si>
-    <t xml:space="preserve">3.67192673683167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.79525828361511</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77844047546387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71397137641907</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.78404641151428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.72798681259155</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.67753314971924</t>
+    <t xml:space="preserve">3.67192792892456</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.79525876045227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77844023704529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.7139720916748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.78404664993286</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.72798705101013</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.67753267288208</t>
   </si>
   <si>
     <t xml:space="preserve">3.6158664226532</t>
   </si>
   <si>
-    <t xml:space="preserve">3.51215577125549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.56821584701538</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.58503389358521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.60465431213379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.62147259712219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.69995665550232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.6326847076416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.62988185882568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.6579122543335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.62707829475403</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.674729347229</t>
+    <t xml:space="preserve">3.51215553283691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.56821537017822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.58503341674805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.60465478897095</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.62147235870361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.699955701828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.63268494606018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.62988138198853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.65791201591492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.62707757949829</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.67472958564758</t>
   </si>
   <si>
     <t xml:space="preserve">3.68033599853516</t>
@@ -260,79 +260,79 @@
     <t xml:space="preserve">3.7448046207428</t>
   </si>
   <si>
-    <t xml:space="preserve">3.79245591163635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80086445808411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73919892311096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.6831386089325</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.76722764968872</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.79806160926819</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77563762664795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.75882053375244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.78684949874878</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.68874478340149</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.7896523475647</t>
+    <t xml:space="preserve">3.79245567321777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.80086469650269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73919868469238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.68313908576965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.76722836494446</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.79806089401245</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77563714981079</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.75881910324097</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.78684997558594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.68874406814575</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.78965258598328</t>
   </si>
   <si>
     <t xml:space="preserve">3.74760723114014</t>
   </si>
   <si>
-    <t xml:space="preserve">3.83169746398926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83730387687683</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80647087097168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85972857475281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85692477226257</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.86813592910767</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84571266174316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85412192344666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92419672012329</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93260622024536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84010624885559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.78124308586121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.76442551612854</t>
+    <t xml:space="preserve">3.83169770240784</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.83730316162109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.80647015571594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85972738265991</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85692381858826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8681366443634</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84571218490601</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85412120819092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92419624328613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93260550498962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84010577201843</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.78124380111694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.76442527770996</t>
   </si>
   <si>
     <t xml:space="preserve">3.87654519081116</t>
@@ -341,97 +341,97 @@
     <t xml:space="preserve">3.96498322486877</t>
   </si>
   <si>
-    <t xml:space="preserve">3.9148690700531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90602469444275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95024442672729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.63776254653931</t>
+    <t xml:space="preserve">3.91486787796021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90602493286133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95024418830872</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.63776206970215</t>
   </si>
   <si>
     <t xml:space="preserve">3.42256188392639</t>
   </si>
   <si>
-    <t xml:space="preserve">3.51394844055176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.50805234909058</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.60533499717712</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.52574038505554</t>
+    <t xml:space="preserve">3.5139479637146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.50805187225342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.60533428192139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.52573943138123</t>
   </si>
   <si>
     <t xml:space="preserve">3.43730139732361</t>
   </si>
   <si>
-    <t xml:space="preserve">3.39897847175598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.3724467754364</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.49920892715454</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.65839815139771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.6495532989502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73504328727722</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.67018985748291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.67313742637634</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.65250182151794</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.70851254463196</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.69672083854675</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.6554491519928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.6466064453125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.60238718986511</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.58469867706299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.52868843078613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80284667015076</t>
+    <t xml:space="preserve">3.39897871017456</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.37244701385498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.49920868873596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.65839767456055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64955377578735</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73504424095154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.67018961906433</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.67313766479492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.65250158309937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.70851278305054</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.69672131538391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.65544939041138</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64660620689392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.6023862361908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.58469915390015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.52868866920471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.80284690856934</t>
   </si>
   <si>
     <t xml:space="preserve">3.78221130371094</t>
   </si>
   <si>
-    <t xml:space="preserve">3.80874276161194</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.81463861465454</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.86770224571228</t>
+    <t xml:space="preserve">3.8087432384491</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.81463813781738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.86770176887512</t>
   </si>
   <si>
     <t xml:space="preserve">3.87949347496033</t>
@@ -440,25 +440,25 @@
     <t xml:space="preserve">3.79989886283875</t>
   </si>
   <si>
-    <t xml:space="preserve">3.72325277328491</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.76157593727112</t>
+    <t xml:space="preserve">3.72325253486633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.76157665252686</t>
   </si>
   <si>
     <t xml:space="preserve">3.667240858078</t>
   </si>
   <si>
-    <t xml:space="preserve">3.68198132514954</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.74388837814331</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.70261645317078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66134572029114</t>
+    <t xml:space="preserve">3.68198180198669</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.74388766288757</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.70261740684509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66134524345398</t>
   </si>
   <si>
     <t xml:space="preserve">3.67903351783752</t>
@@ -467,13 +467,13 @@
     <t xml:space="preserve">3.62597036361694</t>
   </si>
   <si>
-    <t xml:space="preserve">3.69377303123474</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.68492984771729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.70556449890137</t>
+    <t xml:space="preserve">3.69377326965332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.68492937088013</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.70556473731995</t>
   </si>
   <si>
     <t xml:space="preserve">3.71735620498657</t>
@@ -485,10 +485,10 @@
     <t xml:space="preserve">3.76452374458313</t>
   </si>
   <si>
-    <t xml:space="preserve">3.56406331062317</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61712646484375</t>
+    <t xml:space="preserve">3.56406402587891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61712598800659</t>
   </si>
   <si>
     <t xml:space="preserve">3.6141791343689</t>
@@ -497,7 +497,7 @@
     <t xml:space="preserve">3.58175110816956</t>
   </si>
   <si>
-    <t xml:space="preserve">3.5994393825531</t>
+    <t xml:space="preserve">3.59943890571594</t>
   </si>
   <si>
     <t xml:space="preserve">3.60828280448914</t>
@@ -506,28 +506,28 @@
     <t xml:space="preserve">3.58764696121216</t>
   </si>
   <si>
-    <t xml:space="preserve">3.57880401611328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.5729067325592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.55816793441772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.56111574172974</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.50215697288513</t>
+    <t xml:space="preserve">3.5788037776947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.57290720939636</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.55816745758057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.56111550331116</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.50215554237366</t>
   </si>
   <si>
     <t xml:space="preserve">3.54637575149536</t>
   </si>
   <si>
-    <t xml:space="preserve">3.56701111793518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.51689577102661</t>
+    <t xml:space="preserve">3.56701183319092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.51689600944519</t>
   </si>
   <si>
     <t xml:space="preserve">3.57585525512695</t>
@@ -536,10 +536,10 @@
     <t xml:space="preserve">3.64365792274475</t>
   </si>
   <si>
-    <t xml:space="preserve">3.62302184104919</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.51100063323975</t>
+    <t xml:space="preserve">3.62302255630493</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.51100039482117</t>
   </si>
   <si>
     <t xml:space="preserve">3.49036478996277</t>
@@ -548,55 +548,55 @@
     <t xml:space="preserve">3.51984405517578</t>
   </si>
   <si>
-    <t xml:space="preserve">3.55227160453796</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.54342842102051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.53163599967957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.52279257774353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.47857332229614</t>
+    <t xml:space="preserve">3.55227136611938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.54342818260193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.53163623809814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.52279186248779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.47857356071472</t>
   </si>
   <si>
     <t xml:space="preserve">3.44024991989136</t>
   </si>
   <si>
-    <t xml:space="preserve">3.36655139923096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.33117628097534</t>
+    <t xml:space="preserve">3.3665509223938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.33117651939392</t>
   </si>
   <si>
     <t xml:space="preserve">3.32528018951416</t>
   </si>
   <si>
-    <t xml:space="preserve">3.3193838596344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.31054043769836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.26632118225098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.39603042602539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.45793771743774</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.46088528633118</t>
+    <t xml:space="preserve">3.31938481330872</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.31054019927979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.26632142066956</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.39603114128113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.45793724060059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.46088576316833</t>
   </si>
   <si>
     <t xml:space="preserve">3.45204186439514</t>
   </si>
   <si>
-    <t xml:space="preserve">3.73209667205811</t>
+    <t xml:space="preserve">3.73209547996521</t>
   </si>
   <si>
     <t xml:space="preserve">3.74683594703674</t>
@@ -605,82 +605,82 @@
     <t xml:space="preserve">3.73799228668213</t>
   </si>
   <si>
-    <t xml:space="preserve">3.72914814949036</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77926301956177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.7409393787384</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77336740493774</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.79105496406555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.7674720287323</t>
+    <t xml:space="preserve">3.72914838790894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77926397323608</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.74094009399414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77336812019348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.79105544090271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.76747131347656</t>
   </si>
   <si>
     <t xml:space="preserve">3.71440863609314</t>
   </si>
   <si>
-    <t xml:space="preserve">3.63481378555298</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.59649109840393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.56995892524719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.59354281425476</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.44909334182739</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.42845797538757</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.44614577293396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.53753185272217</t>
+    <t xml:space="preserve">3.63481402397156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.59649085998535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.56995940208435</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.59354257583618</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.44909405708313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.42845821380615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.44614601135254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.53753137588501</t>
   </si>
   <si>
     <t xml:space="preserve">3.53458380699158</t>
   </si>
   <si>
-    <t xml:space="preserve">3.59059453010559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.6996693611145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.81758689880371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80579495429993</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.79695105552673</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.75862669944763</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.82937812805176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.79400277137756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.67608547210693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71146154403687</t>
+    <t xml:space="preserve">3.59059500694275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.69966912269592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.81758666038513</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.80579423904419</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.79695177078247</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.75862836837769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8293788433075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.79400300979614</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.67608571052551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71146059036255</t>
   </si>
   <si>
     <t xml:space="preserve">3.74978446960449</t>
@@ -689,67 +689,67 @@
     <t xml:space="preserve">3.77041959762573</t>
   </si>
   <si>
-    <t xml:space="preserve">3.68787693977356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.75273156166077</t>
+    <t xml:space="preserve">3.68787741661072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.75273203849792</t>
   </si>
   <si>
     <t xml:space="preserve">3.83232641220093</t>
   </si>
   <si>
-    <t xml:space="preserve">3.84411811828613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.72030448913574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.69082593917847</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.81169056892395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.82053470611572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.78916692733765</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80171418190002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.81426119804382</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.75779986381531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.76407384872437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77662014961243</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73898005485535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.82053518295288</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.78603100776672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.76093673706055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.7672107219696</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.74525260925293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.72956943511963</t>
+    <t xml:space="preserve">3.84411716461182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.72030401229858</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.69082522392273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.81169104576111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.82053446769714</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.78916668891907</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8017144203186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8142614364624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.75780010223389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.76407241821289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77662038803101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73897910118103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.82053399085999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.78603005409241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.76093649864197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.76720976829529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.74525284767151</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.72956919670105</t>
   </si>
   <si>
     <t xml:space="preserve">3.7954409122467</t>
@@ -758,43 +758,43 @@
     <t xml:space="preserve">3.80485081672668</t>
   </si>
   <si>
-    <t xml:space="preserve">3.84249138832092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.82367157936096</t>
+    <t xml:space="preserve">3.8424916267395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.82367086410522</t>
   </si>
   <si>
     <t xml:space="preserve">3.80798768997192</t>
   </si>
   <si>
-    <t xml:space="preserve">3.79857683181763</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.75152683258057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.74211525917053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77975749969482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9146363735199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92718291282654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9460027217865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.89267921447754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90208959579468</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9052267074585</t>
+    <t xml:space="preserve">3.79857778549194</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.75152611732483</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.74211597442627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77975678443909</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.91463708877563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92718315124512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94600367546082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89267945289612</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90208911895752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90522623062134</t>
   </si>
   <si>
     <t xml:space="preserve">3.942866563797</t>
@@ -806,82 +806,82 @@
     <t xml:space="preserve">3.84562826156616</t>
   </si>
   <si>
-    <t xml:space="preserve">3.89895367622375</t>
+    <t xml:space="preserve">3.89895272254944</t>
   </si>
   <si>
     <t xml:space="preserve">3.90836310386658</t>
   </si>
   <si>
-    <t xml:space="preserve">3.85817503929138</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83935499191284</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.82994484901428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85503816604614</t>
+    <t xml:space="preserve">3.85817527770996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.83935523033142</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8299446105957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85503840446472</t>
   </si>
   <si>
     <t xml:space="preserve">3.8173975944519</t>
   </si>
   <si>
-    <t xml:space="preserve">3.86131191253662</t>
+    <t xml:space="preserve">3.86131238937378</t>
   </si>
   <si>
     <t xml:space="preserve">3.92091035842896</t>
   </si>
   <si>
-    <t xml:space="preserve">3.89581632614136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88640522956848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8895423412323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.86444902420044</t>
+    <t xml:space="preserve">3.8958158493042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88640570640564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88954257965088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.86444878578186</t>
   </si>
   <si>
     <t xml:space="preserve">3.88013291358948</t>
   </si>
   <si>
-    <t xml:space="preserve">3.85190176963806</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87385892868042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93032050132751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.86758470535278</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93659424781799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94914031028748</t>
+    <t xml:space="preserve">3.85190153121948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87385845184326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93031978607178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8675856590271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93659377098083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94914078712463</t>
   </si>
   <si>
     <t xml:space="preserve">3.93345665931702</t>
   </si>
   <si>
-    <t xml:space="preserve">3.93972992897034</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92404723167419</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84876489639282</t>
+    <t xml:space="preserve">3.9397304058075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92404699325562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8487651348114</t>
   </si>
   <si>
     <t xml:space="preserve">3.83621835708618</t>
   </si>
   <si>
-    <t xml:space="preserve">3.82680797576904</t>
+    <t xml:space="preserve">3.82680821418762</t>
   </si>
   <si>
     <t xml:space="preserve">3.99305462837219</t>
@@ -890,79 +890,79 @@
     <t xml:space="preserve">4.02128553390503</t>
   </si>
   <si>
-    <t xml:space="preserve">3.99619078636169</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98364424705505</t>
+    <t xml:space="preserve">3.99619126319885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.98364400863647</t>
   </si>
   <si>
     <t xml:space="preserve">3.97109746932983</t>
   </si>
   <si>
-    <t xml:space="preserve">3.98678135871887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99932789802551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.01814889907837</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.03383159637451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.04637813568115</t>
+    <t xml:space="preserve">3.98678112030029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99932837486267</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.01814842224121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.03383255004883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.04637908935547</t>
   </si>
   <si>
     <t xml:space="preserve">4.05892562866211</t>
   </si>
   <si>
-    <t xml:space="preserve">4.04010534286499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.07147216796875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.10284042358398</t>
+    <t xml:space="preserve">4.04010629653931</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.07147264480591</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.10283994674683</t>
   </si>
   <si>
     <t xml:space="preserve">4.09970331192017</t>
   </si>
   <si>
-    <t xml:space="preserve">4.12793302536011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.21889972686768</t>
+    <t xml:space="preserve">4.12793350219727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.21889877319336</t>
   </si>
   <si>
     <t xml:space="preserve">4.2157621383667</t>
   </si>
   <si>
-    <t xml:space="preserve">4.2000789642334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.1718487739563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.18753242492676</t>
+    <t xml:space="preserve">4.20007944107056</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.17184829711914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.18753147125244</t>
   </si>
   <si>
     <t xml:space="preserve">4.19694185256958</t>
   </si>
   <si>
-    <t xml:space="preserve">4.17310285568237</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.15553712844849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.18063116073608</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.13044357299805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.13922643661499</t>
+    <t xml:space="preserve">4.17310333251953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.15553665161133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.18063163757324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.13044309616089</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.13922691345215</t>
   </si>
   <si>
     <t xml:space="preserve">4.01501178741455</t>
@@ -971,85 +971,85 @@
     <t xml:space="preserve">4.1216607093811</t>
   </si>
   <si>
-    <t xml:space="preserve">4.043869972229</t>
+    <t xml:space="preserve">4.04386949539185</t>
   </si>
   <si>
     <t xml:space="preserve">4.03759622573853</t>
   </si>
   <si>
-    <t xml:space="preserve">4.05516147613525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.09531211853027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.1291880607605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.17561149597168</t>
+    <t xml:space="preserve">4.05516195297241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.09531164169312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.12918901443481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.17561197280884</t>
   </si>
   <si>
     <t xml:space="preserve">4.181884765625</t>
   </si>
   <si>
-    <t xml:space="preserve">4.2534031867981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.2408561706543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.20697975158691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.21074438095093</t>
+    <t xml:space="preserve">4.25340366363525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.24085569381714</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.20698022842407</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.21074295043945</t>
   </si>
   <si>
     <t xml:space="preserve">4.17435741424561</t>
   </si>
   <si>
-    <t xml:space="preserve">4.41651296615601</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.43031358718872</t>
+    <t xml:space="preserve">4.41651248931885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.43031454086304</t>
   </si>
   <si>
     <t xml:space="preserve">4.40271139144897</t>
   </si>
   <si>
-    <t xml:space="preserve">4.30735397338867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.33495807647705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.37134408950806</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.48677587509155</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.6009521484375</t>
+    <t xml:space="preserve">4.30735445022583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.33495759963989</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.3713436126709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.48677492141724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.60095310211182</t>
   </si>
   <si>
     <t xml:space="preserve">4.57711219787598</t>
   </si>
   <si>
-    <t xml:space="preserve">4.65490436553955</t>
+    <t xml:space="preserve">4.65490388870239</t>
   </si>
   <si>
     <t xml:space="preserve">4.55452966690063</t>
   </si>
   <si>
-    <t xml:space="preserve">4.4955587387085</t>
+    <t xml:space="preserve">4.49555826187134</t>
   </si>
   <si>
     <t xml:space="preserve">4.56707620620728</t>
   </si>
   <si>
-    <t xml:space="preserve">4.63859367370605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.60346126556396</t>
+    <t xml:space="preserve">4.6385931968689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.60346174240112</t>
   </si>
   <si>
     <t xml:space="preserve">4.6348295211792</t>
@@ -1061,22 +1061,22 @@
     <t xml:space="preserve">4.58338689804077</t>
   </si>
   <si>
-    <t xml:space="preserve">4.54574632644653</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.52943515777588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.54449081420898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.61475372314453</t>
+    <t xml:space="preserve">4.54574584960938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.52943468093872</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.54449129104614</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.61475467681885</t>
   </si>
   <si>
     <t xml:space="preserve">4.62353658676147</t>
   </si>
   <si>
-    <t xml:space="preserve">4.65866899490356</t>
+    <t xml:space="preserve">4.65866804122925</t>
   </si>
   <si>
     <t xml:space="preserve">4.73645973205566</t>
@@ -1091,31 +1091,31 @@
     <t xml:space="preserve">4.82052278518677</t>
   </si>
   <si>
-    <t xml:space="preserve">4.81299543380737</t>
+    <t xml:space="preserve">4.81299591064453</t>
   </si>
   <si>
     <t xml:space="preserve">4.81675863265991</t>
   </si>
   <si>
-    <t xml:space="preserve">4.81424903869629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.84310817718506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.88702249526978</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.85690879821777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.86694669723511</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.93721008300781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.94222784042358</t>
+    <t xml:space="preserve">4.81424999237061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.8431077003479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.88702201843262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.85690975189209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.86694717407227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.9372091293335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.94222831726074</t>
   </si>
   <si>
     <t xml:space="preserve">4.96355819702148</t>
@@ -1124,19 +1124,19 @@
     <t xml:space="preserve">4.97359657287598</t>
   </si>
   <si>
-    <t xml:space="preserve">5.00119876861572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.08526372909546</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.07146167755127</t>
+    <t xml:space="preserve">5.00119924545288</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.08526420593262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.07146263122559</t>
   </si>
   <si>
     <t xml:space="preserve">5.06267833709717</t>
   </si>
   <si>
-    <t xml:space="preserve">5.11537551879883</t>
+    <t xml:space="preserve">5.1153769493103</t>
   </si>
   <si>
     <t xml:space="preserve">5.09153699874878</t>
@@ -1145,7 +1145,7 @@
     <t xml:space="preserve">5.06769752502441</t>
   </si>
   <si>
-    <t xml:space="preserve">5.11286640167236</t>
+    <t xml:space="preserve">5.11286687850952</t>
   </si>
   <si>
     <t xml:space="preserve">5.15552568435669</t>
@@ -1154,7 +1154,7 @@
     <t xml:space="preserve">4.96230316162109</t>
   </si>
   <si>
-    <t xml:space="preserve">4.95101118087769</t>
+    <t xml:space="preserve">4.95101165771484</t>
   </si>
   <si>
     <t xml:space="preserve">4.78037309646606</t>
@@ -1172,7 +1172,7 @@
     <t xml:space="preserve">4.83432531356812</t>
   </si>
   <si>
-    <t xml:space="preserve">4.76029777526855</t>
+    <t xml:space="preserve">4.7602972984314</t>
   </si>
   <si>
     <t xml:space="preserve">4.60722589492798</t>
@@ -1184,139 +1184,139 @@
     <t xml:space="preserve">4.584641456604</t>
   </si>
   <si>
-    <t xml:space="preserve">4.59467840194702</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.68627119064331</t>
+    <t xml:space="preserve">4.59467935562134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.68627214431763</t>
   </si>
   <si>
     <t xml:space="preserve">4.71261978149414</t>
   </si>
   <si>
-    <t xml:space="preserve">4.58840560913086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.58589649200439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.56833028793335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.44411659240723</t>
+    <t xml:space="preserve">4.58840608596802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.58589553833008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.56833124160767</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.44411611557007</t>
   </si>
   <si>
     <t xml:space="preserve">4.61600875854492</t>
   </si>
   <si>
-    <t xml:space="preserve">4.7038369178772</t>
+    <t xml:space="preserve">4.70383739471436</t>
   </si>
   <si>
     <t xml:space="preserve">4.79292058944702</t>
   </si>
   <si>
-    <t xml:space="preserve">4.90584182739258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.7866473197937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.86100339889526</t>
+    <t xml:space="preserve">4.90584230422974</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.78664636611938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.86100244522095</t>
   </si>
   <si>
     <t xml:space="preserve">4.9101300239563</t>
   </si>
   <si>
-    <t xml:space="preserve">4.93270254135132</t>
+    <t xml:space="preserve">4.93270301818848</t>
   </si>
   <si>
     <t xml:space="preserve">4.87162399291992</t>
   </si>
   <si>
-    <t xml:space="preserve">4.8769359588623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.81320238113403</t>
+    <t xml:space="preserve">4.87693548202515</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.81320190429688</t>
   </si>
   <si>
     <t xml:space="preserve">4.83577442169189</t>
   </si>
   <si>
-    <t xml:space="preserve">4.76672983169556</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.76009130477905</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.80789184570312</t>
+    <t xml:space="preserve">4.7667293548584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.76009082794189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.80789041519165</t>
   </si>
   <si>
     <t xml:space="preserve">4.8198413848877</t>
   </si>
   <si>
-    <t xml:space="preserve">4.93403100967407</t>
+    <t xml:space="preserve">4.93403005599976</t>
   </si>
   <si>
     <t xml:space="preserve">4.97253561019897</t>
   </si>
   <si>
-    <t xml:space="preserve">5.01900720596313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.96589612960815</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.0389256477356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.02697467803955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.10000228881836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.15311431884766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.18099689483643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.12124681472778</t>
+    <t xml:space="preserve">5.01900815963745</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.96589660644531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.03892469406128</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.02697420120239</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.10000371932983</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.1531138420105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.18099737167358</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.1212477684021</t>
   </si>
   <si>
     <t xml:space="preserve">5.13452482223511</t>
   </si>
   <si>
-    <t xml:space="preserve">5.11859130859375</t>
+    <t xml:space="preserve">5.11859178543091</t>
   </si>
   <si>
     <t xml:space="preserve">5.12788534164429</t>
   </si>
   <si>
-    <t xml:space="preserve">5.2115364074707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.23410844802856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.25668048858643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.28854751586914</t>
+    <t xml:space="preserve">5.21153593063354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.23410892486572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.25668096542358</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.28854703903198</t>
   </si>
   <si>
     <t xml:space="preserve">5.28058099746704</t>
   </si>
   <si>
-    <t xml:space="preserve">4.99510860443115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.94465208053589</t>
+    <t xml:space="preserve">4.99510765075684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.94465255737305</t>
   </si>
   <si>
     <t xml:space="preserve">4.92871904373169</t>
   </si>
   <si>
-    <t xml:space="preserve">4.86896896362305</t>
+    <t xml:space="preserve">4.86896944046021</t>
   </si>
   <si>
     <t xml:space="preserve">4.78664684295654</t>
@@ -1331,112 +1331,112 @@
     <t xml:space="preserve">4.74548530578613</t>
   </si>
   <si>
-    <t xml:space="preserve">4.60474061965942</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.54764652252197</t>
+    <t xml:space="preserve">4.60474109649658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.54764604568481</t>
   </si>
   <si>
     <t xml:space="preserve">4.47594594955444</t>
   </si>
   <si>
-    <t xml:space="preserve">4.61801862716675</t>
+    <t xml:space="preserve">4.61801910400391</t>
   </si>
   <si>
     <t xml:space="preserve">4.52772998809814</t>
   </si>
   <si>
-    <t xml:space="preserve">4.51046800613403</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.50250148773193</t>
+    <t xml:space="preserve">4.51046895980835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.50250196456909</t>
   </si>
   <si>
     <t xml:space="preserve">4.48524045944214</t>
   </si>
   <si>
-    <t xml:space="preserve">4.50515747070312</t>
+    <t xml:space="preserve">4.50515699386597</t>
   </si>
   <si>
     <t xml:space="preserve">4.44673538208008</t>
   </si>
   <si>
-    <t xml:space="preserve">4.40291881561279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.47727346420288</t>
+    <t xml:space="preserve">4.40291929244995</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.47727394104004</t>
   </si>
   <si>
     <t xml:space="preserve">4.59544658660889</t>
   </si>
   <si>
-    <t xml:space="preserve">4.68440866470337</t>
+    <t xml:space="preserve">4.68440818786621</t>
   </si>
   <si>
     <t xml:space="preserve">4.65519618988037</t>
   </si>
   <si>
-    <t xml:space="preserve">4.67378520965576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.78133630752563</t>
+    <t xml:space="preserve">4.6737847328186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.78133535385132</t>
   </si>
   <si>
     <t xml:space="preserve">4.75610733032227</t>
   </si>
   <si>
-    <t xml:space="preserve">4.68175220489502</t>
+    <t xml:space="preserve">4.68175268173218</t>
   </si>
   <si>
     <t xml:space="preserve">4.56225156784058</t>
   </si>
   <si>
-    <t xml:space="preserve">4.58880710601807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.63262414932251</t>
+    <t xml:space="preserve">4.58880805969238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.63262462615967</t>
   </si>
   <si>
     <t xml:space="preserve">4.61005210876465</t>
   </si>
   <si>
-    <t xml:space="preserve">4.59810256958008</t>
+    <t xml:space="preserve">4.59810161590576</t>
   </si>
   <si>
     <t xml:space="preserve">4.66050720214844</t>
   </si>
   <si>
-    <t xml:space="preserve">4.69901371002197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.72158622741699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.77735185623169</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.80523490905762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.77336835861206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.56889152526855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.51976299285889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.43876838684082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.4480619430542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.45204591751099</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.38167333602905</t>
+    <t xml:space="preserve">4.69901323318481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.72158527374268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.77735280990601</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.80523586273193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.77336883544922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.5688910484314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.51976251602173</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.43876791000366</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.44806289672852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.45204639434814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.38167285919189</t>
   </si>
   <si>
     <t xml:space="preserve">4.21968460083008</t>
@@ -1445,61 +1445,61 @@
     <t xml:space="preserve">4.2422571182251</t>
   </si>
   <si>
-    <t xml:space="preserve">4.28474569320679</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.16657400131226</t>
+    <t xml:space="preserve">4.28474617004395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.16657257080078</t>
   </si>
   <si>
     <t xml:space="preserve">4.14798498153687</t>
   </si>
   <si>
-    <t xml:space="preserve">4.16391801834106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.23296213150024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.17985153198242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.06300640106201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.16259002685547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.14001750946045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.14931201934814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9820122718811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.06831741333008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.07230043411255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.20109558105469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.10815238952637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.21570110321045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.3498067855835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.38432884216309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.32325172424316</t>
+    <t xml:space="preserve">4.16391754150391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.2329626083374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.17985057830811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.06300687789917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.16259050369263</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.14001798629761</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.1493124961853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.98201203346252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.06831789016724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.07230091094971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.20109510421753</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.10815143585205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.21570062637329</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.34980726242065</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.38432931900024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.32325220108032</t>
   </si>
   <si>
     <t xml:space="preserve">4.29536771774292</t>
@@ -1508,10 +1508,10 @@
     <t xml:space="preserve">4.43744087219238</t>
   </si>
   <si>
-    <t xml:space="preserve">4.53038501739502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.56092405319214</t>
+    <t xml:space="preserve">4.53038549423218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.5609245300293</t>
   </si>
   <si>
     <t xml:space="preserve">4.57021903991699</t>
@@ -1520,19 +1520,19 @@
     <t xml:space="preserve">4.57287406921387</t>
   </si>
   <si>
-    <t xml:space="preserve">4.42681837081909</t>
+    <t xml:space="preserve">4.42681789398193</t>
   </si>
   <si>
     <t xml:space="preserve">4.31528520584106</t>
   </si>
   <si>
-    <t xml:space="preserve">4.32590627670288</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.35113477706909</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.23163461685181</t>
+    <t xml:space="preserve">4.3259072303772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.35113430023193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.23163414001465</t>
   </si>
   <si>
     <t xml:space="preserve">4.37105131149292</t>
@@ -1541,10 +1541,10 @@
     <t xml:space="preserve">4.34847927093506</t>
   </si>
   <si>
-    <t xml:space="preserve">4.54100704193115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.51710653305054</t>
+    <t xml:space="preserve">4.54100751876831</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.51710748672485</t>
   </si>
   <si>
     <t xml:space="preserve">4.44939088821411</t>
@@ -1556,7 +1556,7 @@
     <t xml:space="preserve">4.55826854705811</t>
   </si>
   <si>
-    <t xml:space="preserve">4.52241849899292</t>
+    <t xml:space="preserve">4.52241802215576</t>
   </si>
   <si>
     <t xml:space="preserve">4.58216857910156</t>
@@ -1565,10 +1565,10 @@
     <t xml:space="preserve">4.3405122756958</t>
   </si>
   <si>
-    <t xml:space="preserve">4.36175632476807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.31130075454712</t>
+    <t xml:space="preserve">4.36175727844238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.31130123138428</t>
   </si>
   <si>
     <t xml:space="preserve">4.35379028320312</t>
@@ -1580,70 +1580,70 @@
     <t xml:space="preserve">4.60075759887695</t>
   </si>
   <si>
-    <t xml:space="preserve">4.57818508148193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.57154607772827</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.71892929077148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.65386819839478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.58615303039551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.53569602966309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.63660717010498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.6273136138916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.64590263366699</t>
+    <t xml:space="preserve">4.57818412780762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.57154655456543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.71892976760864</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.65386915206909</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.58615255355835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.53569555282593</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.63660764694214</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.62731266021729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.64590215682983</t>
   </si>
   <si>
     <t xml:space="preserve">4.70299625396729</t>
   </si>
   <si>
-    <t xml:space="preserve">4.67112874984741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.71760225296021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.78000783920288</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.79195880889893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.81452941894531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.79328536987305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.88224697113037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.91278553009033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.03626823425293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.04556322097778</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.99776363372803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.04423570632935</t>
+    <t xml:space="preserve">4.67112922668457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.71760177612305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.78000736236572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.79195737838745</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.81452989578247</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.79328441619873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.88224649429321</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.91278696060181</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.0362696647644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.0455641746521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.99776315689087</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.04423522949219</t>
   </si>
   <si>
     <t xml:space="preserve">5.05618619918823</t>
@@ -1655,37 +1655,37 @@
     <t xml:space="preserve">5.084068775177</t>
   </si>
   <si>
-    <t xml:space="preserve">5.09203672409058</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.98846912384033</t>
+    <t xml:space="preserve">5.09203577041626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.98846864700317</t>
   </si>
   <si>
     <t xml:space="preserve">4.8782639503479</t>
   </si>
   <si>
-    <t xml:space="preserve">4.99245309829712</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.07477521896362</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.10265827178955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.94863557815552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.96456861495972</t>
+    <t xml:space="preserve">4.9924521446228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.07477474212646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.10265779495239</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.94863605499268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.96456909179688</t>
   </si>
   <si>
     <t xml:space="preserve">5.02431869506836</t>
   </si>
   <si>
-    <t xml:space="preserve">5.09867477416992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.15045785903931</t>
+    <t xml:space="preserve">5.09867525100708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.15045833587646</t>
   </si>
   <si>
     <t xml:space="preserve">5.08938074111938</t>
@@ -1694,55 +1694,55 @@
     <t xml:space="preserve">5.14249134063721</t>
   </si>
   <si>
-    <t xml:space="preserve">5.16108083724976</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.14514780044556</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.13054227828979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.16639184951782</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.1876368522644</t>
+    <t xml:space="preserve">5.1610803604126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.1451473236084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.13054132461548</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.16639137268066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.18763637542725</t>
   </si>
   <si>
     <t xml:space="preserve">5.2434024810791</t>
   </si>
   <si>
-    <t xml:space="preserve">5.24473094940186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.26464748382568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.268630027771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.23941946029663</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.26331996917725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.27394104003906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.27659702301025</t>
+    <t xml:space="preserve">5.24473142623901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.26464700698853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.26862955093384</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.23941993713379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.2633204460144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.27394151687622</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.27659845352173</t>
   </si>
   <si>
     <t xml:space="preserve">5.18630886077881</t>
   </si>
   <si>
-    <t xml:space="preserve">5.24605846405029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.27128601074219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.28456401824951</t>
+    <t xml:space="preserve">5.24605798721313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.27128648757935</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.28456354141235</t>
   </si>
   <si>
     <t xml:space="preserve">5.30580854415894</t>
@@ -1757,7 +1757,7 @@
     <t xml:space="preserve">5.55012035369873</t>
   </si>
   <si>
-    <t xml:space="preserve">5.60323047637939</t>
+    <t xml:space="preserve">5.60323143005371</t>
   </si>
   <si>
     <t xml:space="preserve">5.73468112945557</t>
@@ -1790,79 +1790,79 @@
     <t xml:space="preserve">5.8063817024231</t>
   </si>
   <si>
-    <t xml:space="preserve">5.80239772796631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.82497119903564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.92455339431763</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.94579792022705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.93650531768799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.96837091445923</t>
+    <t xml:space="preserve">5.80239820480347</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.82497072219849</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.92455434799194</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.94579839706421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.93650484085083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.96836996078491</t>
   </si>
   <si>
     <t xml:space="preserve">5.95774793624878</t>
   </si>
   <si>
-    <t xml:space="preserve">6.02148246765137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.97633695602417</t>
+    <t xml:space="preserve">6.02148103713989</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.97633743286133</t>
   </si>
   <si>
     <t xml:space="preserve">6.31757640838623</t>
   </si>
   <si>
-    <t xml:space="preserve">6.3202338218689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.28172731399536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.14894866943359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.12372016906738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.14230966567993</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.22330379486084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.31359386444092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.26712083816528</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.20604372024536</t>
+    <t xml:space="preserve">6.32023334503174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.2817268371582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.14894914627075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.12372064590454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.14230871200562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.223304271698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.31359338760376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.2671217918396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.20604276657104</t>
   </si>
   <si>
     <t xml:space="preserve">6.25251531600952</t>
   </si>
   <si>
-    <t xml:space="preserve">6.05467700958252</t>
+    <t xml:space="preserve">6.05467557907104</t>
   </si>
   <si>
     <t xml:space="preserve">5.98032140731812</t>
   </si>
   <si>
-    <t xml:space="preserve">5.97500991821289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.90596580505371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.08787059783936</t>
+    <t xml:space="preserve">5.97500896453857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.90596532821655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.08787107467651</t>
   </si>
   <si>
     <t xml:space="preserve">6.04936599731445</t>
@@ -1871,16 +1871,16 @@
     <t xml:space="preserve">6.12770462036133</t>
   </si>
   <si>
-    <t xml:space="preserve">5.99094247817993</t>
+    <t xml:space="preserve">5.99094343185425</t>
   </si>
   <si>
     <t xml:space="preserve">6.04405403137207</t>
   </si>
   <si>
-    <t xml:space="preserve">6.08256006240845</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.82098722457886</t>
+    <t xml:space="preserve">6.08256101608276</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.82098627090454</t>
   </si>
   <si>
     <t xml:space="preserve">5.92189931869507</t>
@@ -1889,13 +1889,13 @@
     <t xml:space="preserve">5.90729284286499</t>
   </si>
   <si>
-    <t xml:space="preserve">5.86082124710083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.83028268814087</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.77584266662598</t>
+    <t xml:space="preserve">5.86082029342651</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.83028030395508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.77584218978882</t>
   </si>
   <si>
     <t xml:space="preserve">5.78779315948486</t>
@@ -1904,16 +1904,16 @@
     <t xml:space="preserve">5.93517637252808</t>
   </si>
   <si>
-    <t xml:space="preserve">5.89401531219482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.92588138580322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.04272747039795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.09982109069824</t>
+    <t xml:space="preserve">5.89401388168335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.92588186264038</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.04272699356079</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.09982061386108</t>
   </si>
   <si>
     <t xml:space="preserve">6.12903213500977</t>
@@ -1922,73 +1922,73 @@
     <t xml:space="preserve">6.15293216705322</t>
   </si>
   <si>
-    <t xml:space="preserve">6.12106609344482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.16753768920898</t>
+    <t xml:space="preserve">6.12106657028198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.16753721237183</t>
   </si>
   <si>
     <t xml:space="preserve">6.2219762802124</t>
   </si>
   <si>
-    <t xml:space="preserve">6.31624841690063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.42833089828491</t>
+    <t xml:space="preserve">6.31624889373779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.42833042144775</t>
   </si>
   <si>
     <t xml:space="preserve">6.38377714157104</t>
   </si>
   <si>
-    <t xml:space="preserve">6.35732364654541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.36289167404175</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.44643020629883</t>
+    <t xml:space="preserve">6.35732269287109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.36289310455322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.44643068313599</t>
   </si>
   <si>
     <t xml:space="preserve">6.43529319763184</t>
   </si>
   <si>
-    <t xml:space="preserve">6.58983850479126</t>
+    <t xml:space="preserve">6.58983898162842</t>
   </si>
   <si>
     <t xml:space="preserve">6.74577856063843</t>
   </si>
   <si>
-    <t xml:space="preserve">6.78754949569702</t>
+    <t xml:space="preserve">6.78754901885986</t>
   </si>
   <si>
     <t xml:space="preserve">6.76248741149902</t>
   </si>
   <si>
-    <t xml:space="preserve">6.75274181365967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.72071838378906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.78615665435791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.71932601928711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.72350072860718</t>
+    <t xml:space="preserve">6.75274133682251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.7207179069519</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.78615713119507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.71932554244995</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.72350168228149</t>
   </si>
   <si>
     <t xml:space="preserve">6.69426441192627</t>
   </si>
   <si>
-    <t xml:space="preserve">6.67337989807129</t>
+    <t xml:space="preserve">6.67338037490845</t>
   </si>
   <si>
     <t xml:space="preserve">6.65945625305176</t>
   </si>
   <si>
-    <t xml:space="preserve">6.54389238357544</t>
+    <t xml:space="preserve">6.5438928604126</t>
   </si>
   <si>
     <t xml:space="preserve">6.57313203811646</t>
@@ -2000,49 +2000,49 @@
     <t xml:space="preserve">6.59540939331055</t>
   </si>
   <si>
-    <t xml:space="preserve">6.54807043075562</t>
+    <t xml:space="preserve">6.54806995391846</t>
   </si>
   <si>
     <t xml:space="preserve">6.67477130889893</t>
   </si>
   <si>
-    <t xml:space="preserve">6.50073146820068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.72489404678345</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.79172515869141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.71236276626587</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.60515403747559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.60097980499268</t>
+    <t xml:space="preserve">6.50073099136353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.72489547729492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.79172611236572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.7123646736145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.60515451431274</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.60097742080688</t>
   </si>
   <si>
     <t xml:space="preserve">6.70957946777344</t>
   </si>
   <si>
-    <t xml:space="preserve">6.26125335693359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.33504581451416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.48123836517334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.36567640304565</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.61350965499878</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.56756258010864</t>
+    <t xml:space="preserve">6.26125288009644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.33504629135132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.48123931884766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.36567544937134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.61350917816162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.5675630569458</t>
   </si>
   <si>
     <t xml:space="preserve">6.7513484954834</t>
@@ -2051,46 +2051,46 @@
     <t xml:space="preserve">6.7276782989502</t>
   </si>
   <si>
-    <t xml:space="preserve">6.55781650543213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.61211633682251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.54250001907349</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.8502025604248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.80286502838135</t>
+    <t xml:space="preserve">6.55781555175781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.61211681365967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.54250144958496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.85020208358765</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.80286407470703</t>
   </si>
   <si>
     <t xml:space="preserve">6.87526512145996</t>
   </si>
   <si>
-    <t xml:space="preserve">6.89197158813477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.02424192428589</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.99639701843262</t>
+    <t xml:space="preserve">6.89197206497192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.02424240112305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.99639654159546</t>
   </si>
   <si>
     <t xml:space="preserve">7.0137996673584</t>
   </si>
   <si>
-    <t xml:space="preserve">7.01727962493896</t>
+    <t xml:space="preserve">7.01728057861328</t>
   </si>
   <si>
     <t xml:space="preserve">6.89893436431885</t>
   </si>
   <si>
-    <t xml:space="preserve">6.92677974700928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.04860687255859</t>
+    <t xml:space="preserve">6.92678022384644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.04860734939575</t>
   </si>
   <si>
     <t xml:space="preserve">7.0903787612915</t>
@@ -2105,22 +2105,22 @@
     <t xml:space="preserve">7.07297420501709</t>
   </si>
   <si>
-    <t xml:space="preserve">7.08689641952515</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.00683832168579</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.15303134918213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.11126184463501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.10778093338013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.14259004592896</t>
+    <t xml:space="preserve">7.08689832687378</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.00683784484863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.15303230285645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.11126279830933</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.10778141021729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.14259052276611</t>
   </si>
   <si>
     <t xml:space="preserve">7.26093721389771</t>
@@ -2129,94 +2129,94 @@
     <t xml:space="preserve">7.15999364852905</t>
   </si>
   <si>
-    <t xml:space="preserve">6.93652772903442</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.95184183120728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.94766521453857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.14607095718384</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.05208826065063</t>
+    <t xml:space="preserve">6.93652725219727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.95184135437012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.94766426086426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.146071434021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.05208873748779</t>
   </si>
   <si>
     <t xml:space="preserve">7.13562774658203</t>
   </si>
   <si>
-    <t xml:space="preserve">7.36535978317261</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.3758020401001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.47674655914307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.36884164810181</t>
+    <t xml:space="preserve">7.36536073684692</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.37580299377441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.47674703598022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.36884021759033</t>
   </si>
   <si>
     <t xml:space="preserve">7.45238018035889</t>
   </si>
   <si>
-    <t xml:space="preserve">7.49414968490601</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.5185170173645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.60553598403931</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.62294054031372</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.65078544616699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.56028509140015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.59509325027466</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.58117008209229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.57420778274536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.67863321304321</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.72388219833374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.77609348297119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.65426588058472</t>
+    <t xml:space="preserve">7.49415063858032</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.51851606369019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.60553693771362</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.62294101715088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.65078592300415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.56028461456299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.59509420394897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.58116960525513</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.57420682907104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.67863178253174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.72388172149658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.77609491348267</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.65426635742188</t>
   </si>
   <si>
     <t xml:space="preserve">7.54636001586914</t>
   </si>
   <si>
-    <t xml:space="preserve">7.63686323165894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.80046081542969</t>
+    <t xml:space="preserve">7.63686275482178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.800461769104</t>
   </si>
   <si>
     <t xml:space="preserve">7.73780488967896</t>
   </si>
   <si>
-    <t xml:space="preserve">7.75520992279053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.76913261413574</t>
+    <t xml:space="preserve">7.75520801544189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.76913166046143</t>
   </si>
   <si>
     <t xml:space="preserve">7.81078052520752</t>
@@ -2225,13 +2225,13 @@
     <t xml:space="preserve">7.67666006088257</t>
   </si>
   <si>
-    <t xml:space="preserve">7.74724912643433</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.65195226669312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.71548366546631</t>
+    <t xml:space="preserve">7.74724960327148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.65195369720459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.71548414230347</t>
   </si>
   <si>
     <t xml:space="preserve">7.73666191101074</t>
@@ -2240,187 +2240,187 @@
     <t xml:space="preserve">7.66607189178467</t>
   </si>
   <si>
-    <t xml:space="preserve">7.61665821075439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.50724458694458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.47547817230225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.23194217681885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.3095908164978</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.40488862991333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.27076768875122</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.28135633468628</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.18958902359009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.29194450378418</t>
+    <t xml:space="preserve">7.61665773391724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.50724315643311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.47547912597656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.23194360733032</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.30959224700928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.40488719940186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.27076864242554</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.28135538101196</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.18958854675293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.29194498062134</t>
   </si>
   <si>
     <t xml:space="preserve">7.21076536178589</t>
   </si>
   <si>
-    <t xml:space="preserve">7.33076906204224</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.17900133132935</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.24253177642822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.17547130584717</t>
+    <t xml:space="preserve">7.33077049255371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.1790018081665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.24253129959106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.17547035217285</t>
   </si>
   <si>
     <t xml:space="preserve">7.26723718643188</t>
   </si>
   <si>
-    <t xml:space="preserve">7.36253547668457</t>
+    <t xml:space="preserve">7.3625340461731</t>
   </si>
   <si>
     <t xml:space="preserve">7.14370584487915</t>
   </si>
   <si>
-    <t xml:space="preserve">7.19664716720581</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.10488080978394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.04346656799316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.22488355636597</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.12605810165405</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.23900270462036</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.20723628997803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.16488265991211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.10135221481323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.09076356887817</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.26017904281616</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.32723903656006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.34841632843018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.25311899185181</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.47194814682007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.82136964797974</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.76136779785156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.3060622215271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.41547727584839</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.55665636062622</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.57077503204346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.62018775939941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.69783735275269</t>
+    <t xml:space="preserve">7.19664812088013</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.10488033294678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.04346895217896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.22488307952881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.12605905532837</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.23900175094604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.20723676681519</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.16488122940063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.10135173797607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.09076261520386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.260178565979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.32723808288574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.34841585159302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.25311946868896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.47194957733154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.82136869430542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.76136827468872</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.30606412887573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.41547632217407</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.55665731430054</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.57077646255493</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.62018871307373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.69783687591553</t>
   </si>
   <si>
     <t xml:space="preserve">7.78960466384888</t>
   </si>
   <si>
-    <t xml:space="preserve">7.75077962875366</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.7296028137207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.7190146446228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.00490188598633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.12490558624268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.96607875823975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.97313785552979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.40841865539551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.29547357559204</t>
+    <t xml:space="preserve">7.7507791519165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.72960233688354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.71901512145996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.00490379333496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.12490749359131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.96607780456543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.97313690185547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.40841817855835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.2954740524292</t>
   </si>
   <si>
     <t xml:space="preserve">7.44018316268921</t>
   </si>
   <si>
-    <t xml:space="preserve">7.11899900436401</t>
+    <t xml:space="preserve">7.11900043487549</t>
   </si>
   <si>
     <t xml:space="preserve">6.78652048110962</t>
   </si>
   <si>
-    <t xml:space="preserve">6.53804302215576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.79075527191162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.83875608444214</t>
+    <t xml:space="preserve">6.53804397583008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.79075574874878</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.8387565612793</t>
   </si>
   <si>
     <t xml:space="preserve">6.65804672241211</t>
   </si>
   <si>
-    <t xml:space="preserve">6.86275720596313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.97049951553345</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.56107759475708</t>
+    <t xml:space="preserve">6.86275768280029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.97050046920776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.56107807159424</t>
   </si>
   <si>
     <t xml:space="preserve">5.56248998641968</t>
@@ -2429,19 +2429,19 @@
     <t xml:space="preserve">4.33704853057861</t>
   </si>
   <si>
-    <t xml:space="preserve">4.76058769226074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.58975982666016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.585524559021</t>
+    <t xml:space="preserve">4.7605881690979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.589759349823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.58552503585815</t>
   </si>
   <si>
     <t xml:space="preserve">4.49658107757568</t>
   </si>
   <si>
-    <t xml:space="preserve">4.88059091567993</t>
+    <t xml:space="preserve">4.88059186935425</t>
   </si>
   <si>
     <t xml:space="preserve">4.89612150192261</t>
@@ -2450,7 +2450,7 @@
     <t xml:space="preserve">5.06553745269775</t>
   </si>
   <si>
-    <t xml:space="preserve">5.41142702102661</t>
+    <t xml:space="preserve">5.41142749786377</t>
   </si>
   <si>
     <t xml:space="preserve">5.46084070205688</t>
@@ -2462,10 +2462,10 @@
     <t xml:space="preserve">5.542724609375</t>
   </si>
   <si>
-    <t xml:space="preserve">5.58790254592896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.44954681396484</t>
+    <t xml:space="preserve">5.58790159225464</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.44954633712769</t>
   </si>
   <si>
     <t xml:space="preserve">5.21801090240479</t>
@@ -2474,7 +2474,7 @@
     <t xml:space="preserve">5.486252784729</t>
   </si>
   <si>
-    <t xml:space="preserve">5.5271954536438</t>
+    <t xml:space="preserve">5.52719497680664</t>
   </si>
   <si>
     <t xml:space="preserve">5.67543411254883</t>
@@ -2483,28 +2483,28 @@
     <t xml:space="preserve">5.7573184967041</t>
   </si>
   <si>
-    <t xml:space="preserve">5.84343814849854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.86320400238037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.88720417022705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.36907386779785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.41283988952637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.43542861938477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.37330865859985</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.25895357131958</t>
+    <t xml:space="preserve">5.84343719482422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.86320304870605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.88720464706421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.36907339096069</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.41283893585205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.43542814254761</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.37330913543701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.25895261764526</t>
   </si>
   <si>
     <t xml:space="preserve">5.34224939346313</t>
@@ -2513,88 +2513,88 @@
     <t xml:space="preserve">5.3069543838501</t>
   </si>
   <si>
-    <t xml:space="preserve">5.2222466468811</t>
+    <t xml:space="preserve">5.22224617004395</t>
   </si>
   <si>
     <t xml:space="preserve">5.56390190124512</t>
   </si>
   <si>
-    <t xml:space="preserve">5.55401992797852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.66837453842163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.47213506698608</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.33942604064941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.18836307525635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.10224342346191</t>
+    <t xml:space="preserve">5.55401945114136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.66837501525879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.47213459014893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.33942651748657</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.18836355209351</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.10224390029907</t>
   </si>
   <si>
     <t xml:space="preserve">5.36060285568237</t>
   </si>
   <si>
-    <t xml:space="preserve">5.4749584197998</t>
+    <t xml:space="preserve">5.47495889663696</t>
   </si>
   <si>
     <t xml:space="preserve">5.25612926483154</t>
   </si>
   <si>
-    <t xml:space="preserve">5.16012716293335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.07259511947632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.26742458343506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.22648143768311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.23495197296143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.20248126983643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.25330591201782</t>
+    <t xml:space="preserve">5.16012763977051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.07259607315063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.2674241065979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.22648191452026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.23495244979858</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.20248079299927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.25330686569214</t>
   </si>
   <si>
     <t xml:space="preserve">5.46225261688232</t>
   </si>
   <si>
-    <t xml:space="preserve">5.54413652420044</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.57237243652344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.62319707870483</t>
+    <t xml:space="preserve">5.5441370010376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.57237195968628</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.62319803237915</t>
   </si>
   <si>
     <t xml:space="preserve">5.68813991546631</t>
   </si>
   <si>
-    <t xml:space="preserve">5.86038017272949</t>
+    <t xml:space="preserve">5.86037969589233</t>
   </si>
   <si>
     <t xml:space="preserve">6.04814863204956</t>
   </si>
   <si>
-    <t xml:space="preserve">6.19074153900146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.31921482086182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.12438631057739</t>
+    <t xml:space="preserve">6.19074058532715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.3192138671875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.12438583374023</t>
   </si>
   <si>
     <t xml:space="preserve">6.05379676818848</t>
@@ -2603,16 +2603,16 @@
     <t xml:space="preserve">5.73472929000854</t>
   </si>
   <si>
-    <t xml:space="preserve">5.82226228713989</t>
+    <t xml:space="preserve">5.82226085662842</t>
   </si>
   <si>
     <t xml:space="preserve">5.87167406082153</t>
   </si>
   <si>
-    <t xml:space="preserve">5.99026489257812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.96344089508057</t>
+    <t xml:space="preserve">5.99026536941528</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.96344137191772</t>
   </si>
   <si>
     <t xml:space="preserve">5.92108774185181</t>
@@ -2621,79 +2621,79 @@
     <t xml:space="preserve">5.80249643325806</t>
   </si>
   <si>
-    <t xml:space="preserve">5.92205142974854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.02327013015747</t>
+    <t xml:space="preserve">5.92205238342285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.02327156066895</t>
   </si>
   <si>
     <t xml:space="preserve">5.75628709793091</t>
   </si>
   <si>
-    <t xml:space="preserve">5.79736185073853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.68147230148315</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.85457277297974</t>
+    <t xml:space="preserve">5.79736137390137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.68147325515747</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.85457181930542</t>
   </si>
   <si>
     <t xml:space="preserve">5.67707204818726</t>
   </si>
   <si>
-    <t xml:space="preserve">5.68734121322632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.71227931976318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.80469655990601</t>
+    <t xml:space="preserve">5.68734073638916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.71227836608887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.80469703674316</t>
   </si>
   <si>
     <t xml:space="preserve">5.77242374420166</t>
   </si>
   <si>
-    <t xml:space="preserve">5.72694778442383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.59199047088623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.64039850234985</t>
+    <t xml:space="preserve">5.72694873809814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.59198999404907</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.64039897918701</t>
   </si>
   <si>
     <t xml:space="preserve">5.74748563766479</t>
   </si>
   <si>
-    <t xml:space="preserve">5.72548055648804</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.75042009353638</t>
+    <t xml:space="preserve">5.72548151016235</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.75041961669922</t>
   </si>
   <si>
     <t xml:space="preserve">5.76655578613281</t>
   </si>
   <si>
-    <t xml:space="preserve">6.00420045852661</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.04820966720581</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.10248565673828</t>
+    <t xml:space="preserve">6.00420093536377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.04821014404297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.10248613357544</t>
   </si>
   <si>
     <t xml:space="preserve">6.0056676864624</t>
   </si>
   <si>
-    <t xml:space="preserve">5.97632837295532</t>
+    <t xml:space="preserve">5.97632789611816</t>
   </si>
   <si>
     <t xml:space="preserve">5.82670021057129</t>
   </si>
   <si>
-    <t xml:space="preserve">5.79442834854126</t>
+    <t xml:space="preserve">5.7944278717041</t>
   </si>
   <si>
     <t xml:space="preserve">5.7797589302063</t>
@@ -2702,124 +2702,124 @@
     <t xml:space="preserve">5.58172082901001</t>
   </si>
   <si>
-    <t xml:space="preserve">5.68587398529053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.79149389266968</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.8311014175415</t>
+    <t xml:space="preserve">5.68587350845337</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.79149436950684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.83110094070435</t>
   </si>
   <si>
     <t xml:space="preserve">5.82963418960571</t>
   </si>
   <si>
-    <t xml:space="preserve">5.73868370056152</t>
+    <t xml:space="preserve">5.73868417739868</t>
   </si>
   <si>
     <t xml:space="preserve">5.78415966033936</t>
   </si>
   <si>
-    <t xml:space="preserve">5.88537836074829</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.97926235198975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.97192811965942</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.90004730224609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.87510919570923</t>
+    <t xml:space="preserve">5.88537788391113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.97926378250122</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.97192764282227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.90004777908325</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.87511014938354</t>
   </si>
   <si>
     <t xml:space="preserve">5.78269195556641</t>
   </si>
   <si>
-    <t xml:space="preserve">5.76362180709839</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.82376623153687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.72401475906372</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.80176305770874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.8208327293396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.7533540725708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.7577543258667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.67267179489136</t>
+    <t xml:space="preserve">5.76362133026123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.82376670837402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.72401428222656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.80176258087158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.82083225250244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.75335311889648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.75775384902954</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.67267227172852</t>
   </si>
   <si>
     <t xml:space="preserve">5.63013029098511</t>
   </si>
   <si>
-    <t xml:space="preserve">5.64186573028564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.83696937561035</t>
+    <t xml:space="preserve">5.64186429977417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.83696985244751</t>
   </si>
   <si>
     <t xml:space="preserve">5.71668004989624</t>
   </si>
   <si>
-    <t xml:space="preserve">5.85310554504395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.8428373336792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.84577035903931</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.81203079223633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.69320821762085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.49517202377319</t>
+    <t xml:space="preserve">5.8531060218811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.84283781051636</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.84577083587646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.81203174591064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.69320869445801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.49517059326172</t>
   </si>
   <si>
     <t xml:space="preserve">5.57291889190674</t>
   </si>
   <si>
-    <t xml:space="preserve">5.6183934211731</t>
+    <t xml:space="preserve">5.61839437484741</t>
   </si>
   <si>
     <t xml:space="preserve">5.60665941238403</t>
   </si>
   <si>
-    <t xml:space="preserve">5.56411743164062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.66973733901978</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.55678367614746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.55091619491577</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.50984144210815</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.54211330413818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.9323205947876</t>
+    <t xml:space="preserve">5.56411790847778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.66973781585693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.55678176879883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.5509147644043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.50984001159668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.5421142578125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.93232107162476</t>
   </si>
   <si>
     <t xml:space="preserve">5.88097715377808</t>
@@ -2828,31 +2828,31 @@
     <t xml:space="preserve">5.87804412841797</t>
   </si>
   <si>
-    <t xml:space="preserve">5.87951135635376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.89271306991577</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.89418077468872</t>
+    <t xml:space="preserve">5.87951040267944</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.89271259307861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.89418029785156</t>
   </si>
   <si>
     <t xml:space="preserve">5.59932422637939</t>
   </si>
   <si>
-    <t xml:space="preserve">5.66827011108398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.67560529708862</t>
+    <t xml:space="preserve">5.6682710647583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.67560482025146</t>
   </si>
   <si>
     <t xml:space="preserve">5.56998491287231</t>
   </si>
   <si>
-    <t xml:space="preserve">5.57878637313843</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.56851816177368</t>
+    <t xml:space="preserve">5.57878732681274</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.568519115448</t>
   </si>
   <si>
     <t xml:space="preserve">5.47903490066528</t>
@@ -2864,79 +2864,79 @@
     <t xml:space="preserve">5.21058416366577</t>
   </si>
   <si>
-    <t xml:space="preserve">5.14017152786255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.13430261611938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.25752687454224</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.30740308761597</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.47463417053223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.65506792068481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.56265115737915</t>
+    <t xml:space="preserve">5.14017057418823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.13430309295654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.25752735137939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.30740165710449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.47463321685791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.65506744384766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.56265068054199</t>
   </si>
   <si>
     <t xml:space="preserve">5.75922155380249</t>
   </si>
   <si>
-    <t xml:space="preserve">5.90151453018188</t>
+    <t xml:space="preserve">5.90151405334473</t>
   </si>
   <si>
     <t xml:space="preserve">5.85897350311279</t>
   </si>
   <si>
-    <t xml:space="preserve">6.0364727973938</t>
+    <t xml:space="preserve">6.03647327423096</t>
   </si>
   <si>
     <t xml:space="preserve">6.23744487762451</t>
   </si>
   <si>
-    <t xml:space="preserve">6.3181266784668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.42521286010742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.49415969848633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.39440822601318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.4282021522522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.5731782913208</t>
+    <t xml:space="preserve">6.31812763214111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.42521381378174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.49416065216064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.39440774917603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.42820310592651</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.57317686080933</t>
   </si>
   <si>
     <t xml:space="preserve">6.51040506362915</t>
   </si>
   <si>
-    <t xml:space="preserve">6.57616662979126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.38485956192017</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.43567657470703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.33254909515381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.35496854782104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.28322792053223</t>
+    <t xml:space="preserve">6.57616710662842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.38485908508301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.43567609786987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.33254957199097</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.35496759414673</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.28322839736938</t>
   </si>
   <si>
     <t xml:space="preserve">6.27276659011841</t>
@@ -2951,58 +2951,58 @@
     <t xml:space="preserve">6.23988580703735</t>
   </si>
   <si>
-    <t xml:space="preserve">6.23540163040161</t>
+    <t xml:space="preserve">6.23540210723877</t>
   </si>
   <si>
     <t xml:space="preserve">6.33553838729858</t>
   </si>
   <si>
-    <t xml:space="preserve">6.26977777481079</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.24586343765259</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.10238409042358</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.22792816162109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.25333642959595</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.21746635437012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.23390626907349</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.19355392456055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.38187074661255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.51488924026489</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.42222499847412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.37738752365112</t>
+    <t xml:space="preserve">6.26977729797363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.24586296081543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.10238456726074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.22792863845825</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.25333690643311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.21746683120728</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.23390674591064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.19355344772339</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.38187122344971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.51488876342773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.4222240447998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.37738656997681</t>
   </si>
   <si>
     <t xml:space="preserve">6.30265760421753</t>
   </si>
   <si>
-    <t xml:space="preserve">6.24138021469116</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.26230478286743</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.20999383926392</t>
+    <t xml:space="preserve">6.24137926101685</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.26230430603027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.20999431610107</t>
   </si>
   <si>
     <t xml:space="preserve">6.27426052093506</t>
@@ -3011,10 +3011,10 @@
     <t xml:space="preserve">6.21597242355347</t>
   </si>
   <si>
-    <t xml:space="preserve">6.17860746383667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.13377046585083</t>
+    <t xml:space="preserve">6.17860651016235</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.13376951217651</t>
   </si>
   <si>
     <t xml:space="preserve">6.24885368347168</t>
@@ -3023,139 +3023,139 @@
     <t xml:space="preserve">6.09789991378784</t>
   </si>
   <si>
-    <t xml:space="preserve">6.15319967269897</t>
+    <t xml:space="preserve">6.15319919586182</t>
   </si>
   <si>
     <t xml:space="preserve">6.03512763977051</t>
   </si>
   <si>
-    <t xml:space="preserve">6.19803667068481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.18757390975952</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.6284761428833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.73459196090698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.8900294303894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.06639003753662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.15158033370972</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.10973262786865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.21136379241943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.2322883605957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.30103921890259</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.21286106109619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.08581972122192</t>
+    <t xml:space="preserve">6.19803714752197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.187575340271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.62847709655762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.7345929145813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.89003038406372</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.06639099121094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.15158081054688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.10973310470581</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.21136474609375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.23228979110718</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.3010401725769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.21285915374756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.08581876754761</t>
   </si>
   <si>
     <t xml:space="preserve">6.9528021812439</t>
   </si>
   <si>
-    <t xml:space="preserve">7.02304649353027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.20688056945801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.12019491195679</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.13663482666016</t>
+    <t xml:space="preserve">7.02304697036743</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.20688199996948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.12019443511963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.13663530349731</t>
   </si>
   <si>
     <t xml:space="preserve">7.1799783706665</t>
   </si>
   <si>
-    <t xml:space="preserve">7.02753067016602</t>
+    <t xml:space="preserve">7.02753019332886</t>
   </si>
   <si>
     <t xml:space="preserve">7.34438228607178</t>
   </si>
   <si>
-    <t xml:space="preserve">7.38025236129761</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.43555307388306</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.45348739624023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.36082315444946</t>
+    <t xml:space="preserve">7.38025283813477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.43555164337158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.45348644256592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.36082220077515</t>
   </si>
   <si>
     <t xml:space="preserve">7.50280857086182</t>
   </si>
   <si>
-    <t xml:space="preserve">7.57753753662109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.64479398727417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.61116552352905</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.67842149734497</t>
+    <t xml:space="preserve">7.57753801345825</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.64479351043701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.61116504669189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.67842054367065</t>
   </si>
   <si>
     <t xml:space="preserve">7.63358449935913</t>
   </si>
   <si>
-    <t xml:space="preserve">7.7979884147644</t>
+    <t xml:space="preserve">7.79798936843872</t>
   </si>
   <si>
     <t xml:space="preserve">7.75688743591309</t>
   </si>
   <si>
-    <t xml:space="preserve">7.81293487548828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.72699689865112</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.8502984046936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.78304243087769</t>
+    <t xml:space="preserve">7.81293439865112</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.72699594497681</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.85029888153076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.78304290771484</t>
   </si>
   <si>
     <t xml:space="preserve">7.82414436340332</t>
   </si>
   <si>
-    <t xml:space="preserve">7.81666994094849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.88392686843872</t>
+    <t xml:space="preserve">7.81667137145996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.88392639160156</t>
   </si>
   <si>
     <t xml:space="preserve">8.05580425262451</t>
   </si>
   <si>
-    <t xml:space="preserve">8.11184978485107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.10064315795898</t>
+    <t xml:space="preserve">8.11185073852539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.10064220428467</t>
   </si>
   <si>
     <t xml:space="preserve">8.15295219421387</t>
@@ -3164,52 +3164,52 @@
     <t xml:space="preserve">8.17537021636963</t>
   </si>
   <si>
-    <t xml:space="preserve">8.16416263580322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.04833221435547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.06701374053955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.05953884124756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.96986484527588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.96239280700684</t>
+    <t xml:space="preserve">8.16416168212891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.04833030700684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.06701183319092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.05954074859619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.96986627578735</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.96239328384399</t>
   </si>
   <si>
     <t xml:space="preserve">8.05206775665283</t>
   </si>
   <si>
-    <t xml:space="preserve">8.04086017608643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.93250274658203</t>
+    <t xml:space="preserve">8.04085731506348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.93250131607056</t>
   </si>
   <si>
     <t xml:space="preserve">7.92876529693604</t>
   </si>
   <si>
-    <t xml:space="preserve">8.10811424255371</t>
+    <t xml:space="preserve">8.10811614990234</t>
   </si>
   <si>
     <t xml:space="preserve">8.07822322845459</t>
   </si>
   <si>
-    <t xml:space="preserve">8.08943176269531</t>
+    <t xml:space="preserve">8.08943271636963</t>
   </si>
   <si>
     <t xml:space="preserve">8.16042518615723</t>
   </si>
   <si>
-    <t xml:space="preserve">8.15668964385986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.14547824859619</t>
+    <t xml:space="preserve">8.15668773651123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.14547920227051</t>
   </si>
   <si>
     <t xml:space="preserve">8.25757217407227</t>
@@ -3221,7 +3221,7 @@
     <t xml:space="preserve">8.16789722442627</t>
   </si>
   <si>
-    <t xml:space="preserve">8.22020721435547</t>
+    <t xml:space="preserve">8.2202091217041</t>
   </si>
   <si>
     <t xml:space="preserve">8.38834857940674</t>
@@ -3233,7 +3233,7 @@
     <t xml:space="preserve">8.24636268615723</t>
   </si>
   <si>
-    <t xml:space="preserve">8.25010013580322</t>
+    <t xml:space="preserve">8.25010108947754</t>
   </si>
   <si>
     <t xml:space="preserve">8.3098840713501</t>
@@ -3242,19 +3242,19 @@
     <t xml:space="preserve">8.43692302703857</t>
   </si>
   <si>
-    <t xml:space="preserve">8.42571353912354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.3920841217041</t>
+    <t xml:space="preserve">8.42571258544922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.39208507537842</t>
   </si>
   <si>
     <t xml:space="preserve">8.46307849884033</t>
   </si>
   <si>
-    <t xml:space="preserve">8.5938549041748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.74331092834473</t>
+    <t xml:space="preserve">8.59385395050049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.74331188201904</t>
   </si>
   <si>
     <t xml:space="preserve">8.62748336791992</t>
@@ -3263,79 +3263,79 @@
     <t xml:space="preserve">8.53407001495361</t>
   </si>
   <si>
-    <t xml:space="preserve">8.58638191223145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.59759140014648</t>
+    <t xml:space="preserve">8.58638000488281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.59759044647217</t>
   </si>
   <si>
     <t xml:space="preserve">8.64242744445801</t>
   </si>
   <si>
-    <t xml:space="preserve">8.81804180145264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.90024280548096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.01233863830566</t>
+    <t xml:space="preserve">8.81804084777832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.90024471282959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.01233768463135</t>
   </si>
   <si>
     <t xml:space="preserve">9.02728271484375</t>
   </si>
   <si>
-    <t xml:space="preserve">8.95628833770752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.97871112823486</t>
+    <t xml:space="preserve">8.95629024505615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.97871017456055</t>
   </si>
   <si>
     <t xml:space="preserve">8.95255374908447</t>
   </si>
   <si>
-    <t xml:space="preserve">9.01981067657471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.9637622833252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.73957633972168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.85025119781494</t>
+    <t xml:space="preserve">9.01980972290039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.96376323699951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.73957538604736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.85025215148926</t>
   </si>
   <si>
     <t xml:space="preserve">8.73112106323242</t>
   </si>
   <si>
-    <t xml:space="preserve">8.62736320495605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.78107833862305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.75417900085449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.6119909286499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.57356071472168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.56972026824951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.66963291168213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.59277820587158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.71574974060059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.58509159088135</t>
+    <t xml:space="preserve">8.62736129760742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.78107929229736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.75417995452881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.61199188232422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.573561668396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.56971836090088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.66963386535645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.59277629852295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.71574878692627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.58509063720703</t>
   </si>
   <si>
     <t xml:space="preserve">8.61967658996582</t>
@@ -3344,16 +3344,16 @@
     <t xml:space="preserve">8.3199291229248</t>
   </si>
   <si>
-    <t xml:space="preserve">8.45058917999268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.48133182525635</t>
+    <t xml:space="preserve">8.45058822631836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.48133277893066</t>
   </si>
   <si>
     <t xml:space="preserve">8.47748756408691</t>
   </si>
   <si>
-    <t xml:space="preserve">8.44674396514893</t>
+    <t xml:space="preserve">8.44674491882324</t>
   </si>
   <si>
     <t xml:space="preserve">8.33145809173584</t>
@@ -3362,31 +3362,31 @@
     <t xml:space="preserve">8.35835838317871</t>
   </si>
   <si>
-    <t xml:space="preserve">8.07398223876953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.15468215942383</t>
+    <t xml:space="preserve">8.07398128509521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.15468311309814</t>
   </si>
   <si>
     <t xml:space="preserve">8.41215896606445</t>
   </si>
   <si>
-    <t xml:space="preserve">8.53897380828857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.61583518981934</t>
+    <t xml:space="preserve">8.53897476196289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.61583423614502</t>
   </si>
   <si>
     <t xml:space="preserve">8.6850061416626</t>
   </si>
   <si>
-    <t xml:space="preserve">8.60046291351318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.58124732971191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.55050373077393</t>
+    <t xml:space="preserve">8.60046195983887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.5812463760376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.55050277709961</t>
   </si>
   <si>
     <t xml:space="preserve">8.7272777557373</t>
@@ -3395,10 +3395,10 @@
     <t xml:space="preserve">8.85793685913086</t>
   </si>
   <si>
-    <t xml:space="preserve">8.90020942687988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.93479824066162</t>
+    <t xml:space="preserve">8.9002103805542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.93479633331299</t>
   </si>
   <si>
     <t xml:space="preserve">9.00781059265137</t>
@@ -3407,10 +3407,10 @@
     <t xml:space="preserve">9.02702617645264</t>
   </si>
   <si>
-    <t xml:space="preserve">8.98091220855713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.92326641082764</t>
+    <t xml:space="preserve">8.98091125488281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.92326736450195</t>
   </si>
   <si>
     <t xml:space="preserve">8.87331008911133</t>
@@ -3419,7 +3419,7 @@
     <t xml:space="preserve">8.94632530212402</t>
   </si>
   <si>
-    <t xml:space="preserve">8.83487987518311</t>
+    <t xml:space="preserve">8.83488082885742</t>
   </si>
   <si>
     <t xml:space="preserve">8.76955032348633</t>
@@ -3428,16 +3428,16 @@
     <t xml:space="preserve">8.96169567108154</t>
   </si>
   <si>
-    <t xml:space="preserve">8.93863868713379</t>
+    <t xml:space="preserve">8.93864059448242</t>
   </si>
   <si>
     <t xml:space="preserve">8.90789604187012</t>
   </si>
   <si>
-    <t xml:space="preserve">8.82719326019287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.86562347412109</t>
+    <t xml:space="preserve">8.82719421386719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.86562252044678</t>
   </si>
   <si>
     <t xml:space="preserve">8.91173934936523</t>
@@ -3449,7 +3449,7 @@
     <t xml:space="preserve">8.80798053741455</t>
   </si>
   <si>
-    <t xml:space="preserve">8.86946678161621</t>
+    <t xml:space="preserve">8.86946487426758</t>
   </si>
   <si>
     <t xml:space="preserve">8.88483905792236</t>
@@ -3458,82 +3458,82 @@
     <t xml:space="preserve">8.96553993225098</t>
   </si>
   <si>
-    <t xml:space="preserve">9.10772895812988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.02318286895752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.05776977539062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.13847160339355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.20380020141602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.16921520233154</t>
+    <t xml:space="preserve">9.10772800445557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.0231819152832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.05776882171631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.13847064971924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.20380115509033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.16921424865723</t>
   </si>
   <si>
     <t xml:space="preserve">9.25375938415527</t>
   </si>
   <si>
-    <t xml:space="preserve">9.03086757659912</t>
+    <t xml:space="preserve">9.03086948394775</t>
   </si>
   <si>
     <t xml:space="preserve">9.09235668182373</t>
   </si>
   <si>
-    <t xml:space="preserve">9.14999866485596</t>
+    <t xml:space="preserve">9.14999961853027</t>
   </si>
   <si>
     <t xml:space="preserve">9.11157035827637</t>
   </si>
   <si>
-    <t xml:space="preserve">9.29603099822998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.24223041534424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.35751724243164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.36136150360107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.34598827362061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.46896171569824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.50354957580566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.60730648040771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.5496654510498</t>
+    <t xml:space="preserve">9.29603004455566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.24222850799561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.35751819610596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.36136054992676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.34598922729492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.46896362304688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.50354862213135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.60730838775635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.54966449737549</t>
   </si>
   <si>
     <t xml:space="preserve">9.5189208984375</t>
   </si>
   <si>
-    <t xml:space="preserve">9.41516304016113</t>
+    <t xml:space="preserve">9.41516208648682</t>
   </si>
   <si>
     <t xml:space="preserve">9.64958000183105</t>
   </si>
   <si>
-    <t xml:space="preserve">9.61499309539795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.59577941894531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.7418098449707</t>
+    <t xml:space="preserve">9.61499404907227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.595778465271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.74181079864502</t>
   </si>
   <si>
     <t xml:space="preserve">9.65726566314697</t>
@@ -3545,43 +3545,43 @@
     <t xml:space="preserve">9.48433399200439</t>
   </si>
   <si>
-    <t xml:space="preserve">9.56503582000732</t>
+    <t xml:space="preserve">9.56503486633301</t>
   </si>
   <si>
     <t xml:space="preserve">9.53044891357422</t>
   </si>
   <si>
-    <t xml:space="preserve">9.64573669433594</t>
+    <t xml:space="preserve">9.64573764801025</t>
   </si>
   <si>
     <t xml:space="preserve">9.57656478881836</t>
   </si>
   <si>
-    <t xml:space="preserve">9.60346508026123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.56119346618652</t>
+    <t xml:space="preserve">9.60346412658691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.56119251251221</t>
   </si>
   <si>
     <t xml:space="preserve">9.46511936187744</t>
   </si>
   <si>
-    <t xml:space="preserve">9.4113187789917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.42284870147705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.33445930480957</t>
+    <t xml:space="preserve">9.41131973266602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.42284774780273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.3344612121582</t>
   </si>
   <si>
     <t xml:space="preserve">9.27297306060791</t>
   </si>
   <si>
-    <t xml:space="preserve">9.25345802307129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.17930698394775</t>
+    <t xml:space="preserve">9.25345993041992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.17930603027344</t>
   </si>
   <si>
     <t xml:space="preserve">9.15198802947998</t>
@@ -3590,7 +3590,7 @@
     <t xml:space="preserve">9.01539039611816</t>
   </si>
   <si>
-    <t xml:space="preserve">8.64462757110596</t>
+    <t xml:space="preserve">8.64462852478027</t>
   </si>
   <si>
     <t xml:space="preserve">8.73829364776611</t>
@@ -3599,25 +3599,25 @@
     <t xml:space="preserve">8.69536399841309</t>
   </si>
   <si>
-    <t xml:space="preserve">8.85928058624268</t>
+    <t xml:space="preserve">8.85928153991699</t>
   </si>
   <si>
     <t xml:space="preserve">8.7656135559082</t>
   </si>
   <si>
-    <t xml:space="preserve">8.69926738739014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.73048877716064</t>
+    <t xml:space="preserve">8.69926643371582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.73048782348633</t>
   </si>
   <si>
     <t xml:space="preserve">8.85147476196289</t>
   </si>
   <si>
-    <t xml:space="preserve">8.72658729553223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.66414070129395</t>
+    <t xml:space="preserve">8.72658538818359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.66414260864258</t>
   </si>
   <si>
     <t xml:space="preserve">8.62511348724365</t>
@@ -3626,13 +3626,13 @@
     <t xml:space="preserve">8.6290168762207</t>
   </si>
   <si>
-    <t xml:space="preserve">8.64852905273438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.68755912780762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.75000381469727</t>
+    <t xml:space="preserve">8.64853096008301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.6875581741333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.75000286102295</t>
   </si>
   <si>
     <t xml:space="preserve">8.76171112060547</t>
@@ -3641,13 +3641,13 @@
     <t xml:space="preserve">8.56266975402832</t>
   </si>
   <si>
-    <t xml:space="preserve">8.70317077636719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.78903007507324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.86708545684814</t>
+    <t xml:space="preserve">8.70316791534424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.78903102874756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.86708450317383</t>
   </si>
   <si>
     <t xml:space="preserve">8.94514179229736</t>
@@ -3659,7 +3659,7 @@
     <t xml:space="preserve">8.99977970123291</t>
   </si>
   <si>
-    <t xml:space="preserve">9.00758457183838</t>
+    <t xml:space="preserve">9.0075855255127</t>
   </si>
   <si>
     <t xml:space="preserve">9.13637638092041</t>
@@ -3668,13 +3668,13 @@
     <t xml:space="preserve">9.14808464050293</t>
   </si>
   <si>
-    <t xml:space="preserve">9.18321132659912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.1051549911499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.13247299194336</t>
+    <t xml:space="preserve">9.18320941925049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.10515403747559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.13247394561768</t>
   </si>
   <si>
     <t xml:space="preserve">9.15979385375977</t>
@@ -3683,16 +3683,16 @@
     <t xml:space="preserve">9.09734916687012</t>
   </si>
   <si>
-    <t xml:space="preserve">9.05441856384277</t>
+    <t xml:space="preserve">9.05441951751709</t>
   </si>
   <si>
     <t xml:space="preserve">9.06222343444824</t>
   </si>
   <si>
-    <t xml:space="preserve">9.02709865570068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.0466136932373</t>
+    <t xml:space="preserve">9.027099609375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.04661273956299</t>
   </si>
   <si>
     <t xml:space="preserve">9.12076568603516</t>
@@ -3710,19 +3710,19 @@
     <t xml:space="preserve">9.01148796081543</t>
   </si>
   <si>
-    <t xml:space="preserve">8.90220928192139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.31200218200684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.3198070526123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.50022506713867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.55486392974854</t>
+    <t xml:space="preserve">8.9022102355957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.31200122833252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.31980514526367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.50022602081299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.55486583709717</t>
   </si>
   <si>
     <t xml:space="preserve">8.59389209747314</t>
@@ -3740,43 +3740,43 @@
     <t xml:space="preserve">8.69146156311035</t>
   </si>
   <si>
-    <t xml:space="preserve">8.61340618133545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.40265464782715</t>
+    <t xml:space="preserve">8.61340522766113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.4026575088501</t>
   </si>
   <si>
     <t xml:space="preserve">8.37143421173096</t>
   </si>
   <si>
-    <t xml:space="preserve">8.30118370056152</t>
+    <t xml:space="preserve">8.30118465423584</t>
   </si>
   <si>
     <t xml:space="preserve">7.836754322052</t>
   </si>
   <si>
-    <t xml:space="preserve">8.09433841705322</t>
+    <t xml:space="preserve">8.09433746337891</t>
   </si>
   <si>
     <t xml:space="preserve">8.02018451690674</t>
   </si>
   <si>
-    <t xml:space="preserve">7.6962571144104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.68376684188843</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.57605123519897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.08742427825928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.93443536758423</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.25602388381958</t>
+    <t xml:space="preserve">7.69625568389893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.68376636505127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.57605075836182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.0874228477478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.93443489074707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.25602340698242</t>
   </si>
   <si>
     <t xml:space="preserve">7.89919948577881</t>
@@ -3785,37 +3785,37 @@
     <t xml:space="preserve">7.49955654144287</t>
   </si>
   <si>
-    <t xml:space="preserve">7.54482746124268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.74933290481567</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.70718288421631</t>
+    <t xml:space="preserve">7.54482841491699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.74933385848999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.70718336105347</t>
   </si>
   <si>
     <t xml:space="preserve">8.05531024932861</t>
   </si>
   <si>
-    <t xml:space="preserve">7.88749122619629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.86407518386841</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.89529705047607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.10214328765869</t>
+    <t xml:space="preserve">7.88748979568481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.86407566070557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.89529657363892</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.10214424133301</t>
   </si>
   <si>
     <t xml:space="preserve">8.09043502807617</t>
   </si>
   <si>
-    <t xml:space="preserve">8.23483753204346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.12556076049805</t>
+    <t xml:space="preserve">8.23483657836914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.12555885314941</t>
   </si>
   <si>
     <t xml:space="preserve">8.2192268371582</t>
@@ -3827,73 +3827,73 @@
     <t xml:space="preserve">8.25435066223145</t>
   </si>
   <si>
-    <t xml:space="preserve">8.11775398254395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.99676895141602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.82504606246948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.70562219619751</t>
+    <t xml:space="preserve">8.11775493621826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.99676990509033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.82504653930664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.70562267303467</t>
   </si>
   <si>
     <t xml:space="preserve">7.85626840591431</t>
   </si>
   <si>
-    <t xml:space="preserve">7.79304361343384</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.67596006393433</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.59790658950806</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.65878915786743</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.53546333312988</t>
+    <t xml:space="preserve">7.793044090271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.67596101760864</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.5979061126709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.65879011154175</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.53546190261841</t>
   </si>
   <si>
     <t xml:space="preserve">7.73372220993042</t>
   </si>
   <si>
-    <t xml:space="preserve">7.70874404907227</t>
+    <t xml:space="preserve">7.70874500274658</t>
   </si>
   <si>
     <t xml:space="preserve">7.57292795181274</t>
   </si>
   <si>
-    <t xml:space="preserve">7.35905694961548</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.26070642471313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.23729038238525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.28412389755249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.32002830505371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.24665689468384</t>
+    <t xml:space="preserve">7.35905742645264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.26070690155029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.2372899055481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.28412342071533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.32002925872803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.246657371521</t>
   </si>
   <si>
     <t xml:space="preserve">7.18889617919922</t>
   </si>
   <si>
-    <t xml:space="preserve">7.13269662857056</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.02654027938843</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.84389162063599</t>
+    <t xml:space="preserve">7.13269519805908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.02654075622559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.84389114379883</t>
   </si>
   <si>
     <t xml:space="preserve">7.0062460899353</t>
@@ -3902,22 +3902,22 @@
     <t xml:space="preserve">7.16860151290894</t>
   </si>
   <si>
-    <t xml:space="preserve">7.3934006690979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.54794979095459</t>
+    <t xml:space="preserve">7.39340114593506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.54795074462891</t>
   </si>
   <si>
     <t xml:space="preserve">7.44179582595825</t>
   </si>
   <si>
-    <t xml:space="preserve">7.51204538345337</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.46677207946777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.44023370742798</t>
+    <t xml:space="preserve">7.51204395294189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.46677350997925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.44023466110229</t>
   </si>
   <si>
     <t xml:space="preserve">7.41837882995605</t>
@@ -3926,37 +3926,37 @@
     <t xml:space="preserve">7.56356143951416</t>
   </si>
   <si>
-    <t xml:space="preserve">7.43555116653442</t>
+    <t xml:space="preserve">7.43555068969727</t>
   </si>
   <si>
     <t xml:space="preserve">7.55887842178345</t>
   </si>
   <si>
-    <t xml:space="preserve">7.6119556427002</t>
+    <t xml:space="preserve">7.61195659637451</t>
   </si>
   <si>
     <t xml:space="preserve">7.75245571136475</t>
   </si>
   <si>
-    <t xml:space="preserve">7.92261648178101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.82114458084106</t>
+    <t xml:space="preserve">7.92261505126953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.82114410400391</t>
   </si>
   <si>
     <t xml:space="preserve">7.81724119186401</t>
   </si>
   <si>
-    <t xml:space="preserve">7.74308919906616</t>
+    <t xml:space="preserve">7.743088722229</t>
   </si>
   <si>
     <t xml:space="preserve">7.89139366149902</t>
   </si>
   <si>
-    <t xml:space="preserve">7.87578392028809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.76650524139404</t>
+    <t xml:space="preserve">7.87578296661377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.76650476455688</t>
   </si>
   <si>
     <t xml:space="preserve">7.14362382888794</t>
@@ -3965,58 +3965,58 @@
     <t xml:space="preserve">6.90477514266968</t>
   </si>
   <si>
-    <t xml:space="preserve">7.11708545684814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.35125160217285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.98595094680786</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.02185773849487</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.18777847290039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.12729597091675</t>
+    <t xml:space="preserve">7.1170859336853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.35125112533569</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.98595142364502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.02185821533203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.18777942657471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.12729549407959</t>
   </si>
   <si>
     <t xml:space="preserve">7.15998983383179</t>
   </si>
   <si>
-    <t xml:space="preserve">7.10441064834595</t>
+    <t xml:space="preserve">7.10440969467163</t>
   </si>
   <si>
     <t xml:space="preserve">7.31201696395874</t>
   </si>
   <si>
-    <t xml:space="preserve">7.2760534286499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.42154264450073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.36596202850342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.28422689437866</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.28749561309814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.28095722198486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.98834562301636</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.03248262405396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.21393585205078</t>
+    <t xml:space="preserve">7.27605438232422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.42154121398926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.36596250534058</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.2842264175415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.28749656677246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.28095865249634</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.98834609985352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.03248310089111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.21393489837646</t>
   </si>
   <si>
     <t xml:space="preserve">7.10114049911499</t>
@@ -4025,49 +4025,49 @@
     <t xml:space="preserve">6.96709537506104</t>
   </si>
   <si>
-    <t xml:space="preserve">6.99815511703491</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.85103130340576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.50284004211426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.66794490814209</t>
+    <t xml:space="preserve">6.9981541633606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.8510308265686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.5028395652771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.66794443130493</t>
   </si>
   <si>
     <t xml:space="preserve">6.79381704330444</t>
   </si>
   <si>
-    <t xml:space="preserve">7.01940488815308</t>
+    <t xml:space="preserve">7.01940536499023</t>
   </si>
   <si>
     <t xml:space="preserve">6.86410808563232</t>
   </si>
   <si>
-    <t xml:space="preserve">6.5289945602417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.61563396453857</t>
+    <t xml:space="preserve">6.52899551391602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.61563444137573</t>
   </si>
   <si>
     <t xml:space="preserve">6.64342403411865</t>
   </si>
   <si>
-    <t xml:space="preserve">6.62871122360229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.64015436172485</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.5845742225647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.67775297164917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.74314117431641</t>
+    <t xml:space="preserve">6.62871170043945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.64015483856201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.58457469940186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.67775344848633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.74314069747925</t>
   </si>
   <si>
     <t xml:space="preserve">6.66140556335449</t>
@@ -4076,61 +4076,61 @@
     <t xml:space="preserve">6.77419996261597</t>
   </si>
   <si>
-    <t xml:space="preserve">6.85266590118408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.92949724197388</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.86574363708496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.8281455039978</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.86901330947876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.97036361694336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.97690343856812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.91805267333984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.82651090621948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.70227336883545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.53226470947266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.63198184967041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.59928798675537</t>
+    <t xml:space="preserve">6.85266637802124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.92949676513672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.86574411392212</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.82814598083496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.86901235580444</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.97036409378052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.97690296173096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.91805410385132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.82651042938232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.70227289199829</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.5322642326355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.63198137283325</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.59928703308105</t>
   </si>
   <si>
     <t xml:space="preserve">6.57803678512573</t>
   </si>
   <si>
-    <t xml:space="preserve">6.42927885055542</t>
+    <t xml:space="preserve">6.42927932739258</t>
   </si>
   <si>
     <t xml:space="preserve">6.34754276275635</t>
   </si>
   <si>
-    <t xml:space="preserve">6.4946665763855</t>
+    <t xml:space="preserve">6.49466609954834</t>
   </si>
   <si>
     <t xml:space="preserve">6.44562530517578</t>
   </si>
   <si>
-    <t xml:space="preserve">6.62053871154785</t>
+    <t xml:space="preserve">6.62053823471069</t>
   </si>
   <si>
     <t xml:space="preserve">6.44889450073242</t>
@@ -4139,13 +4139,13 @@
     <t xml:space="preserve">6.52245616912842</t>
   </si>
   <si>
-    <t xml:space="preserve">6.54043769836426</t>
+    <t xml:space="preserve">6.54043817520142</t>
   </si>
   <si>
     <t xml:space="preserve">6.60909557342529</t>
   </si>
   <si>
-    <t xml:space="preserve">6.71044731140137</t>
+    <t xml:space="preserve">6.71044635772705</t>
   </si>
   <si>
     <t xml:space="preserve">6.80035543441772</t>
@@ -4154,37 +4154,37 @@
     <t xml:space="preserve">6.8134331703186</t>
   </si>
   <si>
-    <t xml:space="preserve">6.86737871170044</t>
+    <t xml:space="preserve">6.86737823486328</t>
   </si>
   <si>
     <t xml:space="preserve">6.76112270355225</t>
   </si>
   <si>
-    <t xml:space="preserve">6.79054641723633</t>
+    <t xml:space="preserve">6.79054689407349</t>
   </si>
   <si>
     <t xml:space="preserve">6.64832782745361</t>
   </si>
   <si>
-    <t xml:space="preserve">6.64505910873413</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.45379877090454</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.51918697357178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.38350677490234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.3916802406311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.25926876068115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.36715984344482</t>
+    <t xml:space="preserve">6.64505863189697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.4537992477417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.51918745040894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.38350629806519</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.39167976379395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.25926923751831</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.36715936660767</t>
   </si>
   <si>
     <t xml:space="preserve">6.49793577194214</t>
@@ -4196,22 +4196,22 @@
     <t xml:space="preserve">6.59274816513062</t>
   </si>
   <si>
-    <t xml:space="preserve">6.48158884048462</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.39331483840942</t>
+    <t xml:space="preserve">6.48158836364746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.39331579208374</t>
   </si>
   <si>
     <t xml:space="preserve">6.40802717208862</t>
   </si>
   <si>
-    <t xml:space="preserve">6.26090383529663</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.36389064788818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.46033763885498</t>
+    <t xml:space="preserve">6.26090431213379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.36388969421387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.46033716201782</t>
   </si>
   <si>
     <t xml:space="preserve">6.62217330932617</t>
@@ -4220,7 +4220,7 @@
     <t xml:space="preserve">6.86247396469116</t>
   </si>
   <si>
-    <t xml:space="preserve">6.824875831604</t>
+    <t xml:space="preserve">6.82487630844116</t>
   </si>
   <si>
     <t xml:space="preserve">6.80198955535889</t>
@@ -4232,25 +4232,25 @@
     <t xml:space="preserve">6.8918981552124</t>
   </si>
   <si>
-    <t xml:space="preserve">6.95565176010132</t>
+    <t xml:space="preserve">6.95565223693848</t>
   </si>
   <si>
     <t xml:space="preserve">7.02103996276855</t>
   </si>
   <si>
-    <t xml:space="preserve">7.22701263427734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.17143249511719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.20903062820435</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.23028230667114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.19268417358398</t>
+    <t xml:space="preserve">7.22701215744019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.17143201828003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.2090311050415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.23028182983398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.19268321990967</t>
   </si>
   <si>
     <t xml:space="preserve">7.14854621887207</t>
@@ -4259,19 +4259,19 @@
     <t xml:space="preserve">7.37740421295166</t>
   </si>
   <si>
-    <t xml:space="preserve">7.50327682495117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.54904794692993</t>
+    <t xml:space="preserve">7.50327730178833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.54904842376709</t>
   </si>
   <si>
     <t xml:space="preserve">7.64222621917725</t>
   </si>
   <si>
-    <t xml:space="preserve">7.97243595123291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.87762403488159</t>
+    <t xml:space="preserve">7.97243499755859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.87762308120728</t>
   </si>
   <si>
     <t xml:space="preserve">7.93156814575195</t>
@@ -4280,52 +4280,52 @@
     <t xml:space="preserve">7.96099328994751</t>
   </si>
   <si>
-    <t xml:space="preserve">7.86618041992188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.81223630905151</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.8498330116272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.81473779678345</t>
+    <t xml:space="preserve">7.86617946624756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.81223487854004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.84983348846436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.81473684310913</t>
   </si>
   <si>
     <t xml:space="preserve">7.77796936035156</t>
   </si>
   <si>
-    <t xml:space="preserve">7.85818958282471</t>
+    <t xml:space="preserve">7.85818910598755</t>
   </si>
   <si>
     <t xml:space="preserve">7.75624322891235</t>
   </si>
   <si>
-    <t xml:space="preserve">7.89328479766846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.80303859710693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.87323045730591</t>
+    <t xml:space="preserve">7.89328670501709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.80303955078125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.87323141098022</t>
   </si>
   <si>
     <t xml:space="preserve">7.84314823150635</t>
   </si>
   <si>
-    <t xml:space="preserve">7.89662885665894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.87657356262207</t>
+    <t xml:space="preserve">7.8966269493103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.87657260894775</t>
   </si>
   <si>
     <t xml:space="preserve">7.80972385406494</t>
   </si>
   <si>
-    <t xml:space="preserve">7.90498399734497</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.76292896270752</t>
+    <t xml:space="preserve">7.90498495101929</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.7629280090332</t>
   </si>
   <si>
     <t xml:space="preserve">7.83479309082031</t>
@@ -4337,22 +4337,22 @@
     <t xml:space="preserve">7.93172407150269</t>
   </si>
   <si>
-    <t xml:space="preserve">7.9333963394165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.51892757415771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.56070899963379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.56739282608032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.69775009155273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.76125717163086</t>
+    <t xml:space="preserve">7.93339538574219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.51892709732056</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.56070804595947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.56739377975464</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.69774913787842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.76125812530518</t>
   </si>
   <si>
     <t xml:space="preserve">7.69607925415039</t>
@@ -4361,16 +4361,16 @@
     <t xml:space="preserve">7.70443534851074</t>
   </si>
   <si>
-    <t xml:space="preserve">7.71446323394775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.64426946640015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.72950458526611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.6258864402771</t>
+    <t xml:space="preserve">7.71446371078491</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.64427042007446</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.7295036315918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.62588739395142</t>
   </si>
   <si>
     <t xml:space="preserve">7.86487436294556</t>
@@ -4379,7 +4379,7 @@
     <t xml:space="preserve">8.06041049957275</t>
   </si>
   <si>
-    <t xml:space="preserve">7.94843769073486</t>
+    <t xml:space="preserve">7.94843673706055</t>
   </si>
   <si>
     <t xml:space="preserve">8.02698612213135</t>
@@ -4388,19 +4388,19 @@
     <t xml:space="preserve">8.01194381713867</t>
   </si>
   <si>
-    <t xml:space="preserve">8.10553455352783</t>
+    <t xml:space="preserve">8.10553359985352</t>
   </si>
   <si>
     <t xml:space="preserve">8.0353422164917</t>
   </si>
   <si>
-    <t xml:space="preserve">8.10887718200684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.13060283660889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.17572593688965</t>
+    <t xml:space="preserve">8.10887622833252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.13060188293457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.17572689056396</t>
   </si>
   <si>
     <t xml:space="preserve">8.12391757965088</t>
@@ -4409,19 +4409,19 @@
     <t xml:space="preserve">8.16068458557129</t>
   </si>
   <si>
-    <t xml:space="preserve">7.98186111450195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.00693035125732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.04536819458008</t>
+    <t xml:space="preserve">7.98186206817627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.00693130493164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.04536914825439</t>
   </si>
   <si>
     <t xml:space="preserve">8.05372524261475</t>
   </si>
   <si>
-    <t xml:space="preserve">8.16903972625732</t>
+    <t xml:space="preserve">8.16904163360596</t>
   </si>
   <si>
     <t xml:space="preserve">8.14230155944824</t>
@@ -4430,43 +4430,43 @@
     <t xml:space="preserve">8.17739772796631</t>
   </si>
   <si>
-    <t xml:space="preserve">8.20246601104736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.51498889923096</t>
+    <t xml:space="preserve">8.20246505737305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.51498794555664</t>
   </si>
   <si>
     <t xml:space="preserve">8.42306995391846</t>
   </si>
   <si>
-    <t xml:space="preserve">8.43142700195312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.43978214263916</t>
+    <t xml:space="preserve">8.43142604827881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.43978309631348</t>
   </si>
   <si>
     <t xml:space="preserve">8.57348251342773</t>
   </si>
   <si>
-    <t xml:space="preserve">8.39800071716309</t>
+    <t xml:space="preserve">8.39800262451172</t>
   </si>
   <si>
     <t xml:space="preserve">8.51916599273682</t>
   </si>
   <si>
-    <t xml:space="preserve">8.4732084274292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.54841327667236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.54423522949219</t>
+    <t xml:space="preserve">8.47320747375488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.54841232299805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.5442361831665</t>
   </si>
   <si>
     <t xml:space="preserve">8.2793436050415</t>
   </si>
   <si>
-    <t xml:space="preserve">8.33783626556396</t>
+    <t xml:space="preserve">8.33783721923828</t>
   </si>
   <si>
     <t xml:space="preserve">8.23589038848877</t>
@@ -4475,7 +4475,7 @@
     <t xml:space="preserve">8.35287857055664</t>
   </si>
   <si>
-    <t xml:space="preserve">8.52334499359131</t>
+    <t xml:space="preserve">8.52334403991699</t>
   </si>
   <si>
     <t xml:space="preserve">8.39382362365723</t>
@@ -4484,10 +4484,10 @@
     <t xml:space="preserve">8.38964462280273</t>
   </si>
   <si>
-    <t xml:space="preserve">8.46485042572021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.61944198608398</t>
+    <t xml:space="preserve">8.46485137939453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.61944007873535</t>
   </si>
   <si>
     <t xml:space="preserve">8.56512641906738</t>
@@ -4496,13 +4496,13 @@
     <t xml:space="preserve">8.54005813598633</t>
   </si>
   <si>
-    <t xml:space="preserve">8.48156356811523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.34619331359863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.00860118865967</t>
+    <t xml:space="preserve">8.48156261444092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.34619426727295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.00860214233398</t>
   </si>
   <si>
     <t xml:space="preserve">8.13561630249023</t>
@@ -4514,13 +4514,13 @@
     <t xml:space="preserve">7.53062629699707</t>
   </si>
   <si>
-    <t xml:space="preserve">7.60917329788208</t>
+    <t xml:space="preserve">7.6091742515564</t>
   </si>
   <si>
     <t xml:space="preserve">7.86821746826172</t>
   </si>
   <si>
-    <t xml:space="preserve">7.81640768051147</t>
+    <t xml:space="preserve">7.81640958786011</t>
   </si>
   <si>
     <t xml:space="preserve">7.83144998550415</t>
@@ -4541,10 +4541,10 @@
     <t xml:space="preserve">7.79301166534424</t>
   </si>
   <si>
-    <t xml:space="preserve">7.63257169723511</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.72281837463379</t>
+    <t xml:space="preserve">7.63257217407227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.72281932830811</t>
   </si>
   <si>
     <t xml:space="preserve">7.81306600570679</t>
@@ -4556,7 +4556,7 @@
     <t xml:space="preserve">7.97517681121826</t>
   </si>
   <si>
-    <t xml:space="preserve">7.85484647750854</t>
+    <t xml:space="preserve">7.85484743118286</t>
   </si>
   <si>
     <t xml:space="preserve">7.90832614898682</t>
@@ -4565,13 +4565,13 @@
     <t xml:space="preserve">7.99188899993896</t>
   </si>
   <si>
-    <t xml:space="preserve">7.91334199905396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.00525951385498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.928382396698</t>
+    <t xml:space="preserve">7.91334104537964</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.00525760650635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.92838144302368</t>
   </si>
   <si>
     <t xml:space="preserve">7.86988925933838</t>
@@ -4592,7 +4592,7 @@
     <t xml:space="preserve">7.91835403442383</t>
   </si>
   <si>
-    <t xml:space="preserve">7.9567928314209</t>
+    <t xml:space="preserve">7.95679378509521</t>
   </si>
   <si>
     <t xml:space="preserve">8.04035568237305</t>
@@ -4607,7 +4607,7 @@
     <t xml:space="preserve">8.09717750549316</t>
   </si>
   <si>
-    <t xml:space="preserve">8.04704093933105</t>
+    <t xml:space="preserve">8.04703998565674</t>
   </si>
   <si>
     <t xml:space="preserve">8.09550666809082</t>
@@ -4616,22 +4616,22 @@
     <t xml:space="preserve">8.06876659393311</t>
   </si>
   <si>
-    <t xml:space="preserve">8.29772758483887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.27433013916016</t>
+    <t xml:space="preserve">8.29772663116455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.27432918548584</t>
   </si>
   <si>
     <t xml:space="preserve">8.08714962005615</t>
   </si>
   <si>
-    <t xml:space="preserve">8.18575286865234</t>
+    <t xml:space="preserve">8.18575382232666</t>
   </si>
   <si>
     <t xml:space="preserve">8.16402816772461</t>
   </si>
   <si>
-    <t xml:space="preserve">8.1021900177002</t>
+    <t xml:space="preserve">8.10219097137451</t>
   </si>
   <si>
     <t xml:space="preserve">8.15567111968994</t>
@@ -4643,28 +4643,28 @@
     <t xml:space="preserve">8.27767181396484</t>
   </si>
   <si>
-    <t xml:space="preserve">8.30775547027588</t>
+    <t xml:space="preserve">8.30775451660156</t>
   </si>
   <si>
     <t xml:space="preserve">8.33616542816162</t>
   </si>
   <si>
-    <t xml:space="preserve">8.27600193023682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.34786319732666</t>
+    <t xml:space="preserve">8.2760009765625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.34786415100098</t>
   </si>
   <si>
     <t xml:space="preserve">8.37293243408203</t>
   </si>
   <si>
-    <t xml:space="preserve">8.4356050491333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.41053676605225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.43006038665771</t>
+    <t xml:space="preserve">8.43560600280762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.41053581237793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.4300594329834</t>
   </si>
   <si>
     <t xml:space="preserve">8.34443187713623</t>
@@ -4673,16 +4673,16 @@
     <t xml:space="preserve">8.31647109985352</t>
   </si>
   <si>
-    <t xml:space="preserve">8.28326797485352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.31996631622314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.29200553894043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.49471950531006</t>
+    <t xml:space="preserve">8.28326892852783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.31996726989746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.29200649261475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.49471855163574</t>
   </si>
   <si>
     <t xml:space="preserve">8.59782314300537</t>
@@ -4691,73 +4691,73 @@
     <t xml:space="preserve">8.61180305480957</t>
   </si>
   <si>
-    <t xml:space="preserve">8.66422843933105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.63976383209229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.63277244567871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.59957027435303</t>
+    <t xml:space="preserve">8.66422939300537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.63976287841797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.63277339935303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.59957122802734</t>
   </si>
   <si>
     <t xml:space="preserve">8.47374820709229</t>
   </si>
   <si>
-    <t xml:space="preserve">8.53840732574463</t>
+    <t xml:space="preserve">8.53840637207031</t>
   </si>
   <si>
     <t xml:space="preserve">8.54714393615723</t>
   </si>
   <si>
-    <t xml:space="preserve">8.58034706115723</t>
+    <t xml:space="preserve">8.58034801483154</t>
   </si>
   <si>
     <t xml:space="preserve">8.71141147613525</t>
   </si>
   <si>
-    <t xml:space="preserve">8.69568347930908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.6817045211792</t>
+    <t xml:space="preserve">8.6956844329834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.68170356750488</t>
   </si>
   <si>
     <t xml:space="preserve">8.68519878387451</t>
   </si>
   <si>
-    <t xml:space="preserve">8.7096643447876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.82500076293945</t>
+    <t xml:space="preserve">8.70966529846191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.82500171661377</t>
   </si>
   <si>
     <t xml:space="preserve">8.83373832702637</t>
   </si>
   <si>
-    <t xml:space="preserve">8.93859004974365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.03033542633057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.00412273406982</t>
+    <t xml:space="preserve">8.93858909606934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.03033447265625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.00412368774414</t>
   </si>
   <si>
     <t xml:space="preserve">9.09586715698242</t>
   </si>
   <si>
-    <t xml:space="preserve">9.08276271820068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.986647605896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.79005146026611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.78568172454834</t>
+    <t xml:space="preserve">9.08276176452637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.98664665222168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.7900505065918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.78568077087402</t>
   </si>
   <si>
     <t xml:space="preserve">8.80315780639648</t>
@@ -4766,34 +4766,34 @@
     <t xml:space="preserve">8.67995738983154</t>
   </si>
   <si>
-    <t xml:space="preserve">8.81626415252686</t>
+    <t xml:space="preserve">8.81626319885254</t>
   </si>
   <si>
     <t xml:space="preserve">8.88616561889648</t>
   </si>
   <si>
-    <t xml:space="preserve">8.85558223724365</t>
+    <t xml:space="preserve">8.85558414459229</t>
   </si>
   <si>
     <t xml:space="preserve">8.87742710113525</t>
   </si>
   <si>
-    <t xml:space="preserve">8.77257442474365</t>
+    <t xml:space="preserve">8.77257537841797</t>
   </si>
   <si>
     <t xml:space="preserve">8.73762512207031</t>
   </si>
   <si>
-    <t xml:space="preserve">8.75510025024414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.78131294250488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.79441928863525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.820631980896</t>
+    <t xml:space="preserve">8.75509929656982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.7813138961792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.79441833496094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.82063293457031</t>
   </si>
   <si>
     <t xml:space="preserve">8.94732761383057</t>
@@ -4817,37 +4817,37 @@
     <t xml:space="preserve">8.99538421630859</t>
   </si>
   <si>
-    <t xml:space="preserve">8.89490222930908</t>
+    <t xml:space="preserve">8.8949031829834</t>
   </si>
   <si>
     <t xml:space="preserve">8.8424768447876</t>
   </si>
   <si>
-    <t xml:space="preserve">8.83810806274414</t>
+    <t xml:space="preserve">8.83810710906982</t>
   </si>
   <si>
     <t xml:space="preserve">8.92985343933105</t>
   </si>
   <si>
-    <t xml:space="preserve">8.81189441680908</t>
+    <t xml:space="preserve">8.8118953704834</t>
   </si>
   <si>
     <t xml:space="preserve">8.75073146820068</t>
   </si>
   <si>
-    <t xml:space="preserve">8.67296504974365</t>
+    <t xml:space="preserve">8.67296600341797</t>
   </si>
   <si>
     <t xml:space="preserve">8.62054061889648</t>
   </si>
   <si>
-    <t xml:space="preserve">8.4545259475708</t>
+    <t xml:space="preserve">8.45452499389648</t>
   </si>
   <si>
     <t xml:space="preserve">8.3601598739624</t>
   </si>
   <si>
-    <t xml:space="preserve">8.34268379211426</t>
+    <t xml:space="preserve">8.34268474578857</t>
   </si>
   <si>
     <t xml:space="preserve">8.41957473754883</t>
@@ -4868,7 +4868,7 @@
     <t xml:space="preserve">8.62578296661377</t>
   </si>
   <si>
-    <t xml:space="preserve">8.64850044250488</t>
+    <t xml:space="preserve">8.6485013961792</t>
   </si>
   <si>
     <t xml:space="preserve">8.4632625579834</t>
@@ -4883,31 +4883,31 @@
     <t xml:space="preserve">8.01240253448486</t>
   </si>
   <si>
-    <t xml:space="preserve">7.95123910903931</t>
+    <t xml:space="preserve">7.95124006271362</t>
   </si>
   <si>
     <t xml:space="preserve">8.06482696533203</t>
   </si>
   <si>
-    <t xml:space="preserve">7.98793745040894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.03686714172363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.16094303131104</t>
+    <t xml:space="preserve">7.98793649673462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.03686809539795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.16094207763672</t>
   </si>
   <si>
     <t xml:space="preserve">8.14521312713623</t>
   </si>
   <si>
-    <t xml:space="preserve">8.24307537078857</t>
+    <t xml:space="preserve">8.24307632446289</t>
   </si>
   <si>
     <t xml:space="preserve">8.3269567489624</t>
   </si>
   <si>
-    <t xml:space="preserve">8.37239170074463</t>
+    <t xml:space="preserve">8.37239265441895</t>
   </si>
   <si>
     <t xml:space="preserve">8.63452053070068</t>
@@ -4922,13 +4922,13 @@
     <t xml:space="preserve">8.919264793396</t>
   </si>
   <si>
-    <t xml:space="preserve">8.83874988555908</t>
+    <t xml:space="preserve">8.8387508392334</t>
   </si>
   <si>
     <t xml:space="preserve">8.79401969909668</t>
   </si>
   <si>
-    <t xml:space="preserve">8.79938697814941</t>
+    <t xml:space="preserve">8.79938793182373</t>
   </si>
   <si>
     <t xml:space="preserve">8.83338165283203</t>
@@ -4973,13 +4973,13 @@
     <t xml:space="preserve">9.05345630645752</t>
   </si>
   <si>
-    <t xml:space="preserve">9.14739036560059</t>
+    <t xml:space="preserve">9.1473913192749</t>
   </si>
   <si>
     <t xml:space="preserve">9.12502479553223</t>
   </si>
   <si>
-    <t xml:space="preserve">9.10713291168213</t>
+    <t xml:space="preserve">9.10713386535645</t>
   </si>
   <si>
     <t xml:space="preserve">9.19212055206299</t>
@@ -5018,7 +5018,7 @@
     <t xml:space="preserve">9.07582187652588</t>
   </si>
   <si>
-    <t xml:space="preserve">9.08029460906982</t>
+    <t xml:space="preserve">9.08029365539551</t>
   </si>
   <si>
     <t xml:space="preserve">9.04898262023926</t>
@@ -5030,25 +5030,25 @@
     <t xml:space="preserve">9.08476734161377</t>
   </si>
   <si>
-    <t xml:space="preserve">9.04003715515137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.13844394683838</t>
+    <t xml:space="preserve">9.04003620147705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.1384449005127</t>
   </si>
   <si>
     <t xml:space="preserve">9.22343254089355</t>
   </si>
   <si>
-    <t xml:space="preserve">9.2279052734375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.99530696868896</t>
+    <t xml:space="preserve">9.22790431976318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.99530601501465</t>
   </si>
   <si>
     <t xml:space="preserve">8.94252490997314</t>
   </si>
   <si>
-    <t xml:space="preserve">9.00425243377686</t>
+    <t xml:space="preserve">9.00425148010254</t>
   </si>
   <si>
     <t xml:space="preserve">9.0087251663208</t>
@@ -5069,7 +5069,7 @@
     <t xml:space="preserve">8.81906890869141</t>
   </si>
   <si>
-    <t xml:space="preserve">8.90137195587158</t>
+    <t xml:space="preserve">8.9013729095459</t>
   </si>
   <si>
     <t xml:space="preserve">9.03556442260742</t>
@@ -5087,7 +5087,7 @@
     <t xml:space="preserve">9.35762405395508</t>
   </si>
   <si>
-    <t xml:space="preserve">9.40682888031006</t>
+    <t xml:space="preserve">9.40682792663574</t>
   </si>
   <si>
     <t xml:space="preserve">9.69757556915283</t>
@@ -5096,13 +5096,13 @@
     <t xml:space="preserve">10.0956773757935</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0330543518066</t>
+    <t xml:space="preserve">10.033055305481</t>
   </si>
   <si>
     <t xml:space="preserve">10.1896114349365</t>
   </si>
   <si>
-    <t xml:space="preserve">10.252233505249</t>
+    <t xml:space="preserve">10.2522344589233</t>
   </si>
   <si>
     <t xml:space="preserve">10.2924919128418</t>
@@ -5129,7 +5129,7 @@
     <t xml:space="preserve">10.672700881958</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2611799240112</t>
+    <t xml:space="preserve">10.2611808776855</t>
   </si>
   <si>
     <t xml:space="preserve">10.2835454940796</t>
@@ -5147,7 +5147,7 @@
     <t xml:space="preserve">10.3461685180664</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3819522857666</t>
+    <t xml:space="preserve">10.3819532394409</t>
   </si>
   <si>
     <t xml:space="preserve">10.3148565292358</t>
@@ -5159,22 +5159,22 @@
     <t xml:space="preserve">10.3059120178223</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4535207748413</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3103837966919</t>
+    <t xml:space="preserve">10.4535217285156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3103828430176</t>
   </si>
   <si>
     <t xml:space="preserve">10.4132642745972</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3551149368286</t>
+    <t xml:space="preserve">10.3551139831543</t>
   </si>
   <si>
     <t xml:space="preserve">10.4311552047729</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2880191802979</t>
+    <t xml:space="preserve">10.2880182266235</t>
   </si>
   <si>
     <t xml:space="preserve">10.2745990753174</t>
@@ -5183,7 +5183,7 @@
     <t xml:space="preserve">10.426682472229</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4222087860107</t>
+    <t xml:space="preserve">10.4222097396851</t>
   </si>
   <si>
     <t xml:space="preserve">10.4937782287598</t>
@@ -5198,7 +5198,7 @@
     <t xml:space="preserve">10.5564022064209</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6861190795898</t>
+    <t xml:space="preserve">10.6861200332642</t>
   </si>
   <si>
     <t xml:space="preserve">10.6637544631958</t>
@@ -5210,16 +5210,16 @@
     <t xml:space="preserve">10.8158388137817</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0573835372925</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.017126083374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9723958969116</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0081806182861</t>
+    <t xml:space="preserve">11.0573825836182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0171251296997</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9723949432373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0081796646118</t>
   </si>
   <si>
     <t xml:space="preserve">10.9992341995239</t>
@@ -5237,7 +5237,7 @@
     <t xml:space="preserve">11.0618562698364</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1200065612793</t>
+    <t xml:space="preserve">11.1200075149536</t>
   </si>
   <si>
     <t xml:space="preserve">11.0350179672241</t>
@@ -5255,13 +5255,13 @@
     <t xml:space="preserve">11.2631435394287</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2094669342041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2720899581909</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5091609954834</t>
+    <t xml:space="preserve">11.2094659805298</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2720909118652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5091619491577</t>
   </si>
   <si>
     <t xml:space="preserve">11.4420652389526</t>
@@ -5285,7 +5285,7 @@
     <t xml:space="preserve">10.8918809890747</t>
   </si>
   <si>
-    <t xml:space="preserve">11.115532875061</t>
+    <t xml:space="preserve">11.1155338287354</t>
   </si>
   <si>
     <t xml:space="preserve">11.289981842041</t>
@@ -5300,16 +5300,16 @@
     <t xml:space="preserve">11.3185148239136</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1873931884766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2482719421387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1405649185181</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4543180465698</t>
+    <t xml:space="preserve">11.1873941421509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2482709884644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1405658721924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4543170928955</t>
   </si>
   <si>
     <t xml:space="preserve">11.3091487884521</t>
@@ -5324,10 +5324,10 @@
     <t xml:space="preserve">11.2295398712158</t>
   </si>
   <si>
-    <t xml:space="preserve">11.327880859375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2342233657837</t>
+    <t xml:space="preserve">11.3278799057007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2342224121094</t>
   </si>
   <si>
     <t xml:space="preserve">11.3512945175171</t>
@@ -5336,10 +5336,10 @@
     <t xml:space="preserve">11.4683666229248</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3887567520142</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3372459411621</t>
+    <t xml:space="preserve">11.3887577056885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3372449874878</t>
   </si>
   <si>
     <t xml:space="preserve">11.4449520111084</t>
@@ -5348,22 +5348,22 @@
     <t xml:space="preserve">11.5432920455933</t>
   </si>
   <si>
-    <t xml:space="preserve">11.435585975647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3981227874756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3559770584106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8804597854614</t>
+    <t xml:space="preserve">11.4355869293213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3981237411499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.355978012085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8804607391357</t>
   </si>
   <si>
     <t xml:space="preserve">11.7212429046631</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3606605529785</t>
+    <t xml:space="preserve">11.3606595993042</t>
   </si>
   <si>
     <t xml:space="preserve">11.0843706130981</t>
@@ -5387,7 +5387,7 @@
     <t xml:space="preserve">11.1358823776245</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1499300003052</t>
+    <t xml:space="preserve">11.1499309539795</t>
   </si>
   <si>
     <t xml:space="preserve">11.2951002120972</t>
@@ -5402,13 +5402,13 @@
     <t xml:space="preserve">11.5011463165283</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5854377746582</t>
+    <t xml:space="preserve">11.5854387283325</t>
   </si>
   <si>
     <t xml:space="preserve">11.618218421936</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7025108337402</t>
+    <t xml:space="preserve">11.7025098800659</t>
   </si>
   <si>
     <t xml:space="preserve">11.6978273391724</t>
@@ -5417,7 +5417,7 @@
     <t xml:space="preserve">11.6697301864624</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7306079864502</t>
+    <t xml:space="preserve">11.7306070327759</t>
   </si>
   <si>
     <t xml:space="preserve">11.7446565628052</t>
@@ -5432,16 +5432,16 @@
     <t xml:space="preserve">11.5713891983032</t>
   </si>
   <si>
-    <t xml:space="preserve">11.524561882019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.566707611084</t>
+    <t xml:space="preserve">11.5245609283447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5667066574097</t>
   </si>
   <si>
     <t xml:space="preserve">11.5105123519897</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6837787628174</t>
+    <t xml:space="preserve">11.6837797164917</t>
   </si>
   <si>
     <t xml:space="preserve">11.660364151001</t>
@@ -5456,7 +5456,7 @@
     <t xml:space="preserve">11.8242654800415</t>
   </si>
   <si>
-    <t xml:space="preserve">11.87109375</t>
+    <t xml:space="preserve">11.8710947036743</t>
   </si>
   <si>
     <t xml:space="preserve">11.8664112091064</t>
@@ -5486,7 +5486,7 @@
     <t xml:space="preserve">11.6229009628296</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7259254455566</t>
+    <t xml:space="preserve">11.7259244918823</t>
   </si>
   <si>
     <t xml:space="preserve">11.7868022918701</t>
@@ -5501,25 +5501,25 @@
     <t xml:space="preserve">11.9179229736328</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0068969726562</t>
+    <t xml:space="preserve">12.0068979263306</t>
   </si>
   <si>
     <t xml:space="preserve">12.095871925354</t>
   </si>
   <si>
-    <t xml:space="preserve">12.109920501709</t>
+    <t xml:space="preserve">12.1099214553833</t>
   </si>
   <si>
     <t xml:space="preserve">12.1614322662354</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5266962051392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5641593933105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4845504760742</t>
+    <t xml:space="preserve">12.5266971588135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5641603469849</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4845514297485</t>
   </si>
   <si>
     <t xml:space="preserve">12.3908929824829</t>
@@ -5531,7 +5531,7 @@
     <t xml:space="preserve">12.306601524353</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2176275253296</t>
+    <t xml:space="preserve">12.2176265716553</t>
   </si>
   <si>
     <t xml:space="preserve">12.3440647125244</t>
@@ -5543,7 +5543,7 @@
     <t xml:space="preserve">12.1661157608032</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1192855834961</t>
+    <t xml:space="preserve">12.1192865371704</t>
   </si>
   <si>
     <t xml:space="preserve">12.2035779953003</t>
@@ -5552,10 +5552,10 @@
     <t xml:space="preserve">12.1473836898804</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3581123352051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4564542770386</t>
+    <t xml:space="preserve">12.3581132888794</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4564533233643</t>
   </si>
   <si>
     <t xml:space="preserve">12.4470882415771</t>
@@ -6242,7 +6242,7 @@
     <t xml:space="preserve">20.8999996185303</t>
   </si>
   <si>
-    <t xml:space="preserve">20.7299995422363</t>
+    <t xml:space="preserve">20.7099990844727</t>
   </si>
 </sst>
 </file>
@@ -71685,22 +71685,22 @@
     </row>
     <row r="2505">
       <c r="A2505" s="1" t="n">
-        <v>45966.6936342593</v>
+        <v>45967.6911342593</v>
       </c>
       <c r="B2505" t="n">
-        <v>1953819</v>
+        <v>2641486</v>
       </c>
       <c r="C2505" t="n">
-        <v>20.8500003814697</v>
+        <v>20.8899993896484</v>
       </c>
       <c r="D2505" t="n">
-        <v>20.5599994659424</v>
+        <v>20.5699996948242</v>
       </c>
       <c r="E2505" t="n">
-        <v>20.7800006866455</v>
+        <v>20.8899993896484</v>
       </c>
       <c r="F2505" t="n">
-        <v>20.7299995422363</v>
+        <v>20.7099990844727</v>
       </c>
       <c r="G2505" t="s">
         <v>2076</v>

--- a/data/PST.MI.xlsx
+++ b/data/PST.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2080" uniqueCount="2080">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2081" uniqueCount="2081">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,7 +38,7 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">3.90457534790039</t>
+    <t xml:space="preserve">3.90457510948181</t>
   </si>
   <si>
     <t xml:space="preserve">PST.MI</t>
@@ -50,31 +50,31 @@
     <t xml:space="preserve">3.97465062141418</t>
   </si>
   <si>
-    <t xml:space="preserve">3.95222640037537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.91578674316406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87934827804565</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.97184753417969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.01949882507324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99707460403442</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94662022590637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.82889533042908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.75601601600647</t>
+    <t xml:space="preserve">3.95222663879395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9157874584198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87934851646423</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97184777259827</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.0194993019104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.997074842453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94662070274353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.82889461517334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.75601673126221</t>
   </si>
   <si>
     <t xml:space="preserve">3.54859519004822</t>
@@ -83,88 +83,88 @@
     <t xml:space="preserve">3.68594121932983</t>
   </si>
   <si>
-    <t xml:space="preserve">3.73359203338623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.65510964393616</t>
+    <t xml:space="preserve">3.73359322547913</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.65510940551758</t>
   </si>
   <si>
     <t xml:space="preserve">3.7616229057312</t>
   </si>
   <si>
-    <t xml:space="preserve">3.80927324295044</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73078989982605</t>
+    <t xml:space="preserve">3.8092737197876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73078918457031</t>
   </si>
   <si>
     <t xml:space="preserve">3.82609128952026</t>
   </si>
   <si>
-    <t xml:space="preserve">3.72238063812256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64389705657959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.53177762031555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.35518836975098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.00481343269348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.89829921722412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.17019057273865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.03284311294556</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.04405546188354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.1365532875061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.12253928184509</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.24867367744446</t>
+    <t xml:space="preserve">3.72238039970398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64389681816101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.53177714347839</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.35518860816956</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.0048131942749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.8982994556427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.17019009590149</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.03284287452698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.04405522346497</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13655471801758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.12253952026367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.24867415428162</t>
   </si>
   <si>
     <t xml:space="preserve">3.23465895652771</t>
   </si>
   <si>
-    <t xml:space="preserve">3.30473399162292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.42246007919312</t>
+    <t xml:space="preserve">3.30473375320435</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.42245960235596</t>
   </si>
   <si>
     <t xml:space="preserve">3.34677910804749</t>
   </si>
   <si>
-    <t xml:space="preserve">3.31314253807068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.40844511985779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.45609617233276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.51495885848999</t>
+    <t xml:space="preserve">3.31314301490784</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.40844559669495</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.45609569549561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.51495862007141</t>
   </si>
   <si>
     <t xml:space="preserve">3.48412561416626</t>
   </si>
   <si>
-    <t xml:space="preserve">3.45329284667969</t>
+    <t xml:space="preserve">3.45329260826111</t>
   </si>
   <si>
     <t xml:space="preserve">3.47571659088135</t>
@@ -176,106 +176,106 @@
     <t xml:space="preserve">3.45889949798584</t>
   </si>
   <si>
-    <t xml:space="preserve">3.43367171287537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61306381225586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.63829135894775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.63548803329468</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.60745787620544</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.58783674240112</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.60185217857361</t>
+    <t xml:space="preserve">3.43367195129395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61306405067444</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.63829064369202</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.63548707962036</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.60745763778687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.58783626556396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.60185194015503</t>
   </si>
   <si>
     <t xml:space="preserve">3.67192697525024</t>
   </si>
   <si>
-    <t xml:space="preserve">3.79525947570801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77844023704529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71397161483765</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.78404712677002</t>
+    <t xml:space="preserve">3.79525899887085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77843999862671</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71397185325623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.78404641151428</t>
   </si>
   <si>
     <t xml:space="preserve">3.72798681259155</t>
   </si>
   <si>
-    <t xml:space="preserve">3.67753219604492</t>
+    <t xml:space="preserve">3.67753267288208</t>
   </si>
   <si>
     <t xml:space="preserve">3.6158664226532</t>
   </si>
   <si>
-    <t xml:space="preserve">3.51215481758118</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.5682156085968</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.58503437042236</t>
+    <t xml:space="preserve">3.51215648651123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.56821489334106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.58503389358521</t>
   </si>
   <si>
     <t xml:space="preserve">3.60465431213379</t>
   </si>
   <si>
-    <t xml:space="preserve">3.62147283554077</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.69995641708374</t>
+    <t xml:space="preserve">3.62147235870361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.6999568939209</t>
   </si>
   <si>
     <t xml:space="preserve">3.63268423080444</t>
   </si>
   <si>
-    <t xml:space="preserve">3.6298816204071</t>
+    <t xml:space="preserve">3.62988138198853</t>
   </si>
   <si>
     <t xml:space="preserve">3.65791177749634</t>
   </si>
   <si>
-    <t xml:space="preserve">3.62707877159119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.674729347229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.68033576011658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.74480438232422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.79245638847351</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80086469650269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73919796943665</t>
+    <t xml:space="preserve">3.62707853317261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.67472958564758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.68033671379089</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.7448046207428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.79245519638062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.80086445808411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73919868469238</t>
   </si>
   <si>
     <t xml:space="preserve">3.68313908576965</t>
   </si>
   <si>
-    <t xml:space="preserve">3.76722836494446</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.79806208610535</t>
+    <t xml:space="preserve">3.76722860336304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.79806113243103</t>
   </si>
   <si>
     <t xml:space="preserve">3.77563762664795</t>
@@ -284,88 +284,88 @@
     <t xml:space="preserve">3.75881958007812</t>
   </si>
   <si>
-    <t xml:space="preserve">3.78684973716736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.68874478340149</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.78965330123901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.74760746955872</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.831698179245</t>
+    <t xml:space="preserve">3.78685021400452</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.68874526023865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.78965258598328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.74760699272156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.83169722557068</t>
   </si>
   <si>
     <t xml:space="preserve">3.83730340003967</t>
   </si>
   <si>
-    <t xml:space="preserve">3.80647039413452</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85972762107849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85692453384399</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8681366443634</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84571218490601</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85412120819092</t>
+    <t xml:space="preserve">3.8064706325531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85972785949707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85692524909973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.86813735961914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84571242332458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85412192344666</t>
   </si>
   <si>
     <t xml:space="preserve">3.92419624328613</t>
   </si>
   <si>
-    <t xml:space="preserve">3.93260550498962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84010648727417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.78124332427979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.76442551612854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87654590606689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96498394012451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.91486883163452</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90602493286133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95024371147156</t>
+    <t xml:space="preserve">3.93260478973389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84010672569275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.78124260902405</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.7644259929657</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87654495239258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96498322486877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.91486835479736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90602564811707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95024442672729</t>
   </si>
   <si>
     <t xml:space="preserve">3.63776302337646</t>
   </si>
   <si>
-    <t xml:space="preserve">3.42256188392639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.51394867897034</t>
+    <t xml:space="preserve">3.42256236076355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.5139479637146</t>
   </si>
   <si>
     <t xml:space="preserve">3.50805234909058</t>
   </si>
   <si>
-    <t xml:space="preserve">3.60533499717712</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.52574014663696</t>
+    <t xml:space="preserve">3.60533428192139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.5257408618927</t>
   </si>
   <si>
     <t xml:space="preserve">3.43730187416077</t>
@@ -374,406 +374,406 @@
     <t xml:space="preserve">3.39897871017456</t>
   </si>
   <si>
-    <t xml:space="preserve">3.37244725227356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.49920868873596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.65839791297913</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64955353736877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73504424095154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.67018938064575</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.67313718795776</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.65250205993652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.70851278305054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.69672131538391</t>
+    <t xml:space="preserve">3.37244701385498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.49920892715454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.65839743614197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64955401420593</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73504447937012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.67018961906433</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.6731379032135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.65250182151794</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.70851302146912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.69672060012817</t>
   </si>
   <si>
     <t xml:space="preserve">3.65544939041138</t>
   </si>
   <si>
-    <t xml:space="preserve">3.64660668373108</t>
+    <t xml:space="preserve">3.64660549163818</t>
   </si>
   <si>
     <t xml:space="preserve">3.60238671302795</t>
   </si>
   <si>
-    <t xml:space="preserve">3.58469939231873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.52868866920471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80284643173218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.78221082687378</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80874276161194</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.81463885307312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.86770081520081</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87949395179749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.7998993396759</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.72325277328491</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.7615761756897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.667240858078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.68198037147522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.74388742446899</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.70261693000793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66134548187256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.67903280258179</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.62597036361694</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.69377207756042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.68492865562439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.70556449890137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71735596656799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77631497383118</t>
+    <t xml:space="preserve">3.5846996307373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.52868914604187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.80284690856934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.78221106529236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.80874252319336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.81463861465454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.86770129203796</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87949347496033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.79989910125732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.72325325012207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.76157546043396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.6672420501709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.68198132514954</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.74388837814331</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.70261716842651</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66134595870972</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.67903327941895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.6259708404541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.6937735080719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.68492984771729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.70556473731995</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71735620498657</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77631521224976</t>
   </si>
   <si>
     <t xml:space="preserve">3.76452398300171</t>
   </si>
   <si>
-    <t xml:space="preserve">3.56406307220459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61712646484375</t>
+    <t xml:space="preserve">3.56406378746033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61712622642517</t>
   </si>
   <si>
     <t xml:space="preserve">3.61417865753174</t>
   </si>
   <si>
-    <t xml:space="preserve">3.58175110816956</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.59943890571594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.6082820892334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.58764696121216</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.57880330085754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.57290744781494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.55816698074341</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.56111526489258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.50215625762939</t>
+    <t xml:space="preserve">3.58175182342529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.59943842887878</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.60828280448914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.58764672279358</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.57880353927612</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.57290768623352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.55816769599915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.56111574172974</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.50215649604797</t>
   </si>
   <si>
     <t xml:space="preserve">3.54637575149536</t>
   </si>
   <si>
-    <t xml:space="preserve">3.56701135635376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.51689648628235</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.57585573196411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64365839958191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.62302303314209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.51100087165833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.49036550521851</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.51984429359436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.55227160453796</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.54342794418335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.53163647651672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.52279257774353</t>
+    <t xml:space="preserve">3.56701183319092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.51689696311951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.57585477828979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64365720748901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.62302207946777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.51100015640259</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.49036455154419</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.51984477043152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.55227208137512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.54342722892761</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.5316367149353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.52279281616211</t>
   </si>
   <si>
     <t xml:space="preserve">3.47857284545898</t>
   </si>
   <si>
-    <t xml:space="preserve">3.4402494430542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.36655163764954</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.33117580413818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.32528018951416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.31938433647156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.31054043769836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.26632142066956</t>
+    <t xml:space="preserve">3.44024968147278</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.36655116081238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.33117604255676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.325279712677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.3193838596344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.31053996086121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.2663209438324</t>
   </si>
   <si>
     <t xml:space="preserve">3.39603137969971</t>
   </si>
   <si>
-    <t xml:space="preserve">3.45793747901917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.4608850479126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.45204162597656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73209691047668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.74683594703674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73799300193787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.72914838790894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77926278114319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.74094009399414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77336740493774</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.79105448722839</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.76747226715088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.7144091129303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.63481426239014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.59649085998535</t>
+    <t xml:space="preserve">3.45793795585632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.46088600158691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.45204186439514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73209667205811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.74683618545532</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73799228668213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.72914814949036</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77926301956177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.7409405708313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77336716651917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.79105520248413</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.76747179031372</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71440887451172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.63481330871582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.59649062156677</t>
   </si>
   <si>
     <t xml:space="preserve">3.56995892524719</t>
   </si>
   <si>
-    <t xml:space="preserve">3.5935423374176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.44909358024597</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.42845869064331</t>
+    <t xml:space="preserve">3.59354257583618</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.44909310340881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.42845821380615</t>
   </si>
   <si>
     <t xml:space="preserve">3.44614553451538</t>
   </si>
   <si>
-    <t xml:space="preserve">3.53753232955933</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.53458476066589</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.59059500694275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.69966864585876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.81758642196655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80579471588135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.796950340271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.75862789154053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.82937860488892</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.79400324821472</t>
+    <t xml:space="preserve">3.53753209114075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.53458380699158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.59059429168701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.69966888427734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.81758594512939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.80579400062561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.79695200920105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.75862765312195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.82937812805176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.79400300979614</t>
   </si>
   <si>
     <t xml:space="preserve">3.67608547210693</t>
   </si>
   <si>
-    <t xml:space="preserve">3.71146059036255</t>
+    <t xml:space="preserve">3.71146106719971</t>
   </si>
   <si>
     <t xml:space="preserve">3.74978375434875</t>
   </si>
   <si>
-    <t xml:space="preserve">3.77041983604431</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.68787693977356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.75273156166077</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83232688903809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84411883354187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.72030472755432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.69082498550415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.81169080734253</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.82053470611572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.78916716575623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8017144203186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.81426119804382</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.75780034065247</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.76407408714294</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77662014961243</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73897981643677</t>
+    <t xml:space="preserve">3.77041959762573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.68787717819214</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.75273108482361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.83232665061951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84411859512329</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.72030448913574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.69082522392273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.81169056892395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8205349445343</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.78916692733765</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.80171418190002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.81426167488098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.75780057907104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.76407361030579</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77661991119385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73897933959961</t>
   </si>
   <si>
     <t xml:space="preserve">3.82053518295288</t>
   </si>
   <si>
-    <t xml:space="preserve">3.78603005409241</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.76093697547913</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.76721048355103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.74525308609009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.72956919670105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.79544067382812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80485081672668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8424916267395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.82367014884949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80798768997192</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.79857754707336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.75152659416199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.74211740493774</t>
+    <t xml:space="preserve">3.78602981567383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.76093626022339</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.76721024513245</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.74525332450867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.72956967353821</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.79544115066528</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.80485057830811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84249234199524</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8236711025238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.80798745155334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.79857707023621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.75152611732483</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.74211621284485</t>
   </si>
   <si>
     <t xml:space="preserve">3.77975726127625</t>
@@ -782,31 +782,31 @@
     <t xml:space="preserve">3.91463589668274</t>
   </si>
   <si>
-    <t xml:space="preserve">3.92718386650085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94600439071655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8926796913147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90208911895752</t>
+    <t xml:space="preserve">3.9271833896637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94600367546082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89267897605896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90208959579468</t>
   </si>
   <si>
     <t xml:space="preserve">3.90522599220276</t>
   </si>
   <si>
-    <t xml:space="preserve">3.94286704063416</t>
+    <t xml:space="preserve">3.942866563797</t>
   </si>
   <si>
     <t xml:space="preserve">3.83308124542236</t>
   </si>
   <si>
-    <t xml:space="preserve">3.84562826156616</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.89895272254944</t>
+    <t xml:space="preserve">3.8456289768219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89895296096802</t>
   </si>
   <si>
     <t xml:space="preserve">3.908362865448</t>
@@ -815,97 +815,97 @@
     <t xml:space="preserve">3.85817527770996</t>
   </si>
   <si>
-    <t xml:space="preserve">3.83935475349426</t>
+    <t xml:space="preserve">3.83935499191284</t>
   </si>
   <si>
     <t xml:space="preserve">3.82994484901428</t>
   </si>
   <si>
-    <t xml:space="preserve">3.85503888130188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.81739783287048</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8613121509552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92090964317322</t>
+    <t xml:space="preserve">3.8550386428833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.81739807128906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.86131167411804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92091012001038</t>
   </si>
   <si>
     <t xml:space="preserve">3.89581608772278</t>
   </si>
   <si>
-    <t xml:space="preserve">3.8864061832428</t>
+    <t xml:space="preserve">3.88640546798706</t>
   </si>
   <si>
     <t xml:space="preserve">3.8895423412323</t>
   </si>
   <si>
-    <t xml:space="preserve">3.86444878578186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88013291358948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85190200805664</t>
+    <t xml:space="preserve">3.86444902420044</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8801326751709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85190224647522</t>
   </si>
   <si>
     <t xml:space="preserve">3.873859167099</t>
   </si>
   <si>
-    <t xml:space="preserve">3.93031907081604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8675856590271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93659329414368</t>
+    <t xml:space="preserve">3.9303195476532</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.86758518218994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93659377098083</t>
   </si>
   <si>
     <t xml:space="preserve">3.94914078712463</t>
   </si>
   <si>
-    <t xml:space="preserve">3.93345642089844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93972992897034</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9240460395813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8487651348114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8362181186676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.82680797576904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99305462837219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.02128458023071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99619150161743</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9836437702179</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.97109818458557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98678112030029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99932837486267</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.01814842224121</t>
+    <t xml:space="preserve">3.93345713615417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93973135948181</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92404675483704</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84876537322998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.83621788024902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.82680892944336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99305510520935</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.02128553390503</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99619126319885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.98364424705505</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97109842300415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.98678088188171</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99932789802551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.01814889907837</t>
   </si>
   <si>
     <t xml:space="preserve">4.03383159637451</t>
@@ -917,76 +917,76 @@
     <t xml:space="preserve">4.05892562866211</t>
   </si>
   <si>
-    <t xml:space="preserve">4.04010438919067</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.07147312164307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.10284042358398</t>
+    <t xml:space="preserve">4.04010581970215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.07147264480591</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.10283994674683</t>
   </si>
   <si>
     <t xml:space="preserve">4.09970283508301</t>
   </si>
   <si>
-    <t xml:space="preserve">4.12793397903442</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.21889925003052</t>
+    <t xml:space="preserve">4.12793350219727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.21889877319336</t>
   </si>
   <si>
     <t xml:space="preserve">4.2157621383667</t>
   </si>
   <si>
-    <t xml:space="preserve">4.20007801055908</t>
+    <t xml:space="preserve">4.20007848739624</t>
   </si>
   <si>
     <t xml:space="preserve">4.17184829711914</t>
   </si>
   <si>
-    <t xml:space="preserve">4.18753147125244</t>
+    <t xml:space="preserve">4.1875319480896</t>
   </si>
   <si>
     <t xml:space="preserve">4.19694137573242</t>
   </si>
   <si>
-    <t xml:space="preserve">4.17310333251953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.15553712844849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.18063068389893</t>
+    <t xml:space="preserve">4.17310285568237</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.15553665161133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.18063116073608</t>
   </si>
   <si>
     <t xml:space="preserve">4.13044309616089</t>
   </si>
   <si>
-    <t xml:space="preserve">4.13922595977783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.01501131057739</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.12166023254395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.04386949539185</t>
+    <t xml:space="preserve">4.13922643661499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.01501178741455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.1216607093811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.043869972229</t>
   </si>
   <si>
     <t xml:space="preserve">4.03759622573853</t>
   </si>
   <si>
-    <t xml:space="preserve">4.05516147613525</t>
+    <t xml:space="preserve">4.05516195297241</t>
   </si>
   <si>
     <t xml:space="preserve">4.09531164169312</t>
   </si>
   <si>
-    <t xml:space="preserve">4.12918853759766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.17561149597168</t>
+    <t xml:space="preserve">4.1291880607605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.17561197280884</t>
   </si>
   <si>
     <t xml:space="preserve">4.18188571929932</t>
@@ -995,46 +995,46 @@
     <t xml:space="preserve">4.2534031867981</t>
   </si>
   <si>
-    <t xml:space="preserve">4.24085664749146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.20697927474976</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.21074342727661</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.17435693740845</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.41651248931885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.43031406402588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.40271139144897</t>
+    <t xml:space="preserve">4.2408561706543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.20697975158691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.21074295043945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.17435741424561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.41651296615601</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.43031454086304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.40271091461182</t>
   </si>
   <si>
     <t xml:space="preserve">4.30735492706299</t>
   </si>
   <si>
-    <t xml:space="preserve">4.33495807647705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.37134265899658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.48677539825439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.60095310211182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.57711362838745</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.65490484237671</t>
+    <t xml:space="preserve">4.33495759963989</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.3713436126709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.48677635192871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.60095167160034</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.57711315155029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.65490388870239</t>
   </si>
   <si>
     <t xml:space="preserve">4.55452966690063</t>
@@ -1043,70 +1043,70 @@
     <t xml:space="preserve">4.4955587387085</t>
   </si>
   <si>
-    <t xml:space="preserve">4.56707620620728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.63859367370605</t>
+    <t xml:space="preserve">4.56707572937012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.6385931968689</t>
   </si>
   <si>
     <t xml:space="preserve">4.60346174240112</t>
   </si>
   <si>
-    <t xml:space="preserve">4.63482904434204</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.6260461807251</t>
+    <t xml:space="preserve">4.6348295211792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.62604665756226</t>
   </si>
   <si>
     <t xml:space="preserve">4.58338737487793</t>
   </si>
   <si>
-    <t xml:space="preserve">4.54574584960938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.52943468093872</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.5444917678833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.61475372314453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.62353658676147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.65866851806641</t>
+    <t xml:space="preserve">4.54574680328369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.52943420410156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.54449129104614</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.61475419998169</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.62353706359863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.65866756439209</t>
   </si>
   <si>
     <t xml:space="preserve">4.73645925521851</t>
   </si>
   <si>
-    <t xml:space="preserve">4.73144006729126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.76782608032227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.82052278518677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.81299495697021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.81675958633423</t>
+    <t xml:space="preserve">4.73144054412842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.76782655715942</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.82052326202393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.81299543380737</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.81675910949707</t>
   </si>
   <si>
     <t xml:space="preserve">4.81424999237061</t>
   </si>
   <si>
-    <t xml:space="preserve">4.84310817718506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.88702249526978</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.85691022872925</t>
+    <t xml:space="preserve">4.84310722351074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.88702201843262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.85690975189209</t>
   </si>
   <si>
     <t xml:space="preserve">4.86694669723511</t>
@@ -1115,25 +1115,25 @@
     <t xml:space="preserve">4.9372091293335</t>
   </si>
   <si>
-    <t xml:space="preserve">4.9422287940979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.96355867385864</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.9735951423645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.00119924545288</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.08526229858398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.07146167755127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.06267881393433</t>
+    <t xml:space="preserve">4.94222831726074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.96355819702148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.97359609603882</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.00119829177856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.0852632522583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.07146215438843</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.06267929077148</t>
   </si>
   <si>
     <t xml:space="preserve">5.11537551879883</t>
@@ -1142,22 +1142,22 @@
     <t xml:space="preserve">5.09153604507446</t>
   </si>
   <si>
-    <t xml:space="preserve">5.06769800186157</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.11286544799805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.15552616119385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.96230411529541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.951012134552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.78037261962891</t>
+    <t xml:space="preserve">5.06769752502441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.11286640167236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.15552663803101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.96230316162109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.95101118087769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.78037357330322</t>
   </si>
   <si>
     <t xml:space="preserve">4.79041147232056</t>
@@ -1169,40 +1169,40 @@
     <t xml:space="preserve">4.8054666519165</t>
   </si>
   <si>
-    <t xml:space="preserve">4.83432531356812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.76029777526855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.60722589492798</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.40020227432251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.58464241027832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.5946798324585</t>
+    <t xml:space="preserve">4.83432579040527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.76029872894287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.60722541809082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.40020275115967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.58464193344116</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.59467887878418</t>
   </si>
   <si>
     <t xml:space="preserve">4.68627119064331</t>
   </si>
   <si>
-    <t xml:space="preserve">4.71261978149414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.58840560913086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.58589601516724</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.56833028793335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.44411659240723</t>
+    <t xml:space="preserve">4.7126202583313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.5884051322937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.58589649200439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.56833076477051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.44411611557007</t>
   </si>
   <si>
     <t xml:space="preserve">4.61600875854492</t>
@@ -1211,28 +1211,28 @@
     <t xml:space="preserve">4.7038369178772</t>
   </si>
   <si>
-    <t xml:space="preserve">4.79292011260986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.90584230422974</t>
+    <t xml:space="preserve">4.79291963577271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.90584325790405</t>
   </si>
   <si>
     <t xml:space="preserve">4.78664684295654</t>
   </si>
   <si>
-    <t xml:space="preserve">4.86100196838379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.91013050079346</t>
+    <t xml:space="preserve">4.86100244522095</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.91012954711914</t>
   </si>
   <si>
     <t xml:space="preserve">4.93270254135132</t>
   </si>
   <si>
-    <t xml:space="preserve">4.87162446975708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.87693548202515</t>
+    <t xml:space="preserve">4.87162399291992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.8769359588623</t>
   </si>
   <si>
     <t xml:space="preserve">4.81320238113403</t>
@@ -1241,202 +1241,202 @@
     <t xml:space="preserve">4.83577394485474</t>
   </si>
   <si>
-    <t xml:space="preserve">4.76672983169556</t>
+    <t xml:space="preserve">4.76673030853271</t>
   </si>
   <si>
     <t xml:space="preserve">4.76009178161621</t>
   </si>
   <si>
-    <t xml:space="preserve">4.80789184570312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.81984186172485</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.9340295791626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.97253608703613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.01900720596313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.96589756011963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.03892517089844</t>
+    <t xml:space="preserve">4.80789136886597</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.8198413848877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.93403100967407</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.97253561019897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.01900768280029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.96589660644531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.03892469406128</t>
   </si>
   <si>
     <t xml:space="preserve">5.02697467803955</t>
   </si>
   <si>
-    <t xml:space="preserve">5.10000324249268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.15311431884766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.18099784851074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.12124681472778</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.13452482223511</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.11859273910522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.12788534164429</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.2115364074707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.23410844802856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.25668048858643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.28854703903198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.28058052062988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.99510812759399</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.94465208053589</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.92871904373169</t>
+    <t xml:space="preserve">5.10000276565552</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.15311336517334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.18099689483643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.12124729156494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.13452529907227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.11859178543091</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.1278862953186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.21153593063354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.23410797119141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.25668096542358</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.28854751586914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.28058099746704</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.99510860443115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.94465160369873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.92871856689453</t>
   </si>
   <si>
     <t xml:space="preserve">4.86896944046021</t>
   </si>
   <si>
-    <t xml:space="preserve">4.71627378463745</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.69635725021362</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.74548530578613</t>
+    <t xml:space="preserve">4.71627426147461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.69635772705078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.74548482894897</t>
   </si>
   <si>
     <t xml:space="preserve">4.60474061965942</t>
   </si>
   <si>
-    <t xml:space="preserve">4.54764556884766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.47594594955444</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.61801815032959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.52772903442383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.51046848297119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.50250196456909</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.4852409362793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.50515651702881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.44673538208008</t>
+    <t xml:space="preserve">4.54764604568481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.4759464263916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.61801862716675</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.52772998809814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.51046943664551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.50250148773193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.48524045944214</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.50515699386597</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.44673442840576</t>
   </si>
   <si>
     <t xml:space="preserve">4.40291786193848</t>
   </si>
   <si>
-    <t xml:space="preserve">4.47727394104004</t>
+    <t xml:space="preserve">4.4772744178772</t>
   </si>
   <si>
     <t xml:space="preserve">4.59544658660889</t>
   </si>
   <si>
-    <t xml:space="preserve">4.68440818786621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.65519618988037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.67378568649292</t>
+    <t xml:space="preserve">4.68440771102905</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.65519666671753</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.67378520965576</t>
   </si>
   <si>
     <t xml:space="preserve">4.78133583068848</t>
   </si>
   <si>
-    <t xml:space="preserve">4.75610828399658</t>
+    <t xml:space="preserve">4.75610780715942</t>
   </si>
   <si>
     <t xml:space="preserve">4.68175172805786</t>
   </si>
   <si>
-    <t xml:space="preserve">4.56225204467773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.58880758285522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.63262367248535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.61005163192749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.59810256958008</t>
+    <t xml:space="preserve">4.56225156784058</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.58880805969238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.63262462615967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.61005115509033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.59810209274292</t>
   </si>
   <si>
     <t xml:space="preserve">4.6605076789856</t>
   </si>
   <si>
-    <t xml:space="preserve">4.69901323318481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.72158575057983</t>
+    <t xml:space="preserve">4.69901275634766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.72158479690552</t>
   </si>
   <si>
     <t xml:space="preserve">4.77735185623169</t>
   </si>
   <si>
-    <t xml:space="preserve">4.80523538589478</t>
+    <t xml:space="preserve">4.80523490905762</t>
   </si>
   <si>
     <t xml:space="preserve">4.7733678817749</t>
   </si>
   <si>
-    <t xml:space="preserve">4.56889057159424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.51976203918457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.43876838684082</t>
+    <t xml:space="preserve">4.5688910484314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.51976299285889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.43876791000366</t>
   </si>
   <si>
     <t xml:space="preserve">4.44806241989136</t>
   </si>
   <si>
-    <t xml:space="preserve">4.45204544067383</t>
+    <t xml:space="preserve">4.45204591751099</t>
   </si>
   <si>
     <t xml:space="preserve">4.38167381286621</t>
   </si>
   <si>
-    <t xml:space="preserve">4.21968412399292</t>
+    <t xml:space="preserve">4.21968460083008</t>
   </si>
   <si>
     <t xml:space="preserve">4.2422571182251</t>
@@ -1448,13 +1448,13 @@
     <t xml:space="preserve">4.1665735244751</t>
   </si>
   <si>
-    <t xml:space="preserve">4.14798498153687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.16391754150391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.23296117782593</t>
+    <t xml:space="preserve">4.14798545837402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.16391706466675</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.2329626083374</t>
   </si>
   <si>
     <t xml:space="preserve">4.17985153198242</t>
@@ -1466,58 +1466,58 @@
     <t xml:space="preserve">4.16259050369263</t>
   </si>
   <si>
-    <t xml:space="preserve">4.14001846313477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.14931201934814</t>
+    <t xml:space="preserve">4.14001750946045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.14931297302246</t>
   </si>
   <si>
     <t xml:space="preserve">3.98201179504395</t>
   </si>
   <si>
-    <t xml:space="preserve">4.06831741333008</t>
+    <t xml:space="preserve">4.06831836700439</t>
   </si>
   <si>
     <t xml:space="preserve">4.07230043411255</t>
   </si>
   <si>
-    <t xml:space="preserve">4.201096534729</t>
+    <t xml:space="preserve">4.20109605789185</t>
   </si>
   <si>
     <t xml:space="preserve">4.10815095901489</t>
   </si>
   <si>
-    <t xml:space="preserve">4.21570110321045</t>
+    <t xml:space="preserve">4.21570158004761</t>
   </si>
   <si>
     <t xml:space="preserve">4.34980726242065</t>
   </si>
   <si>
-    <t xml:space="preserve">4.3843297958374</t>
+    <t xml:space="preserve">4.38432884216309</t>
   </si>
   <si>
     <t xml:space="preserve">4.32325172424316</t>
   </si>
   <si>
-    <t xml:space="preserve">4.29536724090576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.43743991851807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.53038597106934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.56092405319214</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.57021760940552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.57287454605103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.42681884765625</t>
+    <t xml:space="preserve">4.29536819458008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.43744039535522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.53038549423218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.5609245300293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.57021808624268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.57287406921387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.42681837081909</t>
   </si>
   <si>
     <t xml:space="preserve">4.31528472900391</t>
@@ -1529,46 +1529,46 @@
     <t xml:space="preserve">4.35113477706909</t>
   </si>
   <si>
-    <t xml:space="preserve">4.23163461685181</t>
+    <t xml:space="preserve">4.23163509368896</t>
   </si>
   <si>
     <t xml:space="preserve">4.37105178833008</t>
   </si>
   <si>
-    <t xml:space="preserve">4.34847974777222</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.54100751876831</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.51710796356201</t>
+    <t xml:space="preserve">4.34847927093506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.54100847244263</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.5171070098877</t>
   </si>
   <si>
     <t xml:space="preserve">4.44939041137695</t>
   </si>
   <si>
-    <t xml:space="preserve">4.45071887969971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.55826807022095</t>
+    <t xml:space="preserve">4.45071840286255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.55826854705811</t>
   </si>
   <si>
     <t xml:space="preserve">4.52241849899292</t>
   </si>
   <si>
-    <t xml:space="preserve">4.5821681022644</t>
+    <t xml:space="preserve">4.58216762542725</t>
   </si>
   <si>
     <t xml:space="preserve">4.34051275253296</t>
   </si>
   <si>
-    <t xml:space="preserve">4.36175632476807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.31130218505859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.35379076004028</t>
+    <t xml:space="preserve">4.36175680160522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.31130123138428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.35379028320312</t>
   </si>
   <si>
     <t xml:space="preserve">4.52905750274658</t>
@@ -1583,49 +1583,49 @@
     <t xml:space="preserve">4.57154607772827</t>
   </si>
   <si>
-    <t xml:space="preserve">4.71892976760864</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.65386867523193</t>
+    <t xml:space="preserve">4.71892929077148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.65386819839478</t>
   </si>
   <si>
     <t xml:space="preserve">4.58615207672119</t>
   </si>
   <si>
-    <t xml:space="preserve">4.53569602966309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.63660764694214</t>
+    <t xml:space="preserve">4.53569650650024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.63660717010498</t>
   </si>
   <si>
     <t xml:space="preserve">4.6273136138916</t>
   </si>
   <si>
-    <t xml:space="preserve">4.64590215682983</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.70299673080444</t>
+    <t xml:space="preserve">4.64590167999268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.7029972076416</t>
   </si>
   <si>
     <t xml:space="preserve">4.67112922668457</t>
   </si>
   <si>
-    <t xml:space="preserve">4.71760225296021</t>
+    <t xml:space="preserve">4.71760177612305</t>
   </si>
   <si>
     <t xml:space="preserve">4.78000736236572</t>
   </si>
   <si>
-    <t xml:space="preserve">4.79195737838745</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.81452894210815</t>
+    <t xml:space="preserve">4.79195785522461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.81453084945679</t>
   </si>
   <si>
     <t xml:space="preserve">4.79328536987305</t>
   </si>
   <si>
-    <t xml:space="preserve">4.88224697113037</t>
+    <t xml:space="preserve">4.88224649429321</t>
   </si>
   <si>
     <t xml:space="preserve">4.91278553009033</t>
@@ -1634,49 +1634,49 @@
     <t xml:space="preserve">5.03626918792725</t>
   </si>
   <si>
-    <t xml:space="preserve">5.04556369781494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.99776268005371</t>
+    <t xml:space="preserve">5.04556274414062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.99776411056519</t>
   </si>
   <si>
     <t xml:space="preserve">5.04423522949219</t>
   </si>
   <si>
-    <t xml:space="preserve">5.05618619918823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.10664129257202</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.08406925201416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.09203577041626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.98846912384033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.87826299667358</t>
+    <t xml:space="preserve">5.05618524551392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.10664224624634</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.084068775177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.09203624725342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.98846960067749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.87826347351074</t>
   </si>
   <si>
     <t xml:space="preserve">4.99245262145996</t>
   </si>
   <si>
-    <t xml:space="preserve">5.07477474212646</t>
+    <t xml:space="preserve">5.07477521896362</t>
   </si>
   <si>
     <t xml:space="preserve">5.10265779495239</t>
   </si>
   <si>
-    <t xml:space="preserve">4.94863557815552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.96456956863403</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.02431917190552</t>
+    <t xml:space="preserve">4.94863605499268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.96456909179688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.02431964874268</t>
   </si>
   <si>
     <t xml:space="preserve">5.09867477416992</t>
@@ -1685,10 +1685,10 @@
     <t xml:space="preserve">5.15045785903931</t>
   </si>
   <si>
-    <t xml:space="preserve">5.08938074111938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.14249181747437</t>
+    <t xml:space="preserve">5.08938026428223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.14249134063721</t>
   </si>
   <si>
     <t xml:space="preserve">5.16108131408691</t>
@@ -1700,16 +1700,16 @@
     <t xml:space="preserve">5.13054180145264</t>
   </si>
   <si>
-    <t xml:space="preserve">5.16639089584351</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.18763637542725</t>
+    <t xml:space="preserve">5.16639184951782</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.1876368522644</t>
   </si>
   <si>
     <t xml:space="preserve">5.24340295791626</t>
   </si>
   <si>
-    <t xml:space="preserve">5.24473094940186</t>
+    <t xml:space="preserve">5.2447304725647</t>
   </si>
   <si>
     <t xml:space="preserve">5.26464748382568</t>
@@ -1718,58 +1718,58 @@
     <t xml:space="preserve">5.26863098144531</t>
   </si>
   <si>
-    <t xml:space="preserve">5.23941993713379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.26331853866577</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.27394151687622</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.27659749984741</t>
+    <t xml:space="preserve">5.23942041397095</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.26331949234009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.27394199371338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.27659702301025</t>
   </si>
   <si>
     <t xml:space="preserve">5.18630790710449</t>
   </si>
   <si>
-    <t xml:space="preserve">5.24605798721313</t>
+    <t xml:space="preserve">5.24605894088745</t>
   </si>
   <si>
     <t xml:space="preserve">5.27128648757935</t>
   </si>
   <si>
-    <t xml:space="preserve">5.28456449508667</t>
+    <t xml:space="preserve">5.28456401824951</t>
   </si>
   <si>
     <t xml:space="preserve">5.30580854415894</t>
   </si>
   <si>
-    <t xml:space="preserve">5.36423110961914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.41070175170898</t>
+    <t xml:space="preserve">5.36423063278198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.41070365905762</t>
   </si>
   <si>
     <t xml:space="preserve">5.55011987686157</t>
   </si>
   <si>
-    <t xml:space="preserve">5.60323095321655</t>
+    <t xml:space="preserve">5.60323047637939</t>
   </si>
   <si>
     <t xml:space="preserve">5.73468112945557</t>
   </si>
   <si>
-    <t xml:space="preserve">5.6828989982605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.70281457901001</t>
+    <t xml:space="preserve">5.68289804458618</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.70281505584717</t>
   </si>
   <si>
     <t xml:space="preserve">5.72538661956787</t>
   </si>
   <si>
-    <t xml:space="preserve">5.72671556472778</t>
+    <t xml:space="preserve">5.72671508789062</t>
   </si>
   <si>
     <t xml:space="preserve">5.70679759979248</t>
@@ -1778,25 +1778,25 @@
     <t xml:space="preserve">5.75725412368774</t>
   </si>
   <si>
-    <t xml:space="preserve">5.74264764785767</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.75990962982178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.8063817024231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.80239868164062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.82497072219849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.92455339431763</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.94579792022705</t>
+    <t xml:space="preserve">5.74264860153198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.75990915298462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.80638122558594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.80239820480347</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.82496976852417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.92455387115479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.94579839706421</t>
   </si>
   <si>
     <t xml:space="preserve">5.93650436401367</t>
@@ -1814,37 +1814,37 @@
     <t xml:space="preserve">5.97633743286133</t>
   </si>
   <si>
-    <t xml:space="preserve">6.31757593154907</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.32023239135742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.28172731399536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.14894914627075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.12372255325317</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.14231014251709</t>
+    <t xml:space="preserve">6.31757640838623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.32023334503174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.28172636032104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.14894819259644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.1237211227417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.14230871200562</t>
   </si>
   <si>
     <t xml:space="preserve">6.223304271698</t>
   </si>
   <si>
-    <t xml:space="preserve">6.31359338760376</t>
+    <t xml:space="preserve">6.31359386444092</t>
   </si>
   <si>
     <t xml:space="preserve">6.26712131500244</t>
   </si>
   <si>
-    <t xml:space="preserve">6.2060432434082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.25251626968384</t>
+    <t xml:space="preserve">6.20604372024536</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.25251531600952</t>
   </si>
   <si>
     <t xml:space="preserve">6.0546760559082</t>
@@ -1856,13 +1856,13 @@
     <t xml:space="preserve">5.97500991821289</t>
   </si>
   <si>
-    <t xml:space="preserve">5.90596485137939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.08787202835083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.04936647415161</t>
+    <t xml:space="preserve">5.90596437454224</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.08787059783936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.04936599731445</t>
   </si>
   <si>
     <t xml:space="preserve">6.12770414352417</t>
@@ -1880,34 +1880,34 @@
     <t xml:space="preserve">5.82098722457886</t>
   </si>
   <si>
-    <t xml:space="preserve">5.92189836502075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.90729236602783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.86082077026367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.83028125762939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.77584266662598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.78779268264771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.93517589569092</t>
+    <t xml:space="preserve">5.92189931869507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.90729379653931</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.86081981658936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.83028173446655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.77584314346313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.78779315948486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.93517637252808</t>
   </si>
   <si>
     <t xml:space="preserve">5.89401483535767</t>
   </si>
   <si>
-    <t xml:space="preserve">5.92588138580322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.04272699356079</t>
+    <t xml:space="preserve">5.92588186264038</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.04272651672363</t>
   </si>
   <si>
     <t xml:space="preserve">6.09982109069824</t>
@@ -1916,7 +1916,7 @@
     <t xml:space="preserve">6.12903213500977</t>
   </si>
   <si>
-    <t xml:space="preserve">6.15293169021606</t>
+    <t xml:space="preserve">6.15293264389038</t>
   </si>
   <si>
     <t xml:space="preserve">6.12106561660767</t>
@@ -1928,7 +1928,7 @@
     <t xml:space="preserve">6.22197675704956</t>
   </si>
   <si>
-    <t xml:space="preserve">6.31624937057495</t>
+    <t xml:space="preserve">6.31624794006348</t>
   </si>
   <si>
     <t xml:space="preserve">6.42833042144775</t>
@@ -1937,37 +1937,37 @@
     <t xml:space="preserve">6.38377666473389</t>
   </si>
   <si>
-    <t xml:space="preserve">6.35732269287109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.36289119720459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.44643115997314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.43529319763184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.58983898162842</t>
+    <t xml:space="preserve">6.35732221603394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.36289072036743</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.44643068313599</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.43529415130615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.58983993530273</t>
   </si>
   <si>
     <t xml:space="preserve">6.74577856063843</t>
   </si>
   <si>
-    <t xml:space="preserve">6.78754854202271</t>
+    <t xml:space="preserve">6.78754901885986</t>
   </si>
   <si>
     <t xml:space="preserve">6.76248741149902</t>
   </si>
   <si>
-    <t xml:space="preserve">6.75273990631104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.72071552276611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.78615760803223</t>
+    <t xml:space="preserve">6.75274133682251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.7207179069519</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.78615617752075</t>
   </si>
   <si>
     <t xml:space="preserve">6.71932506561279</t>
@@ -1976,154 +1976,154 @@
     <t xml:space="preserve">6.72350168228149</t>
   </si>
   <si>
-    <t xml:space="preserve">6.69426250457764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.67337894439697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.65945482254028</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.54389238357544</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.57313251495361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.5313606262207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.59540796279907</t>
+    <t xml:space="preserve">6.69426345825195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.67337942123413</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.65945625305176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.5438928604126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.57313203811646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.53136205673218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.59540843963623</t>
   </si>
   <si>
     <t xml:space="preserve">6.54806995391846</t>
   </si>
   <si>
-    <t xml:space="preserve">6.67477083206177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.50073194503784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.72489500045776</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.79172468185425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.71236276626587</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.60515594482422</t>
+    <t xml:space="preserve">6.67477226257324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.50073099136353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.72489404678345</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.79172515869141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.71236371994019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.6051549911499</t>
   </si>
   <si>
     <t xml:space="preserve">6.60097885131836</t>
   </si>
   <si>
-    <t xml:space="preserve">6.70957899093628</t>
+    <t xml:space="preserve">6.7095775604248</t>
   </si>
   <si>
     <t xml:space="preserve">6.26125288009644</t>
   </si>
   <si>
-    <t xml:space="preserve">6.33504676818848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.48123979568481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.36567640304565</t>
+    <t xml:space="preserve">6.33504629135132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.48123931884766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.3656759262085</t>
   </si>
   <si>
     <t xml:space="preserve">6.61350917816162</t>
   </si>
   <si>
-    <t xml:space="preserve">6.56756401062012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.75134801864624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.72767877578735</t>
+    <t xml:space="preserve">6.5675630569458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.75134754180908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.7276782989502</t>
   </si>
   <si>
     <t xml:space="preserve">6.55781602859497</t>
   </si>
   <si>
-    <t xml:space="preserve">6.61211681365967</t>
+    <t xml:space="preserve">6.61211776733398</t>
   </si>
   <si>
     <t xml:space="preserve">6.54249954223633</t>
   </si>
   <si>
-    <t xml:space="preserve">6.85020399093628</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.80286502838135</t>
+    <t xml:space="preserve">6.85020351409912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.80286359786987</t>
   </si>
   <si>
     <t xml:space="preserve">6.8752646446228</t>
   </si>
   <si>
-    <t xml:space="preserve">6.89197206497192</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.02424192428589</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.99639701843262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.01380109786987</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.01728010177612</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.89893388748169</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.92677974700928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.04860877990723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.0903787612915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.00335836410522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.94348812103271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.07297277450562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.08689785003662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.00683784484863</t>
+    <t xml:space="preserve">6.89197111129761</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.02424335479736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.99639558792114</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.01380157470703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.01728057861328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.89893341064453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.92678022384644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.04860830307007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.09037828445435</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.00335693359375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.94348764419556</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.07297325134277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.08689737319946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.00683975219727</t>
   </si>
   <si>
     <t xml:space="preserve">7.15303182601929</t>
   </si>
   <si>
-    <t xml:space="preserve">7.11126232147217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.10778188705444</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.14259004592896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.26093721389771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.15999317169189</t>
+    <t xml:space="preserve">7.11126327514648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.1077823638916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.14259052276611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.26093816757202</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.15999412536621</t>
   </si>
   <si>
     <t xml:space="preserve">6.93652677536011</t>
@@ -2135,106 +2135,106 @@
     <t xml:space="preserve">6.94766473770142</t>
   </si>
   <si>
-    <t xml:space="preserve">7.14607000350952</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.05208873748779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.13562822341919</t>
+    <t xml:space="preserve">7.14607095718384</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.05209016799927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.13562870025635</t>
   </si>
   <si>
     <t xml:space="preserve">7.36536121368408</t>
   </si>
   <si>
-    <t xml:space="preserve">7.37580394744873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.47674560546875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.36884069442749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.45238018035889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.49415063858032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.51851558685303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.60553646087646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.62293815612793</t>
+    <t xml:space="preserve">7.37580347061157</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.47674417495728</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.36884164810181</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.4523811340332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.49414968490601</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.51851511001587</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.60553550720215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.6229395866394</t>
   </si>
   <si>
     <t xml:space="preserve">7.65078496932983</t>
   </si>
   <si>
-    <t xml:space="preserve">7.56028509140015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.59509229660034</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.58117055892944</t>
+    <t xml:space="preserve">7.56028413772583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.59509325027466</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.58116960525513</t>
   </si>
   <si>
     <t xml:space="preserve">7.57420778274536</t>
   </si>
   <si>
-    <t xml:space="preserve">7.67863082885742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.72388124465942</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.77609300613403</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.65426588058472</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.54636287689209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.63686370849609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.80045890808105</t>
+    <t xml:space="preserve">7.67863273620605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.72388315200806</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.77609491348267</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.65426635742188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.54636144638062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.63686323165894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.80046033859253</t>
   </si>
   <si>
     <t xml:space="preserve">7.73780584335327</t>
   </si>
   <si>
-    <t xml:space="preserve">7.75520896911621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.76913166046143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.81078052520752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.67665958404541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.74724960327148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.65195369720459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.71548509597778</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.73666048049927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.66607141494751</t>
+    <t xml:space="preserve">7.75521087646484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.76913213729858</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.81078100204468</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.67666006088257</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.7472505569458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.65195322036743</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.71548414230347</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.73666191101074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.66607189178467</t>
   </si>
   <si>
     <t xml:space="preserve">7.61665868759155</t>
@@ -2243,133 +2243,133 @@
     <t xml:space="preserve">7.50724411010742</t>
   </si>
   <si>
-    <t xml:space="preserve">7.47547721862793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.23194313049316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.30959177017212</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.40488862991333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.27076816558838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.28135538101196</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.18959093093872</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.2919454574585</t>
+    <t xml:space="preserve">7.47547912597656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.23194360733032</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.30959272384644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.40488767623901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.27076721191406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.28135681152344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.1895899772644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.29194450378418</t>
   </si>
   <si>
     <t xml:space="preserve">7.21076679229736</t>
   </si>
   <si>
-    <t xml:space="preserve">7.3307671546936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.17900133132935</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.24253177642822</t>
+    <t xml:space="preserve">7.33076906204224</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.17900037765503</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.24253225326538</t>
   </si>
   <si>
     <t xml:space="preserve">7.17547130584717</t>
   </si>
   <si>
-    <t xml:space="preserve">7.26723766326904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.36253452301025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.14370632171631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.19664812088013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.10488128662109</t>
+    <t xml:space="preserve">7.26723861694336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.36253595352173</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.14370536804199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.19664716720581</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.10488080978394</t>
   </si>
   <si>
     <t xml:space="preserve">7.04346752166748</t>
   </si>
   <si>
-    <t xml:space="preserve">7.22488355636597</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.12605857849121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.23900175094604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.2072377204895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.16488218307495</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.10135126113892</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.09076356887817</t>
+    <t xml:space="preserve">7.22488403320312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.12605953216553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.23900318145752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.20723676681519</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.16488265991211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.10135221481323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.0907621383667</t>
   </si>
   <si>
     <t xml:space="preserve">7.26017904281616</t>
   </si>
   <si>
-    <t xml:space="preserve">7.32723903656006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.34841585159302</t>
+    <t xml:space="preserve">7.3272385597229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.34841632843018</t>
   </si>
   <si>
     <t xml:space="preserve">7.25312042236328</t>
   </si>
   <si>
-    <t xml:space="preserve">7.47194862365723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.82136869430542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.76136827468872</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.30606317520142</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.41547632217407</t>
+    <t xml:space="preserve">7.47194957733154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.82136964797974</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.7613673210144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.30606269836426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.41547775268555</t>
   </si>
   <si>
     <t xml:space="preserve">7.55665636062622</t>
   </si>
   <si>
-    <t xml:space="preserve">7.57077503204346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.62018823623657</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.69783735275269</t>
+    <t xml:space="preserve">7.57077550888062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.62018775939941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.69783639907837</t>
   </si>
   <si>
     <t xml:space="preserve">7.78960418701172</t>
   </si>
   <si>
-    <t xml:space="preserve">7.7507791519165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.72960233688354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.7190146446228</t>
+    <t xml:space="preserve">7.75078058242798</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.72960186004639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.71901559829712</t>
   </si>
   <si>
     <t xml:space="preserve">8.00490379333496</t>
@@ -2381,73 +2381,73 @@
     <t xml:space="preserve">7.96607828140259</t>
   </si>
   <si>
-    <t xml:space="preserve">7.97313785552979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.40841865539551</t>
+    <t xml:space="preserve">7.9731388092041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.40841817855835</t>
   </si>
   <si>
     <t xml:space="preserve">7.29547357559204</t>
   </si>
   <si>
-    <t xml:space="preserve">7.44018363952637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.11899900436401</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.78652095794678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.53804397583008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.7907567024231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.8387565612793</t>
+    <t xml:space="preserve">7.44018411636353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.11899995803833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.78652000427246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.53804349899292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.79075574874878</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.83875608444214</t>
   </si>
   <si>
     <t xml:space="preserve">6.65804719924927</t>
   </si>
   <si>
-    <t xml:space="preserve">6.86275768280029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.97050046920776</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.56107759475708</t>
+    <t xml:space="preserve">6.86275720596313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.97049999237061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.5610785484314</t>
   </si>
   <si>
     <t xml:space="preserve">5.56248998641968</t>
   </si>
   <si>
-    <t xml:space="preserve">4.33704853057861</t>
+    <t xml:space="preserve">4.3370475769043</t>
   </si>
   <si>
     <t xml:space="preserve">4.76058769226074</t>
   </si>
   <si>
-    <t xml:space="preserve">4.58975982666016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.58552503585815</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.49658060073853</t>
+    <t xml:space="preserve">4.589759349823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.585524559021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.49658107757568</t>
   </si>
   <si>
     <t xml:space="preserve">4.88059091567993</t>
   </si>
   <si>
-    <t xml:space="preserve">4.89612007141113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.06553745269775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.41142797470093</t>
+    <t xml:space="preserve">4.89612054824829</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.0655369758606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.41142702102661</t>
   </si>
   <si>
     <t xml:space="preserve">5.46084070205688</t>
@@ -2456,25 +2456,25 @@
     <t xml:space="preserve">5.71637630462646</t>
   </si>
   <si>
-    <t xml:space="preserve">5.54272508621216</t>
+    <t xml:space="preserve">5.542724609375</t>
   </si>
   <si>
     <t xml:space="preserve">5.58790254592896</t>
   </si>
   <si>
-    <t xml:space="preserve">5.44954586029053</t>
+    <t xml:space="preserve">5.44954633712769</t>
   </si>
   <si>
     <t xml:space="preserve">5.21801137924194</t>
   </si>
   <si>
-    <t xml:space="preserve">5.486252784729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.5271954536438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.67543411254883</t>
+    <t xml:space="preserve">5.48625373840332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.52719497680664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.67543363571167</t>
   </si>
   <si>
     <t xml:space="preserve">5.7573184967041</t>
@@ -2483,13 +2483,13 @@
     <t xml:space="preserve">5.84343814849854</t>
   </si>
   <si>
-    <t xml:space="preserve">5.86320304870605</t>
+    <t xml:space="preserve">5.86320352554321</t>
   </si>
   <si>
     <t xml:space="preserve">5.88720417022705</t>
   </si>
   <si>
-    <t xml:space="preserve">5.36907339096069</t>
+    <t xml:space="preserve">5.36907291412354</t>
   </si>
   <si>
     <t xml:space="preserve">5.41283941268921</t>
@@ -2498,7 +2498,7 @@
     <t xml:space="preserve">5.43542814254761</t>
   </si>
   <si>
-    <t xml:space="preserve">5.37330913543701</t>
+    <t xml:space="preserve">5.3733081817627</t>
   </si>
   <si>
     <t xml:space="preserve">5.25895309448242</t>
@@ -2507,25 +2507,25 @@
     <t xml:space="preserve">5.34224939346313</t>
   </si>
   <si>
-    <t xml:space="preserve">5.30695486068726</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.22224712371826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.56390237808228</t>
+    <t xml:space="preserve">5.3069543838501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.22224569320679</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.56390190124512</t>
   </si>
   <si>
     <t xml:space="preserve">5.5540189743042</t>
   </si>
   <si>
-    <t xml:space="preserve">5.66837501525879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.47213506698608</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.33942604064941</t>
+    <t xml:space="preserve">5.66837453842163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.47213554382324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.33942556381226</t>
   </si>
   <si>
     <t xml:space="preserve">5.18836307525635</t>
@@ -2534,19 +2534,19 @@
     <t xml:space="preserve">5.10224390029907</t>
   </si>
   <si>
-    <t xml:space="preserve">5.36060190200806</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.4749584197998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.25612926483154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.16012668609619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.07259559631348</t>
+    <t xml:space="preserve">5.36060285568237</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.47495889663696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.2561297416687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.16012716293335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.07259607315063</t>
   </si>
   <si>
     <t xml:space="preserve">5.2674241065979</t>
@@ -2558,37 +2558,37 @@
     <t xml:space="preserve">5.23495244979858</t>
   </si>
   <si>
-    <t xml:space="preserve">5.20248126983643</t>
+    <t xml:space="preserve">5.20248174667358</t>
   </si>
   <si>
     <t xml:space="preserve">5.25330591201782</t>
   </si>
   <si>
-    <t xml:space="preserve">5.46225261688232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.5441370010376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.57237243652344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.62319803237915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.68813991546631</t>
+    <t xml:space="preserve">5.46225214004517</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.54413652420044</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.5723729133606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.62319707870483</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.68813943862915</t>
   </si>
   <si>
     <t xml:space="preserve">5.86037969589233</t>
   </si>
   <si>
-    <t xml:space="preserve">6.04814958572388</t>
+    <t xml:space="preserve">6.0481481552124</t>
   </si>
   <si>
     <t xml:space="preserve">6.19074106216431</t>
   </si>
   <si>
-    <t xml:space="preserve">6.31921482086182</t>
+    <t xml:space="preserve">6.31921434402466</t>
   </si>
   <si>
     <t xml:space="preserve">6.12438583374023</t>
@@ -2597,13 +2597,13 @@
     <t xml:space="preserve">6.05379581451416</t>
   </si>
   <si>
-    <t xml:space="preserve">5.73472881317139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.82226085662842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.87167406082153</t>
+    <t xml:space="preserve">5.7347297668457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.82226133346558</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.87167358398438</t>
   </si>
   <si>
     <t xml:space="preserve">5.99026536941528</t>
@@ -2621,13 +2621,13 @@
     <t xml:space="preserve">5.92205286026001</t>
   </si>
   <si>
-    <t xml:space="preserve">6.02327013015747</t>
+    <t xml:space="preserve">6.02327108383179</t>
   </si>
   <si>
     <t xml:space="preserve">5.75628709793091</t>
   </si>
   <si>
-    <t xml:space="preserve">5.79736137390137</t>
+    <t xml:space="preserve">5.79736232757568</t>
   </si>
   <si>
     <t xml:space="preserve">5.68147277832031</t>
@@ -2636,31 +2636,31 @@
     <t xml:space="preserve">5.85457277297974</t>
   </si>
   <si>
-    <t xml:space="preserve">5.67707252502441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.68734073638916</t>
+    <t xml:space="preserve">5.67707204818726</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.68734121322632</t>
   </si>
   <si>
     <t xml:space="preserve">5.71227884292603</t>
   </si>
   <si>
-    <t xml:space="preserve">5.80469608306885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.77242279052734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.72694826126099</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.59198951721191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.6403980255127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.74748611450195</t>
+    <t xml:space="preserve">5.80469703674316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.7724232673645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.72694778442383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.59198999404907</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.64039850234985</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.74748516082764</t>
   </si>
   <si>
     <t xml:space="preserve">5.72548151016235</t>
@@ -2672,55 +2672,55 @@
     <t xml:space="preserve">5.76655626296997</t>
   </si>
   <si>
-    <t xml:space="preserve">6.00420045852661</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.04820871353149</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.10248613357544</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.0056676864624</t>
+    <t xml:space="preserve">6.00420093536377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.04820966720581</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.10248565673828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.00566720962524</t>
   </si>
   <si>
     <t xml:space="preserve">5.97632884979248</t>
   </si>
   <si>
-    <t xml:space="preserve">5.82670068740845</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.7944278717041</t>
+    <t xml:space="preserve">5.82670021057129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.79442834854126</t>
   </si>
   <si>
     <t xml:space="preserve">5.77975845336914</t>
   </si>
   <si>
-    <t xml:space="preserve">5.58172082901001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.68587398529053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.79149436950684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.8311014175415</t>
+    <t xml:space="preserve">5.58172130584717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.68587350845337</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.79149341583252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.83110094070435</t>
   </si>
   <si>
     <t xml:space="preserve">5.82963418960571</t>
   </si>
   <si>
-    <t xml:space="preserve">5.73868370056152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.78415966033936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.88537836074829</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.97926235198975</t>
+    <t xml:space="preserve">5.73868417739868</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.78415870666504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.88537883758545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.9792628288269</t>
   </si>
   <si>
     <t xml:space="preserve">5.97192811965942</t>
@@ -2729,85 +2729,85 @@
     <t xml:space="preserve">5.90004730224609</t>
   </si>
   <si>
-    <t xml:space="preserve">5.87511014938354</t>
+    <t xml:space="preserve">5.87510919570923</t>
   </si>
   <si>
     <t xml:space="preserve">5.78269195556641</t>
   </si>
   <si>
-    <t xml:space="preserve">5.76362228393555</t>
+    <t xml:space="preserve">5.76362180709839</t>
   </si>
   <si>
     <t xml:space="preserve">5.82376670837402</t>
   </si>
   <si>
-    <t xml:space="preserve">5.72401428222656</t>
+    <t xml:space="preserve">5.72401475906372</t>
   </si>
   <si>
     <t xml:space="preserve">5.80176258087158</t>
   </si>
   <si>
-    <t xml:space="preserve">5.82083225250244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.75335311889648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.75775384902954</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.6726713180542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.63013076782227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.64186525344849</t>
+    <t xml:space="preserve">5.82083177566528</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.7533540725708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.75775480270386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.67267179489136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.63013029098511</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.64186573028564</t>
   </si>
   <si>
     <t xml:space="preserve">5.83696937561035</t>
   </si>
   <si>
-    <t xml:space="preserve">5.7166805267334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.85310506820679</t>
+    <t xml:space="preserve">5.71668004989624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.85310554504395</t>
   </si>
   <si>
     <t xml:space="preserve">5.8428373336792</t>
   </si>
   <si>
-    <t xml:space="preserve">5.84577131271362</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.81203126907349</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.69320917129517</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.49517154693604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.57291984558105</t>
+    <t xml:space="preserve">5.84577035903931</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.81203079223633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.69320869445801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.49517107009888</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.57291889190674</t>
   </si>
   <si>
     <t xml:space="preserve">5.61839437484741</t>
   </si>
   <si>
-    <t xml:space="preserve">5.60665941238403</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.56411790847778</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.66973781585693</t>
+    <t xml:space="preserve">5.60665893554688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.56411743164062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.66973733901978</t>
   </si>
   <si>
     <t xml:space="preserve">5.55678367614746</t>
   </si>
   <si>
-    <t xml:space="preserve">5.5509147644043</t>
+    <t xml:space="preserve">5.55091524124146</t>
   </si>
   <si>
     <t xml:space="preserve">5.509840965271</t>
@@ -2816,46 +2816,46 @@
     <t xml:space="preserve">5.54211378097534</t>
   </si>
   <si>
-    <t xml:space="preserve">5.9323205947876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.88097715377808</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.87804317474365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.87950992584229</t>
+    <t xml:space="preserve">5.93232107162476</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.88097763061523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.87804412841797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.87951040267944</t>
   </si>
   <si>
     <t xml:space="preserve">5.89271306991577</t>
   </si>
   <si>
-    <t xml:space="preserve">5.8941798210144</t>
+    <t xml:space="preserve">5.89417934417725</t>
   </si>
   <si>
     <t xml:space="preserve">5.59932374954224</t>
   </si>
   <si>
-    <t xml:space="preserve">5.6682710647583</t>
+    <t xml:space="preserve">5.66827058792114</t>
   </si>
   <si>
     <t xml:space="preserve">5.67560529708862</t>
   </si>
   <si>
-    <t xml:space="preserve">5.56998443603516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.57878684997559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.56851816177368</t>
+    <t xml:space="preserve">5.56998538970947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.57878637313843</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.56851863861084</t>
   </si>
   <si>
     <t xml:space="preserve">5.47903442382812</t>
   </si>
   <si>
-    <t xml:space="preserve">5.4394268989563</t>
+    <t xml:space="preserve">5.43942737579346</t>
   </si>
   <si>
     <t xml:space="preserve">5.21058368682861</t>
@@ -2867,22 +2867,22 @@
     <t xml:space="preserve">5.1343035697937</t>
   </si>
   <si>
-    <t xml:space="preserve">5.25752687454224</t>
+    <t xml:space="preserve">5.25752639770508</t>
   </si>
   <si>
     <t xml:space="preserve">5.30740261077881</t>
   </si>
   <si>
-    <t xml:space="preserve">5.47463417053223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.65506839752197</t>
+    <t xml:space="preserve">5.47463464736938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.65506744384766</t>
   </si>
   <si>
     <t xml:space="preserve">5.56265068054199</t>
   </si>
   <si>
-    <t xml:space="preserve">5.75922107696533</t>
+    <t xml:space="preserve">5.75922155380249</t>
   </si>
   <si>
     <t xml:space="preserve">5.90151453018188</t>
@@ -2891,190 +2891,190 @@
     <t xml:space="preserve">5.85897350311279</t>
   </si>
   <si>
-    <t xml:space="preserve">6.03647327423096</t>
+    <t xml:space="preserve">6.03647375106812</t>
   </si>
   <si>
     <t xml:space="preserve">6.2374439239502</t>
   </si>
   <si>
-    <t xml:space="preserve">6.3181266784668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.4252142906189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.49416017532349</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.39440870285034</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.42820358276367</t>
+    <t xml:space="preserve">6.31812620162964</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.42521381378174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.49415922164917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.39440774917603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.42820310592651</t>
   </si>
   <si>
     <t xml:space="preserve">6.57317733764648</t>
   </si>
   <si>
-    <t xml:space="preserve">6.51040506362915</t>
+    <t xml:space="preserve">6.51040410995483</t>
   </si>
   <si>
     <t xml:space="preserve">6.57616662979126</t>
   </si>
   <si>
-    <t xml:space="preserve">6.38486003875732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.43567657470703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.33254957199097</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.35496711730957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.2832293510437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.27276563644409</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.28173351287842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.29070138931274</t>
+    <t xml:space="preserve">6.38486051559448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.43567609786987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.33254909515381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.35496759414673</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.28322887420654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.27276659011841</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.28173398971558</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.29070091247559</t>
   </si>
   <si>
     <t xml:space="preserve">6.23988580703735</t>
   </si>
   <si>
-    <t xml:space="preserve">6.23540115356445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.3355393409729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.26977729797363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.24586391448975</t>
+    <t xml:space="preserve">6.23540210723877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.33553791046143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.26977777481079</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.24586343765259</t>
   </si>
   <si>
     <t xml:space="preserve">6.10238409042358</t>
   </si>
   <si>
-    <t xml:space="preserve">6.22792863845825</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.25333642959595</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.21746683120728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.23390674591064</t>
+    <t xml:space="preserve">6.22792816162109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.25333690643311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.21746635437012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.23390769958496</t>
   </si>
   <si>
     <t xml:space="preserve">6.19355344772339</t>
   </si>
   <si>
-    <t xml:space="preserve">6.38187074661255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.51488924026489</t>
+    <t xml:space="preserve">6.38187026977539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.51488876342773</t>
   </si>
   <si>
     <t xml:space="preserve">6.4222240447998</t>
   </si>
   <si>
-    <t xml:space="preserve">6.37738752365112</t>
+    <t xml:space="preserve">6.37738704681396</t>
   </si>
   <si>
     <t xml:space="preserve">6.30265760421753</t>
   </si>
   <si>
-    <t xml:space="preserve">6.241379737854</t>
+    <t xml:space="preserve">6.24137878417969</t>
   </si>
   <si>
     <t xml:space="preserve">6.26230430603027</t>
   </si>
   <si>
-    <t xml:space="preserve">6.20999336242676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.27426099777222</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.21597242355347</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.17860698699951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.13377046585083</t>
+    <t xml:space="preserve">6.20999431610107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.2742600440979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.21597146987915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.17860794067383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.13376998901367</t>
   </si>
   <si>
     <t xml:space="preserve">6.24885368347168</t>
   </si>
   <si>
-    <t xml:space="preserve">6.097900390625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.15320014953613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.03512763977051</t>
+    <t xml:space="preserve">6.09789943695068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.15319919586182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.03512716293335</t>
   </si>
   <si>
     <t xml:space="preserve">6.19803714752197</t>
   </si>
   <si>
-    <t xml:space="preserve">6.18757486343384</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.62847757339478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.73459196090698</t>
+    <t xml:space="preserve">6.187575340271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.62847661972046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.73459243774414</t>
   </si>
   <si>
     <t xml:space="preserve">6.89002895355225</t>
   </si>
   <si>
-    <t xml:space="preserve">7.06638956069946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.15158081054688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.10973310470581</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.21136474609375</t>
+    <t xml:space="preserve">7.06639051437378</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.15158033370972</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.10973215103149</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.21136522293091</t>
   </si>
   <si>
     <t xml:space="preserve">7.23228931427002</t>
   </si>
   <si>
-    <t xml:space="preserve">7.30103921890259</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.21285963058472</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.08582067489624</t>
+    <t xml:space="preserve">7.30104064941406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.21285915374756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.08581972122192</t>
   </si>
   <si>
     <t xml:space="preserve">6.9528021812439</t>
   </si>
   <si>
-    <t xml:space="preserve">7.02304649353027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.20688104629517</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.12019443511963</t>
+    <t xml:space="preserve">7.02304601669312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.20688152313232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.1201958656311</t>
   </si>
   <si>
     <t xml:space="preserve">7.13663530349731</t>
@@ -3083,901 +3083,901 @@
     <t xml:space="preserve">7.1799783706665</t>
   </si>
   <si>
-    <t xml:space="preserve">7.02753114700317</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.34438180923462</t>
+    <t xml:space="preserve">7.02753162384033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.34438228607178</t>
   </si>
   <si>
     <t xml:space="preserve">7.38025236129761</t>
   </si>
   <si>
+    <t xml:space="preserve">7.43555307388306</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.45348739624023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.36082410812378</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.50280857086182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.57753753662109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.6447925567627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.61116600036621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.67842102050781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.63358545303345</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.79798936843872</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.75688791275024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.81293487548828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.72699737548828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.85029888153076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.78304243087769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.824143409729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.81667041778564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.88392686843872</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.0558032989502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.11185073852539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.10064220428467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.15295314788818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.17536926269531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.16416072845459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.04833221435547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.06701469421387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.05953979492188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.96986627578735</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.96239280700684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.05206775665283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.04085826873779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.93250226974487</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.92876386642456</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.10811424255371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.07822322845459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.08943176269531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.16042423248291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.15668964385986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.14547729492188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.25757312774658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.19778919219971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.16789817810059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.22020816802979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.38834953308105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.35098457336426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.24636363983154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.25010013580322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.30988216400146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.43692398071289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.42571353912354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.3920841217041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.46307849884033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.59385395050049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.74331092834473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.62748146057129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.53407096862793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.58638191223145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.59759044647217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.64242744445801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.81804084777832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.90024375915527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.01233768463135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.02728271484375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.95629024505615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.97871017456055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.95255374908447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.01981067657471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.96376323699951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.73957633972168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.85025215148926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.73112106323242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.62736320495605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.78107929229736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.75417900085449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.61198997497559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.57356071472168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.56971836090088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.66963386535645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.59277534484863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.7157506942749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.58509063720703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.6196756362915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.3199291229248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.45058822631836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.48133182525635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.47748947143555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.44674587249756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.33145713806152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.35835742950439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.07398128509521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.15468311309814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.41215801239014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.53897476196289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.61583423614502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.68500709533691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.60046100616455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.58124828338623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.55050468444824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.7272777557373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.85793781280518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.9002103805542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.93479633331299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.0078125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.02702522277832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.98091125488281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.92326641082764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.8733081817627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.94632625579834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.83487987518311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.76955032348633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.96169567108154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.93863868713379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.9078950881958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.82719326019287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.86562347412109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.91173934936523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.94248199462891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.80797958374023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.86946678161621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.88483810424805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.96553897857666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.1077299118042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.02318382263184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.05777072906494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.13847064971924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.20380115509033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.16921520233154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.25375843048096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.03086853027344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.09235668182373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.14999961853027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.11157131195068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.29603099822998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.24223041534424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.35751724243164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.36136150360107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.34598922729492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.46896266937256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.50354766845703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.60730743408203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.54966354370117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.5189208984375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.4151611328125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.64958000183105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.61499309539795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.595778465271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.74181079864502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.65726566314697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.64189338684082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.48433399200439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.56503582000732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.53044986724854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.64573764801025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.57656478881836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.60346508026123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.56119155883789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.46511936187744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.4113187789917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.42284870147705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.33446025848389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.27297306060791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.25345993041992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.17930793762207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.15198707580566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.01539134979248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.64462757110596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.73829364776611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.6953649520874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.85927963256836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.7656135559082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.69926738739014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.73048877716064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.85147476196289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.72658634185791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.66414165496826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.62511444091797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.62901782989502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.64853000640869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.68755912780762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.75000190734863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.76171016693115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.56267070770264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.70316886901855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.78903007507324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.86708545684814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.94514083862305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.01929378509521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.99977970123291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.0075855255127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.13637542724609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.14808559417725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.1832103729248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.1051549911499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.13247394561768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.15979194641113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.09734916687012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.05441761016846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.06222438812256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.02709865570068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.04661178588867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.12076568603516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.96465396881104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.60560035705566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.81634998321533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.01148891448975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.9022102355957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.31200218200684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.3198070526123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.50022602081299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.55486392974854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.59389209747314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.42607307434082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.58218383789062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.66023826599121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.69146156311035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.61340522766113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.40265560150146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.37143325805664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.30118465423584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.83675527572632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.09433841705322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.02018451690674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.69625616073608</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.68376636505127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.57605123519897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.08742523193359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.93443536758423</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.25602340698242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.89919948577881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.49955654144287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.54482889175415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.74933481216431</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.70718145370483</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.0553092956543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.88748979568481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.86407518386841</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.89529657363892</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.10214328765869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.09043598175049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.23483848571777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.12555885314941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.21922588348389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.289475440979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.25435066223145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.11775398254395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.9967679977417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.82504653930664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.70562219619751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.85626935958862</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.793044090271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.67596054077148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.5979061126709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.65878963470459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.53546190261841</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.73372173309326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.70874500274658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.57292795181274</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.35905647277832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.26070690155029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.23729038238525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.28412389755249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.32002925872803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.24665689468384</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.18889570236206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.13269710540771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.02654027938843</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.84389066696167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.0062460899353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.16860103607178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.39340114593506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.54795074462891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.44179534912109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.51204395294189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.46677350997925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.44023370742798</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.4183783531189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.56356143951416</t>
+  </si>
+  <si>
     <t xml:space="preserve">7.43555116653442</t>
   </si>
   <si>
-    <t xml:space="preserve">7.45348596572876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.36082315444946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.50280904769897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.57753801345825</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.64479303359985</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.61116743087769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.67842102050781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.63358449935913</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.79798793792725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.75688695907593</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.81293439865112</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.72699689865112</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.85029888153076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.78304195404053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.82414388656616</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.81667184829712</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.8839282989502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.05580425262451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.11184978485107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.10064220428467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.15295124053955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.17537117004395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.16416168212891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.04833126068115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.06701374053955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.05953979492188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.96986627578735</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.96239233016968</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.05206680297852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.04085922241211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.93250036239624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.92876291275024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.10811424255371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.07822418212891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.08943176269531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.16042518615723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.15668773651123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.14547824859619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.2575740814209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.19779014587402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.16789817810059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.2202091217041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.38834857940674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.35098361968994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.24636459350586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.25009918212891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.30988311767578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.43692398071289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.42571353912354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.3920841217041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.46307754516602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.59385395050049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.74331283569336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.62748146057129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.53407192230225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.58638095855713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.59759140014648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.64242744445801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.81804180145264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.90024375915527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.01233673095703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.02728366851807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.95629119873047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.97871017456055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.95255279541016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.01980972290039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.96376419067383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.73957633972168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.85025215148926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.73112201690674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.62736225128174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.78107929229736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.75417995452881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.6119909286499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.573561668396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.56971836090088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.66963386535645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.59277725219727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.71574974060059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.58509063720703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.61967658996582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.31992816925049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.45058822631836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.48133182525635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.47748756408691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.44674491882324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.33145809173584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.35835647583008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.07398128509521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.15468215942383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.41215801239014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.53897476196289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.61583423614502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.6850061416626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.60046100616455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.58124732971191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.55050373077393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.7272777557373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.85793685913086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.90020942687988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.93479633331299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.0078125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.02702617645264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.98091125488281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.92326831817627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.87330913543701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.94632434844971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.83487987518311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.76955127716064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.96169567108154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.93863964080811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.90789604187012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.82719421386719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.86562442779541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.91173839569092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.94248199462891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.80798053741455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.86946582794189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.88483715057373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.96554088592529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.10772895812988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.02318286895752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.05776882171631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.13847255706787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.20380210876465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.16921520233154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.25375843048096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.03086948394775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.09235668182373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.14999961853027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.11157035827637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.29603099822998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.24222850799561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.35751819610596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.36136150360107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.34598922729492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.46896171569824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.50354862213135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.60730648040771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.54966354370117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.51891994476318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.41516208648682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.64958000183105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.61499309539795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.595778465271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.74181079864502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.65726566314697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.64189338684082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.48433494567871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.56503391265869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.53044891357422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.64573860168457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.57656383514404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.60346508026123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.56119346618652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.46511840820312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.41131782531738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.42284774780273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.3344612121582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.27297306060791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.25345897674561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.17930603027344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.15198802947998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.01539039611816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.64462757110596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.73829460144043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.69536304473877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.85928058624268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.76561260223389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.69926738739014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.73048973083496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.85147476196289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.72658729553223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.66414260864258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.62511539459229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.62901782989502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.64853000640869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.6875581741333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.75000286102295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.76171112060547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.56267070770264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.70316886901855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.78903102874756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.86708641052246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.94514179229736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.01929473876953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.99977874755859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.00758457183838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.13637542724609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.14808559417725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.18320941925049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.10515594482422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.13247394561768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.15979290008545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.09734916687012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.05441951751709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.06222438812256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.02709865570068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.04661273956299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.12076568603516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.96465492248535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.60560035705566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.81634998321533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.01148796081543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.9022102355957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.31200122833252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.3198070526123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.5002269744873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.55486488342285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.59389114379883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.42607307434082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.58218383789062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.66023921966553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.69146156311035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.61340618133545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.40265560150146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.37143421173096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.30118370056152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.83675622940063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.09433746337891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.02018451690674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.69625520706177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.68376684188843</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.57605171203613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.08742380142212</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.93443489074707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.25602340698242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.89919948577881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.49955606460571</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.54482841491699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.74933385848999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.70718383789062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.05530834197998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.88749122619629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.86407470703125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.89529705047607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.10214328765869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.09043502807617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.23483848571777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.12556076049805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.21922492980957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.28947639465332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.25435161590576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.11775398254395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.99676895141602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.82504606246948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.70562267303467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.85626888275146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.79304456710815</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.67596197128296</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.5979061126709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.65878915786743</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.53546047210693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.73372220993042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.70874452590942</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.57292699813843</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.35905790328979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.26070690155029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.23729038238525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.28412294387817</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.32002973556519</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.24665689468384</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.18889570236206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.1326961517334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.02654123306274</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.84389066696167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.00624752044678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.16860198974609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.39340114593506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.54795074462891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.44179582595825</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.51204586029053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.46677207946777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.44023418426514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.4183783531189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.563560962677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.43555021286011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.55887842178345</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.6119556427002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.75245475769043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.92261648178101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.82114505767822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.8172402381897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.74308919906616</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.89139318466187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.87578296661377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.76650428771973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.1436243057251</t>
+    <t xml:space="preserve">7.55887889862061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.61195468902588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.75245571136475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.92261505126953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.82114458084106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.81724166870117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.743088722229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.89139366149902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.87578201293945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.76650619506836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.14362382888794</t>
   </si>
   <si>
     <t xml:space="preserve">6.90477418899536</t>
   </si>
   <si>
-    <t xml:space="preserve">7.1170859336853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.35125112533569</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.98595094680786</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.02185821533203</t>
+    <t xml:space="preserve">7.11708498001099</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.35125160217285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.98595190048218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.02185678482056</t>
   </si>
   <si>
     <t xml:space="preserve">7.18777942657471</t>
   </si>
   <si>
-    <t xml:space="preserve">7.12729549407959</t>
+    <t xml:space="preserve">7.12729644775391</t>
   </si>
   <si>
     <t xml:space="preserve">7.15998983383179</t>
@@ -3986,16 +3986,16 @@
     <t xml:space="preserve">7.10441064834595</t>
   </si>
   <si>
-    <t xml:space="preserve">7.31201696395874</t>
+    <t xml:space="preserve">7.31201648712158</t>
   </si>
   <si>
     <t xml:space="preserve">7.27605390548706</t>
   </si>
   <si>
-    <t xml:space="preserve">7.42154121398926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.3659610748291</t>
+    <t xml:space="preserve">7.42154169082642</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.36596250534058</t>
   </si>
   <si>
     <t xml:space="preserve">7.2842264175415</t>
@@ -4004,25 +4004,25 @@
     <t xml:space="preserve">7.2874960899353</t>
   </si>
   <si>
-    <t xml:space="preserve">7.28095769882202</t>
+    <t xml:space="preserve">7.28095722198486</t>
   </si>
   <si>
     <t xml:space="preserve">6.98834609985352</t>
   </si>
   <si>
-    <t xml:space="preserve">7.03248262405396</t>
+    <t xml:space="preserve">7.03248357772827</t>
   </si>
   <si>
     <t xml:space="preserve">7.21393442153931</t>
   </si>
   <si>
-    <t xml:space="preserve">7.10114002227783</t>
+    <t xml:space="preserve">7.10114049911499</t>
   </si>
   <si>
     <t xml:space="preserve">6.96709489822388</t>
   </si>
   <si>
-    <t xml:space="preserve">6.9981541633606</t>
+    <t xml:space="preserve">6.99815464019775</t>
   </si>
   <si>
     <t xml:space="preserve">6.85103130340576</t>
@@ -4031,31 +4031,31 @@
     <t xml:space="preserve">6.5028395652771</t>
   </si>
   <si>
-    <t xml:space="preserve">6.66794443130493</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.79381656646729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.01940584182739</t>
+    <t xml:space="preserve">6.66794490814209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.79381704330444</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.01940536499023</t>
   </si>
   <si>
     <t xml:space="preserve">6.86410903930664</t>
   </si>
   <si>
-    <t xml:space="preserve">6.5289945602417</t>
+    <t xml:space="preserve">6.52899503707886</t>
   </si>
   <si>
     <t xml:space="preserve">6.61563396453857</t>
   </si>
   <si>
-    <t xml:space="preserve">6.64342403411865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.62871170043945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.6401538848877</t>
+    <t xml:space="preserve">6.64342451095581</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.62871122360229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.64015483856201</t>
   </si>
   <si>
     <t xml:space="preserve">6.58457469940186</t>
@@ -4073,37 +4073,37 @@
     <t xml:space="preserve">6.77420043945312</t>
   </si>
   <si>
-    <t xml:space="preserve">6.85266590118408</t>
+    <t xml:space="preserve">6.85266542434692</t>
   </si>
   <si>
     <t xml:space="preserve">6.92949676513672</t>
   </si>
   <si>
-    <t xml:space="preserve">6.86574268341064</t>
+    <t xml:space="preserve">6.8657431602478</t>
   </si>
   <si>
     <t xml:space="preserve">6.82814502716064</t>
   </si>
   <si>
-    <t xml:space="preserve">6.86901235580444</t>
+    <t xml:space="preserve">6.86901330947876</t>
   </si>
   <si>
     <t xml:space="preserve">6.97036361694336</t>
   </si>
   <si>
-    <t xml:space="preserve">6.97690391540527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.91805362701416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.82651042938232</t>
+    <t xml:space="preserve">6.97690343856812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.91805410385132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.82651090621948</t>
   </si>
   <si>
     <t xml:space="preserve">6.70227336883545</t>
   </si>
   <si>
-    <t xml:space="preserve">6.53226518630981</t>
+    <t xml:space="preserve">6.5322642326355</t>
   </si>
   <si>
     <t xml:space="preserve">6.63198137283325</t>
@@ -4112,16 +4112,16 @@
     <t xml:space="preserve">6.59928750991821</t>
   </si>
   <si>
-    <t xml:space="preserve">6.57803678512573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.42927837371826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.34754371643066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.49466705322266</t>
+    <t xml:space="preserve">6.57803630828857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.42927885055542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.34754323959351</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.49466609954834</t>
   </si>
   <si>
     <t xml:space="preserve">6.44562530517578</t>
@@ -4133,49 +4133,49 @@
     <t xml:space="preserve">6.44889450073242</t>
   </si>
   <si>
-    <t xml:space="preserve">6.52245569229126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.54043817520142</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.60909605026245</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.71044683456421</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.80035495758057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.81343364715576</t>
+    <t xml:space="preserve">6.52245616912842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.54043769836426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.60909557342529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.71044635772705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.80035543441772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.8134331703186</t>
   </si>
   <si>
     <t xml:space="preserve">6.86737823486328</t>
   </si>
   <si>
-    <t xml:space="preserve">6.76112270355225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.79054689407349</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.64832830429077</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.64505910873413</t>
+    <t xml:space="preserve">6.7611231803894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.79054737091064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.64832782745361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.64505863189697</t>
   </si>
   <si>
     <t xml:space="preserve">6.4537992477417</t>
   </si>
   <si>
-    <t xml:space="preserve">6.51918649673462</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.38350677490234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.3916802406311</t>
+    <t xml:space="preserve">6.51918697357178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.38350629806519</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.39168071746826</t>
   </si>
   <si>
     <t xml:space="preserve">6.25926923751831</t>
@@ -4187,7 +4187,7 @@
     <t xml:space="preserve">6.49793577194214</t>
   </si>
   <si>
-    <t xml:space="preserve">6.68919563293457</t>
+    <t xml:space="preserve">6.68919610977173</t>
   </si>
   <si>
     <t xml:space="preserve">6.59274816513062</t>
@@ -4196,16 +4196,16 @@
     <t xml:space="preserve">6.48158884048462</t>
   </si>
   <si>
-    <t xml:space="preserve">6.39331483840942</t>
+    <t xml:space="preserve">6.39331531524658</t>
   </si>
   <si>
     <t xml:space="preserve">6.40802717208862</t>
   </si>
   <si>
-    <t xml:space="preserve">6.26090431213379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.36389017105103</t>
+    <t xml:space="preserve">6.26090335845947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.36388969421387</t>
   </si>
   <si>
     <t xml:space="preserve">6.46033763885498</t>
@@ -4217,7 +4217,7 @@
     <t xml:space="preserve">6.86247396469116</t>
   </si>
   <si>
-    <t xml:space="preserve">6.82487678527832</t>
+    <t xml:space="preserve">6.82487630844116</t>
   </si>
   <si>
     <t xml:space="preserve">6.80198955535889</t>
@@ -4226,13 +4226,13 @@
     <t xml:space="preserve">6.73660182952881</t>
   </si>
   <si>
-    <t xml:space="preserve">6.8918981552124</t>
+    <t xml:space="preserve">6.89189910888672</t>
   </si>
   <si>
     <t xml:space="preserve">6.95565176010132</t>
   </si>
   <si>
-    <t xml:space="preserve">7.0210394859314</t>
+    <t xml:space="preserve">7.02103996276855</t>
   </si>
   <si>
     <t xml:space="preserve">7.22701215744019</t>
@@ -4241,28 +4241,28 @@
     <t xml:space="preserve">7.17143297195435</t>
   </si>
   <si>
-    <t xml:space="preserve">7.20902967453003</t>
+    <t xml:space="preserve">7.20903015136719</t>
   </si>
   <si>
     <t xml:space="preserve">7.23028135299683</t>
   </si>
   <si>
-    <t xml:space="preserve">7.19268369674683</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.14854717254639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.37740516662598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.50327730178833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.54904890060425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.64222621917725</t>
+    <t xml:space="preserve">7.19268465042114</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.14854669570923</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.37740421295166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.50327682495117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.54904794692993</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.64222526550293</t>
   </si>
   <si>
     <t xml:space="preserve">7.97243595123291</t>
@@ -4271,28 +4271,28 @@
     <t xml:space="preserve">7.87762260437012</t>
   </si>
   <si>
-    <t xml:space="preserve">7.93156862258911</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.96099281311035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.86618041992188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.81223487854004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.84983348846436</t>
+    <t xml:space="preserve">7.93156909942627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.96099376678467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.86617946624756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.81223440170288</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.84983396530151</t>
   </si>
   <si>
     <t xml:space="preserve">7.81473779678345</t>
   </si>
   <si>
-    <t xml:space="preserve">7.77796936035156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.85818958282471</t>
+    <t xml:space="preserve">7.77797031402588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.85819005966187</t>
   </si>
   <si>
     <t xml:space="preserve">7.75624322891235</t>
@@ -4301,22 +4301,22 @@
     <t xml:space="preserve">7.89328575134277</t>
   </si>
   <si>
-    <t xml:space="preserve">7.80303907394409</t>
+    <t xml:space="preserve">7.80303955078125</t>
   </si>
   <si>
     <t xml:space="preserve">7.87323093414307</t>
   </si>
   <si>
-    <t xml:space="preserve">7.84314775466919</t>
+    <t xml:space="preserve">7.84314870834351</t>
   </si>
   <si>
     <t xml:space="preserve">7.89662790298462</t>
   </si>
   <si>
-    <t xml:space="preserve">7.87657260894775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.80972290039062</t>
+    <t xml:space="preserve">7.87657356262207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.80972242355347</t>
   </si>
   <si>
     <t xml:space="preserve">7.90498495101929</t>
@@ -4325,22 +4325,22 @@
     <t xml:space="preserve">7.76292896270752</t>
   </si>
   <si>
-    <t xml:space="preserve">7.83479356765747</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.8364634513855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.93172407150269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.93339681625366</t>
+    <t xml:space="preserve">7.83479261398315</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.83646392822266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.93172454833984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.93339586257935</t>
   </si>
   <si>
     <t xml:space="preserve">7.51892757415771</t>
   </si>
   <si>
-    <t xml:space="preserve">7.56070899963379</t>
+    <t xml:space="preserve">7.56070804595947</t>
   </si>
   <si>
     <t xml:space="preserve">7.56739330291748</t>
@@ -4349,34 +4349,34 @@
     <t xml:space="preserve">7.69775056838989</t>
   </si>
   <si>
-    <t xml:space="preserve">7.76125764846802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.69608020782471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.70443487167358</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.71446371078491</t>
+    <t xml:space="preserve">7.76125717163086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.69607925415039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.70443534851074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.7144627571106</t>
   </si>
   <si>
     <t xml:space="preserve">7.64427089691162</t>
   </si>
   <si>
-    <t xml:space="preserve">7.72950410842896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.6258864402771</t>
+    <t xml:space="preserve">7.72950458526611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.62588691711426</t>
   </si>
   <si>
     <t xml:space="preserve">7.86487483978271</t>
   </si>
   <si>
-    <t xml:space="preserve">8.06041049957275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.94843721389771</t>
+    <t xml:space="preserve">8.06040954589844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.94843673706055</t>
   </si>
   <si>
     <t xml:space="preserve">8.02698516845703</t>
@@ -4385,7 +4385,7 @@
     <t xml:space="preserve">8.01194381713867</t>
   </si>
   <si>
-    <t xml:space="preserve">8.10553455352783</t>
+    <t xml:space="preserve">8.1055326461792</t>
   </si>
   <si>
     <t xml:space="preserve">8.03534126281738</t>
@@ -4397,22 +4397,22 @@
     <t xml:space="preserve">8.13060188293457</t>
   </si>
   <si>
-    <t xml:space="preserve">8.17572593688965</t>
+    <t xml:space="preserve">8.17572689056396</t>
   </si>
   <si>
     <t xml:space="preserve">8.12391757965088</t>
   </si>
   <si>
-    <t xml:space="preserve">8.16068458557129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.98186111450195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.00693130493164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.04536914825439</t>
+    <t xml:space="preserve">8.16068553924561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.98186254501343</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.00692939758301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.04537010192871</t>
   </si>
   <si>
     <t xml:space="preserve">8.05372524261475</t>
@@ -4421,49 +4421,49 @@
     <t xml:space="preserve">8.16904163360596</t>
   </si>
   <si>
-    <t xml:space="preserve">8.14230155944824</t>
+    <t xml:space="preserve">8.14230251312256</t>
   </si>
   <si>
     <t xml:space="preserve">8.17739772796631</t>
   </si>
   <si>
-    <t xml:space="preserve">8.20246696472168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.51498794555664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.42306995391846</t>
+    <t xml:space="preserve">8.20246601104736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.51498985290527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.42306900024414</t>
   </si>
   <si>
     <t xml:space="preserve">8.43142604827881</t>
   </si>
   <si>
-    <t xml:space="preserve">8.43978309631348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.57348155975342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.39800262451172</t>
+    <t xml:space="preserve">8.43978214263916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.57348251342773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.3980016708374</t>
   </si>
   <si>
     <t xml:space="preserve">8.51916694641113</t>
   </si>
   <si>
-    <t xml:space="preserve">8.4732084274292</t>
+    <t xml:space="preserve">8.47320747375488</t>
   </si>
   <si>
     <t xml:space="preserve">8.54841423034668</t>
   </si>
   <si>
-    <t xml:space="preserve">8.54423522949219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.27934169769287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.33783721923828</t>
+    <t xml:space="preserve">8.5442361831665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.2793436050415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.33783626556396</t>
   </si>
   <si>
     <t xml:space="preserve">8.23589134216309</t>
@@ -4472,7 +4472,7 @@
     <t xml:space="preserve">8.35287857055664</t>
   </si>
   <si>
-    <t xml:space="preserve">8.52334499359131</t>
+    <t xml:space="preserve">8.52334594726562</t>
   </si>
   <si>
     <t xml:space="preserve">8.39382362365723</t>
@@ -4493,43 +4493,43 @@
     <t xml:space="preserve">8.54005813598633</t>
   </si>
   <si>
-    <t xml:space="preserve">8.48156356811523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.34619331359863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.00860118865967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.13561534881592</t>
+    <t xml:space="preserve">8.48156261444092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.34619235992432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.00860214233398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.13561630249023</t>
   </si>
   <si>
     <t xml:space="preserve">7.74287366867065</t>
   </si>
   <si>
-    <t xml:space="preserve">7.53062582015991</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.60917377471924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.86821794509888</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.81640863418579</t>
+    <t xml:space="preserve">7.53062629699707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.60917472839355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.86821699142456</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.81640815734863</t>
   </si>
   <si>
     <t xml:space="preserve">7.83144950866699</t>
   </si>
   <si>
-    <t xml:space="preserve">7.68438005447388</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.82476568222046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.95010900497437</t>
+    <t xml:space="preserve">7.68438053131104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.8247652053833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.95010805130005</t>
   </si>
   <si>
     <t xml:space="preserve">7.86320352554321</t>
@@ -4538,28 +4538,28 @@
     <t xml:space="preserve">7.79301118850708</t>
   </si>
   <si>
-    <t xml:space="preserve">7.63257169723511</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.72281837463379</t>
+    <t xml:space="preserve">7.63257122039795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.72281885147095</t>
   </si>
   <si>
     <t xml:space="preserve">7.81306600570679</t>
   </si>
   <si>
-    <t xml:space="preserve">7.84649181365967</t>
+    <t xml:space="preserve">7.84649229049683</t>
   </si>
   <si>
     <t xml:space="preserve">7.9751763343811</t>
   </si>
   <si>
-    <t xml:space="preserve">7.8548469543457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.90832614898682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.99188804626465</t>
+    <t xml:space="preserve">7.85484743118286</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.90832662582397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.99188899993896</t>
   </si>
   <si>
     <t xml:space="preserve">7.91334104537964</t>
@@ -4568,34 +4568,34 @@
     <t xml:space="preserve">8.00525951385498</t>
   </si>
   <si>
-    <t xml:space="preserve">7.92838191986084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.86988878250122</t>
+    <t xml:space="preserve">7.928382396698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.86988830566406</t>
   </si>
   <si>
     <t xml:space="preserve">7.9584641456604</t>
   </si>
   <si>
-    <t xml:space="preserve">7.68939304351807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.75791501998901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.67268133163452</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.91835498809814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.95679378509521</t>
+    <t xml:space="preserve">7.68939447402954</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.75791549682617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.67268228530884</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.91835403442383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.9567928314209</t>
   </si>
   <si>
     <t xml:space="preserve">8.04035568237305</t>
   </si>
   <si>
-    <t xml:space="preserve">7.94175100326538</t>
+    <t xml:space="preserve">7.9417519569397</t>
   </si>
   <si>
     <t xml:space="preserve">8.02531433105469</t>
@@ -4607,10 +4607,10 @@
     <t xml:space="preserve">8.04703998565674</t>
   </si>
   <si>
-    <t xml:space="preserve">8.0955057144165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.06876659393311</t>
+    <t xml:space="preserve">8.09550666809082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.06876564025879</t>
   </si>
   <si>
     <t xml:space="preserve">8.29772663116455</t>
@@ -4622,31 +4622,31 @@
     <t xml:space="preserve">8.08715057373047</t>
   </si>
   <si>
-    <t xml:space="preserve">8.18575382232666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.16402721405029</t>
+    <t xml:space="preserve">8.18575286865234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.16402816772461</t>
   </si>
   <si>
     <t xml:space="preserve">8.10219192504883</t>
   </si>
   <si>
-    <t xml:space="preserve">8.15567207336426</t>
+    <t xml:space="preserve">8.15567111968994</t>
   </si>
   <si>
     <t xml:space="preserve">8.35622024536133</t>
   </si>
   <si>
-    <t xml:space="preserve">8.27767276763916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.30775451660156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.33616542816162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.2760009765625</t>
+    <t xml:space="preserve">8.27767181396484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.30775356292725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.3361644744873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.27600193023682</t>
   </si>
   <si>
     <t xml:space="preserve">8.34786415100098</t>
@@ -4661,13 +4661,13 @@
     <t xml:space="preserve">8.41053581237793</t>
   </si>
   <si>
-    <t xml:space="preserve">8.43006134033203</t>
+    <t xml:space="preserve">8.4300594329834</t>
   </si>
   <si>
     <t xml:space="preserve">8.34443187713623</t>
   </si>
   <si>
-    <t xml:space="preserve">8.3164701461792</t>
+    <t xml:space="preserve">8.31647205352783</t>
   </si>
   <si>
     <t xml:space="preserve">8.28326797485352</t>
@@ -4676,13 +4676,13 @@
     <t xml:space="preserve">8.31996631622314</t>
   </si>
   <si>
-    <t xml:space="preserve">8.29200649261475</t>
+    <t xml:space="preserve">8.29200553894043</t>
   </si>
   <si>
     <t xml:space="preserve">8.49471855163574</t>
   </si>
   <si>
-    <t xml:space="preserve">8.59782218933105</t>
+    <t xml:space="preserve">8.59782314300537</t>
   </si>
   <si>
     <t xml:space="preserve">8.61180305480957</t>
@@ -4700,7 +4700,7 @@
     <t xml:space="preserve">8.59957027435303</t>
   </si>
   <si>
-    <t xml:space="preserve">8.4737491607666</t>
+    <t xml:space="preserve">8.47374820709229</t>
   </si>
   <si>
     <t xml:space="preserve">8.53840732574463</t>
@@ -4718,7 +4718,7 @@
     <t xml:space="preserve">8.6956844329834</t>
   </si>
   <si>
-    <t xml:space="preserve">8.6817045211792</t>
+    <t xml:space="preserve">8.68170356750488</t>
   </si>
   <si>
     <t xml:space="preserve">8.68519878387451</t>
@@ -4727,7 +4727,7 @@
     <t xml:space="preserve">8.70966529846191</t>
   </si>
   <si>
-    <t xml:space="preserve">8.82500171661377</t>
+    <t xml:space="preserve">8.82500076293945</t>
   </si>
   <si>
     <t xml:space="preserve">8.83373832702637</t>
@@ -4751,22 +4751,22 @@
     <t xml:space="preserve">8.98664665222168</t>
   </si>
   <si>
-    <t xml:space="preserve">8.7900505065918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.78568172454834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.80315685272217</t>
+    <t xml:space="preserve">8.79005146026611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.78568267822266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.80315589904785</t>
   </si>
   <si>
     <t xml:space="preserve">8.67995643615723</t>
   </si>
   <si>
-    <t xml:space="preserve">8.81626319885254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.88616371154785</t>
+    <t xml:space="preserve">8.81626415252686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.88616466522217</t>
   </si>
   <si>
     <t xml:space="preserve">8.85558319091797</t>
@@ -4784,25 +4784,25 @@
     <t xml:space="preserve">8.75510025024414</t>
   </si>
   <si>
-    <t xml:space="preserve">8.7813138961792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.79441928863525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.82063293457031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.94732761383057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.02159690856934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.96043395996094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.9342212677002</t>
+    <t xml:space="preserve">8.78131294250488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.79441833496094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.820631980896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.94732666015625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.02159786224365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.96043491363525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.93422222137451</t>
   </si>
   <si>
     <t xml:space="preserve">8.87305736541748</t>
@@ -4817,7 +4817,7 @@
     <t xml:space="preserve">8.8949031829834</t>
   </si>
   <si>
-    <t xml:space="preserve">8.84247589111328</t>
+    <t xml:space="preserve">8.8424768447876</t>
   </si>
   <si>
     <t xml:space="preserve">8.83810710906982</t>
@@ -4835,19 +4835,19 @@
     <t xml:space="preserve">8.67296600341797</t>
   </si>
   <si>
-    <t xml:space="preserve">8.6205415725708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.4545259475708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.3601598739624</t>
+    <t xml:space="preserve">8.62054061889648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.45452499389648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.36015892028809</t>
   </si>
   <si>
     <t xml:space="preserve">8.34268474578857</t>
   </si>
   <si>
-    <t xml:space="preserve">8.41957473754883</t>
+    <t xml:space="preserve">8.41957378387451</t>
   </si>
   <si>
     <t xml:space="preserve">8.33744239807129</t>
@@ -4856,52 +4856,52 @@
     <t xml:space="preserve">8.52966976165771</t>
   </si>
   <si>
-    <t xml:space="preserve">8.59258079528809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.51743698120117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.62578296661377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.64850044250488</t>
+    <t xml:space="preserve">8.59257888793945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.51743602752686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.62578201293945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.6485013961792</t>
   </si>
   <si>
     <t xml:space="preserve">8.46326351165771</t>
   </si>
   <si>
-    <t xml:space="preserve">8.0281286239624</t>
+    <t xml:space="preserve">8.02812957763672</t>
   </si>
   <si>
     <t xml:space="preserve">8.00890731811523</t>
   </si>
   <si>
-    <t xml:space="preserve">8.01240158081055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.95123863220215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.06482696533203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.98793697357178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.03686714172363</t>
+    <t xml:space="preserve">8.01240253448486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.95123910903931</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.06482791900635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.98793649673462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.03686809539795</t>
   </si>
   <si>
     <t xml:space="preserve">8.16094207763672</t>
   </si>
   <si>
-    <t xml:space="preserve">8.14521312713623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.24307537078857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.32695579528809</t>
+    <t xml:space="preserve">8.14521408081055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.24307632446289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.3269567489624</t>
   </si>
   <si>
     <t xml:space="preserve">8.37239170074463</t>
@@ -4910,7 +4910,7 @@
     <t xml:space="preserve">8.634521484375</t>
   </si>
   <si>
-    <t xml:space="preserve">8.73587608337402</t>
+    <t xml:space="preserve">8.73587703704834</t>
   </si>
   <si>
     <t xml:space="preserve">8.76383781433105</t>
@@ -4922,7 +4922,7 @@
     <t xml:space="preserve">8.83874988555908</t>
   </si>
   <si>
-    <t xml:space="preserve">8.79401969909668</t>
+    <t xml:space="preserve">8.79401874542236</t>
   </si>
   <si>
     <t xml:space="preserve">8.79938697814941</t>
@@ -4931,13 +4931,13 @@
     <t xml:space="preserve">8.83338165283203</t>
   </si>
   <si>
-    <t xml:space="preserve">8.73318576812744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.7922306060791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.77970504760742</t>
+    <t xml:space="preserve">8.73318672180176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.79222965240479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.77970600128174</t>
   </si>
   <si>
     <t xml:space="preserve">8.83517169952393</t>
@@ -4946,10 +4946,10 @@
     <t xml:space="preserve">8.87453460693359</t>
   </si>
   <si>
-    <t xml:space="preserve">8.89600563049316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.91568565368652</t>
+    <t xml:space="preserve">8.89600467681885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.91568660736084</t>
   </si>
   <si>
     <t xml:space="preserve">8.95952224731445</t>
@@ -4964,13 +4964,13 @@
     <t xml:space="preserve">9.02214527130127</t>
   </si>
   <si>
-    <t xml:space="preserve">8.98636054992676</t>
+    <t xml:space="preserve">8.98636150360107</t>
   </si>
   <si>
     <t xml:space="preserve">9.05345630645752</t>
   </si>
   <si>
-    <t xml:space="preserve">9.14739036560059</t>
+    <t xml:space="preserve">9.1473913192749</t>
   </si>
   <si>
     <t xml:space="preserve">9.12502479553223</t>
@@ -4997,7 +4997,7 @@
     <t xml:space="preserve">9.27710819244385</t>
   </si>
   <si>
-    <t xml:space="preserve">9.11160659790039</t>
+    <t xml:space="preserve">9.11160564422607</t>
   </si>
   <si>
     <t xml:space="preserve">9.20553970336914</t>
@@ -5015,7 +5015,7 @@
     <t xml:space="preserve">9.07582187652588</t>
   </si>
   <si>
-    <t xml:space="preserve">9.08029460906982</t>
+    <t xml:space="preserve">9.08029365539551</t>
   </si>
   <si>
     <t xml:space="preserve">9.04898262023926</t>
@@ -5027,34 +5027,34 @@
     <t xml:space="preserve">9.08476734161377</t>
   </si>
   <si>
-    <t xml:space="preserve">9.04003715515137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.1384449005127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.22343254089355</t>
+    <t xml:space="preserve">9.04003620147705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.13844394683838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.22343349456787</t>
   </si>
   <si>
     <t xml:space="preserve">9.2279052734375</t>
   </si>
   <si>
-    <t xml:space="preserve">8.99530696868896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.94252586364746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.00425243377686</t>
+    <t xml:space="preserve">8.99530601501465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.94252490997314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.00425148010254</t>
   </si>
   <si>
     <t xml:space="preserve">9.0087251663208</t>
   </si>
   <si>
-    <t xml:space="preserve">9.02661800384521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.88705921173096</t>
+    <t xml:space="preserve">9.02661895751953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.88705825805664</t>
   </si>
   <si>
     <t xml:space="preserve">8.82264709472656</t>
@@ -5069,7 +5069,7 @@
     <t xml:space="preserve">8.90137195587158</t>
   </si>
   <si>
-    <t xml:space="preserve">9.03556442260742</t>
+    <t xml:space="preserve">9.03556346893311</t>
   </si>
   <si>
     <t xml:space="preserve">9.04450988769531</t>
@@ -5078,7 +5078,7 @@
     <t xml:space="preserve">9.10266017913818</t>
   </si>
   <si>
-    <t xml:space="preserve">9.16975593566895</t>
+    <t xml:space="preserve">9.16975498199463</t>
   </si>
   <si>
     <t xml:space="preserve">9.35762405395508</t>
@@ -5099,13 +5099,13 @@
     <t xml:space="preserve">10.1896123886108</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2522344589233</t>
+    <t xml:space="preserve">10.252233505249</t>
   </si>
   <si>
     <t xml:space="preserve">10.2924919128418</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3506412506104</t>
+    <t xml:space="preserve">10.350640296936</t>
   </si>
   <si>
     <t xml:space="preserve">10.399845123291</t>
@@ -5117,19 +5117,19 @@
     <t xml:space="preserve">10.475887298584</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4848337173462</t>
+    <t xml:space="preserve">10.4848327636719</t>
   </si>
   <si>
     <t xml:space="preserve">10.5385093688965</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6727018356323</t>
+    <t xml:space="preserve">10.672700881958</t>
   </si>
   <si>
     <t xml:space="preserve">10.2611808776855</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2835454940796</t>
+    <t xml:space="preserve">10.2835445404053</t>
   </si>
   <si>
     <t xml:space="preserve">10.2343416213989</t>
@@ -5141,13 +5141,13 @@
     <t xml:space="preserve">10.3372230529785</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3461685180664</t>
+    <t xml:space="preserve">10.3461675643921</t>
   </si>
   <si>
     <t xml:space="preserve">10.3819522857666</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3148565292358</t>
+    <t xml:space="preserve">10.3148555755615</t>
   </si>
   <si>
     <t xml:space="preserve">10.4356288909912</t>
@@ -5159,13 +5159,13 @@
     <t xml:space="preserve">10.4535217285156</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3103828430176</t>
+    <t xml:space="preserve">10.3103837966919</t>
   </si>
   <si>
     <t xml:space="preserve">10.4132642745972</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3551149368286</t>
+    <t xml:space="preserve">10.3551139831543</t>
   </si>
   <si>
     <t xml:space="preserve">10.4311561584473</t>
@@ -5183,40 +5183,40 @@
     <t xml:space="preserve">10.4222097396851</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4937791824341</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6682271957397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5519275665283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5564022064209</t>
+    <t xml:space="preserve">10.4937782287598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6682281494141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5519285202026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5564012527466</t>
   </si>
   <si>
     <t xml:space="preserve">10.6861200332642</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6637554168701</t>
+    <t xml:space="preserve">10.6637544631958</t>
   </si>
   <si>
     <t xml:space="preserve">10.6548089981079</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8158378601074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0573835372925</t>
+    <t xml:space="preserve">10.8158388137817</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0573825836182</t>
   </si>
   <si>
     <t xml:space="preserve">11.017126083374</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9723949432373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0081806182861</t>
+    <t xml:space="preserve">10.9723958969116</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0081796646118</t>
   </si>
   <si>
     <t xml:space="preserve">10.9992341995239</t>
@@ -5234,7 +5234,7 @@
     <t xml:space="preserve">11.0618562698364</t>
   </si>
   <si>
-    <t xml:space="preserve">11.120005607605</t>
+    <t xml:space="preserve">11.1200075149536</t>
   </si>
   <si>
     <t xml:space="preserve">11.0350179672241</t>
@@ -5255,7 +5255,7 @@
     <t xml:space="preserve">11.2094669342041</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2720899581909</t>
+    <t xml:space="preserve">11.2720909118652</t>
   </si>
   <si>
     <t xml:space="preserve">11.5091619491577</t>
@@ -5264,7 +5264,7 @@
     <t xml:space="preserve">11.4420652389526</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5896759033203</t>
+    <t xml:space="preserve">11.5896768569946</t>
   </si>
   <si>
     <t xml:space="preserve">11.4465389251709</t>
@@ -5279,10 +5279,10 @@
     <t xml:space="preserve">11.0842218399048</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8918809890747</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.115532875061</t>
+    <t xml:space="preserve">10.8918800354004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1155338287354</t>
   </si>
   <si>
     <t xml:space="preserve">11.289981842041</t>
@@ -5297,16 +5297,16 @@
     <t xml:space="preserve">11.3185148239136</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1873931884766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2482719421387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1405649185181</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4543180465698</t>
+    <t xml:space="preserve">11.1873941421509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2482709884644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1405658721924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4543170928955</t>
   </si>
   <si>
     <t xml:space="preserve">11.3091487884521</t>
@@ -5321,10 +5321,10 @@
     <t xml:space="preserve">11.2295398712158</t>
   </si>
   <si>
-    <t xml:space="preserve">11.327880859375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2342233657837</t>
+    <t xml:space="preserve">11.3278799057007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2342224121094</t>
   </si>
   <si>
     <t xml:space="preserve">11.3512945175171</t>
@@ -5333,10 +5333,10 @@
     <t xml:space="preserve">11.4683666229248</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3887567520142</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3372459411621</t>
+    <t xml:space="preserve">11.3887577056885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3372449874878</t>
   </si>
   <si>
     <t xml:space="preserve">11.4449520111084</t>
@@ -5345,22 +5345,22 @@
     <t xml:space="preserve">11.5432920455933</t>
   </si>
   <si>
-    <t xml:space="preserve">11.435585975647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3981227874756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3559770584106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8804597854614</t>
+    <t xml:space="preserve">11.4355869293213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3981237411499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.355978012085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8804607391357</t>
   </si>
   <si>
     <t xml:space="preserve">11.7212429046631</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3606605529785</t>
+    <t xml:space="preserve">11.3606595993042</t>
   </si>
   <si>
     <t xml:space="preserve">11.0843706130981</t>
@@ -5384,7 +5384,7 @@
     <t xml:space="preserve">11.1358823776245</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1499300003052</t>
+    <t xml:space="preserve">11.1499309539795</t>
   </si>
   <si>
     <t xml:space="preserve">11.2951002120972</t>
@@ -5399,13 +5399,13 @@
     <t xml:space="preserve">11.5011463165283</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5854377746582</t>
+    <t xml:space="preserve">11.5854387283325</t>
   </si>
   <si>
     <t xml:space="preserve">11.618218421936</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7025108337402</t>
+    <t xml:space="preserve">11.7025098800659</t>
   </si>
   <si>
     <t xml:space="preserve">11.6978273391724</t>
@@ -5414,7 +5414,7 @@
     <t xml:space="preserve">11.6697301864624</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7306079864502</t>
+    <t xml:space="preserve">11.7306070327759</t>
   </si>
   <si>
     <t xml:space="preserve">11.7446565628052</t>
@@ -5429,16 +5429,16 @@
     <t xml:space="preserve">11.5713891983032</t>
   </si>
   <si>
-    <t xml:space="preserve">11.524561882019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.566707611084</t>
+    <t xml:space="preserve">11.5245609283447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5667066574097</t>
   </si>
   <si>
     <t xml:space="preserve">11.5105123519897</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6837787628174</t>
+    <t xml:space="preserve">11.6837797164917</t>
   </si>
   <si>
     <t xml:space="preserve">11.660364151001</t>
@@ -5453,7 +5453,7 @@
     <t xml:space="preserve">11.8242654800415</t>
   </si>
   <si>
-    <t xml:space="preserve">11.87109375</t>
+    <t xml:space="preserve">11.8710947036743</t>
   </si>
   <si>
     <t xml:space="preserve">11.8664112091064</t>
@@ -5483,7 +5483,7 @@
     <t xml:space="preserve">11.6229009628296</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7259254455566</t>
+    <t xml:space="preserve">11.7259244918823</t>
   </si>
   <si>
     <t xml:space="preserve">11.7868022918701</t>
@@ -5498,25 +5498,25 @@
     <t xml:space="preserve">11.9179229736328</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0068969726562</t>
+    <t xml:space="preserve">12.0068979263306</t>
   </si>
   <si>
     <t xml:space="preserve">12.095871925354</t>
   </si>
   <si>
-    <t xml:space="preserve">12.109920501709</t>
+    <t xml:space="preserve">12.1099214553833</t>
   </si>
   <si>
     <t xml:space="preserve">12.1614322662354</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5266962051392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5641593933105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4845504760742</t>
+    <t xml:space="preserve">12.5266971588135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5641603469849</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4845514297485</t>
   </si>
   <si>
     <t xml:space="preserve">12.3908929824829</t>
@@ -5528,7 +5528,7 @@
     <t xml:space="preserve">12.306601524353</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2176275253296</t>
+    <t xml:space="preserve">12.2176265716553</t>
   </si>
   <si>
     <t xml:space="preserve">12.3440647125244</t>
@@ -5540,7 +5540,7 @@
     <t xml:space="preserve">12.1661157608032</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1192855834961</t>
+    <t xml:space="preserve">12.1192865371704</t>
   </si>
   <si>
     <t xml:space="preserve">12.2035779953003</t>
@@ -5549,10 +5549,10 @@
     <t xml:space="preserve">12.1473836898804</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3581123352051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4564542770386</t>
+    <t xml:space="preserve">12.3581132888794</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4564533233643</t>
   </si>
   <si>
     <t xml:space="preserve">12.4470882415771</t>
@@ -6252,6 +6252,9 @@
   </si>
   <si>
     <t xml:space="preserve">21.1000003814697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.4899997711182</t>
   </si>
 </sst>
 </file>
@@ -71798,7 +71801,7 @@
     </row>
     <row r="2509">
       <c r="A2509" s="1" t="n">
-        <v>45972.6912731481</v>
+        <v>45972.3333333333</v>
       </c>
       <c r="B2509" t="n">
         <v>1958003</v>
@@ -71819,6 +71822,32 @@
         <v>2079</v>
       </c>
       <c r="H2509" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2510">
+      <c r="A2510" s="1" t="n">
+        <v>45973.6939583333</v>
+      </c>
+      <c r="B2510" t="n">
+        <v>2211286</v>
+      </c>
+      <c r="C2510" t="n">
+        <v>21.4899997711182</v>
+      </c>
+      <c r="D2510" t="n">
+        <v>21.1200008392334</v>
+      </c>
+      <c r="E2510" t="n">
+        <v>21.2299995422363</v>
+      </c>
+      <c r="F2510" t="n">
+        <v>21.4899997711182</v>
+      </c>
+      <c r="G2510" t="s">
+        <v>2080</v>
+      </c>
+      <c r="H2510" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/PST.MI.xlsx
+++ b/data/PST.MI.xlsx
@@ -44,22 +44,22 @@
     <t xml:space="preserve">PST.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">4.03631687164307</t>
+    <t xml:space="preserve">4.03631639480591</t>
   </si>
   <si>
     <t xml:space="preserve">3.97465062141418</t>
   </si>
   <si>
-    <t xml:space="preserve">3.95222687721252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.91578817367554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87934803962708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.97184681892395</t>
+    <t xml:space="preserve">3.95222640037537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9157874584198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87934899330139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97184729576111</t>
   </si>
   <si>
     <t xml:space="preserve">4.01949834823608</t>
@@ -68,94 +68,94 @@
     <t xml:space="preserve">3.99707412719727</t>
   </si>
   <si>
-    <t xml:space="preserve">3.94661974906921</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.82889461517334</t>
+    <t xml:space="preserve">3.94662070274353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.82889485359192</t>
   </si>
   <si>
     <t xml:space="preserve">3.75601673126221</t>
   </si>
   <si>
-    <t xml:space="preserve">3.54859495162964</t>
+    <t xml:space="preserve">3.54859447479248</t>
   </si>
   <si>
     <t xml:space="preserve">3.68594121932983</t>
   </si>
   <si>
-    <t xml:space="preserve">3.73359274864197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.6551079750061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.7616229057312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8092737197876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73078966140747</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.82609152793884</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.7223801612854</t>
+    <t xml:space="preserve">3.73359322547913</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.65510845184326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.76162219047546</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.80927443504333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73079037666321</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.82609128952026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.72238063812256</t>
   </si>
   <si>
     <t xml:space="preserve">3.64389729499817</t>
   </si>
   <si>
-    <t xml:space="preserve">3.53177690505981</t>
+    <t xml:space="preserve">3.53177714347839</t>
   </si>
   <si>
     <t xml:space="preserve">3.35518836975098</t>
   </si>
   <si>
-    <t xml:space="preserve">3.00481367111206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.89829897880554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.17019009590149</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.03284287452698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.04405498504639</t>
+    <t xml:space="preserve">3.00481295585632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.8982994556427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.17018985748291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.03284335136414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.04405522346497</t>
   </si>
   <si>
     <t xml:space="preserve">3.13655400276184</t>
   </si>
   <si>
-    <t xml:space="preserve">3.12253928184509</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.2486743927002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.23465895652771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.30473446846008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.42245984077454</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.34677839279175</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.31314301490784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.40844416618347</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.45609617233276</t>
+    <t xml:space="preserve">3.12253952026367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.24867415428162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.23465919494629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.30473399162292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.42246007919312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.34677910804749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.31314325332642</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.40844488143921</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.45609641075134</t>
   </si>
   <si>
     <t xml:space="preserve">3.51495909690857</t>
@@ -164,205 +164,205 @@
     <t xml:space="preserve">3.48412609100342</t>
   </si>
   <si>
-    <t xml:space="preserve">3.45329260826111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.47571706771851</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.43647503852844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.4588987827301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.43367147445679</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61306428909302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.63829016685486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.6354877948761</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.60745739936829</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.58783674240112</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.60185217857361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.67192673683167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.79525876045227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77844071388245</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.7139720916748</t>
+    <t xml:space="preserve">3.45329236984253</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.47571682929993</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.43647527694702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.45889854431152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.43367099761963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61306381225586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.6382908821106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.63548731803894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.60745763778687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.5878369808197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.60185265541077</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.67192721366882</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.79525828361511</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77844023704529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71397137641907</t>
   </si>
   <si>
     <t xml:space="preserve">3.78404664993286</t>
   </si>
   <si>
-    <t xml:space="preserve">3.72798681259155</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.6775324344635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61586618423462</t>
+    <t xml:space="preserve">3.72798705101013</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.67753291130066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61586689949036</t>
   </si>
   <si>
     <t xml:space="preserve">3.51215529441833</t>
   </si>
   <si>
-    <t xml:space="preserve">3.56821537017822</t>
+    <t xml:space="preserve">3.56821608543396</t>
   </si>
   <si>
     <t xml:space="preserve">3.58503389358521</t>
   </si>
   <si>
-    <t xml:space="preserve">3.60465431213379</t>
+    <t xml:space="preserve">3.60465502738953</t>
   </si>
   <si>
     <t xml:space="preserve">3.62147235870361</t>
   </si>
   <si>
-    <t xml:space="preserve">3.69995641708374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.63268494606018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.6298816204071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.6579122543335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.62707924842834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.67472982406616</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.680335521698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.74480438232422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.79245519638062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80086445808411</t>
+    <t xml:space="preserve">3.69995665550232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.6326847076416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.62988114356995</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.65791130065918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.62707829475403</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.674729347229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.68033576011658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.74480390548706</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.79245567321777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.80086421966553</t>
   </si>
   <si>
     <t xml:space="preserve">3.73919820785522</t>
   </si>
   <si>
-    <t xml:space="preserve">3.68313884735107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.76722860336304</t>
+    <t xml:space="preserve">3.68313908576965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.76722884178162</t>
   </si>
   <si>
     <t xml:space="preserve">3.79806184768677</t>
   </si>
   <si>
-    <t xml:space="preserve">3.77563691139221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.7588198184967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.78684973716736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.68874478340149</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.78965210914612</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.74760842323303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83169770240784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83730340003967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8064706325531</t>
+    <t xml:space="preserve">3.77563714981079</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.75881934165955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.78684997558594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.68874454498291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.78965258598328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.74760794639587</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.83169746398926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.83730363845825</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.80647087097168</t>
   </si>
   <si>
     <t xml:space="preserve">3.85972762107849</t>
   </si>
   <si>
-    <t xml:space="preserve">3.85692453384399</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8681366443634</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84571266174316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8541214466095</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92419672012329</t>
+    <t xml:space="preserve">3.85692405700684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.86813616752625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84571313858032</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85412049293518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92419624328613</t>
   </si>
   <si>
     <t xml:space="preserve">3.93260550498962</t>
   </si>
   <si>
-    <t xml:space="preserve">3.84010601043701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.78124380111694</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.76442623138428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87654590606689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96498346328735</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.91486859321594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90602493286133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95024371147156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.63776206970215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.42256212234497</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.51394820213318</t>
+    <t xml:space="preserve">3.84010648727417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.78124356269836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.7644259929657</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.876544713974</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96498322486877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9148690700531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90602540969849</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95024394989014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.63776230812073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.42256164550781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.51394844055176</t>
   </si>
   <si>
     <t xml:space="preserve">3.50805282592773</t>
   </si>
   <si>
-    <t xml:space="preserve">3.60533475875854</t>
+    <t xml:space="preserve">3.60533404350281</t>
   </si>
   <si>
     <t xml:space="preserve">3.52574014663696</t>
@@ -371,220 +371,220 @@
     <t xml:space="preserve">3.43730187416077</t>
   </si>
   <si>
-    <t xml:space="preserve">3.3989782333374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.37244772911072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.49920868873596</t>
+    <t xml:space="preserve">3.39897894859314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.37244701385498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.49920845031738</t>
   </si>
   <si>
     <t xml:space="preserve">3.65839767456055</t>
   </si>
   <si>
-    <t xml:space="preserve">3.64955353736877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73504376411438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.67018914222717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.67313742637634</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.65250277519226</t>
+    <t xml:space="preserve">3.64955401420593</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73504447937012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.67018961906433</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.67313671112061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.65250205993652</t>
   </si>
   <si>
     <t xml:space="preserve">3.70851302146912</t>
   </si>
   <si>
-    <t xml:space="preserve">3.69672131538391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.65544986724854</t>
+    <t xml:space="preserve">3.69672107696533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.6554491519928</t>
   </si>
   <si>
     <t xml:space="preserve">3.64660596847534</t>
   </si>
   <si>
-    <t xml:space="preserve">3.60238695144653</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.58469915390015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.52868866920471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80284690856934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.78221130371094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80874228477478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.81463861465454</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.86770153045654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87949347496033</t>
+    <t xml:space="preserve">3.60238718986511</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.58469939231873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.52868890762329</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.80284714698792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.78221106529236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.80874300003052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.81463813781738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.86770129203796</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87949275970459</t>
   </si>
   <si>
     <t xml:space="preserve">3.79989886283875</t>
   </si>
   <si>
-    <t xml:space="preserve">3.72325229644775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.7615761756897</t>
+    <t xml:space="preserve">3.72325205802917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.76157546043396</t>
   </si>
   <si>
     <t xml:space="preserve">3.66724157333374</t>
   </si>
   <si>
-    <t xml:space="preserve">3.68198108673096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.74388718605042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.70261645317078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66134595870972</t>
+    <t xml:space="preserve">3.68198132514954</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.74388766288757</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.70261693000793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66134667396545</t>
   </si>
   <si>
     <t xml:space="preserve">3.67903280258179</t>
   </si>
   <si>
-    <t xml:space="preserve">3.62597036361694</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.693772315979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.68492913246155</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.70556449890137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71735692024231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77631497383118</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.76452398300171</t>
+    <t xml:space="preserve">3.62596988677979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.69377326965332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.68492889404297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.70556545257568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71735620498657</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77631545066833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.76452374458313</t>
   </si>
   <si>
     <t xml:space="preserve">3.56406331062317</t>
   </si>
   <si>
-    <t xml:space="preserve">3.61712670326233</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61417841911316</t>
+    <t xml:space="preserve">3.61712718009949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61417865753174</t>
   </si>
   <si>
     <t xml:space="preserve">3.58175086975098</t>
   </si>
   <si>
-    <t xml:space="preserve">3.5994393825531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.60828185081482</t>
+    <t xml:space="preserve">3.59943866729736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.60828232765198</t>
   </si>
   <si>
     <t xml:space="preserve">3.58764696121216</t>
   </si>
   <si>
-    <t xml:space="preserve">3.57880258560181</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.5729067325592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.55816721916199</t>
+    <t xml:space="preserve">3.57880306243896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.57290720939636</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.55816698074341</t>
   </si>
   <si>
     <t xml:space="preserve">3.56111574172974</t>
   </si>
   <si>
-    <t xml:space="preserve">3.50215673446655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.54637598991394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.56701159477234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.51689600944519</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.57585501670837</t>
+    <t xml:space="preserve">3.50215697288513</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.54637575149536</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.56701135635376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.51689648628235</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.57585549354553</t>
   </si>
   <si>
     <t xml:space="preserve">3.64365792274475</t>
   </si>
   <si>
-    <t xml:space="preserve">3.62302207946777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.51100087165833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.49036574363708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.51984333992004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.55227208137512</t>
+    <t xml:space="preserve">3.62302184104919</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.51099991798401</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.49036550521851</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.51984429359436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.5522723197937</t>
   </si>
   <si>
     <t xml:space="preserve">3.54342794418335</t>
   </si>
   <si>
-    <t xml:space="preserve">3.53163695335388</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.52279210090637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.47857332229614</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.44024991989136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.36655187606812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.33117580413818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.32527995109558</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.31938481330872</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.31054067611694</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.2663209438324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.39603090286255</t>
+    <t xml:space="preserve">3.53163599967957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.52279257774353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.47857236862183</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.4402494430542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.3665509223938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.3311755657196</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.32528018951416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.31938457489014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.31054043769836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.26632118225098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.39603114128113</t>
   </si>
   <si>
     <t xml:space="preserve">3.45793724060059</t>
@@ -593,55 +593,55 @@
     <t xml:space="preserve">3.46088528633118</t>
   </si>
   <si>
-    <t xml:space="preserve">3.4520411491394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73209619522095</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.7468364238739</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73799252510071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.72914791107178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77926325798035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.74093985557556</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77336764335632</t>
+    <t xml:space="preserve">3.45204210281372</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73209595680237</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.74683618545532</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73799347877502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.72914862632751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77926349639893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.74094033241272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77336692810059</t>
   </si>
   <si>
     <t xml:space="preserve">3.79105472564697</t>
   </si>
   <si>
-    <t xml:space="preserve">3.76747155189514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71440839767456</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.63481402397156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.59649109840393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.56995916366577</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.59354209899902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.44909334182739</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.42845845222473</t>
+    <t xml:space="preserve">3.7674708366394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71440887451172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.63481426239014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.59649085998535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.56995940208435</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.59354281425476</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.44909405708313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.42845749855042</t>
   </si>
   <si>
     <t xml:space="preserve">3.4461452960968</t>
@@ -650,289 +650,289 @@
     <t xml:space="preserve">3.53753209114075</t>
   </si>
   <si>
-    <t xml:space="preserve">3.53458404541016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.59059548377991</t>
+    <t xml:space="preserve">3.534583568573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.59059453010559</t>
   </si>
   <si>
     <t xml:space="preserve">3.69966888427734</t>
   </si>
   <si>
-    <t xml:space="preserve">3.81758689880371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80579423904419</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.79695057868958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.75862741470337</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.82937836647034</t>
+    <t xml:space="preserve">3.81758642196655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.80579590797424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.79695129394531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.75862789154053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8293788433075</t>
   </si>
   <si>
     <t xml:space="preserve">3.79400300979614</t>
   </si>
   <si>
-    <t xml:space="preserve">3.67608523368835</t>
+    <t xml:space="preserve">3.67608499526978</t>
   </si>
   <si>
     <t xml:space="preserve">3.71146082878113</t>
   </si>
   <si>
-    <t xml:space="preserve">3.74978351593018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77041983604431</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.68787717819214</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.75273180007935</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83232665061951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84411764144897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.72030472755432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.69082546234131</t>
+    <t xml:space="preserve">3.7497832775116</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77041935920715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.68787670135498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.75273132324219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.83232736587524</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84411835670471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.72030448913574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.69082522392273</t>
   </si>
   <si>
     <t xml:space="preserve">3.81169080734253</t>
   </si>
   <si>
-    <t xml:space="preserve">3.82053518295288</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.78916764259338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80171370506287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.81426167488098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.75780010223389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.76407289505005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77661967277527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73897886276245</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.78603029251099</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.76093626022339</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.76721096038818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.74525260925293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.72956919670105</t>
+    <t xml:space="preserve">3.82053422927856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.78916716575623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.80171394348145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8142614364624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.75779986381531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.76407361030579</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77662062644958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73897981643677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.78602981567383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.76093649864197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.76721024513245</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.74525308609009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.72956943511963</t>
   </si>
   <si>
     <t xml:space="preserve">3.7954409122467</t>
   </si>
   <si>
-    <t xml:space="preserve">3.80485153198242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84249114990234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.82367134094238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80798768997192</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.79857754707336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.75152635574341</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.74211645126343</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77975630760193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.91463708877563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9271833896637</t>
+    <t xml:space="preserve">3.80485129356384</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84249186515808</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8236711025238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.80798745155334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.79857778549194</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.75152659416199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.74211668968201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.7797577381134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.91463565826416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92718315124512</t>
   </si>
   <si>
     <t xml:space="preserve">3.94600391387939</t>
   </si>
   <si>
-    <t xml:space="preserve">3.89267945289612</t>
+    <t xml:space="preserve">3.89267897605896</t>
   </si>
   <si>
     <t xml:space="preserve">3.90208983421326</t>
   </si>
   <si>
-    <t xml:space="preserve">3.90522599220276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94286775588989</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83308172225952</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84562921524048</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8989531993866</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.908362865448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85817456245422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83935523033142</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.82994556427002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85503935813904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.81739735603333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.86131143569946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92090940475464</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.89581608772278</t>
+    <t xml:space="preserve">3.90522646903992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94286727905273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.83308219909668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84562873840332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89895343780518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90836262702942</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85817503929138</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8393542766571</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8299446105957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85503792762756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.81739807128906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.86131191253662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92090964317322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89581680297852</t>
   </si>
   <si>
     <t xml:space="preserve">3.8864061832428</t>
   </si>
   <si>
-    <t xml:space="preserve">3.88954257965088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.86444878578186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88013243675232</t>
+    <t xml:space="preserve">3.8895423412323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.86444807052612</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8801326751709</t>
   </si>
   <si>
     <t xml:space="preserve">3.85190200805664</t>
   </si>
   <si>
-    <t xml:space="preserve">3.873859167099</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93032002449036</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8675856590271</t>
+    <t xml:space="preserve">3.87385964393616</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93032026290894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.86758589744568</t>
   </si>
   <si>
     <t xml:space="preserve">3.93659377098083</t>
   </si>
   <si>
-    <t xml:space="preserve">3.94914102554321</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93345713615417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93973088264465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92404723167419</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84876537322998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83621835708618</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.82680749893188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99305486679077</t>
+    <t xml:space="preserve">3.94914078712463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93345665931702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9397304058075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92404675483704</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84876585006714</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.83621788024902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.82680821418762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99305438995361</t>
   </si>
   <si>
     <t xml:space="preserve">4.02128505706787</t>
   </si>
   <si>
-    <t xml:space="preserve">3.99619078636169</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98364448547363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.97109723091125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98678112030029</t>
+    <t xml:space="preserve">3.99619174003601</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9836437702179</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97109770774841</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.98678135871887</t>
   </si>
   <si>
     <t xml:space="preserve">3.99932789802551</t>
   </si>
   <si>
-    <t xml:space="preserve">4.01814889907837</t>
+    <t xml:space="preserve">4.01814794540405</t>
   </si>
   <si>
     <t xml:space="preserve">4.03383159637451</t>
   </si>
   <si>
-    <t xml:space="preserve">4.04637813568115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.05892610549927</t>
+    <t xml:space="preserve">4.04637956619263</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.05892562866211</t>
   </si>
   <si>
     <t xml:space="preserve">4.04010581970215</t>
   </si>
   <si>
-    <t xml:space="preserve">4.07147264480591</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.10284090042114</t>
+    <t xml:space="preserve">4.07147216796875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.10284042358398</t>
   </si>
   <si>
     <t xml:space="preserve">4.09970331192017</t>
   </si>
   <si>
-    <t xml:space="preserve">4.12793445587158</t>
+    <t xml:space="preserve">4.12793350219727</t>
   </si>
   <si>
     <t xml:space="preserve">4.2188982963562</t>
   </si>
   <si>
-    <t xml:space="preserve">4.2157621383667</t>
+    <t xml:space="preserve">4.21576166152954</t>
   </si>
   <si>
     <t xml:space="preserve">4.2000789642334</t>
@@ -941,13 +941,13 @@
     <t xml:space="preserve">4.17184829711914</t>
   </si>
   <si>
-    <t xml:space="preserve">4.18753099441528</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.19694232940674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.17310333251953</t>
+    <t xml:space="preserve">4.18753147125244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.19694089889526</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.17310237884521</t>
   </si>
   <si>
     <t xml:space="preserve">4.15553712844849</t>
@@ -956,13 +956,13 @@
     <t xml:space="preserve">4.18063163757324</t>
   </si>
   <si>
-    <t xml:space="preserve">4.13044309616089</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.13922595977783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.01501083374023</t>
+    <t xml:space="preserve">4.13044357299805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.13922691345215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.01501178741455</t>
   </si>
   <si>
     <t xml:space="preserve">4.12166023254395</t>
@@ -974,40 +974,40 @@
     <t xml:space="preserve">4.03759622573853</t>
   </si>
   <si>
-    <t xml:space="preserve">4.05516147613525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.09531116485596</t>
+    <t xml:space="preserve">4.05516195297241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.09531164169312</t>
   </si>
   <si>
     <t xml:space="preserve">4.1291880607605</t>
   </si>
   <si>
-    <t xml:space="preserve">4.17561197280884</t>
+    <t xml:space="preserve">4.175612449646</t>
   </si>
   <si>
     <t xml:space="preserve">4.18188571929932</t>
   </si>
   <si>
-    <t xml:space="preserve">4.2534031867981</t>
+    <t xml:space="preserve">4.25340366363525</t>
   </si>
   <si>
     <t xml:space="preserve">4.2408561706543</t>
   </si>
   <si>
-    <t xml:space="preserve">4.20697832107544</t>
+    <t xml:space="preserve">4.20697927474976</t>
   </si>
   <si>
     <t xml:space="preserve">4.21074342727661</t>
   </si>
   <si>
-    <t xml:space="preserve">4.17435741424561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.41651344299316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.4303150177002</t>
+    <t xml:space="preserve">4.17435693740845</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.41651296615601</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.43031454086304</t>
   </si>
   <si>
     <t xml:space="preserve">4.40271139144897</t>
@@ -1016,31 +1016,31 @@
     <t xml:space="preserve">4.30735492706299</t>
   </si>
   <si>
-    <t xml:space="preserve">4.33495855331421</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.37134408950806</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.48677587509155</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.60095310211182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.57711362838745</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.65490436553955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.55452919006348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.49555826187134</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.56707572937012</t>
+    <t xml:space="preserve">4.33495807647705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.3713436126709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.48677635192871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.60095262527466</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.57711315155029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.65490484237671</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.55452871322632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.49555778503418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.56707525253296</t>
   </si>
   <si>
     <t xml:space="preserve">4.63859272003174</t>
@@ -1049,19 +1049,19 @@
     <t xml:space="preserve">4.60346174240112</t>
   </si>
   <si>
-    <t xml:space="preserve">4.63482904434204</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.62604713439941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.58338737487793</t>
+    <t xml:space="preserve">4.63482999801636</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.62604665756226</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.58338689804077</t>
   </si>
   <si>
     <t xml:space="preserve">4.54574584960938</t>
   </si>
   <si>
-    <t xml:space="preserve">4.52943468093872</t>
+    <t xml:space="preserve">4.52943515777588</t>
   </si>
   <si>
     <t xml:space="preserve">4.54449129104614</t>
@@ -1070,112 +1070,112 @@
     <t xml:space="preserve">4.61475419998169</t>
   </si>
   <si>
-    <t xml:space="preserve">4.62353754043579</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.65866804122925</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.73645925521851</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.73144054412842</t>
+    <t xml:space="preserve">4.62353706359863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.65866899490356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.73646020889282</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.73144102096558</t>
   </si>
   <si>
     <t xml:space="preserve">4.76782655715942</t>
   </si>
   <si>
-    <t xml:space="preserve">4.82052421569824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.81299543380737</t>
+    <t xml:space="preserve">4.82052373886108</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.81299495697021</t>
   </si>
   <si>
     <t xml:space="preserve">4.81675910949707</t>
   </si>
   <si>
-    <t xml:space="preserve">4.81425046920776</t>
+    <t xml:space="preserve">4.81424903869629</t>
   </si>
   <si>
     <t xml:space="preserve">4.84310817718506</t>
   </si>
   <si>
-    <t xml:space="preserve">4.88702154159546</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.85690879821777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.86694765090942</t>
+    <t xml:space="preserve">4.88702201843262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.85690927505493</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.86694622039795</t>
   </si>
   <si>
     <t xml:space="preserve">4.93720960617065</t>
   </si>
   <si>
-    <t xml:space="preserve">4.9422287940979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.96355867385864</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.9735951423645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.00119876861572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.0852632522583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.07146120071411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.06267929077148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.11537647247314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.09153747558594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.06769847869873</t>
+    <t xml:space="preserve">4.94222831726074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.96355772018433</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.97359609603882</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.00119972229004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.08526372909546</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.07146167755127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.06267881393433</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.11537599563599</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.09153652191162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.06769800186157</t>
   </si>
   <si>
     <t xml:space="preserve">5.11286687850952</t>
   </si>
   <si>
-    <t xml:space="preserve">5.15552663803101</t>
+    <t xml:space="preserve">5.15552616119385</t>
   </si>
   <si>
     <t xml:space="preserve">4.96230363845825</t>
   </si>
   <si>
-    <t xml:space="preserve">4.95101118087769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.78037261962891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.79041194915771</t>
+    <t xml:space="preserve">4.95101165771484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.78037309646606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.79041147232056</t>
   </si>
   <si>
     <t xml:space="preserve">4.82930612564087</t>
   </si>
   <si>
-    <t xml:space="preserve">4.80546712875366</t>
+    <t xml:space="preserve">4.8054666519165</t>
   </si>
   <si>
     <t xml:space="preserve">4.8343243598938</t>
   </si>
   <si>
-    <t xml:space="preserve">4.76029825210571</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.60722637176514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.40020179748535</t>
+    <t xml:space="preserve">4.76029777526855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.60722589492798</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.40020132064819</t>
   </si>
   <si>
     <t xml:space="preserve">4.584641456604</t>
@@ -1196,67 +1196,67 @@
     <t xml:space="preserve">4.58589601516724</t>
   </si>
   <si>
-    <t xml:space="preserve">4.56832981109619</t>
+    <t xml:space="preserve">4.56833028793335</t>
   </si>
   <si>
     <t xml:space="preserve">4.44411611557007</t>
   </si>
   <si>
-    <t xml:space="preserve">4.61600828170776</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.7038369178772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.79292058944702</t>
+    <t xml:space="preserve">4.61600875854492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.70383787155151</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.79292011260986</t>
   </si>
   <si>
     <t xml:space="preserve">4.90584230422974</t>
   </si>
   <si>
-    <t xml:space="preserve">4.78664684295654</t>
+    <t xml:space="preserve">4.78664636611938</t>
   </si>
   <si>
     <t xml:space="preserve">4.86100244522095</t>
   </si>
   <si>
-    <t xml:space="preserve">4.91012859344482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.93270206451416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.87162399291992</t>
+    <t xml:space="preserve">4.9101300239563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.932701587677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.87162446975708</t>
   </si>
   <si>
     <t xml:space="preserve">4.87693548202515</t>
   </si>
   <si>
-    <t xml:space="preserve">4.81320285797119</t>
+    <t xml:space="preserve">4.81320238113403</t>
   </si>
   <si>
     <t xml:space="preserve">4.83577442169189</t>
   </si>
   <si>
-    <t xml:space="preserve">4.76672983169556</t>
+    <t xml:space="preserve">4.76672887802124</t>
   </si>
   <si>
     <t xml:space="preserve">4.76009082794189</t>
   </si>
   <si>
-    <t xml:space="preserve">4.80789089202881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.8198413848877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.93403005599976</t>
+    <t xml:space="preserve">4.80789136886597</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.81984090805054</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.93403053283691</t>
   </si>
   <si>
     <t xml:space="preserve">4.97253561019897</t>
   </si>
   <si>
-    <t xml:space="preserve">5.01900768280029</t>
+    <t xml:space="preserve">5.01900815963745</t>
   </si>
   <si>
     <t xml:space="preserve">4.96589660644531</t>
@@ -1265,7 +1265,7 @@
     <t xml:space="preserve">5.03892517089844</t>
   </si>
   <si>
-    <t xml:space="preserve">5.02697515487671</t>
+    <t xml:space="preserve">5.02697467803955</t>
   </si>
   <si>
     <t xml:space="preserve">5.10000276565552</t>
@@ -1274,10 +1274,10 @@
     <t xml:space="preserve">5.1531138420105</t>
   </si>
   <si>
-    <t xml:space="preserve">5.18099784851074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.12124729156494</t>
+    <t xml:space="preserve">5.18099641799927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.12124824523926</t>
   </si>
   <si>
     <t xml:space="preserve">5.13452529907227</t>
@@ -1286,22 +1286,22 @@
     <t xml:space="preserve">5.11859178543091</t>
   </si>
   <si>
-    <t xml:space="preserve">5.1278862953186</t>
+    <t xml:space="preserve">5.12788581848145</t>
   </si>
   <si>
     <t xml:space="preserve">5.21153593063354</t>
   </si>
   <si>
-    <t xml:space="preserve">5.23410844802856</t>
+    <t xml:space="preserve">5.23410797119141</t>
   </si>
   <si>
     <t xml:space="preserve">5.25668048858643</t>
   </si>
   <si>
-    <t xml:space="preserve">5.28854751586914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.28058099746704</t>
+    <t xml:space="preserve">5.28854703903198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.28058052062988</t>
   </si>
   <si>
     <t xml:space="preserve">4.99510812759399</t>
@@ -1310,91 +1310,91 @@
     <t xml:space="preserve">4.94465255737305</t>
   </si>
   <si>
-    <t xml:space="preserve">4.92871904373169</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.86896944046021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.78664636611938</t>
+    <t xml:space="preserve">4.92871952056885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.86896896362305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.7866473197937</t>
   </si>
   <si>
     <t xml:space="preserve">4.71627426147461</t>
   </si>
   <si>
-    <t xml:space="preserve">4.69635772705078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.74548578262329</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.60474061965942</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.54764652252197</t>
+    <t xml:space="preserve">4.69635677337646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.74548530578613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.60474109649658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.54764604568481</t>
   </si>
   <si>
     <t xml:space="preserve">4.4759464263916</t>
   </si>
   <si>
-    <t xml:space="preserve">4.61801910400391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.52772998809814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.51046800613403</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.50250148773193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.48524045944214</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.50515699386597</t>
+    <t xml:space="preserve">4.61801815032959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.52772951126099</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.51046895980835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.50250196456909</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.48523950576782</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.50515651702881</t>
   </si>
   <si>
     <t xml:space="preserve">4.44673442840576</t>
   </si>
   <si>
-    <t xml:space="preserve">4.40291738510132</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.47727346420288</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.59544658660889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.68440723419189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.65519618988037</t>
+    <t xml:space="preserve">4.40291881561279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.47727394104004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.59544610977173</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.68440818786621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.65519571304321</t>
   </si>
   <si>
     <t xml:space="preserve">4.67378520965576</t>
   </si>
   <si>
-    <t xml:space="preserve">4.78133583068848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.75610733032227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.68175172805786</t>
+    <t xml:space="preserve">4.78133535385132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.75610828399658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.68175220489502</t>
   </si>
   <si>
     <t xml:space="preserve">4.56225204467773</t>
   </si>
   <si>
-    <t xml:space="preserve">4.58880758285522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.63262414932251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.61005067825317</t>
+    <t xml:space="preserve">4.58880710601807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.63262367248535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.61005163192749</t>
   </si>
   <si>
     <t xml:space="preserve">4.59810209274292</t>
@@ -1403,10 +1403,10 @@
     <t xml:space="preserve">4.6605076789856</t>
   </si>
   <si>
-    <t xml:space="preserve">4.69901371002197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.72158622741699</t>
+    <t xml:space="preserve">4.69901275634766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.72158575057983</t>
   </si>
   <si>
     <t xml:space="preserve">4.77735280990601</t>
@@ -1415,43 +1415,43 @@
     <t xml:space="preserve">4.80523538589478</t>
   </si>
   <si>
-    <t xml:space="preserve">4.77336931228638</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.56889057159424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.51976299285889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.43876886367798</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.44806289672852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.45204496383667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.38167381286621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.21968507766724</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.2422571182251</t>
+    <t xml:space="preserve">4.77336883544922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.56888961791992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.51976251602173</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.43876791000366</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.44806241989136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.45204591751099</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.38167333602905</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.21968412399292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.24225616455078</t>
   </si>
   <si>
     <t xml:space="preserve">4.28474569320679</t>
   </si>
   <si>
-    <t xml:space="preserve">4.1665735244751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.14798402786255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.16391754150391</t>
+    <t xml:space="preserve">4.16657304763794</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.14798450469971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.16391801834106</t>
   </si>
   <si>
     <t xml:space="preserve">4.2329626083374</t>
@@ -1460,52 +1460,52 @@
     <t xml:space="preserve">4.17985153198242</t>
   </si>
   <si>
-    <t xml:space="preserve">4.06300687789917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.16259050369263</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.14001750946045</t>
+    <t xml:space="preserve">4.06300592422485</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.16259002685547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.14001798629761</t>
   </si>
   <si>
     <t xml:space="preserve">4.14931201934814</t>
   </si>
   <si>
-    <t xml:space="preserve">3.98201203346252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.06831741333008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.07230043411255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.20109510421753</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.10815000534058</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.21570158004761</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.34980630874634</t>
+    <t xml:space="preserve">3.98201179504395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.06831789016724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.07230138778687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.20109558105469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.10815095901489</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.21570062637329</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.34980726242065</t>
   </si>
   <si>
     <t xml:space="preserve">4.38432931900024</t>
   </si>
   <si>
-    <t xml:space="preserve">4.32325220108032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.29536819458008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.43744087219238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.53038454055786</t>
+    <t xml:space="preserve">4.32325172424316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.29536771774292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.43744039535522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.53038501739502</t>
   </si>
   <si>
     <t xml:space="preserve">4.56092357635498</t>
@@ -1517,43 +1517,43 @@
     <t xml:space="preserve">4.57287406921387</t>
   </si>
   <si>
-    <t xml:space="preserve">4.42681741714478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.31528520584106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.32590675354004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.35113430023193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.23163509368896</t>
+    <t xml:space="preserve">4.42681789398193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.31528568267822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.3259072303772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.35113477706909</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.23163461685181</t>
   </si>
   <si>
     <t xml:space="preserve">4.37105178833008</t>
   </si>
   <si>
-    <t xml:space="preserve">4.34847974777222</t>
+    <t xml:space="preserve">4.3484787940979</t>
   </si>
   <si>
     <t xml:space="preserve">4.54100799560547</t>
   </si>
   <si>
-    <t xml:space="preserve">4.5171070098877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.44939088821411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.45071792602539</t>
+    <t xml:space="preserve">4.51710748672485</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.44939136505127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.45071840286255</t>
   </si>
   <si>
     <t xml:space="preserve">4.55826854705811</t>
   </si>
   <si>
-    <t xml:space="preserve">4.52241945266724</t>
+    <t xml:space="preserve">4.52241849899292</t>
   </si>
   <si>
     <t xml:space="preserve">4.58216857910156</t>
@@ -1562,16 +1562,16 @@
     <t xml:space="preserve">4.3405122756958</t>
   </si>
   <si>
-    <t xml:space="preserve">4.36175727844238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.31130123138428</t>
+    <t xml:space="preserve">4.36175680160522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.31130075454712</t>
   </si>
   <si>
     <t xml:space="preserve">4.35379028320312</t>
   </si>
   <si>
-    <t xml:space="preserve">4.52905654907227</t>
+    <t xml:space="preserve">4.52905702590942</t>
   </si>
   <si>
     <t xml:space="preserve">4.60075759887695</t>
@@ -1580,55 +1580,55 @@
     <t xml:space="preserve">4.57818555831909</t>
   </si>
   <si>
-    <t xml:space="preserve">4.57154607772827</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.71892976760864</t>
+    <t xml:space="preserve">4.57154655456543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.7189302444458</t>
   </si>
   <si>
     <t xml:space="preserve">4.65386867523193</t>
   </si>
   <si>
-    <t xml:space="preserve">4.58615159988403</t>
+    <t xml:space="preserve">4.58615207672119</t>
   </si>
   <si>
     <t xml:space="preserve">4.53569650650024</t>
   </si>
   <si>
-    <t xml:space="preserve">4.6366081237793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.62731313705444</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.64590167999268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.70299625396729</t>
+    <t xml:space="preserve">4.63660717010498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.62731266021729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.64590215682983</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.70299673080444</t>
   </si>
   <si>
     <t xml:space="preserve">4.67112970352173</t>
   </si>
   <si>
-    <t xml:space="preserve">4.71760272979736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.78000736236572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.79195737838745</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.81452989578247</t>
+    <t xml:space="preserve">4.71760225296021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.78000783920288</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.79195833206177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.81452941894531</t>
   </si>
   <si>
     <t xml:space="preserve">4.79328536987305</t>
   </si>
   <si>
-    <t xml:space="preserve">4.88224601745605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.91278505325317</t>
+    <t xml:space="preserve">4.88224649429321</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.91278600692749</t>
   </si>
   <si>
     <t xml:space="preserve">5.03626871109009</t>
@@ -1643,49 +1643,49 @@
     <t xml:space="preserve">5.04423570632935</t>
   </si>
   <si>
-    <t xml:space="preserve">5.05618667602539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.10664176940918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.084068775177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.09203577041626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.98846864700317</t>
+    <t xml:space="preserve">5.05618619918823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.10664129257202</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.08406925201416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.0920352935791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.98846912384033</t>
   </si>
   <si>
     <t xml:space="preserve">4.87826347351074</t>
   </si>
   <si>
-    <t xml:space="preserve">4.9924521446228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.07477521896362</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.10265779495239</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.94863605499268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.96456956863403</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.02431917190552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.09867477416992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.15045881271362</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.08938074111938</t>
+    <t xml:space="preserve">4.99245309829712</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.07477474212646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.10265827178955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.94863557815552</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.96456909179688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.0243182182312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.09867525100708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.15045738220215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.08937978744507</t>
   </si>
   <si>
     <t xml:space="preserve">5.14249134063721</t>
@@ -1694,37 +1694,37 @@
     <t xml:space="preserve">5.16108083724976</t>
   </si>
   <si>
-    <t xml:space="preserve">5.1451473236084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.13054227828979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.16639137268066</t>
+    <t xml:space="preserve">5.14514684677124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.13054180145264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.16639232635498</t>
   </si>
   <si>
     <t xml:space="preserve">5.18763637542725</t>
   </si>
   <si>
-    <t xml:space="preserve">5.24340295791626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.24473094940186</t>
+    <t xml:space="preserve">5.2434024810791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.24472999572754</t>
   </si>
   <si>
     <t xml:space="preserve">5.26464796066284</t>
   </si>
   <si>
-    <t xml:space="preserve">5.26863145828247</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.23941946029663</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.26331949234009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.27394151687622</t>
+    <t xml:space="preserve">5.26863098144531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.23941993713379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.26331996917725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.27394247055054</t>
   </si>
   <si>
     <t xml:space="preserve">5.27659749984741</t>
@@ -1733,43 +1733,43 @@
     <t xml:space="preserve">5.18630838394165</t>
   </si>
   <si>
-    <t xml:space="preserve">5.24605846405029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.27128648757935</t>
+    <t xml:space="preserve">5.24605751037598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.2712869644165</t>
   </si>
   <si>
     <t xml:space="preserve">5.28456401824951</t>
   </si>
   <si>
-    <t xml:space="preserve">5.30580854415894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.36423110961914</t>
+    <t xml:space="preserve">5.30580902099609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.36423063278198</t>
   </si>
   <si>
     <t xml:space="preserve">5.41070365905762</t>
   </si>
   <si>
-    <t xml:space="preserve">5.55012035369873</t>
+    <t xml:space="preserve">5.55011940002441</t>
   </si>
   <si>
     <t xml:space="preserve">5.60323143005371</t>
   </si>
   <si>
-    <t xml:space="preserve">5.73468065261841</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.6828989982605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.70281505584717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.72538661956787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.72671604156494</t>
+    <t xml:space="preserve">5.73468160629272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.68289852142334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.70281457901001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.72538709640503</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.72671556472778</t>
   </si>
   <si>
     <t xml:space="preserve">5.70679807662964</t>
@@ -1778,82 +1778,82 @@
     <t xml:space="preserve">5.75725412368774</t>
   </si>
   <si>
-    <t xml:space="preserve">5.74264764785767</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.75990915298462</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.80638217926025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.80239868164062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.82496976852417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.92455339431763</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.94579839706421</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.93650531768799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.96837043762207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.95774936676025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.02148246765137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.97633695602417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.31757640838623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.32023286819458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.28172731399536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.14894866943359</t>
+    <t xml:space="preserve">5.74264717102051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.75990867614746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.8063817024231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.80239820480347</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.82497024536133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.92455434799194</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.94579982757568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.93650436401367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.96837091445923</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.95774793624878</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.02148151397705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.97633743286133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.31757688522339</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.32023239135742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.28172636032104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.14894819259644</t>
   </si>
   <si>
     <t xml:space="preserve">6.1237211227417</t>
   </si>
   <si>
-    <t xml:space="preserve">6.14230871200562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.22330379486084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.3135929107666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.26711988449097</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.20604276657104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.252516746521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.05467700958252</t>
+    <t xml:space="preserve">6.14230966567993</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.223304271698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.31359386444092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.26712131500244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.20604372024536</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.25251579284668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.05467748641968</t>
   </si>
   <si>
     <t xml:space="preserve">5.98032140731812</t>
   </si>
   <si>
-    <t xml:space="preserve">5.97500896453857</t>
+    <t xml:space="preserve">5.97500991821289</t>
   </si>
   <si>
     <t xml:space="preserve">5.90596437454224</t>
@@ -1862,79 +1862,79 @@
     <t xml:space="preserve">6.08787107467651</t>
   </si>
   <si>
-    <t xml:space="preserve">6.04936504364014</t>
+    <t xml:space="preserve">6.04936552047729</t>
   </si>
   <si>
     <t xml:space="preserve">6.12770462036133</t>
   </si>
   <si>
-    <t xml:space="preserve">5.99094247817993</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.04405546188354</t>
+    <t xml:space="preserve">5.99094390869141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.04405498504639</t>
   </si>
   <si>
     <t xml:space="preserve">6.08256006240845</t>
   </si>
   <si>
-    <t xml:space="preserve">5.82098627090454</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.92189836502075</t>
+    <t xml:space="preserve">5.8209867477417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.92189884185791</t>
   </si>
   <si>
     <t xml:space="preserve">5.90729331970215</t>
   </si>
   <si>
-    <t xml:space="preserve">5.86081981658936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.83028078079224</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.77584314346313</t>
+    <t xml:space="preserve">5.86082124710083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.83028030395508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.77584218978882</t>
   </si>
   <si>
     <t xml:space="preserve">5.78779268264771</t>
   </si>
   <si>
-    <t xml:space="preserve">5.93517589569092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.89401578903198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.92588233947754</t>
+    <t xml:space="preserve">5.93517637252808</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.89401483535767</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.92588090896606</t>
   </si>
   <si>
     <t xml:space="preserve">6.04272651672363</t>
   </si>
   <si>
-    <t xml:space="preserve">6.09982061386108</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.12903213500977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.15293216705322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.12106657028198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.16753721237183</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.2219762802124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.31624841690063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.42833089828491</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.38377666473389</t>
+    <t xml:space="preserve">6.09982013702393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.12903261184692</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.15293264389038</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.12106513977051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.16753768920898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.22197580337524</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.31624889373779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.4283299446106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.38377571105957</t>
   </si>
   <si>
     <t xml:space="preserve">6.35732316970825</t>
@@ -1943,64 +1943,64 @@
     <t xml:space="preserve">6.36289167404175</t>
   </si>
   <si>
-    <t xml:space="preserve">6.44643115997314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.43529224395752</t>
+    <t xml:space="preserve">6.44642972946167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.43529272079468</t>
   </si>
   <si>
     <t xml:space="preserve">6.58983898162842</t>
   </si>
   <si>
-    <t xml:space="preserve">6.74577808380127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.78754854202271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.76248598098755</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.75274038314819</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.72071743011475</t>
+    <t xml:space="preserve">6.74577903747559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.78754949569702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.76248693466187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.75273942947388</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.72071838378906</t>
   </si>
   <si>
     <t xml:space="preserve">6.78615617752075</t>
   </si>
   <si>
-    <t xml:space="preserve">6.71932601928711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.72350215911865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.69426345825195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.67337894439697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.6594557762146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.5438928604126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.57313203811646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.53136253356934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.59540843963623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.54806995391846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.67477178573608</t>
+    <t xml:space="preserve">6.71932554244995</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.72350168228149</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.69426298141479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.67337942123413</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.65945434570312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.54389190673828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.5731315612793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.53136157989502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.59540796279907</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.5480694770813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.67477035522461</t>
   </si>
   <si>
     <t xml:space="preserve">6.50073099136353</t>
@@ -2012,40 +2012,40 @@
     <t xml:space="preserve">6.79172468185425</t>
   </si>
   <si>
-    <t xml:space="preserve">6.71236419677734</t>
+    <t xml:space="preserve">6.71236324310303</t>
   </si>
   <si>
     <t xml:space="preserve">6.6051549911499</t>
   </si>
   <si>
-    <t xml:space="preserve">6.60097885131836</t>
+    <t xml:space="preserve">6.60097932815552</t>
   </si>
   <si>
     <t xml:space="preserve">6.7095775604248</t>
   </si>
   <si>
-    <t xml:space="preserve">6.26125240325928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.33504581451416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.48123931884766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.3656759262085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.61350774765015</t>
+    <t xml:space="preserve">6.26125288009644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.33504629135132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.48123788833618</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.36567640304565</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.61350917816162</t>
   </si>
   <si>
     <t xml:space="preserve">6.56756210327148</t>
   </si>
   <si>
-    <t xml:space="preserve">6.75134706497192</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.72767877578735</t>
+    <t xml:space="preserve">6.75134897232056</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.7276782989502</t>
   </si>
   <si>
     <t xml:space="preserve">6.55781602859497</t>
@@ -2057,82 +2057,82 @@
     <t xml:space="preserve">6.54250049591064</t>
   </si>
   <si>
-    <t xml:space="preserve">6.8502049446106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.80286502838135</t>
+    <t xml:space="preserve">6.85020303726196</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.80286359786987</t>
   </si>
   <si>
     <t xml:space="preserve">6.87526416778564</t>
   </si>
   <si>
-    <t xml:space="preserve">6.89197158813477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.02424287796021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.99639558792114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.01380014419556</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.0172815322876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.89893388748169</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.92678117752075</t>
+    <t xml:space="preserve">6.89197206497192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.02424240112305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.99639797210693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.01380062103271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.01728057861328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.89893436431885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.92678070068359</t>
   </si>
   <si>
     <t xml:space="preserve">7.04860782623291</t>
   </si>
   <si>
-    <t xml:space="preserve">7.09037828445435</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.00335741043091</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.94348859786987</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.07297325134277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.08689641952515</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.00683927536011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.15303134918213</t>
+    <t xml:space="preserve">7.09037780761719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.00335884094238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.94348764419556</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.07297372817993</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.08689737319946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.00683832168579</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.15303230285645</t>
   </si>
   <si>
     <t xml:space="preserve">7.11126279830933</t>
   </si>
   <si>
-    <t xml:space="preserve">7.10778141021729</t>
+    <t xml:space="preserve">7.10778331756592</t>
   </si>
   <si>
     <t xml:space="preserve">7.14259004592896</t>
   </si>
   <si>
-    <t xml:space="preserve">7.26093721389771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.15999412536621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.93652582168579</t>
+    <t xml:space="preserve">7.26093673706055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.15999364852905</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.93652677536011</t>
   </si>
   <si>
     <t xml:space="preserve">6.95184230804443</t>
   </si>
   <si>
-    <t xml:space="preserve">6.94766426086426</t>
+    <t xml:space="preserve">6.94766473770142</t>
   </si>
   <si>
     <t xml:space="preserve">7.146071434021</t>
@@ -2141,13 +2141,13 @@
     <t xml:space="preserve">7.05208873748779</t>
   </si>
   <si>
-    <t xml:space="preserve">7.13562822341919</t>
+    <t xml:space="preserve">7.13562726974487</t>
   </si>
   <si>
     <t xml:space="preserve">7.36535978317261</t>
   </si>
   <si>
-    <t xml:space="preserve">7.37580156326294</t>
+    <t xml:space="preserve">7.37580347061157</t>
   </si>
   <si>
     <t xml:space="preserve">7.47674465179443</t>
@@ -2156,76 +2156,76 @@
     <t xml:space="preserve">7.36884069442749</t>
   </si>
   <si>
-    <t xml:space="preserve">7.45238018035889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.49415016174316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.51851654052734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.60553646087646</t>
+    <t xml:space="preserve">7.45238065719604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.49414968490601</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.51851606369019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.60553550720215</t>
   </si>
   <si>
     <t xml:space="preserve">7.62293910980225</t>
   </si>
   <si>
-    <t xml:space="preserve">7.65078592300415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.5602855682373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.59509325027466</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.58116960525513</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.57420921325684</t>
+    <t xml:space="preserve">7.65078544616699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.56028604507446</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.59509372711182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.58116912841797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.57420778274536</t>
   </si>
   <si>
     <t xml:space="preserve">7.67863130569458</t>
   </si>
   <si>
-    <t xml:space="preserve">7.7238826751709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.77609395980835</t>
+    <t xml:space="preserve">7.72388124465942</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.77609491348267</t>
   </si>
   <si>
     <t xml:space="preserve">7.65426635742188</t>
   </si>
   <si>
-    <t xml:space="preserve">7.54636144638062</t>
+    <t xml:space="preserve">7.54636096954346</t>
   </si>
   <si>
     <t xml:space="preserve">7.63686323165894</t>
   </si>
   <si>
-    <t xml:space="preserve">7.80045938491821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.73780488967896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.75520992279053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.76913118362427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.81078004837036</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.67665958404541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.74725103378296</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.65195226669312</t>
+    <t xml:space="preserve">7.80045986175537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.73780584335327</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.75520896911621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.76913261413574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.81078052520752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.67666053771973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.74724912643433</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.65195274353027</t>
   </si>
   <si>
     <t xml:space="preserve">7.71548509597778</t>
@@ -2234,118 +2234,118 @@
     <t xml:space="preserve">7.73666095733643</t>
   </si>
   <si>
-    <t xml:space="preserve">7.66607141494751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.61665868759155</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.50724411010742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.47547960281372</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.23194217681885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.30959177017212</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.40488719940186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.27076816558838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.28135633468628</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.1895899772644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.29194450378418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.21076631546021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.33076953887939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.17900085449219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.24253225326538</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.17547082901001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.26723766326904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.36253309249878</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.14370489120483</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.19664907455444</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.10488080978394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.04346799850464</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.22488403320312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.12605810165405</t>
+    <t xml:space="preserve">7.66606950759888</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.61665773391724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.50724363327026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.47547817230225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.23194313049316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.30959272384644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.40488815307617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.27076721191406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.2813549041748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.18958854675293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.2919454574585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.21076679229736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.33077001571655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.17900037765503</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.24253129959106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.17547178268433</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.2672381401062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.36253499984741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.14370584487915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.19664812088013</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.10488176345825</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.04346752166748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.2248854637146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.12605953216553</t>
   </si>
   <si>
     <t xml:space="preserve">7.23900270462036</t>
   </si>
   <si>
-    <t xml:space="preserve">7.20723676681519</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.16488313674927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.10135364532471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.09076261520386</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.26017999649048</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.32723999023438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.34841680526733</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.25312042236328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.47194814682007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.82136964797974</t>
+    <t xml:space="preserve">7.20723819732666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.16488075256348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.10135078430176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.09076309204102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.26017951965332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.32724046707153</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.34841632843018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.25311899185181</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.47194910049438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.82136869430542</t>
   </si>
   <si>
     <t xml:space="preserve">7.7613673210144</t>
   </si>
   <si>
-    <t xml:space="preserve">7.30606317520142</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.41547775268555</t>
+    <t xml:space="preserve">7.30606269836426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.41547727584839</t>
   </si>
   <si>
     <t xml:space="preserve">7.55665683746338</t>
@@ -2354,79 +2354,79 @@
     <t xml:space="preserve">7.57077503204346</t>
   </si>
   <si>
-    <t xml:space="preserve">7.62018775939941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.69783735275269</t>
+    <t xml:space="preserve">7.62018966674805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.69783592224121</t>
   </si>
   <si>
     <t xml:space="preserve">7.78960418701172</t>
   </si>
   <si>
-    <t xml:space="preserve">7.75077962875366</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.72960329055786</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.71901321411133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.00490188598633</t>
+    <t xml:space="preserve">7.75077819824219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.72960186004639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.71901416778564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.00490283966064</t>
   </si>
   <si>
     <t xml:space="preserve">8.12490558624268</t>
   </si>
   <si>
-    <t xml:space="preserve">7.96607780456543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.97313785552979</t>
+    <t xml:space="preserve">7.96607828140259</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.97313928604126</t>
   </si>
   <si>
     <t xml:space="preserve">7.40841770172119</t>
   </si>
   <si>
-    <t xml:space="preserve">7.29547595977783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.44018363952637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.11899900436401</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.78652143478394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.53804302215576</t>
+    <t xml:space="preserve">7.29547452926636</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.44018316268921</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.11899852752686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.78652095794678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.53804445266724</t>
   </si>
   <si>
     <t xml:space="preserve">6.79075574874878</t>
   </si>
   <si>
-    <t xml:space="preserve">6.83875799179077</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.65804719924927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.86275720596313</t>
+    <t xml:space="preserve">6.83875703811646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.65804672241211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.86275672912598</t>
   </si>
   <si>
     <t xml:space="preserve">5.97050046920776</t>
   </si>
   <si>
-    <t xml:space="preserve">5.56107807159424</t>
+    <t xml:space="preserve">5.5610785484314</t>
   </si>
   <si>
     <t xml:space="preserve">5.56249046325684</t>
   </si>
   <si>
-    <t xml:space="preserve">4.33704805374146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.76058769226074</t>
+    <t xml:space="preserve">4.3370475769043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.7605881690979</t>
   </si>
   <si>
     <t xml:space="preserve">4.58976030349731</t>
@@ -2438,61 +2438,61 @@
     <t xml:space="preserve">4.49658107757568</t>
   </si>
   <si>
-    <t xml:space="preserve">4.88058996200562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.89612054824829</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.0655369758606</t>
+    <t xml:space="preserve">4.88059091567993</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.89612102508545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.06553649902344</t>
   </si>
   <si>
     <t xml:space="preserve">5.41142749786377</t>
   </si>
   <si>
-    <t xml:space="preserve">5.46083974838257</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.71637535095215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.542724609375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.5879020690918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.44954586029053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.21801137924194</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.48625326156616</t>
+    <t xml:space="preserve">5.46084070205688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.71637630462646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.54272508621216</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.58790159225464</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.44954633712769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.21801090240479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.486252784729</t>
   </si>
   <si>
     <t xml:space="preserve">5.5271954536438</t>
   </si>
   <si>
-    <t xml:space="preserve">5.67543315887451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.7573184967041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.84343767166138</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.86320304870605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.88720369338989</t>
+    <t xml:space="preserve">5.67543411254883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.75731801986694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.84343814849854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.86320352554321</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.88720417022705</t>
   </si>
   <si>
     <t xml:space="preserve">5.36907339096069</t>
   </si>
   <si>
-    <t xml:space="preserve">5.41283988952637</t>
+    <t xml:space="preserve">5.41284036636353</t>
   </si>
   <si>
     <t xml:space="preserve">5.43542814254761</t>
@@ -2510,16 +2510,16 @@
     <t xml:space="preserve">5.3069543838501</t>
   </si>
   <si>
-    <t xml:space="preserve">5.22224617004395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.56390190124512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.55401945114136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.66837596893311</t>
+    <t xml:space="preserve">5.2222466468811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.56390142440796</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.5540189743042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.66837453842163</t>
   </si>
   <si>
     <t xml:space="preserve">5.47213459014893</t>
@@ -2531,37 +2531,37 @@
     <t xml:space="preserve">5.18836307525635</t>
   </si>
   <si>
-    <t xml:space="preserve">5.10224390029907</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.36060285568237</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.47495937347412</t>
+    <t xml:space="preserve">5.10224342346191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.36060333251953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.47495794296265</t>
   </si>
   <si>
     <t xml:space="preserve">5.25613021850586</t>
   </si>
   <si>
-    <t xml:space="preserve">5.16012716293335</t>
+    <t xml:space="preserve">5.16012763977051</t>
   </si>
   <si>
     <t xml:space="preserve">5.07259559631348</t>
   </si>
   <si>
-    <t xml:space="preserve">5.2674241065979</t>
+    <t xml:space="preserve">5.26742362976074</t>
   </si>
   <si>
     <t xml:space="preserve">5.22648143768311</t>
   </si>
   <si>
-    <t xml:space="preserve">5.23495244979858</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.20248126983643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.25330591201782</t>
+    <t xml:space="preserve">5.23495292663574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.20248174667358</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.25330686569214</t>
   </si>
   <si>
     <t xml:space="preserve">5.46225214004517</t>
@@ -2573,19 +2573,19 @@
     <t xml:space="preserve">5.5723729133606</t>
   </si>
   <si>
-    <t xml:space="preserve">5.62319707870483</t>
+    <t xml:space="preserve">5.62319755554199</t>
   </si>
   <si>
     <t xml:space="preserve">5.68813943862915</t>
   </si>
   <si>
-    <t xml:space="preserve">5.86037969589233</t>
+    <t xml:space="preserve">5.86038017272949</t>
   </si>
   <si>
     <t xml:space="preserve">6.04814958572388</t>
   </si>
   <si>
-    <t xml:space="preserve">6.19074153900146</t>
+    <t xml:space="preserve">6.19074201583862</t>
   </si>
   <si>
     <t xml:space="preserve">6.31921434402466</t>
@@ -2594,25 +2594,25 @@
     <t xml:space="preserve">6.12438631057739</t>
   </si>
   <si>
-    <t xml:space="preserve">6.05379629135132</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.73472881317139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.82226181030273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.87167358398438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.99026536941528</t>
+    <t xml:space="preserve">6.05379676818848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.73472929000854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.82226133346558</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.87167406082153</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.99026584625244</t>
   </si>
   <si>
     <t xml:space="preserve">5.96344184875488</t>
   </si>
   <si>
-    <t xml:space="preserve">5.92108726501465</t>
+    <t xml:space="preserve">5.92108678817749</t>
   </si>
   <si>
     <t xml:space="preserve">5.8024959564209</t>
@@ -2624,52 +2624,52 @@
     <t xml:space="preserve">6.02327108383179</t>
   </si>
   <si>
-    <t xml:space="preserve">5.75628709793091</t>
+    <t xml:space="preserve">5.75628662109375</t>
   </si>
   <si>
     <t xml:space="preserve">5.79736137390137</t>
   </si>
   <si>
-    <t xml:space="preserve">5.68147325515747</t>
+    <t xml:space="preserve">5.68147277832031</t>
   </si>
   <si>
     <t xml:space="preserve">5.85457277297974</t>
   </si>
   <si>
-    <t xml:space="preserve">5.6770715713501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.68734121322632</t>
+    <t xml:space="preserve">5.67707204818726</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.68734073638916</t>
   </si>
   <si>
     <t xml:space="preserve">5.71227884292603</t>
   </si>
   <si>
-    <t xml:space="preserve">5.80469608306885</t>
+    <t xml:space="preserve">5.80469703674316</t>
   </si>
   <si>
     <t xml:space="preserve">5.7724232673645</t>
   </si>
   <si>
-    <t xml:space="preserve">5.7269492149353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.59198999404907</t>
+    <t xml:space="preserve">5.72694873809814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.59198951721191</t>
   </si>
   <si>
     <t xml:space="preserve">5.64039850234985</t>
   </si>
   <si>
-    <t xml:space="preserve">5.74748563766479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.72548198699951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.75042009353638</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.76655530929565</t>
+    <t xml:space="preserve">5.74748516082764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.7254810333252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.75041961669922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.76655626296997</t>
   </si>
   <si>
     <t xml:space="preserve">6.00420045852661</t>
@@ -2690,7 +2690,7 @@
     <t xml:space="preserve">5.82670021057129</t>
   </si>
   <si>
-    <t xml:space="preserve">5.79442834854126</t>
+    <t xml:space="preserve">5.7944278717041</t>
   </si>
   <si>
     <t xml:space="preserve">5.77975845336914</t>
@@ -2699,19 +2699,19 @@
     <t xml:space="preserve">5.58172082901001</t>
   </si>
   <si>
-    <t xml:space="preserve">5.68587398529053</t>
+    <t xml:space="preserve">5.68587350845337</t>
   </si>
   <si>
     <t xml:space="preserve">5.79149389266968</t>
   </si>
   <si>
-    <t xml:space="preserve">5.8311014175415</t>
+    <t xml:space="preserve">5.83110094070435</t>
   </si>
   <si>
     <t xml:space="preserve">5.82963418960571</t>
   </si>
   <si>
-    <t xml:space="preserve">5.73868370056152</t>
+    <t xml:space="preserve">5.73868322372437</t>
   </si>
   <si>
     <t xml:space="preserve">5.7841591835022</t>
@@ -2720,7 +2720,7 @@
     <t xml:space="preserve">5.88537836074829</t>
   </si>
   <si>
-    <t xml:space="preserve">5.97926330566406</t>
+    <t xml:space="preserve">5.9792628288269</t>
   </si>
   <si>
     <t xml:space="preserve">5.97192811965942</t>
@@ -2729,19 +2729,19 @@
     <t xml:space="preserve">5.90004730224609</t>
   </si>
   <si>
-    <t xml:space="preserve">5.87510967254639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.78269243240356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.76362180709839</t>
+    <t xml:space="preserve">5.87510919570923</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.78269195556641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.76362133026123</t>
   </si>
   <si>
     <t xml:space="preserve">5.82376623153687</t>
   </si>
   <si>
-    <t xml:space="preserve">5.72401428222656</t>
+    <t xml:space="preserve">5.72401475906372</t>
   </si>
   <si>
     <t xml:space="preserve">5.80176258087158</t>
@@ -2753,10 +2753,10 @@
     <t xml:space="preserve">5.75335359573364</t>
   </si>
   <si>
-    <t xml:space="preserve">5.75775384902954</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.6726713180542</t>
+    <t xml:space="preserve">5.7577543258667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.67267227172852</t>
   </si>
   <si>
     <t xml:space="preserve">5.63013029098511</t>
@@ -2768,88 +2768,88 @@
     <t xml:space="preserve">5.83696889877319</t>
   </si>
   <si>
-    <t xml:space="preserve">5.71668004989624</t>
+    <t xml:space="preserve">5.7166805267334</t>
   </si>
   <si>
     <t xml:space="preserve">5.8531060218811</t>
   </si>
   <si>
-    <t xml:space="preserve">5.84283638000488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.84577083587646</t>
+    <t xml:space="preserve">5.84283685684204</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.84577035903931</t>
   </si>
   <si>
     <t xml:space="preserve">5.81203126907349</t>
   </si>
   <si>
-    <t xml:space="preserve">5.69320869445801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.49517107009888</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.57291984558105</t>
+    <t xml:space="preserve">5.69320917129517</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.49517154693604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.57291889190674</t>
   </si>
   <si>
     <t xml:space="preserve">5.61839437484741</t>
   </si>
   <si>
-    <t xml:space="preserve">5.60665845870972</t>
+    <t xml:space="preserve">5.60665893554688</t>
   </si>
   <si>
     <t xml:space="preserve">5.56411743164062</t>
   </si>
   <si>
-    <t xml:space="preserve">5.66973781585693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.55678272247314</t>
+    <t xml:space="preserve">5.66973733901978</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.5567831993103</t>
   </si>
   <si>
     <t xml:space="preserve">5.55091524124146</t>
   </si>
   <si>
-    <t xml:space="preserve">5.50984144210815</t>
+    <t xml:space="preserve">5.509840965271</t>
   </si>
   <si>
     <t xml:space="preserve">5.54211378097534</t>
   </si>
   <si>
-    <t xml:space="preserve">5.93232107162476</t>
+    <t xml:space="preserve">5.9323205947876</t>
   </si>
   <si>
     <t xml:space="preserve">5.88097715377808</t>
   </si>
   <si>
-    <t xml:space="preserve">5.87804317474365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.87951040267944</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.89271354675293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.8941798210144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.59932374954224</t>
+    <t xml:space="preserve">5.87804412841797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.87950944900513</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.89271306991577</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.89417934417725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.59932518005371</t>
   </si>
   <si>
     <t xml:space="preserve">5.66827058792114</t>
   </si>
   <si>
-    <t xml:space="preserve">5.67560529708862</t>
+    <t xml:space="preserve">5.67560482025146</t>
   </si>
   <si>
     <t xml:space="preserve">5.56998538970947</t>
   </si>
   <si>
-    <t xml:space="preserve">5.57878732681274</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.56851863861084</t>
+    <t xml:space="preserve">5.57878637313843</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.56851816177368</t>
   </si>
   <si>
     <t xml:space="preserve">5.47903442382812</t>
@@ -2858,13 +2858,13 @@
     <t xml:space="preserve">5.43942785263062</t>
   </si>
   <si>
-    <t xml:space="preserve">5.21058464050293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.14017009735107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.1343035697937</t>
+    <t xml:space="preserve">5.21058416366577</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.14017057418823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.13430261611938</t>
   </si>
   <si>
     <t xml:space="preserve">5.25752639770508</t>
@@ -2873,61 +2873,61 @@
     <t xml:space="preserve">5.30740261077881</t>
   </si>
   <si>
-    <t xml:space="preserve">5.47463464736938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.65506839752197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.56265020370483</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.75922107696533</t>
+    <t xml:space="preserve">5.47463369369507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.65506887435913</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.56265068054199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.75922203063965</t>
   </si>
   <si>
     <t xml:space="preserve">5.90151405334473</t>
   </si>
   <si>
-    <t xml:space="preserve">5.85897397994995</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.0364727973938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.23744487762451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.31812715530396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.42521333694458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.49416065216064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.39440822601318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.42820262908936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.57317733764648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.51040458679199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.5761661529541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.38485860824585</t>
+    <t xml:space="preserve">5.85897302627563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.03647375106812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.23744440078735</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.31812620162964</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.4252142906189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.49415922164917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.39440774917603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.42820358276367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.57317686080933</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.51040410995483</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.57616710662842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.38486003875732</t>
   </si>
   <si>
     <t xml:space="preserve">6.43567609786987</t>
   </si>
   <si>
-    <t xml:space="preserve">6.33254957199097</t>
+    <t xml:space="preserve">6.33254909515381</t>
   </si>
   <si>
     <t xml:space="preserve">6.35496807098389</t>
@@ -2936,91 +2936,91 @@
     <t xml:space="preserve">6.28322839736938</t>
   </si>
   <si>
-    <t xml:space="preserve">6.27276611328125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.28173398971558</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.29070091247559</t>
+    <t xml:space="preserve">6.27276515960693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.28173446655273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.29070138931274</t>
   </si>
   <si>
     <t xml:space="preserve">6.23988580703735</t>
   </si>
   <si>
-    <t xml:space="preserve">6.23540115356445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.33553838729858</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.26977777481079</t>
+    <t xml:space="preserve">6.23540163040161</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.33553743362427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.26977825164795</t>
   </si>
   <si>
     <t xml:space="preserve">6.24586391448975</t>
   </si>
   <si>
-    <t xml:space="preserve">6.10238361358643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.22792911529541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.25333738327026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.21746730804443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.23390674591064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.19355297088623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.38187026977539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.51488828659058</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.42222452163696</t>
+    <t xml:space="preserve">6.10238409042358</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.22792816162109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.25333642959595</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.21746635437012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.2339072227478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.19355440139771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.38187074661255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.51488876342773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.42222356796265</t>
   </si>
   <si>
     <t xml:space="preserve">6.37738752365112</t>
   </si>
   <si>
-    <t xml:space="preserve">6.30265808105469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.24138021469116</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.26230430603027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.20999336242676</t>
+    <t xml:space="preserve">6.30265760421753</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.24137926101685</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.26230478286743</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.20999383926392</t>
   </si>
   <si>
     <t xml:space="preserve">6.27426052093506</t>
   </si>
   <si>
-    <t xml:space="preserve">6.21597194671631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.17860698699951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.13376998901367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.24885320663452</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.09789991378784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.15320014953613</t>
+    <t xml:space="preserve">6.21597146987915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.17860651016235</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.13376951217651</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.24885272979736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.097900390625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.15319871902466</t>
   </si>
   <si>
     <t xml:space="preserve">6.03512763977051</t>
@@ -3029,7 +3029,7 @@
     <t xml:space="preserve">6.19803667068481</t>
   </si>
   <si>
-    <t xml:space="preserve">6.18757390975952</t>
+    <t xml:space="preserve">6.18757486343384</t>
   </si>
   <si>
     <t xml:space="preserve">6.62847709655762</t>
@@ -3041,7 +3041,7 @@
     <t xml:space="preserve">6.8900294303894</t>
   </si>
   <si>
-    <t xml:space="preserve">7.06639099121094</t>
+    <t xml:space="preserve">7.06639003753662</t>
   </si>
   <si>
     <t xml:space="preserve">7.15158128738403</t>
@@ -3050,97 +3050,97 @@
     <t xml:space="preserve">7.10973262786865</t>
   </si>
   <si>
-    <t xml:space="preserve">7.21136426925659</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.23228931427002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.30104064941406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.21285963058472</t>
+    <t xml:space="preserve">7.21136379241943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.23228883743286</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.30103969573975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.21285915374756</t>
   </si>
   <si>
     <t xml:space="preserve">7.08581924438477</t>
   </si>
   <si>
-    <t xml:space="preserve">6.95280075073242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.02304553985596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.20688104629517</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.12019491195679</t>
+    <t xml:space="preserve">6.95280170440674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.02304649353027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.20688056945801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.12019538879395</t>
   </si>
   <si>
     <t xml:space="preserve">7.13663530349731</t>
   </si>
   <si>
-    <t xml:space="preserve">7.17997789382935</t>
+    <t xml:space="preserve">7.17997884750366</t>
   </si>
   <si>
     <t xml:space="preserve">7.02753114700317</t>
   </si>
   <si>
-    <t xml:space="preserve">7.34438180923462</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.38025236129761</t>
+    <t xml:space="preserve">7.34438228607178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.38025283813477</t>
   </si>
   <si>
     <t xml:space="preserve">7.4355525970459</t>
   </si>
   <si>
-    <t xml:space="preserve">7.45348644256592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.36082363128662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.50280809402466</t>
+    <t xml:space="preserve">7.45348691940308</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.36082410812378</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.5028076171875</t>
   </si>
   <si>
     <t xml:space="preserve">7.57753753662109</t>
   </si>
   <si>
-    <t xml:space="preserve">7.64479303359985</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.61116647720337</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.67842245101929</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.63358545303345</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.79798889160156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.75688743591309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.81293439865112</t>
+    <t xml:space="preserve">7.64479351043701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.61116504669189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.67842102050781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.63358497619629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.79798936843872</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.7568883895874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.81293344497681</t>
   </si>
   <si>
     <t xml:space="preserve">7.72699594497681</t>
   </si>
   <si>
-    <t xml:space="preserve">7.8502984046936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.78304195404053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.824143409729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.8166708946228</t>
+    <t xml:space="preserve">7.85029935836792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.78304290771484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.82414484024048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.81667137145996</t>
   </si>
   <si>
     <t xml:space="preserve">7.88392734527588</t>
@@ -3149,7 +3149,7 @@
     <t xml:space="preserve">8.05580425262451</t>
   </si>
   <si>
-    <t xml:space="preserve">8.11185073852539</t>
+    <t xml:space="preserve">8.11184978485107</t>
   </si>
   <si>
     <t xml:space="preserve">8.10064220428467</t>
@@ -3158,58 +3158,58 @@
     <t xml:space="preserve">8.15295219421387</t>
   </si>
   <si>
-    <t xml:space="preserve">8.17537117004395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.16416358947754</t>
+    <t xml:space="preserve">8.17537021636963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.16416168212891</t>
   </si>
   <si>
     <t xml:space="preserve">8.04833126068115</t>
   </si>
   <si>
-    <t xml:space="preserve">8.06701278686523</t>
+    <t xml:space="preserve">8.06701564788818</t>
   </si>
   <si>
     <t xml:space="preserve">8.05954074859619</t>
   </si>
   <si>
-    <t xml:space="preserve">7.9698657989502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.96239233016968</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.05206680297852</t>
+    <t xml:space="preserve">7.96986484527588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.96239328384399</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.05206871032715</t>
   </si>
   <si>
     <t xml:space="preserve">8.04085826873779</t>
   </si>
   <si>
-    <t xml:space="preserve">7.93250179290771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.9287633895874</t>
+    <t xml:space="preserve">7.9325008392334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.92876434326172</t>
   </si>
   <si>
     <t xml:space="preserve">8.10811519622803</t>
   </si>
   <si>
-    <t xml:space="preserve">8.07822322845459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.08943176269531</t>
+    <t xml:space="preserve">8.07822227478027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.08943271636963</t>
   </si>
   <si>
     <t xml:space="preserve">8.16042423248291</t>
   </si>
   <si>
-    <t xml:space="preserve">8.15668869018555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.14547824859619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.25757503509521</t>
+    <t xml:space="preserve">8.15668964385986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.14547729492188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.2575740814209</t>
   </si>
   <si>
     <t xml:space="preserve">8.19778919219971</t>
@@ -3221,28 +3221,28 @@
     <t xml:space="preserve">8.22020816802979</t>
   </si>
   <si>
-    <t xml:space="preserve">8.38834762573242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.35098552703857</t>
+    <t xml:space="preserve">8.38834857940674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.35098361968994</t>
   </si>
   <si>
     <t xml:space="preserve">8.24636363983154</t>
   </si>
   <si>
-    <t xml:space="preserve">8.25010013580322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.30988311767578</t>
+    <t xml:space="preserve">8.25009918212891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.30988121032715</t>
   </si>
   <si>
     <t xml:space="preserve">8.43692302703857</t>
   </si>
   <si>
-    <t xml:space="preserve">8.4257116317749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.39208602905273</t>
+    <t xml:space="preserve">8.42571258544922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.39208507537842</t>
   </si>
   <si>
     <t xml:space="preserve">8.46307849884033</t>
@@ -3251,22 +3251,22 @@
     <t xml:space="preserve">8.59385395050049</t>
   </si>
   <si>
-    <t xml:space="preserve">8.74331283569336</t>
+    <t xml:space="preserve">8.74331188201904</t>
   </si>
   <si>
     <t xml:space="preserve">8.62748336791992</t>
   </si>
   <si>
-    <t xml:space="preserve">8.53407096862793</t>
+    <t xml:space="preserve">8.53407001495361</t>
   </si>
   <si>
     <t xml:space="preserve">8.58638095855713</t>
   </si>
   <si>
-    <t xml:space="preserve">8.59759140014648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.64242839813232</t>
+    <t xml:space="preserve">8.59759044647217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.64242744445801</t>
   </si>
   <si>
     <t xml:space="preserve">8.81804084777832</t>
@@ -3275,10 +3275,10 @@
     <t xml:space="preserve">8.90024375915527</t>
   </si>
   <si>
-    <t xml:space="preserve">9.01233768463135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.02728462219238</t>
+    <t xml:space="preserve">9.01233673095703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.02728366851807</t>
   </si>
   <si>
     <t xml:space="preserve">8.95629024505615</t>
@@ -3296,10 +3296,10 @@
     <t xml:space="preserve">8.96376323699951</t>
   </si>
   <si>
-    <t xml:space="preserve">8.73957538604736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.85025119781494</t>
+    <t xml:space="preserve">8.73957633972168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.85025215148926</t>
   </si>
   <si>
     <t xml:space="preserve">8.73112106323242</t>
@@ -3308,73 +3308,73 @@
     <t xml:space="preserve">8.62736225128174</t>
   </si>
   <si>
-    <t xml:space="preserve">8.78107833862305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.75417995452881</t>
+    <t xml:space="preserve">8.78108024597168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.75417900085449</t>
   </si>
   <si>
     <t xml:space="preserve">8.6119909286499</t>
   </si>
   <si>
-    <t xml:space="preserve">8.57355976104736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.56971740722656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.66963291168213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.59277629852295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.71574878692627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.58509063720703</t>
+    <t xml:space="preserve">8.57356071472168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.56971836090088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.66963386535645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.59277534484863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.71574974060059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.58509159088135</t>
   </si>
   <si>
     <t xml:space="preserve">8.61967658996582</t>
   </si>
   <si>
-    <t xml:space="preserve">8.3199291229248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.45058917999268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.48133087158203</t>
+    <t xml:space="preserve">8.31992816925049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.45058727264404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.48133182525635</t>
   </si>
   <si>
     <t xml:space="preserve">8.47748756408691</t>
   </si>
   <si>
-    <t xml:space="preserve">8.44674396514893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.33145809173584</t>
+    <t xml:space="preserve">8.44674491882324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.33145713806152</t>
   </si>
   <si>
     <t xml:space="preserve">8.35835742950439</t>
   </si>
   <si>
-    <t xml:space="preserve">8.0739803314209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.15468120574951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.41215801239014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.53897571563721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.6158332824707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.68500518798828</t>
+    <t xml:space="preserve">8.07398128509521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.15468215942383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.41215896606445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.53897380828857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.61583232879639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.68500709533691</t>
   </si>
   <si>
     <t xml:space="preserve">8.60046195983887</t>
@@ -3389,31 +3389,31 @@
     <t xml:space="preserve">8.7272777557373</t>
   </si>
   <si>
-    <t xml:space="preserve">8.85793781280518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.90020942687988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.93479537963867</t>
+    <t xml:space="preserve">8.85793685913086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.9002103805542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.93479633331299</t>
   </si>
   <si>
     <t xml:space="preserve">9.0078125</t>
   </si>
   <si>
-    <t xml:space="preserve">9.02702617645264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.98091220855713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.92326641082764</t>
+    <t xml:space="preserve">9.02702522277832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.98091125488281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.92326736450195</t>
   </si>
   <si>
     <t xml:space="preserve">8.87331008911133</t>
   </si>
   <si>
-    <t xml:space="preserve">8.94632530212402</t>
+    <t xml:space="preserve">8.94632434844971</t>
   </si>
   <si>
     <t xml:space="preserve">8.83487987518311</t>
@@ -3428,25 +3428,25 @@
     <t xml:space="preserve">8.93863868713379</t>
   </si>
   <si>
-    <t xml:space="preserve">8.9078950881958</t>
+    <t xml:space="preserve">8.90789604187012</t>
   </si>
   <si>
     <t xml:space="preserve">8.82719421386719</t>
   </si>
   <si>
-    <t xml:space="preserve">8.86562442779541</t>
+    <t xml:space="preserve">8.86562347412109</t>
   </si>
   <si>
     <t xml:space="preserve">8.91174030303955</t>
   </si>
   <si>
-    <t xml:space="preserve">8.94248199462891</t>
+    <t xml:space="preserve">8.94248104095459</t>
   </si>
   <si>
     <t xml:space="preserve">8.80797958374023</t>
   </si>
   <si>
-    <t xml:space="preserve">8.86946773529053</t>
+    <t xml:space="preserve">8.86946678161621</t>
   </si>
   <si>
     <t xml:space="preserve">8.88483905792236</t>
@@ -3455,16 +3455,16 @@
     <t xml:space="preserve">8.96553993225098</t>
   </si>
   <si>
-    <t xml:space="preserve">9.10772895812988</t>
+    <t xml:space="preserve">9.10772800445557</t>
   </si>
   <si>
     <t xml:space="preserve">9.02318286895752</t>
   </si>
   <si>
-    <t xml:space="preserve">9.05776882171631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.13847064971924</t>
+    <t xml:space="preserve">9.05776977539062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.13847160339355</t>
   </si>
   <si>
     <t xml:space="preserve">9.20380115509033</t>
@@ -3473,7 +3473,7 @@
     <t xml:space="preserve">9.16921424865723</t>
   </si>
   <si>
-    <t xml:space="preserve">9.25375938415527</t>
+    <t xml:space="preserve">9.25375843048096</t>
   </si>
   <si>
     <t xml:space="preserve">9.03086948394775</t>
@@ -3482,19 +3482,19 @@
     <t xml:space="preserve">9.09235668182373</t>
   </si>
   <si>
-    <t xml:space="preserve">9.15000057220459</t>
+    <t xml:space="preserve">9.14999961853027</t>
   </si>
   <si>
     <t xml:space="preserve">9.11157035827637</t>
   </si>
   <si>
-    <t xml:space="preserve">9.29603099822998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.24223041534424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.35751724243164</t>
+    <t xml:space="preserve">9.2960319519043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.24222946166992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.35751819610596</t>
   </si>
   <si>
     <t xml:space="preserve">9.36136054992676</t>
@@ -3503,10 +3503,10 @@
     <t xml:space="preserve">9.34598922729492</t>
   </si>
   <si>
-    <t xml:space="preserve">9.46896266937256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.50354766845703</t>
+    <t xml:space="preserve">9.46896171569824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.50354957580566</t>
   </si>
   <si>
     <t xml:space="preserve">9.60730743408203</t>
@@ -3515,34 +3515,34 @@
     <t xml:space="preserve">9.54966354370117</t>
   </si>
   <si>
-    <t xml:space="preserve">9.51891994476318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.4151611328125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.64958000183105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.61499500274658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.59577941894531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.74180889129639</t>
+    <t xml:space="preserve">9.51892185211182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.41516304016113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.64957904815674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.61499404907227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.59577751159668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.74181175231934</t>
   </si>
   <si>
     <t xml:space="preserve">9.65726566314697</t>
   </si>
   <si>
-    <t xml:space="preserve">9.64189529418945</t>
+    <t xml:space="preserve">9.64189434051514</t>
   </si>
   <si>
     <t xml:space="preserve">9.48433399200439</t>
   </si>
   <si>
-    <t xml:space="preserve">9.56503582000732</t>
+    <t xml:space="preserve">9.56503486633301</t>
   </si>
   <si>
     <t xml:space="preserve">9.53044891357422</t>
@@ -3551,31 +3551,31 @@
     <t xml:space="preserve">9.64573764801025</t>
   </si>
   <si>
-    <t xml:space="preserve">9.57656574249268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.6034631729126</t>
+    <t xml:space="preserve">9.57656383514404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.60346412658691</t>
   </si>
   <si>
     <t xml:space="preserve">9.56119251251221</t>
   </si>
   <si>
-    <t xml:space="preserve">9.46511936187744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.4113187789917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.42284774780273</t>
+    <t xml:space="preserve">9.46511840820312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.41131973266602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.42284870147705</t>
   </si>
   <si>
     <t xml:space="preserve">9.3344612121582</t>
   </si>
   <si>
-    <t xml:space="preserve">9.27297306060791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.25345993041992</t>
+    <t xml:space="preserve">9.27297210693359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.25345897674561</t>
   </si>
   <si>
     <t xml:space="preserve">9.17930698394775</t>
@@ -3587,40 +3587,40 @@
     <t xml:space="preserve">9.01539039611816</t>
   </si>
   <si>
-    <t xml:space="preserve">8.64462661743164</t>
+    <t xml:space="preserve">8.64462757110596</t>
   </si>
   <si>
     <t xml:space="preserve">8.73829460144043</t>
   </si>
   <si>
-    <t xml:space="preserve">8.6953649520874</t>
+    <t xml:space="preserve">8.69536399841309</t>
   </si>
   <si>
     <t xml:space="preserve">8.85927963256836</t>
   </si>
   <si>
-    <t xml:space="preserve">8.76561450958252</t>
+    <t xml:space="preserve">8.76561260223389</t>
   </si>
   <si>
     <t xml:space="preserve">8.69926738739014</t>
   </si>
   <si>
-    <t xml:space="preserve">8.73048877716064</t>
+    <t xml:space="preserve">8.73048973083496</t>
   </si>
   <si>
     <t xml:space="preserve">8.85147476196289</t>
   </si>
   <si>
-    <t xml:space="preserve">8.72658729553223</t>
+    <t xml:space="preserve">8.72658538818359</t>
   </si>
   <si>
     <t xml:space="preserve">8.66414165496826</t>
   </si>
   <si>
-    <t xml:space="preserve">8.62511444091797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.62901878356934</t>
+    <t xml:space="preserve">8.62511539459229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.6290168762207</t>
   </si>
   <si>
     <t xml:space="preserve">8.64853096008301</t>
@@ -3632,58 +3632,58 @@
     <t xml:space="preserve">8.75000190734863</t>
   </si>
   <si>
-    <t xml:space="preserve">8.76171112060547</t>
+    <t xml:space="preserve">8.76171016693115</t>
   </si>
   <si>
     <t xml:space="preserve">8.562668800354</t>
   </si>
   <si>
-    <t xml:space="preserve">8.70316886901855</t>
+    <t xml:space="preserve">8.70316982269287</t>
   </si>
   <si>
     <t xml:space="preserve">8.78903007507324</t>
   </si>
   <si>
-    <t xml:space="preserve">8.86708545684814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.94514083862305</t>
+    <t xml:space="preserve">8.86708450317383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.94514179229736</t>
   </si>
   <si>
     <t xml:space="preserve">9.01929378509521</t>
   </si>
   <si>
-    <t xml:space="preserve">8.99977970123291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.0075855255127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.13637638092041</t>
+    <t xml:space="preserve">8.99977874755859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.00758457183838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.13637733459473</t>
   </si>
   <si>
     <t xml:space="preserve">9.14808559417725</t>
   </si>
   <si>
-    <t xml:space="preserve">9.18320846557617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.1051549911499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.13247299194336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.15979194641113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.09735012054443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.05441761016846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.06222438812256</t>
+    <t xml:space="preserve">9.1832103729248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.10515403747559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.13247489929199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.15979290008545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.0973482131958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.05441856384277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.06222343444824</t>
   </si>
   <si>
     <t xml:space="preserve">9.02709865570068</t>
@@ -3695,31 +3695,31 @@
     <t xml:space="preserve">9.12076568603516</t>
   </si>
   <si>
-    <t xml:space="preserve">8.96465492248535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.60560131072998</t>
+    <t xml:space="preserve">8.96465396881104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.60559940338135</t>
   </si>
   <si>
     <t xml:space="preserve">8.81634998321533</t>
   </si>
   <si>
-    <t xml:space="preserve">9.01148891448975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.9022102355957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.31200218200684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.31980514526367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.50022602081299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.55486392974854</t>
+    <t xml:space="preserve">9.01148700714111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.90220928192139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.31199932098389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.31980609893799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.50022506713867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.55486297607422</t>
   </si>
   <si>
     <t xml:space="preserve">8.59389209747314</t>
@@ -3728,22 +3728,22 @@
     <t xml:space="preserve">8.42607307434082</t>
   </si>
   <si>
-    <t xml:space="preserve">8.58218479156494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.66023826599121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.69146060943604</t>
+    <t xml:space="preserve">8.58218288421631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.66023921966553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.69146156311035</t>
   </si>
   <si>
     <t xml:space="preserve">8.61340522766113</t>
   </si>
   <si>
-    <t xml:space="preserve">8.4026575088501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.37143421173096</t>
+    <t xml:space="preserve">8.40265655517578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.37143516540527</t>
   </si>
   <si>
     <t xml:space="preserve">8.30118465423584</t>
@@ -3755,19 +3755,19 @@
     <t xml:space="preserve">8.09433746337891</t>
   </si>
   <si>
-    <t xml:space="preserve">8.02018642425537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.69625473022461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.68376731872559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.57605123519897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.08742427825928</t>
+    <t xml:space="preserve">8.02018451690674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.69625425338745</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.68376684188843</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.5760498046875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.08742380142212</t>
   </si>
   <si>
     <t xml:space="preserve">6.93443584442139</t>
@@ -3776,31 +3776,31 @@
     <t xml:space="preserve">7.25602340698242</t>
   </si>
   <si>
-    <t xml:space="preserve">7.89919805526733</t>
+    <t xml:space="preserve">7.89919900894165</t>
   </si>
   <si>
     <t xml:space="preserve">7.49955654144287</t>
   </si>
   <si>
-    <t xml:space="preserve">7.54482793807983</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.74933433532715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.70718383789062</t>
+    <t xml:space="preserve">7.54482841491699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.74933385848999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.70718288421631</t>
   </si>
   <si>
     <t xml:space="preserve">8.05531024932861</t>
   </si>
   <si>
-    <t xml:space="preserve">7.88749074935913</t>
+    <t xml:space="preserve">7.88749027252197</t>
   </si>
   <si>
     <t xml:space="preserve">7.86407518386841</t>
   </si>
   <si>
-    <t xml:space="preserve">7.89529609680176</t>
+    <t xml:space="preserve">7.89529705047607</t>
   </si>
   <si>
     <t xml:space="preserve">8.10214424133301</t>
@@ -3809,13 +3809,13 @@
     <t xml:space="preserve">8.09043502807617</t>
   </si>
   <si>
-    <t xml:space="preserve">8.23483753204346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.12555980682373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.2192268371582</t>
+    <t xml:space="preserve">8.23483657836914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.12555885314941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.21922588348389</t>
   </si>
   <si>
     <t xml:space="preserve">8.28947639465332</t>
@@ -3824,46 +3824,46 @@
     <t xml:space="preserve">8.25435066223145</t>
   </si>
   <si>
-    <t xml:space="preserve">8.11775398254395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.99676752090454</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.82504653930664</t>
+    <t xml:space="preserve">8.11775493621826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.9967679977417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.82504558563232</t>
   </si>
   <si>
     <t xml:space="preserve">7.70562219619751</t>
   </si>
   <si>
-    <t xml:space="preserve">7.85626745223999</t>
+    <t xml:space="preserve">7.85626840591431</t>
   </si>
   <si>
     <t xml:space="preserve">7.79304456710815</t>
   </si>
   <si>
-    <t xml:space="preserve">7.67596054077148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.59790563583374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.65878868103027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.53546142578125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.73372220993042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.70874452590942</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.5729284286499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.35905694961548</t>
+    <t xml:space="preserve">7.67596006393433</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.5979061126709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.65879011154175</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.53546237945557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.73372268676758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.70874404907227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.57292795181274</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.35905742645264</t>
   </si>
   <si>
     <t xml:space="preserve">7.26070737838745</t>
@@ -3872,13 +3872,13 @@
     <t xml:space="preserve">7.23728942871094</t>
   </si>
   <si>
-    <t xml:space="preserve">7.28412294387817</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.32002925872803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.24665832519531</t>
+    <t xml:space="preserve">7.28412342071533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.32002878189087</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.246657371521</t>
   </si>
   <si>
     <t xml:space="preserve">7.18889617919922</t>
@@ -3887,76 +3887,76 @@
     <t xml:space="preserve">7.13269567489624</t>
   </si>
   <si>
-    <t xml:space="preserve">7.02654075622559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.84389066696167</t>
+    <t xml:space="preserve">7.02654027938843</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.84389162063599</t>
   </si>
   <si>
     <t xml:space="preserve">7.00624656677246</t>
   </si>
   <si>
-    <t xml:space="preserve">7.16860198974609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.39340162277222</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.54795026779175</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.44179534912109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.51204490661621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.46677255630493</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.44023418426514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.41837787628174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.563560962677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.43555068969727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.55887794494629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.61195516586304</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.7524561882019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.92261648178101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.82114410400391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.81724214553833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.74308776855469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.89139413833618</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.87578344345093</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.7665057182312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.1436243057251</t>
+    <t xml:space="preserve">7.16860151290894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.3934006690979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.54795074462891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.44179677963257</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.51204395294189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.46677160263062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.44023370742798</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.41837882995605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.56356048583984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.43555116653442</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.55887842178345</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.61195659637451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.75245475769043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.92261505126953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.82114362716675</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.81724119186401</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.74308967590332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.89139366149902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.87578392028809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.76650476455688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.14362335205078</t>
   </si>
   <si>
     <t xml:space="preserve">6.90477418899536</t>
@@ -3965,16 +3965,16 @@
     <t xml:space="preserve">7.11708545684814</t>
   </si>
   <si>
-    <t xml:space="preserve">7.35125064849854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.98595142364502</t>
+    <t xml:space="preserve">7.35125160217285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.98595285415649</t>
   </si>
   <si>
     <t xml:space="preserve">7.02185821533203</t>
   </si>
   <si>
-    <t xml:space="preserve">7.18777990341187</t>
+    <t xml:space="preserve">7.18777942657471</t>
   </si>
   <si>
     <t xml:space="preserve">7.12729597091675</t>
@@ -3983,40 +3983,40 @@
     <t xml:space="preserve">7.15998983383179</t>
   </si>
   <si>
-    <t xml:space="preserve">7.10441064834595</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.31201696395874</t>
+    <t xml:space="preserve">7.10440969467163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.3120174407959</t>
   </si>
   <si>
     <t xml:space="preserve">7.27605390548706</t>
   </si>
   <si>
-    <t xml:space="preserve">7.42154216766357</t>
+    <t xml:space="preserve">7.42154169082642</t>
   </si>
   <si>
     <t xml:space="preserve">7.36596202850342</t>
   </si>
   <si>
-    <t xml:space="preserve">7.28422737121582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.28749704360962</t>
+    <t xml:space="preserve">7.2842264175415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.2874960899353</t>
   </si>
   <si>
     <t xml:space="preserve">7.28095722198486</t>
   </si>
   <si>
-    <t xml:space="preserve">6.98834657669067</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.03248262405396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.21393394470215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.10114049911499</t>
+    <t xml:space="preserve">6.98834609985352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.03248310089111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.21393537521362</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.10113954544067</t>
   </si>
   <si>
     <t xml:space="preserve">6.96709537506104</t>
@@ -4037,19 +4037,19 @@
     <t xml:space="preserve">6.79381704330444</t>
   </si>
   <si>
-    <t xml:space="preserve">7.01940584182739</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.86410903930664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.52899551391602</t>
+    <t xml:space="preserve">7.01940536499023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.86410808563232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.52899503707886</t>
   </si>
   <si>
     <t xml:space="preserve">6.61563491821289</t>
   </si>
   <si>
-    <t xml:space="preserve">6.64342451095581</t>
+    <t xml:space="preserve">6.64342403411865</t>
   </si>
   <si>
     <t xml:space="preserve">6.62871122360229</t>
@@ -4058,70 +4058,70 @@
     <t xml:space="preserve">6.64015436172485</t>
   </si>
   <si>
-    <t xml:space="preserve">6.5845742225647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.67775297164917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.74314117431641</t>
+    <t xml:space="preserve">6.58457469940186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.67775249481201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.74314069747925</t>
   </si>
   <si>
     <t xml:space="preserve">6.66140604019165</t>
   </si>
   <si>
-    <t xml:space="preserve">6.77419996261597</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.85266637802124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.9294958114624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.8657431602478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.8281455039978</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.8690128326416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.97036409378052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.97690296173096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.918053150177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.82651138305664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.70227336883545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.53226470947266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.63198184967041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.59928703308105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.57803630828857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.42927837371826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.34754276275635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.4946665763855</t>
+    <t xml:space="preserve">6.77420043945312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.85266590118408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.92949724197388</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.86574268341064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.82814502716064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.86901330947876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.97036457061768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.97690391540527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.91805362701416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.82651090621948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.70227384567261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.5322642326355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.63198137283325</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.59928750991821</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.57803678512573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.42927885055542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.34754323959351</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.49466609954834</t>
   </si>
   <si>
     <t xml:space="preserve">6.44562530517578</t>
@@ -4130,7 +4130,7 @@
     <t xml:space="preserve">6.62053871154785</t>
   </si>
   <si>
-    <t xml:space="preserve">6.44889402389526</t>
+    <t xml:space="preserve">6.44889450073242</t>
   </si>
   <si>
     <t xml:space="preserve">6.52245616912842</t>
@@ -4139,10 +4139,10 @@
     <t xml:space="preserve">6.54043769836426</t>
   </si>
   <si>
-    <t xml:space="preserve">6.60909605026245</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.71044683456421</t>
+    <t xml:space="preserve">6.60909557342529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.71044778823853</t>
   </si>
   <si>
     <t xml:space="preserve">6.80035543441772</t>
@@ -4151,22 +4151,22 @@
     <t xml:space="preserve">6.81343364715576</t>
   </si>
   <si>
-    <t xml:space="preserve">6.86737871170044</t>
+    <t xml:space="preserve">6.86737775802612</t>
   </si>
   <si>
     <t xml:space="preserve">6.76112270355225</t>
   </si>
   <si>
-    <t xml:space="preserve">6.79054689407349</t>
+    <t xml:space="preserve">6.79054737091064</t>
   </si>
   <si>
     <t xml:space="preserve">6.64832782745361</t>
   </si>
   <si>
-    <t xml:space="preserve">6.64505863189697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.4537992477417</t>
+    <t xml:space="preserve">6.64505958557129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.45379877090454</t>
   </si>
   <si>
     <t xml:space="preserve">6.51918697357178</t>
@@ -4175,19 +4175,19 @@
     <t xml:space="preserve">6.38350677490234</t>
   </si>
   <si>
-    <t xml:space="preserve">6.3916802406311</t>
+    <t xml:space="preserve">6.39167976379395</t>
   </si>
   <si>
     <t xml:space="preserve">6.25926971435547</t>
   </si>
   <si>
-    <t xml:space="preserve">6.36715936660767</t>
+    <t xml:space="preserve">6.36715984344482</t>
   </si>
   <si>
     <t xml:space="preserve">6.49793577194214</t>
   </si>
   <si>
-    <t xml:space="preserve">6.68919515609741</t>
+    <t xml:space="preserve">6.68919563293457</t>
   </si>
   <si>
     <t xml:space="preserve">6.59274816513062</t>
@@ -4199,25 +4199,25 @@
     <t xml:space="preserve">6.39331436157227</t>
   </si>
   <si>
-    <t xml:space="preserve">6.40802669525146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.26090478897095</t>
+    <t xml:space="preserve">6.40802717208862</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.26090431213379</t>
   </si>
   <si>
     <t xml:space="preserve">6.36389017105103</t>
   </si>
   <si>
-    <t xml:space="preserve">6.46033811569214</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.62217283248901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.86247396469116</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.824875831604</t>
+    <t xml:space="preserve">6.46033763885498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.62217378616333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.86247444152832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.82487630844116</t>
   </si>
   <si>
     <t xml:space="preserve">6.80199003219604</t>
@@ -4229,34 +4229,34 @@
     <t xml:space="preserve">6.89189910888672</t>
   </si>
   <si>
-    <t xml:space="preserve">6.95565223693848</t>
+    <t xml:space="preserve">6.95565176010132</t>
   </si>
   <si>
     <t xml:space="preserve">7.02103996276855</t>
   </si>
   <si>
-    <t xml:space="preserve">7.22701215744019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.17143297195435</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.20903062820435</t>
+    <t xml:space="preserve">7.22701263427734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.17143201828003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.20903015136719</t>
   </si>
   <si>
     <t xml:space="preserve">7.23028135299683</t>
   </si>
   <si>
-    <t xml:space="preserve">7.19268465042114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.14854764938354</t>
+    <t xml:space="preserve">7.19268369674683</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.14854621887207</t>
   </si>
   <si>
     <t xml:space="preserve">7.37740421295166</t>
   </si>
   <si>
-    <t xml:space="preserve">7.50327682495117</t>
+    <t xml:space="preserve">7.50327587127686</t>
   </si>
   <si>
     <t xml:space="preserve">7.54904842376709</t>
@@ -4268,52 +4268,52 @@
     <t xml:space="preserve">7.97243595123291</t>
   </si>
   <si>
-    <t xml:space="preserve">7.87762355804443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.93156814575195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.96099233627319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.86618041992188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.81223392486572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.84983396530151</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.81473827362061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.77796983718872</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.85819005966187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.75624322891235</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.89328622817993</t>
+    <t xml:space="preserve">7.87762260437012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.93156957626343</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.96099185943604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.8661789894104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.8122353553772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.84983348846436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.81473779678345</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.77796936035156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.85818958282471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.75624370574951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.89328575134277</t>
   </si>
   <si>
     <t xml:space="preserve">7.80303907394409</t>
   </si>
   <si>
-    <t xml:space="preserve">7.87323045730591</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.84314775466919</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.89662742614746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.87657308578491</t>
+    <t xml:space="preserve">7.87323188781738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.84314870834351</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.89662790298462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.87657260894775</t>
   </si>
   <si>
     <t xml:space="preserve">7.80972337722778</t>
@@ -4322,10 +4322,10 @@
     <t xml:space="preserve">7.90498399734497</t>
   </si>
   <si>
-    <t xml:space="preserve">7.76292896270752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.834792137146</t>
+    <t xml:space="preserve">7.76292848587036</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.83479261398315</t>
   </si>
   <si>
     <t xml:space="preserve">7.8364634513855</t>
@@ -4337,49 +4337,49 @@
     <t xml:space="preserve">7.93339586257935</t>
   </si>
   <si>
-    <t xml:space="preserve">7.51892805099487</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.56070899963379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.56739377975464</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.69774961471558</t>
+    <t xml:space="preserve">7.51892709732056</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.56070804595947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.56739330291748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.69774913787842</t>
   </si>
   <si>
     <t xml:space="preserve">7.76125812530518</t>
   </si>
   <si>
-    <t xml:space="preserve">7.69607925415039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.70443630218506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.7144627571106</t>
+    <t xml:space="preserve">7.69607877731323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.70443534851074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.71446323394775</t>
   </si>
   <si>
     <t xml:space="preserve">7.64427042007446</t>
   </si>
   <si>
-    <t xml:space="preserve">7.72950410842896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.6258864402771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.86487436294556</t>
+    <t xml:space="preserve">7.72950315475464</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.62588691711426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.86487483978271</t>
   </si>
   <si>
     <t xml:space="preserve">8.06041049957275</t>
   </si>
   <si>
-    <t xml:space="preserve">7.94843578338623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.02698612213135</t>
+    <t xml:space="preserve">7.94843721389771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.02698516845703</t>
   </si>
   <si>
     <t xml:space="preserve">8.01194477081299</t>
@@ -4388,49 +4388,49 @@
     <t xml:space="preserve">8.10553359985352</t>
   </si>
   <si>
-    <t xml:space="preserve">8.03534126281738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.10887622833252</t>
+    <t xml:space="preserve">8.0353422164917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.10887718200684</t>
   </si>
   <si>
     <t xml:space="preserve">8.13060188293457</t>
   </si>
   <si>
-    <t xml:space="preserve">8.17572593688965</t>
+    <t xml:space="preserve">8.17572689056396</t>
   </si>
   <si>
     <t xml:space="preserve">8.12391757965088</t>
   </si>
   <si>
-    <t xml:space="preserve">8.16068458557129</t>
+    <t xml:space="preserve">8.16068363189697</t>
   </si>
   <si>
     <t xml:space="preserve">7.98186206817627</t>
   </si>
   <si>
-    <t xml:space="preserve">8.00693130493164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.04536914825439</t>
+    <t xml:space="preserve">8.00693035125732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.04537010192871</t>
   </si>
   <si>
     <t xml:space="preserve">8.05372524261475</t>
   </si>
   <si>
-    <t xml:space="preserve">8.16904163360596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.14230251312256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.17739677429199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.20246505737305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.51498889923096</t>
+    <t xml:space="preserve">8.16904067993164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.14230060577393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.17739772796631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.20246601104736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.51498794555664</t>
   </si>
   <si>
     <t xml:space="preserve">8.42306995391846</t>
@@ -4439,13 +4439,13 @@
     <t xml:space="preserve">8.43142604827881</t>
   </si>
   <si>
-    <t xml:space="preserve">8.43978309631348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.57348346710205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.3980016708374</t>
+    <t xml:space="preserve">8.43978214263916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.57348251342773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.39800262451172</t>
   </si>
   <si>
     <t xml:space="preserve">8.51916694641113</t>
@@ -4475,7 +4475,7 @@
     <t xml:space="preserve">8.52334499359131</t>
   </si>
   <si>
-    <t xml:space="preserve">8.39382266998291</t>
+    <t xml:space="preserve">8.39382362365723</t>
   </si>
   <si>
     <t xml:space="preserve">8.38964462280273</t>
@@ -4484,43 +4484,43 @@
     <t xml:space="preserve">8.46485137939453</t>
   </si>
   <si>
-    <t xml:space="preserve">8.61944198608398</t>
+    <t xml:space="preserve">8.61944103240967</t>
   </si>
   <si>
     <t xml:space="preserve">8.56512546539307</t>
   </si>
   <si>
-    <t xml:space="preserve">8.54005718231201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.48156356811523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.34619331359863</t>
+    <t xml:space="preserve">8.54005908966064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.48156261444092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.34619426727295</t>
   </si>
   <si>
     <t xml:space="preserve">8.00860118865967</t>
   </si>
   <si>
-    <t xml:space="preserve">8.13561630249023</t>
+    <t xml:space="preserve">8.13561534881592</t>
   </si>
   <si>
     <t xml:space="preserve">7.74287366867065</t>
   </si>
   <si>
-    <t xml:space="preserve">7.53062629699707</t>
+    <t xml:space="preserve">7.53062582015991</t>
   </si>
   <si>
     <t xml:space="preserve">7.60917472839355</t>
   </si>
   <si>
-    <t xml:space="preserve">7.86821746826172</t>
+    <t xml:space="preserve">7.86821794509888</t>
   </si>
   <si>
     <t xml:space="preserve">7.81640863418579</t>
   </si>
   <si>
-    <t xml:space="preserve">7.83144903182983</t>
+    <t xml:space="preserve">7.83144950866699</t>
   </si>
   <si>
     <t xml:space="preserve">7.68438005447388</t>
@@ -4529,85 +4529,85 @@
     <t xml:space="preserve">7.82476568222046</t>
   </si>
   <si>
-    <t xml:space="preserve">7.95010757446289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.86320352554321</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.79301071166992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.63257122039795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.72281932830811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.81306743621826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.84648990631104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.97517585754395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.8548469543457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.90832710266113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.99188947677612</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.91334199905396</t>
+    <t xml:space="preserve">7.95010805130005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.8632025718689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.7930121421814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.63257265090942</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.72281885147095</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.81306648254395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.84649181365967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.9751763343811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.85484790802002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.90832614898682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.99188899993896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.91334009170532</t>
   </si>
   <si>
     <t xml:space="preserve">8.00525856018066</t>
   </si>
   <si>
-    <t xml:space="preserve">7.92838287353516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.86988878250122</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.95846509933472</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.68939447402954</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.75791597366333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.67268228530884</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.91835451126099</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.95679378509521</t>
+    <t xml:space="preserve">7.92838096618652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.86988973617554</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.9584641456604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.68939352035522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.75791501998901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.67268133163452</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.91835403442383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.9567928314209</t>
   </si>
   <si>
     <t xml:space="preserve">8.04035568237305</t>
   </si>
   <si>
-    <t xml:space="preserve">7.94175148010254</t>
+    <t xml:space="preserve">7.94175100326538</t>
   </si>
   <si>
     <t xml:space="preserve">8.02531433105469</t>
   </si>
   <si>
-    <t xml:space="preserve">8.09717655181885</t>
+    <t xml:space="preserve">8.09717750549316</t>
   </si>
   <si>
     <t xml:space="preserve">8.04703998565674</t>
   </si>
   <si>
-    <t xml:space="preserve">8.0955057144165</t>
+    <t xml:space="preserve">8.09550762176514</t>
   </si>
   <si>
     <t xml:space="preserve">8.06876659393311</t>
@@ -4616,46 +4616,46 @@
     <t xml:space="preserve">8.29772758483887</t>
   </si>
   <si>
-    <t xml:space="preserve">8.27432918548584</t>
+    <t xml:space="preserve">8.27433013916016</t>
   </si>
   <si>
     <t xml:space="preserve">8.08715057373047</t>
   </si>
   <si>
-    <t xml:space="preserve">8.18575286865234</t>
+    <t xml:space="preserve">8.18575382232666</t>
   </si>
   <si>
     <t xml:space="preserve">8.16402721405029</t>
   </si>
   <si>
-    <t xml:space="preserve">8.10219097137451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.15567207336426</t>
+    <t xml:space="preserve">8.10219192504883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.15567111968994</t>
   </si>
   <si>
     <t xml:space="preserve">8.35622024536133</t>
   </si>
   <si>
-    <t xml:space="preserve">8.27767276763916</t>
+    <t xml:space="preserve">8.27767181396484</t>
   </si>
   <si>
     <t xml:space="preserve">8.30775451660156</t>
   </si>
   <si>
-    <t xml:space="preserve">8.33616542816162</t>
+    <t xml:space="preserve">8.33616638183594</t>
   </si>
   <si>
     <t xml:space="preserve">8.2760009765625</t>
   </si>
   <si>
-    <t xml:space="preserve">8.34786415100098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.37293338775635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.43560409545898</t>
+    <t xml:space="preserve">8.34786510467529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.37293243408203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.4356050491333</t>
   </si>
   <si>
     <t xml:space="preserve">8.41053485870361</t>
@@ -4667,13 +4667,13 @@
     <t xml:space="preserve">8.34443187713623</t>
   </si>
   <si>
-    <t xml:space="preserve">8.3164701461792</t>
+    <t xml:space="preserve">8.31647109985352</t>
   </si>
   <si>
     <t xml:space="preserve">8.28326797485352</t>
   </si>
   <si>
-    <t xml:space="preserve">8.31996726989746</t>
+    <t xml:space="preserve">8.31996631622314</t>
   </si>
   <si>
     <t xml:space="preserve">8.29200649261475</t>
@@ -4682,34 +4682,34 @@
     <t xml:space="preserve">8.49471855163574</t>
   </si>
   <si>
-    <t xml:space="preserve">8.59782314300537</t>
+    <t xml:space="preserve">8.59782218933105</t>
   </si>
   <si>
     <t xml:space="preserve">8.61180305480957</t>
   </si>
   <si>
-    <t xml:space="preserve">8.66422843933105</t>
+    <t xml:space="preserve">8.66422939300537</t>
   </si>
   <si>
     <t xml:space="preserve">8.63976287841797</t>
   </si>
   <si>
-    <t xml:space="preserve">8.63277339935303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.59957027435303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.47374820709229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.53840732574463</t>
+    <t xml:space="preserve">8.63277435302734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.59957122802734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.4737491607666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.53840637207031</t>
   </si>
   <si>
     <t xml:space="preserve">8.54714393615723</t>
   </si>
   <si>
-    <t xml:space="preserve">8.58034610748291</t>
+    <t xml:space="preserve">8.58034801483154</t>
   </si>
   <si>
     <t xml:space="preserve">8.71141242980957</t>
@@ -4718,10 +4718,10 @@
     <t xml:space="preserve">8.6956844329834</t>
   </si>
   <si>
-    <t xml:space="preserve">8.6817045211792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.6851978302002</t>
+    <t xml:space="preserve">8.68170356750488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.68519878387451</t>
   </si>
   <si>
     <t xml:space="preserve">8.70966529846191</t>
@@ -4733,13 +4733,13 @@
     <t xml:space="preserve">8.83373832702637</t>
   </si>
   <si>
-    <t xml:space="preserve">8.93858909606934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.03033542633057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.00412178039551</t>
+    <t xml:space="preserve">8.93859004974365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.03033447265625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.00412273406982</t>
   </si>
   <si>
     <t xml:space="preserve">9.09586715698242</t>
@@ -4748,19 +4748,19 @@
     <t xml:space="preserve">9.08276176452637</t>
   </si>
   <si>
-    <t xml:space="preserve">8.98664665222168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.79004955291748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.78568267822266</t>
+    <t xml:space="preserve">8.98664569854736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.7900505065918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.78568077087402</t>
   </si>
   <si>
     <t xml:space="preserve">8.80315685272217</t>
   </si>
   <si>
-    <t xml:space="preserve">8.67995548248291</t>
+    <t xml:space="preserve">8.67995643615723</t>
   </si>
   <si>
     <t xml:space="preserve">8.81626319885254</t>
@@ -4769,19 +4769,19 @@
     <t xml:space="preserve">8.88616466522217</t>
   </si>
   <si>
-    <t xml:space="preserve">8.85558319091797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.87742614746094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.77257537841797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.737624168396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.75510120391846</t>
+    <t xml:space="preserve">8.85558414459229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.87742710113525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.77257442474365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.73762512207031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.75509929656982</t>
   </si>
   <si>
     <t xml:space="preserve">8.7813138961792</t>
@@ -4793,28 +4793,28 @@
     <t xml:space="preserve">8.82063293457031</t>
   </si>
   <si>
-    <t xml:space="preserve">8.94732666015625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.02159786224365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.96043395996094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.9342212677002</t>
+    <t xml:space="preserve">8.94732761383057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.02159690856934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.96043491363525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.93422222137451</t>
   </si>
   <si>
     <t xml:space="preserve">8.87305736541748</t>
   </si>
   <si>
-    <t xml:space="preserve">8.79878807067871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.99538516998291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.89490127563477</t>
+    <t xml:space="preserve">8.79878711700439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.99538421630859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.8949031829834</t>
   </si>
   <si>
     <t xml:space="preserve">8.84247589111328</t>
@@ -4823,10 +4823,10 @@
     <t xml:space="preserve">8.83810710906982</t>
   </si>
   <si>
-    <t xml:space="preserve">8.92985248565674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.81189441680908</t>
+    <t xml:space="preserve">8.92985343933105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.8118953704834</t>
   </si>
   <si>
     <t xml:space="preserve">8.75073146820068</t>
@@ -4835,10 +4835,10 @@
     <t xml:space="preserve">8.67296600341797</t>
   </si>
   <si>
-    <t xml:space="preserve">8.62053966522217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.45452499389648</t>
+    <t xml:space="preserve">8.62054061889648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.4545259475708</t>
   </si>
   <si>
     <t xml:space="preserve">8.36015892028809</t>
@@ -4853,7 +4853,7 @@
     <t xml:space="preserve">8.33744144439697</t>
   </si>
   <si>
-    <t xml:space="preserve">8.5296688079834</t>
+    <t xml:space="preserve">8.52966976165771</t>
   </si>
   <si>
     <t xml:space="preserve">8.59257984161377</t>
@@ -4862,10 +4862,10 @@
     <t xml:space="preserve">8.51743698120117</t>
   </si>
   <si>
-    <t xml:space="preserve">8.62578201293945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.6485013961792</t>
+    <t xml:space="preserve">8.62578296661377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.64850044250488</t>
   </si>
   <si>
     <t xml:space="preserve">8.46326351165771</t>
@@ -4880,13 +4880,13 @@
     <t xml:space="preserve">8.01240253448486</t>
   </si>
   <si>
-    <t xml:space="preserve">7.95123863220215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.06482791900635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.98793649673462</t>
+    <t xml:space="preserve">7.95123958587646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.06482696533203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.98793697357178</t>
   </si>
   <si>
     <t xml:space="preserve">8.03686714172363</t>
@@ -4901,10 +4901,10 @@
     <t xml:space="preserve">8.24307632446289</t>
   </si>
   <si>
-    <t xml:space="preserve">8.3269567489624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.37239265441895</t>
+    <t xml:space="preserve">8.32695579528809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.37239170074463</t>
   </si>
   <si>
     <t xml:space="preserve">8.63452053070068</t>
@@ -4913,13 +4913,13 @@
     <t xml:space="preserve">8.73587703704834</t>
   </si>
   <si>
-    <t xml:space="preserve">8.76383781433105</t>
+    <t xml:space="preserve">8.76383686065674</t>
   </si>
   <si>
     <t xml:space="preserve">8.919264793396</t>
   </si>
   <si>
-    <t xml:space="preserve">8.83874988555908</t>
+    <t xml:space="preserve">8.8387508392334</t>
   </si>
   <si>
     <t xml:space="preserve">8.79401969909668</t>
@@ -4934,10 +4934,10 @@
     <t xml:space="preserve">8.73318576812744</t>
   </si>
   <si>
-    <t xml:space="preserve">8.7922306060791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.77970504760742</t>
+    <t xml:space="preserve">8.79222965240479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.77970600128174</t>
   </si>
   <si>
     <t xml:space="preserve">8.83517169952393</t>
@@ -4946,16 +4946,16 @@
     <t xml:space="preserve">8.87453460693359</t>
   </si>
   <si>
-    <t xml:space="preserve">8.89600467681885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.91568565368652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.95952320098877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.92284393310547</t>
+    <t xml:space="preserve">8.89600563049316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.91568660736084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.95952224731445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.92284297943115</t>
   </si>
   <si>
     <t xml:space="preserve">8.97741413116455</t>
@@ -4973,16 +4973,16 @@
     <t xml:space="preserve">9.1473913192749</t>
   </si>
   <si>
-    <t xml:space="preserve">9.12502574920654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.10713291168213</t>
+    <t xml:space="preserve">9.12502479553223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.10713386535645</t>
   </si>
   <si>
     <t xml:space="preserve">9.19212055206299</t>
   </si>
   <si>
-    <t xml:space="preserve">9.15186214447021</t>
+    <t xml:space="preserve">9.15186309814453</t>
   </si>
   <si>
     <t xml:space="preserve">9.1831750869751</t>
@@ -4997,16 +4997,16 @@
     <t xml:space="preserve">9.27710819244385</t>
   </si>
   <si>
-    <t xml:space="preserve">9.11160564422607</t>
+    <t xml:space="preserve">9.11160659790039</t>
   </si>
   <si>
     <t xml:space="preserve">9.20553970336914</t>
   </si>
   <si>
-    <t xml:space="preserve">9.18764877319336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.12949752807617</t>
+    <t xml:space="preserve">9.18764781951904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.12949848175049</t>
   </si>
   <si>
     <t xml:space="preserve">9.03109169006348</t>
@@ -5015,7 +5015,7 @@
     <t xml:space="preserve">9.07582187652588</t>
   </si>
   <si>
-    <t xml:space="preserve">9.08029460906982</t>
+    <t xml:space="preserve">9.08029365539551</t>
   </si>
   <si>
     <t xml:space="preserve">9.04898262023926</t>
@@ -5027,19 +5027,19 @@
     <t xml:space="preserve">9.08476734161377</t>
   </si>
   <si>
-    <t xml:space="preserve">9.04003715515137</t>
+    <t xml:space="preserve">9.04003620147705</t>
   </si>
   <si>
     <t xml:space="preserve">9.1384449005127</t>
   </si>
   <si>
-    <t xml:space="preserve">9.22343158721924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.2279052734375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.99530696868896</t>
+    <t xml:space="preserve">9.22343254089355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.22790431976318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.99530601501465</t>
   </si>
   <si>
     <t xml:space="preserve">8.94252490997314</t>
@@ -5048,13 +5048,13 @@
     <t xml:space="preserve">9.00425148010254</t>
   </si>
   <si>
-    <t xml:space="preserve">9.00872611999512</t>
+    <t xml:space="preserve">9.0087251663208</t>
   </si>
   <si>
     <t xml:space="preserve">9.02661800384521</t>
   </si>
   <si>
-    <t xml:space="preserve">8.88705825805664</t>
+    <t xml:space="preserve">8.88705921173096</t>
   </si>
   <si>
     <t xml:space="preserve">8.82264709472656</t>
@@ -5063,7 +5063,7 @@
     <t xml:space="preserve">8.76002407073975</t>
   </si>
   <si>
-    <t xml:space="preserve">8.81906795501709</t>
+    <t xml:space="preserve">8.81906890869141</t>
   </si>
   <si>
     <t xml:space="preserve">8.9013729095459</t>
@@ -5072,7 +5072,7 @@
     <t xml:space="preserve">9.03556442260742</t>
   </si>
   <si>
-    <t xml:space="preserve">9.044508934021</t>
+    <t xml:space="preserve">9.04450988769531</t>
   </si>
   <si>
     <t xml:space="preserve">9.10266017913818</t>
@@ -5090,16 +5090,16 @@
     <t xml:space="preserve">9.69757556915283</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0956783294678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0330543518066</t>
+    <t xml:space="preserve">10.0956773757935</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.033055305481</t>
   </si>
   <si>
     <t xml:space="preserve">10.1896114349365</t>
   </si>
   <si>
-    <t xml:space="preserve">10.252233505249</t>
+    <t xml:space="preserve">10.2522344589233</t>
   </si>
   <si>
     <t xml:space="preserve">10.2924919128418</t>
@@ -5117,7 +5117,7 @@
     <t xml:space="preserve">10.4758863449097</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4848337173462</t>
+    <t xml:space="preserve">10.4848327636719</t>
   </si>
   <si>
     <t xml:space="preserve">10.5385093688965</t>
@@ -5132,7 +5132,7 @@
     <t xml:space="preserve">10.2835454940796</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2343416213989</t>
+    <t xml:space="preserve">10.2343406677246</t>
   </si>
   <si>
     <t xml:space="preserve">10.2477607727051</t>
@@ -5141,19 +5141,19 @@
     <t xml:space="preserve">10.3372230529785</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3461675643921</t>
+    <t xml:space="preserve">10.3461685180664</t>
   </si>
   <si>
     <t xml:space="preserve">10.3819532394409</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3148574829102</t>
+    <t xml:space="preserve">10.3148565292358</t>
   </si>
   <si>
     <t xml:space="preserve">10.4356288909912</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3059110641479</t>
+    <t xml:space="preserve">10.3059120178223</t>
   </si>
   <si>
     <t xml:space="preserve">10.4535217285156</t>
@@ -5168,7 +5168,7 @@
     <t xml:space="preserve">10.3551139831543</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4311561584473</t>
+    <t xml:space="preserve">10.4311552047729</t>
   </si>
   <si>
     <t xml:space="preserve">10.2880182266235</t>
@@ -5177,16 +5177,16 @@
     <t xml:space="preserve">10.2745990753174</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4266834259033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4222106933594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4937791824341</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6682281494141</t>
+    <t xml:space="preserve">10.426682472229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4222097396851</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4937782287598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6682271957397</t>
   </si>
   <si>
     <t xml:space="preserve">10.5519285202026</t>
@@ -5198,7 +5198,7 @@
     <t xml:space="preserve">10.6861200332642</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6637554168701</t>
+    <t xml:space="preserve">10.6637544631958</t>
   </si>
   <si>
     <t xml:space="preserve">10.6548089981079</t>
@@ -5213,7 +5213,7 @@
     <t xml:space="preserve">11.0171251296997</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9723958969116</t>
+    <t xml:space="preserve">10.9723949432373</t>
   </si>
   <si>
     <t xml:space="preserve">11.0081796646118</t>
@@ -5222,7 +5222,7 @@
     <t xml:space="preserve">10.9992341995239</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2273588180542</t>
+    <t xml:space="preserve">11.2273597717285</t>
   </si>
   <si>
     <t xml:space="preserve">11.0797491073608</t>
@@ -5234,13 +5234,13 @@
     <t xml:space="preserve">11.0618562698364</t>
   </si>
   <si>
-    <t xml:space="preserve">11.120005607605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0350189208984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1110591888428</t>
+    <t xml:space="preserve">11.1200075149536</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0350179672241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1110601425171</t>
   </si>
   <si>
     <t xml:space="preserve">11.2989282608032</t>
@@ -5249,46 +5249,46 @@
     <t xml:space="preserve">11.2810354232788</t>
   </si>
   <si>
-    <t xml:space="preserve">11.263144493103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2094669342041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2720899581909</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5091609954834</t>
+    <t xml:space="preserve">11.2631435394287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2094659805298</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2720909118652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5091619491577</t>
   </si>
   <si>
     <t xml:space="preserve">11.4420652389526</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5896768569946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4465379714966</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4107551574707</t>
+    <t xml:space="preserve">11.5896759033203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4465389251709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4107542037964</t>
   </si>
   <si>
     <t xml:space="preserve">11.2497243881226</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0842227935791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8918800354004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.115532875061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2899808883667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2407789230347</t>
+    <t xml:space="preserve">11.0842218399048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8918809890747</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1155338287354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.289981842041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2407779693604</t>
   </si>
   <si>
     <t xml:space="preserve">11.2716856002808</t>
@@ -5297,16 +5297,16 @@
     <t xml:space="preserve">11.3185148239136</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1873931884766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2482719421387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1405649185181</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4543180465698</t>
+    <t xml:space="preserve">11.1873941421509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2482709884644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1405658721924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4543170928955</t>
   </si>
   <si>
     <t xml:space="preserve">11.3091487884521</t>
@@ -5321,10 +5321,10 @@
     <t xml:space="preserve">11.2295398712158</t>
   </si>
   <si>
-    <t xml:space="preserve">11.327880859375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2342233657837</t>
+    <t xml:space="preserve">11.3278799057007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2342224121094</t>
   </si>
   <si>
     <t xml:space="preserve">11.3512945175171</t>
@@ -5333,10 +5333,10 @@
     <t xml:space="preserve">11.4683666229248</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3887567520142</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3372459411621</t>
+    <t xml:space="preserve">11.3887577056885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3372449874878</t>
   </si>
   <si>
     <t xml:space="preserve">11.4449520111084</t>
@@ -5345,22 +5345,22 @@
     <t xml:space="preserve">11.5432920455933</t>
   </si>
   <si>
-    <t xml:space="preserve">11.435585975647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3981227874756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3559770584106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8804597854614</t>
+    <t xml:space="preserve">11.4355869293213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3981237411499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.355978012085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8804607391357</t>
   </si>
   <si>
     <t xml:space="preserve">11.7212429046631</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3606605529785</t>
+    <t xml:space="preserve">11.3606595993042</t>
   </si>
   <si>
     <t xml:space="preserve">11.0843706130981</t>
@@ -5384,7 +5384,7 @@
     <t xml:space="preserve">11.1358823776245</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1499300003052</t>
+    <t xml:space="preserve">11.1499309539795</t>
   </si>
   <si>
     <t xml:space="preserve">11.2951002120972</t>
@@ -5399,13 +5399,13 @@
     <t xml:space="preserve">11.5011463165283</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5854377746582</t>
+    <t xml:space="preserve">11.5854387283325</t>
   </si>
   <si>
     <t xml:space="preserve">11.618218421936</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7025108337402</t>
+    <t xml:space="preserve">11.7025098800659</t>
   </si>
   <si>
     <t xml:space="preserve">11.6978273391724</t>
@@ -5414,7 +5414,7 @@
     <t xml:space="preserve">11.6697301864624</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7306079864502</t>
+    <t xml:space="preserve">11.7306070327759</t>
   </si>
   <si>
     <t xml:space="preserve">11.7446565628052</t>
@@ -5429,16 +5429,16 @@
     <t xml:space="preserve">11.5713891983032</t>
   </si>
   <si>
-    <t xml:space="preserve">11.524561882019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.566707611084</t>
+    <t xml:space="preserve">11.5245609283447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5667066574097</t>
   </si>
   <si>
     <t xml:space="preserve">11.5105123519897</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6837787628174</t>
+    <t xml:space="preserve">11.6837797164917</t>
   </si>
   <si>
     <t xml:space="preserve">11.660364151001</t>
@@ -5453,7 +5453,7 @@
     <t xml:space="preserve">11.8242654800415</t>
   </si>
   <si>
-    <t xml:space="preserve">11.87109375</t>
+    <t xml:space="preserve">11.8710947036743</t>
   </si>
   <si>
     <t xml:space="preserve">11.8664112091064</t>
@@ -5483,7 +5483,7 @@
     <t xml:space="preserve">11.6229009628296</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7259254455566</t>
+    <t xml:space="preserve">11.7259244918823</t>
   </si>
   <si>
     <t xml:space="preserve">11.7868022918701</t>
@@ -5498,25 +5498,25 @@
     <t xml:space="preserve">11.9179229736328</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0068969726562</t>
+    <t xml:space="preserve">12.0068979263306</t>
   </si>
   <si>
     <t xml:space="preserve">12.095871925354</t>
   </si>
   <si>
-    <t xml:space="preserve">12.109920501709</t>
+    <t xml:space="preserve">12.1099214553833</t>
   </si>
   <si>
     <t xml:space="preserve">12.1614322662354</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5266962051392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5641593933105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4845504760742</t>
+    <t xml:space="preserve">12.5266971588135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5641603469849</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4845514297485</t>
   </si>
   <si>
     <t xml:space="preserve">12.3908929824829</t>
@@ -5528,7 +5528,7 @@
     <t xml:space="preserve">12.306601524353</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2176275253296</t>
+    <t xml:space="preserve">12.2176265716553</t>
   </si>
   <si>
     <t xml:space="preserve">12.3440647125244</t>
@@ -5540,7 +5540,7 @@
     <t xml:space="preserve">12.1661157608032</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1192855834961</t>
+    <t xml:space="preserve">12.1192865371704</t>
   </si>
   <si>
     <t xml:space="preserve">12.2035779953003</t>
@@ -5549,10 +5549,10 @@
     <t xml:space="preserve">12.1473836898804</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3581123352051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4564542770386</t>
+    <t xml:space="preserve">12.3581132888794</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4564533233643</t>
   </si>
   <si>
     <t xml:space="preserve">12.4470882415771</t>
@@ -71914,7 +71914,7 @@
     </row>
     <row r="2513">
       <c r="A2513" s="1" t="n">
-        <v>45978.6911921296</v>
+        <v>45978.3333333333</v>
       </c>
       <c r="B2513" t="n">
         <v>1897283</v>
@@ -71935,6 +71935,32 @@
         <v>2083</v>
       </c>
       <c r="H2513" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2514">
+      <c r="A2514" s="1" t="n">
+        <v>45979.6914467593</v>
+      </c>
+      <c r="B2514" t="n">
+        <v>2564480</v>
+      </c>
+      <c r="C2514" t="n">
+        <v>21.0200004577637</v>
+      </c>
+      <c r="D2514" t="n">
+        <v>20.7299995422363</v>
+      </c>
+      <c r="E2514" t="n">
+        <v>20.9599990844727</v>
+      </c>
+      <c r="F2514" t="n">
+        <v>20.8899993896484</v>
+      </c>
+      <c r="G2514" t="s">
+        <v>2073</v>
+      </c>
+      <c r="H2514" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/PST.MI.xlsx
+++ b/data/PST.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2093" uniqueCount="2093">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2094" uniqueCount="2094">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -44,70 +44,70 @@
     <t xml:space="preserve">PST.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">3.95891857147217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.89843463897705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87644052505493</t>
+    <t xml:space="preserve">3.95891880989075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89843511581421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87643980979919</t>
   </si>
   <si>
     <t xml:space="preserve">3.84070062637329</t>
   </si>
   <si>
-    <t xml:space="preserve">3.80496048927307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.89568519592285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94242310523987</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92042922973633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87094140052795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.75547385215759</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.68399286270142</t>
+    <t xml:space="preserve">3.80495953559875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89568591117859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94242262840271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92042827606201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87094235420227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.75547313690186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.68399310112</t>
   </si>
   <si>
     <t xml:space="preserve">3.48054885864258</t>
   </si>
   <si>
-    <t xml:space="preserve">3.61526203155518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66199922561646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.58502006530762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.68949174880981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73622965812683</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.65925002098083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.75272536277771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.65100169181824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.57402348518372</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.46405434608459</t>
+    <t xml:space="preserve">3.61526226997375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66199970245361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.58501935005188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.68949151039124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73622918128967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.65924978256226</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.75272417068481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.6510021686554</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.57402300834656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.46405363082886</t>
   </si>
   <si>
     <t xml:space="preserve">3.29085063934326</t>
@@ -116,31 +116,31 @@
     <t xml:space="preserve">2.94719481468201</t>
   </si>
   <si>
-    <t xml:space="preserve">2.84272336959839</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.10940003395081</t>
+    <t xml:space="preserve">2.84272313117981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.10940051078796</t>
   </si>
   <si>
     <t xml:space="preserve">2.97468686103821</t>
   </si>
   <si>
-    <t xml:space="preserve">2.98568391799927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.07640981674194</t>
+    <t xml:space="preserve">2.98568439483643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.07640933990479</t>
   </si>
   <si>
     <t xml:space="preserve">3.06266283988953</t>
   </si>
   <si>
-    <t xml:space="preserve">3.18637919425964</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.17263293266296</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.24136471748352</t>
+    <t xml:space="preserve">3.18637895584106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.17263269424438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.2413637638092</t>
   </si>
   <si>
     <t xml:space="preserve">3.35683274269104</t>
@@ -149,484 +149,484 @@
     <t xml:space="preserve">3.28260278701782</t>
   </si>
   <si>
-    <t xml:space="preserve">3.24961185455322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.34308648109436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.38982343673706</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.4475576877594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.41731595993042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.38707423210144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.40906810760498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.37057828903198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.39257264137268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.36782956123352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.543781042099</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.5685248374939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.56577587127686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.5382833480835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.51903772354126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.53278517723083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.60151600837708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.72248315811157</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.70598673820496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64275503158569</t>
+    <t xml:space="preserve">3.24961256980896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.34308552742004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.3898241519928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.44755792617798</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.41731667518616</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.38707494735718</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.4090678691864</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.37057876586914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.39257287979126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.3678286075592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.54378128051758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.56852459907532</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.56577610969543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.53828263282776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.519038438797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.53278470039368</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.60151529312134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.72248339653015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.70598697662354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64275527000427</t>
   </si>
   <si>
     <t xml:space="preserve">3.71148490905762</t>
   </si>
   <si>
-    <t xml:space="preserve">3.65650081634521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.60701370239258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.54653072357178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.44480919837952</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.4997935295105</t>
+    <t xml:space="preserve">3.65650105476379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.60701441764832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.5465304851532</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.44480872154236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.49979305267334</t>
   </si>
   <si>
     <t xml:space="preserve">3.51628923416138</t>
   </si>
   <si>
-    <t xml:space="preserve">3.5355339050293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.55202960968018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.62900853157043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.56302523612976</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.56027770042419</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.58776950836182</t>
+    <t xml:space="preserve">3.53553414344788</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.55202984809875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.62900805473328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.56302642822266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.56027722358704</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.58776998519897</t>
   </si>
   <si>
     <t xml:space="preserve">3.55752801895142</t>
   </si>
   <si>
-    <t xml:space="preserve">3.6042652130127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.60976338386536</t>
+    <t xml:space="preserve">3.60426473617554</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.6097629070282</t>
   </si>
   <si>
     <t xml:space="preserve">3.67299604415894</t>
   </si>
   <si>
-    <t xml:space="preserve">3.71973299980164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.72798156738281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66749811172485</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.6125123500824</t>
+    <t xml:space="preserve">3.71973323822021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.72798132896423</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66749858856201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61251306533813</t>
   </si>
   <si>
     <t xml:space="preserve">3.69498991966248</t>
   </si>
   <si>
-    <t xml:space="preserve">3.72523140907288</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.70323777198792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.68674230575562</t>
+    <t xml:space="preserve">3.72523164749146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.70323801040649</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.68674206733704</t>
   </si>
   <si>
     <t xml:space="preserve">3.7142345905304</t>
   </si>
   <si>
-    <t xml:space="preserve">3.61801028251648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71698451042175</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.67574501037598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.75822305679321</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.76372122764587</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73347973823547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.78571534156799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.78296589851379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.79396295547485</t>
+    <t xml:space="preserve">3.61801147460938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71698474884033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.67574596405029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.75822329521179</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.76372170448303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73348045349121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.78571581840515</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.78296661376953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.79396343231201</t>
   </si>
   <si>
     <t xml:space="preserve">3.77196955680847</t>
   </si>
   <si>
-    <t xml:space="preserve">3.78021717071533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84894847869873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85719585418701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.76647067070007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.70873641967773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.69224071502686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80221056938171</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88895297050476</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83979868888855</t>
+    <t xml:space="preserve">3.78021669387817</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84894800186157</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85719561576843</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.76647043228149</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.70873713493347</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.69224143028259</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.80221080780029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88895392417908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.83979964256287</t>
   </si>
   <si>
     <t xml:space="preserve">3.83112549781799</t>
   </si>
   <si>
-    <t xml:space="preserve">3.87449598312378</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.56800580024719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.35693287849426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.44656705856323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.44078326225281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.53620076179504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.45813250541687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.37139010429382</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.33380126953125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.30777883529663</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.43210983276367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.58824610710144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.57957124710083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66342282295227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.59981107711792</t>
+    <t xml:space="preserve">3.87449526786804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.56800627708435</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.35693311691284</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.44656658172607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.44078350067139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.53620100021362</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.45813274383545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.37138962745667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.33380174636841</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.30777859687805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.43210935592651</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.5882465839386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.57957220077515</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66342329978943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.5998113155365</t>
   </si>
   <si>
     <t xml:space="preserve">3.60270309448242</t>
   </si>
   <si>
-    <t xml:space="preserve">3.58246326446533</t>
+    <t xml:space="preserve">3.58246397972107</t>
   </si>
   <si>
     <t xml:space="preserve">3.63740038871765</t>
   </si>
   <si>
-    <t xml:space="preserve">3.62583446502686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.58535432815552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.5766806602478</t>
+    <t xml:space="preserve">3.62583470344543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.58535385131836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.57668089866638</t>
   </si>
   <si>
     <t xml:space="preserve">3.53330969810486</t>
   </si>
   <si>
-    <t xml:space="preserve">3.51596117019653</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.46102404594421</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.72992563247681</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.70968580245972</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73570871353149</t>
+    <t xml:space="preserve">3.51596093177795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.46102452278137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.72992515563965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.70968556404114</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73570823669434</t>
   </si>
   <si>
     <t xml:space="preserve">3.74149131774902</t>
   </si>
   <si>
-    <t xml:space="preserve">3.79353618621826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80510091781616</t>
+    <t xml:space="preserve">3.79353666305542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.80510258674622</t>
   </si>
   <si>
     <t xml:space="preserve">3.72703385353088</t>
   </si>
   <si>
-    <t xml:space="preserve">3.65185761451721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.68944525718689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.59692001342773</t>
+    <t xml:space="preserve">3.65185713768005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.68944573402405</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.59692049026489</t>
   </si>
   <si>
     <t xml:space="preserve">3.61137747764587</t>
   </si>
   <si>
-    <t xml:space="preserve">3.67209672927856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.63161849975586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.59113717079163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.60848593711853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.55644083023071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.62294363975525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.6142692565918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.63450860977173</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64607453346252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.70390272140503</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.69233655929565</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.49572086334229</t>
+    <t xml:space="preserve">3.67209768295288</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.63161778450012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.59113740921021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.60848546028137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.55644035339355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.62294340133667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61426854133606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.63450813293457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64607405662537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.70390319824219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.69233679771423</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.49572110176086</t>
   </si>
   <si>
     <t xml:space="preserve">3.54776692390442</t>
   </si>
   <si>
-    <t xml:space="preserve">3.54487442970276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.51306962966919</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.53041815757751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.53909182548523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.51885223388672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.510178565979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.50439524650574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.4899377822876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.49282956123352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.43500113487244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.47837138175964</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.49861192703247</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.44945859909058</t>
+    <t xml:space="preserve">3.54487490653992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.51306891441345</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.53041768074036</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.53909230232239</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.51885151863098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.51017761230469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.50439500808716</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.48993849754333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.49282908439636</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.43500089645386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.47837233543396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.49861288070679</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.44945788383484</t>
   </si>
   <si>
     <t xml:space="preserve">3.5072865486145</t>
   </si>
   <si>
-    <t xml:space="preserve">3.57378888130188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.55354881286621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.44367575645447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.4234356880188</t>
+    <t xml:space="preserve">3.57378935813904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.55354857444763</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.44367504119873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.42343544960022</t>
   </si>
   <si>
     <t xml:space="preserve">3.45234942436218</t>
   </si>
   <si>
-    <t xml:space="preserve">3.48415541648865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.47548079490662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.4639151096344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.45524048805237</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.411869764328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.37428164482117</t>
+    <t xml:space="preserve">3.48415517807007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.47548055648804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.46391534805298</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.45524096488953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.41187000274658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.37428116798401</t>
   </si>
   <si>
     <t xml:space="preserve">3.3019962310791</t>
   </si>
   <si>
-    <t xml:space="preserve">3.26729917526245</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.26151609420776</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.25573348999023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.2470588684082</t>
+    <t xml:space="preserve">3.26729869842529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.26151633262634</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.25573396682739</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.24705934524536</t>
   </si>
   <si>
     <t xml:space="preserve">3.20368790626526</t>
   </si>
   <si>
-    <t xml:space="preserve">3.33091020584106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.39162945747375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.39452123641968</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.3858470916748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66053152084351</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.67498850822449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66631436347961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.657639503479</t>
+    <t xml:space="preserve">3.33091044425964</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.39162921905518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.39452075958252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.38584661483765</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66053080558777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.67498874664307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66631460189819</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.65763926506042</t>
   </si>
   <si>
     <t xml:space="preserve">3.70679354667664</t>
   </si>
   <si>
-    <t xml:space="preserve">3.66920518875122</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.70101118087769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71835994720459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.69522833824158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.6431839466095</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.56511449813843</t>
+    <t xml:space="preserve">3.66920566558838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.70101094245911</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71836018562317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.695228099823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64318346977234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.56511521339417</t>
   </si>
   <si>
     <t xml:space="preserve">3.52752661705017</t>
@@ -635,67 +635,67 @@
     <t xml:space="preserve">3.50150370597839</t>
   </si>
   <si>
-    <t xml:space="preserve">3.52463459968567</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.38295555114746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.36271548271179</t>
+    <t xml:space="preserve">3.52463483810425</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.38295578956604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.36271619796753</t>
   </si>
   <si>
     <t xml:space="preserve">3.3800642490387</t>
   </si>
   <si>
-    <t xml:space="preserve">3.46969771385193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.46680665016174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.52174401283264</t>
+    <t xml:space="preserve">3.46969842910767</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.46680688858032</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.52174377441406</t>
   </si>
   <si>
     <t xml:space="preserve">3.6287260055542</t>
   </si>
   <si>
-    <t xml:space="preserve">3.74438309669495</t>
+    <t xml:space="preserve">3.74438238143921</t>
   </si>
   <si>
     <t xml:space="preserve">3.73281669616699</t>
   </si>
   <si>
-    <t xml:space="preserve">3.72414350509644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.6865541934967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.75594806671143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.72125172615051</t>
+    <t xml:space="preserve">3.72414231300354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.68655490875244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.75594878196716</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.72125101089478</t>
   </si>
   <si>
     <t xml:space="preserve">3.60559439659119</t>
   </si>
   <si>
-    <t xml:space="preserve">3.640291929245</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.67788004875183</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.6981201171875</t>
+    <t xml:space="preserve">3.64029145240784</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.67787981033325</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.69812035560608</t>
   </si>
   <si>
     <t xml:space="preserve">3.61716032028198</t>
   </si>
   <si>
-    <t xml:space="preserve">3.68077158927917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.75883984565735</t>
+    <t xml:space="preserve">3.6807713508606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.75884032249451</t>
   </si>
   <si>
     <t xml:space="preserve">3.77040505409241</t>
@@ -704,142 +704,142 @@
     <t xml:space="preserve">3.64896607398987</t>
   </si>
   <si>
-    <t xml:space="preserve">3.62005209922791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73860049247742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.74727320671082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71650862693787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.72881484031677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.74112129211426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.68574237823486</t>
+    <t xml:space="preserve">3.62005162239075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73860025405884</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.74727487564087</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71650767326355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.72881460189819</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.7411208152771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.68574213981628</t>
   </si>
   <si>
     <t xml:space="preserve">3.69189524650574</t>
   </si>
   <si>
-    <t xml:space="preserve">3.70420169830322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.6672830581665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.74727439880371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.7134313583374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.68881893157959</t>
+    <t xml:space="preserve">3.7042019367218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66728258132935</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.74727511405945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71343159675598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.68881964683533</t>
   </si>
   <si>
     <t xml:space="preserve">3.69497275352478</t>
   </si>
   <si>
-    <t xml:space="preserve">3.67343592643738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.65805387496948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.72266101837158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73189115524292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.76880979537964</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.7503502368927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.7349681854248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.72573804855347</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.67958927154541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.67035984992981</t>
+    <t xml:space="preserve">3.67343640327454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.65805339813232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.72266149520874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.7318913936615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.7688102722168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.75035047531128</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73496794700623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.72573757171631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.67958974838257</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.67035937309265</t>
   </si>
   <si>
     <t xml:space="preserve">3.70727872848511</t>
   </si>
   <si>
-    <t xml:space="preserve">3.83957123756409</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85187816619873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87033724784851</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.818035364151</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8272647857666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83034086227417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.86726045608521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.7595808506012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77188611030579</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.82418823242188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83341813087463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.78419351577759</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.76573300361633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.75650405883789</t>
+    <t xml:space="preserve">3.83957147598267</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85187840461731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87033605575562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.81803584098816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.82726430892944</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.83034133911133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.86726093292236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.75957989692688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77188682556152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.82418847084045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.83341836929321</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.78419327735901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.76573371887207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.75650334358215</t>
   </si>
   <si>
     <t xml:space="preserve">3.78111624717712</t>
   </si>
   <si>
-    <t xml:space="preserve">3.74419736862183</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.78727030754089</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84572505950928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.82111144065857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.81188201904297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8149585723877</t>
+    <t xml:space="preserve">3.74419760704041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.78726959228516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84572458267212</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.82111239433289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.81188154220581</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.81495833396912</t>
   </si>
   <si>
     <t xml:space="preserve">3.79034614562988</t>
@@ -848,61 +848,61 @@
     <t xml:space="preserve">3.80572915077209</t>
   </si>
   <si>
-    <t xml:space="preserve">3.77803993225098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.79957556724548</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85495495796204</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.79342246055603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.86110758781433</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87341403961182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85803079605103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.86418509483337</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84880137443542</t>
+    <t xml:space="preserve">3.7780396938324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.79957580566406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8549542427063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.79342293739319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.86110711097717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87341380119324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85802984237671</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.86418461799622</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.848801612854</t>
   </si>
   <si>
     <t xml:space="preserve">3.77496361732483</t>
   </si>
   <si>
-    <t xml:space="preserve">3.76265716552734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.75342726707458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.91648626327515</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94417452812195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.91956210136414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90725541114807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8949499130249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.91033267974854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92263889312744</t>
+    <t xml:space="preserve">3.76265692710876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.75342679023743</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.91648554801941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94417476654053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.91956257820129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90725588798523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89494967460632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.91033315658569</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9226393699646</t>
   </si>
   <si>
     <t xml:space="preserve">3.94109845161438</t>
@@ -911,16 +911,16 @@
     <t xml:space="preserve">3.95648145675659</t>
   </si>
   <si>
-    <t xml:space="preserve">3.96878790855408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98109436035156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96263527870178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99340081214905</t>
+    <t xml:space="preserve">3.96878719329834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9810938835144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96263480186462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99340057373047</t>
   </si>
   <si>
     <t xml:space="preserve">4.02416610717773</t>
@@ -929,58 +929,58 @@
     <t xml:space="preserve">4.02108955383301</t>
   </si>
   <si>
-    <t xml:space="preserve">4.04877758026123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.13799953460693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.13492298126221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.11954069137573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.09185123443604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.10723352432251</t>
+    <t xml:space="preserve">4.04877853393555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.13800001144409</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.13492202758789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.11953973770142</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.09185171127319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.10723400115967</t>
   </si>
   <si>
     <t xml:space="preserve">4.11646413803101</t>
   </si>
   <si>
-    <t xml:space="preserve">4.09308099746704</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.075852394104</t>
+    <t xml:space="preserve">4.0930814743042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.07585287094116</t>
   </si>
   <si>
     <t xml:space="preserve">4.10046577453613</t>
   </si>
   <si>
-    <t xml:space="preserve">4.05123996734619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.05985355377197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93802165985107</t>
+    <t xml:space="preserve">4.05124044418335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.05985546112061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93802237510681</t>
   </si>
   <si>
     <t xml:space="preserve">4.04262542724609</t>
   </si>
   <si>
-    <t xml:space="preserve">3.96632695198059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96017384529114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.97740268707275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.01678276062012</t>
+    <t xml:space="preserve">3.96632742881775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96017241477966</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97740292549133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.01678228378296</t>
   </si>
   <si>
     <t xml:space="preserve">4.05000925064087</t>
@@ -992,28 +992,28 @@
     <t xml:space="preserve">4.1016960144043</t>
   </si>
   <si>
-    <t xml:space="preserve">4.17184209823608</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.15953636169434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.12630891799927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.13000059127808</t>
+    <t xml:space="preserve">4.17184257507324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.15953588485718</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.12630796432495</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.13000106811523</t>
   </si>
   <si>
     <t xml:space="preserve">4.09431171417236</t>
   </si>
   <si>
-    <t xml:space="preserve">4.33182334899902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.34536123275757</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.31828737258911</t>
+    <t xml:space="preserve">4.33182430267334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.34536075592041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.31828689575195</t>
   </si>
   <si>
     <t xml:space="preserve">4.22475910186768</t>
@@ -1028,7 +1028,7 @@
     <t xml:space="preserve">4.4007396697998</t>
   </si>
   <si>
-    <t xml:space="preserve">4.51272773742676</t>
+    <t xml:space="preserve">4.51272678375244</t>
   </si>
   <si>
     <t xml:space="preserve">4.48934507369995</t>
@@ -1037,106 +1037,106 @@
     <t xml:space="preserve">4.56564426422119</t>
   </si>
   <si>
-    <t xml:space="preserve">4.46719360351562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.4093542098999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.47949934005737</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.54964637756348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.51518821716309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.54595422744751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.53733968734741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.49549770355225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.45857810974121</t>
+    <t xml:space="preserve">4.46719312667847</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.40935468673706</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.47949981689453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.54964542388916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.51518869400024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.54595375061035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.53733921051025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.4954981803894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.45857906341553</t>
   </si>
   <si>
     <t xml:space="preserve">4.44258117675781</t>
   </si>
   <si>
-    <t xml:space="preserve">4.45734834671021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.52626371383667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.53487920761108</t>
+    <t xml:space="preserve">4.45734930038452</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.52626419067383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.53487825393677</t>
   </si>
   <si>
     <t xml:space="preserve">4.5693359375</t>
   </si>
   <si>
-    <t xml:space="preserve">4.6456356048584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.64071130752563</t>
+    <t xml:space="preserve">4.64563655853271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.64071369171143</t>
   </si>
   <si>
     <t xml:space="preserve">4.67640066146851</t>
   </si>
   <si>
-    <t xml:space="preserve">4.72808837890625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.72070455551147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.72439527511597</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.72193336486816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.75023889541626</t>
+    <t xml:space="preserve">4.72808694839478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.72070407867432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.72439622879028</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.72193431854248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.75023937225342</t>
   </si>
   <si>
     <t xml:space="preserve">4.79331111907959</t>
   </si>
   <si>
-    <t xml:space="preserve">4.76377582550049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.77362108230591</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.84253597259521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.84745836257935</t>
+    <t xml:space="preserve">4.76377630233765</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.77362012863159</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.84253549575806</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.84745931625366</t>
   </si>
   <si>
     <t xml:space="preserve">4.86837959289551</t>
   </si>
   <si>
-    <t xml:space="preserve">4.87822437286377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.90529823303223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.98775005340576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.97421360015869</t>
+    <t xml:space="preserve">4.87822484970093</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.90529870986938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.98775100708008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.97421407699585</t>
   </si>
   <si>
     <t xml:space="preserve">4.96559906005859</t>
   </si>
   <si>
-    <t xml:space="preserve">5.0172872543335</t>
+    <t xml:space="preserve">5.01728677749634</t>
   </si>
   <si>
     <t xml:space="preserve">4.99390459060669</t>
@@ -1145,7 +1145,7 @@
     <t xml:space="preserve">4.9705228805542</t>
   </si>
   <si>
-    <t xml:space="preserve">5.01482486724854</t>
+    <t xml:space="preserve">5.01482534408569</t>
   </si>
   <si>
     <t xml:space="preserve">5.05666637420654</t>
@@ -1154,25 +1154,25 @@
     <t xml:space="preserve">4.86714887619019</t>
   </si>
   <si>
-    <t xml:space="preserve">4.85607290267944</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.68870782852173</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.69855213165283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.73670196533203</t>
+    <t xml:space="preserve">4.8560733795166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.68870639801025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.69855308532715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.73670148849487</t>
   </si>
   <si>
     <t xml:space="preserve">4.71331977844238</t>
   </si>
   <si>
-    <t xml:space="preserve">4.74162435531616</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.66901636123657</t>
+    <t xml:space="preserve">4.74162483215332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.66901683807373</t>
   </si>
   <si>
     <t xml:space="preserve">4.51887989044189</t>
@@ -1181,19 +1181,19 @@
     <t xml:space="preserve">4.31582593917847</t>
   </si>
   <si>
-    <t xml:space="preserve">4.49672985076904</t>
+    <t xml:space="preserve">4.49672889709473</t>
   </si>
   <si>
     <t xml:space="preserve">4.50657367706299</t>
   </si>
   <si>
-    <t xml:space="preserve">4.59640979766846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.62225341796875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.50041961669922</t>
+    <t xml:space="preserve">4.59641075134277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.62225294113159</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.50042057037354</t>
   </si>
   <si>
     <t xml:space="preserve">4.49795913696289</t>
@@ -1205,136 +1205,136 @@
     <t xml:space="preserve">4.3588981628418</t>
   </si>
   <si>
-    <t xml:space="preserve">4.52749443054199</t>
+    <t xml:space="preserve">4.52749490737915</t>
   </si>
   <si>
     <t xml:space="preserve">4.61363887786865</t>
   </si>
   <si>
-    <t xml:space="preserve">4.70101356506348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.81177043914795</t>
+    <t xml:space="preserve">4.70101404190063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.81177091598511</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.69486045837402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.76779079437256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.8159761428833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.83811521530151</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.77820920944214</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.78341817855835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.72090721130371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.74304628372192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.67532587051392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.66881370544434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.71569776535034</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.72741794586182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.83941888809204</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.87718486785889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.92276620864868</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.87067365646362</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.94230079650879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.930579662323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.00220727920532</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.0543007850647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.08164978027344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.0230450630188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.03606843948364</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.02044057846069</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.02955675125122</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.11160182952881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.13374137878418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.15588188171387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.18713760375977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.17932224273682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.89932489395142</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.8498363494873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.83420848846436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.77560377120972</t>
   </si>
   <si>
     <t xml:space="preserve">4.69486093521118</t>
   </si>
   <si>
-    <t xml:space="preserve">4.7677903175354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.8159761428833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.83811521530151</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.77820920944214</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.78341817855835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.72090625762939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.74304628372192</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.6753249168396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.66881418228149</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.71569728851318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.72741889953613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.83941841125488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.87718486785889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.92276573181152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.87067365646362</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.94230175018311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.93058013916016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.00220727920532</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.05430030822754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.08164930343628</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.02304553985596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.03606748580933</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.02043962478638</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.02955675125122</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.11160278320312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.13374185562134</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.15588188171387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.18713665008545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.17932224273682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.8993239402771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.8498363494873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.8342080116272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.77560424804688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.69486045837402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.62583780288696</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.6063027381897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.6544885635376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.51644325256348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.46044301986694</t>
+    <t xml:space="preserve">4.6258373260498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.60630321502686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.65448808670044</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.51644277572632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.46044254302979</t>
   </si>
   <si>
     <t xml:space="preserve">4.39011812210083</t>
@@ -1343,16 +1343,16 @@
     <t xml:space="preserve">4.529465675354</t>
   </si>
   <si>
-    <t xml:space="preserve">4.44090890884399</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.42397785186768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.4161639213562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.3992338180542</t>
+    <t xml:space="preserve">4.44090843200684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.42397832870483</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.41616439819336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.39923429489136</t>
   </si>
   <si>
     <t xml:space="preserve">4.41876840591431</t>
@@ -1361,28 +1361,28 @@
     <t xml:space="preserve">4.36146688461304</t>
   </si>
   <si>
-    <t xml:space="preserve">4.31849050521851</t>
+    <t xml:space="preserve">4.31849098205566</t>
   </si>
   <si>
     <t xml:space="preserve">4.39142036437988</t>
   </si>
   <si>
-    <t xml:space="preserve">4.50732707977295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.59458255767822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.56593132019043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.58416223526001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.68965148925781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.66490650177002</t>
+    <t xml:space="preserve">4.50732660293579</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.59458160400391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.56592988967896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.58416318893433</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.6896505355835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.66490697860718</t>
   </si>
   <si>
     <t xml:space="preserve">4.59197759628296</t>
@@ -1394,13 +1394,13 @@
     <t xml:space="preserve">4.50081491470337</t>
   </si>
   <si>
-    <t xml:space="preserve">4.5437912940979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.52165174484253</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.5099310874939</t>
+    <t xml:space="preserve">4.54379224777222</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.52165222167969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.50993061065674</t>
   </si>
   <si>
     <t xml:space="preserve">4.57114028930664</t>
@@ -1418,7 +1418,7 @@
     <t xml:space="preserve">4.71309280395508</t>
   </si>
   <si>
-    <t xml:space="preserve">4.68183660507202</t>
+    <t xml:space="preserve">4.68183708190918</t>
   </si>
   <si>
     <t xml:space="preserve">4.4812798500061</t>
@@ -1430,25 +1430,25 @@
     <t xml:space="preserve">4.3536524772644</t>
   </si>
   <si>
-    <t xml:space="preserve">4.36276912689209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.36667680740356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.29765272140503</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.13877058029175</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.1609091758728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.20258331298828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.08667755126953</t>
+    <t xml:space="preserve">4.36276865005493</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.36667585372925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.29765319824219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.13877010345459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.16090965270996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.20258378982544</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.08667659759521</t>
   </si>
   <si>
     <t xml:space="preserve">4.06844520568848</t>
@@ -1457,52 +1457,52 @@
     <t xml:space="preserve">4.08407258987427</t>
   </si>
   <si>
-    <t xml:space="preserve">4.15179300308228</t>
+    <t xml:space="preserve">4.15179347991943</t>
   </si>
   <si>
     <t xml:space="preserve">4.09970045089722</t>
   </si>
   <si>
-    <t xml:space="preserve">3.9850959777832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.08277034759521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.06063079833984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.06974649429321</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90565538406372</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99030542373657</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99421358108521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.12053775787354</t>
+    <t xml:space="preserve">3.98509645462036</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.0827693939209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.060631275177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.06974697113037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90565514564514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99030566215515</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99421262741089</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.12053823471069</t>
   </si>
   <si>
     <t xml:space="preserve">4.02937507629395</t>
   </si>
   <si>
-    <t xml:space="preserve">4.13486337661743</t>
+    <t xml:space="preserve">4.13486289978027</t>
   </si>
   <si>
     <t xml:space="preserve">4.26639699935913</t>
   </si>
   <si>
-    <t xml:space="preserve">4.30025768280029</t>
+    <t xml:space="preserve">4.30025815963745</t>
   </si>
   <si>
     <t xml:space="preserve">4.2403507232666</t>
   </si>
   <si>
-    <t xml:space="preserve">4.21300268173218</t>
+    <t xml:space="preserve">4.21300220489502</t>
   </si>
   <si>
     <t xml:space="preserve">4.35235071182251</t>
@@ -1511,46 +1511,46 @@
     <t xml:space="preserve">4.44351243972778</t>
   </si>
   <si>
-    <t xml:space="preserve">4.47346639633179</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.48258256912231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.48518753051758</t>
+    <t xml:space="preserve">4.47346591949463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.482581615448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.48518705368042</t>
   </si>
   <si>
     <t xml:space="preserve">4.34193181991577</t>
   </si>
   <si>
-    <t xml:space="preserve">4.23253679275513</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.24295568466187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.26769924163818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.15049171447754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.28723430633545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.26509571075439</t>
+    <t xml:space="preserve">4.23253726959229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.24295473098755</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.26769876480103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.15049123764038</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.28723478317261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.26509428024292</t>
   </si>
   <si>
     <t xml:space="preserve">4.45393133163452</t>
   </si>
   <si>
-    <t xml:space="preserve">4.4304895401001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.36407089233398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.36537265777588</t>
+    <t xml:space="preserve">4.43049049377441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.3640718460083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.36537408828735</t>
   </si>
   <si>
     <t xml:space="preserve">4.47086143493652</t>
@@ -1559,13 +1559,13 @@
     <t xml:space="preserve">4.43569850921631</t>
   </si>
   <si>
-    <t xml:space="preserve">4.49430370330811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.25728130340576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.27811861038208</t>
+    <t xml:space="preserve">4.49430274963379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.2572808265686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.27811813354492</t>
   </si>
   <si>
     <t xml:space="preserve">4.22863006591797</t>
@@ -1574,22 +1574,22 @@
     <t xml:space="preserve">4.27030515670776</t>
   </si>
   <si>
-    <t xml:space="preserve">4.44221019744873</t>
+    <t xml:space="preserve">4.44221067428589</t>
   </si>
   <si>
     <t xml:space="preserve">4.512535572052</t>
   </si>
   <si>
-    <t xml:space="preserve">4.49039602279663</t>
+    <t xml:space="preserve">4.49039649963379</t>
   </si>
   <si>
     <t xml:space="preserve">4.48388481140137</t>
   </si>
   <si>
-    <t xml:space="preserve">4.62844181060791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.56462860107422</t>
+    <t xml:space="preserve">4.62844228744507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.56462907791138</t>
   </si>
   <si>
     <t xml:space="preserve">4.49821043014526</t>
@@ -1598,37 +1598,37 @@
     <t xml:space="preserve">4.44872188568115</t>
   </si>
   <si>
-    <t xml:space="preserve">4.54769849777222</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.53858184814453</t>
+    <t xml:space="preserve">4.54769802093506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.53858232498169</t>
   </si>
   <si>
     <t xml:space="preserve">4.55681419372559</t>
   </si>
   <si>
-    <t xml:space="preserve">4.61281394958496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.58155918121338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.62714052200317</t>
+    <t xml:space="preserve">4.61281442642212</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.58155822753906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.62713956832886</t>
   </si>
   <si>
     <t xml:space="preserve">4.6883487701416</t>
   </si>
   <si>
-    <t xml:space="preserve">4.70007038116455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.72220993041992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.70137166976929</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.78862762451172</t>
+    <t xml:space="preserve">4.70006990432739</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.72220849990845</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.70137214660645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.78862714767456</t>
   </si>
   <si>
     <t xml:space="preserve">4.81858062744141</t>
@@ -1640,19 +1640,19 @@
     <t xml:space="preserve">4.94881248474121</t>
   </si>
   <si>
-    <t xml:space="preserve">4.90192937850952</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.94751119613647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.95923137664795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.00871849060059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.98657989501953</t>
+    <t xml:space="preserve">4.90192985534668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.94751071929932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.95923185348511</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.0087194442749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.98658037185669</t>
   </si>
   <si>
     <t xml:space="preserve">4.99439382553101</t>
@@ -1661,10 +1661,10 @@
     <t xml:space="preserve">4.89281272888184</t>
   </si>
   <si>
-    <t xml:space="preserve">4.78472089767456</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.89671993255615</t>
+    <t xml:space="preserve">4.78471946716309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.89671945571899</t>
   </si>
   <si>
     <t xml:space="preserve">4.97746419906616</t>
@@ -1676,25 +1676,25 @@
     <t xml:space="preserve">4.85374307632446</t>
   </si>
   <si>
-    <t xml:space="preserve">4.86937141418457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.92797613143921</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.00090599060059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.05169630050659</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.99178886413574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.04388236999512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.06211471557617</t>
+    <t xml:space="preserve">4.86937093734741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.92797565460205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.00090503692627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.05169534683228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.99178838729858</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.04388189315796</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.06211423873901</t>
   </si>
   <si>
     <t xml:space="preserve">5.04648637771606</t>
@@ -1703,100 +1703,100 @@
     <t xml:space="preserve">5.03216123580933</t>
   </si>
   <si>
-    <t xml:space="preserve">5.06732368469238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.08816194534302</t>
+    <t xml:space="preserve">5.06732416152954</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.08816146850586</t>
   </si>
   <si>
     <t xml:space="preserve">5.14285755157471</t>
   </si>
   <si>
-    <t xml:space="preserve">5.14416027069092</t>
+    <t xml:space="preserve">5.14416122436523</t>
   </si>
   <si>
     <t xml:space="preserve">5.16369485855103</t>
   </si>
   <si>
-    <t xml:space="preserve">5.1676025390625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.13895082473755</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.16239356994629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.17281150817871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.17541694641113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.08685827255249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.14546298980713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.17020654678345</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.18323087692261</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.20406723022461</t>
+    <t xml:space="preserve">5.16760158538818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.13895130157471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.16239309310913</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.17281103134155</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.17541646957397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.08685779571533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.14546251296997</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.17020702362061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.18322992324829</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.20406770706177</t>
   </si>
   <si>
     <t xml:space="preserve">5.26136875152588</t>
   </si>
   <si>
-    <t xml:space="preserve">5.30695009231567</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.44369316101074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.49578666687012</t>
+    <t xml:space="preserve">5.30695104598999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.4436936378479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.49578714370728</t>
   </si>
   <si>
     <t xml:space="preserve">5.62471580505371</t>
   </si>
   <si>
-    <t xml:space="preserve">5.57392597198486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.59346151351929</t>
+    <t xml:space="preserve">5.57392644882202</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.59346055984497</t>
   </si>
   <si>
     <t xml:space="preserve">5.61560010910034</t>
   </si>
   <si>
-    <t xml:space="preserve">5.61690282821655</t>
+    <t xml:space="preserve">5.61690235137939</t>
   </si>
   <si>
     <t xml:space="preserve">5.59736728668213</t>
   </si>
   <si>
-    <t xml:space="preserve">5.64685535430908</t>
+    <t xml:space="preserve">5.6468563079834</t>
   </si>
   <si>
     <t xml:space="preserve">5.63253021240234</t>
   </si>
   <si>
-    <t xml:space="preserve">5.64946031570435</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.69504117965698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.69113445281982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.71327352523804</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.81094837188721</t>
+    <t xml:space="preserve">5.64945936203003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.69504165649414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.69113397598267</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.71327447891235</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.81094741821289</t>
   </si>
   <si>
     <t xml:space="preserve">5.83178567886353</t>
@@ -1814,37 +1814,37 @@
     <t xml:space="preserve">5.9060173034668</t>
   </si>
   <si>
-    <t xml:space="preserve">5.86173868179321</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.19643402099609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.19903945922852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.16127157211304</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.03103971481323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.00629615783691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.02452802658081</t>
+    <t xml:space="preserve">5.86173915863037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.19643449783325</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.19903898239136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.16127109527588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.03104114532471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.0062952041626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.02452850341797</t>
   </si>
   <si>
     <t xml:space="preserve">6.10397005081177</t>
   </si>
   <si>
-    <t xml:space="preserve">6.19252824783325</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.14694547653198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.08703899383545</t>
+    <t xml:space="preserve">6.19252729415894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.1469464302063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.08703994750977</t>
   </si>
   <si>
     <t xml:space="preserve">6.13262176513672</t>
@@ -1856,70 +1856,70 @@
     <t xml:space="preserve">5.86564540863037</t>
   </si>
   <si>
-    <t xml:space="preserve">5.860435962677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.79271507263184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.97113370895386</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.93336629867554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.01020193099976</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.87606430053711</t>
+    <t xml:space="preserve">5.86043548583984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.79271554946899</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.9711332321167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.93336582183838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.01020288467407</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.87606334686279</t>
   </si>
   <si>
     <t xml:space="preserve">5.92815685272217</t>
   </si>
   <si>
-    <t xml:space="preserve">5.96592378616333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.70936727523804</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.8083438873291</t>
+    <t xml:space="preserve">5.96592426300049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.70936679840088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.80834245681763</t>
   </si>
   <si>
     <t xml:space="preserve">5.79401779174805</t>
   </si>
   <si>
-    <t xml:space="preserve">5.74843692779541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.71848201751709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.66508817672729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.67680978775024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.82136631011963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.78099489212036</t>
+    <t xml:space="preserve">5.74843740463257</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.71848344802856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.66508865356445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.67680931091309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.82136678695679</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.78099584579468</t>
   </si>
   <si>
     <t xml:space="preserve">5.81224966049194</t>
   </si>
   <si>
-    <t xml:space="preserve">5.92685556411743</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.98285388946533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.01150560379028</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.03494644165039</t>
+    <t xml:space="preserve">5.92685508728027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.98285436630249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.01150512695312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.03494691848755</t>
   </si>
   <si>
     <t xml:space="preserve">6.00369167327881</t>
@@ -1928,31 +1928,31 @@
     <t xml:space="preserve">6.0492730140686</t>
   </si>
   <si>
-    <t xml:space="preserve">6.10266637802124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.19513130187988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.30506467819214</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.26136541366577</t>
+    <t xml:space="preserve">6.10266733169556</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.19513177871704</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.3050651550293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.26136493682861</t>
   </si>
   <si>
     <t xml:space="preserve">6.23541784286499</t>
   </si>
   <si>
-    <t xml:space="preserve">6.24088001251221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.32281732559204</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.31189250946045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.46347570419312</t>
+    <t xml:space="preserve">6.24088048934937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.3228178024292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.31189298629761</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.46347665786743</t>
   </si>
   <si>
     <t xml:space="preserve">6.61642599105835</t>
@@ -1961,58 +1961,58 @@
     <t xml:space="preserve">6.65739440917969</t>
   </si>
   <si>
-    <t xml:space="preserve">6.63281297683716</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.6232533454895</t>
+    <t xml:space="preserve">6.63281393051147</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.62325429916382</t>
   </si>
   <si>
     <t xml:space="preserve">6.59184503555298</t>
   </si>
   <si>
-    <t xml:space="preserve">6.65602731704712</t>
+    <t xml:space="preserve">6.65602874755859</t>
   </si>
   <si>
     <t xml:space="preserve">6.59047937393188</t>
   </si>
   <si>
-    <t xml:space="preserve">6.59457588195801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.56589651107788</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.54541492462158</t>
+    <t xml:space="preserve">6.59457492828369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.56589698791504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.54541397094727</t>
   </si>
   <si>
     <t xml:space="preserve">6.53175735473633</t>
   </si>
   <si>
-    <t xml:space="preserve">6.41841125488281</t>
+    <t xml:space="preserve">6.41841077804565</t>
   </si>
   <si>
     <t xml:space="preserve">6.44708919525146</t>
   </si>
   <si>
-    <t xml:space="preserve">6.40612077713013</t>
+    <t xml:space="preserve">6.40612030029297</t>
   </si>
   <si>
     <t xml:space="preserve">6.46893882751465</t>
   </si>
   <si>
-    <t xml:space="preserve">6.42250919342041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.54678106307983</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.37607574462891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.59594106674194</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.66149044036865</t>
+    <t xml:space="preserve">6.42250728607178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.5467791557312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.37607765197754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.59594058990479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.66149234771729</t>
   </si>
   <si>
     <t xml:space="preserve">6.58365106582642</t>
@@ -2024,205 +2024,205 @@
     <t xml:space="preserve">6.47440099716187</t>
   </si>
   <si>
-    <t xml:space="preserve">6.58091974258423</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.14119052886963</t>
+    <t xml:space="preserve">6.58091878890991</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.14119005203247</t>
   </si>
   <si>
     <t xml:space="preserve">6.21356868743896</t>
   </si>
   <si>
-    <t xml:space="preserve">6.35695743560791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.24361181259155</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.48669052124023</t>
+    <t xml:space="preserve">6.35695838928223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.24361276626587</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.48669195175171</t>
   </si>
   <si>
     <t xml:space="preserve">6.44162607192993</t>
   </si>
   <si>
-    <t xml:space="preserve">6.62188911437988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.59867238998413</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.43206787109375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.48532629013062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.4170446395874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.71884727478027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.67241621017456</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.74342775344849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.75981569290161</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.88955116271973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.86223793029785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.87930822372437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.8827223777771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.76664304733276</t>
+    <t xml:space="preserve">6.62188768386841</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.59867286682129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.43206691741943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.48532676696777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.41704511642456</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.71884632110596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.67241668701172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.74342727661133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.75981521606445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.88955020904541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.86223745346069</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.87930727005005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.88272094726562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.76664352416992</t>
   </si>
   <si>
     <t xml:space="preserve">6.79395627975464</t>
   </si>
   <si>
-    <t xml:space="preserve">6.91344785690308</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.95441675186157</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.86906623840332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.81034326553345</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.93734645843506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.95100116729736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.87247943878174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.015869140625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.97490262985229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.9714879989624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.00562810897827</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.12170457839966</t>
+    <t xml:space="preserve">6.91344881057739</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.95441627502441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.86906671524048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.81034374237061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.9373459815979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.95100164413452</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.87248039245605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.01587009429932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.97490072250366</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.97148704528809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.0056266784668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.12170505523682</t>
   </si>
   <si>
     <t xml:space="preserve">7.02269697189331</t>
   </si>
   <si>
-    <t xml:space="preserve">6.80351448059082</t>
+    <t xml:space="preserve">6.80351495742798</t>
   </si>
   <si>
     <t xml:space="preserve">6.81853723526001</t>
   </si>
   <si>
-    <t xml:space="preserve">6.81443929672241</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.00904178619385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.91686248779297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.99879884719849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.22412538528442</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.23436832427979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.33337545394897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.22754049301147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.30947875976562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.35044574737549</t>
+    <t xml:space="preserve">6.81444120407104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.00904083251953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.91686153411865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.9987998008728</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.2241268157959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.23436975479126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.33337450027466</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.22753953933716</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.30947780609131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.35044765472412</t>
   </si>
   <si>
     <t xml:space="preserve">7.37434434890747</t>
   </si>
   <si>
-    <t xml:space="preserve">7.45969676971436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.47676515579224</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.50407838821411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.41531372070312</t>
+    <t xml:space="preserve">7.45969533920288</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.47676610946655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.50407886505127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.41531229019165</t>
   </si>
   <si>
     <t xml:space="preserve">7.44945287704468</t>
   </si>
   <si>
-    <t xml:space="preserve">7.43579626083374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.4289698600769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.53139066696167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.57577419281006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.62698459625244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.507493019104</t>
+    <t xml:space="preserve">7.43579912185669</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.42896938323975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.53139019012451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.57577466964722</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.62698411941528</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.50749158859253</t>
   </si>
   <si>
     <t xml:space="preserve">7.40165758132935</t>
   </si>
   <si>
-    <t xml:space="preserve">7.49042272567749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.65088033676147</t>
+    <t xml:space="preserve">7.49042081832886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.65088176727295</t>
   </si>
   <si>
     <t xml:space="preserve">7.58942890167236</t>
   </si>
   <si>
-    <t xml:space="preserve">7.60650062561035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.62015628814697</t>
+    <t xml:space="preserve">7.60649824142456</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.62015676498413</t>
   </si>
   <si>
     <t xml:space="preserve">7.66100549697876</t>
   </si>
   <si>
-    <t xml:space="preserve">7.529456615448</t>
+    <t xml:space="preserve">7.52945566177368</t>
   </si>
   <si>
     <t xml:space="preserve">7.59869384765625</t>
@@ -2231,73 +2231,73 @@
     <t xml:space="preserve">7.50522422790527</t>
   </si>
   <si>
-    <t xml:space="preserve">7.56753730773926</t>
+    <t xml:space="preserve">7.56753492355347</t>
   </si>
   <si>
     <t xml:space="preserve">7.58830690383911</t>
   </si>
   <si>
-    <t xml:space="preserve">7.51907205581665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.47060585021973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.36328887939453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.33213329315186</t>
+    <t xml:space="preserve">7.51907110214233</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.47060632705688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.36328935623169</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.33213186264038</t>
   </si>
   <si>
     <t xml:space="preserve">7.09326648712158</t>
   </si>
   <si>
-    <t xml:space="preserve">7.16942691802979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.26289463043213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.13134813308716</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.14173316955566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.05172634124756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.15211820602417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.07249689102173</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.1901969909668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.04133939743042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.10365295410156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.03787803649902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.12788581848145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.22135400772095</t>
+    <t xml:space="preserve">7.1694278717041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.26289558410645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.13134765625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.14173269271851</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.05172491073608</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.15211629867554</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.07249546051025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.19019746780396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.04134035110474</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.1036524772644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.03787899017334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.12788486480713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.22135591506958</t>
   </si>
   <si>
     <t xml:space="preserve">7.00672101974487</t>
   </si>
   <si>
-    <t xml:space="preserve">7.05864953994751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.96864128112793</t>
+    <t xml:space="preserve">7.05864810943604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.96864318847656</t>
   </si>
   <si>
     <t xml:space="preserve">6.90840530395508</t>
@@ -2306,13 +2306,13 @@
     <t xml:space="preserve">7.08634328842163</t>
   </si>
   <si>
-    <t xml:space="preserve">6.98941230773926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.10019207000732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.06903600692749</t>
+    <t xml:space="preserve">6.98941326141357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.10019063949585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.06903505325317</t>
   </si>
   <si>
     <t xml:space="preserve">7.02749252319336</t>
@@ -2321,52 +2321,52 @@
     <t xml:space="preserve">6.96518039703369</t>
   </si>
   <si>
-    <t xml:space="preserve">6.95479393005371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.12096118927002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.18673610687256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.20750761032104</t>
+    <t xml:space="preserve">6.95479488372803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.12096261978149</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.18673706054688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.20750713348389</t>
   </si>
   <si>
     <t xml:space="preserve">7.11403846740723</t>
   </si>
   <si>
-    <t xml:space="preserve">7.32867193222046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.67138957977295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.61254072189331</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.16596651077271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.27328252792358</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.41175556182861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.42560386657715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.47406816482544</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.55022716522217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.64023447036743</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.60215520858765</t>
+    <t xml:space="preserve">7.32867002487183</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.67139005661011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.61253976821899</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.16596555709839</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.27328157424927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.4117546081543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.42560243606567</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.47406625747681</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.55022764205933</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.64023351669312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.60215473175049</t>
   </si>
   <si>
     <t xml:space="preserve">7.58138370513916</t>
@@ -2375,52 +2375,52 @@
     <t xml:space="preserve">7.57099914550781</t>
   </si>
   <si>
-    <t xml:space="preserve">7.85140514373779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.96910667419434</t>
+    <t xml:space="preserve">7.85140609741211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.96910715103149</t>
   </si>
   <si>
     <t xml:space="preserve">7.81332492828369</t>
   </si>
   <si>
-    <t xml:space="preserve">7.82024955749512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.266357421875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.15558052062988</t>
+    <t xml:space="preserve">7.82024908065796</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.26635885238647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.15558004379272</t>
   </si>
   <si>
     <t xml:space="preserve">7.29751396179199</t>
   </si>
   <si>
-    <t xml:space="preserve">6.98249006271362</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.65638637542725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.41267347335815</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.6605396270752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.7076210975647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.53037452697754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.73116064071655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.85601329803467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.45444250106812</t>
+    <t xml:space="preserve">6.98248958587646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.65638589859009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.41267442703247</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.66054010391235</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.70762062072754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.5303750038147</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.73116111755371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.85601282119751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.4544415473938</t>
   </si>
   <si>
     <t xml:space="preserve">5.45582675933838</t>
@@ -2429,10 +2429,10 @@
     <t xml:space="preserve">4.25388336181641</t>
   </si>
   <si>
-    <t xml:space="preserve">4.66930246353149</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.50174951553345</t>
+    <t xml:space="preserve">4.66930103302002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.50174903869629</t>
   </si>
   <si>
     <t xml:space="preserve">4.49759531021118</t>
@@ -2447,28 +2447,28 @@
     <t xml:space="preserve">4.80223512649536</t>
   </si>
   <si>
-    <t xml:space="preserve">4.96840238571167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.30766105651855</t>
+    <t xml:space="preserve">4.96840286254883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.30766010284424</t>
   </si>
   <si>
     <t xml:space="preserve">5.356125831604</t>
   </si>
   <si>
-    <t xml:space="preserve">5.60676097869873</t>
+    <t xml:space="preserve">5.60676240921021</t>
   </si>
   <si>
     <t xml:space="preserve">5.43644046783447</t>
   </si>
   <si>
-    <t xml:space="preserve">5.48075246810913</t>
+    <t xml:space="preserve">5.48075199127197</t>
   </si>
   <si>
     <t xml:space="preserve">5.34504842758179</t>
   </si>
   <si>
-    <t xml:space="preserve">5.11795377731323</t>
+    <t xml:space="preserve">5.11795425415039</t>
   </si>
   <si>
     <t xml:space="preserve">5.38105154037476</t>
@@ -2477,34 +2477,34 @@
     <t xml:space="preserve">5.42120838165283</t>
   </si>
   <si>
-    <t xml:space="preserve">5.56660461425781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.64691925048828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.73138809204102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.75077390670776</t>
+    <t xml:space="preserve">5.56660413742065</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.64691972732544</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.73138856887817</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.75077438354492</t>
   </si>
   <si>
     <t xml:space="preserve">5.77431440353394</t>
   </si>
   <si>
-    <t xml:space="preserve">5.26611948013306</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.30904674530029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.33120155334473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.27027320861816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.15811014175415</t>
+    <t xml:space="preserve">5.26611995697021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.30904626846313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.33120107650757</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.27027273178101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.15810966491699</t>
   </si>
   <si>
     <t xml:space="preserve">5.23980903625488</t>
@@ -2516,10 +2516,10 @@
     <t xml:space="preserve">5.12210750579834</t>
   </si>
   <si>
-    <t xml:space="preserve">5.4572114944458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.44751834869385</t>
+    <t xml:space="preserve">5.45721197128296</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.44751882553101</t>
   </si>
   <si>
     <t xml:space="preserve">5.55968141555786</t>
@@ -2528,10 +2528,10 @@
     <t xml:space="preserve">5.36720371246338</t>
   </si>
   <si>
-    <t xml:space="preserve">5.23703956604004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.08887386322021</t>
+    <t xml:space="preserve">5.2370400428772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.08887434005737</t>
   </si>
   <si>
     <t xml:space="preserve">5.00440549850464</t>
@@ -2540,10 +2540,10 @@
     <t xml:space="preserve">5.25781059265137</t>
   </si>
   <si>
-    <t xml:space="preserve">5.36997318267822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.15534067153931</t>
+    <t xml:space="preserve">5.36997365951538</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.15534114837646</t>
   </si>
   <si>
     <t xml:space="preserve">5.06117916107178</t>
@@ -2558,22 +2558,22 @@
     <t xml:space="preserve">5.12626123428345</t>
   </si>
   <si>
-    <t xml:space="preserve">5.13456964492798</t>
+    <t xml:space="preserve">5.13456916809082</t>
   </si>
   <si>
     <t xml:space="preserve">5.10272121429443</t>
   </si>
   <si>
-    <t xml:space="preserve">5.15257215499878</t>
+    <t xml:space="preserve">5.1525707244873</t>
   </si>
   <si>
     <t xml:space="preserve">5.35751104354858</t>
   </si>
   <si>
-    <t xml:space="preserve">5.43782615661621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.46552038192749</t>
+    <t xml:space="preserve">5.43782567977905</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.46551990509033</t>
   </si>
   <si>
     <t xml:space="preserve">5.51536989212036</t>
@@ -2594,97 +2594,97 @@
     <t xml:space="preserve">6.19804048538208</t>
   </si>
   <si>
-    <t xml:space="preserve">6.00694847106934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.93771171569824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.62476301193237</t>
+    <t xml:space="preserve">6.00694799423218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.9377121925354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.62476348876953</t>
   </si>
   <si>
     <t xml:space="preserve">5.71061658859253</t>
   </si>
   <si>
-    <t xml:space="preserve">5.75908184051514</t>
+    <t xml:space="preserve">5.75908231735229</t>
   </si>
   <si>
     <t xml:space="preserve">5.87539911270142</t>
   </si>
   <si>
-    <t xml:space="preserve">5.84909009933472</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.80754709243774</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.69123125076294</t>
+    <t xml:space="preserve">5.8490891456604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.8075475692749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.69122982025146</t>
   </si>
   <si>
     <t xml:space="preserve">5.80849361419678</t>
   </si>
   <si>
-    <t xml:space="preserve">5.90777206420898</t>
+    <t xml:space="preserve">5.90777158737183</t>
   </si>
   <si>
     <t xml:space="preserve">5.64590787887573</t>
   </si>
   <si>
-    <t xml:space="preserve">5.686194896698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.57252836227417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.74230861663818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.56821155548096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.57828378677368</t>
+    <t xml:space="preserve">5.68619394302368</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.57252788543701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.74230766296387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.56821203231812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.57828426361084</t>
   </si>
   <si>
     <t xml:space="preserve">5.60274314880371</t>
   </si>
   <si>
-    <t xml:space="preserve">5.69338798522949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.66173458099365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.61713171005249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.48476028442383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.5322413444519</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.63727521896362</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.61569356918335</t>
+    <t xml:space="preserve">5.69338846206665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.66173362731934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.61713123321533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.48476076126099</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.53224182128906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.63727474212646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.61569309234619</t>
   </si>
   <si>
     <t xml:space="preserve">5.64015245437622</t>
   </si>
   <si>
-    <t xml:space="preserve">5.65597915649414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.88906764984131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.93223142623901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.9854679107666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.89050626754761</t>
+    <t xml:space="preserve">5.6559796333313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.88906717300415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.93223190307617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.98546743392944</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.89050579071045</t>
   </si>
   <si>
     <t xml:space="preserve">5.86172962188721</t>
@@ -2693,13 +2693,13 @@
     <t xml:space="preserve">5.71497011184692</t>
   </si>
   <si>
-    <t xml:space="preserve">5.6833176612854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.66892910003662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.4746880531311</t>
+    <t xml:space="preserve">5.68331670761108</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.66892957687378</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.47468852996826</t>
   </si>
   <si>
     <t xml:space="preserve">5.57684469223022</t>
@@ -2711,7 +2711,7 @@
     <t xml:space="preserve">5.71928691864014</t>
   </si>
   <si>
-    <t xml:space="preserve">5.71784782409668</t>
+    <t xml:space="preserve">5.71784830093384</t>
   </si>
   <si>
     <t xml:space="preserve">5.6286416053772</t>
@@ -2723,61 +2723,61 @@
     <t xml:space="preserve">5.77252340316772</t>
   </si>
   <si>
-    <t xml:space="preserve">5.86460828781128</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.85741376876831</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.78691053390503</t>
+    <t xml:space="preserve">5.86460781097412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.85741281509399</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.78691148757935</t>
   </si>
   <si>
     <t xml:space="preserve">5.76245212554932</t>
   </si>
   <si>
-    <t xml:space="preserve">5.67180633544922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.65310144424438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.71209287643433</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.61425304412842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.69051122665405</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.70921564102173</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.64302921295166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.64734649658203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.5638952255249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.52216958999634</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.53368043899536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.72504281997681</t>
+    <t xml:space="preserve">5.6718053817749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.6531023979187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.71209335327148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.61425399780273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.69051074981689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.70921516418457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.64302968978882</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.64734745025635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.56389617919922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.5221700668335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.5336799621582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.72504234313965</t>
   </si>
   <si>
     <t xml:space="preserve">5.60705995559692</t>
   </si>
   <si>
-    <t xml:space="preserve">5.74086952209473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.73079824447632</t>
+    <t xml:space="preserve">5.74086904525757</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.730797290802</t>
   </si>
   <si>
     <t xml:space="preserve">5.73367547988892</t>
@@ -2786,49 +2786,49 @@
     <t xml:space="preserve">5.70058250427246</t>
   </si>
   <si>
-    <t xml:space="preserve">5.58403873443604</t>
+    <t xml:space="preserve">5.58403921127319</t>
   </si>
   <si>
     <t xml:space="preserve">5.38979864120483</t>
   </si>
   <si>
-    <t xml:space="preserve">5.46605587005615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.51065969467163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.49914884567261</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.45742321014404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.56101846694946</t>
+    <t xml:space="preserve">5.46605539321899</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.51065921783447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.49914836883545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.45742273330688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.5610179901123</t>
   </si>
   <si>
     <t xml:space="preserve">5.45022916793823</t>
   </si>
   <si>
-    <t xml:space="preserve">5.44447326660156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.40418672561646</t>
+    <t xml:space="preserve">5.44447374343872</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.40418720245361</t>
   </si>
   <si>
     <t xml:space="preserve">5.43584108352661</t>
   </si>
   <si>
-    <t xml:space="preserve">5.81856536865234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.76820707321167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.76532888412476</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.76676845550537</t>
+    <t xml:space="preserve">5.8185658454895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.76820659637451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.76532936096191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.76676797866821</t>
   </si>
   <si>
     <t xml:space="preserve">5.77971792221069</t>
@@ -2840,10 +2840,10 @@
     <t xml:space="preserve">5.49195432662964</t>
   </si>
   <si>
-    <t xml:space="preserve">5.55957889556885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.56677293777466</t>
+    <t xml:space="preserve">5.55957937240601</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.56677341461182</t>
   </si>
   <si>
     <t xml:space="preserve">5.46317768096924</t>
@@ -2855,10 +2855,10 @@
     <t xml:space="preserve">5.4617395401001</t>
   </si>
   <si>
-    <t xml:space="preserve">5.3739709854126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.33512449264526</t>
+    <t xml:space="preserve">5.37397146224976</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.33512353897095</t>
   </si>
   <si>
     <t xml:space="preserve">5.11066865921021</t>
@@ -2870,37 +2870,37 @@
     <t xml:space="preserve">5.03585052490234</t>
   </si>
   <si>
-    <t xml:space="preserve">5.15671062469482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.20563077926636</t>
+    <t xml:space="preserve">5.15671157836914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.2056303024292</t>
   </si>
   <si>
     <t xml:space="preserve">5.36965560913086</t>
   </si>
   <si>
-    <t xml:space="preserve">5.54663038253784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.45598459243774</t>
+    <t xml:space="preserve">5.54662990570068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.45598411560059</t>
   </si>
   <si>
     <t xml:space="preserve">5.64878511428833</t>
   </si>
   <si>
-    <t xml:space="preserve">5.78835010528564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.74662494659424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.92072153091431</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.11783933639526</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.1969747543335</t>
+    <t xml:space="preserve">5.78834915161133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.74662399291992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.92072105407715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.11783790588379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.19697284698486</t>
   </si>
   <si>
     <t xml:space="preserve">6.30200719833374</t>
@@ -2909,25 +2909,25 @@
     <t xml:space="preserve">6.36963224411011</t>
   </si>
   <si>
-    <t xml:space="preserve">6.2717924118042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.30493831634521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.44713306427002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.38556432723999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.45006704330444</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.26242542266846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.31226968765259</t>
+    <t xml:space="preserve">6.27179193496704</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.30494022369385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.44713354110718</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.38556528091431</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.45006608963013</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.26242685317993</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.31226825714111</t>
   </si>
   <si>
     <t xml:space="preserve">6.21111965179443</t>
@@ -2939,61 +2939,61 @@
     <t xml:space="preserve">6.16274404525757</t>
   </si>
   <si>
-    <t xml:space="preserve">6.1524829864502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.16127824783325</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.17007398605347</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.12023258209229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.11583423614502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.21405124664307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.14955139160156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.12609672546387</t>
+    <t xml:space="preserve">6.15248346328735</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.16127872467041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.17007446289062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.12023210525513</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.11583566665649</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.21405172348022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.1495509147644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.12609577178955</t>
   </si>
   <si>
     <t xml:space="preserve">5.98536777496338</t>
   </si>
   <si>
-    <t xml:space="preserve">6.10850477218628</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.13342618942261</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.09824419021606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.11436891555786</t>
+    <t xml:space="preserve">6.10850429534912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.13342571258545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.09824323654175</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.11436939239502</t>
   </si>
   <si>
     <t xml:space="preserve">6.07478904724121</t>
   </si>
   <si>
-    <t xml:space="preserve">6.2594952583313</t>
+    <t xml:space="preserve">6.25949478149414</t>
   </si>
   <si>
     <t xml:space="preserve">6.38996267318726</t>
   </si>
   <si>
-    <t xml:space="preserve">6.29907464981079</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.25509786605835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.18180179595947</t>
+    <t xml:space="preserve">6.29907512664795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.25509881973267</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.18180084228516</t>
   </si>
   <si>
     <t xml:space="preserve">6.12169885635376</t>
@@ -3002,85 +3002,85 @@
     <t xml:space="preserve">6.14222192764282</t>
   </si>
   <si>
-    <t xml:space="preserve">6.09091424942017</t>
+    <t xml:space="preserve">6.09091472625732</t>
   </si>
   <si>
     <t xml:space="preserve">6.15394926071167</t>
   </si>
   <si>
-    <t xml:space="preserve">6.09677743911743</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.06012964248657</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.01615190505981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.12902784347534</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.98096990585327</t>
+    <t xml:space="preserve">6.09677791595459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.06012916564941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.01615238189697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.12902879714966</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.98096895217896</t>
   </si>
   <si>
     <t xml:space="preserve">6.03520917892456</t>
   </si>
   <si>
-    <t xml:space="preserve">5.91940116882324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.07918691635132</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.06892538070679</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.50137376785278</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.6054539680481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.75791025161743</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.93088960647583</t>
+    <t xml:space="preserve">5.91940069198608</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.079185962677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.06892490386963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.50137233734131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.60545253753662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.75791072845459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.93088912963867</t>
   </si>
   <si>
     <t xml:space="preserve">7.01444673538208</t>
   </si>
   <si>
-    <t xml:space="preserve">6.9734001159668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.07308292388916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.0936074256897</t>
+    <t xml:space="preserve">6.97340106964111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.073082447052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.09360694885254</t>
   </si>
   <si>
     <t xml:space="preserve">7.16103887557983</t>
   </si>
   <si>
-    <t xml:space="preserve">7.07454872131348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.94994592666626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.81947803497314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.88837575912476</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.06868505477905</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.9836630821228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.99978733062744</t>
+    <t xml:space="preserve">7.07454967498779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.94994640350342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.81947898864746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.88837718963623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.06868553161621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.98366165161133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.99978828430176</t>
   </si>
   <si>
     <t xml:space="preserve">7.04229879379272</t>
@@ -3089,16 +3089,16 @@
     <t xml:space="preserve">6.89277505874634</t>
   </si>
   <si>
-    <t xml:space="preserve">7.20355081558228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.23873233795166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.29297208786011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.31056308746338</t>
+    <t xml:space="preserve">7.20355033874512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.23873138427734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.29297256469727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.31056213378906</t>
   </si>
   <si>
     <t xml:space="preserve">7.21967506408691</t>
@@ -3107,79 +3107,79 @@
     <t xml:space="preserve">7.35893821716309</t>
   </si>
   <si>
-    <t xml:space="preserve">7.43223476409912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.49820041656494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.46521902084351</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.53118371963501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.48720693588257</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.64845943450928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.60814571380615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.66311740875244</t>
+    <t xml:space="preserve">7.4322361946106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.4982008934021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.46521711349487</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.53118515014648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.48720741271973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.64845895767212</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.60814619064331</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.66311693191528</t>
   </si>
   <si>
     <t xml:space="preserve">7.57882690429688</t>
   </si>
   <si>
-    <t xml:space="preserve">7.69976472854614</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.63380002975464</t>
+    <t xml:space="preserve">7.69976615905762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.63379955291748</t>
   </si>
   <si>
     <t xml:space="preserve">7.67411327362061</t>
   </si>
   <si>
-    <t xml:space="preserve">7.66678047180176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.73274946212769</t>
+    <t xml:space="preserve">7.66678285598755</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.73274898529053</t>
   </si>
   <si>
     <t xml:space="preserve">7.90133047103882</t>
   </si>
   <si>
-    <t xml:space="preserve">7.95630121231079</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.94530868530273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.99661445617676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.01860427856445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.00761032104492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.89400053024292</t>
+    <t xml:space="preserve">7.95630216598511</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.94530963897705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.99661493301392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.01860332489014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.00760936737061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.89400005340576</t>
   </si>
   <si>
     <t xml:space="preserve">7.91232395172119</t>
   </si>
   <si>
-    <t xml:space="preserve">7.90499448776245</t>
+    <t xml:space="preserve">7.90499687194824</t>
   </si>
   <si>
     <t xml:space="preserve">7.81703853607178</t>
   </si>
   <si>
-    <t xml:space="preserve">7.80970907211304</t>
+    <t xml:space="preserve">7.80971050262451</t>
   </si>
   <si>
     <t xml:space="preserve">7.89766454696655</t>
@@ -3188,49 +3188,49 @@
     <t xml:space="preserve">7.88667106628418</t>
   </si>
   <si>
-    <t xml:space="preserve">7.78039216995239</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.77672529220581</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.95263814926147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.92331838607788</t>
+    <t xml:space="preserve">7.78039121627808</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.77672672271729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.95263767242432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.9233193397522</t>
   </si>
   <si>
     <t xml:space="preserve">7.93431425094604</t>
   </si>
   <si>
-    <t xml:space="preserve">8.00394344329834</t>
+    <t xml:space="preserve">8.00394535064697</t>
   </si>
   <si>
     <t xml:space="preserve">8.00027942657471</t>
   </si>
   <si>
-    <t xml:space="preserve">7.98928594589233</t>
+    <t xml:space="preserve">7.98928546905518</t>
   </si>
   <si>
     <t xml:space="preserve">8.09922981262207</t>
   </si>
   <si>
-    <t xml:space="preserve">8.04059314727783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.0112771987915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.06258296966553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.22749614715576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.19085121154785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.08823585510254</t>
+    <t xml:space="preserve">8.04059410095215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.01127529144287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.06258106231689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.22749900817871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.19084930419922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.08823490142822</t>
   </si>
   <si>
     <t xml:space="preserve">8.09190082550049</t>
@@ -3239,28 +3239,28 @@
     <t xml:space="preserve">8.15053749084473</t>
   </si>
   <si>
-    <t xml:space="preserve">8.27514266967773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.26414585113525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.23116397857666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.30079364776611</t>
+    <t xml:space="preserve">8.27513980865479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.26414680480957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.23116302490234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.30079555511475</t>
   </si>
   <si>
     <t xml:space="preserve">8.42906284332275</t>
   </si>
   <si>
-    <t xml:space="preserve">8.57565593719482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.46204662322998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.37042617797852</t>
+    <t xml:space="preserve">8.57565498352051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.46204566955566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.3704252243042</t>
   </si>
   <si>
     <t xml:space="preserve">8.42173385620117</t>
@@ -3269,22 +3269,22 @@
     <t xml:space="preserve">8.43272876739502</t>
   </si>
   <si>
-    <t xml:space="preserve">8.47670459747314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.64895057678223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.72957801818848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.83952140808105</t>
+    <t xml:space="preserve">8.47670555114746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.64895153045654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.72957706451416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.83952331542969</t>
   </si>
   <si>
     <t xml:space="preserve">8.85418128967285</t>
   </si>
   <si>
-    <t xml:space="preserve">8.78454780578613</t>
+    <t xml:space="preserve">8.78454971313477</t>
   </si>
   <si>
     <t xml:space="preserve">8.80653953552246</t>
@@ -3293,49 +3293,49 @@
     <t xml:space="preserve">8.78088474273682</t>
   </si>
   <si>
-    <t xml:space="preserve">8.84685134887695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.79187870025635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.57199001312256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.68054485321045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.56369876861572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.46192646026611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.61269569396973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.58631420135498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.44685077667236</t>
+    <t xml:space="preserve">8.84685039520264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.79187774658203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.57199096679688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.68054389953613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.56369781494141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.46192932128906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.61269855499268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.5863151550293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.44684982299805</t>
   </si>
   <si>
     <t xml:space="preserve">8.40915870666504</t>
   </si>
   <si>
-    <t xml:space="preserve">8.4053897857666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.50338840484619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.42800617218018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.54862117767334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.42046642303467</t>
+    <t xml:space="preserve">8.40538883209229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.50339031219482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.42800521850586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.54862213134766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.42046737670898</t>
   </si>
   <si>
     <t xml:space="preserve">8.45439052581787</t>
@@ -3344,82 +3344,82 @@
     <t xml:space="preserve">8.16039085388184</t>
   </si>
   <si>
-    <t xml:space="preserve">8.28854465484619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.31869792938232</t>
+    <t xml:space="preserve">8.28854370117188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.31869697570801</t>
   </si>
   <si>
     <t xml:space="preserve">8.31492900848389</t>
   </si>
   <si>
-    <t xml:space="preserve">8.28477573394775</t>
+    <t xml:space="preserve">8.28477478027344</t>
   </si>
   <si>
     <t xml:space="preserve">8.17169857025146</t>
   </si>
   <si>
-    <t xml:space="preserve">8.19808387756348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.91915798187256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.9983115196228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.25085067749023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.37523555755615</t>
+    <t xml:space="preserve">8.19808197021484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.91915893554688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.99831342697144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.25085163116455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.37523651123047</t>
   </si>
   <si>
     <t xml:space="preserve">8.45062065124512</t>
   </si>
   <si>
-    <t xml:space="preserve">8.51846694946289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.43554496765137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.41669750213623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.3865442276001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.55992794036865</t>
+    <t xml:space="preserve">8.51846790313721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.43554401397705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.41669845581055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.38654232025146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.55992984771729</t>
   </si>
   <si>
     <t xml:space="preserve">8.68808174133301</t>
   </si>
   <si>
-    <t xml:space="preserve">8.72954368591309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.76346588134766</t>
+    <t xml:space="preserve">8.7295446395874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.76346683502197</t>
   </si>
   <si>
     <t xml:space="preserve">8.8350830078125</t>
   </si>
   <si>
-    <t xml:space="preserve">8.853928565979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.80869770050049</t>
+    <t xml:space="preserve">8.85393047332764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.8086986541748</t>
   </si>
   <si>
     <t xml:space="preserve">8.75216007232666</t>
   </si>
   <si>
-    <t xml:space="preserve">8.70316028594971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.77477550506592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.66546726226807</t>
+    <t xml:space="preserve">8.70315933227539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.7747745513916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.66546630859375</t>
   </si>
   <si>
     <t xml:space="preserve">8.60139083862305</t>
@@ -3428,19 +3428,19 @@
     <t xml:space="preserve">8.78985118865967</t>
   </si>
   <si>
-    <t xml:space="preserve">8.76723670959473</t>
+    <t xml:space="preserve">8.76723766326904</t>
   </si>
   <si>
     <t xml:space="preserve">8.73708248138428</t>
   </si>
   <si>
-    <t xml:space="preserve">8.65792751312256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.6956205368042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.74085330963135</t>
+    <t xml:space="preserve">8.65792942047119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.69562149047852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.74085235595703</t>
   </si>
   <si>
     <t xml:space="preserve">8.77100467681885</t>
@@ -3449,52 +3449,52 @@
     <t xml:space="preserve">8.63908195495605</t>
   </si>
   <si>
-    <t xml:space="preserve">8.69939041137695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.71446800231934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.79362106323242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.93308448791504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.85015773773193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.88408184051514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.96323585510254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.02731418609619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.9933910369873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.07631206512451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.85769844055176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.91800594329834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.9745454788208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.93685150146484</t>
+    <t xml:space="preserve">8.69939136505127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.71446704864502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.79362201690674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.93308353424072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.85015964508057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.88408374786377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.96323680877686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.02731513977051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.99339008331299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.07631397247314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.85769748687744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.91800498962402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.97454452514648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.93685245513916</t>
   </si>
   <si>
     <t xml:space="preserve">9.11777496337891</t>
   </si>
   <si>
-    <t xml:space="preserve">9.06500625610352</t>
+    <t xml:space="preserve">9.0650053024292</t>
   </si>
   <si>
     <t xml:space="preserve">9.1780834197998</t>
@@ -3506,58 +3506,58 @@
     <t xml:space="preserve">9.16677570343018</t>
   </si>
   <si>
-    <t xml:space="preserve">9.28739070892334</t>
+    <t xml:space="preserve">9.28738975524902</t>
   </si>
   <si>
     <t xml:space="preserve">9.32131385803223</t>
   </si>
   <si>
-    <t xml:space="preserve">9.42308235168457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.36654472351074</t>
+    <t xml:space="preserve">9.42308330535889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.36654376983643</t>
   </si>
   <si>
     <t xml:space="preserve">9.33639144897461</t>
   </si>
   <si>
-    <t xml:space="preserve">9.23462104797363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.46454429626465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.43062210083008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.41177463531494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.555006980896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.47208309173584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.45700454711914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.30246829986572</t>
+    <t xml:space="preserve">9.23462200164795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.46454524993896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.43062114715576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.41177558898926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.55500793457031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.47208213806152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.45700645446777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.30246639251709</t>
   </si>
   <si>
     <t xml:space="preserve">9.38162136077881</t>
   </si>
   <si>
-    <t xml:space="preserve">9.34769821166992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.46077632904053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.39292907714844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.41931343078613</t>
+    <t xml:space="preserve">9.34769725799561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.46077537536621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.39293003082275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.41931438446045</t>
   </si>
   <si>
     <t xml:space="preserve">9.37785148620605</t>
@@ -3566,49 +3566,49 @@
     <t xml:space="preserve">9.28362083435059</t>
   </si>
   <si>
-    <t xml:space="preserve">9.2308521270752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.24215984344482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.15546798706055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.09515857696533</t>
+    <t xml:space="preserve">9.23085308074951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.24215888977051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.15546703338623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.09516048431396</t>
   </si>
   <si>
     <t xml:space="preserve">9.07601928710938</t>
   </si>
   <si>
-    <t xml:space="preserve">9.00328922271729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.97649478912354</t>
+    <t xml:space="preserve">9.0032901763916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.97649383544922</t>
   </si>
   <si>
     <t xml:space="preserve">8.84251594543457</t>
   </si>
   <si>
-    <t xml:space="preserve">8.47886180877686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.57073402404785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.52862739562988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.68939971923828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.5975284576416</t>
+    <t xml:space="preserve">8.47886276245117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.57073211669922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.52862548828125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.6894006729126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.59752750396729</t>
   </si>
   <si>
     <t xml:space="preserve">8.5324535369873</t>
   </si>
   <si>
-    <t xml:space="preserve">8.56307888031006</t>
+    <t xml:space="preserve">8.56307697296143</t>
   </si>
   <si>
     <t xml:space="preserve">8.68174362182617</t>
@@ -3617,64 +3617,64 @@
     <t xml:space="preserve">8.55924987792969</t>
   </si>
   <si>
-    <t xml:space="preserve">8.49800205230713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.45972347259521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.46355152130127</t>
+    <t xml:space="preserve">8.49800395965576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.4597225189209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.46355247497559</t>
   </si>
   <si>
     <t xml:space="preserve">8.48269176483154</t>
   </si>
   <si>
-    <t xml:space="preserve">8.52097129821777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.58221626281738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.59369945526123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.39847564697266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.53628158569336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.62049674987793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.69705581665039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.77361297607422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.84634590148926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.82720470428467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.83486080169678</t>
+    <t xml:space="preserve">8.52097034454346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.5822172164917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.59370231628418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.39847660064697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.53628253936768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.62049770355225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.69705486297607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.77361392974854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.84634494781494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.82720375061035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.83485984802246</t>
   </si>
   <si>
     <t xml:space="preserve">8.961181640625</t>
   </si>
   <si>
-    <t xml:space="preserve">8.97266674041748</t>
+    <t xml:space="preserve">8.97266483306885</t>
   </si>
   <si>
     <t xml:space="preserve">9.00711727142334</t>
   </si>
   <si>
-    <t xml:space="preserve">8.9305591583252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.95735454559326</t>
+    <t xml:space="preserve">8.93055820465088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.95735549926758</t>
   </si>
   <si>
     <t xml:space="preserve">8.98414993286133</t>
@@ -3692,7 +3692,7 @@
     <t xml:space="preserve">8.85400009155273</t>
   </si>
   <si>
-    <t xml:space="preserve">8.87313938140869</t>
+    <t xml:space="preserve">8.87314033508301</t>
   </si>
   <si>
     <t xml:space="preserve">8.9458703994751</t>
@@ -3707,13 +3707,13 @@
     <t xml:space="preserve">8.647292137146</t>
   </si>
   <si>
-    <t xml:space="preserve">8.83868980407715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.73150634765625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.13343906402588</t>
+    <t xml:space="preserve">8.83868789672852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.73150730133057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.1334400177002</t>
   </si>
   <si>
     <t xml:space="preserve">9.14109420776367</t>
@@ -3722,7 +3722,7 @@
     <t xml:space="preserve">8.33722972869873</t>
   </si>
   <si>
-    <t xml:space="preserve">8.39082050323486</t>
+    <t xml:space="preserve">8.39081954956055</t>
   </si>
   <si>
     <t xml:space="preserve">8.42910003662109</t>
@@ -3734,211 +3734,211 @@
     <t xml:space="preserve">8.41761684417725</t>
   </si>
   <si>
-    <t xml:space="preserve">8.49417495727539</t>
+    <t xml:space="preserve">8.49417400360107</t>
   </si>
   <si>
     <t xml:space="preserve">8.52479839324951</t>
   </si>
   <si>
-    <t xml:space="preserve">8.44824028015137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.24153137207031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.21090888977051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.14200592041016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.68648195266724</t>
+    <t xml:space="preserve">8.44823932647705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.24153232574463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.21090793609619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.14200496673584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.68648242950439</t>
   </si>
   <si>
     <t xml:space="preserve">7.939124584198</t>
   </si>
   <si>
-    <t xml:space="preserve">7.86639356613159</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.54867696762085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.53642702102661</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.43077659606934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.95151996612549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.80146503448486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.11688566207886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.74772787094116</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.35574865341187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.40015316009521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.60073614120483</t>
+    <t xml:space="preserve">7.86639404296875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.54867601394653</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.53642654418945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.43077611923218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.95151948928833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.80146408081055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.1168851852417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.74772977828979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.35574817657471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.40015363693237</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.60073757171631</t>
   </si>
   <si>
     <t xml:space="preserve">7.55939388275146</t>
   </si>
   <si>
-    <t xml:space="preserve">7.90084505081177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.736243724823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.7132773399353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.74390125274658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.94678163528442</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.9352970123291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.07693099975586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.96974849700928</t>
+    <t xml:space="preserve">7.90084600448608</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.73624467849731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.71327781677246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.74390077590942</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.94678020477295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.93529796600342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.07693004608154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.96974802017212</t>
   </si>
   <si>
     <t xml:space="preserve">8.06161880493164</t>
   </si>
   <si>
-    <t xml:space="preserve">8.13052177429199</t>
+    <t xml:space="preserve">8.13052082061768</t>
   </si>
   <si>
     <t xml:space="preserve">8.09607028961182</t>
   </si>
   <si>
-    <t xml:space="preserve">7.96209239959717</t>
+    <t xml:space="preserve">7.96209144592285</t>
   </si>
   <si>
     <t xml:space="preserve">7.84342622756958</t>
   </si>
   <si>
-    <t xml:space="preserve">7.67499828338623</t>
+    <t xml:space="preserve">7.67499732971191</t>
   </si>
   <si>
     <t xml:space="preserve">7.55786323547363</t>
   </si>
   <si>
-    <t xml:space="preserve">7.70562028884888</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.64360904693604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.52877044677734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.45221185684204</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.51192760467529</t>
+    <t xml:space="preserve">7.70562219619751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.64361047744751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.5287709236145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.45221376419067</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.51192808151245</t>
   </si>
   <si>
     <t xml:space="preserve">7.39096593856812</t>
   </si>
   <si>
-    <t xml:space="preserve">7.58542442321777</t>
+    <t xml:space="preserve">7.58542490005493</t>
   </si>
   <si>
     <t xml:space="preserve">7.56092596054077</t>
   </si>
   <si>
-    <t xml:space="preserve">7.42771244049072</t>
+    <t xml:space="preserve">7.42771291732788</t>
   </si>
   <si>
     <t xml:space="preserve">7.21794462203979</t>
   </si>
   <si>
-    <t xml:space="preserve">7.1214804649353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.09851217269897</t>
+    <t xml:space="preserve">7.12147951126099</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.09851121902466</t>
   </si>
   <si>
     <t xml:space="preserve">7.144446849823</t>
   </si>
   <si>
-    <t xml:space="preserve">7.17966413497925</t>
+    <t xml:space="preserve">7.17966508865356</t>
   </si>
   <si>
     <t xml:space="preserve">7.10769987106323</t>
   </si>
   <si>
-    <t xml:space="preserve">7.05104541778564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.99592304229736</t>
+    <t xml:space="preserve">7.05104637145996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.99592256546021</t>
   </si>
   <si>
     <t xml:space="preserve">6.89180326461792</t>
   </si>
   <si>
-    <t xml:space="preserve">6.71265602111816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.87189817428589</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.03114032745361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.25162935256958</t>
+    <t xml:space="preserve">6.71265554428101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.87189865112305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.03113985061646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.25162887573242</t>
   </si>
   <si>
     <t xml:space="preserve">7.40321493148804</t>
   </si>
   <si>
-    <t xml:space="preserve">7.29909610748291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.36799812316895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.32359409332275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.29756450653076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.27612686157227</t>
+    <t xml:space="preserve">7.29909420013428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.3679986000061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.32359457015991</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.29756546020508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.27612733840942</t>
   </si>
   <si>
     <t xml:space="preserve">7.41852569580078</t>
   </si>
   <si>
-    <t xml:space="preserve">7.29297065734863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.41393184661865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.46599245071411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.60379886627197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.77069664001465</t>
+    <t xml:space="preserve">7.29297161102295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.4139347076416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.46599292755127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.60379981994629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.77069473266602</t>
   </si>
   <si>
     <t xml:space="preserve">7.67117071151733</t>
@@ -3950,25 +3950,25 @@
     <t xml:space="preserve">7.59461116790771</t>
   </si>
   <si>
-    <t xml:space="preserve">7.74007272720337</t>
+    <t xml:space="preserve">7.74007225036621</t>
   </si>
   <si>
     <t xml:space="preserve">7.72476196289062</t>
   </si>
   <si>
-    <t xml:space="preserve">7.61757946014404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.00664234161377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.77237129211426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.98061084747314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.21028709411621</t>
+    <t xml:space="preserve">7.61757898330688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.00664186477661</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.77237224578857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.9806113243103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.21028804779053</t>
   </si>
   <si>
     <t xml:space="preserve">6.8519926071167</t>
@@ -3977,58 +3977,58 @@
     <t xml:space="preserve">6.88721036911011</t>
   </si>
   <si>
-    <t xml:space="preserve">7.04995107650757</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.9906268119812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.0226936340332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.96818017959595</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.17180585861206</t>
+    <t xml:space="preserve">7.04994916915894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.99062633514404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.02269268035889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.96817922592163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.1718053817749</t>
   </si>
   <si>
     <t xml:space="preserve">7.13653230667114</t>
   </si>
   <si>
-    <t xml:space="preserve">7.27923059463501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.22471618652344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.14454936981201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.14775609970093</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.14134120941162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.85434198379517</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.89763212203979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.07560348510742</t>
+    <t xml:space="preserve">7.27922964096069</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.2247166633606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.1445484161377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.14775562286377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.14134216308594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.85434150695801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.89763164520264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.07560396194458</t>
   </si>
   <si>
     <t xml:space="preserve">6.96497297286987</t>
   </si>
   <si>
-    <t xml:space="preserve">6.83349800109863</t>
+    <t xml:space="preserve">6.83349752426147</t>
   </si>
   <si>
     <t xml:space="preserve">6.8639612197876</t>
   </si>
   <si>
-    <t xml:space="preserve">6.71965932846069</t>
+    <t xml:space="preserve">6.71965980529785</t>
   </si>
   <si>
     <t xml:space="preserve">6.37814474105835</t>
@@ -4037,7 +4037,7 @@
     <t xml:space="preserve">6.54008340835571</t>
   </si>
   <si>
-    <t xml:space="preserve">6.66354179382324</t>
+    <t xml:space="preserve">6.6635422706604</t>
   </si>
   <si>
     <t xml:space="preserve">6.88480520248413</t>
@@ -4046,7 +4046,7 @@
     <t xml:space="preserve">6.73248624801636</t>
   </si>
   <si>
-    <t xml:space="preserve">6.40379905700684</t>
+    <t xml:space="preserve">6.40379858016968</t>
   </si>
   <si>
     <t xml:space="preserve">6.48877668380737</t>
@@ -4055,52 +4055,52 @@
     <t xml:space="preserve">6.51603317260742</t>
   </si>
   <si>
-    <t xml:space="preserve">6.50160312652588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.51282644271851</t>
+    <t xml:space="preserve">6.50160264968872</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.51282691955566</t>
   </si>
   <si>
     <t xml:space="preserve">6.45831251144409</t>
   </si>
   <si>
-    <t xml:space="preserve">6.54970455169678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.61383819580078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.53367042541504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.64430141448975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.72126293182373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.79661989212036</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.73408937454224</t>
+    <t xml:space="preserve">6.54970359802246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.61383771896362</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.53366994857788</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.6443018913269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.72126245498657</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.79662084579468</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.73408889770508</t>
   </si>
   <si>
     <t xml:space="preserve">6.69721269607544</t>
   </si>
   <si>
-    <t xml:space="preserve">6.73729610443115</t>
+    <t xml:space="preserve">6.73729658126831</t>
   </si>
   <si>
     <t xml:space="preserve">6.83670425415039</t>
   </si>
   <si>
-    <t xml:space="preserve">6.84311771392822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.78539705276489</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.69560956954956</t>
+    <t xml:space="preserve">6.84311819076538</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.78539657592773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.69560861587524</t>
   </si>
   <si>
     <t xml:space="preserve">6.57375431060791</t>
@@ -4109,10 +4109,10 @@
     <t xml:space="preserve">6.40700531005859</t>
   </si>
   <si>
-    <t xml:space="preserve">6.50481033325195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.47274255752563</t>
+    <t xml:space="preserve">6.50480985641479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.47274303436279</t>
   </si>
   <si>
     <t xml:space="preserve">6.45189952850342</t>
@@ -4127,22 +4127,22 @@
     <t xml:space="preserve">6.37012815475464</t>
   </si>
   <si>
-    <t xml:space="preserve">6.32202768325806</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.49358654022217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.32523345947266</t>
+    <t xml:space="preserve">6.3220272064209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.49358701705933</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.32523393630981</t>
   </si>
   <si>
     <t xml:space="preserve">6.39738512039185</t>
   </si>
   <si>
-    <t xml:space="preserve">6.41502237319946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.4823637008667</t>
+    <t xml:space="preserve">6.4150218963623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.48236322402954</t>
   </si>
   <si>
     <t xml:space="preserve">6.58177089691162</t>
@@ -4154,10 +4154,10 @@
     <t xml:space="preserve">6.68278217315674</t>
   </si>
   <si>
-    <t xml:space="preserve">6.73569345474243</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.63147497177124</t>
+    <t xml:space="preserve">6.73569393157959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.6314754486084</t>
   </si>
   <si>
     <t xml:space="preserve">6.66033506393433</t>
@@ -4169,7 +4169,7 @@
     <t xml:space="preserve">6.51763725280762</t>
   </si>
   <si>
-    <t xml:space="preserve">6.33004474639893</t>
+    <t xml:space="preserve">6.33004426956177</t>
   </si>
   <si>
     <t xml:space="preserve">6.39417839050293</t>
@@ -4178,16 +4178,16 @@
     <t xml:space="preserve">6.26109981536865</t>
   </si>
   <si>
-    <t xml:space="preserve">6.26911640167236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.13924551010132</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.24506616592407</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.3733344078064</t>
+    <t xml:space="preserve">6.26911735534668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.13924503326416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.24506711959839</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.37333488464355</t>
   </si>
   <si>
     <t xml:space="preserve">6.56092739105225</t>
@@ -4196,31 +4196,31 @@
     <t xml:space="preserve">6.4663290977478</t>
   </si>
   <si>
-    <t xml:space="preserve">6.35730075836182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.27071952819824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.28514957427979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.14084911346436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.24185943603516</t>
+    <t xml:space="preserve">6.35730123519897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.2707200050354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.2851505279541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.14084815979004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.24185991287231</t>
   </si>
   <si>
     <t xml:space="preserve">6.3364577293396</t>
   </si>
   <si>
-    <t xml:space="preserve">6.49519014358521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.73088264465332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.69400596618652</t>
+    <t xml:space="preserve">6.49518966674805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.73088312149048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.69400691986084</t>
   </si>
   <si>
     <t xml:space="preserve">6.67155838012695</t>
@@ -4232,160 +4232,160 @@
     <t xml:space="preserve">6.75974369049072</t>
   </si>
   <si>
-    <t xml:space="preserve">6.82227420806885</t>
+    <t xml:space="preserve">6.82227373123169</t>
   </si>
   <si>
     <t xml:space="preserve">6.88640785217285</t>
   </si>
   <si>
-    <t xml:space="preserve">7.08843088150024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.03391695022583</t>
+    <t xml:space="preserve">7.0884313583374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.03391742706299</t>
   </si>
   <si>
     <t xml:space="preserve">7.07079410552979</t>
   </si>
   <si>
-    <t xml:space="preserve">7.09163665771484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.05476093292236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.01147031784058</t>
+    <t xml:space="preserve">7.09163808822632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.05475997924805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.01147079467773</t>
   </si>
   <si>
     <t xml:space="preserve">7.23593950271606</t>
   </si>
   <si>
-    <t xml:space="preserve">7.35939788818359</t>
+    <t xml:space="preserve">7.35939836502075</t>
   </si>
   <si>
     <t xml:space="preserve">7.40429210662842</t>
   </si>
   <si>
-    <t xml:space="preserve">7.49568367004395</t>
+    <t xml:space="preserve">7.4956841468811</t>
   </si>
   <si>
     <t xml:space="preserve">7.8195595741272</t>
   </si>
   <si>
-    <t xml:space="preserve">7.72656631469727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.7794771194458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.80833625793457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.71534252166748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.66243171691895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.69930934906006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.66488647460938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.62882280349731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.70750617980957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.60751342773438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.74192810058594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.65341186523438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.7222580909729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.69275188446045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.74520635604858</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.72553539276123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.65996885299683</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.7534031867981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.61407136917114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.68455696105957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.68619537353516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.77963066101074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.78126811981201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.37474918365479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.41572904586792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.42228555679321</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.55014181137085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.61243295669556</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.54850292205811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.55670022964478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.56653499603271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.49768733978271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.58128643035889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.47965669631958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.71406221389771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.90584945678711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.79602146148682</t>
+    <t xml:space="preserve">7.72656583786011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.77947664260864</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.80833721160889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.71534156799316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.66243124008179</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.6993088722229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.66488599777222</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.62882328033447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.7075047492981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.60751485824585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.74192953109741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.65341138839722</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.72225856781006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.69275236129761</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.74520587921143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.72553682327271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.65996742248535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.75340270996094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.61407041549683</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.68455743789673</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.68619632720947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.77962970733643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.78126955032349</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.37474775314331</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.41572761535645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.4222846031189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.55014228820801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.6124324798584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.54850339889526</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.5566987991333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.56653451919556</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.49768781661987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.5812873840332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.47965717315674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.71406173706055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.90584754943848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.79602098464966</t>
   </si>
   <si>
     <t xml:space="preserve">7.8730640411377</t>
   </si>
   <si>
-    <t xml:space="preserve">7.85831212997437</t>
+    <t xml:space="preserve">7.85831069946289</t>
   </si>
   <si>
     <t xml:space="preserve">7.95010614395142</t>
@@ -4394,49 +4394,49 @@
     <t xml:space="preserve">7.88125991821289</t>
   </si>
   <si>
-    <t xml:space="preserve">7.95338487625122</t>
+    <t xml:space="preserve">7.95338582992554</t>
   </si>
   <si>
     <t xml:space="preserve">7.974693775177</t>
   </si>
   <si>
-    <t xml:space="preserve">8.01895332336426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.96813774108887</t>
+    <t xml:space="preserve">8.01895236968994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.96813726425171</t>
   </si>
   <si>
     <t xml:space="preserve">8.00419998168945</t>
   </si>
   <si>
-    <t xml:space="preserve">7.82880592346191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.85339450836182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.89109563827515</t>
+    <t xml:space="preserve">7.82880735397339</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.85339307785034</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.8910961151123</t>
   </si>
   <si>
     <t xml:space="preserve">7.89929103851318</t>
   </si>
   <si>
-    <t xml:space="preserve">8.01239585876465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.98616933822632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.02059268951416</t>
+    <t xml:space="preserve">8.01239490509033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.986168384552</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.02059173583984</t>
   </si>
   <si>
     <t xml:space="preserve">8.04518032073975</t>
   </si>
   <si>
-    <t xml:space="preserve">8.35171031951904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.26155376434326</t>
+    <t xml:space="preserve">8.35170841217041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.26155471801758</t>
   </si>
   <si>
     <t xml:space="preserve">8.26974964141846</t>
@@ -4448,19 +4448,19 @@
     <t xml:space="preserve">8.40908241271973</t>
   </si>
   <si>
-    <t xml:space="preserve">8.23696708679199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.35580730438232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.31073093414307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.38449382781982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.38039684295654</t>
+    <t xml:space="preserve">8.23696613311768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.35580825805664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.31072998046875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.38449287414551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.38039588928223</t>
   </si>
   <si>
     <t xml:space="preserve">8.12058258056641</t>
@@ -4472,169 +4472,169 @@
     <t xml:space="preserve">8.07796382904053</t>
   </si>
   <si>
-    <t xml:space="preserve">8.19270801544189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.35990619659424</t>
+    <t xml:space="preserve">8.19270896911621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.35990524291992</t>
   </si>
   <si>
     <t xml:space="preserve">8.23286724090576</t>
   </si>
   <si>
-    <t xml:space="preserve">8.22877025604248</t>
+    <t xml:space="preserve">8.22876930236816</t>
   </si>
   <si>
     <t xml:space="preserve">8.30253410339355</t>
   </si>
   <si>
-    <t xml:space="preserve">8.4541597366333</t>
+    <t xml:space="preserve">8.45415878295898</t>
   </si>
   <si>
     <t xml:space="preserve">8.40088558197021</t>
   </si>
   <si>
-    <t xml:space="preserve">8.37629890441895</t>
+    <t xml:space="preserve">8.37629795074463</t>
   </si>
   <si>
     <t xml:space="preserve">8.31892585754395</t>
   </si>
   <si>
-    <t xml:space="preserve">8.18615055084229</t>
+    <t xml:space="preserve">8.1861515045166</t>
   </si>
   <si>
     <t xml:space="preserve">7.85503244400024</t>
   </si>
   <si>
-    <t xml:space="preserve">7.97961187362671</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.59440040588379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.38622331619263</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.46326494216919</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.71734046936035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.66652536392212</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.68127679824829</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.53702831268311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.67472219467163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.79766082763672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.7124228477478</t>
+    <t xml:space="preserve">7.97961235046387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.59440088272095</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.38622236251831</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.46326589584351</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.71733903884888</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.66652488708496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.68127870559692</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.53702974319458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.67472171783447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.79766035079956</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.71242237091064</t>
   </si>
   <si>
     <t xml:space="preserve">7.64357709884644</t>
   </si>
   <si>
-    <t xml:space="preserve">7.48621416091919</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.57473039627075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.66324710845947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.69603061676025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.8222484588623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.70422744750977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.75668144226074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.83864068984985</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.76160001754761</t>
+    <t xml:space="preserve">7.48621368408203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.57472944259644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.66324758529663</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.69603157043457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.82224893569946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.70422649383545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.75668001174927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.83864164352417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.76159858703613</t>
   </si>
   <si>
     <t xml:space="preserve">7.8517541885376</t>
   </si>
   <si>
-    <t xml:space="preserve">7.77635145187378</t>
+    <t xml:space="preserve">7.77635192871094</t>
   </si>
   <si>
     <t xml:space="preserve">7.71897983551025</t>
   </si>
   <si>
-    <t xml:space="preserve">7.80585765838623</t>
+    <t xml:space="preserve">7.80585813522339</t>
   </si>
   <si>
     <t xml:space="preserve">7.54194641113281</t>
   </si>
   <si>
-    <t xml:space="preserve">7.60915422439575</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.52555465698242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.76651573181152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.80421829223633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.88617706298828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.78946495056152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.87142515182495</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.9419093132019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.89273309707642</t>
+    <t xml:space="preserve">7.60915327072144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.52555418014526</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.76651620864868</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.80421781539917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.88617849349976</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.78946542739868</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.87142419815063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.94191026687622</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.89273452758789</t>
   </si>
   <si>
     <t xml:space="preserve">7.94027137756348</t>
   </si>
   <si>
-    <t xml:space="preserve">7.9140453338623</t>
+    <t xml:space="preserve">7.91404438018799</t>
   </si>
   <si>
     <t xml:space="preserve">8.1386137008667</t>
   </si>
   <si>
-    <t xml:space="preserve">8.11566638946533</t>
+    <t xml:space="preserve">8.1156644821167</t>
   </si>
   <si>
     <t xml:space="preserve">7.93207550048828</t>
   </si>
   <si>
-    <t xml:space="preserve">8.02878761291504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.00747776031494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.94682788848877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.99928331375122</t>
+    <t xml:space="preserve">8.02878856658936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.00747871398926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.94682884216309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.9992823600769</t>
   </si>
   <si>
     <t xml:space="preserve">8.19598579406738</t>
@@ -4646,13 +4646,13 @@
     <t xml:space="preserve">8.1484489440918</t>
   </si>
   <si>
-    <t xml:space="preserve">8.17631530761719</t>
+    <t xml:space="preserve">8.1763162612915</t>
   </si>
   <si>
     <t xml:space="preserve">8.11730480194092</t>
   </si>
   <si>
-    <t xml:space="preserve">8.18778896331787</t>
+    <t xml:space="preserve">8.1877908706665</t>
   </si>
   <si>
     <t xml:space="preserve">8.21237754821777</t>
@@ -4664,55 +4664,55 @@
     <t xml:space="preserve">8.24925899505615</t>
   </si>
   <si>
-    <t xml:space="preserve">8.26841068267822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.18442344665527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.15699768066406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.12443256378174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.16042804718018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.13300323486328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.33182811737061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.43295574188232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.44666767120361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.49808788299561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.47409248352051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.46723461151123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.43467044830322</t>
+    <t xml:space="preserve">8.26840972900391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.18442440032959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.1569995880127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.12443161010742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.16042709350586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.13300228118896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.33182907104492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.43295478820801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.4466667175293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.49808979034424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.47409152984619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.46723651885986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.43466949462891</t>
   </si>
   <si>
     <t xml:space="preserve">8.31126022338867</t>
   </si>
   <si>
-    <t xml:space="preserve">8.37467956542969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.38324928283691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.41581439971924</t>
+    <t xml:space="preserve">8.37467861175537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.3832483291626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.41581535339355</t>
   </si>
   <si>
     <t xml:space="preserve">8.54436683654785</t>
@@ -4721,19 +4721,19 @@
     <t xml:space="preserve">8.52894020080566</t>
   </si>
   <si>
-    <t xml:space="preserve">8.51522827148438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.51865482330322</t>
+    <t xml:space="preserve">8.51522731781006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.51865577697754</t>
   </si>
   <si>
     <t xml:space="preserve">8.54265308380127</t>
   </si>
   <si>
-    <t xml:space="preserve">8.65577793121338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.66434764862061</t>
+    <t xml:space="preserve">8.65577697753906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.66434669494629</t>
   </si>
   <si>
     <t xml:space="preserve">8.76718807220459</t>
@@ -4742,7 +4742,7 @@
     <t xml:space="preserve">8.85717391967773</t>
   </si>
   <si>
-    <t xml:space="preserve">8.83146381378174</t>
+    <t xml:space="preserve">8.83146476745605</t>
   </si>
   <si>
     <t xml:space="preserve">8.92144966125488</t>
@@ -4757,7 +4757,7 @@
     <t xml:space="preserve">8.62149715423584</t>
   </si>
   <si>
-    <t xml:space="preserve">8.61721229553223</t>
+    <t xml:space="preserve">8.61721134185791</t>
   </si>
   <si>
     <t xml:space="preserve">8.63435173034668</t>
@@ -4769,7 +4769,7 @@
     <t xml:space="preserve">8.64720726013184</t>
   </si>
   <si>
-    <t xml:space="preserve">8.71576690673828</t>
+    <t xml:space="preserve">8.7157678604126</t>
   </si>
   <si>
     <t xml:space="preserve">8.68577289581299</t>
@@ -4778,40 +4778,40 @@
     <t xml:space="preserve">8.70719814300537</t>
   </si>
   <si>
-    <t xml:space="preserve">8.60435676574707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.57007598876953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.58721733093262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.61292743682861</t>
+    <t xml:space="preserve">8.60435771942139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.57007694244385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.5872163772583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.61292839050293</t>
   </si>
   <si>
     <t xml:space="preserve">8.62578105926514</t>
   </si>
   <si>
-    <t xml:space="preserve">8.65149307250977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.77575778961182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.84860420227051</t>
+    <t xml:space="preserve">8.65149211883545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.77575874328613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.84860324859619</t>
   </si>
   <si>
     <t xml:space="preserve">8.78861331939697</t>
   </si>
   <si>
-    <t xml:space="preserve">8.76290321350098</t>
+    <t xml:space="preserve">8.76290416717529</t>
   </si>
   <si>
     <t xml:space="preserve">8.70291233062744</t>
   </si>
   <si>
-    <t xml:space="preserve">8.63006687164307</t>
+    <t xml:space="preserve">8.63006782531738</t>
   </si>
   <si>
     <t xml:space="preserve">8.82289409637451</t>
@@ -4820,22 +4820,22 @@
     <t xml:space="preserve">8.72433853149414</t>
   </si>
   <si>
-    <t xml:space="preserve">8.67291641235352</t>
+    <t xml:space="preserve">8.67291831970215</t>
   </si>
   <si>
     <t xml:space="preserve">8.66863250732422</t>
   </si>
   <si>
-    <t xml:space="preserve">8.75861835479736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.64292335510254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.582932472229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.50665760040283</t>
+    <t xml:space="preserve">8.75861930847168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.64292240142822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.58293056488037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.50665950775146</t>
   </si>
   <si>
     <t xml:space="preserve">8.45523738861084</t>
@@ -4844,7 +4844,7 @@
     <t xml:space="preserve">8.29240608215332</t>
   </si>
   <si>
-    <t xml:space="preserve">8.19984912872314</t>
+    <t xml:space="preserve">8.19985008239746</t>
   </si>
   <si>
     <t xml:space="preserve">8.18270969390869</t>
@@ -4856,10 +4856,10 @@
     <t xml:space="preserve">8.17756748199463</t>
   </si>
   <si>
-    <t xml:space="preserve">8.36610889434814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.42781448364258</t>
+    <t xml:space="preserve">8.36610984802246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.42781257629395</t>
   </si>
   <si>
     <t xml:space="preserve">8.35411071777344</t>
@@ -4868,52 +4868,52 @@
     <t xml:space="preserve">8.4603796005249</t>
   </si>
   <si>
-    <t xml:space="preserve">8.48266124725342</t>
+    <t xml:space="preserve">8.48266220092773</t>
   </si>
   <si>
     <t xml:space="preserve">8.30097579956055</t>
   </si>
   <si>
-    <t xml:space="preserve">7.87418556213379</t>
+    <t xml:space="preserve">7.87418603897095</t>
   </si>
   <si>
     <t xml:space="preserve">7.85533285140991</t>
   </si>
   <si>
-    <t xml:space="preserve">7.85876083374023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.79877090454102</t>
+    <t xml:space="preserve">7.85876035690308</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.79877042770386</t>
   </si>
   <si>
     <t xml:space="preserve">7.91018009185791</t>
   </si>
   <si>
-    <t xml:space="preserve">7.83476448059082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.88275718688965</t>
+    <t xml:space="preserve">7.8347635269165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.88275623321533</t>
   </si>
   <si>
     <t xml:space="preserve">8.00445175170898</t>
   </si>
   <si>
-    <t xml:space="preserve">7.98902463912964</t>
+    <t xml:space="preserve">7.9890251159668</t>
   </si>
   <si>
     <t xml:space="preserve">8.08501052856445</t>
   </si>
   <si>
-    <t xml:space="preserve">8.16728210449219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.21184825897217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.46894931793213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.56836223602295</t>
+    <t xml:space="preserve">8.1672830581665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.21184730529785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.46895027160645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.56836318969727</t>
   </si>
   <si>
     <t xml:space="preserve">8.59578704833984</t>
@@ -4922,7 +4922,7 @@
     <t xml:space="preserve">8.74823379516602</t>
   </si>
   <si>
-    <t xml:space="preserve">8.66926193237305</t>
+    <t xml:space="preserve">8.66926288604736</t>
   </si>
   <si>
     <t xml:space="preserve">8.62539005279541</t>
@@ -4931,16 +4931,16 @@
     <t xml:space="preserve">8.63065528869629</t>
   </si>
   <si>
-    <t xml:space="preserve">8.66399765014648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.56572246551514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.62363529205322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.61135005950928</t>
+    <t xml:space="preserve">8.66399669647217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.56572341918945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.62363433837891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.61135101318359</t>
   </si>
   <si>
     <t xml:space="preserve">8.66575336456299</t>
@@ -4958,7 +4958,7 @@
     <t xml:space="preserve">8.78771877288818</t>
   </si>
   <si>
-    <t xml:space="preserve">8.75174427032471</t>
+    <t xml:space="preserve">8.75174331665039</t>
   </si>
   <si>
     <t xml:space="preserve">8.80526828765869</t>
@@ -4967,22 +4967,22 @@
     <t xml:space="preserve">8.84914112091064</t>
   </si>
   <si>
-    <t xml:space="preserve">8.81404304504395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.87985134124756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.97198486328125</t>
+    <t xml:space="preserve">8.81404399871826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.87985229492188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.97198581695557</t>
   </si>
   <si>
     <t xml:space="preserve">8.95004844665527</t>
   </si>
   <si>
-    <t xml:space="preserve">8.93249893188477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.0158576965332</t>
+    <t xml:space="preserve">8.93249988555908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.01585674285889</t>
   </si>
   <si>
     <t xml:space="preserve">8.97637176513672</t>
@@ -5003,28 +5003,28 @@
     <t xml:space="preserve">8.93688678741455</t>
   </si>
   <si>
-    <t xml:space="preserve">9.02901935577393</t>
+    <t xml:space="preserve">9.02902030944824</t>
   </si>
   <si>
     <t xml:space="preserve">9.01147079467773</t>
   </si>
   <si>
-    <t xml:space="preserve">8.95443630218506</t>
+    <t xml:space="preserve">8.95443534851074</t>
   </si>
   <si>
     <t xml:space="preserve">8.8579158782959</t>
   </si>
   <si>
-    <t xml:space="preserve">8.90178966522217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.906174659729</t>
+    <t xml:space="preserve">8.90178871154785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.90617561340332</t>
   </si>
   <si>
     <t xml:space="preserve">8.87546443939209</t>
   </si>
   <si>
-    <t xml:space="preserve">8.84036636352539</t>
+    <t xml:space="preserve">8.84036540985107</t>
   </si>
   <si>
     <t xml:space="preserve">8.91056251525879</t>
@@ -5033,22 +5033,22 @@
     <t xml:space="preserve">8.86668968200684</t>
   </si>
   <si>
-    <t xml:space="preserve">8.963210105896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.04656887054443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.05095672607422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.8228178024292</t>
+    <t xml:space="preserve">8.96321105957031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.04656982421875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.0509557723999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.82281684875488</t>
   </si>
   <si>
     <t xml:space="preserve">8.77104759216309</t>
   </si>
   <si>
-    <t xml:space="preserve">8.83159065246582</t>
+    <t xml:space="preserve">8.83159160614014</t>
   </si>
   <si>
     <t xml:space="preserve">8.83597946166992</t>
@@ -5057,34 +5057,34 @@
     <t xml:space="preserve">8.85352802276611</t>
   </si>
   <si>
-    <t xml:space="preserve">8.71664428710938</t>
+    <t xml:space="preserve">8.71664524078369</t>
   </si>
   <si>
     <t xml:space="preserve">8.65346908569336</t>
   </si>
   <si>
-    <t xml:space="preserve">8.5920467376709</t>
+    <t xml:space="preserve">8.59204769134521</t>
   </si>
   <si>
     <t xml:space="preserve">8.64995861053467</t>
   </si>
   <si>
-    <t xml:space="preserve">8.73068523406982</t>
+    <t xml:space="preserve">8.73068428039551</t>
   </si>
   <si>
     <t xml:space="preserve">8.86230278015137</t>
   </si>
   <si>
-    <t xml:space="preserve">8.87107753753662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.9281120300293</t>
+    <t xml:space="preserve">8.8710765838623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.92811298370361</t>
   </si>
   <si>
     <t xml:space="preserve">8.99392032623291</t>
   </si>
   <si>
-    <t xml:space="preserve">9.17818737030029</t>
+    <t xml:space="preserve">9.17818641662598</t>
   </si>
   <si>
     <t xml:space="preserve">9.22644710540771</t>
@@ -5096,34 +5096,34 @@
     <t xml:space="preserve">9.9020881652832</t>
   </si>
   <si>
-    <t xml:space="preserve">9.84066581726074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.99422073364258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0556421279907</t>
+    <t xml:space="preserve">9.84066677093506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.99422168731689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.055643081665</t>
   </si>
   <si>
     <t xml:space="preserve">10.0951290130615</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1521625518799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2004232406616</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2179718017578</t>
+    <t xml:space="preserve">10.1521615982056</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2004222869873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2179727554321</t>
   </si>
   <si>
     <t xml:space="preserve">10.2750062942505</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2837820053101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3364286422729</t>
+    <t xml:space="preserve">10.2837810516357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3364276885986</t>
   </si>
   <si>
     <t xml:space="preserve">10.4680471420288</t>
@@ -5135,22 +5135,22 @@
     <t xml:space="preserve">10.086353302002</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0380935668945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0512552261353</t>
+    <t xml:space="preserve">10.0380926132202</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0512542724609</t>
   </si>
   <si>
     <t xml:space="preserve">10.1390018463135</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1477746963501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1828737258911</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1170644760132</t>
+    <t xml:space="preserve">10.1477756500244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1828727722168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1170635223389</t>
   </si>
   <si>
     <t xml:space="preserve">10.235520362854</t>
@@ -5159,22 +5159,22 @@
     <t xml:space="preserve">10.1082906723022</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2530708312988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1126775741577</t>
+    <t xml:space="preserve">10.2530698776245</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1126756668091</t>
   </si>
   <si>
     <t xml:space="preserve">10.2135848999023</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1565494537354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2311344146729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0907402038574</t>
+    <t xml:space="preserve">10.1565504074097</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2311334609985</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0907411575317</t>
   </si>
   <si>
     <t xml:space="preserve">10.0775785446167</t>
@@ -5183,22 +5183,22 @@
     <t xml:space="preserve">10.2267465591431</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2223587036133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2925548553467</t>
+    <t xml:space="preserve">10.2223596572876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.292555809021</t>
   </si>
   <si>
     <t xml:space="preserve">10.4636602401733</t>
   </si>
   <si>
-    <t xml:space="preserve">10.349591255188</t>
+    <t xml:space="preserve">10.3495903015137</t>
   </si>
   <si>
     <t xml:space="preserve">10.3539772033691</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4812088012695</t>
+    <t xml:space="preserve">10.4812078475952</t>
   </si>
   <si>
     <t xml:space="preserve">10.4592723846436</t>
@@ -5210,19 +5210,19 @@
     <t xml:space="preserve">10.6084403991699</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8453521728516</t>
+    <t xml:space="preserve">10.8453531265259</t>
   </si>
   <si>
     <t xml:space="preserve">10.8058662414551</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7619962692261</t>
+    <t xml:space="preserve">10.7619953155518</t>
   </si>
   <si>
     <t xml:space="preserve">10.7970924377441</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7883186340332</t>
+    <t xml:space="preserve">10.7883176803589</t>
   </si>
   <si>
     <t xml:space="preserve">11.0120697021484</t>
@@ -5231,7 +5231,7 @@
     <t xml:space="preserve">10.8672895431519</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8804512023926</t>
+    <t xml:space="preserve">10.8804502487183</t>
   </si>
   <si>
     <t xml:space="preserve">10.8497400283813</t>
@@ -5243,34 +5243,34 @@
     <t xml:space="preserve">10.8234167098999</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8979997634888</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0822668075562</t>
+    <t xml:space="preserve">10.8980007171631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0822658538818</t>
   </si>
   <si>
     <t xml:space="preserve">11.0647163391113</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0471677780151</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9945201873779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0559434890747</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2884674072266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2226581573486</t>
+    <t xml:space="preserve">11.0471687316895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9945211410522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0559425354004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2884683609009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2226591110229</t>
   </si>
   <si>
     <t xml:space="preserve">11.3674392700195</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2270460128784</t>
+    <t xml:space="preserve">11.2270450592041</t>
   </si>
   <si>
     <t xml:space="preserve">11.1919479370117</t>
@@ -5282,25 +5282,25 @@
     <t xml:space="preserve">10.8716764450073</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6830244064331</t>
+    <t xml:space="preserve">10.6830234527588</t>
   </si>
   <si>
     <t xml:space="preserve">10.9023876190186</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0734901428223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0252313613892</t>
+    <t xml:space="preserve">11.0734910964966</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0252304077148</t>
   </si>
   <si>
     <t xml:space="preserve">11.0555458068848</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1014766693115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9728708267212</t>
+    <t xml:space="preserve">11.1014776229858</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9728698730469</t>
   </si>
   <si>
     <t xml:space="preserve">11.0325803756714</t>
@@ -5318,16 +5318,16 @@
     <t xml:space="preserve">11.083104133606</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1520013809204</t>
+    <t xml:space="preserve">11.1520004272461</t>
   </si>
   <si>
     <t xml:space="preserve">11.0142078399658</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1106624603271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0188007354736</t>
+    <t xml:space="preserve">11.1106634140015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0188016891479</t>
   </si>
   <si>
     <t xml:space="preserve">11.1336278915405</t>
@@ -5339,7 +5339,7 @@
     <t xml:space="preserve">11.1703729629517</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1198482513428</t>
+    <t xml:space="preserve">11.1198492050171</t>
   </si>
   <si>
     <t xml:space="preserve">11.225489616394</t>
@@ -5369,7 +5369,7 @@
     <t xml:space="preserve">10.8718223571777</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5916442871094</t>
+    <t xml:space="preserve">10.5916433334351</t>
   </si>
   <si>
     <t xml:space="preserve">10.6192035675049</t>
@@ -5378,10 +5378,10 @@
     <t xml:space="preserve">10.8901948928833</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8167057037354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9177541732788</t>
+    <t xml:space="preserve">10.816704750061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9177532196045</t>
   </si>
   <si>
     <t xml:space="preserve">10.9223470687866</t>
@@ -5399,7 +5399,7 @@
     <t xml:space="preserve">11.4046201705933</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2806062698364</t>
+    <t xml:space="preserve">11.2806072235107</t>
   </si>
   <si>
     <t xml:space="preserve">11.3632822036743</t>
@@ -5408,22 +5408,22 @@
     <t xml:space="preserve">11.3954334259033</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4781084060669</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4735164642334</t>
+    <t xml:space="preserve">11.4781093597412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4735155105591</t>
   </si>
   <si>
     <t xml:space="preserve">11.4459571838379</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5056667327881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5194473266602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5286340713501</t>
+    <t xml:space="preserve">11.5056676864624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5194463729858</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5286331176758</t>
   </si>
   <si>
     <t xml:space="preserve">11.4551439285278</t>
@@ -5435,7 +5435,7 @@
     <t xml:space="preserve">11.3035717010498</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3449096679688</t>
+    <t xml:space="preserve">11.3449106216431</t>
   </si>
   <si>
     <t xml:space="preserve">11.2897930145264</t>
@@ -5453,22 +5453,22 @@
     <t xml:space="preserve">11.5699710845947</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5975294113159</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.643461227417</t>
+    <t xml:space="preserve">11.5975284576416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6434602737427</t>
   </si>
   <si>
     <t xml:space="preserve">11.6388673782349</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3816547393799</t>
+    <t xml:space="preserve">11.3816537857056</t>
   </si>
   <si>
     <t xml:space="preserve">11.3678750991821</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4643297195435</t>
+    <t xml:space="preserve">11.4643287658691</t>
   </si>
   <si>
     <t xml:space="preserve">11.5791568756104</t>
@@ -5477,7 +5477,7 @@
     <t xml:space="preserve">11.6250867843628</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5653772354126</t>
+    <t xml:space="preserve">11.5653781890869</t>
   </si>
   <si>
     <t xml:space="preserve">11.5424118041992</t>
@@ -5501,25 +5501,25 @@
     <t xml:space="preserve">11.6893911361694</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7766599655151</t>
+    <t xml:space="preserve">11.7766590118408</t>
   </si>
   <si>
     <t xml:space="preserve">11.8639278411865</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8777084350586</t>
+    <t xml:space="preserve">11.8777074813843</t>
   </si>
   <si>
     <t xml:space="preserve">11.9282312393188</t>
   </si>
   <si>
-    <t xml:space="preserve">12.286491394043</t>
+    <t xml:space="preserve">12.2864923477173</t>
   </si>
   <si>
     <t xml:space="preserve">12.3232364654541</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2451543807983</t>
+    <t xml:space="preserve">12.245153427124</t>
   </si>
   <si>
     <t xml:space="preserve">12.1532917022705</t>
@@ -5540,13 +5540,13 @@
     <t xml:space="preserve">12.0338726043701</t>
   </si>
   <si>
-    <t xml:space="preserve">11.932825088501</t>
+    <t xml:space="preserve">11.9328241348267</t>
   </si>
   <si>
     <t xml:space="preserve">11.8868932723999</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9695682525635</t>
+    <t xml:space="preserve">11.9695692062378</t>
   </si>
   <si>
     <t xml:space="preserve">11.9144515991211</t>
@@ -5567,22 +5567,22 @@
     <t xml:space="preserve">12.0476512908936</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2038154602051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3094568252563</t>
+    <t xml:space="preserve">12.2038164138794</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.309455871582</t>
   </si>
   <si>
     <t xml:space="preserve">12.1681852340698</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2482395172119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.328293800354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3800935745239</t>
+    <t xml:space="preserve">12.2482385635376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3282928466797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3800926208496</t>
   </si>
   <si>
     <t xml:space="preserve">12.4789819717407</t>
@@ -5597,10 +5597,10 @@
     <t xml:space="preserve">12.5119457244873</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6673440933228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7097253799438</t>
+    <t xml:space="preserve">12.6673450469971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7097263336182</t>
   </si>
   <si>
     <t xml:space="preserve">12.8462886810303</t>
@@ -5612,19 +5612,19 @@
     <t xml:space="preserve">12.964015007019</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8651237487793</t>
+    <t xml:space="preserve">12.8651247024536</t>
   </si>
   <si>
     <t xml:space="preserve">12.8604154586792</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9875602722168</t>
+    <t xml:space="preserve">12.9875593185425</t>
   </si>
   <si>
     <t xml:space="preserve">12.9969778060913</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0393600463867</t>
+    <t xml:space="preserve">13.0393590927124</t>
   </si>
   <si>
     <t xml:space="preserve">13.0629043579102</t>
@@ -5633,13 +5633,13 @@
     <t xml:space="preserve">12.9122152328491</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7850713729858</t>
+    <t xml:space="preserve">12.7850704193115</t>
   </si>
   <si>
     <t xml:space="preserve">12.7568168640137</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6908893585205</t>
+    <t xml:space="preserve">12.6908903121948</t>
   </si>
   <si>
     <t xml:space="preserve">12.8509979248047</t>
@@ -5654,10 +5654,10 @@
     <t xml:space="preserve">13.0111045837402</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0487775802612</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1476669311523</t>
+    <t xml:space="preserve">13.0487766265869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1476678848267</t>
   </si>
   <si>
     <t xml:space="preserve">13.2465572357178</t>
@@ -5666,13 +5666,13 @@
     <t xml:space="preserve">13.1241226196289</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0440683364868</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1806316375732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3737020492554</t>
+    <t xml:space="preserve">13.0440692901611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1806306838989</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3737010955811</t>
   </si>
   <si>
     <t xml:space="preserve">13.463173866272</t>
@@ -5696,7 +5696,7 @@
     <t xml:space="preserve">13.4961376190186</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6374082565308</t>
+    <t xml:space="preserve">13.6374092102051</t>
   </si>
   <si>
     <t xml:space="preserve">13.6232814788818</t>
@@ -5708,7 +5708,7 @@
     <t xml:space="preserve">13.802225112915</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8351879119873</t>
+    <t xml:space="preserve">13.8351888656616</t>
   </si>
   <si>
     <t xml:space="preserve">13.6703729629517</t>
@@ -5723,7 +5723,7 @@
     <t xml:space="preserve">13.7551345825195</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7315893173218</t>
+    <t xml:space="preserve">13.7315902709961</t>
   </si>
   <si>
     <t xml:space="preserve">13.8116436004639</t>
@@ -5762,7 +5762,7 @@
     <t xml:space="preserve">14.621600151062</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8052539825439</t>
+    <t xml:space="preserve">14.8052530288696</t>
   </si>
   <si>
     <t xml:space="preserve">14.6922369003296</t>
@@ -5774,31 +5774,31 @@
     <t xml:space="preserve">15.0595417022705</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2102317810059</t>
+    <t xml:space="preserve">15.2102308273315</t>
   </si>
   <si>
     <t xml:space="preserve">15.1066331863403</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0454149246216</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1961040496826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3656301498413</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4221391677856</t>
+    <t xml:space="preserve">15.0454158782959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1961050033569</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3656311035156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4221382141113</t>
   </si>
   <si>
     <t xml:space="preserve">15.3891754150391</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6152095794678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5634107589722</t>
+    <t xml:space="preserve">15.6152086257935</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5634088516235</t>
   </si>
   <si>
     <t xml:space="preserve">15.4786462783813</t>
@@ -5813,22 +5813,22 @@
     <t xml:space="preserve">15.5445737838745</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5021924972534</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5869550704956</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6858463287354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4739389419556</t>
+    <t xml:space="preserve">15.5021915435791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5869541168213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.685845375061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4739398956299</t>
   </si>
   <si>
     <t xml:space="preserve">15.6528825759888</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8694982528687</t>
+    <t xml:space="preserve">15.869499206543</t>
   </si>
   <si>
     <t xml:space="preserve">15.5963735580444</t>
@@ -5852,13 +5852,13 @@
     <t xml:space="preserve">14.8382167816162</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3562126159668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5351572036743</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7564811706543</t>
+    <t xml:space="preserve">15.3562116622925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.53515625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.75648021698</t>
   </si>
   <si>
     <t xml:space="preserve">15.9495525360107</t>
@@ -5879,7 +5879,7 @@
     <t xml:space="preserve">16.5381832122803</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5852756500244</t>
+    <t xml:space="preserve">16.5852737426758</t>
   </si>
   <si>
     <t xml:space="preserve">16.8018894195557</t>
@@ -5903,7 +5903,7 @@
     <t xml:space="preserve">17.3198852539062</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2021598815918</t>
+    <t xml:space="preserve">17.2021579742432</t>
   </si>
   <si>
     <t xml:space="preserve">17.0891437530518</t>
@@ -5936,10 +5936,10 @@
     <t xml:space="preserve">17.9697341918945</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9508972167969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.899097442627</t>
+    <t xml:space="preserve">17.9508991241455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8990993499756</t>
   </si>
   <si>
     <t xml:space="preserve">17.997989654541</t>
@@ -5948,7 +5948,7 @@
     <t xml:space="preserve">18.0121154785156</t>
   </si>
   <si>
-    <t xml:space="preserve">17.7484092712402</t>
+    <t xml:space="preserve">17.7484073638916</t>
   </si>
   <si>
     <t xml:space="preserve">17.8567161560059</t>
@@ -5957,7 +5957,7 @@
     <t xml:space="preserve">17.9744434356689</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9414806365967</t>
+    <t xml:space="preserve">17.941478729248</t>
   </si>
   <si>
     <t xml:space="preserve">17.7625370025635</t>
@@ -5972,7 +5972,7 @@
     <t xml:space="preserve">17.6683559417725</t>
   </si>
   <si>
-    <t xml:space="preserve">17.5741729736328</t>
+    <t xml:space="preserve">17.5741748809814</t>
   </si>
   <si>
     <t xml:space="preserve">17.5930099487305</t>
@@ -6291,6 +6291,9 @@
   </si>
   <si>
     <t xml:space="preserve">20.6100006103516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.5</t>
   </si>
 </sst>
 </file>
@@ -72175,7 +72178,7 @@
     </row>
     <row r="2522">
       <c r="A2522" s="1" t="n">
-        <v>45989.6917708333</v>
+        <v>45989.3333333333</v>
       </c>
       <c r="B2522" t="n">
         <v>1214388</v>
@@ -72196,6 +72199,32 @@
         <v>2092</v>
       </c>
       <c r="H2522" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2523">
+      <c r="A2523" s="1" t="n">
+        <v>45992.6929976852</v>
+      </c>
+      <c r="B2523" t="n">
+        <v>1584275</v>
+      </c>
+      <c r="C2523" t="n">
+        <v>20.6499996185303</v>
+      </c>
+      <c r="D2523" t="n">
+        <v>20.3400001525879</v>
+      </c>
+      <c r="E2523" t="n">
+        <v>20.6200008392334</v>
+      </c>
+      <c r="F2523" t="n">
+        <v>20.5</v>
+      </c>
+      <c r="G2523" t="s">
+        <v>2093</v>
+      </c>
+      <c r="H2523" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/PST.MI.xlsx
+++ b/data/PST.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2094" uniqueCount="2094">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2095" uniqueCount="2095">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,31 +38,31 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">3.82970333099365</t>
+    <t xml:space="preserve">3.82970404624939</t>
   </si>
   <si>
     <t xml:space="preserve">PST.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">3.95891833305359</t>
+    <t xml:space="preserve">3.95891809463501</t>
   </si>
   <si>
     <t xml:space="preserve">3.89843535423279</t>
   </si>
   <si>
-    <t xml:space="preserve">3.87644076347351</t>
+    <t xml:space="preserve">3.87644052505493</t>
   </si>
   <si>
     <t xml:space="preserve">3.84070014953613</t>
   </si>
   <si>
-    <t xml:space="preserve">3.80496096611023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.89568543434143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94242286682129</t>
+    <t xml:space="preserve">3.80496001243591</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89568495750427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94242215156555</t>
   </si>
   <si>
     <t xml:space="preserve">3.92042899131775</t>
@@ -71,385 +71,385 @@
     <t xml:space="preserve">3.87094187736511</t>
   </si>
   <si>
-    <t xml:space="preserve">3.75547337532043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.68399286270142</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.48054933547974</t>
+    <t xml:space="preserve">3.75547385215759</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.68399310112</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.480548620224</t>
   </si>
   <si>
     <t xml:space="preserve">3.6152617931366</t>
   </si>
   <si>
-    <t xml:space="preserve">3.6619987487793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.58502054214478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.68949198722839</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73622870445251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.65924954414368</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.75272369384766</t>
+    <t xml:space="preserve">3.66199898719788</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.58502078056335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.68949270248413</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73622918128967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.65925049781799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.75272464752197</t>
   </si>
   <si>
     <t xml:space="preserve">3.6510021686554</t>
   </si>
   <si>
-    <t xml:space="preserve">3.57402348518372</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.46405363082886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.2908501625061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.94719457626343</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.84272336959839</t>
+    <t xml:space="preserve">3.57402300834656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.46405291557312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.29085063934326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.94719433784485</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.84272313117981</t>
   </si>
   <si>
     <t xml:space="preserve">3.10940003395081</t>
   </si>
   <si>
-    <t xml:space="preserve">2.97468733787537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.98568391799927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.07640933990479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.06266283988953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.18637871742249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.17263317108154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.2413637638092</t>
+    <t xml:space="preserve">2.97468709945679</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.98568415641785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.07640886306763</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.06266260147095</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.18637943267822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.17263293266296</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.24136447906494</t>
   </si>
   <si>
     <t xml:space="preserve">3.35683250427246</t>
   </si>
   <si>
-    <t xml:space="preserve">3.2826030254364</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.24961185455322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.3430860042572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.3898229598999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.44755840301514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.417316198349</t>
+    <t xml:space="preserve">3.28260231018066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.24961161613464</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.34308648109436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.38982391357422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.44755792617798</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.41731667518616</t>
   </si>
   <si>
     <t xml:space="preserve">3.38707423210144</t>
   </si>
   <si>
-    <t xml:space="preserve">3.40906810760498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.37057900428772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.39257287979126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.3678297996521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.54378199577332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.56852507591248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.56577610969543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.53828287124634</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.51903796195984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.53278565406799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.60151553153992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.72248339653015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.70598721504211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64275479316711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71148586273193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.65650033950806</t>
+    <t xml:space="preserve">3.4090678691864</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.37057876586914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.39257264137268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.36782956123352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.54378175735474</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.5685248374939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.56577563285828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.53828263282776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.519038438797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.53278470039368</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.6015157699585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.72248220443726</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.70598769187927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.6427538394928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71148633956909</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.65650105476379</t>
   </si>
   <si>
     <t xml:space="preserve">3.60701394081116</t>
   </si>
   <si>
-    <t xml:space="preserve">3.54653120040894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.44480848312378</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.49979376792908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.5162889957428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.53553414344788</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.55202889442444</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.62900876998901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.56302642822266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.56027626991272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.58776998519897</t>
+    <t xml:space="preserve">3.54653000831604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.44480776786804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.4997935295105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.51628947257996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.53553318977356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.5520293712616</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.62900757789612</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.56302666664124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.56027674674988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.5877697467804</t>
   </si>
   <si>
     <t xml:space="preserve">3.55752825737</t>
   </si>
   <si>
-    <t xml:space="preserve">3.60426497459412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.60976266860962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.67299604415894</t>
+    <t xml:space="preserve">3.60426545143127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.60976409912109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.67299628257751</t>
   </si>
   <si>
     <t xml:space="preserve">3.71973323822021</t>
   </si>
   <si>
-    <t xml:space="preserve">3.72798109054565</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66749787330627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61251187324524</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.69499039649963</t>
+    <t xml:space="preserve">3.72798132896423</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66749715805054</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61251330375671</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.69499063491821</t>
   </si>
   <si>
     <t xml:space="preserve">3.72523212432861</t>
   </si>
   <si>
-    <t xml:space="preserve">3.70323753356934</t>
+    <t xml:space="preserve">3.70323848724365</t>
   </si>
   <si>
     <t xml:space="preserve">3.68674254417419</t>
   </si>
   <si>
-    <t xml:space="preserve">3.71423506736755</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61801147460938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71698427200317</t>
+    <t xml:space="preserve">3.71423578262329</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61801099777222</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71698379516602</t>
   </si>
   <si>
     <t xml:space="preserve">3.67574548721313</t>
   </si>
   <si>
-    <t xml:space="preserve">3.75822281837463</t>
+    <t xml:space="preserve">3.75822234153748</t>
   </si>
   <si>
     <t xml:space="preserve">3.76372170448303</t>
   </si>
   <si>
-    <t xml:space="preserve">3.73347973823547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.78571534156799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.78296709060669</t>
+    <t xml:space="preserve">3.73347997665405</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.78571581840515</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.78296613693237</t>
   </si>
   <si>
     <t xml:space="preserve">3.79396367073059</t>
   </si>
   <si>
-    <t xml:space="preserve">3.77196931838989</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.78021717071533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84894752502441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85719609260559</t>
+    <t xml:space="preserve">3.77196907997131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.78021693229675</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84894824028015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85719585418701</t>
   </si>
   <si>
     <t xml:space="preserve">3.76646995544434</t>
   </si>
   <si>
-    <t xml:space="preserve">3.70873641967773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.69224119186401</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80221104621887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88895344734192</t>
+    <t xml:space="preserve">3.70873665809631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.69223999977112</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.80221056938171</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88895273208618</t>
   </si>
   <si>
     <t xml:space="preserve">3.83979892730713</t>
   </si>
   <si>
-    <t xml:space="preserve">3.83112454414368</t>
+    <t xml:space="preserve">3.83112502098083</t>
   </si>
   <si>
     <t xml:space="preserve">3.87449598312378</t>
   </si>
   <si>
-    <t xml:space="preserve">3.56800603866577</t>
+    <t xml:space="preserve">3.56800627708435</t>
   </si>
   <si>
     <t xml:space="preserve">3.35693311691284</t>
   </si>
   <si>
-    <t xml:space="preserve">3.44656682014465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.44078397750854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.53620004653931</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.45813250541687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.37139010429382</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.33380126953125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.30777907371521</t>
+    <t xml:space="preserve">3.44656658172607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.44078373908997</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.53620052337646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.45813202857971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.37138962745667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.33380198478699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.30777931213379</t>
   </si>
   <si>
     <t xml:space="preserve">3.43210959434509</t>
   </si>
   <si>
-    <t xml:space="preserve">3.58824563026428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.57957220077515</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66342329978943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.59981179237366</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.602703332901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.58246302604675</t>
+    <t xml:space="preserve">3.58824682235718</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.57957172393799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66342353820801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.59981203079224</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.60270357131958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.58246350288391</t>
   </si>
   <si>
     <t xml:space="preserve">3.63739991188049</t>
   </si>
   <si>
-    <t xml:space="preserve">3.62583422660828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.5853545665741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.57668018341064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.53330945968628</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.51596117019653</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.46102333068848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.72992491722107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.70968556404114</t>
+    <t xml:space="preserve">3.62583470344543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.58535504341125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.57667970657349</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.53330850601196</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.51596069335938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.46102380752563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.72992539405823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.70968675613403</t>
   </si>
   <si>
     <t xml:space="preserve">3.73570871353149</t>
   </si>
   <si>
-    <t xml:space="preserve">3.74149084091187</t>
+    <t xml:space="preserve">3.74149107933044</t>
   </si>
   <si>
     <t xml:space="preserve">3.79353618621826</t>
   </si>
   <si>
-    <t xml:space="preserve">3.80510187149048</t>
+    <t xml:space="preserve">3.80510210990906</t>
   </si>
   <si>
     <t xml:space="preserve">3.72703409194946</t>
   </si>
   <si>
-    <t xml:space="preserve">3.65185785293579</t>
+    <t xml:space="preserve">3.65185713768005</t>
   </si>
   <si>
     <t xml:space="preserve">3.68944621086121</t>
   </si>
   <si>
-    <t xml:space="preserve">3.59692025184631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61137747764587</t>
+    <t xml:space="preserve">3.59692049026489</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61137795448303</t>
   </si>
   <si>
     <t xml:space="preserve">3.67209720611572</t>
@@ -458,193 +458,193 @@
     <t xml:space="preserve">3.63161730766296</t>
   </si>
   <si>
-    <t xml:space="preserve">3.59113740921021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.60848641395569</t>
+    <t xml:space="preserve">3.59113836288452</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.60848617553711</t>
   </si>
   <si>
     <t xml:space="preserve">3.55644059181213</t>
   </si>
   <si>
-    <t xml:space="preserve">3.62294316291809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61426949501038</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.63450884819031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64607429504395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.70390343666077</t>
+    <t xml:space="preserve">3.62294268608093</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.6142692565918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.63450908660889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64607405662537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.70390248298645</t>
   </si>
   <si>
     <t xml:space="preserve">3.69233751296997</t>
   </si>
   <si>
-    <t xml:space="preserve">3.49572086334229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.54776668548584</t>
+    <t xml:space="preserve">3.49572110176086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.54776620864868</t>
   </si>
   <si>
     <t xml:space="preserve">3.54487490653992</t>
   </si>
   <si>
-    <t xml:space="preserve">3.51306939125061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.53041744232178</t>
+    <t xml:space="preserve">3.51306986808777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.53041791915894</t>
   </si>
   <si>
     <t xml:space="preserve">3.53909230232239</t>
   </si>
   <si>
-    <t xml:space="preserve">3.51885223388672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.51017785072327</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.50439524650574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.4899377822876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.49282932281494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.43500113487244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.47837257385254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.49861192703247</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.449458360672</t>
+    <t xml:space="preserve">3.51885199546814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.51017832756042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.50439500808716</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.48993825912476</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.49282956123352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.43500137329102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.47837233543396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.49861264228821</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.44945812225342</t>
   </si>
   <si>
     <t xml:space="preserve">3.50728631019592</t>
   </si>
   <si>
-    <t xml:space="preserve">3.57378816604614</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.55354928970337</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.44367504119873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.4234356880188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.45235013961792</t>
+    <t xml:space="preserve">3.5737886428833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.55354881286621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.44367456436157</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.42343473434448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.45234894752502</t>
   </si>
   <si>
     <t xml:space="preserve">3.48415565490723</t>
   </si>
   <si>
-    <t xml:space="preserve">3.47548055648804</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.46391558647156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.45524120330811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.411869764328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.37428092956543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.3019962310791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.26729989051819</t>
+    <t xml:space="preserve">3.47548127174377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.46391534805298</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.45524072647095</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.41187047958374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.37428140640259</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.30199599266052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.26729917526245</t>
   </si>
   <si>
     <t xml:space="preserve">3.26151633262634</t>
   </si>
   <si>
-    <t xml:space="preserve">3.25573348999023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.24705910682678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.20368814468384</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.33091044425964</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.39162993431091</t>
+    <t xml:space="preserve">3.25573396682739</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.2470588684082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.203688621521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.33091068267822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.39163017272949</t>
   </si>
   <si>
     <t xml:space="preserve">3.39452123641968</t>
   </si>
   <si>
-    <t xml:space="preserve">3.38584685325623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66053199768066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.67498803138733</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66631460189819</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.6576406955719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.70679378509521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66920495033264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.70101141929626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71835970878601</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.69522857666016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64318346977234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.5651159286499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.52752661705017</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.50150370597839</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.52463459968567</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.38295555114746</t>
+    <t xml:space="preserve">3.3858470916748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66053104400635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.67498850822449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66631436347961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.65763974189758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.70679450035095</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66920566558838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.701012134552</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71836042404175</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.695228099823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64318323135376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.56511449813843</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.52752614021301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.50150322914124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.52463436126709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.38295602798462</t>
   </si>
   <si>
     <t xml:space="preserve">3.36271572113037</t>
   </si>
   <si>
-    <t xml:space="preserve">3.38006377220154</t>
+    <t xml:space="preserve">3.3800642490387</t>
   </si>
   <si>
     <t xml:space="preserve">3.46969819068909</t>
@@ -653,31 +653,31 @@
     <t xml:space="preserve">3.46680688858032</t>
   </si>
   <si>
-    <t xml:space="preserve">3.52174377441406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.62872624397278</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.74438285827637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73281621932983</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.72414207458496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.68655443191528</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.75594735145569</t>
+    <t xml:space="preserve">3.52174353599548</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.6287260055542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.74438261985779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73281693458557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.7241427898407</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.68655395507812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.75594854354858</t>
   </si>
   <si>
     <t xml:space="preserve">3.72125124931335</t>
   </si>
   <si>
-    <t xml:space="preserve">3.60559439659119</t>
+    <t xml:space="preserve">3.60559487342834</t>
   </si>
   <si>
     <t xml:space="preserve">3.64029216766357</t>
@@ -686,88 +686,88 @@
     <t xml:space="preserve">3.67787981033325</t>
   </si>
   <si>
-    <t xml:space="preserve">3.6981201171875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.6171600818634</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.68077063560486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.75883960723877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77040505409241</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64896607398987</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.62005162239075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73860001564026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.74727416038513</t>
+    <t xml:space="preserve">3.69812035560608</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61716055870056</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.68077087402344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.75883889198303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77040553092957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64896535873413</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.62005209922791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.7385995388031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.74727439880371</t>
   </si>
   <si>
     <t xml:space="preserve">3.71650815010071</t>
   </si>
   <si>
-    <t xml:space="preserve">3.72881507873535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.74112129211426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.68574261665344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.69189548492432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.70420169830322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66728281974792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.7134313583374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.68881940841675</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.69497299194336</t>
+    <t xml:space="preserve">3.72881460189819</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.7411208152771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.68574237823486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.69189596176147</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.70420145988464</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66728329658508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71343183517456</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.68881893157959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.6949725151062</t>
   </si>
   <si>
     <t xml:space="preserve">3.67343616485596</t>
   </si>
   <si>
-    <t xml:space="preserve">3.65805268287659</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.72266125679016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73189091682434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.7688102722168</t>
+    <t xml:space="preserve">3.6580536365509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.72266149520874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73189043998718</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.76881003379822</t>
   </si>
   <si>
     <t xml:space="preserve">3.7503502368927</t>
   </si>
   <si>
-    <t xml:space="preserve">3.73496770858765</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.72573781013489</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.67958879470825</t>
+    <t xml:space="preserve">3.73496842384338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.72573804855347</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.67958927154541</t>
   </si>
   <si>
     <t xml:space="preserve">3.67035984992981</t>
@@ -776,124 +776,124 @@
     <t xml:space="preserve">3.70727849006653</t>
   </si>
   <si>
-    <t xml:space="preserve">3.83957123756409</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85187721252441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87033700942993</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.81803488731384</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.82726526260376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83034205436707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.86726045608521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.75958061218262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77188658714294</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.82418942451477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83341884613037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.78419280052185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.76573371887207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.75650334358215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.7811164855957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.74419760704041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.78726959228516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84572434425354</t>
+    <t xml:space="preserve">3.83957171440125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85187768936157</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87033724784851</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.81803512573242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.82726502418518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.83034157752991</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.86726021766663</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.75958013534546</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.7718870639801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.82418894767761</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.83341836929321</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.78419303894043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.76573348045349</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.75650405883789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.78111600875854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.74419713020325</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.78727030754089</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8457248210907</t>
   </si>
   <si>
     <t xml:space="preserve">3.82111215591431</t>
   </si>
   <si>
-    <t xml:space="preserve">3.81188154220581</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8149585723877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.79034638404846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80572891235352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.7780396938324</t>
+    <t xml:space="preserve">3.81188225746155</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.81495881080627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.79034686088562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.80572915077209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77803897857666</t>
   </si>
   <si>
     <t xml:space="preserve">3.79957628250122</t>
   </si>
   <si>
-    <t xml:space="preserve">3.8549542427063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.79342317581177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.86110758781433</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87341451644897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8580310344696</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8641836643219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84880113601685</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77496385574341</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.76265645027161</t>
+    <t xml:space="preserve">3.85495376586914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.79342293739319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.86110687255859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8734142780304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85803079605103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.86418342590332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84880137443542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77496361732483</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.76265668869019</t>
   </si>
   <si>
     <t xml:space="preserve">3.75342702865601</t>
   </si>
   <si>
-    <t xml:space="preserve">3.91648554801941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94417524337769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.91956186294556</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90725660324097</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.89495062828064</t>
+    <t xml:space="preserve">3.91648602485657</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94417500495911</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.91956281661987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90725541114807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89494919776917</t>
   </si>
   <si>
     <t xml:space="preserve">3.91033244132996</t>
@@ -902,22 +902,22 @@
     <t xml:space="preserve">3.92263913154602</t>
   </si>
   <si>
-    <t xml:space="preserve">3.9410994052887</t>
+    <t xml:space="preserve">3.94109869003296</t>
   </si>
   <si>
     <t xml:space="preserve">3.95648121833801</t>
   </si>
   <si>
-    <t xml:space="preserve">3.96878743171692</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9810938835144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96263384819031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99340057373047</t>
+    <t xml:space="preserve">3.96878719329834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.98109436035156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96263527870178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99340009689331</t>
   </si>
   <si>
     <t xml:space="preserve">4.02416563034058</t>
@@ -926,88 +926,88 @@
     <t xml:space="preserve">4.02108907699585</t>
   </si>
   <si>
-    <t xml:space="preserve">4.04877901077271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.13800001144409</t>
+    <t xml:space="preserve">4.04877948760986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.13799953460693</t>
   </si>
   <si>
     <t xml:space="preserve">4.13492298126221</t>
   </si>
   <si>
-    <t xml:space="preserve">4.11953973770142</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.09185171127319</t>
+    <t xml:space="preserve">4.11954069137573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.09185123443604</t>
   </si>
   <si>
     <t xml:space="preserve">4.10723400115967</t>
   </si>
   <si>
-    <t xml:space="preserve">4.11646366119385</t>
+    <t xml:space="preserve">4.11646413803101</t>
   </si>
   <si>
     <t xml:space="preserve">4.0930814743042</t>
   </si>
   <si>
-    <t xml:space="preserve">4.07585287094116</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.10046577453613</t>
+    <t xml:space="preserve">4.075852394104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.10046434402466</t>
   </si>
   <si>
     <t xml:space="preserve">4.05124044418335</t>
   </si>
   <si>
-    <t xml:space="preserve">4.05985403060913</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93802213668823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.04262542724609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96632552146912</t>
+    <t xml:space="preserve">4.05985498428345</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93802189826965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.04262590408325</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96632647514343</t>
   </si>
   <si>
     <t xml:space="preserve">3.96017265319824</t>
   </si>
   <si>
-    <t xml:space="preserve">3.9774022102356</t>
+    <t xml:space="preserve">3.97740197181702</t>
   </si>
   <si>
     <t xml:space="preserve">4.01678276062012</t>
   </si>
   <si>
-    <t xml:space="preserve">4.05000925064087</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.09554290771484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.10169649124146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.17184162139893</t>
+    <t xml:space="preserve">4.05000972747803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.09554243087769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.1016960144043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.17184257507324</t>
   </si>
   <si>
     <t xml:space="preserve">4.15953540802002</t>
   </si>
   <si>
-    <t xml:space="preserve">4.12630844116211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.12999963760376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.09431266784668</t>
+    <t xml:space="preserve">4.12630891799927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.13000154495239</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.09431219100952</t>
   </si>
   <si>
     <t xml:space="preserve">4.33182334899902</t>
   </si>
   <si>
-    <t xml:space="preserve">4.34536027908325</t>
+    <t xml:space="preserve">4.34536123275757</t>
   </si>
   <si>
     <t xml:space="preserve">4.31828737258911</t>
@@ -1019,46 +1019,46 @@
     <t xml:space="preserve">4.25183248519897</t>
   </si>
   <si>
-    <t xml:space="preserve">4.28752136230469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.4007396697998</t>
+    <t xml:space="preserve">4.28752183914185</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.40073919296265</t>
   </si>
   <si>
     <t xml:space="preserve">4.51272630691528</t>
   </si>
   <si>
-    <t xml:space="preserve">4.48934507369995</t>
+    <t xml:space="preserve">4.48934459686279</t>
   </si>
   <si>
     <t xml:space="preserve">4.56564474105835</t>
   </si>
   <si>
-    <t xml:space="preserve">4.46719360351562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.40935373306274</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.47950029373169</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.54964590072632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.51518869400024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.54595375061035</t>
+    <t xml:space="preserve">4.46719408035278</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.40935468673706</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.47950124740601</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.54964637756348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.51518821716309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.54595422744751</t>
   </si>
   <si>
     <t xml:space="preserve">4.53733968734741</t>
   </si>
   <si>
-    <t xml:space="preserve">4.4954981803894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.45857954025269</t>
+    <t xml:space="preserve">4.49549913406372</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.45857906341553</t>
   </si>
   <si>
     <t xml:space="preserve">4.44258069992065</t>
@@ -1067,16 +1067,16 @@
     <t xml:space="preserve">4.45734882354736</t>
   </si>
   <si>
-    <t xml:space="preserve">4.52626466751099</t>
+    <t xml:space="preserve">4.52626371383667</t>
   </si>
   <si>
     <t xml:space="preserve">4.53487825393677</t>
   </si>
   <si>
-    <t xml:space="preserve">4.56933546066284</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.6456356048584</t>
+    <t xml:space="preserve">4.5693359375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.64563512802124</t>
   </si>
   <si>
     <t xml:space="preserve">4.64071273803711</t>
@@ -1085,34 +1085,34 @@
     <t xml:space="preserve">4.67640113830566</t>
   </si>
   <si>
-    <t xml:space="preserve">4.72808694839478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.72070360183716</t>
+    <t xml:space="preserve">4.72808790206909</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.72070264816284</t>
   </si>
   <si>
     <t xml:space="preserve">4.72439527511597</t>
   </si>
   <si>
-    <t xml:space="preserve">4.7219352722168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.75023889541626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.79331159591675</t>
+    <t xml:space="preserve">4.72193479537964</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.75023937225342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.79331111907959</t>
   </si>
   <si>
     <t xml:space="preserve">4.76377630233765</t>
   </si>
   <si>
-    <t xml:space="preserve">4.77362060546875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.84253549575806</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.84745931625366</t>
+    <t xml:space="preserve">4.77362155914307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.84253597259521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.8474588394165</t>
   </si>
   <si>
     <t xml:space="preserve">4.86837959289551</t>
@@ -1121,61 +1121,61 @@
     <t xml:space="preserve">4.87822484970093</t>
   </si>
   <si>
-    <t xml:space="preserve">4.90529870986938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.98775100708008</t>
+    <t xml:space="preserve">4.90529823303223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.98775148391724</t>
   </si>
   <si>
     <t xml:space="preserve">4.97421407699585</t>
   </si>
   <si>
-    <t xml:space="preserve">4.96559953689575</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.01728582382202</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.99390411376953</t>
+    <t xml:space="preserve">4.96560001373291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.01728630065918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.99390459060669</t>
   </si>
   <si>
     <t xml:space="preserve">4.97052240371704</t>
   </si>
   <si>
-    <t xml:space="preserve">5.01482439041138</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.05666637420654</t>
+    <t xml:space="preserve">5.01482391357422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.05666589736938</t>
   </si>
   <si>
     <t xml:space="preserve">4.86714887619019</t>
   </si>
   <si>
-    <t xml:space="preserve">4.8560733795166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.68870782852173</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.69855260848999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.73670148849487</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.71331977844238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.74162483215332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.66901683807373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.51887989044189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.31582593917847</t>
+    <t xml:space="preserve">4.85607385635376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.68870735168457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.69855213165283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.73670101165771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.71331930160522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.74162435531616</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.66901779174805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.51888036727905</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.31582546234131</t>
   </si>
   <si>
     <t xml:space="preserve">4.49672842025757</t>
@@ -1184,7 +1184,7 @@
     <t xml:space="preserve">4.50657415390015</t>
   </si>
   <si>
-    <t xml:space="preserve">4.59641075134277</t>
+    <t xml:space="preserve">4.5964093208313</t>
   </si>
   <si>
     <t xml:space="preserve">4.62225294113159</t>
@@ -1193,16 +1193,16 @@
     <t xml:space="preserve">4.50042104721069</t>
   </si>
   <si>
-    <t xml:space="preserve">4.49796009063721</t>
+    <t xml:space="preserve">4.49795961380005</t>
   </si>
   <si>
     <t xml:space="preserve">4.48073101043701</t>
   </si>
   <si>
-    <t xml:space="preserve">4.35889911651611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.52749490737915</t>
+    <t xml:space="preserve">4.35889768600464</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.52749443054199</t>
   </si>
   <si>
     <t xml:space="preserve">4.61363935470581</t>
@@ -1211,52 +1211,52 @@
     <t xml:space="preserve">4.70101356506348</t>
   </si>
   <si>
-    <t xml:space="preserve">4.81177043914795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.69486093521118</t>
+    <t xml:space="preserve">4.81177091598511</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.69486045837402</t>
   </si>
   <si>
     <t xml:space="preserve">4.76779079437256</t>
   </si>
   <si>
-    <t xml:space="preserve">4.81597566604614</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.83811616897583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.77820873260498</t>
+    <t xml:space="preserve">4.8159761428833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.83811569213867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.77820825576782</t>
   </si>
   <si>
     <t xml:space="preserve">4.78341865539551</t>
   </si>
   <si>
-    <t xml:space="preserve">4.72090673446655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.74304676055908</t>
+    <t xml:space="preserve">4.72090721130371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.74304533004761</t>
   </si>
   <si>
     <t xml:space="preserve">4.67532539367676</t>
   </si>
   <si>
-    <t xml:space="preserve">4.66881370544434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.71569776535034</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.72741842269897</t>
+    <t xml:space="preserve">4.66881322860718</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.7156982421875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.72741889953613</t>
   </si>
   <si>
     <t xml:space="preserve">4.83941841125488</t>
   </si>
   <si>
-    <t xml:space="preserve">4.87718439102173</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.92276525497437</t>
+    <t xml:space="preserve">4.87718534469604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.92276620864868</t>
   </si>
   <si>
     <t xml:space="preserve">4.87067365646362</t>
@@ -1271,31 +1271,31 @@
     <t xml:space="preserve">5.00220775604248</t>
   </si>
   <si>
-    <t xml:space="preserve">5.0543007850647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.08164978027344</t>
+    <t xml:space="preserve">5.05430030822754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.08164882659912</t>
   </si>
   <si>
     <t xml:space="preserve">5.02304553985596</t>
   </si>
   <si>
-    <t xml:space="preserve">5.03606843948364</t>
+    <t xml:space="preserve">5.03606796264648</t>
   </si>
   <si>
     <t xml:space="preserve">5.02044057846069</t>
   </si>
   <si>
-    <t xml:space="preserve">5.0295557975769</t>
+    <t xml:space="preserve">5.02955722808838</t>
   </si>
   <si>
     <t xml:space="preserve">5.11160230636597</t>
   </si>
   <si>
-    <t xml:space="preserve">5.13374137878418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.15588140487671</t>
+    <t xml:space="preserve">5.1337423324585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.15588092803955</t>
   </si>
   <si>
     <t xml:space="preserve">5.18713760375977</t>
@@ -1304,34 +1304,34 @@
     <t xml:space="preserve">5.17932319641113</t>
   </si>
   <si>
-    <t xml:space="preserve">4.89932441711426</t>
+    <t xml:space="preserve">4.89932489395142</t>
   </si>
   <si>
     <t xml:space="preserve">4.8498363494873</t>
   </si>
   <si>
-    <t xml:space="preserve">4.8342080116272</t>
+    <t xml:space="preserve">4.83420848846436</t>
   </si>
   <si>
     <t xml:space="preserve">4.77560377120972</t>
   </si>
   <si>
-    <t xml:space="preserve">4.62583780288696</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.6063027381897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.65448808670044</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.51644277572632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.46044301986694</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.39011764526367</t>
+    <t xml:space="preserve">4.62583827972412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.60630226135254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.6544885635376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.516441822052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.46044206619263</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.39011812210083</t>
   </si>
   <si>
     <t xml:space="preserve">4.52946615219116</t>
@@ -1340,7 +1340,7 @@
     <t xml:space="preserve">4.44090843200684</t>
   </si>
   <si>
-    <t xml:space="preserve">4.42397737503052</t>
+    <t xml:space="preserve">4.42397832870483</t>
   </si>
   <si>
     <t xml:space="preserve">4.41616439819336</t>
@@ -1349,28 +1349,28 @@
     <t xml:space="preserve">4.39923429489136</t>
   </si>
   <si>
-    <t xml:space="preserve">4.41876888275146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.36146640777588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.31848955154419</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.39141988754272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.50732660293579</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.59458160400391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.56593084335327</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.58416366577148</t>
+    <t xml:space="preserve">4.41876840591431</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.36146688461304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.31849050521851</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.39142084121704</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.50732707977295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.59458255767822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.56593132019043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.58416318893433</t>
   </si>
   <si>
     <t xml:space="preserve">4.68965101242065</t>
@@ -1385,43 +1385,43 @@
     <t xml:space="preserve">4.474769115448</t>
   </si>
   <si>
-    <t xml:space="preserve">4.50081586837769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.54379081726074</t>
+    <t xml:space="preserve">4.50081491470337</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.54379177093506</t>
   </si>
   <si>
     <t xml:space="preserve">4.52165174484253</t>
   </si>
   <si>
-    <t xml:space="preserve">4.50993204116821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.57113933563232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.60890769958496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.63104629516602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.6857442855835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.71309232711792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.68183660507202</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.48128080368042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.43309354782104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.35365295410156</t>
+    <t xml:space="preserve">4.50993061065674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.5711407661438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.6089072227478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.63104677200317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.68574476242065</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.71309280395508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.68183755874634</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.4812798500061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.4330940246582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.3536524772644</t>
   </si>
   <si>
     <t xml:space="preserve">4.36276865005493</t>
@@ -1430,82 +1430,82 @@
     <t xml:space="preserve">4.36667585372925</t>
   </si>
   <si>
-    <t xml:space="preserve">4.29765367507935</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.13876962661743</t>
+    <t xml:space="preserve">4.29765272140503</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.13877010345459</t>
   </si>
   <si>
     <t xml:space="preserve">4.16090965270996</t>
   </si>
   <si>
-    <t xml:space="preserve">4.20258378982544</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.08667707443237</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.06844520568848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.08407211303711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.15179347991943</t>
+    <t xml:space="preserve">4.2025842666626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.08667755126953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.06844472885132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.08407258987427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.15179300308228</t>
   </si>
   <si>
     <t xml:space="preserve">4.09970092773438</t>
   </si>
   <si>
-    <t xml:space="preserve">3.98509693145752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.08277034759521</t>
+    <t xml:space="preserve">3.98509669303894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.08276987075806</t>
   </si>
   <si>
     <t xml:space="preserve">4.06063079833984</t>
   </si>
   <si>
-    <t xml:space="preserve">4.06974697113037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9056556224823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99030542373657</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99421334266663</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.12053775787354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.02937507629395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.13486337661743</t>
+    <t xml:space="preserve">4.06974744796753</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90565538406372</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99030613899231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99421167373657</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.12053728103638</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.0293755531311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.13486289978027</t>
   </si>
   <si>
     <t xml:space="preserve">4.26639795303345</t>
   </si>
   <si>
-    <t xml:space="preserve">4.30025815963745</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.24035167694092</t>
+    <t xml:space="preserve">4.30025672912598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.24035120010376</t>
   </si>
   <si>
     <t xml:space="preserve">4.21300268173218</t>
   </si>
   <si>
-    <t xml:space="preserve">4.35235023498535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.44351243972778</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.47346591949463</t>
+    <t xml:space="preserve">4.35234975814819</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.44351291656494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.47346639633179</t>
   </si>
   <si>
     <t xml:space="preserve">4.482581615448</t>
@@ -1514,37 +1514,37 @@
     <t xml:space="preserve">4.48518753051758</t>
   </si>
   <si>
-    <t xml:space="preserve">4.34193134307861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.23253726959229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.24295520782471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.26769924163818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.15049076080322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.28723335266113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.26509523391724</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.45393133163452</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.43049001693726</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.3640718460083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.36537408828735</t>
+    <t xml:space="preserve">4.34193181991577</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.23253679275513</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.24295568466187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.2677001953125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.15049123764038</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.28723526000977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.26509428024292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.45393180847168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.4304895401001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.36407041549683</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.3653736114502</t>
   </si>
   <si>
     <t xml:space="preserve">4.47086143493652</t>
@@ -1553,10 +1553,10 @@
     <t xml:space="preserve">4.43569898605347</t>
   </si>
   <si>
-    <t xml:space="preserve">4.49430274963379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.25728178024292</t>
+    <t xml:space="preserve">4.49430227279663</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.25728130340576</t>
   </si>
   <si>
     <t xml:space="preserve">4.27811813354492</t>
@@ -1571,19 +1571,19 @@
     <t xml:space="preserve">4.44221067428589</t>
   </si>
   <si>
-    <t xml:space="preserve">4.512535572052</t>
+    <t xml:space="preserve">4.51253604888916</t>
   </si>
   <si>
     <t xml:space="preserve">4.49039649963379</t>
   </si>
   <si>
-    <t xml:space="preserve">4.48388528823853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.62844228744507</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.56462907791138</t>
+    <t xml:space="preserve">4.48388481140137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.62844133377075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.56462860107422</t>
   </si>
   <si>
     <t xml:space="preserve">4.49821043014526</t>
@@ -1595,16 +1595,16 @@
     <t xml:space="preserve">4.54769849777222</t>
   </si>
   <si>
-    <t xml:space="preserve">4.53858280181885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.55681562423706</t>
+    <t xml:space="preserve">4.53858184814453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.5568151473999</t>
   </si>
   <si>
     <t xml:space="preserve">4.61281394958496</t>
   </si>
   <si>
-    <t xml:space="preserve">4.58155822753906</t>
+    <t xml:space="preserve">4.58155870437622</t>
   </si>
   <si>
     <t xml:space="preserve">4.62713956832886</t>
@@ -1613,37 +1613,37 @@
     <t xml:space="preserve">4.6883487701416</t>
   </si>
   <si>
-    <t xml:space="preserve">4.70006942749023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.72220897674561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.70137166976929</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.78862714767456</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.81858158111572</t>
+    <t xml:space="preserve">4.70006990432739</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.72220945358276</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.70137214660645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.78862762451172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.81858110427856</t>
   </si>
   <si>
     <t xml:space="preserve">4.93969631195068</t>
   </si>
   <si>
-    <t xml:space="preserve">4.94881200790405</t>
+    <t xml:space="preserve">4.94881248474121</t>
   </si>
   <si>
     <t xml:space="preserve">4.90192890167236</t>
   </si>
   <si>
-    <t xml:space="preserve">4.94751024246216</t>
+    <t xml:space="preserve">4.947509765625</t>
   </si>
   <si>
     <t xml:space="preserve">4.95923137664795</t>
   </si>
   <si>
-    <t xml:space="preserve">5.0087194442749</t>
+    <t xml:space="preserve">5.00871896743774</t>
   </si>
   <si>
     <t xml:space="preserve">4.98657989501953</t>
@@ -1658,16 +1658,16 @@
     <t xml:space="preserve">4.7847204208374</t>
   </si>
   <si>
-    <t xml:space="preserve">4.89671945571899</t>
+    <t xml:space="preserve">4.89672040939331</t>
   </si>
   <si>
     <t xml:space="preserve">4.97746324539185</t>
   </si>
   <si>
-    <t xml:space="preserve">5.00481224060059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.85374307632446</t>
+    <t xml:space="preserve">5.00481271743774</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.85374355316162</t>
   </si>
   <si>
     <t xml:space="preserve">4.86937093734741</t>
@@ -1676,10 +1676,10 @@
     <t xml:space="preserve">4.92797565460205</t>
   </si>
   <si>
-    <t xml:space="preserve">5.00090551376343</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.05169582366943</t>
+    <t xml:space="preserve">5.00090599060059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.05169630050659</t>
   </si>
   <si>
     <t xml:space="preserve">4.9917893409729</t>
@@ -1691,10 +1691,10 @@
     <t xml:space="preserve">5.06211471557617</t>
   </si>
   <si>
-    <t xml:space="preserve">5.04648685455322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.03216171264648</t>
+    <t xml:space="preserve">5.04648637771606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.03216123580933</t>
   </si>
   <si>
     <t xml:space="preserve">5.06732416152954</t>
@@ -1703,10 +1703,10 @@
     <t xml:space="preserve">5.0881609916687</t>
   </si>
   <si>
-    <t xml:space="preserve">5.14285755157471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.14416074752808</t>
+    <t xml:space="preserve">5.14285850524902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.14416027069092</t>
   </si>
   <si>
     <t xml:space="preserve">5.16369581222534</t>
@@ -1715,13 +1715,13 @@
     <t xml:space="preserve">5.1676025390625</t>
   </si>
   <si>
-    <t xml:space="preserve">5.13895130157471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.16239404678345</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.17281103134155</t>
+    <t xml:space="preserve">5.13895177841187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.16239309310913</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.17281198501587</t>
   </si>
   <si>
     <t xml:space="preserve">5.17541646957397</t>
@@ -1730,67 +1730,67 @@
     <t xml:space="preserve">5.08685827255249</t>
   </si>
   <si>
-    <t xml:space="preserve">5.14546346664429</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.17020702362061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.18323040008545</t>
+    <t xml:space="preserve">5.14546394348145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.17020750045776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.18322992324829</t>
   </si>
   <si>
     <t xml:space="preserve">5.20406770706177</t>
   </si>
   <si>
-    <t xml:space="preserve">5.26136922836304</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.30695056915283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.44369411468506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.49578666687012</t>
+    <t xml:space="preserve">5.26136875152588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.30694961547852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.4436936378479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.49578619003296</t>
   </si>
   <si>
     <t xml:space="preserve">5.62471580505371</t>
   </si>
   <si>
-    <t xml:space="preserve">5.57392549514771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.59346008300781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.61560010910034</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.61690235137939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.59736680984497</t>
+    <t xml:space="preserve">5.57392644882202</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.59346103668213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.6156005859375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.61690282821655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.59736728668213</t>
   </si>
   <si>
     <t xml:space="preserve">5.64685583114624</t>
   </si>
   <si>
-    <t xml:space="preserve">5.63253021240234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.64946031570435</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.6950421333313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.69113397598267</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.7132740020752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.81094837188721</t>
+    <t xml:space="preserve">5.6325306892395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.64945983886719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.69504165649414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.69113445281982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.71327447891235</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.81094789505005</t>
   </si>
   <si>
     <t xml:space="preserve">5.83178472518921</t>
@@ -1799,22 +1799,22 @@
     <t xml:space="preserve">5.822669506073</t>
   </si>
   <si>
-    <t xml:space="preserve">5.8539252281189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.84350490570068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.90601587295532</t>
+    <t xml:space="preserve">5.85392379760742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.843505859375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.9060173034668</t>
   </si>
   <si>
     <t xml:space="preserve">5.86173820495605</t>
   </si>
   <si>
-    <t xml:space="preserve">6.19643449783325</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.19903993606567</t>
+    <t xml:space="preserve">6.19643497467041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.1990385055542</t>
   </si>
   <si>
     <t xml:space="preserve">6.16127157211304</t>
@@ -1823,49 +1823,49 @@
     <t xml:space="preserve">6.03104019165039</t>
   </si>
   <si>
-    <t xml:space="preserve">6.00629615783691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.02452754974365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.10396909713745</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.19252777099609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.14694595336914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.08703804016113</t>
+    <t xml:space="preserve">6.00629568099976</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.02452802658081</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.10397052764893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.19252681732178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.14694547653198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.08703994750977</t>
   </si>
   <si>
     <t xml:space="preserve">6.13262128829956</t>
   </si>
   <si>
-    <t xml:space="preserve">5.93857526779175</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.86564445495605</t>
+    <t xml:space="preserve">5.93857431411743</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.86564493179321</t>
   </si>
   <si>
     <t xml:space="preserve">5.860435962677</t>
   </si>
   <si>
-    <t xml:space="preserve">5.79271554946899</t>
+    <t xml:space="preserve">5.79271459579468</t>
   </si>
   <si>
     <t xml:space="preserve">5.97113275527954</t>
   </si>
   <si>
-    <t xml:space="preserve">5.9333667755127</t>
+    <t xml:space="preserve">5.93336534500122</t>
   </si>
   <si>
     <t xml:space="preserve">6.01020240783691</t>
   </si>
   <si>
-    <t xml:space="preserve">5.87606382369995</t>
+    <t xml:space="preserve">5.87606430053711</t>
   </si>
   <si>
     <t xml:space="preserve">5.92815589904785</t>
@@ -1874,37 +1874,37 @@
     <t xml:space="preserve">5.96592426300049</t>
   </si>
   <si>
-    <t xml:space="preserve">5.70936727523804</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.8083438873291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.79401683807373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.74843645095825</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.71848201751709</t>
+    <t xml:space="preserve">5.70936632156372</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.80834341049194</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.79401779174805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.74843740463257</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.71848344802856</t>
   </si>
   <si>
     <t xml:space="preserve">5.66508817672729</t>
   </si>
   <si>
-    <t xml:space="preserve">5.67680931091309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.82136535644531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.78099489212036</t>
+    <t xml:space="preserve">5.6768102645874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.82136631011963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.7809944152832</t>
   </si>
   <si>
     <t xml:space="preserve">5.81224966049194</t>
   </si>
   <si>
-    <t xml:space="preserve">5.92685413360596</t>
+    <t xml:space="preserve">5.9268536567688</t>
   </si>
   <si>
     <t xml:space="preserve">5.98285341262817</t>
@@ -1922,55 +1922,55 @@
     <t xml:space="preserve">6.04927206039429</t>
   </si>
   <si>
-    <t xml:space="preserve">6.10266876220703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.1951322555542</t>
+    <t xml:space="preserve">6.10266780853271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.19513130187988</t>
   </si>
   <si>
     <t xml:space="preserve">6.30506467819214</t>
   </si>
   <si>
-    <t xml:space="preserve">6.26136445999146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.23541688919067</t>
+    <t xml:space="preserve">6.26136350631714</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.23541784286499</t>
   </si>
   <si>
     <t xml:space="preserve">6.24088096618652</t>
   </si>
   <si>
-    <t xml:space="preserve">6.32281827926636</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.31189346313477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.46347570419312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.61642503738403</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.65739440917969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.63281297683716</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.6232533454895</t>
+    <t xml:space="preserve">6.32281684875488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.31189250946045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.46347618103027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.61642551422119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.65739488601685</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.63281393051147</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.62325477600098</t>
   </si>
   <si>
     <t xml:space="preserve">6.59184551239014</t>
   </si>
   <si>
-    <t xml:space="preserve">6.65602779388428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.59047889709473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.59457683563232</t>
+    <t xml:space="preserve">6.65602874755859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.59048080444336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.59457540512085</t>
   </si>
   <si>
     <t xml:space="preserve">6.56589794158936</t>
@@ -1982,136 +1982,136 @@
     <t xml:space="preserve">6.53175735473633</t>
   </si>
   <si>
-    <t xml:space="preserve">6.41840982437134</t>
+    <t xml:space="preserve">6.41841077804565</t>
   </si>
   <si>
     <t xml:space="preserve">6.44708824157715</t>
   </si>
   <si>
-    <t xml:space="preserve">6.40611982345581</t>
+    <t xml:space="preserve">6.40612077713013</t>
   </si>
   <si>
     <t xml:space="preserve">6.46893835067749</t>
   </si>
   <si>
-    <t xml:space="preserve">6.42250823974609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.5467791557312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.37607574462891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.5959415435791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.66149139404297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.5836501121521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.4784984588623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.47440052032471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.58091926574707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.14118957519531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.21356916427612</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.35695886611938</t>
+    <t xml:space="preserve">6.42250871658325</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.54677820205688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.37607717514038</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.59594106674194</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.66149091720581</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.58365106582642</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.47849702835083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.47440242767334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.58091831207275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.14119052886963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.21356773376465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.35695791244507</t>
   </si>
   <si>
     <t xml:space="preserve">6.24361181259155</t>
   </si>
   <si>
-    <t xml:space="preserve">6.48669099807739</t>
+    <t xml:space="preserve">6.48669195175171</t>
   </si>
   <si>
     <t xml:space="preserve">6.44162607192993</t>
   </si>
   <si>
-    <t xml:space="preserve">6.62188768386841</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.59867238998413</t>
+    <t xml:space="preserve">6.62188816070557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.59867191314697</t>
   </si>
   <si>
     <t xml:space="preserve">6.43206691741943</t>
   </si>
   <si>
-    <t xml:space="preserve">6.48532676696777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.41704368591309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.71884632110596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.67241525650024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.74342823028564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.75981569290161</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.88954925537109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.86223697662354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.87930631637573</t>
+    <t xml:space="preserve">6.48532581329346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.4170446395874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.71884679794312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.6724157333374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.74342966079712</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.75981426239014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.88955020904541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.86223793029785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.87930774688721</t>
   </si>
   <si>
     <t xml:space="preserve">6.88272142410278</t>
   </si>
   <si>
-    <t xml:space="preserve">6.76664352416992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.79395627975464</t>
+    <t xml:space="preserve">6.76664257049561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.7939567565918</t>
   </si>
   <si>
     <t xml:space="preserve">6.91344738006592</t>
   </si>
   <si>
-    <t xml:space="preserve">6.95441579818726</t>
+    <t xml:space="preserve">6.95441627502441</t>
   </si>
   <si>
     <t xml:space="preserve">6.86906623840332</t>
   </si>
   <si>
-    <t xml:space="preserve">6.81034231185913</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.93734693527222</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.95100212097168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.87247896194458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.01586866378784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.97490072250366</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.97148704528809</t>
+    <t xml:space="preserve">6.81034374237061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.93734550476074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.95100164413452</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.8724799156189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.01586818695068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.9749002456665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.97148656845093</t>
   </si>
   <si>
     <t xml:space="preserve">7.00562763214111</t>
@@ -2120,7 +2120,7 @@
     <t xml:space="preserve">7.12170457839966</t>
   </si>
   <si>
-    <t xml:space="preserve">7.02269697189331</t>
+    <t xml:space="preserve">7.02269792556763</t>
   </si>
   <si>
     <t xml:space="preserve">6.80351543426514</t>
@@ -2129,49 +2129,49 @@
     <t xml:space="preserve">6.81853771209717</t>
   </si>
   <si>
-    <t xml:space="preserve">6.81444072723389</t>
+    <t xml:space="preserve">6.81444025039673</t>
   </si>
   <si>
     <t xml:space="preserve">7.00904130935669</t>
   </si>
   <si>
-    <t xml:space="preserve">6.91686105728149</t>
+    <t xml:space="preserve">6.91686153411865</t>
   </si>
   <si>
     <t xml:space="preserve">6.99879884719849</t>
   </si>
   <si>
-    <t xml:space="preserve">7.22412633895874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.23436832427979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.33337593078613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.22753953933716</t>
+    <t xml:space="preserve">7.22412586212158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.23436880111694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.33337545394897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.22754049301147</t>
   </si>
   <si>
     <t xml:space="preserve">7.30947685241699</t>
   </si>
   <si>
-    <t xml:space="preserve">7.35044574737549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.37434434890747</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.45969486236572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.47676563262939</t>
+    <t xml:space="preserve">7.35044622421265</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.37434482574463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.45969533920288</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.47676610946655</t>
   </si>
   <si>
     <t xml:space="preserve">7.50407838821411</t>
   </si>
   <si>
-    <t xml:space="preserve">7.41531276702881</t>
+    <t xml:space="preserve">7.41531133651733</t>
   </si>
   <si>
     <t xml:space="preserve">7.44945335388184</t>
@@ -2180,22 +2180,22 @@
     <t xml:space="preserve">7.43579769134521</t>
   </si>
   <si>
-    <t xml:space="preserve">7.42897033691406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.53139019012451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.57577276229858</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.62698554992676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.50749349594116</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.40165615081787</t>
+    <t xml:space="preserve">7.42896795272827</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.53139114379883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.5757737159729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.62698411941528</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.50749206542969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.40165662765503</t>
   </si>
   <si>
     <t xml:space="preserve">7.49042224884033</t>
@@ -2207,13 +2207,13 @@
     <t xml:space="preserve">7.58942890167236</t>
   </si>
   <si>
-    <t xml:space="preserve">7.60650062561035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.62015628814697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.66100549697876</t>
+    <t xml:space="preserve">7.60649967193604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.62015581130981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.66100597381592</t>
   </si>
   <si>
     <t xml:space="preserve">7.52945613861084</t>
@@ -2222,34 +2222,34 @@
     <t xml:space="preserve">7.59869194030762</t>
   </si>
   <si>
-    <t xml:space="preserve">7.50522327423096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.56753540039062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.58830785751343</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.51907062530518</t>
+    <t xml:space="preserve">7.50522375106812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.56753635406494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.58830690383911</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.5190691947937</t>
   </si>
   <si>
     <t xml:space="preserve">7.47060632705688</t>
   </si>
   <si>
-    <t xml:space="preserve">7.36328887939453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.33213233947754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.09326696395874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.16942739486694</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.26289653778076</t>
+    <t xml:space="preserve">7.36329030990601</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.3321328163147</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.09326791763306</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.16942644119263</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.26289558410645</t>
   </si>
   <si>
     <t xml:space="preserve">7.13134717941284</t>
@@ -2258,49 +2258,49 @@
     <t xml:space="preserve">7.14173221588135</t>
   </si>
   <si>
-    <t xml:space="preserve">7.05172491073608</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.1521167755127</t>
+    <t xml:space="preserve">7.05172538757324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.15211772918701</t>
   </si>
   <si>
     <t xml:space="preserve">7.07249593734741</t>
   </si>
   <si>
-    <t xml:space="preserve">7.19019842147827</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.04134035110474</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.10365343093872</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.03787660598755</t>
+    <t xml:space="preserve">7.19019889831543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.04133939743042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.10365295410156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.03787851333618</t>
   </si>
   <si>
     <t xml:space="preserve">7.12788486480713</t>
   </si>
   <si>
-    <t xml:space="preserve">7.22135400772095</t>
+    <t xml:space="preserve">7.22135448455811</t>
   </si>
   <si>
     <t xml:space="preserve">7.00672149658203</t>
   </si>
   <si>
-    <t xml:space="preserve">7.05864953994751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.96864128112793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.90840625762939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.08634424209595</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.98941373825073</t>
+    <t xml:space="preserve">7.05864906311035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.96864223480225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.90840530395508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.08634281158447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.98941326141357</t>
   </si>
   <si>
     <t xml:space="preserve">7.10019111633301</t>
@@ -2309,37 +2309,37 @@
     <t xml:space="preserve">7.06903457641602</t>
   </si>
   <si>
-    <t xml:space="preserve">7.02749300003052</t>
+    <t xml:space="preserve">7.02749252319336</t>
   </si>
   <si>
     <t xml:space="preserve">6.96518087387085</t>
   </si>
   <si>
-    <t xml:space="preserve">6.95479536056519</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.12096118927002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.18673610687256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.20750761032104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.11403751373291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.32867002487183</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.67139148712158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.61254119873047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.16596651077271</t>
+    <t xml:space="preserve">6.95479345321655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.12096214294434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.18673753738403</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.20750713348389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.11403703689575</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.32867097854614</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.67139101028442</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.61253976821899</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.16596555709839</t>
   </si>
   <si>
     <t xml:space="preserve">7.27328252792358</t>
@@ -2351,25 +2351,25 @@
     <t xml:space="preserve">7.42560243606567</t>
   </si>
   <si>
-    <t xml:space="preserve">7.47406673431396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.55022716522217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.64023351669312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.60215473175049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.581383228302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.5709981918335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.85140609741211</t>
+    <t xml:space="preserve">7.47406721115112</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.55022573471069</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.64023494720459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.60215425491333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.58138418197632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.57099771499634</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.85140752792358</t>
   </si>
   <si>
     <t xml:space="preserve">7.96910810470581</t>
@@ -2381,25 +2381,25 @@
     <t xml:space="preserve">7.82024908065796</t>
   </si>
   <si>
-    <t xml:space="preserve">7.266357421875</t>
+    <t xml:space="preserve">7.26635599136353</t>
   </si>
   <si>
     <t xml:space="preserve">7.15558004379272</t>
   </si>
   <si>
-    <t xml:space="preserve">7.29751348495483</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.98249006271362</t>
+    <t xml:space="preserve">7.29751443862915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.98248910903931</t>
   </si>
   <si>
     <t xml:space="preserve">6.65638494491577</t>
   </si>
   <si>
-    <t xml:space="preserve">6.41267347335815</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.66054010391235</t>
+    <t xml:space="preserve">6.41267395019531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.6605396270752</t>
   </si>
   <si>
     <t xml:space="preserve">6.7076210975647</t>
@@ -2408,19 +2408,19 @@
     <t xml:space="preserve">6.5303750038147</t>
   </si>
   <si>
-    <t xml:space="preserve">6.73116111755371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.85601377487183</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.45444250106812</t>
+    <t xml:space="preserve">6.73116207122803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.85601282119751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.45444202423096</t>
   </si>
   <si>
     <t xml:space="preserve">5.45582723617554</t>
   </si>
   <si>
-    <t xml:space="preserve">4.25388288497925</t>
+    <t xml:space="preserve">4.25388336181641</t>
   </si>
   <si>
     <t xml:space="preserve">4.66930103302002</t>
@@ -2429,34 +2429,34 @@
     <t xml:space="preserve">4.50174951553345</t>
   </si>
   <si>
-    <t xml:space="preserve">4.49759483337402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.41035652160645</t>
+    <t xml:space="preserve">4.49759531021118</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.41035747528076</t>
   </si>
   <si>
     <t xml:space="preserve">4.78700304031372</t>
   </si>
   <si>
-    <t xml:space="preserve">4.80223560333252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.96840286254883</t>
+    <t xml:space="preserve">4.8022346496582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.96840238571167</t>
   </si>
   <si>
     <t xml:space="preserve">5.30766105651855</t>
   </si>
   <si>
-    <t xml:space="preserve">5.356125831604</t>
+    <t xml:space="preserve">5.35612678527832</t>
   </si>
   <si>
     <t xml:space="preserve">5.60676240921021</t>
   </si>
   <si>
-    <t xml:space="preserve">5.43644094467163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.48075199127197</t>
+    <t xml:space="preserve">5.43644046783447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.48075151443481</t>
   </si>
   <si>
     <t xml:space="preserve">5.34504842758179</t>
@@ -2465,85 +2465,85 @@
     <t xml:space="preserve">5.11795377731323</t>
   </si>
   <si>
-    <t xml:space="preserve">5.38105058670044</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.42120885848999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.56660509109497</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.64691972732544</t>
+    <t xml:space="preserve">5.38105201721191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.42120790481567</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.56660461425781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.64691877365112</t>
   </si>
   <si>
     <t xml:space="preserve">5.73138761520386</t>
   </si>
   <si>
-    <t xml:space="preserve">5.75077295303345</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.77431440353394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.26611995697021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.30904579162598</t>
+    <t xml:space="preserve">5.75077390670776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.77431392669678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.26611948013306</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.30904531478882</t>
   </si>
   <si>
     <t xml:space="preserve">5.33120107650757</t>
   </si>
   <si>
-    <t xml:space="preserve">5.27027320861816</t>
+    <t xml:space="preserve">5.27027368545532</t>
   </si>
   <si>
     <t xml:space="preserve">5.15811014175415</t>
   </si>
   <si>
-    <t xml:space="preserve">5.23980951309204</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.20519113540649</t>
+    <t xml:space="preserve">5.23980855941772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.20519018173218</t>
   </si>
   <si>
     <t xml:space="preserve">5.12210702896118</t>
   </si>
   <si>
-    <t xml:space="preserve">5.45721101760864</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.44751882553101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.55968141555786</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.36720418930054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.2370400428772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.08887386322021</t>
+    <t xml:space="preserve">5.4572114944458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.44751834869385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.5596809387207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.3672046661377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.23703956604004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.08887434005737</t>
   </si>
   <si>
     <t xml:space="preserve">5.00440549850464</t>
   </si>
   <si>
-    <t xml:space="preserve">5.25781011581421</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.36997318267822</t>
+    <t xml:space="preserve">5.25781059265137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.36997413635254</t>
   </si>
   <si>
     <t xml:space="preserve">5.15534114837646</t>
   </si>
   <si>
-    <t xml:space="preserve">5.06118011474609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.97532558441162</t>
+    <t xml:space="preserve">5.06117963790894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.97532653808594</t>
   </si>
   <si>
     <t xml:space="preserve">5.16641855239868</t>
@@ -2552,55 +2552,55 @@
     <t xml:space="preserve">5.12626123428345</t>
   </si>
   <si>
-    <t xml:space="preserve">5.13456964492798</t>
+    <t xml:space="preserve">5.13457059860229</t>
   </si>
   <si>
     <t xml:space="preserve">5.10272121429443</t>
   </si>
   <si>
-    <t xml:space="preserve">5.15257120132446</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.35751104354858</t>
+    <t xml:space="preserve">5.15257167816162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.35751056671143</t>
   </si>
   <si>
     <t xml:space="preserve">5.43782520294189</t>
   </si>
   <si>
-    <t xml:space="preserve">5.46551990509033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.51537036895752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.57906770706177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.74800395965576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.93217277526855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.07203102111816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.19804048538208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.00694799423218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.93771171569824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.62476301193237</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.71061754226685</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.75908136367798</t>
+    <t xml:space="preserve">5.46552038192749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.51536989212036</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.57906675338745</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.74800491333008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.93217372894287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.07203054428101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.19804096221924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.00694847106934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.93771266937256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.62476396560669</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.71061658859253</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.75908184051514</t>
   </si>
   <si>
     <t xml:space="preserve">5.87539958953857</t>
@@ -2609,13 +2609,13 @@
     <t xml:space="preserve">5.84908962249756</t>
   </si>
   <si>
-    <t xml:space="preserve">5.8075475692749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.69123029708862</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.80849361419678</t>
+    <t xml:space="preserve">5.80754661560059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.69123125076294</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.80849456787109</t>
   </si>
   <si>
     <t xml:space="preserve">5.90777206420898</t>
@@ -2624,10 +2624,10 @@
     <t xml:space="preserve">5.64590740203857</t>
   </si>
   <si>
-    <t xml:space="preserve">5.68619394302368</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.57252883911133</t>
+    <t xml:space="preserve">5.686194896698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.57252836227417</t>
   </si>
   <si>
     <t xml:space="preserve">5.74230766296387</t>
@@ -2636,58 +2636,58 @@
     <t xml:space="preserve">5.56821155548096</t>
   </si>
   <si>
-    <t xml:space="preserve">5.57828330993652</t>
+    <t xml:space="preserve">5.57828426361084</t>
   </si>
   <si>
     <t xml:space="preserve">5.60274362564087</t>
   </si>
   <si>
-    <t xml:space="preserve">5.69338941574097</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.66173458099365</t>
+    <t xml:space="preserve">5.69338893890381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.66173410415649</t>
   </si>
   <si>
     <t xml:space="preserve">5.61713075637817</t>
   </si>
   <si>
-    <t xml:space="preserve">5.48476076126099</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.5322413444519</t>
+    <t xml:space="preserve">5.48476123809814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.53224086761475</t>
   </si>
   <si>
     <t xml:space="preserve">5.63727474212646</t>
   </si>
   <si>
-    <t xml:space="preserve">5.61569213867188</t>
+    <t xml:space="preserve">5.61569261550903</t>
   </si>
   <si>
     <t xml:space="preserve">5.64015293121338</t>
   </si>
   <si>
-    <t xml:space="preserve">5.65597867965698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.88906717300415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.93223237991333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.9854679107666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.89050579071045</t>
+    <t xml:space="preserve">5.65597915649414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.88906764984131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.93223094940186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.98546743392944</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.89050531387329</t>
   </si>
   <si>
     <t xml:space="preserve">5.86172962188721</t>
   </si>
   <si>
-    <t xml:space="preserve">5.71497011184692</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.68331718444824</t>
+    <t xml:space="preserve">5.71497058868408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.6833176612854</t>
   </si>
   <si>
     <t xml:space="preserve">5.66892862319946</t>
@@ -2699,7 +2699,7 @@
     <t xml:space="preserve">5.57684469223022</t>
   </si>
   <si>
-    <t xml:space="preserve">5.68043899536133</t>
+    <t xml:space="preserve">5.68043947219849</t>
   </si>
   <si>
     <t xml:space="preserve">5.71928739547729</t>
@@ -2711,16 +2711,16 @@
     <t xml:space="preserve">5.6286416053772</t>
   </si>
   <si>
-    <t xml:space="preserve">5.67324542999268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.77252340316772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.86460781097412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.85741376876831</t>
+    <t xml:space="preserve">5.67324495315552</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.77252292633057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.86460733413696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.85741424560547</t>
   </si>
   <si>
     <t xml:space="preserve">5.78691148757935</t>
@@ -2732,7 +2732,7 @@
     <t xml:space="preserve">5.67180633544922</t>
   </si>
   <si>
-    <t xml:space="preserve">5.65310144424438</t>
+    <t xml:space="preserve">5.65310192108154</t>
   </si>
   <si>
     <t xml:space="preserve">5.71209335327148</t>
@@ -2741,16 +2741,16 @@
     <t xml:space="preserve">5.61425447463989</t>
   </si>
   <si>
-    <t xml:space="preserve">5.69051122665405</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.70921564102173</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.64303064346313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.64734601974487</t>
+    <t xml:space="preserve">5.69051027297974</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.70921611785889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.64303016662598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.64734649658203</t>
   </si>
   <si>
     <t xml:space="preserve">5.56389570236206</t>
@@ -2762,64 +2762,64 @@
     <t xml:space="preserve">5.5336799621582</t>
   </si>
   <si>
-    <t xml:space="preserve">5.72504234313965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.60705995559692</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.74086999893188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.73079824447632</t>
+    <t xml:space="preserve">5.72504281997681</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.60705947875977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.74086952209473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.73079776763916</t>
   </si>
   <si>
     <t xml:space="preserve">5.7336745262146</t>
   </si>
   <si>
-    <t xml:space="preserve">5.70058345794678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.58403968811035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.38979864120483</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.46605634689331</t>
+    <t xml:space="preserve">5.70058250427246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.58403873443604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.38979911804199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.46605587005615</t>
   </si>
   <si>
     <t xml:space="preserve">5.51065921783447</t>
   </si>
   <si>
-    <t xml:space="preserve">5.49914884567261</t>
+    <t xml:space="preserve">5.49914789199829</t>
   </si>
   <si>
     <t xml:space="preserve">5.45742273330688</t>
   </si>
   <si>
-    <t xml:space="preserve">5.56101703643799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.45022869110107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.44447374343872</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.40418672561646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.43584156036377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.8185658454895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.76820659637451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.76532936096191</t>
+    <t xml:space="preserve">5.56101751327515</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.45022916793823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.44447326660156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.4041862487793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.43584108352661</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.81856632232666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.76820611953735</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.76532888412476</t>
   </si>
   <si>
     <t xml:space="preserve">5.76676797866821</t>
@@ -2828,7 +2828,7 @@
     <t xml:space="preserve">5.77971744537354</t>
   </si>
   <si>
-    <t xml:space="preserve">5.78115653991699</t>
+    <t xml:space="preserve">5.78115606307983</t>
   </si>
   <si>
     <t xml:space="preserve">5.49195432662964</t>
@@ -2837,64 +2837,64 @@
     <t xml:space="preserve">5.55957889556885</t>
   </si>
   <si>
-    <t xml:space="preserve">5.56677293777466</t>
+    <t xml:space="preserve">5.5667724609375</t>
   </si>
   <si>
     <t xml:space="preserve">5.4631781578064</t>
   </si>
   <si>
-    <t xml:space="preserve">5.47181177139282</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.4617395401001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.37397193908691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.33512353897095</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.11066913604736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.0416054725647</t>
+    <t xml:space="preserve">5.47181129455566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.46173906326294</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.3739709854126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.33512401580811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.11066818237305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.04160499572754</t>
   </si>
   <si>
     <t xml:space="preserve">5.03585004806519</t>
   </si>
   <si>
-    <t xml:space="preserve">5.15671110153198</t>
+    <t xml:space="preserve">5.15671062469482</t>
   </si>
   <si>
     <t xml:space="preserve">5.2056303024292</t>
   </si>
   <si>
-    <t xml:space="preserve">5.3696551322937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.54662942886353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.45598459243774</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.64878559112549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.78834962844849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.74662446975708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.92072105407715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.11783933639526</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.19697332382202</t>
+    <t xml:space="preserve">5.36965560913086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.54663038253784</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.4559850692749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.64878511428833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.78835010528564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.74662399291992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.92072057723999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.11783885955811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.19697380065918</t>
   </si>
   <si>
     <t xml:space="preserve">6.30200719833374</t>
@@ -2903,34 +2903,34 @@
     <t xml:space="preserve">6.36963081359863</t>
   </si>
   <si>
-    <t xml:space="preserve">6.27179288864136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.30493879318237</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.44713354110718</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.38556385040283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.45006513595581</t>
+    <t xml:space="preserve">6.2717924118042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.30493927001953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.44713401794434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.38556432723999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.45006608963013</t>
   </si>
   <si>
     <t xml:space="preserve">6.26242685317993</t>
   </si>
   <si>
-    <t xml:space="preserve">6.31226873397827</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.21112060546875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.23310947418213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.16274356842041</t>
+    <t xml:space="preserve">6.31226968765259</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.21112012863159</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.23310899734497</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.16274452209473</t>
   </si>
   <si>
     <t xml:space="preserve">6.1524829864502</t>
@@ -2939,25 +2939,25 @@
     <t xml:space="preserve">6.16127872467041</t>
   </si>
   <si>
-    <t xml:space="preserve">6.17007493972778</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.12023258209229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.11583471298218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.21405172348022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.1495509147644</t>
+    <t xml:space="preserve">6.17007398605347</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.12023305892944</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.11583423614502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.21405124664307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.14955186843872</t>
   </si>
   <si>
     <t xml:space="preserve">6.12609577178955</t>
   </si>
   <si>
-    <t xml:space="preserve">5.98536777496338</t>
+    <t xml:space="preserve">5.98536729812622</t>
   </si>
   <si>
     <t xml:space="preserve">6.10850477218628</t>
@@ -2966,7 +2966,7 @@
     <t xml:space="preserve">6.13342618942261</t>
   </si>
   <si>
-    <t xml:space="preserve">6.09824371337891</t>
+    <t xml:space="preserve">6.09824323654175</t>
   </si>
   <si>
     <t xml:space="preserve">6.11436891555786</t>
@@ -2975,25 +2975,25 @@
     <t xml:space="preserve">6.07478952407837</t>
   </si>
   <si>
-    <t xml:space="preserve">6.25949573516846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.38996362686157</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.29907512664795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.25509691238403</t>
+    <t xml:space="preserve">6.2594952583313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.38996315002441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.29907560348511</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.25509834289551</t>
   </si>
   <si>
     <t xml:space="preserve">6.18180131912231</t>
   </si>
   <si>
-    <t xml:space="preserve">6.1216983795166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.14222097396851</t>
+    <t xml:space="preserve">6.12169885635376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.14222145080566</t>
   </si>
   <si>
     <t xml:space="preserve">6.09091472625732</t>
@@ -3005,229 +3005,229 @@
     <t xml:space="preserve">6.09677743911743</t>
   </si>
   <si>
-    <t xml:space="preserve">6.06012916564941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.01615190505981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.12902879714966</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.98097038269043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.0352087020874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.9194016456604</t>
+    <t xml:space="preserve">6.06012964248657</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.01615238189697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.1290283203125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.98096990585327</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.03520965576172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.91940116882324</t>
   </si>
   <si>
     <t xml:space="preserve">6.07918643951416</t>
   </si>
   <si>
-    <t xml:space="preserve">6.06892538070679</t>
+    <t xml:space="preserve">6.06892490386963</t>
   </si>
   <si>
     <t xml:space="preserve">6.50137329101562</t>
   </si>
   <si>
-    <t xml:space="preserve">6.6054539680481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.75790977478027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.93088817596436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.01444578170776</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.97340059280396</t>
+    <t xml:space="preserve">6.60545253753662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.75790929794312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.93088865280151</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.01444482803345</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.97339963912964</t>
   </si>
   <si>
     <t xml:space="preserve">7.07308292388916</t>
   </si>
   <si>
-    <t xml:space="preserve">7.09360599517822</t>
+    <t xml:space="preserve">7.09360647201538</t>
   </si>
   <si>
     <t xml:space="preserve">7.16103887557983</t>
   </si>
   <si>
-    <t xml:space="preserve">7.07454919815063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.9499454498291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.81947755813599</t>
+    <t xml:space="preserve">7.07455110549927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.94994688034058</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.81947803497314</t>
   </si>
   <si>
     <t xml:space="preserve">6.88837623596191</t>
   </si>
   <si>
-    <t xml:space="preserve">7.06868505477905</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.98366165161133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.99978685379028</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.04229831695557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.89277410507202</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.20355033874512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.23873281478882</t>
+    <t xml:space="preserve">7.06868553161621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.98366212844849</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.99978733062744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.04229927062988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.89277601242065</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.2035493850708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.23873329162598</t>
   </si>
   <si>
     <t xml:space="preserve">7.29297208786011</t>
   </si>
   <si>
-    <t xml:space="preserve">7.3105616569519</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.21967601776123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.3589391708374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.43223571777344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.49819898605347</t>
+    <t xml:space="preserve">7.31056308746338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.21967506408691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.35893821716309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.4322338104248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.4982008934021</t>
   </si>
   <si>
     <t xml:space="preserve">7.46521806716919</t>
   </si>
   <si>
-    <t xml:space="preserve">7.53118371963501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.48720693588257</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.64845895767212</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.60814523696899</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.6631178855896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.57882690429688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.69976568222046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.63379812240601</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.67411279678345</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.66678333282471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.73274993896484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.90133094787598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.95630216598511</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.94530820846558</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.99661540985107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.01860427856445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.00760936737061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.89400005340576</t>
+    <t xml:space="preserve">7.53118324279785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.48720645904541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.64845848083496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.60814714431763</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.66311693191528</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.57882642745972</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.69976615905762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.63379955291748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.67411231994629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.66678190231323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.73274898529053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.90133047103882</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.95630264282227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.94530773162842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.99661493301392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.01860237121582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.00761032104492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.89400148391724</t>
   </si>
   <si>
     <t xml:space="preserve">7.91232395172119</t>
   </si>
   <si>
-    <t xml:space="preserve">7.90499401092529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.81703996658325</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.80971002578735</t>
+    <t xml:space="preserve">7.90499544143677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.81704044342041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.8097095489502</t>
   </si>
   <si>
     <t xml:space="preserve">7.89766550064087</t>
   </si>
   <si>
-    <t xml:space="preserve">7.88667058944702</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.78039216995239</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.77672624588013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.95263767242432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.92331838607788</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.93431329727173</t>
+    <t xml:space="preserve">7.88667154312134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.78039121627808</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.77672576904297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.95263671875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.92331886291504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.93431377410889</t>
   </si>
   <si>
     <t xml:space="preserve">8.00394535064697</t>
   </si>
   <si>
-    <t xml:space="preserve">8.00028038024902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.98928499221802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.09922981262207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.04059410095215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.01127433776855</t>
+    <t xml:space="preserve">8.00028133392334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.98928594589233</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.09923076629639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.04059314727783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.01127529144287</t>
   </si>
   <si>
     <t xml:space="preserve">8.06258201599121</t>
   </si>
   <si>
-    <t xml:space="preserve">8.22749805450439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.19085025787354</t>
+    <t xml:space="preserve">8.22749900817871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.19084930419922</t>
   </si>
   <si>
     <t xml:space="preserve">8.08823585510254</t>
   </si>
   <si>
-    <t xml:space="preserve">8.09190082550049</t>
+    <t xml:space="preserve">8.09189987182617</t>
   </si>
   <si>
     <t xml:space="preserve">8.15053749084473</t>
@@ -3236,61 +3236,61 @@
     <t xml:space="preserve">8.2751407623291</t>
   </si>
   <si>
-    <t xml:space="preserve">8.26414680480957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.23116302490234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.30079555511475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.42906379699707</t>
+    <t xml:space="preserve">8.26414489746094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.23116207122803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.30079460144043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.42906188964844</t>
   </si>
   <si>
     <t xml:space="preserve">8.57565498352051</t>
   </si>
   <si>
-    <t xml:space="preserve">8.46204662322998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.37042713165283</t>
+    <t xml:space="preserve">8.46204471588135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.37042617797852</t>
   </si>
   <si>
     <t xml:space="preserve">8.42173290252686</t>
   </si>
   <si>
-    <t xml:space="preserve">8.4327278137207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.47670555114746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.64895248413086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.72957897186279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.83952045440674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.85418033599854</t>
+    <t xml:space="preserve">8.43272686004639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.47670650482178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.64895153045654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.72957611083984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.83952236175537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.85418128967285</t>
   </si>
   <si>
     <t xml:space="preserve">8.78454875946045</t>
   </si>
   <si>
-    <t xml:space="preserve">8.80653953552246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.78088474273682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.84685039520264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.79187965393066</t>
+    <t xml:space="preserve">8.80653858184814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.7808837890625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.84685230255127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.79187679290771</t>
   </si>
   <si>
     <t xml:space="preserve">8.57199001312256</t>
@@ -3299,43 +3299,43 @@
     <t xml:space="preserve">8.68054485321045</t>
   </si>
   <si>
-    <t xml:space="preserve">8.56369590759277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.46192741394043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.61269760131836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.58631420135498</t>
+    <t xml:space="preserve">8.56369686126709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.46192836761475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.61269855499268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.58631324768066</t>
   </si>
   <si>
     <t xml:space="preserve">8.44685077667236</t>
   </si>
   <si>
-    <t xml:space="preserve">8.40915966033936</t>
+    <t xml:space="preserve">8.40915870666504</t>
   </si>
   <si>
     <t xml:space="preserve">8.4053897857666</t>
   </si>
   <si>
-    <t xml:space="preserve">8.50339126586914</t>
+    <t xml:space="preserve">8.50339031219482</t>
   </si>
   <si>
     <t xml:space="preserve">8.42800617218018</t>
   </si>
   <si>
-    <t xml:space="preserve">8.54862117767334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.4204683303833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.45439052581787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.1603889465332</t>
+    <t xml:space="preserve">8.54862213134766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.42046642303467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.45438957214355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.16038990020752</t>
   </si>
   <si>
     <t xml:space="preserve">8.28854465484619</t>
@@ -3344,55 +3344,55 @@
     <t xml:space="preserve">8.31869792938232</t>
   </si>
   <si>
-    <t xml:space="preserve">8.31492805480957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.28477382659912</t>
+    <t xml:space="preserve">8.31492900848389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.28477478027344</t>
   </si>
   <si>
     <t xml:space="preserve">8.17169761657715</t>
   </si>
   <si>
-    <t xml:space="preserve">8.19808197021484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.91915893554688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.99831342697144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.25085258483887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.37523555755615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.45062065124512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.51846790313721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.43554306030273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.41669940948486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.3865442276001</t>
+    <t xml:space="preserve">8.19808292388916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.91915941238403</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.99831247329712</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.25085163116455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.37523651123047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.4506196975708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.51846694946289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.43554401397705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.41669654846191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.38654327392578</t>
   </si>
   <si>
     <t xml:space="preserve">8.55992794036865</t>
   </si>
   <si>
-    <t xml:space="preserve">8.68808078765869</t>
+    <t xml:space="preserve">8.68808174133301</t>
   </si>
   <si>
     <t xml:space="preserve">8.72954368591309</t>
   </si>
   <si>
-    <t xml:space="preserve">8.76346588134766</t>
+    <t xml:space="preserve">8.76346683502197</t>
   </si>
   <si>
     <t xml:space="preserve">8.8350830078125</t>
@@ -3401,31 +3401,31 @@
     <t xml:space="preserve">8.853928565979</t>
   </si>
   <si>
-    <t xml:space="preserve">8.8086986541748</t>
+    <t xml:space="preserve">8.80869960784912</t>
   </si>
   <si>
     <t xml:space="preserve">8.75215911865234</t>
   </si>
   <si>
-    <t xml:space="preserve">8.70316028594971</t>
+    <t xml:space="preserve">8.70316123962402</t>
   </si>
   <si>
     <t xml:space="preserve">8.77477550506592</t>
   </si>
   <si>
-    <t xml:space="preserve">8.66546630859375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.60138988494873</t>
+    <t xml:space="preserve">8.66546726226807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.60138893127441</t>
   </si>
   <si>
     <t xml:space="preserve">8.78985214233398</t>
   </si>
   <si>
-    <t xml:space="preserve">8.76723670959473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.73708248138428</t>
+    <t xml:space="preserve">8.76723575592041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.73708343505859</t>
   </si>
   <si>
     <t xml:space="preserve">8.65792942047119</t>
@@ -3437,49 +3437,49 @@
     <t xml:space="preserve">8.74085235595703</t>
   </si>
   <si>
-    <t xml:space="preserve">8.77100563049316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.63908195495605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.69938945770264</t>
+    <t xml:space="preserve">8.77100658416748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.63908290863037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.69939136505127</t>
   </si>
   <si>
     <t xml:space="preserve">8.71446704864502</t>
   </si>
   <si>
-    <t xml:space="preserve">8.79362201690674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.93308448791504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.85015964508057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.88408279418945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.96323680877686</t>
+    <t xml:space="preserve">8.79362106323242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.93308353424072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.85016059875488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.88408374786377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.96323776245117</t>
   </si>
   <si>
     <t xml:space="preserve">9.02731418609619</t>
   </si>
   <si>
-    <t xml:space="preserve">8.9933910369873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.07631397247314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.85769844055176</t>
+    <t xml:space="preserve">8.99339199066162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.07631301879883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.85769748687744</t>
   </si>
   <si>
     <t xml:space="preserve">8.91800594329834</t>
   </si>
   <si>
-    <t xml:space="preserve">8.97454452514648</t>
+    <t xml:space="preserve">8.97454357147217</t>
   </si>
   <si>
     <t xml:space="preserve">8.93685150146484</t>
@@ -3491,37 +3491,37 @@
     <t xml:space="preserve">9.0650053024292</t>
   </si>
   <si>
-    <t xml:space="preserve">9.1780834197998</t>
+    <t xml:space="preserve">9.17808151245117</t>
   </si>
   <si>
     <t xml:space="preserve">9.18185234069824</t>
   </si>
   <si>
-    <t xml:space="preserve">9.16677570343018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.28739070892334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.32131290435791</t>
+    <t xml:space="preserve">9.16677474975586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.28738975524902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.32131385803223</t>
   </si>
   <si>
     <t xml:space="preserve">9.42308330535889</t>
   </si>
   <si>
-    <t xml:space="preserve">9.36654472351074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.33639144897461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.23462200164795</t>
+    <t xml:space="preserve">9.36654567718506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.33639240264893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.23462009429932</t>
   </si>
   <si>
     <t xml:space="preserve">9.46454524993896</t>
   </si>
   <si>
-    <t xml:space="preserve">9.43062114715576</t>
+    <t xml:space="preserve">9.43062210083008</t>
   </si>
   <si>
     <t xml:space="preserve">9.41177558898926</t>
@@ -3530,40 +3530,40 @@
     <t xml:space="preserve">9.55500602722168</t>
   </si>
   <si>
-    <t xml:space="preserve">9.47208118438721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.45700645446777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.30246829986572</t>
+    <t xml:space="preserve">9.47208213806152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.45700740814209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.30246734619141</t>
   </si>
   <si>
     <t xml:space="preserve">9.38162136077881</t>
   </si>
   <si>
-    <t xml:space="preserve">9.34769821166992</t>
+    <t xml:space="preserve">9.34769916534424</t>
   </si>
   <si>
     <t xml:space="preserve">9.46077537536621</t>
   </si>
   <si>
-    <t xml:space="preserve">9.39292907714844</t>
+    <t xml:space="preserve">9.39293003082275</t>
   </si>
   <si>
     <t xml:space="preserve">9.41931438446045</t>
   </si>
   <si>
-    <t xml:space="preserve">9.37785243988037</t>
+    <t xml:space="preserve">9.37785148620605</t>
   </si>
   <si>
     <t xml:space="preserve">9.28362083435059</t>
   </si>
   <si>
-    <t xml:space="preserve">9.23085117340088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.24216079711914</t>
+    <t xml:space="preserve">9.23085021972656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.24215984344482</t>
   </si>
   <si>
     <t xml:space="preserve">9.15546798706055</t>
@@ -3575,13 +3575,13 @@
     <t xml:space="preserve">9.07601928710938</t>
   </si>
   <si>
-    <t xml:space="preserve">9.00328922271729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.9764928817749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.84251689910889</t>
+    <t xml:space="preserve">9.0032901763916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.97649478912354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.84251594543457</t>
   </si>
   <si>
     <t xml:space="preserve">8.47886371612549</t>
@@ -3596,19 +3596,19 @@
     <t xml:space="preserve">8.6894006729126</t>
   </si>
   <si>
-    <t xml:space="preserve">8.59752941131592</t>
+    <t xml:space="preserve">8.59752750396729</t>
   </si>
   <si>
     <t xml:space="preserve">8.53245449066162</t>
   </si>
   <si>
-    <t xml:space="preserve">8.56307792663574</t>
+    <t xml:space="preserve">8.56307601928711</t>
   </si>
   <si>
     <t xml:space="preserve">8.68174457550049</t>
   </si>
   <si>
-    <t xml:space="preserve">8.55924892425537</t>
+    <t xml:space="preserve">8.55924987792969</t>
   </si>
   <si>
     <t xml:space="preserve">8.49800300598145</t>
@@ -3617,61 +3617,61 @@
     <t xml:space="preserve">8.4597225189209</t>
   </si>
   <si>
-    <t xml:space="preserve">8.46355247497559</t>
+    <t xml:space="preserve">8.46355152130127</t>
   </si>
   <si>
     <t xml:space="preserve">8.48269176483154</t>
   </si>
   <si>
-    <t xml:space="preserve">8.52097034454346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.5822172164917</t>
+    <t xml:space="preserve">8.52096939086914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.58221626281738</t>
   </si>
   <si>
     <t xml:space="preserve">8.59370136260986</t>
   </si>
   <si>
-    <t xml:space="preserve">8.39847755432129</t>
+    <t xml:space="preserve">8.39847660064697</t>
   </si>
   <si>
     <t xml:space="preserve">8.53628158569336</t>
   </si>
   <si>
-    <t xml:space="preserve">8.62049579620361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.69705486297607</t>
+    <t xml:space="preserve">8.62049674987793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.69705390930176</t>
   </si>
   <si>
     <t xml:space="preserve">8.77361392974854</t>
   </si>
   <si>
-    <t xml:space="preserve">8.84634494781494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.82720375061035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.83485984802246</t>
+    <t xml:space="preserve">8.84634399414062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.82720565795898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.83486080169678</t>
   </si>
   <si>
     <t xml:space="preserve">8.96118259429932</t>
   </si>
   <si>
-    <t xml:space="preserve">8.97266578674316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.00711727142334</t>
+    <t xml:space="preserve">8.97266674041748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.00711822509766</t>
   </si>
   <si>
     <t xml:space="preserve">8.93055820465088</t>
   </si>
   <si>
-    <t xml:space="preserve">8.95735263824463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.98414897918701</t>
+    <t xml:space="preserve">8.95735454559326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.98415088653564</t>
   </si>
   <si>
     <t xml:space="preserve">8.92290306091309</t>
@@ -3686,22 +3686,22 @@
     <t xml:space="preserve">8.85400009155273</t>
   </si>
   <si>
-    <t xml:space="preserve">8.87313938140869</t>
+    <t xml:space="preserve">8.87314033508301</t>
   </si>
   <si>
     <t xml:space="preserve">8.94587135314941</t>
   </si>
   <si>
-    <t xml:space="preserve">8.79275226593018</t>
+    <t xml:space="preserve">8.79275417327881</t>
   </si>
   <si>
     <t xml:space="preserve">8.44058322906494</t>
   </si>
   <si>
-    <t xml:space="preserve">8.64729118347168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.83868789672852</t>
+    <t xml:space="preserve">8.647292137146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.83868980407715</t>
   </si>
   <si>
     <t xml:space="preserve">8.73150634765625</t>
@@ -3710,16 +3710,16 @@
     <t xml:space="preserve">9.1334400177002</t>
   </si>
   <si>
-    <t xml:space="preserve">9.14109420776367</t>
+    <t xml:space="preserve">9.14109325408936</t>
   </si>
   <si>
     <t xml:space="preserve">8.33722972869873</t>
   </si>
   <si>
-    <t xml:space="preserve">8.39082145690918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.42910003662109</t>
+    <t xml:space="preserve">8.39081954956055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.42910099029541</t>
   </si>
   <si>
     <t xml:space="preserve">8.26449871063232</t>
@@ -3737,19 +3737,19 @@
     <t xml:space="preserve">8.44824028015137</t>
   </si>
   <si>
-    <t xml:space="preserve">8.24153137207031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.21090984344482</t>
+    <t xml:space="preserve">8.24153232574463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.21090888977051</t>
   </si>
   <si>
     <t xml:space="preserve">8.14200496673584</t>
   </si>
   <si>
-    <t xml:space="preserve">7.68648242950439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.93912506103516</t>
+    <t xml:space="preserve">7.68648290634155</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.93912553787231</t>
   </si>
   <si>
     <t xml:space="preserve">7.86639404296875</t>
@@ -3758,100 +3758,100 @@
     <t xml:space="preserve">7.54867601394653</t>
   </si>
   <si>
-    <t xml:space="preserve">7.53642702102661</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.43077564239502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.95151996612549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.80146455764771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.1168851852417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.74772834777832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.35574769973755</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.40015316009521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.60073661804199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.55939292907715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.90084648132324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.73624467849731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.71327638626099</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.74390029907227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.94678163528442</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.93529605865479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.07693099975586</t>
+    <t xml:space="preserve">7.53642606735229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.43077659606934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.95151901245117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.80146408081055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.11688566207886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.74772930145264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.35574913024902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.4001522064209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.60073614120483</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.55939340591431</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.90084457397461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.73624420166016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.71327781677246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.74389982223511</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.94678211212158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.9352970123291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.07693004608154</t>
   </si>
   <si>
     <t xml:space="preserve">7.96974849700928</t>
   </si>
   <si>
-    <t xml:space="preserve">8.06161975860596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.13052082061768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.0960693359375</t>
+    <t xml:space="preserve">8.06161880493164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.13052177429199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.09607028961182</t>
   </si>
   <si>
     <t xml:space="preserve">7.96209192276001</t>
   </si>
   <si>
-    <t xml:space="preserve">7.84342527389526</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.67499685287476</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.55786371231079</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.70562076568604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.64360857009888</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.52877140045166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.45221281051636</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.51192712783813</t>
+    <t xml:space="preserve">7.8434271812439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.67499780654907</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.55786323547363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.70562219619751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.64361000061035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.52877044677734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.45221376419067</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.51192855834961</t>
   </si>
   <si>
     <t xml:space="preserve">7.39096641540527</t>
   </si>
   <si>
-    <t xml:space="preserve">7.58542394638062</t>
+    <t xml:space="preserve">7.58542442321777</t>
   </si>
   <si>
     <t xml:space="preserve">7.56092643737793</t>
@@ -3860,97 +3860,97 @@
     <t xml:space="preserve">7.4277138710022</t>
   </si>
   <si>
-    <t xml:space="preserve">7.21794414520264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.12147951126099</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.09851312637329</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.14444589614868</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.17966461181641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.10769891738892</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.05104637145996</t>
+    <t xml:space="preserve">7.21794319152832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.12147998809814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.09851169586182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.14444732666016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.17966508865356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.10769939422607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.05104494094849</t>
   </si>
   <si>
     <t xml:space="preserve">6.99592256546021</t>
   </si>
   <si>
-    <t xml:space="preserve">6.89180326461792</t>
+    <t xml:space="preserve">6.89180374145508</t>
   </si>
   <si>
     <t xml:space="preserve">6.71265602111816</t>
   </si>
   <si>
-    <t xml:space="preserve">6.87189912796021</t>
+    <t xml:space="preserve">6.87189769744873</t>
   </si>
   <si>
     <t xml:space="preserve">7.03114032745361</t>
   </si>
   <si>
-    <t xml:space="preserve">7.25162839889526</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.40321397781372</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.29909563064575</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.36799764633179</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.32359457015991</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.29756450653076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.27612733840942</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.41852617263794</t>
+    <t xml:space="preserve">7.25162887573242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.4032154083252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.29909515380859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.36799812316895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.32359409332275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.29756355285645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.27612781524658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.4185266494751</t>
   </si>
   <si>
     <t xml:space="preserve">7.29297065734863</t>
   </si>
   <si>
-    <t xml:space="preserve">7.41393423080444</t>
+    <t xml:space="preserve">7.41393280029297</t>
   </si>
   <si>
     <t xml:space="preserve">7.46599388122559</t>
   </si>
   <si>
-    <t xml:space="preserve">7.60379791259766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.77069520950317</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.67117023468018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.66734218597412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.59461164474487</t>
+    <t xml:space="preserve">7.60379886627197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.77069568634033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.67117118835449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.6673412322998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.59461116790771</t>
   </si>
   <si>
     <t xml:space="preserve">7.74007272720337</t>
   </si>
   <si>
-    <t xml:space="preserve">7.72476148605347</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.61757898330688</t>
+    <t xml:space="preserve">7.72476100921631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.61757946014404</t>
   </si>
   <si>
     <t xml:space="preserve">7.00664234161377</t>
@@ -3962,52 +3962,52 @@
     <t xml:space="preserve">6.98061180114746</t>
   </si>
   <si>
-    <t xml:space="preserve">7.21028709411621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.85199308395386</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.88721084594727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.04994964599609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.99062633514404</t>
+    <t xml:space="preserve">7.21028757095337</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.85199213027954</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.88721036911011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.04995012283325</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.9906268119812</t>
   </si>
   <si>
     <t xml:space="preserve">7.0226936340332</t>
   </si>
   <si>
-    <t xml:space="preserve">6.96817970275879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.1718053817749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.13653182983398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.27923011779785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.2247166633606</t>
+    <t xml:space="preserve">6.96818017959595</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.17180585861206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.13653135299683</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.27922964096069</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.22471523284912</t>
   </si>
   <si>
     <t xml:space="preserve">7.14454746246338</t>
   </si>
   <si>
-    <t xml:space="preserve">7.14775514602661</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.14134168624878</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.85434103012085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.89763164520264</t>
+    <t xml:space="preserve">7.14775609970093</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.14134216308594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.85434198379517</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.89763212203979</t>
   </si>
   <si>
     <t xml:space="preserve">7.0756049156189</t>
@@ -4019,67 +4019,67 @@
     <t xml:space="preserve">6.83349800109863</t>
   </si>
   <si>
-    <t xml:space="preserve">6.8639612197876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.71965980529785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.37814474105835</t>
+    <t xml:space="preserve">6.86396217346191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.71965885162354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.37814521789551</t>
   </si>
   <si>
     <t xml:space="preserve">6.54008340835571</t>
   </si>
   <si>
-    <t xml:space="preserve">6.66354179382324</t>
+    <t xml:space="preserve">6.66354274749756</t>
   </si>
   <si>
     <t xml:space="preserve">6.88480472564697</t>
   </si>
   <si>
-    <t xml:space="preserve">6.73248529434204</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.40379858016968</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.48877620697021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.51603317260742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.50160264968872</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.51282644271851</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.45831203460693</t>
+    <t xml:space="preserve">6.73248624801636</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.40379810333252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.48877668380737</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.51603364944458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.50160312652588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.51282691955566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.45831251144409</t>
   </si>
   <si>
     <t xml:space="preserve">6.54970407485962</t>
   </si>
   <si>
-    <t xml:space="preserve">6.61383771896362</t>
+    <t xml:space="preserve">6.61383867263794</t>
   </si>
   <si>
     <t xml:space="preserve">6.53366994857788</t>
   </si>
   <si>
-    <t xml:space="preserve">6.64430141448975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.72126293182373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.79661989212036</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.73408985137939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.6972131729126</t>
+    <t xml:space="preserve">6.6443018913269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.72126245498657</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.79662036895752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.73408889770508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.69721221923828</t>
   </si>
   <si>
     <t xml:space="preserve">6.73729610443115</t>
@@ -4091,58 +4091,58 @@
     <t xml:space="preserve">6.84311771392822</t>
   </si>
   <si>
-    <t xml:space="preserve">6.78539609909058</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.6956090927124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.57375431060791</t>
+    <t xml:space="preserve">6.78539705276489</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.69560956954956</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.57375335693359</t>
   </si>
   <si>
     <t xml:space="preserve">6.40700531005859</t>
   </si>
   <si>
-    <t xml:space="preserve">6.50480985641479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.47274351119995</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.45190000534058</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.30599451065063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.22582626342773</t>
+    <t xml:space="preserve">6.50481081008911</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.47274303436279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.45189905166626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.30599403381348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.22582578659058</t>
   </si>
   <si>
     <t xml:space="preserve">6.37012815475464</t>
   </si>
   <si>
-    <t xml:space="preserve">6.32202768325806</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.49358654022217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.32523345947266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.397385597229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.41502237319946</t>
+    <t xml:space="preserve">6.3220272064209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.49358701705933</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.32523393630981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.39738512039185</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.4150218963623</t>
   </si>
   <si>
     <t xml:space="preserve">6.48236322402954</t>
   </si>
   <si>
-    <t xml:space="preserve">6.58177089691162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.66995525360107</t>
+    <t xml:space="preserve">6.58177137374878</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.66995477676392</t>
   </si>
   <si>
     <t xml:space="preserve">6.6827826499939</t>
@@ -4151,34 +4151,34 @@
     <t xml:space="preserve">6.73569297790527</t>
   </si>
   <si>
-    <t xml:space="preserve">6.63147497177124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.66033458709717</t>
+    <t xml:space="preserve">6.63147592544556</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.66033506393433</t>
   </si>
   <si>
     <t xml:space="preserve">6.52084350585938</t>
   </si>
   <si>
-    <t xml:space="preserve">6.51763677597046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.33004379272461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.39417839050293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.26109981536865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.26911687850952</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.13924503326416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.24506616592407</t>
+    <t xml:space="preserve">6.51763725280762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.33004474639893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.39417791366577</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.26110029220581</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.26911640167236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.139244556427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.24506664276123</t>
   </si>
   <si>
     <t xml:space="preserve">6.3733344078064</t>
@@ -4193,241 +4193,241 @@
     <t xml:space="preserve">6.35730123519897</t>
   </si>
   <si>
-    <t xml:space="preserve">6.27072048187256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.28515005111694</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.1408486366272</t>
+    <t xml:space="preserve">6.2707200050354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.2851505279541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.14084815979004</t>
   </si>
   <si>
     <t xml:space="preserve">6.24185991287231</t>
   </si>
   <si>
-    <t xml:space="preserve">6.33645725250244</t>
+    <t xml:space="preserve">6.3364577293396</t>
   </si>
   <si>
     <t xml:space="preserve">6.49519014358521</t>
   </si>
   <si>
-    <t xml:space="preserve">6.73088312149048</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.69400548934937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.67155838012695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.60742473602295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.75974321365356</t>
+    <t xml:space="preserve">6.73088359832764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.69400596618652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.67155790328979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.60742425918579</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.75974369049072</t>
   </si>
   <si>
     <t xml:space="preserve">6.82227420806885</t>
   </si>
   <si>
-    <t xml:space="preserve">6.88640880584717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.08843183517456</t>
+    <t xml:space="preserve">6.88640785217285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.08843088150024</t>
   </si>
   <si>
     <t xml:space="preserve">7.03391695022583</t>
   </si>
   <si>
-    <t xml:space="preserve">7.07079315185547</t>
+    <t xml:space="preserve">7.07079410552979</t>
   </si>
   <si>
     <t xml:space="preserve">7.09163761138916</t>
   </si>
   <si>
-    <t xml:space="preserve">7.05475997924805</t>
+    <t xml:space="preserve">7.05476188659668</t>
   </si>
   <si>
     <t xml:space="preserve">7.01146984100342</t>
   </si>
   <si>
-    <t xml:space="preserve">7.23593902587891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.35939884185791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.40429210662842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.49568271636963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.81956148147583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.72656536102295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.77947664260864</t>
+    <t xml:space="preserve">7.23593950271606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.35939741134644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.40429162979126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.49568367004395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.81956100463867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.72656583786011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.77947759628296</t>
   </si>
   <si>
     <t xml:space="preserve">7.80833673477173</t>
   </si>
   <si>
-    <t xml:space="preserve">7.71534204483032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.66243314743042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.69930982589722</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.66488599777222</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.62882328033447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.70750522613525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.60751485824585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.74192905426025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.65341186523438</t>
+    <t xml:space="preserve">7.71534252166748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.66243171691895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.69930791854858</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.66488552093506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.62882232666016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.70750665664673</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.60751342773438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.7419285774231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.65341234207153</t>
   </si>
   <si>
     <t xml:space="preserve">7.72225856781006</t>
   </si>
   <si>
-    <t xml:space="preserve">7.69275236129761</t>
+    <t xml:space="preserve">7.69275188446045</t>
   </si>
   <si>
     <t xml:space="preserve">7.74520635604858</t>
   </si>
   <si>
-    <t xml:space="preserve">7.72553539276123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.65996789932251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.7534031867981</t>
+    <t xml:space="preserve">7.72553634643555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.65996932983398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.75340223312378</t>
   </si>
   <si>
     <t xml:space="preserve">7.61407089233398</t>
   </si>
   <si>
-    <t xml:space="preserve">7.68455696105957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.68619632720947</t>
+    <t xml:space="preserve">7.68455743789673</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.68619680404663</t>
   </si>
   <si>
     <t xml:space="preserve">7.77962970733643</t>
   </si>
   <si>
-    <t xml:space="preserve">7.78126859664917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.37474870681763</t>
+    <t xml:space="preserve">7.78126907348633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.37474822998047</t>
   </si>
   <si>
     <t xml:space="preserve">7.41572856903076</t>
   </si>
   <si>
-    <t xml:space="preserve">7.4222846031189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.55014133453369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.61243152618408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.54850387573242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.55669832229614</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.56653451919556</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.49768829345703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.58128643035889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.47965669631958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.71406126022339</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.90584850311279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.79602146148682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.87306308746338</t>
+    <t xml:space="preserve">7.42228364944458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.55014228820801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.61243200302124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.54850292205811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.55669927597046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.56653547286987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.49768733978271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.5812873840332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.47965717315674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.71406221389771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.90584802627563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.79602193832397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.87306451797485</t>
   </si>
   <si>
     <t xml:space="preserve">7.85831069946289</t>
   </si>
   <si>
-    <t xml:space="preserve">7.95010614395142</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.88125991821289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.95338487625122</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.97469472885132</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.01895332336426</t>
+    <t xml:space="preserve">7.95010757446289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.88126039505005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.95338535308838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.97469425201416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.01895236968994</t>
   </si>
   <si>
     <t xml:space="preserve">7.96813821792603</t>
   </si>
   <si>
-    <t xml:space="preserve">8.00419902801514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.82880640029907</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.8533935546875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.89109516143799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.89929103851318</t>
+    <t xml:space="preserve">8.00419998168945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.82880544662476</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.85339307785034</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.89109563827515</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.89929151535034</t>
   </si>
   <si>
     <t xml:space="preserve">8.01239490509033</t>
   </si>
   <si>
-    <t xml:space="preserve">7.98616933822632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.02059268951416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.04518032073975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.35170841217041</t>
+    <t xml:space="preserve">7.98616981506348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.02059173583984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.04517936706543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.35170936584473</t>
   </si>
   <si>
     <t xml:space="preserve">8.26155376434326</t>
@@ -4439,46 +4439,46 @@
     <t xml:space="preserve">8.27794551849365</t>
   </si>
   <si>
-    <t xml:space="preserve">8.40908145904541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.23696708679199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.35580635070801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.31072998046875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.38449382781982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.38039684295654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.12058258056641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.17795562744141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.07796287536621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.19270801544189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.35990524291992</t>
+    <t xml:space="preserve">8.40908241271973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.23696613311768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.35580730438232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.31072902679443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.38449287414551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.38039588928223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.12058353424072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.17795467376709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.07796382904053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.19270896911621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.35990619659424</t>
   </si>
   <si>
     <t xml:space="preserve">8.23286819458008</t>
   </si>
   <si>
-    <t xml:space="preserve">8.2287712097168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.30253410339355</t>
+    <t xml:space="preserve">8.22877025604248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.30253314971924</t>
   </si>
   <si>
     <t xml:space="preserve">8.4541597366333</t>
@@ -4487,70 +4487,70 @@
     <t xml:space="preserve">8.40088558197021</t>
   </si>
   <si>
-    <t xml:space="preserve">8.37629795074463</t>
+    <t xml:space="preserve">8.37629699707031</t>
   </si>
   <si>
     <t xml:space="preserve">8.31892490386963</t>
   </si>
   <si>
-    <t xml:space="preserve">8.1861515045166</t>
+    <t xml:space="preserve">8.18615055084229</t>
   </si>
   <si>
     <t xml:space="preserve">7.8550329208374</t>
   </si>
   <si>
-    <t xml:space="preserve">7.97961282730103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.59440040588379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.38622283935547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.46326446533203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.71734142303467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.66652631759644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.68127870559692</t>
+    <t xml:space="preserve">7.97961235046387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.59440135955811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.38622140884399</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.46326494216919</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.71734094619751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.66652488708496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.68127775192261</t>
   </si>
   <si>
     <t xml:space="preserve">7.53702878952026</t>
   </si>
   <si>
-    <t xml:space="preserve">7.67472124099731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.79766130447388</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.71242237091064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.64357757568359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.48621368408203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.57473087310791</t>
+    <t xml:space="preserve">7.67472219467163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.79766035079956</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.7124228477478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.64357709884644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.48621320724487</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.57472991943359</t>
   </si>
   <si>
     <t xml:space="preserve">7.66324710845947</t>
   </si>
   <si>
-    <t xml:space="preserve">7.69603061676025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.82224798202515</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.70422601699829</t>
+    <t xml:space="preserve">7.69603157043457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.82224941253662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.70422649383545</t>
   </si>
   <si>
     <t xml:space="preserve">7.75668048858643</t>
@@ -4559,85 +4559,85 @@
     <t xml:space="preserve">7.83864116668701</t>
   </si>
   <si>
-    <t xml:space="preserve">7.76159906387329</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.8517541885376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.77635145187378</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.7189793586731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.80585765838623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.54194688796997</t>
+    <t xml:space="preserve">7.76159858703613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.85175514221191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.77635049819946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.71898031234741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.8058557510376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.5419454574585</t>
   </si>
   <si>
     <t xml:space="preserve">7.60915374755859</t>
   </si>
   <si>
-    <t xml:space="preserve">7.52555465698242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.76651620864868</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.80421829223633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.8861780166626</t>
+    <t xml:space="preserve">7.52555322647095</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.76651525497437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.80421781539917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.88617753982544</t>
   </si>
   <si>
     <t xml:space="preserve">7.78946495056152</t>
   </si>
   <si>
-    <t xml:space="preserve">7.87142562866211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.9419093132019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.89273548126221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.94027090072632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.91404390335083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.1386137008667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.1156644821167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.93207502365112</t>
+    <t xml:space="preserve">7.87142372131348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.94191074371338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.89273452758789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.94027185440063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.91404485702515</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.13861465454102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.11566638946533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.93207597732544</t>
   </si>
   <si>
     <t xml:space="preserve">8.02878761291504</t>
   </si>
   <si>
-    <t xml:space="preserve">8.00747776031494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.94682741165161</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.99928188323975</t>
+    <t xml:space="preserve">8.00747871398926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.94682693481445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.99928283691406</t>
   </si>
   <si>
     <t xml:space="preserve">8.19598579406738</t>
   </si>
   <si>
-    <t xml:space="preserve">8.1189432144165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.1484489440918</t>
+    <t xml:space="preserve">8.11894416809082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.14844989776611</t>
   </si>
   <si>
     <t xml:space="preserve">8.17631530761719</t>
@@ -4646,7 +4646,7 @@
     <t xml:space="preserve">8.11730480194092</t>
   </si>
   <si>
-    <t xml:space="preserve">8.18778991699219</t>
+    <t xml:space="preserve">8.18778896331787</t>
   </si>
   <si>
     <t xml:space="preserve">8.21237850189209</t>
@@ -4655,7 +4655,7 @@
     <t xml:space="preserve">8.27384853363037</t>
   </si>
   <si>
-    <t xml:space="preserve">8.24925994873047</t>
+    <t xml:space="preserve">8.24926090240479</t>
   </si>
   <si>
     <t xml:space="preserve">8.26840972900391</t>
@@ -4667,10 +4667,10 @@
     <t xml:space="preserve">8.15699863433838</t>
   </si>
   <si>
-    <t xml:space="preserve">8.12443256378174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.16042804718018</t>
+    <t xml:space="preserve">8.12443351745605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.16042709350586</t>
   </si>
   <si>
     <t xml:space="preserve">8.13300323486328</t>
@@ -4682,10 +4682,10 @@
     <t xml:space="preserve">8.43295478820801</t>
   </si>
   <si>
-    <t xml:space="preserve">8.4466667175293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.49808979034424</t>
+    <t xml:space="preserve">8.44666767120361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.49808788299561</t>
   </si>
   <si>
     <t xml:space="preserve">8.47409152984619</t>
@@ -4709,7 +4709,7 @@
     <t xml:space="preserve">8.41581439971924</t>
   </si>
   <si>
-    <t xml:space="preserve">8.54436683654785</t>
+    <t xml:space="preserve">8.54436779022217</t>
   </si>
   <si>
     <t xml:space="preserve">8.52894020080566</t>
@@ -4718,7 +4718,7 @@
     <t xml:space="preserve">8.51522827148438</t>
   </si>
   <si>
-    <t xml:space="preserve">8.51865577697754</t>
+    <t xml:space="preserve">8.51865673065186</t>
   </si>
   <si>
     <t xml:space="preserve">8.54265308380127</t>
@@ -4736,10 +4736,10 @@
     <t xml:space="preserve">8.85717487335205</t>
   </si>
   <si>
-    <t xml:space="preserve">8.83146572113037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.9214506149292</t>
+    <t xml:space="preserve">8.83146476745605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.92144966125488</t>
   </si>
   <si>
     <t xml:space="preserve">8.90859508514404</t>
@@ -4754,19 +4754,19 @@
     <t xml:space="preserve">8.61721229553223</t>
   </si>
   <si>
-    <t xml:space="preserve">8.63435077667236</t>
+    <t xml:space="preserve">8.63435173034668</t>
   </si>
   <si>
     <t xml:space="preserve">8.51351451873779</t>
   </si>
   <si>
-    <t xml:space="preserve">8.64720821380615</t>
+    <t xml:space="preserve">8.64720726013184</t>
   </si>
   <si>
     <t xml:space="preserve">8.7157678604126</t>
   </si>
   <si>
-    <t xml:space="preserve">8.6857738494873</t>
+    <t xml:space="preserve">8.68577289581299</t>
   </si>
   <si>
     <t xml:space="preserve">8.70719718933105</t>
@@ -4775,13 +4775,13 @@
     <t xml:space="preserve">8.60435771942139</t>
   </si>
   <si>
-    <t xml:space="preserve">8.57007694244385</t>
+    <t xml:space="preserve">8.57007598876953</t>
   </si>
   <si>
     <t xml:space="preserve">8.58721733093262</t>
   </si>
   <si>
-    <t xml:space="preserve">8.61292743682861</t>
+    <t xml:space="preserve">8.61292839050293</t>
   </si>
   <si>
     <t xml:space="preserve">8.62578201293945</t>
@@ -4790,7 +4790,7 @@
     <t xml:space="preserve">8.65149307250977</t>
   </si>
   <si>
-    <t xml:space="preserve">8.77575874328613</t>
+    <t xml:space="preserve">8.77575778961182</t>
   </si>
   <si>
     <t xml:space="preserve">8.84860420227051</t>
@@ -4802,19 +4802,19 @@
     <t xml:space="preserve">8.76290416717529</t>
   </si>
   <si>
-    <t xml:space="preserve">8.70291328430176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.63006782531738</t>
+    <t xml:space="preserve">8.70291233062744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.63006591796875</t>
   </si>
   <si>
     <t xml:space="preserve">8.82289409637451</t>
   </si>
   <si>
-    <t xml:space="preserve">8.72433853149414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.67291736602783</t>
+    <t xml:space="preserve">8.72433757781982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.67291831970215</t>
   </si>
   <si>
     <t xml:space="preserve">8.66863250732422</t>
@@ -4823,16 +4823,16 @@
     <t xml:space="preserve">8.75861835479736</t>
   </si>
   <si>
-    <t xml:space="preserve">8.64292240142822</t>
+    <t xml:space="preserve">8.64292335510254</t>
   </si>
   <si>
     <t xml:space="preserve">8.58293151855469</t>
   </si>
   <si>
-    <t xml:space="preserve">8.50665855407715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.45523834228516</t>
+    <t xml:space="preserve">8.50665760040283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.45523738861084</t>
   </si>
   <si>
     <t xml:space="preserve">8.29240608215332</t>
@@ -4841,13 +4841,13 @@
     <t xml:space="preserve">8.19984912872314</t>
   </si>
   <si>
-    <t xml:space="preserve">8.18271064758301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.25812530517578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.17756843566895</t>
+    <t xml:space="preserve">8.18270969390869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.2581262588501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.17756652832031</t>
   </si>
   <si>
     <t xml:space="preserve">8.36610889434814</t>
@@ -4862,46 +4862,46 @@
     <t xml:space="preserve">8.4603796005249</t>
   </si>
   <si>
-    <t xml:space="preserve">8.48266315460205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.30097579956055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.87418556213379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.85533285140991</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.85876083374023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.79877090454102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.91018056869507</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.83476448059082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.88275671005249</t>
+    <t xml:space="preserve">8.48266124725342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.30097675323486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.87418651580811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.85533237457275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.85876035690308</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.7987699508667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.91018104553223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.83476495742798</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.88275623321533</t>
   </si>
   <si>
     <t xml:space="preserve">8.00445175170898</t>
   </si>
   <si>
-    <t xml:space="preserve">7.9890251159668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.08501052856445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.16728401184082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.21184730529785</t>
+    <t xml:space="preserve">7.98902559280396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.08500957489014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.1672830581665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.21184635162354</t>
   </si>
   <si>
     <t xml:space="preserve">8.46895027160645</t>
@@ -4916,16 +4916,16 @@
     <t xml:space="preserve">8.74823379516602</t>
   </si>
   <si>
-    <t xml:space="preserve">8.66926383972168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.62539005279541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.63065624237061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.66399669647217</t>
+    <t xml:space="preserve">8.66926288604736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.62539100646973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.63065528869629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.66399765014648</t>
   </si>
   <si>
     <t xml:space="preserve">8.56572246551514</t>
@@ -4934,28 +4934,28 @@
     <t xml:space="preserve">8.62363529205322</t>
   </si>
   <si>
-    <t xml:space="preserve">8.61135101318359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.66575336456299</t>
+    <t xml:space="preserve">8.61135005950928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.66575241088867</t>
   </si>
   <si>
     <t xml:space="preserve">8.70436096191406</t>
   </si>
   <si>
-    <t xml:space="preserve">8.72541999816895</t>
+    <t xml:space="preserve">8.72541904449463</t>
   </si>
   <si>
     <t xml:space="preserve">8.74472332000732</t>
   </si>
   <si>
-    <t xml:space="preserve">8.78771877288818</t>
+    <t xml:space="preserve">8.7877197265625</t>
   </si>
   <si>
     <t xml:space="preserve">8.75174331665039</t>
   </si>
   <si>
-    <t xml:space="preserve">8.80526828765869</t>
+    <t xml:space="preserve">8.80526733398438</t>
   </si>
   <si>
     <t xml:space="preserve">8.84914112091064</t>
@@ -4964,25 +4964,25 @@
     <t xml:space="preserve">8.81404304504395</t>
   </si>
   <si>
-    <t xml:space="preserve">8.87985134124756</t>
+    <t xml:space="preserve">8.87985229492188</t>
   </si>
   <si>
     <t xml:space="preserve">8.97198581695557</t>
   </si>
   <si>
-    <t xml:space="preserve">8.95004749298096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.93249988555908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.01585674285889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.97637176513672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.00708389282227</t>
+    <t xml:space="preserve">8.95004844665527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.93249893188477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.0158576965332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.9763708114624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.00708293914795</t>
   </si>
   <si>
     <t xml:space="preserve">9.03779411315918</t>
@@ -5000,28 +5000,28 @@
     <t xml:space="preserve">9.02901935577393</t>
   </si>
   <si>
-    <t xml:space="preserve">9.01146984100342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.95443630218506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.8579158782959</t>
+    <t xml:space="preserve">9.01147079467773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.95443534851074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.85791683197021</t>
   </si>
   <si>
     <t xml:space="preserve">8.90178871154785</t>
   </si>
   <si>
-    <t xml:space="preserve">8.906174659729</t>
+    <t xml:space="preserve">8.90617561340332</t>
   </si>
   <si>
     <t xml:space="preserve">8.87546443939209</t>
   </si>
   <si>
-    <t xml:space="preserve">8.84036540985107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.91056346893311</t>
+    <t xml:space="preserve">8.84036636352539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.91056251525879</t>
   </si>
   <si>
     <t xml:space="preserve">8.86668968200684</t>
@@ -5030,7 +5030,7 @@
     <t xml:space="preserve">8.96321105957031</t>
   </si>
   <si>
-    <t xml:space="preserve">9.04656982421875</t>
+    <t xml:space="preserve">9.04656887054443</t>
   </si>
   <si>
     <t xml:space="preserve">9.0509557723999</t>
@@ -5039,7 +5039,7 @@
     <t xml:space="preserve">8.8228178024292</t>
   </si>
   <si>
-    <t xml:space="preserve">8.77104759216309</t>
+    <t xml:space="preserve">8.77104663848877</t>
   </si>
   <si>
     <t xml:space="preserve">8.83159160614014</t>
@@ -5054,79 +5054,79 @@
     <t xml:space="preserve">8.71664524078369</t>
   </si>
   <si>
-    <t xml:space="preserve">8.65346813201904</t>
+    <t xml:space="preserve">8.65346908569336</t>
   </si>
   <si>
     <t xml:space="preserve">8.5920467376709</t>
   </si>
   <si>
-    <t xml:space="preserve">8.64995861053467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.73068428039551</t>
+    <t xml:space="preserve">8.64995765686035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.73068523406982</t>
   </si>
   <si>
     <t xml:space="preserve">8.86230278015137</t>
   </si>
   <si>
-    <t xml:space="preserve">8.87107753753662</t>
+    <t xml:space="preserve">8.8710765838623</t>
   </si>
   <si>
     <t xml:space="preserve">8.9281120300293</t>
   </si>
   <si>
-    <t xml:space="preserve">8.99392032623291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.17818737030029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.22644710540771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.51161956787109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.90208721160889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.84066677093506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.99422168731689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.055643081665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0951290130615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1521615982056</t>
+    <t xml:space="preserve">8.99392127990723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.17818641662598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.22644805908203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.51162052154541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.90208911895752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.84066486358643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.99422073364258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0556421279907</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0951280593872</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1521625518799</t>
   </si>
   <si>
     <t xml:space="preserve">10.2004232406616</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2179727554321</t>
+    <t xml:space="preserve">10.2179718017578</t>
   </si>
   <si>
     <t xml:space="preserve">10.2750062942505</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2837810516357</t>
+    <t xml:space="preserve">10.2837820053101</t>
   </si>
   <si>
     <t xml:space="preserve">10.3364286422729</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4680471420288</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.064416885376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.086353302002</t>
+    <t xml:space="preserve">10.4680461883545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0644178390503</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0863542556763</t>
   </si>
   <si>
     <t xml:space="preserve">10.0380926132202</t>
@@ -5138,19 +5138,19 @@
     <t xml:space="preserve">10.1390018463135</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1477756500244</t>
+    <t xml:space="preserve">10.1477746963501</t>
   </si>
   <si>
     <t xml:space="preserve">10.1828737258911</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1170635223389</t>
+    <t xml:space="preserve">10.1170644760132</t>
   </si>
   <si>
     <t xml:space="preserve">10.2355213165283</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1082897186279</t>
+    <t xml:space="preserve">10.1082906723022</t>
   </si>
   <si>
     <t xml:space="preserve">10.2530708312988</t>
@@ -5162,7 +5162,7 @@
     <t xml:space="preserve">10.2135848999023</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1565504074097</t>
+    <t xml:space="preserve">10.1565494537354</t>
   </si>
   <si>
     <t xml:space="preserve">10.2311334609985</t>
@@ -5174,7 +5174,7 @@
     <t xml:space="preserve">10.0775785446167</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2267465591431</t>
+    <t xml:space="preserve">10.2267475128174</t>
   </si>
   <si>
     <t xml:space="preserve">10.2223596572876</t>
@@ -5186,79 +5186,79 @@
     <t xml:space="preserve">10.4636602401733</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3495893478394</t>
+    <t xml:space="preserve">10.3495903015137</t>
   </si>
   <si>
     <t xml:space="preserve">10.3539781570435</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4812078475952</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4592714309692</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4504985809326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6084394454956</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8453531265259</t>
+    <t xml:space="preserve">10.4812088012695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4592723846436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4504976272583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6084403991699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8453521728516</t>
   </si>
   <si>
     <t xml:space="preserve">10.8058662414551</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7619943618774</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7970924377441</t>
+    <t xml:space="preserve">10.7619953155518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7970933914185</t>
   </si>
   <si>
     <t xml:space="preserve">10.7883186340332</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0120697021484</t>
+    <t xml:space="preserve">11.0120687484741</t>
   </si>
   <si>
     <t xml:space="preserve">10.8672895431519</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8804502487183</t>
+    <t xml:space="preserve">10.8804512023926</t>
   </si>
   <si>
     <t xml:space="preserve">10.8497400283813</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9067754745483</t>
+    <t xml:space="preserve">10.906774520874</t>
   </si>
   <si>
     <t xml:space="preserve">10.8234167098999</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8980007171631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0822658538818</t>
+    <t xml:space="preserve">10.8979997634888</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0822668075562</t>
   </si>
   <si>
     <t xml:space="preserve">11.0647163391113</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0471677780151</t>
+    <t xml:space="preserve">11.0471687316895</t>
   </si>
   <si>
     <t xml:space="preserve">10.9945201873779</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0559434890747</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2884683609009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2226591110229</t>
+    <t xml:space="preserve">11.0559425354004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2884664535522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2226581573486</t>
   </si>
   <si>
     <t xml:space="preserve">11.3674392700195</t>
@@ -5267,31 +5267,31 @@
     <t xml:space="preserve">11.2270460128784</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1919479370117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0340061187744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.871675491333</t>
+    <t xml:space="preserve">11.191948890686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0340051651001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8716773986816</t>
   </si>
   <si>
     <t xml:space="preserve">10.6830234527588</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9023885726929</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0734920501709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0252304077148</t>
+    <t xml:space="preserve">10.9023876190186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0734901428223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0252323150635</t>
   </si>
   <si>
     <t xml:space="preserve">11.0555458068848</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1014776229858</t>
+    <t xml:space="preserve">11.1014766693115</t>
   </si>
   <si>
     <t xml:space="preserve">10.9728698730469</t>
@@ -5303,19 +5303,19 @@
     <t xml:space="preserve">10.9269399642944</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2346754074097</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0922908782959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.083104133606</t>
+    <t xml:space="preserve">11.234676361084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0922899246216</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0831031799316</t>
   </si>
   <si>
     <t xml:space="preserve">11.1520004272461</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0142078399658</t>
+    <t xml:space="preserve">11.0142068862915</t>
   </si>
   <si>
     <t xml:space="preserve">11.1106634140015</t>
@@ -5330,13 +5330,13 @@
     <t xml:space="preserve">11.2484550476074</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1703729629517</t>
+    <t xml:space="preserve">11.1703720092773</t>
   </si>
   <si>
     <t xml:space="preserve">11.1198492050171</t>
   </si>
   <si>
-    <t xml:space="preserve">11.225489616394</t>
+    <t xml:space="preserve">11.2254905700684</t>
   </si>
   <si>
     <t xml:space="preserve">11.3219442367554</t>
@@ -5345,28 +5345,28 @@
     <t xml:space="preserve">11.2163038253784</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1795597076416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1382217407227</t>
+    <t xml:space="preserve">11.1795587539673</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1382207870483</t>
   </si>
   <si>
     <t xml:space="preserve">11.6526470184326</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4964828491211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1428136825562</t>
+    <t xml:space="preserve">11.4964818954468</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1428146362305</t>
   </si>
   <si>
     <t xml:space="preserve">10.8718223571777</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5916433334351</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6192035675049</t>
+    <t xml:space="preserve">10.5916442871094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6192026138306</t>
   </si>
   <si>
     <t xml:space="preserve">10.8901948928833</t>
@@ -5375,7 +5375,7 @@
     <t xml:space="preserve">10.816704750061</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9177532196045</t>
+    <t xml:space="preserve">10.9177541732788</t>
   </si>
   <si>
     <t xml:space="preserve">10.9223470687866</t>
@@ -5393,7 +5393,7 @@
     <t xml:space="preserve">11.4046201705933</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2806072235107</t>
+    <t xml:space="preserve">11.2806062698364</t>
   </si>
   <si>
     <t xml:space="preserve">11.3632822036743</t>
@@ -5408,7 +5408,7 @@
     <t xml:space="preserve">11.4735155105591</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4459571838379</t>
+    <t xml:space="preserve">11.4459581375122</t>
   </si>
   <si>
     <t xml:space="preserve">11.5056676864624</t>
@@ -5420,22 +5420,22 @@
     <t xml:space="preserve">11.5286331176758</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4551439285278</t>
+    <t xml:space="preserve">11.4551448822021</t>
   </si>
   <si>
     <t xml:space="preserve">11.3495025634766</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3035717010498</t>
+    <t xml:space="preserve">11.3035736083984</t>
   </si>
   <si>
     <t xml:space="preserve">11.3449106216431</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2897930145264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.45973777771</t>
+    <t xml:space="preserve">11.2897920608521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4597368240356</t>
   </si>
   <si>
     <t xml:space="preserve">11.4367713928223</t>
@@ -5444,19 +5444,19 @@
     <t xml:space="preserve">11.524040222168</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5699710845947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5975284576416</t>
+    <t xml:space="preserve">11.569972038269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5975294113159</t>
   </si>
   <si>
     <t xml:space="preserve">11.6434602737427</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6388673782349</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3816537857056</t>
+    <t xml:space="preserve">11.6388683319092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3816547393799</t>
   </si>
   <si>
     <t xml:space="preserve">11.3678750991821</t>
@@ -5471,7 +5471,7 @@
     <t xml:space="preserve">11.6250867843628</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5653781890869</t>
+    <t xml:space="preserve">11.5653772354126</t>
   </si>
   <si>
     <t xml:space="preserve">11.5424118041992</t>
@@ -5480,19 +5480,19 @@
     <t xml:space="preserve">11.4000263214111</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5010747909546</t>
+    <t xml:space="preserve">11.5010757446289</t>
   </si>
   <si>
     <t xml:space="preserve">11.5607852935791</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6802043914795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6296806335449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6893911361694</t>
+    <t xml:space="preserve">11.6802053451538</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6296815872192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6893920898438</t>
   </si>
   <si>
     <t xml:space="preserve">11.7766590118408</t>
@@ -5507,7 +5507,7 @@
     <t xml:space="preserve">11.9282312393188</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2864923477173</t>
+    <t xml:space="preserve">12.286491394043</t>
   </si>
   <si>
     <t xml:space="preserve">12.3232364654541</t>
@@ -5540,16 +5540,16 @@
     <t xml:space="preserve">11.8868932723999</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9695692062378</t>
+    <t xml:space="preserve">11.9695682525635</t>
   </si>
   <si>
     <t xml:space="preserve">11.9144515991211</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1211404800415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2175951004028</t>
+    <t xml:space="preserve">12.1211395263672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2175960540771</t>
   </si>
   <si>
     <t xml:space="preserve">12.2084093093872</t>
@@ -5561,22 +5561,22 @@
     <t xml:space="preserve">12.0476512908936</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2038164138794</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.309455871582</t>
+    <t xml:space="preserve">12.2038154602051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3094568252563</t>
   </si>
   <si>
     <t xml:space="preserve">12.1681852340698</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2482385635376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3282928466797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3800926208496</t>
+    <t xml:space="preserve">12.2482395172119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.328293800354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3800935745239</t>
   </si>
   <si>
     <t xml:space="preserve">12.4789819717407</t>
@@ -5591,10 +5591,10 @@
     <t xml:space="preserve">12.5119457244873</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6673450469971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7097263336182</t>
+    <t xml:space="preserve">12.6673440933228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7097253799438</t>
   </si>
   <si>
     <t xml:space="preserve">12.8462886810303</t>
@@ -5606,19 +5606,19 @@
     <t xml:space="preserve">12.964015007019</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8651247024536</t>
+    <t xml:space="preserve">12.8651237487793</t>
   </si>
   <si>
     <t xml:space="preserve">12.8604154586792</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9875593185425</t>
+    <t xml:space="preserve">12.9875602722168</t>
   </si>
   <si>
     <t xml:space="preserve">12.9969778060913</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0393590927124</t>
+    <t xml:space="preserve">13.0393600463867</t>
   </si>
   <si>
     <t xml:space="preserve">13.0629043579102</t>
@@ -5627,13 +5627,13 @@
     <t xml:space="preserve">12.9122152328491</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7850704193115</t>
+    <t xml:space="preserve">12.7850713729858</t>
   </si>
   <si>
     <t xml:space="preserve">12.7568168640137</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6908903121948</t>
+    <t xml:space="preserve">12.6908893585205</t>
   </si>
   <si>
     <t xml:space="preserve">12.8509979248047</t>
@@ -5648,10 +5648,10 @@
     <t xml:space="preserve">13.0111045837402</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0487766265869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1476678848267</t>
+    <t xml:space="preserve">13.0487775802612</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1476669311523</t>
   </si>
   <si>
     <t xml:space="preserve">13.2465572357178</t>
@@ -5660,13 +5660,13 @@
     <t xml:space="preserve">13.1241226196289</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0440692901611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1806306838989</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3737010955811</t>
+    <t xml:space="preserve">13.0440683364868</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1806316375732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3737020492554</t>
   </si>
   <si>
     <t xml:space="preserve">13.463173866272</t>
@@ -5690,7 +5690,7 @@
     <t xml:space="preserve">13.4961376190186</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6374092102051</t>
+    <t xml:space="preserve">13.6374082565308</t>
   </si>
   <si>
     <t xml:space="preserve">13.6232814788818</t>
@@ -5702,7 +5702,7 @@
     <t xml:space="preserve">13.802225112915</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8351888656616</t>
+    <t xml:space="preserve">13.8351879119873</t>
   </si>
   <si>
     <t xml:space="preserve">13.6703729629517</t>
@@ -5717,7 +5717,7 @@
     <t xml:space="preserve">13.7551345825195</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7315902709961</t>
+    <t xml:space="preserve">13.7315893173218</t>
   </si>
   <si>
     <t xml:space="preserve">13.8116436004639</t>
@@ -5756,7 +5756,7 @@
     <t xml:space="preserve">14.621600151062</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8052530288696</t>
+    <t xml:space="preserve">14.8052539825439</t>
   </si>
   <si>
     <t xml:space="preserve">14.6922369003296</t>
@@ -5768,31 +5768,31 @@
     <t xml:space="preserve">15.0595417022705</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2102308273315</t>
+    <t xml:space="preserve">15.2102317810059</t>
   </si>
   <si>
     <t xml:space="preserve">15.1066331863403</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0454158782959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1961050033569</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3656311035156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4221382141113</t>
+    <t xml:space="preserve">15.0454149246216</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1961040496826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3656301498413</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4221391677856</t>
   </si>
   <si>
     <t xml:space="preserve">15.3891754150391</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6152086257935</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5634088516235</t>
+    <t xml:space="preserve">15.6152095794678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5634107589722</t>
   </si>
   <si>
     <t xml:space="preserve">15.4786462783813</t>
@@ -5807,22 +5807,22 @@
     <t xml:space="preserve">15.5445737838745</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5021915435791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5869541168213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.685845375061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4739398956299</t>
+    <t xml:space="preserve">15.5021924972534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5869550704956</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6858463287354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4739389419556</t>
   </si>
   <si>
     <t xml:space="preserve">15.6528825759888</t>
   </si>
   <si>
-    <t xml:space="preserve">15.869499206543</t>
+    <t xml:space="preserve">15.8694982528687</t>
   </si>
   <si>
     <t xml:space="preserve">15.5963735580444</t>
@@ -5846,13 +5846,13 @@
     <t xml:space="preserve">14.8382167816162</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3562116622925</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.53515625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.75648021698</t>
+    <t xml:space="preserve">15.3562126159668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5351572036743</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7564811706543</t>
   </si>
   <si>
     <t xml:space="preserve">15.9495525360107</t>
@@ -5873,7 +5873,7 @@
     <t xml:space="preserve">16.5381832122803</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5852737426758</t>
+    <t xml:space="preserve">16.5852756500244</t>
   </si>
   <si>
     <t xml:space="preserve">16.8018894195557</t>
@@ -5897,7 +5897,7 @@
     <t xml:space="preserve">17.3198852539062</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2021579742432</t>
+    <t xml:space="preserve">17.2021598815918</t>
   </si>
   <si>
     <t xml:space="preserve">17.0891437530518</t>
@@ -5930,10 +5930,10 @@
     <t xml:space="preserve">17.9697341918945</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9508991241455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8990993499756</t>
+    <t xml:space="preserve">17.9508972167969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.899097442627</t>
   </si>
   <si>
     <t xml:space="preserve">17.997989654541</t>
@@ -5942,7 +5942,7 @@
     <t xml:space="preserve">18.0121154785156</t>
   </si>
   <si>
-    <t xml:space="preserve">17.7484073638916</t>
+    <t xml:space="preserve">17.7484092712402</t>
   </si>
   <si>
     <t xml:space="preserve">17.8567161560059</t>
@@ -5951,7 +5951,7 @@
     <t xml:space="preserve">17.9744434356689</t>
   </si>
   <si>
-    <t xml:space="preserve">17.941478729248</t>
+    <t xml:space="preserve">17.9414806365967</t>
   </si>
   <si>
     <t xml:space="preserve">17.7625370025635</t>
@@ -5966,7 +5966,7 @@
     <t xml:space="preserve">17.6683559417725</t>
   </si>
   <si>
-    <t xml:space="preserve">17.5741748809814</t>
+    <t xml:space="preserve">17.5741729736328</t>
   </si>
   <si>
     <t xml:space="preserve">17.5930099487305</t>
@@ -6294,6 +6294,9 @@
   </si>
   <si>
     <t xml:space="preserve">20.3199996948242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1900005340576</t>
   </si>
 </sst>
 </file>
@@ -72256,7 +72259,7 @@
     </row>
     <row r="2525">
       <c r="A2525" s="1" t="n">
-        <v>45994.6937037037</v>
+        <v>45994.3333333333</v>
       </c>
       <c r="B2525" t="n">
         <v>1847269</v>
@@ -72277,6 +72280,32 @@
         <v>2093</v>
       </c>
       <c r="H2525" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2526">
+      <c r="A2526" s="1" t="n">
+        <v>45995.6912847222</v>
+      </c>
+      <c r="B2526" t="n">
+        <v>1821563</v>
+      </c>
+      <c r="C2526" t="n">
+        <v>20.3999996185303</v>
+      </c>
+      <c r="D2526" t="n">
+        <v>20.1399993896484</v>
+      </c>
+      <c r="E2526" t="n">
+        <v>20.3999996185303</v>
+      </c>
+      <c r="F2526" t="n">
+        <v>20.1900005340576</v>
+      </c>
+      <c r="G2526" t="s">
+        <v>2094</v>
+      </c>
+      <c r="H2526" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/PST.MI.xlsx
+++ b/data/PST.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2098" uniqueCount="2098">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2099" uniqueCount="2099">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,118 +38,118 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">3.82970356941223</t>
+    <t xml:space="preserve">3.82970428466797</t>
   </si>
   <si>
     <t xml:space="preserve">PST.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">3.95891737937927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.89843368530273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87644147872925</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84070062637329</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80496048927307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.89568519592285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94242215156555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92042875289917</t>
+    <t xml:space="preserve">3.95891809463501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89843487739563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87644100189209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84070038795471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.80496025085449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89568614959717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94242262840271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92042922973633</t>
   </si>
   <si>
     <t xml:space="preserve">3.87094235420227</t>
   </si>
   <si>
-    <t xml:space="preserve">3.75547337532043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.68399333953857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.480548620224</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61526226997375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66199922561646</t>
+    <t xml:space="preserve">3.75547361373901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.68399286270142</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.48054885864258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61526083946228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.6619987487793</t>
   </si>
   <si>
     <t xml:space="preserve">3.58502006530762</t>
   </si>
   <si>
-    <t xml:space="preserve">3.68949222564697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73622870445251</t>
+    <t xml:space="preserve">3.68949198722839</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73622918128967</t>
   </si>
   <si>
     <t xml:space="preserve">3.65924978256226</t>
   </si>
   <si>
-    <t xml:space="preserve">3.75272393226624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.65100264549255</t>
+    <t xml:space="preserve">3.75272440910339</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.65100145339966</t>
   </si>
   <si>
     <t xml:space="preserve">3.57402324676514</t>
   </si>
   <si>
-    <t xml:space="preserve">3.46405386924744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.29085040092468</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.94719481468201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.84272360801697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.10940074920654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.97468733787537</t>
+    <t xml:space="preserve">3.46405410766602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.29085063934326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.94719457626343</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.84272336959839</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.10940027236938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.97468686103821</t>
   </si>
   <si>
     <t xml:space="preserve">2.98568415641785</t>
   </si>
   <si>
-    <t xml:space="preserve">3.07640933990479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.06266307830811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.18637919425964</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.17263317108154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.24136424064636</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.3568332195282</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.28260231018066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.24961185455322</t>
+    <t xml:space="preserve">3.07640981674194</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.06266331672668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.1863796710968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.17263340950012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.24136400222778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.35683298110962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.28260254859924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.24961113929749</t>
   </si>
   <si>
     <t xml:space="preserve">3.34308648109436</t>
@@ -158,91 +158,91 @@
     <t xml:space="preserve">3.3898241519928</t>
   </si>
   <si>
-    <t xml:space="preserve">3.44755792617798</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.41731595993042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.38707423210144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.40906834602356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.37057900428772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.39257311820984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.36782932281494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.54378128051758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.56852459907532</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.56577515602112</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.53828287124634</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.51903796195984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.53278422355652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.60151648521423</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.72248291969299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.70598721504211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64275479316711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71148490905762</t>
+    <t xml:space="preserve">3.44755744934082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.417316198349</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.38707399368286</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.4090678691864</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.3705792427063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.39257287979126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.36782908439636</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.54378223419189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.5685248374939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.56577634811401</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.5382833480835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.51903867721558</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.53278493881226</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.60151553153992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.72248196601868</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.70598697662354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64275431632996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71148586273193</t>
   </si>
   <si>
     <t xml:space="preserve">3.65650105476379</t>
   </si>
   <si>
-    <t xml:space="preserve">3.60701417922974</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.5465304851532</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.44480800628662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.49979376792908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.5162889957428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.53553438186646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.55202960968018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.62900876998901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.56302618980408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.5602765083313</t>
+    <t xml:space="preserve">3.60701441764832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.54653120040894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.44480776786804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.49979305267334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.51628923416138</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.53553366661072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.55202913284302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.62900805473328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.56302690505981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.56027722358704</t>
   </si>
   <si>
     <t xml:space="preserve">3.58776998519897</t>
@@ -251,16 +251,16 @@
     <t xml:space="preserve">3.55752778053284</t>
   </si>
   <si>
-    <t xml:space="preserve">3.6042640209198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.60976362228394</t>
+    <t xml:space="preserve">3.60426449775696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.60976338386536</t>
   </si>
   <si>
     <t xml:space="preserve">3.67299628257751</t>
   </si>
   <si>
-    <t xml:space="preserve">3.71973323822021</t>
+    <t xml:space="preserve">3.71973276138306</t>
   </si>
   <si>
     <t xml:space="preserve">3.72798132896423</t>
@@ -269,7 +269,7 @@
     <t xml:space="preserve">3.6674976348877</t>
   </si>
   <si>
-    <t xml:space="preserve">3.61251330375671</t>
+    <t xml:space="preserve">3.61251282691956</t>
   </si>
   <si>
     <t xml:space="preserve">3.69499015808105</t>
@@ -278,58 +278,58 @@
     <t xml:space="preserve">3.72523212432861</t>
   </si>
   <si>
-    <t xml:space="preserve">3.70323777198792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.68674254417419</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71423530578613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61801075935364</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71698427200317</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.67574548721313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.75822329521179</t>
+    <t xml:space="preserve">3.70323824882507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.68674206733704</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71423506736755</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61801099777222</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71698403358459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.67574596405029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.75822305679321</t>
   </si>
   <si>
     <t xml:space="preserve">3.76372122764587</t>
   </si>
   <si>
-    <t xml:space="preserve">3.73347949981689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.78571581840515</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.78296613693237</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.79396343231201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77196955680847</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.78021717071533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84894824028015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85719585418701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.76647043228149</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.70873618125916</t>
+    <t xml:space="preserve">3.73347973823547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.78571605682373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.78296566009521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.79396319389343</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77196836471558</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.78021693229675</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84894800186157</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85719609260559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.76647114753723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.70873594284058</t>
   </si>
   <si>
     <t xml:space="preserve">3.69224095344543</t>
@@ -338,49 +338,49 @@
     <t xml:space="preserve">3.80221080780029</t>
   </si>
   <si>
-    <t xml:space="preserve">3.88895392417908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83979940414429</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83112478256226</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87449622154236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.56800603866577</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.35693311691284</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.44656658172607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.44078373908997</t>
+    <t xml:space="preserve">3.88895344734192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.83979916572571</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.83112525939941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87449669837952</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.56800651550293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.35693287849426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.44656562805176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.44078397750854</t>
   </si>
   <si>
     <t xml:space="preserve">3.53620100021362</t>
   </si>
   <si>
-    <t xml:space="preserve">3.45813274383545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.37139010429382</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.33380174636841</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.30777859687805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.43211007118225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.58824634552002</t>
+    <t xml:space="preserve">3.45813202857971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.37139058113098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.33380150794983</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.30777835845947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.43210983276367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.58824610710144</t>
   </si>
   <si>
     <t xml:space="preserve">3.57957220077515</t>
@@ -389,85 +389,85 @@
     <t xml:space="preserve">3.66342353820801</t>
   </si>
   <si>
-    <t xml:space="preserve">3.59981179237366</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.60270309448242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.58246302604675</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.63739991188049</t>
+    <t xml:space="preserve">3.5998113155365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.602703332901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.58246350288391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.63740038871765</t>
   </si>
   <si>
     <t xml:space="preserve">3.62583494186401</t>
   </si>
   <si>
-    <t xml:space="preserve">3.5853545665741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.5766806602478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.53330850601196</t>
+    <t xml:space="preserve">3.58535408973694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.57668018341064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.53330969810486</t>
   </si>
   <si>
     <t xml:space="preserve">3.51596069335938</t>
   </si>
   <si>
-    <t xml:space="preserve">3.46102380752563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.72992515563965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.70968556404114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73570871353149</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.74149131774902</t>
+    <t xml:space="preserve">3.46102356910706</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.72992563247681</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.7096848487854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73570775985718</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.74149060249329</t>
   </si>
   <si>
     <t xml:space="preserve">3.79353618621826</t>
   </si>
   <si>
-    <t xml:space="preserve">3.80510234832764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.72703456878662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.65185713768005</t>
+    <t xml:space="preserve">3.80510330200195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.72703385353088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.65185737609863</t>
   </si>
   <si>
     <t xml:space="preserve">3.68944573402405</t>
   </si>
   <si>
-    <t xml:space="preserve">3.59692049026489</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61137747764587</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.67209672927856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.63161778450012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.59113812446594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.60848617553711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.55644083023071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.62294244766235</t>
+    <t xml:space="preserve">3.59692001342773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61137723922729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.67209768295288</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.6316180229187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.59113693237305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.60848522186279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.55644035339355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.62294340133667</t>
   </si>
   <si>
     <t xml:space="preserve">3.61426854133606</t>
@@ -476,94 +476,94 @@
     <t xml:space="preserve">3.63450908660889</t>
   </si>
   <si>
-    <t xml:space="preserve">3.64607357978821</t>
+    <t xml:space="preserve">3.64607381820679</t>
   </si>
   <si>
     <t xml:space="preserve">3.70390295982361</t>
   </si>
   <si>
-    <t xml:space="preserve">3.69233703613281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.49572062492371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.54776620864868</t>
+    <t xml:space="preserve">3.69233751296997</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.49572086334229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.547767162323</t>
   </si>
   <si>
     <t xml:space="preserve">3.5448751449585</t>
   </si>
   <si>
-    <t xml:space="preserve">3.51306915283203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.53041791915894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.53909254074097</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.51885199546814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.51017832756042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.50439453125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.48993802070618</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.49282932281494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.43500089645386</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.4783718585968</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.49861240386963</t>
+    <t xml:space="preserve">3.51306939125061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.53041744232178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.53909206390381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.5188524723053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.51017785072327</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.50439500808716</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.48993825912476</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.4928297996521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.43500161170959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.47837281227112</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.49861288070679</t>
   </si>
   <si>
     <t xml:space="preserve">3.449458360672</t>
   </si>
   <si>
-    <t xml:space="preserve">3.5072865486145</t>
+    <t xml:space="preserve">3.50728678703308</t>
   </si>
   <si>
     <t xml:space="preserve">3.57378888130188</t>
   </si>
   <si>
-    <t xml:space="preserve">3.55354928970337</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.44367551803589</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.4234356880188</t>
+    <t xml:space="preserve">3.55354881286621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.44367480278015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.42343592643738</t>
   </si>
   <si>
     <t xml:space="preserve">3.45234942436218</t>
   </si>
   <si>
-    <t xml:space="preserve">3.48415517807007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.4754810333252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.46391439437866</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.45524048805237</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.41187024116516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.37428140640259</t>
+    <t xml:space="preserve">3.48415565490723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.47548079490662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.46391487121582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.45524096488953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.41186928749084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.37428212165833</t>
   </si>
   <si>
     <t xml:space="preserve">3.3019962310791</t>
@@ -572,178 +572,178 @@
     <t xml:space="preserve">3.26729941368103</t>
   </si>
   <si>
-    <t xml:space="preserve">3.26151657104492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.25573325157166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.24705862998962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.20368814468384</t>
+    <t xml:space="preserve">3.26151633262634</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.25573348999023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.24705910682678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.20368790626526</t>
   </si>
   <si>
     <t xml:space="preserve">3.33091020584106</t>
   </si>
   <si>
-    <t xml:space="preserve">3.39162945747375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.39452147483826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.38584685325623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66053175926208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.67498803138733</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66631436347961</t>
+    <t xml:space="preserve">3.39163017272949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.39452171325684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.38584733009338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66053128242493</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.67498898506165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66631507873535</t>
   </si>
   <si>
     <t xml:space="preserve">3.65764021873474</t>
   </si>
   <si>
-    <t xml:space="preserve">3.70679402351379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66920566558838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.70101094245911</t>
+    <t xml:space="preserve">3.70679450035095</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66920518875122</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.70101141929626</t>
   </si>
   <si>
     <t xml:space="preserve">3.71835970878601</t>
   </si>
   <si>
-    <t xml:space="preserve">3.69522881507874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64318346977234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.56511545181274</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.52752685546875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.50150346755981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.52463483810425</t>
+    <t xml:space="preserve">3.69522786140442</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.6431827545166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.56511521339417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.52752637863159</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.50150370597839</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.52463507652283</t>
   </si>
   <si>
     <t xml:space="preserve">3.38295602798462</t>
   </si>
   <si>
-    <t xml:space="preserve">3.36271572113037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.38006472587585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.46969771385193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.46680641174316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.52174353599548</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.6287260055542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.74438285827637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73281669616699</t>
+    <t xml:space="preserve">3.36271619796753</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.3800642490387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.46969795227051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.46680617332458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.52174377441406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.62872624397278</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.74438214302063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73281764984131</t>
   </si>
   <si>
     <t xml:space="preserve">3.7241427898407</t>
   </si>
   <si>
-    <t xml:space="preserve">3.68655347824097</t>
+    <t xml:space="preserve">3.68655395507812</t>
   </si>
   <si>
     <t xml:space="preserve">3.75594806671143</t>
   </si>
   <si>
-    <t xml:space="preserve">3.72125148773193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.60559439659119</t>
+    <t xml:space="preserve">3.72125172615051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.60559487342834</t>
   </si>
   <si>
     <t xml:space="preserve">3.640291929245</t>
   </si>
   <si>
-    <t xml:space="preserve">3.67788028717041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.6981201171875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61716032028198</t>
+    <t xml:space="preserve">3.67788004875183</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.69811964035034</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61716055870056</t>
   </si>
   <si>
     <t xml:space="preserve">3.68077158927917</t>
   </si>
   <si>
-    <t xml:space="preserve">3.75883984565735</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77040529251099</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64896607398987</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.62005138397217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.7385995388031</t>
+    <t xml:space="preserve">3.75883960723877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77040505409241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64896631240845</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.62005186080933</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73860001564026</t>
   </si>
   <si>
     <t xml:space="preserve">3.74727392196655</t>
   </si>
   <si>
-    <t xml:space="preserve">3.71650815010071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.72881412506104</t>
+    <t xml:space="preserve">3.71650838851929</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.72881460189819</t>
   </si>
   <si>
     <t xml:space="preserve">3.7411208152771</t>
   </si>
   <si>
-    <t xml:space="preserve">3.68574166297913</t>
+    <t xml:space="preserve">3.68574213981628</t>
   </si>
   <si>
     <t xml:space="preserve">3.69189524650574</t>
   </si>
   <si>
-    <t xml:space="preserve">3.7042019367218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66728258132935</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.74727344512939</t>
+    <t xml:space="preserve">3.70420217514038</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66728162765503</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.74727439880371</t>
   </si>
   <si>
     <t xml:space="preserve">3.71343159675598</t>
   </si>
   <si>
-    <t xml:space="preserve">3.68881893157959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.69497275352478</t>
+    <t xml:space="preserve">3.68881845474243</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.69497203826904</t>
   </si>
   <si>
     <t xml:space="preserve">3.67343592643738</t>
@@ -752,40 +752,40 @@
     <t xml:space="preserve">3.65805292129517</t>
   </si>
   <si>
-    <t xml:space="preserve">3.72266173362732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73189091682434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.7688102722168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.7503502368927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73496842384338</t>
+    <t xml:space="preserve">3.7226619720459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73189187049866</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.76880955696106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.75035071372986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73496770858765</t>
   </si>
   <si>
     <t xml:space="preserve">3.72573781013489</t>
   </si>
   <si>
-    <t xml:space="preserve">3.67958927154541</t>
+    <t xml:space="preserve">3.67958855628967</t>
   </si>
   <si>
     <t xml:space="preserve">3.67035961151123</t>
   </si>
   <si>
-    <t xml:space="preserve">3.70727825164795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83957147598267</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85187745094299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87033724784851</t>
+    <t xml:space="preserve">3.70727896690369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.83957076072693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85187840461731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87033748626709</t>
   </si>
   <si>
     <t xml:space="preserve">3.81803512573242</t>
@@ -794,130 +794,130 @@
     <t xml:space="preserve">3.82726502418518</t>
   </si>
   <si>
-    <t xml:space="preserve">3.83034157752991</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.86726069450378</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.75958013534546</t>
+    <t xml:space="preserve">3.83034086227417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.86726093292236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.75958061218262</t>
   </si>
   <si>
     <t xml:space="preserve">3.77188682556152</t>
   </si>
   <si>
-    <t xml:space="preserve">3.82418894767761</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83341836929321</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.78419327735901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.76573395729065</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.75650429725647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.7811164855957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.74419713020325</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.78726935386658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84572386741638</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.82111215591431</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.81188225746155</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8149585723877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.79034543037415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80572915077209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77803993225098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.79957675933838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85495376586914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.79342341423035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.86110687255859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8734142780304</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85803127288818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.86418414115906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84880089759827</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77496314048767</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.76265740394592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.75342774391174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9164867401123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94417500495911</t>
+    <t xml:space="preserve">3.82418823242188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.83341813087463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.78419256210327</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.76573324203491</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.75650358200073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.78111624717712</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.74419808387756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.78726983070374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84572434425354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.82111144065857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.81188249588013</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.81495809555054</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.79034566879272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.80572867393494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77803945541382</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.79957604408264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85495448112488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.79342293739319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.86110758781433</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87341403961182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8580310344696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.86418485641479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.848801612854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77496409416199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.76265692710876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.75342726707458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.91648626327515</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94417572021484</t>
   </si>
   <si>
     <t xml:space="preserve">3.91956186294556</t>
   </si>
   <si>
-    <t xml:space="preserve">3.90725588798523</t>
+    <t xml:space="preserve">3.90725660324097</t>
   </si>
   <si>
     <t xml:space="preserve">3.8949499130249</t>
   </si>
   <si>
-    <t xml:space="preserve">3.9103319644928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92263865470886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94109916687012</t>
+    <t xml:space="preserve">3.91033315658569</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9226393699646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94109869003296</t>
   </si>
   <si>
     <t xml:space="preserve">3.95648145675659</t>
   </si>
   <si>
-    <t xml:space="preserve">3.96878695487976</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98109436035156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96263456344604</t>
+    <t xml:space="preserve">3.96878790855408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.98109340667725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9626350402832</t>
   </si>
   <si>
     <t xml:space="preserve">3.99340033531189</t>
@@ -929,40 +929,40 @@
     <t xml:space="preserve">4.02109003067017</t>
   </si>
   <si>
-    <t xml:space="preserve">4.04877853393555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.13800048828125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.13492345809937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.11953973770142</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.09185171127319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.10723447799683</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.11646366119385</t>
+    <t xml:space="preserve">4.04877948760986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.13800001144409</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.13492202758789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.11954021453857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.09185075759888</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.10723400115967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.11646318435669</t>
   </si>
   <si>
     <t xml:space="preserve">4.0930814743042</t>
   </si>
   <si>
-    <t xml:space="preserve">4.075852394104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.10046529769897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.05123949050903</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.05985403060913</t>
+    <t xml:space="preserve">4.07585287094116</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.10046625137329</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.05124044418335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.05985450744629</t>
   </si>
   <si>
     <t xml:space="preserve">3.93802213668823</t>
@@ -971,55 +971,55 @@
     <t xml:space="preserve">4.04262542724609</t>
   </si>
   <si>
-    <t xml:space="preserve">3.96632623672485</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96017265319824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.97740173339844</t>
+    <t xml:space="preserve">3.96632695198059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96017289161682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9774022102356</t>
   </si>
   <si>
     <t xml:space="preserve">4.01678228378296</t>
   </si>
   <si>
-    <t xml:space="preserve">4.05000925064087</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.095543384552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.10169553756714</t>
+    <t xml:space="preserve">4.05001020431519</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.09554290771484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.1016960144043</t>
   </si>
   <si>
     <t xml:space="preserve">4.17184209823608</t>
   </si>
   <si>
-    <t xml:space="preserve">4.15953636169434</t>
+    <t xml:space="preserve">4.15953588485718</t>
   </si>
   <si>
     <t xml:space="preserve">4.12630891799927</t>
   </si>
   <si>
-    <t xml:space="preserve">4.13000059127808</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.09431219100952</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.33182382583618</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.34536123275757</t>
+    <t xml:space="preserve">4.13000011444092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.09431171417236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.33182430267334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.34536075592041</t>
   </si>
   <si>
     <t xml:space="preserve">4.31828784942627</t>
   </si>
   <si>
-    <t xml:space="preserve">4.22475957870483</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.25183343887329</t>
+    <t xml:space="preserve">4.22476005554199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.25183248519897</t>
   </si>
   <si>
     <t xml:space="preserve">4.28752136230469</t>
@@ -1028,85 +1028,85 @@
     <t xml:space="preserve">4.4007396697998</t>
   </si>
   <si>
-    <t xml:space="preserve">4.51272773742676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.48934555053711</t>
+    <t xml:space="preserve">4.51272678375244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.48934507369995</t>
   </si>
   <si>
     <t xml:space="preserve">4.56564378738403</t>
   </si>
   <si>
-    <t xml:space="preserve">4.46719360351562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.40935373306274</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.47950077056885</t>
+    <t xml:space="preserve">4.46719408035278</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.40935277938843</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.47949934005737</t>
   </si>
   <si>
     <t xml:space="preserve">4.54964590072632</t>
   </si>
   <si>
-    <t xml:space="preserve">4.51518869400024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.54595422744751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.53733968734741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.4954981803894</t>
+    <t xml:space="preserve">4.51518821716309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.54595375061035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.53734016418457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.49549865722656</t>
   </si>
   <si>
     <t xml:space="preserve">4.45857954025269</t>
   </si>
   <si>
-    <t xml:space="preserve">4.44258069992065</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.45734930038452</t>
+    <t xml:space="preserve">4.44258117675781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.45734882354736</t>
   </si>
   <si>
     <t xml:space="preserve">4.52626371383667</t>
   </si>
   <si>
-    <t xml:space="preserve">4.53487920761108</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.56933546066284</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.6456356048584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.64071321487427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.67640161514282</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.72808790206909</t>
+    <t xml:space="preserve">4.53487873077393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.56933641433716</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.64563608169556</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.64071273803711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.67640113830566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.72808837890625</t>
   </si>
   <si>
     <t xml:space="preserve">4.72070407867432</t>
   </si>
   <si>
-    <t xml:space="preserve">4.72439575195312</t>
+    <t xml:space="preserve">4.72439527511597</t>
   </si>
   <si>
     <t xml:space="preserve">4.72193431854248</t>
   </si>
   <si>
-    <t xml:space="preserve">4.75023889541626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.79331064224243</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.76377630233765</t>
+    <t xml:space="preserve">4.75023937225342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.79331111907959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.76377534866333</t>
   </si>
   <si>
     <t xml:space="preserve">4.77362108230591</t>
@@ -1115,40 +1115,40 @@
     <t xml:space="preserve">4.84253644943237</t>
   </si>
   <si>
-    <t xml:space="preserve">4.8474588394165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.86837959289551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.87822437286377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.90529918670654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.98775100708008</t>
+    <t xml:space="preserve">4.84745788574219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.86837911605835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.87822484970093</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.9052996635437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.98775148391724</t>
   </si>
   <si>
     <t xml:space="preserve">4.97421360015869</t>
   </si>
   <si>
-    <t xml:space="preserve">4.96559906005859</t>
+    <t xml:space="preserve">4.96560001373291</t>
   </si>
   <si>
     <t xml:space="preserve">5.01728582382202</t>
   </si>
   <si>
-    <t xml:space="preserve">4.99390363693237</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.97052192687988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.01482534408569</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.0566668510437</t>
+    <t xml:space="preserve">4.99390459060669</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.97052145004272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.01482439041138</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.05666732788086</t>
   </si>
   <si>
     <t xml:space="preserve">4.86714887619019</t>
@@ -1157,61 +1157,61 @@
     <t xml:space="preserve">4.8560733795166</t>
   </si>
   <si>
-    <t xml:space="preserve">4.68870735168457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.69855308532715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.73670244216919</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.71332025527954</t>
+    <t xml:space="preserve">4.68870687484741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.69855260848999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.73670291900635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.71331930160522</t>
   </si>
   <si>
     <t xml:space="preserve">4.74162483215332</t>
   </si>
   <si>
-    <t xml:space="preserve">4.66901731491089</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.51887989044189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.31582498550415</t>
+    <t xml:space="preserve">4.66901683807373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.51888036727905</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.31582546234131</t>
   </si>
   <si>
     <t xml:space="preserve">4.49672889709473</t>
   </si>
   <si>
-    <t xml:space="preserve">4.50657320022583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.5964093208313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.62225341796875</t>
+    <t xml:space="preserve">4.5065746307373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.59640979766846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.62225389480591</t>
   </si>
   <si>
     <t xml:space="preserve">4.50042057037354</t>
   </si>
   <si>
-    <t xml:space="preserve">4.49796009063721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.48073101043701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.35889720916748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.52749443054199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.61363935470581</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.70101356506348</t>
+    <t xml:space="preserve">4.49795961380005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.48073053359985</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.35889768600464</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.52749538421631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.61363887786865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.70101261138916</t>
   </si>
   <si>
     <t xml:space="preserve">4.81177043914795</t>
@@ -1223,13 +1223,13 @@
     <t xml:space="preserve">4.7677903175354</t>
   </si>
   <si>
-    <t xml:space="preserve">4.81597661972046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.83811616897583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.77820920944214</t>
+    <t xml:space="preserve">4.81597518920898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.83811521530151</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.77820873260498</t>
   </si>
   <si>
     <t xml:space="preserve">4.78341865539551</t>
@@ -1238,19 +1238,19 @@
     <t xml:space="preserve">4.72090673446655</t>
   </si>
   <si>
-    <t xml:space="preserve">4.74304723739624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.6753249168396</t>
+    <t xml:space="preserve">4.74304628372192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.67532539367676</t>
   </si>
   <si>
     <t xml:space="preserve">4.66881465911865</t>
   </si>
   <si>
-    <t xml:space="preserve">4.71569728851318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.72741842269897</t>
+    <t xml:space="preserve">4.7156982421875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.72741889953613</t>
   </si>
   <si>
     <t xml:space="preserve">4.83941841125488</t>
@@ -1259,64 +1259,64 @@
     <t xml:space="preserve">4.87718486785889</t>
   </si>
   <si>
-    <t xml:space="preserve">4.92276573181152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.87067365646362</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.94230031967163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.93058013916016</t>
+    <t xml:space="preserve">4.92276668548584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.87067317962646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.94230127334595</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.93057918548584</t>
   </si>
   <si>
     <t xml:space="preserve">5.00220775604248</t>
   </si>
   <si>
-    <t xml:space="preserve">5.05430030822754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.08164978027344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.0230450630188</t>
+    <t xml:space="preserve">5.05429983139038</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.08164882659912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.02304601669312</t>
   </si>
   <si>
     <t xml:space="preserve">5.0360689163208</t>
   </si>
   <si>
-    <t xml:space="preserve">5.02044010162354</t>
+    <t xml:space="preserve">5.02044057846069</t>
   </si>
   <si>
     <t xml:space="preserve">5.02955627441406</t>
   </si>
   <si>
-    <t xml:space="preserve">5.11160182952881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.13374185562134</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.15588188171387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.18713712692261</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.17932319641113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.89932441711426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.8498363494873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.83420848846436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.77560472488403</t>
+    <t xml:space="preserve">5.11160278320312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.13374137878418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.15588140487671</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.18713760375977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.17932367324829</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.89932489395142</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.84983682632446</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.83420896530151</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.77560377120972</t>
   </si>
   <si>
     <t xml:space="preserve">4.69486045837402</t>
@@ -1334,22 +1334,22 @@
     <t xml:space="preserve">4.51644277572632</t>
   </si>
   <si>
-    <t xml:space="preserve">4.46044254302979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.39011812210083</t>
+    <t xml:space="preserve">4.46044301986694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.39011764526367</t>
   </si>
   <si>
     <t xml:space="preserve">4.52946615219116</t>
   </si>
   <si>
-    <t xml:space="preserve">4.44090795516968</t>
+    <t xml:space="preserve">4.44090843200684</t>
   </si>
   <si>
     <t xml:space="preserve">4.42397832870483</t>
   </si>
   <si>
-    <t xml:space="preserve">4.41616344451904</t>
+    <t xml:space="preserve">4.4161639213562</t>
   </si>
   <si>
     <t xml:space="preserve">4.39923429489136</t>
@@ -1358,10 +1358,10 @@
     <t xml:space="preserve">4.41876888275146</t>
   </si>
   <si>
-    <t xml:space="preserve">4.36146640777588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.31849050521851</t>
+    <t xml:space="preserve">4.3614673614502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.31848955154419</t>
   </si>
   <si>
     <t xml:space="preserve">4.39141941070557</t>
@@ -1370,40 +1370,40 @@
     <t xml:space="preserve">4.50732612609863</t>
   </si>
   <si>
-    <t xml:space="preserve">4.59458160400391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.56593036651611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.58416318893433</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.68965148925781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.66490793228149</t>
+    <t xml:space="preserve">4.59458208084106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.56593132019043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.58416366577148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.68965101242065</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.66490745544434</t>
   </si>
   <si>
     <t xml:space="preserve">4.59197759628296</t>
   </si>
   <si>
-    <t xml:space="preserve">4.47476816177368</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.50081539154053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.54379224777222</t>
+    <t xml:space="preserve">4.474769115448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.50081396102905</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.54379177093506</t>
   </si>
   <si>
     <t xml:space="preserve">4.52165174484253</t>
   </si>
   <si>
-    <t xml:space="preserve">4.50993061065674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.57113981246948</t>
+    <t xml:space="preserve">4.5099310874939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.57114028930664</t>
   </si>
   <si>
     <t xml:space="preserve">4.6089072227478</t>
@@ -1412,130 +1412,130 @@
     <t xml:space="preserve">4.63104677200317</t>
   </si>
   <si>
-    <t xml:space="preserve">4.68574476242065</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.71309280395508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.68183755874634</t>
+    <t xml:space="preserve">4.68574380874634</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.71309328079224</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.68183708190918</t>
   </si>
   <si>
     <t xml:space="preserve">4.4812798500061</t>
   </si>
   <si>
-    <t xml:space="preserve">4.43309450149536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.3536524772644</t>
+    <t xml:space="preserve">4.4330940246582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.35365343093872</t>
   </si>
   <si>
     <t xml:space="preserve">4.36276912689209</t>
   </si>
   <si>
-    <t xml:space="preserve">4.36667633056641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.29765224456787</t>
+    <t xml:space="preserve">4.36667585372925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.29765367507935</t>
   </si>
   <si>
     <t xml:space="preserve">4.13877010345459</t>
   </si>
   <si>
-    <t xml:space="preserve">4.16090965270996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.2025842666626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.08667755126953</t>
+    <t xml:space="preserve">4.16090869903564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.20258378982544</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.08667802810669</t>
   </si>
   <si>
     <t xml:space="preserve">4.06844472885132</t>
   </si>
   <si>
-    <t xml:space="preserve">4.08407211303711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.15179300308228</t>
+    <t xml:space="preserve">4.08407258987427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.15179347991943</t>
   </si>
   <si>
     <t xml:space="preserve">4.09970045089722</t>
   </si>
   <si>
-    <t xml:space="preserve">3.98509693145752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.08277082443237</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.06063079833984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.06974649429321</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9056556224823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99030613899231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99421191215515</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.12053871154785</t>
+    <t xml:space="preserve">3.98509645462036</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.08277034759521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.06063032150269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.06974697113037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90565490722656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99030590057373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99421310424805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.12053728103638</t>
   </si>
   <si>
     <t xml:space="preserve">4.0293755531311</t>
   </si>
   <si>
-    <t xml:space="preserve">4.13486289978027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.26639747619629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.30025863647461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.24035167694092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.21300268173218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.35235071182251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.44351196289062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.47346544265747</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.48258209228516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.48518657684326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.34193229675293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.23253726959229</t>
+    <t xml:space="preserve">4.13486385345459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.26639699935913</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.30025815963745</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.24035120010376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.2130012512207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.35235118865967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.44351243972778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.47346639633179</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.48258256912231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.48518753051758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.34193181991577</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.23253679275513</t>
   </si>
   <si>
     <t xml:space="preserve">4.24295568466187</t>
   </si>
   <si>
-    <t xml:space="preserve">4.26769924163818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.15049171447754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.28723382949829</t>
+    <t xml:space="preserve">4.26769971847534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.15049076080322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.28723478317261</t>
   </si>
   <si>
     <t xml:space="preserve">4.26509475708008</t>
@@ -1544,22 +1544,22 @@
     <t xml:space="preserve">4.45393180847168</t>
   </si>
   <si>
-    <t xml:space="preserve">4.43049001693726</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.36407232284546</t>
+    <t xml:space="preserve">4.4304895401001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.3640718460083</t>
   </si>
   <si>
     <t xml:space="preserve">4.36537408828735</t>
   </si>
   <si>
-    <t xml:space="preserve">4.47086191177368</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.43569850921631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.49430274963379</t>
+    <t xml:space="preserve">4.47086238861084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.43569803237915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.49430322647095</t>
   </si>
   <si>
     <t xml:space="preserve">4.25728130340576</t>
@@ -1568,22 +1568,22 @@
     <t xml:space="preserve">4.27811813354492</t>
   </si>
   <si>
-    <t xml:space="preserve">4.22862958908081</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.27030515670776</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.44221067428589</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.51253509521484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.49039602279663</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.48388481140137</t>
+    <t xml:space="preserve">4.22863006591797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.27030372619629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.44220972061157</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.51253461837769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.49039506912231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.48388528823853</t>
   </si>
   <si>
     <t xml:space="preserve">4.62844228744507</t>
@@ -1592,70 +1592,70 @@
     <t xml:space="preserve">4.56462860107422</t>
   </si>
   <si>
-    <t xml:space="preserve">4.49821043014526</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.44872140884399</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.5476975440979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.53858137130737</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.55681371688843</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.6128134727478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.58155822753906</t>
+    <t xml:space="preserve">4.49820947647095</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.44872283935547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.54769897460938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.53858184814453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.55681419372559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.61281394958496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.58155918121338</t>
   </si>
   <si>
     <t xml:space="preserve">4.62714004516602</t>
   </si>
   <si>
-    <t xml:space="preserve">4.6883487701416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.70006942749023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.72220945358276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.70137166976929</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.78862762451172</t>
+    <t xml:space="preserve">4.68834829330444</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.70006895065308</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.72220849990845</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.70137214660645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.78862714767456</t>
   </si>
   <si>
     <t xml:space="preserve">4.81858062744141</t>
   </si>
   <si>
-    <t xml:space="preserve">4.93969678878784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.94881343841553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.90192937850952</t>
+    <t xml:space="preserve">4.93969631195068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.94881248474121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.90192985534668</t>
   </si>
   <si>
     <t xml:space="preserve">4.94751071929932</t>
   </si>
   <si>
-    <t xml:space="preserve">4.95923089981079</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.00871896743774</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.98657989501953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.99439382553101</t>
+    <t xml:space="preserve">4.95923185348511</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.0087194442749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.98657941818237</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.99439430236816</t>
   </si>
   <si>
     <t xml:space="preserve">4.89281272888184</t>
@@ -1664,22 +1664,22 @@
     <t xml:space="preserve">4.78472089767456</t>
   </si>
   <si>
-    <t xml:space="preserve">4.89671945571899</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.97746467590332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.00481224060059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.85374307632446</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.86937093734741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.92797565460205</t>
+    <t xml:space="preserve">4.89671897888184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.977463722229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.00481271743774</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.85374402999878</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.86937141418457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.92797470092773</t>
   </si>
   <si>
     <t xml:space="preserve">5.00090551376343</t>
@@ -1688,31 +1688,31 @@
     <t xml:space="preserve">5.05169582366943</t>
   </si>
   <si>
-    <t xml:space="preserve">4.9917893409729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.04388189315796</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.06211566925049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.04648590087891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.03216075897217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.06732416152954</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.08816051483154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.14285898208618</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.14416027069092</t>
+    <t xml:space="preserve">4.99178838729858</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.04388236999512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.06211376190186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.04648637771606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.03216123580933</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.0673246383667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.0881609916687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.14285802841187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.14416074752808</t>
   </si>
   <si>
     <t xml:space="preserve">5.16369533538818</t>
@@ -1724,34 +1724,34 @@
     <t xml:space="preserve">5.13895130157471</t>
   </si>
   <si>
-    <t xml:space="preserve">5.16239261627197</t>
+    <t xml:space="preserve">5.16239309310913</t>
   </si>
   <si>
     <t xml:space="preserve">5.17281150817871</t>
   </si>
   <si>
-    <t xml:space="preserve">5.17541646957397</t>
+    <t xml:space="preserve">5.17541599273682</t>
   </si>
   <si>
     <t xml:space="preserve">5.08685779571533</t>
   </si>
   <si>
-    <t xml:space="preserve">5.14546394348145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.17020702362061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.18322992324829</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.20406770706177</t>
+    <t xml:space="preserve">5.14546298980713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.17020654678345</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.18323040008545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.20406723022461</t>
   </si>
   <si>
     <t xml:space="preserve">5.26136922836304</t>
   </si>
   <si>
-    <t xml:space="preserve">5.30695104598999</t>
+    <t xml:space="preserve">5.30695009231567</t>
   </si>
   <si>
     <t xml:space="preserve">5.4436936378479</t>
@@ -1760,43 +1760,43 @@
     <t xml:space="preserve">5.49578619003296</t>
   </si>
   <si>
-    <t xml:space="preserve">5.62471628189087</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.57392549514771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.59346103668213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.61560010910034</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.61690235137939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.59736728668213</t>
+    <t xml:space="preserve">5.62471580505371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.57392597198486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.59346151351929</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.61559867858887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.61690282821655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.59736680984497</t>
   </si>
   <si>
     <t xml:space="preserve">5.64685583114624</t>
   </si>
   <si>
-    <t xml:space="preserve">5.6325306892395</t>
+    <t xml:space="preserve">5.63253021240234</t>
   </si>
   <si>
     <t xml:space="preserve">5.64945983886719</t>
   </si>
   <si>
-    <t xml:space="preserve">5.6950421333313</t>
+    <t xml:space="preserve">5.69504165649414</t>
   </si>
   <si>
     <t xml:space="preserve">5.69113445281982</t>
   </si>
   <si>
-    <t xml:space="preserve">5.71327352523804</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.81094694137573</t>
+    <t xml:space="preserve">5.7132740020752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.81094789505005</t>
   </si>
   <si>
     <t xml:space="preserve">5.83178520202637</t>
@@ -1805,55 +1805,55 @@
     <t xml:space="preserve">5.82266902923584</t>
   </si>
   <si>
-    <t xml:space="preserve">5.85392427444458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.84350538253784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.90601634979248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.86173915863037</t>
+    <t xml:space="preserve">5.85392475128174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.84350681304932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.9060173034668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.8617377281189</t>
   </si>
   <si>
     <t xml:space="preserve">6.19643402099609</t>
   </si>
   <si>
-    <t xml:space="preserve">6.19903898239136</t>
+    <t xml:space="preserve">6.19903945922852</t>
   </si>
   <si>
     <t xml:space="preserve">6.1612720489502</t>
   </si>
   <si>
-    <t xml:space="preserve">6.03103971481323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.00629568099976</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.02452754974365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.10396957397461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.19252920150757</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.14694547653198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.08703947067261</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.1326208114624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.93857431411743</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.86564540863037</t>
+    <t xml:space="preserve">6.03104066848755</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.00629663467407</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.02452898025513</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.10396862030029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.19252729415894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.14694595336914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.08703899383545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.13262176513672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.93857526779175</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.86564493179321</t>
   </si>
   <si>
     <t xml:space="preserve">5.860435962677</t>
@@ -1862,106 +1862,106 @@
     <t xml:space="preserve">5.79271554946899</t>
   </si>
   <si>
-    <t xml:space="preserve">5.97113275527954</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.93336725234985</t>
+    <t xml:space="preserve">5.97113370895386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.93336534500122</t>
   </si>
   <si>
     <t xml:space="preserve">6.01020288467407</t>
   </si>
   <si>
-    <t xml:space="preserve">5.87606334686279</t>
+    <t xml:space="preserve">5.87606382369995</t>
   </si>
   <si>
     <t xml:space="preserve">5.92815685272217</t>
   </si>
   <si>
-    <t xml:space="preserve">5.96592426300049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.7093677520752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.80834293365479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.79401683807373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.74843692779541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.71848249435425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.66508865356445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.67680883407593</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.8213677406311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.78099489212036</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.81225061416626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.92685461044312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.98285436630249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.01150512695312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.03494644165039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.00369119644165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.04927253723145</t>
+    <t xml:space="preserve">5.96592330932617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.70936679840088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.8083438873291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.79401779174805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.74843740463257</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.71848440170288</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.66508817672729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.67680835723877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.82136535644531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.78099584579468</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.8122501373291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.9268536567688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.98285341262817</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.01150560379028</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.03494691848755</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.00369071960449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.04927206039429</t>
   </si>
   <si>
     <t xml:space="preserve">6.10266733169556</t>
   </si>
   <si>
-    <t xml:space="preserve">6.19513177871704</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.30506610870361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.26136350631714</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.23541831970215</t>
+    <t xml:space="preserve">6.19513130187988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.30506467819214</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.26136445999146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.23541736602783</t>
   </si>
   <si>
     <t xml:space="preserve">6.24088048934937</t>
   </si>
   <si>
-    <t xml:space="preserve">6.32281732559204</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.31189298629761</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.4634747505188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.61642456054688</t>
+    <t xml:space="preserve">6.32281684875488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.31189250946045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.46347570419312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.61642503738403</t>
   </si>
   <si>
     <t xml:space="preserve">6.65739440917969</t>
   </si>
   <si>
-    <t xml:space="preserve">6.63281297683716</t>
+    <t xml:space="preserve">6.63281345367432</t>
   </si>
   <si>
     <t xml:space="preserve">6.62325429916382</t>
@@ -1970,43 +1970,43 @@
     <t xml:space="preserve">6.59184455871582</t>
   </si>
   <si>
-    <t xml:space="preserve">6.65602874755859</t>
+    <t xml:space="preserve">6.65602827072144</t>
   </si>
   <si>
     <t xml:space="preserve">6.59047937393188</t>
   </si>
   <si>
-    <t xml:space="preserve">6.59457588195801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.56589841842651</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.54541444778442</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.53175783157349</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.41841173171997</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.44708871841431</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.40612030029297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.46893787384033</t>
+    <t xml:space="preserve">6.59457635879517</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.5658974647522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.54541301727295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.53175735473633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.41841077804565</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.44708967208862</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.40612125396729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.46893882751465</t>
   </si>
   <si>
     <t xml:space="preserve">6.42250776290894</t>
   </si>
   <si>
-    <t xml:space="preserve">6.54677820205688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.37607765197754</t>
+    <t xml:space="preserve">6.54677963256836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.37607622146606</t>
   </si>
   <si>
     <t xml:space="preserve">6.59594106674194</t>
@@ -2015,181 +2015,181 @@
     <t xml:space="preserve">6.66148996353149</t>
   </si>
   <si>
-    <t xml:space="preserve">6.58365106582642</t>
+    <t xml:space="preserve">6.58365154266357</t>
   </si>
   <si>
     <t xml:space="preserve">6.47849798202515</t>
   </si>
   <si>
-    <t xml:space="preserve">6.47440242767334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.58092021942139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.14118957519531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.21356821060181</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.35695838928223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.24361181259155</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.48669290542603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.44162750244141</t>
+    <t xml:space="preserve">6.47440195083618</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.5809178352356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.14119052886963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.21356773376465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.35695886611938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.24361133575439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.48669099807739</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.44162654876709</t>
   </si>
   <si>
     <t xml:space="preserve">6.62188863754272</t>
   </si>
   <si>
-    <t xml:space="preserve">6.59867286682129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.43206739425659</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.48532581329346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.4170446395874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.71884775161743</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.67241668701172</t>
+    <t xml:space="preserve">6.59867238998413</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.43206787109375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.4853253364563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.41704511642456</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.71884727478027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.6724157333374</t>
   </si>
   <si>
     <t xml:space="preserve">6.74342775344849</t>
   </si>
   <si>
-    <t xml:space="preserve">6.75981521606445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.88954877853394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.86223793029785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.87930631637573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.8827223777771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.76664400100708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.79395627975464</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.91344881057739</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.95441722869873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.86906480789185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.81034326553345</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.93734550476074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.95100212097168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.87247848510742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.01587009429932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.97490072250366</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.97148561477661</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.00562715530396</t>
+    <t xml:space="preserve">6.75981426239014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.88955116271973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.86223745346069</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.87930727005005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.88271999359131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.76664352416992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.7939567565918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.91344690322876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.95441675186157</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.86906576156616</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.81034421920776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.9373459815979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.95100164413452</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.87247943878174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.01586961746216</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.97490167617798</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.97148704528809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.0056266784668</t>
   </si>
   <si>
     <t xml:space="preserve">7.12170505523682</t>
   </si>
   <si>
-    <t xml:space="preserve">7.02269744873047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.80351686477661</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.81853723526001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.81444025039673</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.00904130935669</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.91686201095581</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.99879932403564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.22412538528442</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.23436737060547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.33337593078613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.22754144668579</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.30947732925415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.3504467010498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.37434387207031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.45969724655151</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.47676467895508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.50407743453979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.41531133651733</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.44945335388184</t>
+    <t xml:space="preserve">7.02269649505615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.80351543426514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.81853771209717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.81444072723389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.00904178619385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.91686153411865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.99879884719849</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.2241268157959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.2343692779541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.33337545394897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.2275390625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.30947685241699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.35044574737549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.37434434890747</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.45969533920288</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.47676658630371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.50407838821411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.41531324386597</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.44945383071899</t>
   </si>
   <si>
     <t xml:space="preserve">7.43579769134521</t>
   </si>
   <si>
-    <t xml:space="preserve">7.42896842956543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.53139114379883</t>
+    <t xml:space="preserve">7.42897033691406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.53139066696167</t>
   </si>
   <si>
     <t xml:space="preserve">7.5757737159729</t>
@@ -2198,40 +2198,40 @@
     <t xml:space="preserve">7.62698459625244</t>
   </si>
   <si>
-    <t xml:space="preserve">7.50749254226685</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.40165758132935</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.49042272567749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.65088176727295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.58942937850952</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.60649967193604</t>
+    <t xml:space="preserve">7.50749111175537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.40165710449219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.49042081832886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.65088272094727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.58942890167236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.60650014877319</t>
   </si>
   <si>
     <t xml:space="preserve">7.62015628814697</t>
   </si>
   <si>
-    <t xml:space="preserve">7.66100645065308</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.529456615448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.59869384765625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.5052227973938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.5675368309021</t>
+    <t xml:space="preserve">7.66100549697876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.52945470809937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.59869337081909</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.50522232055664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.56753587722778</t>
   </si>
   <si>
     <t xml:space="preserve">7.58830642700195</t>
@@ -2240,61 +2240,61 @@
     <t xml:space="preserve">7.51907110214233</t>
   </si>
   <si>
-    <t xml:space="preserve">7.47060489654541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.36328887939453</t>
+    <t xml:space="preserve">7.47060537338257</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.36328983306885</t>
   </si>
   <si>
     <t xml:space="preserve">7.33213233947754</t>
   </si>
   <si>
-    <t xml:space="preserve">7.0932674407959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.16942739486694</t>
+    <t xml:space="preserve">7.09326648712158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.16942644119263</t>
   </si>
   <si>
     <t xml:space="preserve">7.26289653778076</t>
   </si>
   <si>
-    <t xml:space="preserve">7.13134717941284</t>
+    <t xml:space="preserve">7.13134670257568</t>
   </si>
   <si>
     <t xml:space="preserve">7.14173269271851</t>
   </si>
   <si>
-    <t xml:space="preserve">7.0517258644104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.15211725234985</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.07249546051025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.19019746780396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.04134082794189</t>
+    <t xml:space="preserve">7.05172634124756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.15211629867554</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.07249736785889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.1901969909668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.04133939743042</t>
   </si>
   <si>
     <t xml:space="preserve">7.1036524772644</t>
   </si>
   <si>
-    <t xml:space="preserve">7.03787755966187</t>
+    <t xml:space="preserve">7.03787851333618</t>
   </si>
   <si>
     <t xml:space="preserve">7.12788534164429</t>
   </si>
   <si>
-    <t xml:space="preserve">7.22135543823242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.00672149658203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.05864810943604</t>
+    <t xml:space="preserve">7.22135400772095</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.00672101974487</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.05864953994751</t>
   </si>
   <si>
     <t xml:space="preserve">6.96864223480225</t>
@@ -2303,49 +2303,49 @@
     <t xml:space="preserve">6.90840673446655</t>
   </si>
   <si>
-    <t xml:space="preserve">7.08634328842163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.98941278457642</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.10019207000732</t>
+    <t xml:space="preserve">7.08634376525879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.98941230773926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.10019159317017</t>
   </si>
   <si>
     <t xml:space="preserve">7.06903409957886</t>
   </si>
   <si>
-    <t xml:space="preserve">7.02749109268188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.96517992019653</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.95479440689087</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.12096309661865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.18673610687256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.20750570297241</t>
+    <t xml:space="preserve">7.02749061584473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.96518039703369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.95479488372803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.12096214294434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.1867356300354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.20750665664673</t>
   </si>
   <si>
     <t xml:space="preserve">7.11403751373291</t>
   </si>
   <si>
-    <t xml:space="preserve">7.32867002487183</t>
+    <t xml:space="preserve">7.32867097854614</t>
   </si>
   <si>
     <t xml:space="preserve">7.67139148712158</t>
   </si>
   <si>
-    <t xml:space="preserve">7.61253881454468</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.16596508026123</t>
+    <t xml:space="preserve">7.61253929138184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.16596460342407</t>
   </si>
   <si>
     <t xml:space="preserve">7.27328205108643</t>
@@ -2354,73 +2354,73 @@
     <t xml:space="preserve">7.4117546081543</t>
   </si>
   <si>
-    <t xml:space="preserve">7.42560148239136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.47406768798828</t>
+    <t xml:space="preserve">7.42560243606567</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.47406721115112</t>
   </si>
   <si>
     <t xml:space="preserve">7.55022764205933</t>
   </si>
   <si>
-    <t xml:space="preserve">7.64023494720459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.60215425491333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.58138275146484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.57099866867065</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.85140514373779</t>
+    <t xml:space="preserve">7.64023399353027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.60215377807617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.58138465881348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.5709981918335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.85140609741211</t>
   </si>
   <si>
     <t xml:space="preserve">7.96910810470581</t>
   </si>
   <si>
-    <t xml:space="preserve">7.81332397460938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.82025003433228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.26635837554932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.15557861328125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.29751539230347</t>
+    <t xml:space="preserve">7.81332445144653</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.82024955749512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.26635932922363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.15558004379272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.29751348495483</t>
   </si>
   <si>
     <t xml:space="preserve">6.98248910903931</t>
   </si>
   <si>
-    <t xml:space="preserve">6.65638732910156</t>
+    <t xml:space="preserve">6.65638637542725</t>
   </si>
   <si>
     <t xml:space="preserve">6.41267347335815</t>
   </si>
   <si>
-    <t xml:space="preserve">6.6605396270752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.70762252807617</t>
+    <t xml:space="preserve">6.66054010391235</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.70761966705322</t>
   </si>
   <si>
     <t xml:space="preserve">6.53037595748901</t>
   </si>
   <si>
-    <t xml:space="preserve">6.73116159439087</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.85601329803467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.45444107055664</t>
+    <t xml:space="preserve">6.73116064071655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.85601234436035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.45444202423096</t>
   </si>
   <si>
     <t xml:space="preserve">5.45582723617554</t>
@@ -2429,55 +2429,55 @@
     <t xml:space="preserve">4.25388336181641</t>
   </si>
   <si>
-    <t xml:space="preserve">4.66930103302002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.50174856185913</t>
+    <t xml:space="preserve">4.66930055618286</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.50174951553345</t>
   </si>
   <si>
     <t xml:space="preserve">4.49759531021118</t>
   </si>
   <si>
-    <t xml:space="preserve">4.4103569984436</t>
+    <t xml:space="preserve">4.41035747528076</t>
   </si>
   <si>
     <t xml:space="preserve">4.78700351715088</t>
   </si>
   <si>
-    <t xml:space="preserve">4.80223512649536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.96840333938599</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.30766153335571</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.356125831604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.60676097869873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.43644046783447</t>
+    <t xml:space="preserve">4.8022346496582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.96840286254883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.30766105651855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.35612678527832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.60676193237305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.43644094467163</t>
   </si>
   <si>
     <t xml:space="preserve">5.48075151443481</t>
   </si>
   <si>
-    <t xml:space="preserve">5.34504842758179</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.11795330047607</t>
+    <t xml:space="preserve">5.34504890441895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.11795282363892</t>
   </si>
   <si>
     <t xml:space="preserve">5.3810510635376</t>
   </si>
   <si>
-    <t xml:space="preserve">5.42120838165283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.56660461425781</t>
+    <t xml:space="preserve">5.42120885848999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.56660556793213</t>
   </si>
   <si>
     <t xml:space="preserve">5.64691972732544</t>
@@ -2486,31 +2486,31 @@
     <t xml:space="preserve">5.73138809204102</t>
   </si>
   <si>
-    <t xml:space="preserve">5.75077390670776</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.77431392669678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.2661190032959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.30904674530029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.33120203018188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.27027320861816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.15810966491699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.2398099899292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.20519065856934</t>
+    <t xml:space="preserve">5.75077438354492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.77431440353394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.26611852645874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.30904579162598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.33120107650757</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.27027368545532</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.15811061859131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.23980951309204</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.20519113540649</t>
   </si>
   <si>
     <t xml:space="preserve">5.12210702896118</t>
@@ -2519,106 +2519,106 @@
     <t xml:space="preserve">5.4572114944458</t>
   </si>
   <si>
-    <t xml:space="preserve">5.44751834869385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.55968189239502</t>
+    <t xml:space="preserve">5.44751787185669</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.55968141555786</t>
   </si>
   <si>
     <t xml:space="preserve">5.36720418930054</t>
   </si>
   <si>
-    <t xml:space="preserve">5.23704051971436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.08887338638306</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.00440549850464</t>
+    <t xml:space="preserve">5.23703956604004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.0888729095459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.00440502166748</t>
   </si>
   <si>
     <t xml:space="preserve">5.25781059265137</t>
   </si>
   <si>
-    <t xml:space="preserve">5.3699746131897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.15534162521362</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.06117963790894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.97532653808594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.16641855239868</t>
+    <t xml:space="preserve">5.36997318267822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.15534067153931</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.06117868423462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.97532558441162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.16641902923584</t>
   </si>
   <si>
     <t xml:space="preserve">5.12626171112061</t>
   </si>
   <si>
-    <t xml:space="preserve">5.13456964492798</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.10272121429443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.15257215499878</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.35751104354858</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.43782615661621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.46551990509033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.5153694152832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.57906770706177</t>
+    <t xml:space="preserve">5.13457012176514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.10272073745728</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.15257120132446</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.35751056671143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.43782472610474</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.46552038192749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.51536989212036</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.57906675338745</t>
   </si>
   <si>
     <t xml:space="preserve">5.74800395965576</t>
   </si>
   <si>
-    <t xml:space="preserve">5.93217372894287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.07203102111816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.19804096221924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.00694799423218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.9377121925354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.62476444244385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.71061611175537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.75908088684082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.87539863586426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.84908962249756</t>
+    <t xml:space="preserve">5.93217277526855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.07203054428101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.19804000854492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.00694751739502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.93771171569824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.62476348876953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.71061754226685</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.75908184051514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.87539911270142</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.84908866882324</t>
   </si>
   <si>
     <t xml:space="preserve">5.80754709243774</t>
   </si>
   <si>
-    <t xml:space="preserve">5.69122934341431</t>
+    <t xml:space="preserve">5.69122982025146</t>
   </si>
   <si>
     <t xml:space="preserve">5.80849409103394</t>
@@ -2627,55 +2627,55 @@
     <t xml:space="preserve">5.90777158737183</t>
   </si>
   <si>
-    <t xml:space="preserve">5.64590787887573</t>
+    <t xml:space="preserve">5.64590740203857</t>
   </si>
   <si>
     <t xml:space="preserve">5.686194896698</t>
   </si>
   <si>
-    <t xml:space="preserve">5.57252836227417</t>
+    <t xml:space="preserve">5.5725269317627</t>
   </si>
   <si>
     <t xml:space="preserve">5.74230766296387</t>
   </si>
   <si>
-    <t xml:space="preserve">5.5682110786438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.57828330993652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.60274314880371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.69338798522949</t>
+    <t xml:space="preserve">5.56821203231812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.57828378677368</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.60274267196655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.69338941574097</t>
   </si>
   <si>
     <t xml:space="preserve">5.66173458099365</t>
   </si>
   <si>
-    <t xml:space="preserve">5.61713218688965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.48476028442383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.53224182128906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.63727521896362</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.61569309234619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.64015245437622</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.6559796333313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.88906669616699</t>
+    <t xml:space="preserve">5.61713123321533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.48476076126099</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.5322413444519</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.63727474212646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.61569261550903</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.64015293121338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.65597915649414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.88906717300415</t>
   </si>
   <si>
     <t xml:space="preserve">5.93223190307617</t>
@@ -2690,7 +2690,7 @@
     <t xml:space="preserve">5.86172962188721</t>
   </si>
   <si>
-    <t xml:space="preserve">5.71497011184692</t>
+    <t xml:space="preserve">5.71497106552124</t>
   </si>
   <si>
     <t xml:space="preserve">5.68331670761108</t>
@@ -2699,25 +2699,25 @@
     <t xml:space="preserve">5.66892910003662</t>
   </si>
   <si>
-    <t xml:space="preserve">5.47468852996826</t>
+    <t xml:space="preserve">5.47468900680542</t>
   </si>
   <si>
     <t xml:space="preserve">5.57684469223022</t>
   </si>
   <si>
-    <t xml:space="preserve">5.68043947219849</t>
+    <t xml:space="preserve">5.68043851852417</t>
   </si>
   <si>
     <t xml:space="preserve">5.71928691864014</t>
   </si>
   <si>
-    <t xml:space="preserve">5.71784830093384</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.6286416053772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.67324495315552</t>
+    <t xml:space="preserve">5.717848777771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.62864255905151</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.67324542999268</t>
   </si>
   <si>
     <t xml:space="preserve">5.77252292633057</t>
@@ -2729,22 +2729,22 @@
     <t xml:space="preserve">5.85741329193115</t>
   </si>
   <si>
-    <t xml:space="preserve">5.78691101074219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.76245164871216</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.67180681228638</t>
+    <t xml:space="preserve">5.78691148757935</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.76245212554932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.67180633544922</t>
   </si>
   <si>
     <t xml:space="preserve">5.65310144424438</t>
   </si>
   <si>
-    <t xml:space="preserve">5.71209335327148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.61425447463989</t>
+    <t xml:space="preserve">5.71209287643433</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.61425399780273</t>
   </si>
   <si>
     <t xml:space="preserve">5.69051074981689</t>
@@ -2753,22 +2753,22 @@
     <t xml:space="preserve">5.70921564102173</t>
   </si>
   <si>
-    <t xml:space="preserve">5.64303016662598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.64734697341919</t>
+    <t xml:space="preserve">5.64303112030029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.64734649658203</t>
   </si>
   <si>
     <t xml:space="preserve">5.5638952255249</t>
   </si>
   <si>
-    <t xml:space="preserve">5.52216958999634</t>
+    <t xml:space="preserve">5.52216911315918</t>
   </si>
   <si>
     <t xml:space="preserve">5.5336799621582</t>
   </si>
   <si>
-    <t xml:space="preserve">5.72504281997681</t>
+    <t xml:space="preserve">5.72504234313965</t>
   </si>
   <si>
     <t xml:space="preserve">5.60705995559692</t>
@@ -2786,37 +2786,37 @@
     <t xml:space="preserve">5.70058250427246</t>
   </si>
   <si>
-    <t xml:space="preserve">5.58403873443604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.38979768753052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.46605587005615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.51065921783447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.49914836883545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.45742225646973</t>
+    <t xml:space="preserve">5.58403921127319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.38979864120483</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.46605634689331</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.51065874099731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.49914884567261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.45742321014404</t>
   </si>
   <si>
     <t xml:space="preserve">5.56101751327515</t>
   </si>
   <si>
-    <t xml:space="preserve">5.45022869110107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.44447326660156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.40418672561646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.43584108352661</t>
+    <t xml:space="preserve">5.45022821426392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.44447374343872</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.40418720245361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.43584060668945</t>
   </si>
   <si>
     <t xml:space="preserve">5.81856536865234</t>
@@ -2825,46 +2825,46 @@
     <t xml:space="preserve">5.76820707321167</t>
   </si>
   <si>
-    <t xml:space="preserve">5.76532888412476</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.76676750183105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.77971744537354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.78115653991699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.4919548034668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.55957889556885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.56677293777466</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.46317863464355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.47181129455566</t>
+    <t xml:space="preserve">5.76532983779907</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.76676797866821</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.77971792221069</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.78115701675415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.49195432662964</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.55957984924316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.5667724609375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.4631781578064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.47181034088135</t>
   </si>
   <si>
     <t xml:space="preserve">5.4617395401001</t>
   </si>
   <si>
-    <t xml:space="preserve">5.37397193908691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.33512353897095</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.11066865921021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.04160499572754</t>
+    <t xml:space="preserve">5.37397241592407</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.33512401580811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.11066913604736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.04160594940186</t>
   </si>
   <si>
     <t xml:space="preserve">5.03585004806519</t>
@@ -2879,7 +2879,7 @@
     <t xml:space="preserve">5.3696551322937</t>
   </si>
   <si>
-    <t xml:space="preserve">5.54662895202637</t>
+    <t xml:space="preserve">5.54662990570068</t>
   </si>
   <si>
     <t xml:space="preserve">5.45598411560059</t>
@@ -2888,79 +2888,79 @@
     <t xml:space="preserve">5.64878559112549</t>
   </si>
   <si>
-    <t xml:space="preserve">5.7883505821228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.74662494659424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.92072105407715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.11783885955811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.19697427749634</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.30200624465942</t>
+    <t xml:space="preserve">5.78834962844849</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.74662446975708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.92072057723999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.11783933639526</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.19697380065918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.30200719833374</t>
   </si>
   <si>
     <t xml:space="preserve">6.36963129043579</t>
   </si>
   <si>
-    <t xml:space="preserve">6.2717924118042</t>
+    <t xml:space="preserve">6.27179193496704</t>
   </si>
   <si>
     <t xml:space="preserve">6.30493927001953</t>
   </si>
   <si>
-    <t xml:space="preserve">6.44713401794434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.38556480407715</t>
+    <t xml:space="preserve">6.44713306427002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.38556528091431</t>
   </si>
   <si>
     <t xml:space="preserve">6.45006608963013</t>
   </si>
   <si>
-    <t xml:space="preserve">6.26242637634277</t>
+    <t xml:space="preserve">6.26242780685425</t>
   </si>
   <si>
     <t xml:space="preserve">6.31226921081543</t>
   </si>
   <si>
-    <t xml:space="preserve">6.21111917495728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.23310852050781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.16274452209473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.1524829864502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.16127872467041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.17007398605347</t>
+    <t xml:space="preserve">6.21112108230591</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.23310899734497</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.16274404525757</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.15248346328735</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.16127920150757</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.17007446289062</t>
   </si>
   <si>
     <t xml:space="preserve">6.12023305892944</t>
   </si>
   <si>
-    <t xml:space="preserve">6.11583423614502</t>
+    <t xml:space="preserve">6.11583471298218</t>
   </si>
   <si>
     <t xml:space="preserve">6.21405172348022</t>
   </si>
   <si>
-    <t xml:space="preserve">6.14955186843872</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.12609624862671</t>
+    <t xml:space="preserve">6.14955282211304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.12609672546387</t>
   </si>
   <si>
     <t xml:space="preserve">5.98536729812622</t>
@@ -2972,7 +2972,7 @@
     <t xml:space="preserve">6.13342666625977</t>
   </si>
   <si>
-    <t xml:space="preserve">6.09824275970459</t>
+    <t xml:space="preserve">6.09824371337891</t>
   </si>
   <si>
     <t xml:space="preserve">6.1143684387207</t>
@@ -2981,199 +2981,199 @@
     <t xml:space="preserve">6.07478857040405</t>
   </si>
   <si>
-    <t xml:space="preserve">6.25949573516846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.38996315002441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.29907512664795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.25509786605835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.18180179595947</t>
+    <t xml:space="preserve">6.2594952583313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.38996267318726</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.29907464981079</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.25509738922119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.18180131912231</t>
   </si>
   <si>
     <t xml:space="preserve">6.12169933319092</t>
   </si>
   <si>
-    <t xml:space="preserve">6.14222240447998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.09091377258301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.15394926071167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.09677791595459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.06012916564941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.01615238189697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.1290283203125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.98096990585327</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.03520965576172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.91940021514893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.079185962677</t>
+    <t xml:space="preserve">6.14222145080566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.09091567993164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.15394878387451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.09677743911743</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.06013011932373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.01615142822266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.12902879714966</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.98097038269043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.03520917892456</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.9194016456604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.07918739318848</t>
   </si>
   <si>
     <t xml:space="preserve">6.06892490386963</t>
   </si>
   <si>
-    <t xml:space="preserve">6.50137281417847</t>
+    <t xml:space="preserve">6.50137233734131</t>
   </si>
   <si>
     <t xml:space="preserve">6.60545349121094</t>
   </si>
   <si>
-    <t xml:space="preserve">6.75791072845459</t>
+    <t xml:space="preserve">6.75790929794312</t>
   </si>
   <si>
     <t xml:space="preserve">6.93088912963867</t>
   </si>
   <si>
-    <t xml:space="preserve">7.01444673538208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.9734001159668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.07308387756348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.09360647201538</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.16104030609131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.07454967498779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.94994735717773</t>
+    <t xml:space="preserve">7.01444578170776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.97340059280396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.07308292388916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.09360551834106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.16103887557983</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.07454872131348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.94994592666626</t>
   </si>
   <si>
     <t xml:space="preserve">6.81947755813599</t>
   </si>
   <si>
-    <t xml:space="preserve">6.88837623596191</t>
+    <t xml:space="preserve">6.88837671279907</t>
   </si>
   <si>
     <t xml:space="preserve">7.06868505477905</t>
   </si>
   <si>
-    <t xml:space="preserve">6.98366212844849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.9997878074646</t>
+    <t xml:space="preserve">6.98366117477417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.99978637695312</t>
   </si>
   <si>
     <t xml:space="preserve">7.04229831695557</t>
   </si>
   <si>
-    <t xml:space="preserve">6.8927755355835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.20355081558228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.23873233795166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.29297256469727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.31056261062622</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.21967601776123</t>
+    <t xml:space="preserve">6.89277458190918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.20355033874512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.2387318611145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.29297161102295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.31056356430054</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.21967506408691</t>
   </si>
   <si>
     <t xml:space="preserve">7.35893821716309</t>
   </si>
   <si>
-    <t xml:space="preserve">7.43223524093628</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.4982008934021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.46521759033203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.53118371963501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.48720741271973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.64845895767212</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.60814571380615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.66311693191528</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.57882642745972</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.69976711273193</t>
+    <t xml:space="preserve">7.43223476409912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.49820137023926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.46521806716919</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.53118467330933</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.48720693588257</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.6484580039978</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.60814666748047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.6631178855896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.57882785797119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.6997652053833</t>
   </si>
   <si>
     <t xml:space="preserve">7.63379859924316</t>
   </si>
   <si>
-    <t xml:space="preserve">7.67411327362061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.66678237915039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.73274898529053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.90133047103882</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.95630025863647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.9453067779541</t>
+    <t xml:space="preserve">7.67411279678345</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.66678285598755</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.732750415802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.9013295173645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.95630264282227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.94530868530273</t>
   </si>
   <si>
     <t xml:space="preserve">7.99661493301392</t>
   </si>
   <si>
-    <t xml:space="preserve">8.01860427856445</t>
+    <t xml:space="preserve">8.01860332489014</t>
   </si>
   <si>
     <t xml:space="preserve">8.00761127471924</t>
   </si>
   <si>
-    <t xml:space="preserve">7.89400005340576</t>
+    <t xml:space="preserve">7.89400148391724</t>
   </si>
   <si>
     <t xml:space="preserve">7.91232490539551</t>
   </si>
   <si>
-    <t xml:space="preserve">7.90499353408813</t>
+    <t xml:space="preserve">7.90499544143677</t>
   </si>
   <si>
     <t xml:space="preserve">7.81703948974609</t>
@@ -3185,76 +3185,76 @@
     <t xml:space="preserve">7.89766550064087</t>
   </si>
   <si>
-    <t xml:space="preserve">7.8866720199585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.78039121627808</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.77672672271729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.95263910293579</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.9233193397522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.93431234359741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.00394439697266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.00027942657471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.98928546905518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.09923076629639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.04059410095215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.01127624511719</t>
+    <t xml:space="preserve">7.88667058944702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.78039216995239</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.77672624588013</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.95263767242432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.92332077026367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.93431377410889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.00394725799561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.00028038024902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.98928499221802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.09922981262207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.04059314727783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.01127529144287</t>
   </si>
   <si>
     <t xml:space="preserve">8.06258201599121</t>
   </si>
   <si>
-    <t xml:space="preserve">8.22749900817871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.19085025787354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.08823490142822</t>
+    <t xml:space="preserve">8.22749805450439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.19084930419922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.08823585510254</t>
   </si>
   <si>
     <t xml:space="preserve">8.09190082550049</t>
   </si>
   <si>
-    <t xml:space="preserve">8.15053844451904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.2751407623291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.26414585113525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.23116111755371</t>
+    <t xml:space="preserve">8.15053749084473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.27514171600342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.26414775848389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.23116207122803</t>
   </si>
   <si>
     <t xml:space="preserve">8.30079460144043</t>
   </si>
   <si>
-    <t xml:space="preserve">8.42906379699707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.57565593719482</t>
+    <t xml:space="preserve">8.42906284332275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.57565498352051</t>
   </si>
   <si>
     <t xml:space="preserve">8.46204566955566</t>
@@ -3263,55 +3263,55 @@
     <t xml:space="preserve">8.3704252243042</t>
   </si>
   <si>
-    <t xml:space="preserve">8.42173290252686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.4327278137207</t>
+    <t xml:space="preserve">8.42173480987549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.43272686004639</t>
   </si>
   <si>
     <t xml:space="preserve">8.47670650482178</t>
   </si>
   <si>
-    <t xml:space="preserve">8.64895248413086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.72957706451416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.83952140808105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.85418128967285</t>
+    <t xml:space="preserve">8.64895153045654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.72957801818848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.83952236175537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.85418033599854</t>
   </si>
   <si>
     <t xml:space="preserve">8.78454875946045</t>
   </si>
   <si>
-    <t xml:space="preserve">8.80653762817383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.78088569641113</t>
+    <t xml:space="preserve">8.80653953552246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.78088474273682</t>
   </si>
   <si>
     <t xml:space="preserve">8.84685134887695</t>
   </si>
   <si>
-    <t xml:space="preserve">8.79187870025635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.57198905944824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.68054294586182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.56369876861572</t>
+    <t xml:space="preserve">8.79187965393066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.57199001312256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.68054389953613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.56369686126709</t>
   </si>
   <si>
     <t xml:space="preserve">8.46192836761475</t>
   </si>
   <si>
-    <t xml:space="preserve">8.61269760131836</t>
+    <t xml:space="preserve">8.61269855499268</t>
   </si>
   <si>
     <t xml:space="preserve">8.58631324768066</t>
@@ -3320,19 +3320,19 @@
     <t xml:space="preserve">8.44685077667236</t>
   </si>
   <si>
-    <t xml:space="preserve">8.40915966033936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.40538883209229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.50339031219482</t>
+    <t xml:space="preserve">8.40915870666504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.4053897857666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.50338935852051</t>
   </si>
   <si>
     <t xml:space="preserve">8.42800617218018</t>
   </si>
   <si>
-    <t xml:space="preserve">8.54862213134766</t>
+    <t xml:space="preserve">8.54862022399902</t>
   </si>
   <si>
     <t xml:space="preserve">8.42046737670898</t>
@@ -3344,13 +3344,13 @@
     <t xml:space="preserve">8.16039085388184</t>
   </si>
   <si>
-    <t xml:space="preserve">8.28854465484619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.31869697570801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.31492900848389</t>
+    <t xml:space="preserve">8.28854370117188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.31869792938232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.31492805480957</t>
   </si>
   <si>
     <t xml:space="preserve">8.28477478027344</t>
@@ -3362,10 +3362,10 @@
     <t xml:space="preserve">8.19808197021484</t>
   </si>
   <si>
-    <t xml:space="preserve">7.91915893554688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.99831199645996</t>
+    <t xml:space="preserve">7.91915941238403</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.99831247329712</t>
   </si>
   <si>
     <t xml:space="preserve">8.25085163116455</t>
@@ -3377,13 +3377,13 @@
     <t xml:space="preserve">8.45062160491943</t>
   </si>
   <si>
-    <t xml:space="preserve">8.51846885681152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.43554496765137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.41669940948486</t>
+    <t xml:space="preserve">8.51846694946289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.43554306030273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.41669750213623</t>
   </si>
   <si>
     <t xml:space="preserve">8.38654327392578</t>
@@ -3395,7 +3395,7 @@
     <t xml:space="preserve">8.68808174133301</t>
   </si>
   <si>
-    <t xml:space="preserve">8.7295446395874</t>
+    <t xml:space="preserve">8.72954559326172</t>
   </si>
   <si>
     <t xml:space="preserve">8.76346683502197</t>
@@ -3404,28 +3404,28 @@
     <t xml:space="preserve">8.8350830078125</t>
   </si>
   <si>
-    <t xml:space="preserve">8.853928565979</t>
+    <t xml:space="preserve">8.85392761230469</t>
   </si>
   <si>
     <t xml:space="preserve">8.80869960784912</t>
   </si>
   <si>
-    <t xml:space="preserve">8.75216007232666</t>
+    <t xml:space="preserve">8.75215911865234</t>
   </si>
   <si>
     <t xml:space="preserve">8.70315933227539</t>
   </si>
   <si>
-    <t xml:space="preserve">8.7747745513916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.66546630859375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.60139083862305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.78985118865967</t>
+    <t xml:space="preserve">8.77477550506592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.66546726226807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.60138988494873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.7898530960083</t>
   </si>
   <si>
     <t xml:space="preserve">8.76723670959473</t>
@@ -3434,16 +3434,16 @@
     <t xml:space="preserve">8.73708343505859</t>
   </si>
   <si>
-    <t xml:space="preserve">8.65792942047119</t>
+    <t xml:space="preserve">8.65792751312256</t>
   </si>
   <si>
     <t xml:space="preserve">8.69562149047852</t>
   </si>
   <si>
-    <t xml:space="preserve">8.74085235595703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.77100563049316</t>
+    <t xml:space="preserve">8.74085330963135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.77100658416748</t>
   </si>
   <si>
     <t xml:space="preserve">8.63908195495605</t>
@@ -3452,19 +3452,19 @@
     <t xml:space="preserve">8.69939041137695</t>
   </si>
   <si>
-    <t xml:space="preserve">8.71446800231934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.79362201690674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.93308258056641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.85015964508057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.88408279418945</t>
+    <t xml:space="preserve">8.71446704864502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.79362106323242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.93308353424072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.85016059875488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.88408374786377</t>
   </si>
   <si>
     <t xml:space="preserve">8.96323680877686</t>
@@ -3476,7 +3476,7 @@
     <t xml:space="preserve">8.99339008331299</t>
   </si>
   <si>
-    <t xml:space="preserve">9.07631301879883</t>
+    <t xml:space="preserve">9.07631397247314</t>
   </si>
   <si>
     <t xml:space="preserve">8.85769748687744</t>
@@ -3488,13 +3488,13 @@
     <t xml:space="preserve">8.97454452514648</t>
   </si>
   <si>
-    <t xml:space="preserve">8.93685054779053</t>
+    <t xml:space="preserve">8.93685245513916</t>
   </si>
   <si>
     <t xml:space="preserve">9.11777591705322</t>
   </si>
   <si>
-    <t xml:space="preserve">9.0650053024292</t>
+    <t xml:space="preserve">9.06500625610352</t>
   </si>
   <si>
     <t xml:space="preserve">9.17808246612549</t>
@@ -3503,31 +3503,31 @@
     <t xml:space="preserve">9.18185234069824</t>
   </si>
   <si>
-    <t xml:space="preserve">9.16677570343018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.28739166259766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.32131290435791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.42308330535889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.36654472351074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.33639049530029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.23462104797363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.46454524993896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.43062210083008</t>
+    <t xml:space="preserve">9.16677474975586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.28739070892334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.32131385803223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.42308235168457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.36654663085938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.33639144897461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.23462200164795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.46454429626465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.43062114715576</t>
   </si>
   <si>
     <t xml:space="preserve">9.41177463531494</t>
@@ -3536,55 +3536,55 @@
     <t xml:space="preserve">9.555006980896</t>
   </si>
   <si>
-    <t xml:space="preserve">9.47208309173584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.45700645446777</t>
+    <t xml:space="preserve">9.47208213806152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.45700550079346</t>
   </si>
   <si>
     <t xml:space="preserve">9.30246734619141</t>
   </si>
   <si>
-    <t xml:space="preserve">9.38162136077881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.34770011901855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.46077442169189</t>
+    <t xml:space="preserve">9.38162040710449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.34769916534424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.46077537536621</t>
   </si>
   <si>
     <t xml:space="preserve">9.39292907714844</t>
   </si>
   <si>
-    <t xml:space="preserve">9.41931247711182</t>
+    <t xml:space="preserve">9.41931343078613</t>
   </si>
   <si>
     <t xml:space="preserve">9.37785243988037</t>
   </si>
   <si>
-    <t xml:space="preserve">9.28362083435059</t>
+    <t xml:space="preserve">9.2836217880249</t>
   </si>
   <si>
     <t xml:space="preserve">9.2308521270752</t>
   </si>
   <si>
-    <t xml:space="preserve">9.24215888977051</t>
+    <t xml:space="preserve">9.24216079711914</t>
   </si>
   <si>
     <t xml:space="preserve">9.15546798706055</t>
   </si>
   <si>
-    <t xml:space="preserve">9.09515857696533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.07601833343506</t>
+    <t xml:space="preserve">9.09515953063965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.07602024078369</t>
   </si>
   <si>
     <t xml:space="preserve">9.00328826904297</t>
   </si>
   <si>
-    <t xml:space="preserve">8.97649574279785</t>
+    <t xml:space="preserve">8.97649383544922</t>
   </si>
   <si>
     <t xml:space="preserve">8.84251689910889</t>
@@ -3596,10 +3596,10 @@
     <t xml:space="preserve">8.57073211669922</t>
   </si>
   <si>
-    <t xml:space="preserve">8.52862453460693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.68939971923828</t>
+    <t xml:space="preserve">8.52862548828125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.68939781188965</t>
   </si>
   <si>
     <t xml:space="preserve">8.5975284576416</t>
@@ -3611,7 +3611,7 @@
     <t xml:space="preserve">8.56307792663574</t>
   </si>
   <si>
-    <t xml:space="preserve">8.68174266815186</t>
+    <t xml:space="preserve">8.68174362182617</t>
   </si>
   <si>
     <t xml:space="preserve">8.55924987792969</t>
@@ -3620,16 +3620,16 @@
     <t xml:space="preserve">8.49800300598145</t>
   </si>
   <si>
-    <t xml:space="preserve">8.45972442626953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.46355247497559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.48269176483154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.52097129821777</t>
+    <t xml:space="preserve">8.45972347259521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.46355056762695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.48269081115723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.52096939086914</t>
   </si>
   <si>
     <t xml:space="preserve">8.5822172164917</t>
@@ -3647,34 +3647,34 @@
     <t xml:space="preserve">8.62049674987793</t>
   </si>
   <si>
-    <t xml:space="preserve">8.69705581665039</t>
+    <t xml:space="preserve">8.69705390930176</t>
   </si>
   <si>
     <t xml:space="preserve">8.77361392974854</t>
   </si>
   <si>
-    <t xml:space="preserve">8.84634494781494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.82720565795898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.83485984802246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.96118259429932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.97266578674316</t>
+    <t xml:space="preserve">8.84634399414062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.82720470428467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.83486080169678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.961181640625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.97266674041748</t>
   </si>
   <si>
     <t xml:space="preserve">9.00711727142334</t>
   </si>
   <si>
-    <t xml:space="preserve">8.93055820465088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.95735359191895</t>
+    <t xml:space="preserve">8.9305591583252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.95735454559326</t>
   </si>
   <si>
     <t xml:space="preserve">8.98414897918701</t>
@@ -3692,79 +3692,79 @@
     <t xml:space="preserve">8.85400009155273</t>
   </si>
   <si>
-    <t xml:space="preserve">8.87314128875732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.9458703994751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.79275417327881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.44058227539062</t>
+    <t xml:space="preserve">8.87314033508301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.94587135314941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.79275321960449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.44058418273926</t>
   </si>
   <si>
     <t xml:space="preserve">8.647292137146</t>
   </si>
   <si>
-    <t xml:space="preserve">8.83868789672852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.73150634765625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.13343906402588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.14109325408936</t>
+    <t xml:space="preserve">8.83868980407715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.73150539398193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.1334400177002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.14109420776367</t>
   </si>
   <si>
     <t xml:space="preserve">8.33722972869873</t>
   </si>
   <si>
-    <t xml:space="preserve">8.39082145690918</t>
+    <t xml:space="preserve">8.39082050323486</t>
   </si>
   <si>
     <t xml:space="preserve">8.42910003662109</t>
   </si>
   <si>
-    <t xml:space="preserve">8.26449871063232</t>
+    <t xml:space="preserve">8.26449966430664</t>
   </si>
   <si>
     <t xml:space="preserve">8.41761684417725</t>
   </si>
   <si>
-    <t xml:space="preserve">8.49417495727539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.52479839324951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.44823837280273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.24153232574463</t>
+    <t xml:space="preserve">8.49417591094971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.52479934692383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.44824028015137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.24153137207031</t>
   </si>
   <si>
     <t xml:space="preserve">8.21090793609619</t>
   </si>
   <si>
-    <t xml:space="preserve">8.14200496673584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.68648147583008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.939124584198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.86639499664307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.54867649078369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.53642702102661</t>
+    <t xml:space="preserve">8.14200592041016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.68648242950439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.93912363052368</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.86639404296875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.54867553710938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.53642606735229</t>
   </si>
   <si>
     <t xml:space="preserve">7.43077659606934</t>
@@ -3776,10 +3776,10 @@
     <t xml:space="preserve">6.80146408081055</t>
   </si>
   <si>
-    <t xml:space="preserve">7.11688613891602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.74772882461548</t>
+    <t xml:space="preserve">7.11688661575317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.74772930145264</t>
   </si>
   <si>
     <t xml:space="preserve">7.35574769973755</t>
@@ -3788,37 +3788,37 @@
     <t xml:space="preserve">7.40015268325806</t>
   </si>
   <si>
-    <t xml:space="preserve">7.60073566436768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.55939388275146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.9008469581604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.73624467849731</t>
+    <t xml:space="preserve">7.60073661804199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.55939435958862</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.90084457397461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.736243724823</t>
   </si>
   <si>
     <t xml:space="preserve">7.71327686309814</t>
   </si>
   <si>
-    <t xml:space="preserve">7.74390077590942</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.94678020477295</t>
+    <t xml:space="preserve">7.74390029907227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.94678115844727</t>
   </si>
   <si>
     <t xml:space="preserve">7.9352970123291</t>
   </si>
   <si>
-    <t xml:space="preserve">8.07693099975586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.96974897384644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.06161880493164</t>
+    <t xml:space="preserve">8.07692909240723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.96974754333496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.06161975860596</t>
   </si>
   <si>
     <t xml:space="preserve">8.13052082061768</t>
@@ -3827,79 +3827,79 @@
     <t xml:space="preserve">8.09607028961182</t>
   </si>
   <si>
-    <t xml:space="preserve">7.96209144592285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.84342622756958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.67499732971191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.55786180496216</t>
+    <t xml:space="preserve">7.96209192276001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.8434271812439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.6749963760376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.55786275863647</t>
   </si>
   <si>
     <t xml:space="preserve">7.70562124252319</t>
   </si>
   <si>
-    <t xml:space="preserve">7.64360952377319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.52877044677734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.45221281051636</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.51192808151245</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.39096689224243</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.58542394638062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.56092596054077</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.42771244049072</t>
+    <t xml:space="preserve">7.64360809326172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.5287709236145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.4522123336792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.51192855834961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.39096593856812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.58542490005493</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.56092548370361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.4277138710022</t>
   </si>
   <si>
     <t xml:space="preserve">7.21794462203979</t>
   </si>
   <si>
-    <t xml:space="preserve">7.12147903442383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.09851217269897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.144446849823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.17966365814209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.10769939422607</t>
+    <t xml:space="preserve">7.12147951126099</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.09851169586182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.14444637298584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.17966508865356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.10769891738892</t>
   </si>
   <si>
     <t xml:space="preserve">7.0510458946228</t>
   </si>
   <si>
-    <t xml:space="preserve">6.99592351913452</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.89180326461792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.71265554428101</t>
+    <t xml:space="preserve">6.99592208862305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.89180421829224</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.71265697479248</t>
   </si>
   <si>
     <t xml:space="preserve">6.87189865112305</t>
   </si>
   <si>
-    <t xml:space="preserve">7.03114080429077</t>
+    <t xml:space="preserve">7.03114128112793</t>
   </si>
   <si>
     <t xml:space="preserve">7.25162887573242</t>
@@ -3911,67 +3911,67 @@
     <t xml:space="preserve">7.29909610748291</t>
   </si>
   <si>
-    <t xml:space="preserve">7.36799716949463</t>
+    <t xml:space="preserve">7.36799764633179</t>
   </si>
   <si>
     <t xml:space="preserve">7.32359457015991</t>
   </si>
   <si>
-    <t xml:space="preserve">7.29756355285645</t>
+    <t xml:space="preserve">7.29756450653076</t>
   </si>
   <si>
     <t xml:space="preserve">7.27612733840942</t>
   </si>
   <si>
-    <t xml:space="preserve">7.41852569580078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.29296970367432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.41393280029297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.46599292755127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.60379838943481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.77069664001465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.67117071151733</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.66734313964844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.59461164474487</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.74007225036621</t>
+    <t xml:space="preserve">7.41852521896362</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.29297018051147</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.41393375396729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.46599388122559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.60379886627197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.77069711685181</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.67117118835449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.66734170913696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.59461069107056</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.74007272720337</t>
   </si>
   <si>
     <t xml:space="preserve">7.72476100921631</t>
   </si>
   <si>
-    <t xml:space="preserve">7.61757898330688</t>
+    <t xml:space="preserve">7.61757946014404</t>
   </si>
   <si>
     <t xml:space="preserve">7.00664138793945</t>
   </si>
   <si>
-    <t xml:space="preserve">6.77237224578857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.98061275482178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.21028757095337</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.85199308395386</t>
+    <t xml:space="preserve">6.77237176895142</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.98061180114746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.21028804779053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.85199356079102</t>
   </si>
   <si>
     <t xml:space="preserve">6.88720989227295</t>
@@ -3980,103 +3980,103 @@
     <t xml:space="preserve">7.04995012283325</t>
   </si>
   <si>
-    <t xml:space="preserve">6.99062585830688</t>
+    <t xml:space="preserve">6.99062633514404</t>
   </si>
   <si>
     <t xml:space="preserve">7.0226936340332</t>
   </si>
   <si>
-    <t xml:space="preserve">6.96818017959595</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.17180490493774</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.13653135299683</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.27923011779785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.22471570968628</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.14454889297485</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.14775609970093</t>
+    <t xml:space="preserve">6.96817922592163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.1718053817749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.13653182983398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.27922964096069</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.22471618652344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.14454746246338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.14775514602661</t>
   </si>
   <si>
     <t xml:space="preserve">7.14134168624878</t>
   </si>
   <si>
-    <t xml:space="preserve">6.85434198379517</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.89763164520264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.07560396194458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.96497249603271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.83349752426147</t>
+    <t xml:space="preserve">6.85434103012085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.89763116836548</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.07560443878174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.96497297286987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.83349800109863</t>
   </si>
   <si>
     <t xml:space="preserve">6.86396217346191</t>
   </si>
   <si>
-    <t xml:space="preserve">6.71965980529785</t>
+    <t xml:space="preserve">6.71965932846069</t>
   </si>
   <si>
     <t xml:space="preserve">6.37814474105835</t>
   </si>
   <si>
-    <t xml:space="preserve">6.54008436203003</t>
+    <t xml:space="preserve">6.54008388519287</t>
   </si>
   <si>
     <t xml:space="preserve">6.6635422706604</t>
   </si>
   <si>
-    <t xml:space="preserve">6.88480472564697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.73248624801636</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.40379905700684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.48877620697021</t>
+    <t xml:space="preserve">6.88480567932129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.7324857711792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.40379858016968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.48877668380737</t>
   </si>
   <si>
     <t xml:space="preserve">6.51603317260742</t>
   </si>
   <si>
-    <t xml:space="preserve">6.50160264968872</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.51282644271851</t>
+    <t xml:space="preserve">6.50160312652588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.51282596588135</t>
   </si>
   <si>
     <t xml:space="preserve">6.45831251144409</t>
   </si>
   <si>
-    <t xml:space="preserve">6.54970407485962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.61383819580078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.53366947174072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.64430141448975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.72126340866089</t>
+    <t xml:space="preserve">6.54970359802246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.61383771896362</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.53366994857788</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.64430236816406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.72126245498657</t>
   </si>
   <si>
     <t xml:space="preserve">6.79661989212036</t>
@@ -4085,7 +4085,7 @@
     <t xml:space="preserve">6.73408889770508</t>
   </si>
   <si>
-    <t xml:space="preserve">6.69721221923828</t>
+    <t xml:space="preserve">6.69721269607544</t>
   </si>
   <si>
     <t xml:space="preserve">6.73729658126831</t>
@@ -4094,40 +4094,40 @@
     <t xml:space="preserve">6.83670377731323</t>
   </si>
   <si>
-    <t xml:space="preserve">6.84311771392822</t>
+    <t xml:space="preserve">6.84311819076538</t>
   </si>
   <si>
     <t xml:space="preserve">6.78539705276489</t>
   </si>
   <si>
-    <t xml:space="preserve">6.69560956954956</t>
+    <t xml:space="preserve">6.6956090927124</t>
   </si>
   <si>
     <t xml:space="preserve">6.57375383377075</t>
   </si>
   <si>
-    <t xml:space="preserve">6.40700578689575</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.50480985641479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.47274303436279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.45190000534058</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.30599403381348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.22582626342773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.37012720108032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.3220272064209</t>
+    <t xml:space="preserve">6.40700531005859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.50481033325195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.47274351119995</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.45189952850342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.30599451065063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.22582578659058</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.37012767791748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.32202768325806</t>
   </si>
   <si>
     <t xml:space="preserve">6.49358654022217</t>
@@ -4142,37 +4142,37 @@
     <t xml:space="preserve">6.4150218963623</t>
   </si>
   <si>
-    <t xml:space="preserve">6.4823637008667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.58177089691162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.66995573043823</t>
+    <t xml:space="preserve">6.48236274719238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.58177137374878</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.66995525360107</t>
   </si>
   <si>
     <t xml:space="preserve">6.6827826499939</t>
   </si>
   <si>
-    <t xml:space="preserve">6.73569297790527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.63147497177124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.66033506393433</t>
+    <t xml:space="preserve">6.73569345474243</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.6314754486084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.66033554077148</t>
   </si>
   <si>
     <t xml:space="preserve">6.52084302902222</t>
   </si>
   <si>
-    <t xml:space="preserve">6.51763725280762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.33004474639893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.39417886734009</t>
+    <t xml:space="preserve">6.51763677597046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.33004426956177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.39417839050293</t>
   </si>
   <si>
     <t xml:space="preserve">6.26110029220581</t>
@@ -4187,22 +4187,22 @@
     <t xml:space="preserve">6.24506616592407</t>
   </si>
   <si>
-    <t xml:space="preserve">6.37333393096924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.5609278678894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.4663290977478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.35730171203613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.2707200050354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.28515005111694</t>
+    <t xml:space="preserve">6.3733344078064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.56092739105225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.46632862091064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.35730075836182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.27072048187256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.2851505279541</t>
   </si>
   <si>
     <t xml:space="preserve">6.1408486366272</t>
@@ -4211,22 +4211,22 @@
     <t xml:space="preserve">6.24185943603516</t>
   </si>
   <si>
-    <t xml:space="preserve">6.33645820617676</t>
+    <t xml:space="preserve">6.33645725250244</t>
   </si>
   <si>
     <t xml:space="preserve">6.49519014358521</t>
   </si>
   <si>
-    <t xml:space="preserve">6.73088264465332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.69400596618652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.67155933380127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.60742378234863</t>
+    <t xml:space="preserve">6.73088312149048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.69400644302368</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.67155838012695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.60742425918579</t>
   </si>
   <si>
     <t xml:space="preserve">6.75974416732788</t>
@@ -4235,175 +4235,175 @@
     <t xml:space="preserve">6.82227420806885</t>
   </si>
   <si>
-    <t xml:space="preserve">6.88640880584717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.08843040466309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.03391742706299</t>
+    <t xml:space="preserve">6.88640832901001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.08843088150024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.03391647338867</t>
   </si>
   <si>
     <t xml:space="preserve">7.07079362869263</t>
   </si>
   <si>
-    <t xml:space="preserve">7.09163761138916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.05476140975952</t>
+    <t xml:space="preserve">7.091637134552</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.05476093292236</t>
   </si>
   <si>
     <t xml:space="preserve">7.01146984100342</t>
   </si>
   <si>
-    <t xml:space="preserve">7.23593997955322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.35939836502075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.40429210662842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.49568319320679</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.81956052780151</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.72656488418579</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.77947664260864</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.80833721160889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.71534156799316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.6624321937561</t>
+    <t xml:space="preserve">7.23593950271606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.35939741134644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.40429258346558</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.49568367004395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.81956005096436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.72656536102295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.77947759628296</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.80833673477173</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.71534204483032</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.66243267059326</t>
   </si>
   <si>
     <t xml:space="preserve">7.6993088722229</t>
   </si>
   <si>
-    <t xml:space="preserve">7.66488695144653</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.62882471084595</t>
+    <t xml:space="preserve">7.66488552093506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.62882280349731</t>
   </si>
   <si>
     <t xml:space="preserve">7.70750570297241</t>
   </si>
   <si>
-    <t xml:space="preserve">7.60751438140869</t>
+    <t xml:space="preserve">7.60751342773438</t>
   </si>
   <si>
     <t xml:space="preserve">7.7419285774231</t>
   </si>
   <si>
-    <t xml:space="preserve">7.65341281890869</t>
+    <t xml:space="preserve">7.65341234207153</t>
   </si>
   <si>
     <t xml:space="preserve">7.72225856781006</t>
   </si>
   <si>
-    <t xml:space="preserve">7.69275140762329</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.74520587921143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.72553682327271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.65996932983398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.75340270996094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.61407136917114</t>
+    <t xml:space="preserve">7.69275188446045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.74520635604858</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.72553539276123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.65996837615967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.75340223312378</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.61407041549683</t>
   </si>
   <si>
     <t xml:space="preserve">7.68455743789673</t>
   </si>
   <si>
-    <t xml:space="preserve">7.686194896698</t>
+    <t xml:space="preserve">7.68619680404663</t>
   </si>
   <si>
     <t xml:space="preserve">7.77962970733643</t>
   </si>
   <si>
-    <t xml:space="preserve">7.78126859664917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.37474870681763</t>
+    <t xml:space="preserve">7.78126907348633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.37474822998047</t>
   </si>
   <si>
     <t xml:space="preserve">7.4157280921936</t>
   </si>
   <si>
-    <t xml:space="preserve">7.42228555679321</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.55014085769653</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.61243295669556</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.54850292205811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.55669975280762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.56653451919556</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.49768686294556</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.58128690719604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.4796576499939</t>
+    <t xml:space="preserve">7.4222846031189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.55014228820801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.61243200302124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.54850339889526</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.5566987991333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.56653499603271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.49768733978271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.5812873840332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.47965717315674</t>
   </si>
   <si>
     <t xml:space="preserve">7.71406173706055</t>
   </si>
   <si>
-    <t xml:space="preserve">7.90584850311279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.79602098464966</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.87306308746338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.85831165313721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.9501051902771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.88126087188721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.95338487625122</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.974693775177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.01895236968994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.96813821792603</t>
+    <t xml:space="preserve">7.90584802627563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.79602289199829</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.87306451797485</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.85831069946289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.95010757446289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.88126134872437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.95338535308838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.97469425201416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.01895332336426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.96813726425171</t>
   </si>
   <si>
     <t xml:space="preserve">8.00419998168945</t>
@@ -4415,61 +4415,61 @@
     <t xml:space="preserve">7.85339403152466</t>
   </si>
   <si>
-    <t xml:space="preserve">7.8910961151123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.89929008483887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.01239681243896</t>
+    <t xml:space="preserve">7.89109563827515</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.89929151535034</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.01239490509033</t>
   </si>
   <si>
     <t xml:space="preserve">7.98616886138916</t>
   </si>
   <si>
-    <t xml:space="preserve">8.02059268951416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.04518032073975</t>
+    <t xml:space="preserve">8.02059173583984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.04517936706543</t>
   </si>
   <si>
     <t xml:space="preserve">8.35170936584473</t>
   </si>
   <si>
-    <t xml:space="preserve">8.26155471801758</t>
+    <t xml:space="preserve">8.26155376434326</t>
   </si>
   <si>
     <t xml:space="preserve">8.26974868774414</t>
   </si>
   <si>
-    <t xml:space="preserve">8.27794647216797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.40908145904541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.23696613311768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.35580730438232</t>
+    <t xml:space="preserve">8.27794456481934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.40908241271973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.23696517944336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.35580825805664</t>
   </si>
   <si>
     <t xml:space="preserve">8.31072998046875</t>
   </si>
   <si>
-    <t xml:space="preserve">8.38449192047119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.38039493560791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.12058258056641</t>
+    <t xml:space="preserve">8.38449382781982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.38039588928223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.12058353424072</t>
   </si>
   <si>
     <t xml:space="preserve">8.17795467376709</t>
   </si>
   <si>
-    <t xml:space="preserve">8.07796382904053</t>
+    <t xml:space="preserve">8.07796287536621</t>
   </si>
   <si>
     <t xml:space="preserve">8.19270801544189</t>
@@ -4484,40 +4484,40 @@
     <t xml:space="preserve">8.22876930236816</t>
   </si>
   <si>
-    <t xml:space="preserve">8.30253410339355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.4541597366333</t>
+    <t xml:space="preserve">8.30253314971924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.45415878295898</t>
   </si>
   <si>
     <t xml:space="preserve">8.40088558197021</t>
   </si>
   <si>
-    <t xml:space="preserve">8.37629890441895</t>
+    <t xml:space="preserve">8.37629795074463</t>
   </si>
   <si>
     <t xml:space="preserve">8.31892585754395</t>
   </si>
   <si>
-    <t xml:space="preserve">8.1861515045166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.85503339767456</t>
+    <t xml:space="preserve">8.18615055084229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.8550329208374</t>
   </si>
   <si>
     <t xml:space="preserve">7.97961235046387</t>
   </si>
   <si>
-    <t xml:space="preserve">7.59439945220947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.38622331619263</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.46326589584351</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.71734189987183</t>
+    <t xml:space="preserve">7.59440088272095</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.38622188568115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.46326398849487</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.71733999252319</t>
   </si>
   <si>
     <t xml:space="preserve">7.66652584075928</t>
@@ -4529,22 +4529,22 @@
     <t xml:space="preserve">7.53702831268311</t>
   </si>
   <si>
-    <t xml:space="preserve">7.67472171783447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.79766130447388</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.71242237091064</t>
+    <t xml:space="preserve">7.67472219467163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.79766035079956</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.7124228477478</t>
   </si>
   <si>
     <t xml:space="preserve">7.64357662200928</t>
   </si>
   <si>
-    <t xml:space="preserve">7.48621273040771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.57472991943359</t>
+    <t xml:space="preserve">7.48621320724487</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.57472944259644</t>
   </si>
   <si>
     <t xml:space="preserve">7.66324710845947</t>
@@ -4553,40 +4553,40 @@
     <t xml:space="preserve">7.69603061676025</t>
   </si>
   <si>
-    <t xml:space="preserve">7.82224893569946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.70422744750977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.75668096542358</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.83863973617554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.76160049438477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.85175323486328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.77635097503662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.71897888183594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.80585813522339</t>
+    <t xml:space="preserve">7.82224941253662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.70422649383545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.75668048858643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.83864116668701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.76159858703613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.85175514221191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.77635049819946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.71898126602173</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.8058557510376</t>
   </si>
   <si>
     <t xml:space="preserve">7.5419454574585</t>
   </si>
   <si>
-    <t xml:space="preserve">7.60915470123291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.52555465698242</t>
+    <t xml:space="preserve">7.60915422439575</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.52555370330811</t>
   </si>
   <si>
     <t xml:space="preserve">7.76651620864868</t>
@@ -4595,46 +4595,46 @@
     <t xml:space="preserve">7.80421876907349</t>
   </si>
   <si>
-    <t xml:space="preserve">7.88617753982544</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.78946447372437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.87142515182495</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.94191026687622</t>
+    <t xml:space="preserve">7.88617658615112</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.78946495056152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.87142372131348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.94191074371338</t>
   </si>
   <si>
     <t xml:space="preserve">7.89273452758789</t>
   </si>
   <si>
-    <t xml:space="preserve">7.94027042388916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.9140453338623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.1386137008667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.11566543579102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.9320764541626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.02878665924072</t>
+    <t xml:space="preserve">7.94027090072632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.91404485702515</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.13861465454102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.11566638946533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.93207502365112</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.02878761291504</t>
   </si>
   <si>
     <t xml:space="preserve">8.00747966766357</t>
   </si>
   <si>
-    <t xml:space="preserve">7.94682693481445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.9992823600769</t>
+    <t xml:space="preserve">7.94682788848877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.99928283691406</t>
   </si>
   <si>
     <t xml:space="preserve">8.19598579406738</t>
@@ -4652,7 +4652,7 @@
     <t xml:space="preserve">8.11730480194092</t>
   </si>
   <si>
-    <t xml:space="preserve">8.18778800964355</t>
+    <t xml:space="preserve">8.18778896331787</t>
   </si>
   <si>
     <t xml:space="preserve">8.21237754821777</t>
@@ -4661,31 +4661,31 @@
     <t xml:space="preserve">8.27384757995605</t>
   </si>
   <si>
-    <t xml:space="preserve">8.24925899505615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.26841068267822</t>
+    <t xml:space="preserve">8.24926090240479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.26840972900391</t>
   </si>
   <si>
     <t xml:space="preserve">8.18442344665527</t>
   </si>
   <si>
-    <t xml:space="preserve">8.15699768066406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.12443161010742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.16042804718018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.13300228118896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.33183002471924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.43295574188232</t>
+    <t xml:space="preserve">8.15699863433838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.12443351745605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.16042709350586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.13300323486328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.33182907104492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.43295478820801</t>
   </si>
   <si>
     <t xml:space="preserve">8.44666767120361</t>
@@ -4694,7 +4694,7 @@
     <t xml:space="preserve">8.49808788299561</t>
   </si>
   <si>
-    <t xml:space="preserve">8.47409248352051</t>
+    <t xml:space="preserve">8.47409152984619</t>
   </si>
   <si>
     <t xml:space="preserve">8.46723651885986</t>
@@ -4706,7 +4706,7 @@
     <t xml:space="preserve">8.31126022338867</t>
   </si>
   <si>
-    <t xml:space="preserve">8.374680519104</t>
+    <t xml:space="preserve">8.37467861175537</t>
   </si>
   <si>
     <t xml:space="preserve">8.3832483291626</t>
@@ -4715,34 +4715,34 @@
     <t xml:space="preserve">8.41581439971924</t>
   </si>
   <si>
-    <t xml:space="preserve">8.54436683654785</t>
+    <t xml:space="preserve">8.54436779022217</t>
   </si>
   <si>
     <t xml:space="preserve">8.52894020080566</t>
   </si>
   <si>
-    <t xml:space="preserve">8.51522731781006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.51865482330322</t>
+    <t xml:space="preserve">8.51522827148438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.51865673065186</t>
   </si>
   <si>
     <t xml:space="preserve">8.54265308380127</t>
   </si>
   <si>
-    <t xml:space="preserve">8.65577793121338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.66434669494629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.76718711853027</t>
+    <t xml:space="preserve">8.65577697753906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.66434764862061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.76718807220459</t>
   </si>
   <si>
     <t xml:space="preserve">8.85717487335205</t>
   </si>
   <si>
-    <t xml:space="preserve">8.83146381378174</t>
+    <t xml:space="preserve">8.83146476745605</t>
   </si>
   <si>
     <t xml:space="preserve">8.92144966125488</t>
@@ -4754,13 +4754,13 @@
     <t xml:space="preserve">8.81432437896729</t>
   </si>
   <si>
-    <t xml:space="preserve">8.62149620056152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.61721134185791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.634352684021</t>
+    <t xml:space="preserve">8.62149810791016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.61721229553223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.63435173034668</t>
   </si>
   <si>
     <t xml:space="preserve">8.51351451873779</t>
@@ -4778,25 +4778,25 @@
     <t xml:space="preserve">8.70719718933105</t>
   </si>
   <si>
-    <t xml:space="preserve">8.60435676574707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.57007694244385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.5872163772583</t>
+    <t xml:space="preserve">8.60435771942139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.57007598876953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.58721733093262</t>
   </si>
   <si>
     <t xml:space="preserve">8.61292839050293</t>
   </si>
   <si>
-    <t xml:space="preserve">8.62578105926514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.65149211883545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.77575874328613</t>
+    <t xml:space="preserve">8.62578201293945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.65149307250977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.77575778961182</t>
   </si>
   <si>
     <t xml:space="preserve">8.84860420227051</t>
@@ -4805,16 +4805,16 @@
     <t xml:space="preserve">8.78861427307129</t>
   </si>
   <si>
-    <t xml:space="preserve">8.76290321350098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.70291328430176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.63006782531738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.8228931427002</t>
+    <t xml:space="preserve">8.76290416717529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.70291233062744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.63006591796875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.82289409637451</t>
   </si>
   <si>
     <t xml:space="preserve">8.72433757781982</t>
@@ -4826,22 +4826,22 @@
     <t xml:space="preserve">8.66863250732422</t>
   </si>
   <si>
-    <t xml:space="preserve">8.75861930847168</t>
+    <t xml:space="preserve">8.75861835479736</t>
   </si>
   <si>
     <t xml:space="preserve">8.64292335510254</t>
   </si>
   <si>
-    <t xml:space="preserve">8.582932472229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.50665855407715</t>
+    <t xml:space="preserve">8.58293151855469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.50665760040283</t>
   </si>
   <si>
     <t xml:space="preserve">8.45523738861084</t>
   </si>
   <si>
-    <t xml:space="preserve">8.292405128479</t>
+    <t xml:space="preserve">8.29240608215332</t>
   </si>
   <si>
     <t xml:space="preserve">8.19984912872314</t>
@@ -4850,7 +4850,7 @@
     <t xml:space="preserve">8.18270969390869</t>
   </si>
   <si>
-    <t xml:space="preserve">8.25812530517578</t>
+    <t xml:space="preserve">8.2581262588501</t>
   </si>
   <si>
     <t xml:space="preserve">8.17756652832031</t>
@@ -4862,34 +4862,34 @@
     <t xml:space="preserve">8.42781352996826</t>
   </si>
   <si>
-    <t xml:space="preserve">8.35411167144775</t>
+    <t xml:space="preserve">8.35411071777344</t>
   </si>
   <si>
     <t xml:space="preserve">8.4603796005249</t>
   </si>
   <si>
-    <t xml:space="preserve">8.48266220092773</t>
+    <t xml:space="preserve">8.48266124725342</t>
   </si>
   <si>
     <t xml:space="preserve">8.30097675323486</t>
   </si>
   <si>
-    <t xml:space="preserve">7.87418699264526</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.85533285140991</t>
+    <t xml:space="preserve">7.87418651580811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.85533237457275</t>
   </si>
   <si>
     <t xml:space="preserve">7.85876035690308</t>
   </si>
   <si>
-    <t xml:space="preserve">7.79877042770386</t>
+    <t xml:space="preserve">7.7987699508667</t>
   </si>
   <si>
     <t xml:space="preserve">7.91018104553223</t>
   </si>
   <si>
-    <t xml:space="preserve">7.8347635269165</t>
+    <t xml:space="preserve">7.83476495742798</t>
   </si>
   <si>
     <t xml:space="preserve">7.88275623321533</t>
@@ -4898,22 +4898,22 @@
     <t xml:space="preserve">8.00445175170898</t>
   </si>
   <si>
-    <t xml:space="preserve">7.9890251159668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.08501052856445</t>
+    <t xml:space="preserve">7.98902559280396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.08500957489014</t>
   </si>
   <si>
     <t xml:space="preserve">8.1672830581665</t>
   </si>
   <si>
-    <t xml:space="preserve">8.21184730529785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.46894931793213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.56836223602295</t>
+    <t xml:space="preserve">8.21184635162354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.46895027160645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.56836318969727</t>
   </si>
   <si>
     <t xml:space="preserve">8.59578704833984</t>
@@ -4922,10 +4922,10 @@
     <t xml:space="preserve">8.74823379516602</t>
   </si>
   <si>
-    <t xml:space="preserve">8.66926193237305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.62539005279541</t>
+    <t xml:space="preserve">8.66926288604736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.62539100646973</t>
   </si>
   <si>
     <t xml:space="preserve">8.63065528869629</t>
@@ -4937,7 +4937,7 @@
     <t xml:space="preserve">8.56572246551514</t>
   </si>
   <si>
-    <t xml:space="preserve">8.62363433837891</t>
+    <t xml:space="preserve">8.62363529205322</t>
   </si>
   <si>
     <t xml:space="preserve">8.61135005950928</t>
@@ -4952,7 +4952,7 @@
     <t xml:space="preserve">8.72541904449463</t>
   </si>
   <si>
-    <t xml:space="preserve">8.74472427368164</t>
+    <t xml:space="preserve">8.74472332000732</t>
   </si>
   <si>
     <t xml:space="preserve">8.7877197265625</t>
@@ -4961,7 +4961,7 @@
     <t xml:space="preserve">8.75174331665039</t>
   </si>
   <si>
-    <t xml:space="preserve">8.80526828765869</t>
+    <t xml:space="preserve">8.80526733398438</t>
   </si>
   <si>
     <t xml:space="preserve">8.84914112091064</t>
@@ -4970,28 +4970,28 @@
     <t xml:space="preserve">8.81404304504395</t>
   </si>
   <si>
-    <t xml:space="preserve">8.87985134124756</t>
+    <t xml:space="preserve">8.87985229492188</t>
   </si>
   <si>
     <t xml:space="preserve">8.97198581695557</t>
   </si>
   <si>
-    <t xml:space="preserve">8.95004940032959</t>
+    <t xml:space="preserve">8.95004844665527</t>
   </si>
   <si>
     <t xml:space="preserve">8.93249893188477</t>
   </si>
   <si>
-    <t xml:space="preserve">9.01585674285889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.97637176513672</t>
+    <t xml:space="preserve">9.0158576965332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.9763708114624</t>
   </si>
   <si>
     <t xml:space="preserve">9.00708293914795</t>
   </si>
   <si>
-    <t xml:space="preserve">9.03779315948486</t>
+    <t xml:space="preserve">9.03779411315918</t>
   </si>
   <si>
     <t xml:space="preserve">9.00269603729248</t>
@@ -5009,10 +5009,10 @@
     <t xml:space="preserve">9.01147079467773</t>
   </si>
   <si>
-    <t xml:space="preserve">8.95443630218506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.8579158782959</t>
+    <t xml:space="preserve">8.95443534851074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.85791683197021</t>
   </si>
   <si>
     <t xml:space="preserve">8.90178871154785</t>
@@ -5036,7 +5036,7 @@
     <t xml:space="preserve">8.96321105957031</t>
   </si>
   <si>
-    <t xml:space="preserve">9.04656791687012</t>
+    <t xml:space="preserve">9.04656887054443</t>
   </si>
   <si>
     <t xml:space="preserve">9.0509557723999</t>
@@ -5045,16 +5045,16 @@
     <t xml:space="preserve">8.8228178024292</t>
   </si>
   <si>
-    <t xml:space="preserve">8.77104759216309</t>
+    <t xml:space="preserve">8.77104663848877</t>
   </si>
   <si>
     <t xml:space="preserve">8.83159160614014</t>
   </si>
   <si>
-    <t xml:space="preserve">8.83598041534424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.85352802276611</t>
+    <t xml:space="preserve">8.83597946166992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.85352897644043</t>
   </si>
   <si>
     <t xml:space="preserve">8.71664524078369</t>
@@ -5066,10 +5066,10 @@
     <t xml:space="preserve">8.5920467376709</t>
   </si>
   <si>
-    <t xml:space="preserve">8.64995861053467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.73068428039551</t>
+    <t xml:space="preserve">8.64995765686035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.73068523406982</t>
   </si>
   <si>
     <t xml:space="preserve">8.86230278015137</t>
@@ -5081,7 +5081,7 @@
     <t xml:space="preserve">8.9281120300293</t>
   </si>
   <si>
-    <t xml:space="preserve">8.99392032623291</t>
+    <t xml:space="preserve">8.99392127990723</t>
   </si>
   <si>
     <t xml:space="preserve">9.17818641662598</t>
@@ -5093,28 +5093,28 @@
     <t xml:space="preserve">9.51162052154541</t>
   </si>
   <si>
-    <t xml:space="preserve">9.9020881652832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.84066677093506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.99422168731689</t>
+    <t xml:space="preserve">9.90208911895752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.84066486358643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.99422073364258</t>
   </si>
   <si>
     <t xml:space="preserve">10.0556421279907</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0951290130615</t>
+    <t xml:space="preserve">10.0951280593872</t>
   </si>
   <si>
     <t xml:space="preserve">10.1521625518799</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2004222869873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2179727554321</t>
+    <t xml:space="preserve">10.2004232406616</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2179718017578</t>
   </si>
   <si>
     <t xml:space="preserve">10.2750062942505</t>
@@ -5123,34 +5123,34 @@
     <t xml:space="preserve">10.2837820053101</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3364276885986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4680471420288</t>
+    <t xml:space="preserve">10.3364286422729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4680461883545</t>
   </si>
   <si>
     <t xml:space="preserve">10.0644178390503</t>
   </si>
   <si>
-    <t xml:space="preserve">10.086353302002</t>
+    <t xml:space="preserve">10.0863542556763</t>
   </si>
   <si>
     <t xml:space="preserve">10.0380926132202</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0512542724609</t>
+    <t xml:space="preserve">10.0512552261353</t>
   </si>
   <si>
     <t xml:space="preserve">10.1390018463135</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1477756500244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1828727722168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1170654296875</t>
+    <t xml:space="preserve">10.1477746963501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1828737258911</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1170644760132</t>
   </si>
   <si>
     <t xml:space="preserve">10.2355213165283</t>
@@ -5165,13 +5165,13 @@
     <t xml:space="preserve">10.1126766204834</t>
   </si>
   <si>
-    <t xml:space="preserve">10.213583946228</t>
+    <t xml:space="preserve">10.2135848999023</t>
   </si>
   <si>
     <t xml:space="preserve">10.1565494537354</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2311344146729</t>
+    <t xml:space="preserve">10.2311334609985</t>
   </si>
   <si>
     <t xml:space="preserve">10.0907411575317</t>
@@ -5189,22 +5189,22 @@
     <t xml:space="preserve">10.292555809021</t>
   </si>
   <si>
-    <t xml:space="preserve">10.463659286499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.349591255188</t>
+    <t xml:space="preserve">10.4636602401733</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3495903015137</t>
   </si>
   <si>
     <t xml:space="preserve">10.3539781570435</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4812078475952</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4592714309692</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.450496673584</t>
+    <t xml:space="preserve">10.4812088012695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4592723846436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4504976272583</t>
   </si>
   <si>
     <t xml:space="preserve">10.6084403991699</t>
@@ -5219,16 +5219,16 @@
     <t xml:space="preserve">10.7619953155518</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7970924377441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7883176803589</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0120697021484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8672904968262</t>
+    <t xml:space="preserve">10.7970933914185</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7883186340332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0120687484741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8672895431519</t>
   </si>
   <si>
     <t xml:space="preserve">10.8804512023926</t>
@@ -5246,22 +5246,22 @@
     <t xml:space="preserve">10.8979997634888</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0822658538818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.064715385437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0471677780151</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9945211410522</t>
+    <t xml:space="preserve">11.0822668075562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0647163391113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0471687316895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9945201873779</t>
   </si>
   <si>
     <t xml:space="preserve">11.0559425354004</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2884674072266</t>
+    <t xml:space="preserve">11.2884664535522</t>
   </si>
   <si>
     <t xml:space="preserve">11.2226581573486</t>
@@ -5270,10 +5270,10 @@
     <t xml:space="preserve">11.3674392700195</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2270450592041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1919479370117</t>
+    <t xml:space="preserve">11.2270460128784</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.191948890686</t>
   </si>
   <si>
     <t xml:space="preserve">11.0340051651001</t>
@@ -5291,16 +5291,16 @@
     <t xml:space="preserve">11.0734901428223</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0252313613892</t>
+    <t xml:space="preserve">11.0252323150635</t>
   </si>
   <si>
     <t xml:space="preserve">11.0555458068848</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1014776229858</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9728708267212</t>
+    <t xml:space="preserve">11.1014766693115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9728698730469</t>
   </si>
   <si>
     <t xml:space="preserve">11.0325803756714</t>
@@ -5309,25 +5309,25 @@
     <t xml:space="preserve">10.9269399642944</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2346754074097</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0922908782959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.083104133606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1520013809204</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0142078399658</t>
+    <t xml:space="preserve">11.234676361084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0922899246216</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0831031799316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1520004272461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0142068862915</t>
   </si>
   <si>
     <t xml:space="preserve">11.1106634140015</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0188007354736</t>
+    <t xml:space="preserve">11.0188016891479</t>
   </si>
   <si>
     <t xml:space="preserve">11.1336278915405</t>
@@ -5336,13 +5336,13 @@
     <t xml:space="preserve">11.2484550476074</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1703729629517</t>
+    <t xml:space="preserve">11.1703720092773</t>
   </si>
   <si>
     <t xml:space="preserve">11.1198492050171</t>
   </si>
   <si>
-    <t xml:space="preserve">11.225489616394</t>
+    <t xml:space="preserve">11.2254905700684</t>
   </si>
   <si>
     <t xml:space="preserve">11.3219442367554</t>
@@ -5351,16 +5351,16 @@
     <t xml:space="preserve">11.2163038253784</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1795597076416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1382217407227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6526460647583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4964828491211</t>
+    <t xml:space="preserve">11.1795587539673</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1382207870483</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6526470184326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4964818954468</t>
   </si>
   <si>
     <t xml:space="preserve">11.1428146362305</t>
@@ -5372,19 +5372,19 @@
     <t xml:space="preserve">10.5916442871094</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6192035675049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.890193939209</t>
+    <t xml:space="preserve">10.6192026138306</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8901948928833</t>
   </si>
   <si>
     <t xml:space="preserve">10.816704750061</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9177532196045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9223480224609</t>
+    <t xml:space="preserve">10.9177541732788</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9223470687866</t>
   </si>
   <si>
     <t xml:space="preserve">10.9361257553101</t>
@@ -5393,13 +5393,13 @@
     <t xml:space="preserve">11.0785112380981</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3081665039062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4046192169189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2806072235107</t>
+    <t xml:space="preserve">11.3081655502319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4046201705933</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2806062698364</t>
   </si>
   <si>
     <t xml:space="preserve">11.3632822036743</t>
@@ -5426,22 +5426,22 @@
     <t xml:space="preserve">11.5286331176758</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4551429748535</t>
+    <t xml:space="preserve">11.4551448822021</t>
   </si>
   <si>
     <t xml:space="preserve">11.3495025634766</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3035726547241</t>
+    <t xml:space="preserve">11.3035736083984</t>
   </si>
   <si>
     <t xml:space="preserve">11.3449106216431</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2897930145264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.45973777771</t>
+    <t xml:space="preserve">11.2897920608521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4597368240356</t>
   </si>
   <si>
     <t xml:space="preserve">11.4367713928223</t>
@@ -5450,7 +5450,7 @@
     <t xml:space="preserve">11.524040222168</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5699710845947</t>
+    <t xml:space="preserve">11.569972038269</t>
   </si>
   <si>
     <t xml:space="preserve">11.5975294113159</t>
@@ -5459,25 +5459,25 @@
     <t xml:space="preserve">11.6434602737427</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6388673782349</t>
+    <t xml:space="preserve">11.6388683319092</t>
   </si>
   <si>
     <t xml:space="preserve">11.3816547393799</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3678760528564</t>
+    <t xml:space="preserve">11.3678750991821</t>
   </si>
   <si>
     <t xml:space="preserve">11.4643287658691</t>
   </si>
   <si>
-    <t xml:space="preserve">11.579155921936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6250877380371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5653781890869</t>
+    <t xml:space="preserve">11.5791568756104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6250867843628</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5653772354126</t>
   </si>
   <si>
     <t xml:space="preserve">11.5424118041992</t>
@@ -5486,19 +5486,19 @@
     <t xml:space="preserve">11.4000263214111</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5010747909546</t>
+    <t xml:space="preserve">11.5010757446289</t>
   </si>
   <si>
     <t xml:space="preserve">11.5607852935791</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6802043914795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6296806335449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6893911361694</t>
+    <t xml:space="preserve">11.6802053451538</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6296815872192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6893920898438</t>
   </si>
   <si>
     <t xml:space="preserve">11.7766590118408</t>
@@ -5513,7 +5513,7 @@
     <t xml:space="preserve">11.9282312393188</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2864923477173</t>
+    <t xml:space="preserve">12.286491394043</t>
   </si>
   <si>
     <t xml:space="preserve">12.3232364654541</t>
@@ -5528,13 +5528,13 @@
     <t xml:space="preserve">12.0798025131226</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0706176757812</t>
+    <t xml:space="preserve">12.0706167221069</t>
   </si>
   <si>
     <t xml:space="preserve">11.9833478927612</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1073627471924</t>
+    <t xml:space="preserve">12.1073617935181</t>
   </si>
   <si>
     <t xml:space="preserve">12.0338726043701</t>
@@ -5543,22 +5543,22 @@
     <t xml:space="preserve">11.9328241348267</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8868923187256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9695692062378</t>
+    <t xml:space="preserve">11.8868932723999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9695682525635</t>
   </si>
   <si>
     <t xml:space="preserve">11.9144515991211</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1211404800415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2175951004028</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2084083557129</t>
+    <t xml:space="preserve">12.1211395263672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2175960540771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2084093093872</t>
   </si>
   <si>
     <t xml:space="preserve">12.2405605316162</t>
@@ -5570,19 +5570,19 @@
     <t xml:space="preserve">12.2038154602051</t>
   </si>
   <si>
-    <t xml:space="preserve">12.309455871582</t>
+    <t xml:space="preserve">12.3094568252563</t>
   </si>
   <si>
     <t xml:space="preserve">12.1681852340698</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2482385635376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3282928466797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3800926208496</t>
+    <t xml:space="preserve">12.2482395172119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.328293800354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3800935745239</t>
   </si>
   <si>
     <t xml:space="preserve">12.4789819717407</t>
@@ -5597,10 +5597,10 @@
     <t xml:space="preserve">12.5119457244873</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6673450469971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7097263336182</t>
+    <t xml:space="preserve">12.6673440933228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7097253799438</t>
   </si>
   <si>
     <t xml:space="preserve">12.8462886810303</t>
@@ -5612,19 +5612,19 @@
     <t xml:space="preserve">12.964015007019</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8651247024536</t>
+    <t xml:space="preserve">12.8651237487793</t>
   </si>
   <si>
     <t xml:space="preserve">12.8604154586792</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9875593185425</t>
+    <t xml:space="preserve">12.9875602722168</t>
   </si>
   <si>
     <t xml:space="preserve">12.9969778060913</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0393590927124</t>
+    <t xml:space="preserve">13.0393600463867</t>
   </si>
   <si>
     <t xml:space="preserve">13.0629043579102</t>
@@ -5633,13 +5633,13 @@
     <t xml:space="preserve">12.9122152328491</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7850704193115</t>
+    <t xml:space="preserve">12.7850713729858</t>
   </si>
   <si>
     <t xml:space="preserve">12.7568168640137</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6908903121948</t>
+    <t xml:space="preserve">12.6908893585205</t>
   </si>
   <si>
     <t xml:space="preserve">12.8509979248047</t>
@@ -5654,10 +5654,10 @@
     <t xml:space="preserve">13.0111045837402</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0487766265869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1476678848267</t>
+    <t xml:space="preserve">13.0487775802612</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1476669311523</t>
   </si>
   <si>
     <t xml:space="preserve">13.2465572357178</t>
@@ -5666,13 +5666,13 @@
     <t xml:space="preserve">13.1241226196289</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0440692901611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1806306838989</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3737010955811</t>
+    <t xml:space="preserve">13.0440683364868</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1806316375732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3737020492554</t>
   </si>
   <si>
     <t xml:space="preserve">13.463173866272</t>
@@ -5696,7 +5696,7 @@
     <t xml:space="preserve">13.4961376190186</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6374092102051</t>
+    <t xml:space="preserve">13.6374082565308</t>
   </si>
   <si>
     <t xml:space="preserve">13.6232814788818</t>
@@ -5708,7 +5708,7 @@
     <t xml:space="preserve">13.802225112915</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8351888656616</t>
+    <t xml:space="preserve">13.8351879119873</t>
   </si>
   <si>
     <t xml:space="preserve">13.6703729629517</t>
@@ -5723,7 +5723,7 @@
     <t xml:space="preserve">13.7551345825195</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7315902709961</t>
+    <t xml:space="preserve">13.7315893173218</t>
   </si>
   <si>
     <t xml:space="preserve">13.8116436004639</t>
@@ -5762,7 +5762,7 @@
     <t xml:space="preserve">14.621600151062</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8052530288696</t>
+    <t xml:space="preserve">14.8052539825439</t>
   </si>
   <si>
     <t xml:space="preserve">14.6922369003296</t>
@@ -5774,31 +5774,31 @@
     <t xml:space="preserve">15.0595417022705</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2102308273315</t>
+    <t xml:space="preserve">15.2102317810059</t>
   </si>
   <si>
     <t xml:space="preserve">15.1066331863403</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0454158782959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1961050033569</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3656311035156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4221382141113</t>
+    <t xml:space="preserve">15.0454149246216</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1961040496826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3656301498413</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4221391677856</t>
   </si>
   <si>
     <t xml:space="preserve">15.3891754150391</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6152086257935</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5634088516235</t>
+    <t xml:space="preserve">15.6152095794678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5634107589722</t>
   </si>
   <si>
     <t xml:space="preserve">15.4786462783813</t>
@@ -5813,22 +5813,22 @@
     <t xml:space="preserve">15.5445737838745</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5021915435791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5869541168213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.685845375061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4739398956299</t>
+    <t xml:space="preserve">15.5021924972534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5869550704956</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6858463287354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4739389419556</t>
   </si>
   <si>
     <t xml:space="preserve">15.6528825759888</t>
   </si>
   <si>
-    <t xml:space="preserve">15.869499206543</t>
+    <t xml:space="preserve">15.8694982528687</t>
   </si>
   <si>
     <t xml:space="preserve">15.5963735580444</t>
@@ -5852,13 +5852,13 @@
     <t xml:space="preserve">14.8382167816162</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3562116622925</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.53515625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.75648021698</t>
+    <t xml:space="preserve">15.3562126159668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5351572036743</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7564811706543</t>
   </si>
   <si>
     <t xml:space="preserve">15.9495525360107</t>
@@ -5879,7 +5879,7 @@
     <t xml:space="preserve">16.5381832122803</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5852737426758</t>
+    <t xml:space="preserve">16.5852756500244</t>
   </si>
   <si>
     <t xml:space="preserve">16.8018894195557</t>
@@ -5903,7 +5903,7 @@
     <t xml:space="preserve">17.3198852539062</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2021579742432</t>
+    <t xml:space="preserve">17.2021598815918</t>
   </si>
   <si>
     <t xml:space="preserve">17.0891437530518</t>
@@ -5936,10 +5936,10 @@
     <t xml:space="preserve">17.9697341918945</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9508991241455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8990993499756</t>
+    <t xml:space="preserve">17.9508972167969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.899097442627</t>
   </si>
   <si>
     <t xml:space="preserve">17.997989654541</t>
@@ -5948,7 +5948,7 @@
     <t xml:space="preserve">18.0121154785156</t>
   </si>
   <si>
-    <t xml:space="preserve">17.7484073638916</t>
+    <t xml:space="preserve">17.7484092712402</t>
   </si>
   <si>
     <t xml:space="preserve">17.8567161560059</t>
@@ -5957,7 +5957,7 @@
     <t xml:space="preserve">17.9744434356689</t>
   </si>
   <si>
-    <t xml:space="preserve">17.941478729248</t>
+    <t xml:space="preserve">17.9414806365967</t>
   </si>
   <si>
     <t xml:space="preserve">17.7625370025635</t>
@@ -5972,7 +5972,7 @@
     <t xml:space="preserve">17.6683559417725</t>
   </si>
   <si>
-    <t xml:space="preserve">17.5741748809814</t>
+    <t xml:space="preserve">17.5741729736328</t>
   </si>
   <si>
     <t xml:space="preserve">17.5930099487305</t>
@@ -6306,6 +6306,9 @@
   </si>
   <si>
     <t xml:space="preserve">20.25</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.5900001525879</t>
   </si>
 </sst>
 </file>
@@ -72372,7 +72375,7 @@
     </row>
     <row r="2529">
       <c r="A2529" s="1" t="n">
-        <v>46000.6923263889</v>
+        <v>46000.3333333333</v>
       </c>
       <c r="B2529" t="n">
         <v>1252294</v>
@@ -72393,6 +72396,32 @@
         <v>2093</v>
       </c>
       <c r="H2529" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2530">
+      <c r="A2530" s="1" t="n">
+        <v>46001.691087963</v>
+      </c>
+      <c r="B2530" t="n">
+        <v>1538355</v>
+      </c>
+      <c r="C2530" t="n">
+        <v>20.6800003051758</v>
+      </c>
+      <c r="D2530" t="n">
+        <v>20.3999996185303</v>
+      </c>
+      <c r="E2530" t="n">
+        <v>20.4799995422363</v>
+      </c>
+      <c r="F2530" t="n">
+        <v>20.5900001525879</v>
+      </c>
+      <c r="G2530" t="s">
+        <v>2098</v>
+      </c>
+      <c r="H2530" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/PST.MI.xlsx
+++ b/data/PST.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2108" uniqueCount="2108">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2109" uniqueCount="2109">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,43 +38,43 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">3.82970333099365</t>
+    <t xml:space="preserve">3.82970309257507</t>
   </si>
   <si>
     <t xml:space="preserve">PST.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">3.95891737937927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.89843440055847</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87644100189209</t>
+    <t xml:space="preserve">3.95891761779785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89843392372131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87644028663635</t>
   </si>
   <si>
     <t xml:space="preserve">3.84070038795471</t>
   </si>
   <si>
-    <t xml:space="preserve">3.80495977401733</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.89568519592285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94242262840271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92042875289917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87094283103943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.75547361373901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.68399286270142</t>
+    <t xml:space="preserve">3.80496096611023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89568471908569</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94242310523987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92042851448059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87094187736511</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.75547385215759</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.68399333953857</t>
   </si>
   <si>
     <t xml:space="preserve">3.48054909706116</t>
@@ -83,142 +83,142 @@
     <t xml:space="preserve">3.61526250839233</t>
   </si>
   <si>
-    <t xml:space="preserve">3.66199922561646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.5850203037262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.68949246406555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73622941970825</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.65924978256226</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.75272440910339</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.65100240707397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.57402300834656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.4640531539917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.29085063934326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.94719529151917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.84272289276123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.10940074920654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.97468686103821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.98568367958069</t>
+    <t xml:space="preserve">3.66199970245361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.58502006530762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.68949151039124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73622918128967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.65925025939941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.75272369384766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.6510021686554</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.57402324676514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.46405339241028</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.290851354599</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.94719505310059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.84272360801697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.10940098762512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.97468733787537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.98568391799927</t>
   </si>
   <si>
     <t xml:space="preserve">3.07640910148621</t>
   </si>
   <si>
-    <t xml:space="preserve">3.06266307830811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.1863796710968</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.17263317108154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.24136424064636</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.35683226585388</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.2826030254364</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.24961137771606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.34308576583862</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.38982319831848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.44755744934082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.41731572151184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.38707399368286</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.40906858444214</t>
+    <t xml:space="preserve">3.06266260147095</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.18637919425964</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.17263293266296</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.24136400222778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.35683178901672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.28260278701782</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.24961161613464</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.3430860042572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.38982367515564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.44755840301514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.41731595993042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.38707375526428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.40906834602356</t>
   </si>
   <si>
     <t xml:space="preserve">3.3705792427063</t>
   </si>
   <si>
-    <t xml:space="preserve">3.39257287979126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.36783027648926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.54378151893616</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.56852412223816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.56577563285828</t>
+    <t xml:space="preserve">3.39257311820984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.36782956123352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.54378128051758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.56852436065674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.56577634811401</t>
   </si>
   <si>
     <t xml:space="preserve">3.53828310966492</t>
   </si>
   <si>
-    <t xml:space="preserve">3.51903867721558</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.53278422355652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.60151553153992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.72248220443726</t>
+    <t xml:space="preserve">3.51903891563416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.5327844619751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.60151600837708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.72248196601868</t>
   </si>
   <si>
     <t xml:space="preserve">3.70598697662354</t>
   </si>
   <si>
-    <t xml:space="preserve">3.64275431632996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71148538589478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.65650057792664</t>
+    <t xml:space="preserve">3.64275407791138</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71148586273193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.65650129318237</t>
   </si>
   <si>
     <t xml:space="preserve">3.60701417922974</t>
   </si>
   <si>
-    <t xml:space="preserve">3.54653072357178</t>
+    <t xml:space="preserve">3.54653096199036</t>
   </si>
   <si>
     <t xml:space="preserve">3.44480848312378</t>
@@ -227,19 +227,19 @@
     <t xml:space="preserve">3.49979424476624</t>
   </si>
   <si>
-    <t xml:space="preserve">3.51628875732422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.53553366661072</t>
+    <t xml:space="preserve">3.5162889957428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.53553414344788</t>
   </si>
   <si>
     <t xml:space="preserve">3.55202913284302</t>
   </si>
   <si>
-    <t xml:space="preserve">3.62900757789612</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.56302690505981</t>
+    <t xml:space="preserve">3.62900829315186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.56302666664124</t>
   </si>
   <si>
     <t xml:space="preserve">3.56027674674988</t>
@@ -248,232 +248,232 @@
     <t xml:space="preserve">3.58776903152466</t>
   </si>
   <si>
-    <t xml:space="preserve">3.55752849578857</t>
+    <t xml:space="preserve">3.55752754211426</t>
   </si>
   <si>
     <t xml:space="preserve">3.6042652130127</t>
   </si>
   <si>
-    <t xml:space="preserve">3.60976386070251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.67299628257751</t>
+    <t xml:space="preserve">3.60976338386536</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.67299652099609</t>
   </si>
   <si>
     <t xml:space="preserve">3.71973371505737</t>
   </si>
   <si>
-    <t xml:space="preserve">3.72798085212708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66749787330627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61251330375671</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.69499063491821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.72523164749146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.70323777198792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.68674206733704</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71423506736755</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61801052093506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71698451042175</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.67574572563171</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.75822257995605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.76372170448303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73347949981689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.78571510314941</t>
+    <t xml:space="preserve">3.72798180580139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66749835014343</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61251282691956</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.69498991966248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.72523212432861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.70323824882507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.68674302101135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71423435211182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.6180112361908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71698403358459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.67574524879456</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.75822353363037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.76372146606445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73347926139832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.78571581840515</t>
   </si>
   <si>
     <t xml:space="preserve">3.78296613693237</t>
   </si>
   <si>
-    <t xml:space="preserve">3.79396390914917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77196931838989</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.78021693229675</t>
+    <t xml:space="preserve">3.79396295547485</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77196884155273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.78021669387817</t>
   </si>
   <si>
     <t xml:space="preserve">3.84894847869873</t>
   </si>
   <si>
-    <t xml:space="preserve">3.85719609260559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.76647114753723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.70873594284058</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.69224119186401</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80221080780029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88895344734192</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83979868888855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83112525939941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8744957447052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.56800627708435</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.35693311691284</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.44656753540039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.44078326225281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.53620004653931</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.45813250541687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.37139010429382</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.33380126953125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.30777883529663</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.43210983276367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.58824563026428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.57957172393799</t>
+    <t xml:space="preserve">3.85719561576843</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.76647138595581</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.70873641967773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.69224143028259</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.80221128463745</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88895320892334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.83979964256287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.83112478256226</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87449669837952</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.56800603866577</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.35693264007568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.44656682014465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.44078373908997</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.53620100021362</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.45813202857971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.3713903427124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.33380150794983</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.30777859687805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.43210911750793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.58824610710144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.57957196235657</t>
   </si>
   <si>
     <t xml:space="preserve">3.66342306137085</t>
   </si>
   <si>
-    <t xml:space="preserve">3.59981179237366</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.602703332901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.58246374130249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.63740062713623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.62583494186401</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.58535480499268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.57668018341064</t>
+    <t xml:space="preserve">3.59981203079224</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.60270309448242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.58246326446533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.63740086555481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.62583446502686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.5853545665741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.57668042182922</t>
   </si>
   <si>
     <t xml:space="preserve">3.5333092212677</t>
   </si>
   <si>
-    <t xml:space="preserve">3.51596021652222</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.46102404594421</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.72992563247681</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.70968532562256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73570823669434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.74149060249329</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.79353737831116</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80510258674622</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.72703433036804</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.65185785293579</t>
+    <t xml:space="preserve">3.51596117019653</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.46102428436279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.72992515563965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.70968556404114</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73570799827576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.74149036407471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.79353618621826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.80510187149048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.72703456878662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.65185737609863</t>
   </si>
   <si>
     <t xml:space="preserve">3.68944573402405</t>
   </si>
   <si>
-    <t xml:space="preserve">3.596919298172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61137652397156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.67209696769714</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.63161778450012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.59113788604736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.60848593711853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.55644106864929</t>
+    <t xml:space="preserve">3.59692001342773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61137747764587</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.67209720611572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.63161730766296</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.59113717079163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.60848569869995</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.55644059181213</t>
   </si>
   <si>
     <t xml:space="preserve">3.62294316291809</t>
   </si>
   <si>
-    <t xml:space="preserve">3.61426901817322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.63450860977173</t>
+    <t xml:space="preserve">3.61426830291748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.63450884819031</t>
   </si>
   <si>
     <t xml:space="preserve">3.64607429504395</t>
@@ -482,43 +482,43 @@
     <t xml:space="preserve">3.70390248298645</t>
   </si>
   <si>
-    <t xml:space="preserve">3.69233751296997</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.49572134017944</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.54776644706726</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.54487466812134</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.51306915283203</t>
+    <t xml:space="preserve">3.69233655929565</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.49572038650513</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.54776740074158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.54487562179565</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.51306962966919</t>
   </si>
   <si>
     <t xml:space="preserve">3.53041744232178</t>
   </si>
   <si>
-    <t xml:space="preserve">3.53909230232239</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.51885175704956</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.51017785072327</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.50439524650574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.48993825912476</t>
+    <t xml:space="preserve">3.53909277915955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.51885271072388</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.51017808914185</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.50439453125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.48993754386902</t>
   </si>
   <si>
     <t xml:space="preserve">3.49282956123352</t>
   </si>
   <si>
-    <t xml:space="preserve">3.43500161170959</t>
+    <t xml:space="preserve">3.43500089645386</t>
   </si>
   <si>
     <t xml:space="preserve">3.47837162017822</t>
@@ -527,79 +527,79 @@
     <t xml:space="preserve">3.49861216545105</t>
   </si>
   <si>
-    <t xml:space="preserve">3.449458360672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.5072865486145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.57378888130188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.55354928970337</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.44367551803589</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.4234356880188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.45235013961792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.48415589332581</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.47548079490662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.46391534805298</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.45524144172668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.41186928749084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.37428212165833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.30199551582336</t>
+    <t xml:space="preserve">3.44945812225342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.50728678703308</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.57378911972046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.55355000495911</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.44367527961731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.42343521118164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.45234966278076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.48415470123291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.47548055648804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.46391558647156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.45524120330811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.41187000274658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.37428164482117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.30199599266052</t>
   </si>
   <si>
     <t xml:space="preserve">3.26729917526245</t>
   </si>
   <si>
-    <t xml:space="preserve">3.26151657104492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.25573348999023</t>
+    <t xml:space="preserve">3.26151585578918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.25573372840881</t>
   </si>
   <si>
     <t xml:space="preserve">3.24705910682678</t>
   </si>
   <si>
-    <t xml:space="preserve">3.20368766784668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.33091020584106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.39163041114807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.39452123641968</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.38584733009338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66053223609924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.67498898506165</t>
+    <t xml:space="preserve">3.20368790626526</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.33090972900391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.39162993431091</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.39452052116394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.38584637641907</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66053128242493</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.67498826980591</t>
   </si>
   <si>
     <t xml:space="preserve">3.66631412506104</t>
@@ -608,139 +608,139 @@
     <t xml:space="preserve">3.65764021873474</t>
   </si>
   <si>
-    <t xml:space="preserve">3.70679402351379</t>
+    <t xml:space="preserve">3.70679354667664</t>
   </si>
   <si>
     <t xml:space="preserve">3.66920518875122</t>
   </si>
   <si>
-    <t xml:space="preserve">3.70101141929626</t>
+    <t xml:space="preserve">3.70101165771484</t>
   </si>
   <si>
     <t xml:space="preserve">3.71835994720459</t>
   </si>
   <si>
-    <t xml:space="preserve">3.69522905349731</t>
+    <t xml:space="preserve">3.69522762298584</t>
   </si>
   <si>
     <t xml:space="preserve">3.6431827545166</t>
   </si>
   <si>
-    <t xml:space="preserve">3.56511497497559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.52752637863159</t>
+    <t xml:space="preserve">3.56511569023132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.52752661705017</t>
   </si>
   <si>
     <t xml:space="preserve">3.50150370597839</t>
   </si>
   <si>
-    <t xml:space="preserve">3.52463483810425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.38295602798462</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.36271572113037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.3800642490387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.46969771385193</t>
+    <t xml:space="preserve">3.52463507652283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.38295555114746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.36271619796753</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.38006401062012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.46969842910767</t>
   </si>
   <si>
     <t xml:space="preserve">3.46680665016174</t>
   </si>
   <si>
-    <t xml:space="preserve">3.52174377441406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.62872552871704</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.74438214302063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73281669616699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.72414326667786</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.68655443191528</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.75594878196716</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.72125124931335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.60559463500977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64029145240784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.67787957191467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.69811940193176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61716079711914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.68077158927917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.75884008407593</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77040553092957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64896535873413</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.62005233764648</t>
+    <t xml:space="preserve">3.5217432975769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.62872624397278</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.74438285827637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73281621932983</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.72414183616638</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.68655371665955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.75594854354858</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.72125172615051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.60559439659119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64029121398926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.67787981033325</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.6981201171875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61716055870056</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.6807713508606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.75883913040161</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77040481567383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64896631240845</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.62005209922791</t>
   </si>
   <si>
     <t xml:space="preserve">3.73860001564026</t>
   </si>
   <si>
+    <t xml:space="preserve">3.74727416038513</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71650838851929</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.72881460189819</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.7411208152771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.68574333190918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.69189643859863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.70420241355896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66728281974792</t>
+  </si>
+  <si>
     <t xml:space="preserve">3.74727392196655</t>
   </si>
   <si>
-    <t xml:space="preserve">3.71650838851929</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.72881364822388</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.74112129211426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.68574213981628</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.6918957233429</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.70420169830322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66728281974792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.74727439880371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71343207359314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.68881893157959</t>
+    <t xml:space="preserve">3.7134313583374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.68881869316101</t>
   </si>
   <si>
     <t xml:space="preserve">3.69497227668762</t>
@@ -749,22 +749,22 @@
     <t xml:space="preserve">3.67343592643738</t>
   </si>
   <si>
-    <t xml:space="preserve">3.65805244445801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.72266149520874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.7318913936615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.76880931854248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.75035071372986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.7349681854248</t>
+    <t xml:space="preserve">3.65805339813232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.72266125679016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73189115524292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.76881003379822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.75034999847412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73496842384338</t>
   </si>
   <si>
     <t xml:space="preserve">3.72573781013489</t>
@@ -773,73 +773,73 @@
     <t xml:space="preserve">3.67958903312683</t>
   </si>
   <si>
-    <t xml:space="preserve">3.67036008834839</t>
+    <t xml:space="preserve">3.67035913467407</t>
   </si>
   <si>
     <t xml:space="preserve">3.70727849006653</t>
   </si>
   <si>
-    <t xml:space="preserve">3.83957171440125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85187792778015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87033748626709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.81803512573242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.82726502418518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83034133911133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.86726045608521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.75958013534546</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77188634872437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.82418870925903</t>
+    <t xml:space="preserve">3.83957147598267</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85187864303589</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87033820152283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.81803560256958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.82726526260376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.83034181594849</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.86726069450378</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.75957942008972</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77188682556152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.82418847084045</t>
   </si>
   <si>
     <t xml:space="preserve">3.83341813087463</t>
   </si>
   <si>
-    <t xml:space="preserve">3.78419351577759</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.76573371887207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.75650382041931</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.78111577033997</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.74419665336609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.78726935386658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8457248210907</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.82111144065857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.81188249588013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.81495881080627</t>
+    <t xml:space="preserve">3.78419256210327</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.76573348045349</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.75650334358215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.78111672401428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.74419713020325</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.78726983070374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84572410583496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.82111191749573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.81188201904297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.81495833396912</t>
   </si>
   <si>
     <t xml:space="preserve">3.79034614562988</t>
@@ -848,76 +848,76 @@
     <t xml:space="preserve">3.80572938919067</t>
   </si>
   <si>
-    <t xml:space="preserve">3.77803945541382</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.79957556724548</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85495400428772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.79342293739319</t>
+    <t xml:space="preserve">3.77804017066956</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.7995765209198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8549542427063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.79342341423035</t>
   </si>
   <si>
     <t xml:space="preserve">3.86110782623291</t>
   </si>
   <si>
-    <t xml:space="preserve">3.8734130859375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85803055763245</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8641836643219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84880113601685</t>
+    <t xml:space="preserve">3.87341332435608</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85803079605103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.86418318748474</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.848801612854</t>
   </si>
   <si>
     <t xml:space="preserve">3.77496361732483</t>
   </si>
   <si>
-    <t xml:space="preserve">3.76265645027161</t>
+    <t xml:space="preserve">3.76265668869019</t>
   </si>
   <si>
     <t xml:space="preserve">3.75342702865601</t>
   </si>
   <si>
-    <t xml:space="preserve">3.9164867401123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94417572021484</t>
+    <t xml:space="preserve">3.91648650169373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94417500495911</t>
   </si>
   <si>
     <t xml:space="preserve">3.91956233978271</t>
   </si>
   <si>
-    <t xml:space="preserve">3.90725612640381</t>
+    <t xml:space="preserve">3.90725588798523</t>
   </si>
   <si>
     <t xml:space="preserve">3.89495038986206</t>
   </si>
   <si>
-    <t xml:space="preserve">3.91033315658569</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92263984680176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94109869003296</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95648193359375</t>
+    <t xml:space="preserve">3.91033291816711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92263889312744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94109797477722</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95648145675659</t>
   </si>
   <si>
     <t xml:space="preserve">3.96878790855408</t>
   </si>
   <si>
-    <t xml:space="preserve">3.98109459877014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9626350402832</t>
+    <t xml:space="preserve">3.9810938835144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96263384819031</t>
   </si>
   <si>
     <t xml:space="preserve">3.99339985847473</t>
@@ -926,43 +926,43 @@
     <t xml:space="preserve">4.02416610717773</t>
   </si>
   <si>
-    <t xml:space="preserve">4.02109003067017</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.04877948760986</t>
+    <t xml:space="preserve">4.02108907699585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.04877853393555</t>
   </si>
   <si>
     <t xml:space="preserve">4.13800001144409</t>
   </si>
   <si>
-    <t xml:space="preserve">4.13492298126221</t>
+    <t xml:space="preserve">4.13492250442505</t>
   </si>
   <si>
     <t xml:space="preserve">4.11954069137573</t>
   </si>
   <si>
-    <t xml:space="preserve">4.09185123443604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.10723447799683</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.11646270751953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.09308099746704</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.07585191726685</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.10046577453613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.05124044418335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.05985450744629</t>
+    <t xml:space="preserve">4.09185171127319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.10723352432251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.11646318435669</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.09308195114136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.07585287094116</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.10046672821045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.05124092102051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.05985498428345</t>
   </si>
   <si>
     <t xml:space="preserve">3.93802213668823</t>
@@ -971,19 +971,19 @@
     <t xml:space="preserve">4.04262542724609</t>
   </si>
   <si>
-    <t xml:space="preserve">3.96632647514343</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9601743221283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9774022102356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.01678228378296</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.05001020431519</t>
+    <t xml:space="preserve">3.96632695198059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96017289161682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97740173339844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.01678276062012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.05000925064087</t>
   </si>
   <si>
     <t xml:space="preserve">4.09554243087769</t>
@@ -992,10 +992,10 @@
     <t xml:space="preserve">4.1016960144043</t>
   </si>
   <si>
-    <t xml:space="preserve">4.17184257507324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.15953636169434</t>
+    <t xml:space="preserve">4.17184209823608</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.15953588485718</t>
   </si>
   <si>
     <t xml:space="preserve">4.12630844116211</t>
@@ -1007,40 +1007,40 @@
     <t xml:space="preserve">4.09431219100952</t>
   </si>
   <si>
-    <t xml:space="preserve">4.33182382583618</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.34536123275757</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.31828784942627</t>
+    <t xml:space="preserve">4.3318247795105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.34536075592041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.31828737258911</t>
   </si>
   <si>
     <t xml:space="preserve">4.22475957870483</t>
   </si>
   <si>
-    <t xml:space="preserve">4.25183248519897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.28752088546753</t>
+    <t xml:space="preserve">4.25183296203613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.28752136230469</t>
   </si>
   <si>
     <t xml:space="preserve">4.4007396697998</t>
   </si>
   <si>
-    <t xml:space="preserve">4.5127272605896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.48934507369995</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.56564474105835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.46719312667847</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.40935325622559</t>
+    <t xml:space="preserve">4.51272773742676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.48934602737427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.56564426422119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.46719360351562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.40935373306274</t>
   </si>
   <si>
     <t xml:space="preserve">4.47949981689453</t>
@@ -1049,73 +1049,73 @@
     <t xml:space="preserve">4.54964637756348</t>
   </si>
   <si>
-    <t xml:space="preserve">4.51518774032593</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.54595470428467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.53734016418457</t>
+    <t xml:space="preserve">4.51518821716309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.54595518112183</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.53734064102173</t>
   </si>
   <si>
     <t xml:space="preserve">4.4954981803894</t>
   </si>
   <si>
-    <t xml:space="preserve">4.45857810974121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.44258117675781</t>
+    <t xml:space="preserve">4.45857954025269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.44258165359497</t>
   </si>
   <si>
     <t xml:space="preserve">4.45734882354736</t>
   </si>
   <si>
-    <t xml:space="preserve">4.52626466751099</t>
+    <t xml:space="preserve">4.52626371383667</t>
   </si>
   <si>
     <t xml:space="preserve">4.53487825393677</t>
   </si>
   <si>
-    <t xml:space="preserve">4.56933689117432</t>
+    <t xml:space="preserve">4.5693359375</t>
   </si>
   <si>
     <t xml:space="preserve">4.6456356048584</t>
   </si>
   <si>
-    <t xml:space="preserve">4.64071226119995</t>
+    <t xml:space="preserve">4.64071178436279</t>
   </si>
   <si>
     <t xml:space="preserve">4.67640113830566</t>
   </si>
   <si>
-    <t xml:space="preserve">4.72808837890625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.72070407867432</t>
+    <t xml:space="preserve">4.72808790206909</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.72070455551147</t>
   </si>
   <si>
     <t xml:space="preserve">4.72439622879028</t>
   </si>
   <si>
-    <t xml:space="preserve">4.72193431854248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.75023937225342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.79331159591675</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.76377582550049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.77362108230591</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.84253692626953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.84745836257935</t>
+    <t xml:space="preserve">4.72193384170532</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.75023889541626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.79331111907959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.76377630233765</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.77362155914307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.84253644943237</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.84745931625366</t>
   </si>
   <si>
     <t xml:space="preserve">4.86838006973267</t>
@@ -1127,34 +1127,34 @@
     <t xml:space="preserve">4.90529870986938</t>
   </si>
   <si>
-    <t xml:space="preserve">4.98775148391724</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.97421360015869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.96559953689575</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.01728677749634</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.99390459060669</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.9705228805542</t>
+    <t xml:space="preserve">4.98775100708008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.97421407699585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.96560049057007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.01728582382202</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.99390411376953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.97052192687988</t>
   </si>
   <si>
     <t xml:space="preserve">5.01482486724854</t>
   </si>
   <si>
-    <t xml:space="preserve">5.05666732788086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.86714935302734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.85607290267944</t>
+    <t xml:space="preserve">5.05666589736938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.86714839935303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.85607385635376</t>
   </si>
   <si>
     <t xml:space="preserve">4.68870687484741</t>
@@ -1166,31 +1166,31 @@
     <t xml:space="preserve">4.73670196533203</t>
   </si>
   <si>
-    <t xml:space="preserve">4.71331930160522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.74162435531616</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.66901636123657</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.51888084411621</t>
+    <t xml:space="preserve">4.71332025527954</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.74162483215332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.66901779174805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.51887989044189</t>
   </si>
   <si>
     <t xml:space="preserve">4.31582641601562</t>
   </si>
   <si>
-    <t xml:space="preserve">4.49672889709473</t>
+    <t xml:space="preserve">4.49672842025757</t>
   </si>
   <si>
     <t xml:space="preserve">4.50657415390015</t>
   </si>
   <si>
-    <t xml:space="preserve">4.5964093208313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.62225389480591</t>
+    <t xml:space="preserve">4.59640979766846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.62225341796875</t>
   </si>
   <si>
     <t xml:space="preserve">4.50042104721069</t>
@@ -1199,43 +1199,43 @@
     <t xml:space="preserve">4.49795961380005</t>
   </si>
   <si>
-    <t xml:space="preserve">4.48073196411133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.3588981628418</t>
+    <t xml:space="preserve">4.48073148727417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.35889768600464</t>
   </si>
   <si>
     <t xml:space="preserve">4.52749490737915</t>
   </si>
   <si>
-    <t xml:space="preserve">4.61363935470581</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.70101308822632</t>
+    <t xml:space="preserve">4.61363840103149</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.70101404190063</t>
   </si>
   <si>
     <t xml:space="preserve">4.81177043914795</t>
   </si>
   <si>
-    <t xml:space="preserve">4.69485998153687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.76778984069824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.81597518920898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.83811521530151</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.77820825576782</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.78341865539551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.72090625762939</t>
+    <t xml:space="preserve">4.69486045837402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.76779079437256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.8159761428833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.83811569213867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.77820873260498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.78341913223267</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.72090673446655</t>
   </si>
   <si>
     <t xml:space="preserve">4.74304628372192</t>
@@ -1247,16 +1247,16 @@
     <t xml:space="preserve">4.66881418228149</t>
   </si>
   <si>
-    <t xml:space="preserve">4.71569728851318</t>
+    <t xml:space="preserve">4.71569776535034</t>
   </si>
   <si>
     <t xml:space="preserve">4.72741842269897</t>
   </si>
   <si>
-    <t xml:space="preserve">4.83941793441772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.8771858215332</t>
+    <t xml:space="preserve">4.83941745758057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.87718439102173</t>
   </si>
   <si>
     <t xml:space="preserve">4.92276620864868</t>
@@ -1265,19 +1265,19 @@
     <t xml:space="preserve">4.87067365646362</t>
   </si>
